--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1299,7 +1299,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 26 Aug 2026, 06:03 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 26 Aug 2026, 10:05 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1658,7 +1658,7 @@
         <v>8</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>62.04029454808514</v>
+        <v>62.04029454808516</v>
       </c>
       <c r="H18" s="29" t="n">
         <v>3.850615805296131</v>
@@ -1691,7 +1691,7 @@
         <v>6</v>
       </c>
       <c r="G19" s="35" t="n">
-        <v>61.36674366386454</v>
+        <v>61.36674366386453</v>
       </c>
       <c r="H19" s="36" t="n">
         <v>3.502304616298746</v>
@@ -1724,7 +1724,7 @@
         <v>8</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>53.84806999833309</v>
+        <v>53.84806999833307</v>
       </c>
       <c r="H20" s="29" t="n">
         <v>1.677612020963348</v>
@@ -1757,7 +1757,7 @@
         <v>7</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>55.72403245489501</v>
+        <v>55.72403245489503</v>
       </c>
       <c r="H21" s="36" t="n">
         <v>2.334771339416752</v>
@@ -1790,7 +1790,7 @@
         <v>7</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>51.26009095403064</v>
+        <v>51.26009095403063</v>
       </c>
       <c r="H22" s="29" t="n">
         <v>0.4723917478886008</v>
@@ -1823,7 +1823,7 @@
         <v>3</v>
       </c>
       <c r="G23" s="35" t="n">
-        <v>50.42712796477651</v>
+        <v>50.42712796477652</v>
       </c>
       <c r="H23" s="36" t="n">
         <v>0.8233884627173671</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="L29" s="28" t="n">
-        <v>40.54233000178774</v>
+        <v>40.54233000178775</v>
       </c>
     </row>
     <row r="30">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="L32" s="35" t="n">
-        <v>48.45164047982114</v>
+        <v>48.45164047982113</v>
       </c>
     </row>
     <row r="33">
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="L33" s="28" t="n">
-        <v>34.35141804178001</v>
+        <v>34.35141804178002</v>
       </c>
     </row>
     <row r="34">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="F35" s="28" t="n">
-        <v>62.04029454808514</v>
+        <v>62.04029454808516</v>
       </c>
       <c r="H35" s="24" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="L35" s="28" t="n">
-        <v>46.48159720235044</v>
+        <v>46.48159720235043</v>
       </c>
     </row>
     <row r="36">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="F36" s="35" t="n">
-        <v>53.84806999833309</v>
+        <v>53.84806999833307</v>
       </c>
       <c r="H36" s="31" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="L36" s="35" t="n">
-        <v>44.17580057127281</v>
+        <v>44.1758005712728</v>
       </c>
     </row>
     <row r="37">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="L37" s="28" t="n">
-        <v>49.32754022394879</v>
+        <v>49.32754022394877</v>
       </c>
     </row>
     <row r="38">
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="L38" s="35" t="n">
-        <v>41.64475577348347</v>
+        <v>41.64475577348348</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="L43" s="28" t="n">
-        <v>46.48159720235044</v>
+        <v>46.48159720235043</v>
       </c>
     </row>
     <row r="44">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="L44" s="35" t="n">
-        <v>48.45164047982114</v>
+        <v>48.45164047982113</v>
       </c>
     </row>
     <row r="45">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="L45" s="28" t="n">
-        <v>40.54233000178774</v>
+        <v>40.54233000178775</v>
       </c>
     </row>
     <row r="46">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="L46" s="35" t="n">
-        <v>65.91918115103154</v>
+        <v>65.91918115103152</v>
       </c>
     </row>
     <row r="47">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="L47" s="28" t="n">
-        <v>46.29461603460204</v>
+        <v>46.29461603460202</v>
       </c>
     </row>
     <row r="48">
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="L49" s="28" t="n">
-        <v>44.17580057127281</v>
+        <v>44.1758005712728</v>
       </c>
     </row>
     <row r="50">
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="F51" s="28" t="n">
-        <v>38.68957529046556</v>
+        <v>38.68957529046554</v>
       </c>
       <c r="H51" s="24" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="F52" s="35" t="n">
-        <v>41.64475577348347</v>
+        <v>41.64475577348348</v>
       </c>
       <c r="H52" s="31" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 26 Aug 2026, 06:03 PM · Yahoo Finance data</t>
+          <t>Built 26 Aug 2026, 10:05 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -3632,13 +3632,13 @@
         <v>16.4526082570781</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>-0.4138516997481361</v>
+        <v>-0.4138516997480792</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>0.3970533948307476</v>
+        <v>0.3970533948307661</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-0.8109050945788836</v>
+        <v>-0.8109050945788453</v>
       </c>
       <c r="AE7" s="72" t="n">
         <v>180.9187612216489</v>
@@ -3671,7 +3671,7 @@
         <v>6.454309765571018</v>
       </c>
       <c r="AO7" s="77" t="n">
-        <v>1.39292521015973</v>
+        <v>1.392925210159729</v>
       </c>
       <c r="AP7" s="72" t="n">
         <v>188.1900024414062</v>
@@ -3825,10 +3825,10 @@
         <v>3.493614207117389</v>
       </c>
       <c r="AC8" s="86" t="n">
-        <v>3.077248830849709</v>
+        <v>3.077248830849713</v>
       </c>
       <c r="AD8" s="86" t="n">
-        <v>0.41636537626768</v>
+        <v>0.4163653762676764</v>
       </c>
       <c r="AE8" s="83" t="n">
         <v>172.8232855505502</v>
@@ -4003,28 +4003,28 @@
         <v>0.7032712234993728</v>
       </c>
       <c r="Y9" s="28" t="n">
-        <v>61.36674366386454</v>
+        <v>61.36674366386453</v>
       </c>
       <c r="Z9" s="28" t="n">
         <v>91.83655463057153</v>
       </c>
       <c r="AA9" s="28" t="n">
-        <v>25.79843227400332</v>
+        <v>25.79843227400331</v>
       </c>
       <c r="AB9" s="75" t="n">
         <v>0.4969865847179022</v>
       </c>
       <c r="AC9" s="75" t="n">
-        <v>0.5618788641829781</v>
+        <v>0.5618788641829783</v>
       </c>
       <c r="AD9" s="75" t="n">
-        <v>-0.06489227946507581</v>
+        <v>-0.06489227946507603</v>
       </c>
       <c r="AE9" s="72" t="n">
         <v>57.9280479541618</v>
       </c>
       <c r="AF9" s="72" t="n">
-        <v>57.53039955810175</v>
+        <v>57.53039955810173</v>
       </c>
       <c r="AG9" s="72" t="n">
         <v>56.28860008239746</v>
@@ -4051,7 +4051,7 @@
         <v>2.913392015548033</v>
       </c>
       <c r="AO9" s="77" t="n">
-        <v>1.06176028383828</v>
+        <v>1.061760283838279</v>
       </c>
       <c r="AP9" s="72" t="n">
         <v>58.40999984741211</v>
@@ -4199,22 +4199,22 @@
         <v>70.09225641211214</v>
       </c>
       <c r="AA10" s="35" t="n">
-        <v>27.34330835731434</v>
+        <v>27.34330835731433</v>
       </c>
       <c r="AB10" s="86" t="n">
-        <v>1.445584747339318</v>
+        <v>1.445584747339346</v>
       </c>
       <c r="AC10" s="86" t="n">
-        <v>1.429644280853887</v>
+        <v>1.42964428085391</v>
       </c>
       <c r="AD10" s="86" t="n">
-        <v>0.01594046648543035</v>
+        <v>0.01594046648543568</v>
       </c>
       <c r="AE10" s="83" t="n">
         <v>62.549695529112</v>
       </c>
       <c r="AF10" s="83" t="n">
-        <v>61.16086208606473</v>
+        <v>61.16086208606474</v>
       </c>
       <c r="AG10" s="83" t="n">
         <v>57.85300033569336</v>
@@ -4241,7 +4241,7 @@
         <v>14.01327947293425</v>
       </c>
       <c r="AO10" s="88" t="n">
-        <v>1.936150951015983</v>
+        <v>1.936150951015984</v>
       </c>
       <c r="AP10" s="83" t="n">
         <v>64.69999694824219</v>
@@ -4383,25 +4383,25 @@
         <v>0.7597386255355429</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>53.84806999833309</v>
+        <v>53.84806999833307</v>
       </c>
       <c r="Z11" s="28" t="n">
         <v>65.31777759647548</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>17.45653049212892</v>
+        <v>17.4565304921289</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.4420399160984232</v>
+        <v>0.442039916098409</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.3544100448925548</v>
+        <v>0.3544100448925464</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>0.0876298712058684</v>
+        <v>0.08762987120586258</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>86.17865261585126</v>
+        <v>86.17865261585129</v>
       </c>
       <c r="AF11" s="72" t="n">
         <v>85.6865789591929</v>
@@ -4573,7 +4573,7 @@
         <v>0.5329376429742044</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>50.42712796477651</v>
+        <v>50.42712796477652</v>
       </c>
       <c r="Z12" s="35" t="n">
         <v>24.94286686976789</v>
@@ -4582,13 +4582,13 @@
         <v>15.64060422898862</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.5154321191799198</v>
+        <v>0.5154321191798914</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.5984382989982735</v>
+        <v>0.5984382989982509</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.08300617981835368</v>
+        <v>-0.08300617981835945</v>
       </c>
       <c r="AE12" s="83" t="n">
         <v>117.6672952764053</v>
@@ -4763,7 +4763,7 @@
         <v>0.7902139645142569</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>55.72403245489501</v>
+        <v>55.72403245489503</v>
       </c>
       <c r="Z13" s="28" t="n">
         <v>66.62578938401367</v>
@@ -4772,13 +4772,13 @@
         <v>12.27988756693516</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.5700338760275372</v>
+        <v>0.5700338760275514</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.3967881469793335</v>
+        <v>0.3967881469793474</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>0.1732457290482037</v>
+        <v>0.173245729048204</v>
       </c>
       <c r="AE13" s="72" t="n">
         <v>111.9884143324007</v>
@@ -4811,7 +4811,7 @@
         <v>5.410347929161659</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.496313782302052</v>
+        <v>1.496313782302051</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -4953,7 +4953,7 @@
         <v>0.6373686096740276</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>62.04029454808514</v>
+        <v>62.04029454808516</v>
       </c>
       <c r="Z14" s="35" t="n">
         <v>78.68849383472659</v>
@@ -4962,19 +4962,19 @@
         <v>14.33128316618643</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.5386345755857462</v>
+        <v>0.5386345755857604</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.4354214055087228</v>
+        <v>0.4354214055087293</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>0.1032131700770235</v>
+        <v>0.1032131700770311</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>53.14641220471837</v>
+        <v>53.14641220471838</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.54297436056718</v>
+        <v>52.54297436056719</v>
       </c>
       <c r="AG14" s="83" t="n">
         <v>51.67999992370606</v>
@@ -4995,10 +4995,10 @@
         <v>50.81229886626581</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.8483841080251376</v>
+        <v>0.8483841080251392</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>6.416432840738438</v>
+        <v>6.416432840738411</v>
       </c>
       <c r="AO14" s="88" t="n">
         <v>1.558331777154998</v>
@@ -5149,19 +5149,19 @@
         <v>31.09041988246123</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>14.99702773641917</v>
+        <v>14.99702773641918</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.4700564206462161</v>
+        <v>0.4700564206461877</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>1.111396078500238</v>
+        <v>1.111396078500189</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.6413396578540216</v>
+        <v>-0.6413396578540016</v>
       </c>
       <c r="AE15" s="72" t="n">
-        <v>183.3955257248659</v>
+        <v>183.3955257248658</v>
       </c>
       <c r="AF15" s="72" t="n">
         <v>183.4876617315641</v>
@@ -5333,22 +5333,22 @@
         <v>0.6429532113855079</v>
       </c>
       <c r="Y16" s="35" t="n">
-        <v>51.26009095403064</v>
+        <v>51.26009095403063</v>
       </c>
       <c r="Z16" s="35" t="n">
         <v>74.2268365581249</v>
       </c>
       <c r="AA16" s="35" t="n">
-        <v>8.716528246003152</v>
+        <v>8.716528246003158</v>
       </c>
       <c r="AB16" s="86" t="n">
-        <v>0.05686250986147456</v>
+        <v>0.05686250986146035</v>
       </c>
       <c r="AC16" s="86" t="n">
-        <v>0.02838774247306352</v>
+        <v>0.02838774247305886</v>
       </c>
       <c r="AD16" s="86" t="n">
-        <v>0.02847476738841104</v>
+        <v>0.0284747673884015</v>
       </c>
       <c r="AE16" s="83" t="n">
         <v>45.10375662193221</v>
@@ -5529,22 +5529,22 @@
         <v>41.53832008623169</v>
       </c>
       <c r="AA17" s="28" t="n">
-        <v>12.50429004089615</v>
+        <v>12.50429004089614</v>
       </c>
       <c r="AB17" s="75" t="n">
         <v>-0.3990657580782866</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.3757725423320826</v>
+        <v>-0.3757725423320815</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.02329321574620397</v>
+        <v>-0.02329321574620513</v>
       </c>
       <c r="AE17" s="72" t="n">
         <v>43.52576986755673</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>43.92757694504953</v>
+        <v>43.92757694504954</v>
       </c>
       <c r="AG17" s="72" t="n">
         <v>44.75960014343261</v>
@@ -5732,7 +5732,7 @@
         <v>0.6402208114922574</v>
       </c>
       <c r="Y19" s="28" t="n">
-        <v>54.34691558526233</v>
+        <v>54.34691558526234</v>
       </c>
       <c r="Z19" s="28" t="n">
         <v>23.31237783295473</v>
@@ -5741,19 +5741,19 @@
         <v>15.57658565363274</v>
       </c>
       <c r="AB19" s="75" t="n">
-        <v>4.17637838017265</v>
+        <v>4.176378380172764</v>
       </c>
       <c r="AC19" s="75" t="n">
-        <v>5.554428549438741</v>
+        <v>5.554428549438956</v>
       </c>
       <c r="AD19" s="75" t="n">
-        <v>-1.378050169266091</v>
+        <v>-1.378050169266192</v>
       </c>
       <c r="AE19" s="72" t="n">
-        <v>766.5448307273668</v>
+        <v>766.5448307273671</v>
       </c>
       <c r="AF19" s="72" t="n">
-        <v>763.7926810682034</v>
+        <v>763.7926810682033</v>
       </c>
       <c r="AG19" s="72" t="n">
         <v>752.9720031738282</v>
@@ -5780,7 +5780,7 @@
         <v>4.591420818066163</v>
       </c>
       <c r="AO19" s="77" t="n">
-        <v>0.8184882699237064</v>
+        <v>0.8184882699237067</v>
       </c>
       <c r="AP19" s="72" t="n">
         <v>779.3699951171875</v>
@@ -5920,7 +5920,7 @@
         <v>0.5147073924065079</v>
       </c>
       <c r="Y20" s="35" t="n">
-        <v>49.32754022394879</v>
+        <v>49.32754022394877</v>
       </c>
       <c r="Z20" s="35" t="n">
         <v>27.1956762303713</v>
@@ -5929,13 +5929,13 @@
         <v>14.60118008594105</v>
       </c>
       <c r="AB20" s="86" t="n">
-        <v>1.390211938533412</v>
+        <v>1.390211938533525</v>
       </c>
       <c r="AC20" s="86" t="n">
-        <v>2.582433749822338</v>
+        <v>2.582433749822537</v>
       </c>
       <c r="AD20" s="86" t="n">
-        <v>-1.192221811288926</v>
+        <v>-1.192221811289012</v>
       </c>
       <c r="AE20" s="83" t="n">
         <v>713.4389344615754</v>
@@ -6120,16 +6120,16 @@
         <v>1.128592498110777</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>1.653755684578091</v>
+        <v>1.653755684578136</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.5251631864673136</v>
+        <v>-0.5251631864673589</v>
       </c>
       <c r="AE21" s="72" t="n">
         <v>299.642956869981</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>299.0518935657001</v>
+        <v>299.0518935657</v>
       </c>
       <c r="AG21" s="72" t="n">
         <v>297.0416003417969</v>
@@ -6156,7 +6156,7 @@
         <v>4.528134641701535</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.109134554788116</v>
+        <v>1.109134554788115</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -6296,7 +6296,7 @@
         <v>0.5190593233390074</v>
       </c>
       <c r="Y22" s="35" t="n">
-        <v>41.64475577348347</v>
+        <v>41.64475577348348</v>
       </c>
       <c r="Z22" s="35" t="n">
         <v>20.81696554456229</v>
@@ -6305,13 +6305,13 @@
         <v>19.56899162932239</v>
       </c>
       <c r="AB22" s="86" t="n">
-        <v>-10.39753700379759</v>
+        <v>-10.39753700379765</v>
       </c>
       <c r="AC22" s="86" t="n">
-        <v>-10.38487131395094</v>
+        <v>-10.38487131395102</v>
       </c>
       <c r="AD22" s="86" t="n">
-        <v>-0.01266568984665284</v>
+        <v>-0.01266568984663508</v>
       </c>
       <c r="AE22" s="83" t="n">
         <v>121.6907553341597</v>
@@ -6335,13 +6335,13 @@
         <v>128.6890003204346</v>
       </c>
       <c r="AL22" s="83" t="n">
-        <v>104.7003052519382</v>
+        <v>104.7003052519383</v>
       </c>
       <c r="AM22" s="87" t="n">
-        <v>0.2480271058555912</v>
+        <v>0.2480271058555904</v>
       </c>
       <c r="AN22" s="36" t="n">
-        <v>37.28165578839634</v>
+        <v>37.28165578839626</v>
       </c>
       <c r="AO22" s="88" t="n">
         <v>14.37755198854149</v>
@@ -6517,16 +6517,16 @@
         <v>-1.100666433354547</v>
       </c>
       <c r="AC24" s="75" t="n">
-        <v>-1.252388921609016</v>
+        <v>-1.252388921609029</v>
       </c>
       <c r="AD24" s="75" t="n">
-        <v>0.1517224882544683</v>
+        <v>0.1517224882544821</v>
       </c>
       <c r="AE24" s="72" t="n">
         <v>310.8529456398178</v>
       </c>
       <c r="AF24" s="72" t="n">
-        <v>311.9279805713444</v>
+        <v>311.9279805713443</v>
       </c>
       <c r="AG24" s="72" t="n">
         <v>311.2181994628907</v>
@@ -6538,19 +6538,19 @@
         <v>282.1202494812012</v>
       </c>
       <c r="AJ24" s="72" t="n">
-        <v>323.0593527107619</v>
+        <v>323.059352710762</v>
       </c>
       <c r="AK24" s="72" t="n">
         <v>310.2639999389648</v>
       </c>
       <c r="AL24" s="72" t="n">
-        <v>297.4686471671678</v>
+        <v>297.4686471671677</v>
       </c>
       <c r="AM24" s="76" t="n">
-        <v>0.6244988053431738</v>
+        <v>0.6244988053431733</v>
       </c>
       <c r="AN24" s="29" t="n">
-        <v>8.248042166873484</v>
+        <v>8.248042166873521</v>
       </c>
       <c r="AO24" s="77" t="n">
         <v>2.293538363535856</v>
@@ -6693,28 +6693,28 @@
         <v>0.5752682165795007</v>
       </c>
       <c r="Y25" s="35" t="n">
-        <v>48.42793339577184</v>
+        <v>48.42793339577185</v>
       </c>
       <c r="Z25" s="35" t="n">
         <v>45.1092745874721</v>
       </c>
       <c r="AA25" s="35" t="n">
-        <v>9.652036221327275</v>
+        <v>9.652036221327274</v>
       </c>
       <c r="AB25" s="86" t="n">
-        <v>-7.696982234293728</v>
+        <v>-7.696982234293841</v>
       </c>
       <c r="AC25" s="86" t="n">
-        <v>-7.594999867318916</v>
+        <v>-7.59499986731895</v>
       </c>
       <c r="AD25" s="86" t="n">
-        <v>-0.1019823669748119</v>
+        <v>-0.1019823669748918</v>
       </c>
       <c r="AE25" s="83" t="n">
         <v>477.0152836850392</v>
       </c>
       <c r="AF25" s="83" t="n">
-        <v>484.6191100665501</v>
+        <v>484.61911006655</v>
       </c>
       <c r="AG25" s="83" t="n">
         <v>507.6258001708985</v>
@@ -6741,7 +6741,7 @@
         <v>12.27681789522737</v>
       </c>
       <c r="AO25" s="88" t="n">
-        <v>5.599959013488063</v>
+        <v>5.599959013488064</v>
       </c>
       <c r="AP25" s="83" t="n">
         <v>584.72998046875</v>
@@ -6890,13 +6890,13 @@
         <v>20.42527419062405</v>
       </c>
       <c r="AB26" s="75" t="n">
-        <v>2.434823475025041</v>
+        <v>2.434823475024984</v>
       </c>
       <c r="AC26" s="75" t="n">
-        <v>3.899599920725663</v>
+        <v>3.899599920725618</v>
       </c>
       <c r="AD26" s="75" t="n">
-        <v>-1.464776445700622</v>
+        <v>-1.464776445700633</v>
       </c>
       <c r="AE26" s="72" t="n">
         <v>261.709693532038</v>
@@ -7078,13 +7078,13 @@
         <v>23.82615946065637</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.327864220405758</v>
+        <v>2.327864220405743</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>1.630770778063491</v>
+        <v>1.630770778063477</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.697093442342267</v>
+        <v>0.6970934423422659</v>
       </c>
       <c r="AE27" s="83" t="n">
         <v>84.02987347099715</v>
@@ -7117,7 +7117,7 @@
         <v>21.65990006558451</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.771382612320362</v>
+        <v>2.771382612320363</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -7263,22 +7263,22 @@
         <v>26.92628453457984</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>10.85663935716729</v>
+        <v>10.85663935716728</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-10.62039291948079</v>
+        <v>-10.62039291948088</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-9.946621094123326</v>
+        <v>-9.946621094123369</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-0.6737718253574663</v>
+        <v>-0.6737718253575089</v>
       </c>
       <c r="AE28" s="72" t="n">
         <v>250.7147036320347</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>261.2002220859253</v>
+        <v>261.2002220859254</v>
       </c>
       <c r="AG28" s="72" t="n">
         <v>294.2797988891601</v>
@@ -7296,13 +7296,13 @@
         <v>260.5474983215332</v>
       </c>
       <c r="AL28" s="72" t="n">
-        <v>227.1595892578675</v>
+        <v>227.1595892578674</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.3579201119655586</v>
+        <v>0.3579201119655589</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>25.62903829724195</v>
+        <v>25.62903829724196</v>
       </c>
       <c r="AO28" s="77" t="n">
         <v>7.564505554407311</v>
@@ -7445,7 +7445,7 @@
         <v>0.6381101094516113</v>
       </c>
       <c r="Y29" s="35" t="n">
-        <v>40.54233000178774</v>
+        <v>40.54233000178775</v>
       </c>
       <c r="Z29" s="35" t="n">
         <v>2.875403955682241</v>
@@ -7457,10 +7457,10 @@
         <v>-1.424470110540113</v>
       </c>
       <c r="AC29" s="86" t="n">
-        <v>-0.8205604386820264</v>
+        <v>-0.8205604386820315</v>
       </c>
       <c r="AD29" s="86" t="n">
-        <v>-0.603909671858087</v>
+        <v>-0.6039096718580819</v>
       </c>
       <c r="AE29" s="83" t="n">
         <v>64.46951888569396</v>
@@ -7478,19 +7478,19 @@
         <v>81.54682483673096</v>
       </c>
       <c r="AJ29" s="83" t="n">
-        <v>76.12762692622535</v>
+        <v>76.12762692622536</v>
       </c>
       <c r="AK29" s="83" t="n">
         <v>66.93599948883056</v>
       </c>
       <c r="AL29" s="83" t="n">
-        <v>57.74437205143578</v>
+        <v>57.74437205143576</v>
       </c>
       <c r="AM29" s="87" t="n">
-        <v>0.1161725184808387</v>
+        <v>0.1161725184808393</v>
       </c>
       <c r="AN29" s="36" t="n">
-        <v>27.46392825262457</v>
+        <v>27.46392825262461</v>
       </c>
       <c r="AO29" s="88" t="n">
         <v>8.387129548640001</v>
@@ -7633,28 +7633,28 @@
         <v>0.9426288138598523</v>
       </c>
       <c r="Y30" s="28" t="n">
-        <v>34.35141804178001</v>
+        <v>34.35141804178002</v>
       </c>
       <c r="Z30" s="28" t="n">
         <v>6.677944312990866</v>
       </c>
       <c r="AA30" s="28" t="n">
-        <v>22.49327899195314</v>
+        <v>22.49327899195313</v>
       </c>
       <c r="AB30" s="75" t="n">
-        <v>-9.40189610337967</v>
+        <v>-9.401896103379613</v>
       </c>
       <c r="AC30" s="75" t="n">
-        <v>-3.408294639600133</v>
+        <v>-3.4082946396001</v>
       </c>
       <c r="AD30" s="75" t="n">
-        <v>-5.993601463779537</v>
+        <v>-5.993601463779513</v>
       </c>
       <c r="AE30" s="72" t="n">
-        <v>368.5421325436394</v>
+        <v>368.5421325436395</v>
       </c>
       <c r="AF30" s="72" t="n">
-        <v>382.634987832344</v>
+        <v>382.6349878323441</v>
       </c>
       <c r="AG30" s="72" t="n">
         <v>386.6929998779297</v>
@@ -7681,7 +7681,7 @@
         <v>25.20142695210253</v>
       </c>
       <c r="AO30" s="77" t="n">
-        <v>3.941467805417561</v>
+        <v>3.94146780541756</v>
       </c>
       <c r="AP30" s="72" t="n">
         <v>495</v>
@@ -7827,22 +7827,22 @@
         <v>76.29040864220558</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>19.8195404335193</v>
+        <v>19.81954043351929</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>2.744569682550917</v>
+        <v>2.744569682550903</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.379914361510529</v>
+        <v>1.379914361510517</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>1.364655321040389</v>
+        <v>1.364655321040386</v>
       </c>
       <c r="AE31" s="83" t="n">
         <v>102.198267376567</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>98.30292641006179</v>
+        <v>98.3029264100618</v>
       </c>
       <c r="AG31" s="83" t="n">
         <v>96.33679977416992</v>
@@ -7860,13 +7860,13 @@
         <v>97.02699966430664</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>86.47836335829409</v>
+        <v>86.4783633582941</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.9897789935252235</v>
+        <v>0.9897789935252241</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>21.74371328085719</v>
+        <v>21.74371328085716</v>
       </c>
       <c r="AO31" s="88" t="n">
         <v>3.786628282885747</v>
@@ -8021,16 +8021,16 @@
         <v>0.9779232576620132</v>
       </c>
       <c r="AC32" s="75" t="n">
-        <v>1.832786692668555</v>
+        <v>1.832786692668541</v>
       </c>
       <c r="AD32" s="75" t="n">
-        <v>-0.8548634350065418</v>
+        <v>-0.8548634350065283</v>
       </c>
       <c r="AE32" s="72" t="n">
-        <v>90.20161934578603</v>
+        <v>90.20161934578604</v>
       </c>
       <c r="AF32" s="72" t="n">
-        <v>89.85069441235657</v>
+        <v>89.85069441235659</v>
       </c>
       <c r="AG32" s="72" t="n">
         <v>89.10180023193359</v>
@@ -8048,16 +8048,16 @@
         <v>90.84800071716309</v>
       </c>
       <c r="AL32" s="72" t="n">
-        <v>72.24514217961124</v>
+        <v>72.24514217961126</v>
       </c>
       <c r="AM32" s="76" t="n">
-        <v>0.4237214384229225</v>
+        <v>0.4237214384229224</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>40.9538094194678</v>
+        <v>40.95380941946773</v>
       </c>
       <c r="AO32" s="77" t="n">
-        <v>8.216041999608047</v>
+        <v>8.216041999608043</v>
       </c>
       <c r="AP32" s="72" t="n">
         <v>153.1999969482422</v>
@@ -8206,13 +8206,13 @@
         <v>10.06418765773691</v>
       </c>
       <c r="AB33" s="86" t="n">
-        <v>8.273838928041414</v>
+        <v>8.273838928041471</v>
       </c>
       <c r="AC33" s="86" t="n">
-        <v>11.25363610598318</v>
+        <v>11.2536361059833</v>
       </c>
       <c r="AD33" s="86" t="n">
-        <v>-2.979797177941762</v>
+        <v>-2.97979717794183</v>
       </c>
       <c r="AE33" s="83" t="n">
         <v>452.6444618190594</v>
@@ -8245,7 +8245,7 @@
         <v>21.81936249173543</v>
       </c>
       <c r="AO33" s="88" t="n">
-        <v>6.245747943327794</v>
+        <v>6.245747943327797</v>
       </c>
       <c r="AP33" s="83" t="n">
         <v>514</v>
@@ -8385,28 +8385,28 @@
         <v>0.926428159871308</v>
       </c>
       <c r="Y34" s="28" t="n">
-        <v>44.17580057127281</v>
+        <v>44.1758005712728</v>
       </c>
       <c r="Z34" s="28" t="n">
         <v>13.70437880667276</v>
       </c>
       <c r="AA34" s="28" t="n">
-        <v>8.331268527853542</v>
+        <v>8.331268527853545</v>
       </c>
       <c r="AB34" s="75" t="n">
-        <v>-2.547841759808023</v>
+        <v>-2.547841759808136</v>
       </c>
       <c r="AC34" s="75" t="n">
-        <v>-2.152851631934006</v>
+        <v>-2.152851631934081</v>
       </c>
       <c r="AD34" s="75" t="n">
-        <v>-0.3949901278740171</v>
+        <v>-0.3949901278740553</v>
       </c>
       <c r="AE34" s="72" t="n">
         <v>342.2739152012462</v>
       </c>
       <c r="AF34" s="72" t="n">
-        <v>344.9694406435615</v>
+        <v>344.9694406435616</v>
       </c>
       <c r="AG34" s="72" t="n">
         <v>349.0611999511719</v>
@@ -8418,7 +8418,7 @@
         <v>332.9585993957519</v>
       </c>
       <c r="AJ34" s="72" t="n">
-        <v>370.3525147381513</v>
+        <v>370.3525147381512</v>
       </c>
       <c r="AK34" s="72" t="n">
         <v>348.4235015869141</v>
@@ -8427,10 +8427,10 @@
         <v>326.4944884356769</v>
       </c>
       <c r="AM34" s="76" t="n">
-        <v>0.2874164373221591</v>
+        <v>0.2874164373221586</v>
       </c>
       <c r="AN34" s="29" t="n">
-        <v>12.58756257907994</v>
+        <v>12.58756257907991</v>
       </c>
       <c r="AO34" s="77" t="n">
         <v>2.499746159581853</v>
@@ -8573,7 +8573,7 @@
         <v>0.8307516594584379</v>
       </c>
       <c r="Y35" s="35" t="n">
-        <v>46.48159720235044</v>
+        <v>46.48159720235043</v>
       </c>
       <c r="Z35" s="35" t="n">
         <v>19.18386356064453</v>
@@ -8582,16 +8582,16 @@
         <v>14.29327626637358</v>
       </c>
       <c r="AB35" s="86" t="n">
-        <v>-0.01071277422492045</v>
+        <v>-0.01071277422493466</v>
       </c>
       <c r="AC35" s="86" t="n">
-        <v>-0.08707334493374719</v>
+        <v>-0.08707334493376138</v>
       </c>
       <c r="AD35" s="86" t="n">
-        <v>0.07636057070882674</v>
+        <v>0.07636057070882672</v>
       </c>
       <c r="AE35" s="83" t="n">
-        <v>41.37106753000089</v>
+        <v>41.37106753000088</v>
       </c>
       <c r="AF35" s="83" t="n">
         <v>41.23021329233674</v>
@@ -8606,7 +8606,7 @@
         <v>46.17115005493164</v>
       </c>
       <c r="AJ35" s="83" t="n">
-        <v>45.62498442709825</v>
+        <v>45.62498442709824</v>
       </c>
       <c r="AK35" s="83" t="n">
         <v>41.02549991607666</v>
@@ -8615,10 +8615,10 @@
         <v>36.42601540505508</v>
       </c>
       <c r="AM35" s="87" t="n">
-        <v>0.3428630337206075</v>
+        <v>0.3428630337206073</v>
       </c>
       <c r="AN35" s="36" t="n">
-        <v>22.42256411466268</v>
+        <v>22.42256411466265</v>
       </c>
       <c r="AO35" s="88" t="n">
         <v>9.25447107305177</v>
@@ -8761,28 +8761,28 @@
         <v>0.6863140381203934</v>
       </c>
       <c r="Y36" s="28" t="n">
-        <v>38.68957529046556</v>
+        <v>38.68957529046554</v>
       </c>
       <c r="Z36" s="28" t="n">
         <v>13.82076875587808</v>
       </c>
       <c r="AA36" s="28" t="n">
-        <v>16.7575027550535</v>
+        <v>16.75750275505351</v>
       </c>
       <c r="AB36" s="75" t="n">
         <v>-3.706662888506159</v>
       </c>
       <c r="AC36" s="75" t="n">
-        <v>-2.960170434203456</v>
+        <v>-2.960170434203442</v>
       </c>
       <c r="AD36" s="75" t="n">
-        <v>-0.7464924543027025</v>
+        <v>-0.7464924543027172</v>
       </c>
       <c r="AE36" s="72" t="n">
         <v>91.39019820156382</v>
       </c>
       <c r="AF36" s="72" t="n">
-        <v>95.48859186050019</v>
+        <v>95.48859186050018</v>
       </c>
       <c r="AG36" s="72" t="n">
         <v>106.0531997680664</v>
@@ -8955,22 +8955,22 @@
         <v>52.54239550562173</v>
       </c>
       <c r="AA37" s="35" t="n">
-        <v>34.6042364248401</v>
+        <v>34.60423642484008</v>
       </c>
       <c r="AB37" s="86" t="n">
         <v>17.89620979438286</v>
       </c>
       <c r="AC37" s="86" t="n">
-        <v>20.82104785980603</v>
+        <v>20.82104785980598</v>
       </c>
       <c r="AD37" s="86" t="n">
-        <v>-2.924838065423177</v>
+        <v>-2.924838065423128</v>
       </c>
       <c r="AE37" s="83" t="n">
         <v>488.8647252362495</v>
       </c>
       <c r="AF37" s="83" t="n">
-        <v>474.3679512580783</v>
+        <v>474.3679512580784</v>
       </c>
       <c r="AG37" s="83" t="n">
         <v>425.7355975341797</v>
@@ -8988,13 +8988,13 @@
         <v>488.2119964599609</v>
       </c>
       <c r="AL37" s="83" t="n">
-        <v>462.8877404413858</v>
+        <v>462.8877404413857</v>
       </c>
       <c r="AM37" s="87" t="n">
-        <v>0.6610708455016947</v>
+        <v>0.661070845501695</v>
       </c>
       <c r="AN37" s="36" t="n">
-        <v>10.37428666325369</v>
+        <v>10.3742866632537</v>
       </c>
       <c r="AO37" s="88" t="n">
         <v>2.351232448660088</v>
@@ -9137,22 +9137,22 @@
         <v>0.7205462878538916</v>
       </c>
       <c r="Y38" s="28" t="n">
-        <v>65.91918115103154</v>
+        <v>65.91918115103152</v>
       </c>
       <c r="Z38" s="28" t="n">
         <v>85.21221841474447</v>
       </c>
       <c r="AA38" s="28" t="n">
-        <v>22.73023991586635</v>
+        <v>22.73023991586636</v>
       </c>
       <c r="AB38" s="75" t="n">
-        <v>5.488110376914776</v>
+        <v>5.48811037691479</v>
       </c>
       <c r="AC38" s="75" t="n">
-        <v>1.76785608733239</v>
+        <v>1.767856087332385</v>
       </c>
       <c r="AD38" s="75" t="n">
-        <v>3.720254289582386</v>
+        <v>3.720254289582405</v>
       </c>
       <c r="AE38" s="72" t="n">
         <v>115.1108736796374</v>
@@ -9176,13 +9176,13 @@
         <v>102.7944999694824</v>
       </c>
       <c r="AL38" s="72" t="n">
-        <v>80.80444572390086</v>
+        <v>80.8044457239008</v>
       </c>
       <c r="AM38" s="76" t="n">
-        <v>0.9637437962669392</v>
+        <v>0.963743796266938</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>42.78449576992924</v>
+        <v>42.78449576992935</v>
       </c>
       <c r="AO38" s="77" t="n">
         <v>5.733495272265694</v>
@@ -9331,16 +9331,16 @@
         <v>48.96873506071326</v>
       </c>
       <c r="AA39" s="35" t="n">
-        <v>11.31473278314212</v>
+        <v>11.31473278314213</v>
       </c>
       <c r="AB39" s="86" t="n">
         <v>7.697148649104179</v>
       </c>
       <c r="AC39" s="86" t="n">
-        <v>3.607901867749354</v>
+        <v>3.607901867749257</v>
       </c>
       <c r="AD39" s="86" t="n">
-        <v>4.089246781354825</v>
+        <v>4.089246781354921</v>
       </c>
       <c r="AE39" s="83" t="n">
         <v>938.8806723932449</v>
@@ -9364,16 +9364,16 @@
         <v>912.3459991455078</v>
       </c>
       <c r="AL39" s="83" t="n">
-        <v>814.4951354715624</v>
+        <v>814.4951354715625</v>
       </c>
       <c r="AM39" s="87" t="n">
-        <v>0.6331312994608349</v>
+        <v>0.6331312994608351</v>
       </c>
       <c r="AN39" s="36" t="n">
-        <v>21.45038478068436</v>
+        <v>21.45038478068434</v>
       </c>
       <c r="AO39" s="88" t="n">
-        <v>6.631064296731617</v>
+        <v>6.631064296731616</v>
       </c>
       <c r="AP39" s="83" t="n">
         <v>1255</v>
@@ -9513,7 +9513,7 @@
         <v>0.344567590657927</v>
       </c>
       <c r="Y40" s="28" t="n">
-        <v>48.45164047982114</v>
+        <v>48.45164047982113</v>
       </c>
       <c r="Z40" s="28" t="n">
         <v>33.23286593556736</v>
@@ -9525,10 +9525,10 @@
         <v>3.531265535503451</v>
       </c>
       <c r="AC40" s="75" t="n">
-        <v>5.212965262260775</v>
+        <v>5.212965262260766</v>
       </c>
       <c r="AD40" s="75" t="n">
-        <v>-1.681699726757325</v>
+        <v>-1.681699726757315</v>
       </c>
       <c r="AE40" s="72" t="n">
         <v>222.820943302779</v>
@@ -9710,19 +9710,19 @@
         <v>23.1962890471435</v>
       </c>
       <c r="AB41" s="86" t="n">
-        <v>1.924097988679193</v>
+        <v>1.924097988679165</v>
       </c>
       <c r="AC41" s="86" t="n">
-        <v>1.239406683683346</v>
+        <v>1.239406683683325</v>
       </c>
       <c r="AD41" s="86" t="n">
-        <v>0.6846913049958474</v>
+        <v>0.6846913049958403</v>
       </c>
       <c r="AE41" s="83" t="n">
-        <v>79.8618190303811</v>
+        <v>79.86181903038108</v>
       </c>
       <c r="AF41" s="83" t="n">
-        <v>77.3747290479299</v>
+        <v>77.37472904792992</v>
       </c>
       <c r="AG41" s="83" t="n">
         <v>74.52879943847657</v>
@@ -9734,19 +9734,19 @@
         <v>87.99163471221924</v>
       </c>
       <c r="AJ41" s="83" t="n">
-        <v>82.86342737000362</v>
+        <v>82.86342737000361</v>
       </c>
       <c r="AK41" s="83" t="n">
         <v>76.64699974060059</v>
       </c>
       <c r="AL41" s="83" t="n">
-        <v>70.43057211119756</v>
+        <v>70.43057211119758</v>
       </c>
       <c r="AM41" s="87" t="n">
-        <v>0.8871193900100356</v>
+        <v>0.8871193900100365</v>
       </c>
       <c r="AN41" s="36" t="n">
-        <v>16.22092880462777</v>
+        <v>16.22092880462774</v>
       </c>
       <c r="AO41" s="88" t="n">
         <v>2.77917927093863</v>
@@ -9898,13 +9898,13 @@
         <v>15.83299793648407</v>
       </c>
       <c r="AB42" s="75" t="n">
-        <v>-0.1159799429861117</v>
+        <v>-0.1159799429861135</v>
       </c>
       <c r="AC42" s="75" t="n">
-        <v>-0.2596436767949669</v>
+        <v>-0.2596436767949689</v>
       </c>
       <c r="AD42" s="75" t="n">
-        <v>0.1436637338088552</v>
+        <v>0.1436637338088554</v>
       </c>
       <c r="AE42" s="72" t="n">
         <v>10.24081364712333</v>
@@ -9928,13 +9928,13 @@
         <v>9.92350001335144</v>
       </c>
       <c r="AL42" s="72" t="n">
-        <v>8.830078267606792</v>
+        <v>8.830078267606794</v>
       </c>
       <c r="AM42" s="76" t="n">
-        <v>0.7224666904394476</v>
+        <v>0.7224666904394479</v>
       </c>
       <c r="AN42" s="29" t="n">
-        <v>22.03701807373443</v>
+        <v>22.03701807373439</v>
       </c>
       <c r="AO42" s="77" t="n">
         <v>5.172013938759462</v>
@@ -10077,7 +10077,7 @@
         <v>1.262552435393197</v>
       </c>
       <c r="Y43" s="35" t="n">
-        <v>46.29461603460204</v>
+        <v>46.29461603460202</v>
       </c>
       <c r="Z43" s="35" t="n">
         <v>11.65942852249583</v>
@@ -10086,13 +10086,13 @@
         <v>17.12657428852534</v>
       </c>
       <c r="AB43" s="86" t="n">
-        <v>1.54311691246599</v>
+        <v>1.543116912465905</v>
       </c>
       <c r="AC43" s="86" t="n">
-        <v>3.074823025245346</v>
+        <v>3.074823025245309</v>
       </c>
       <c r="AD43" s="86" t="n">
-        <v>-1.531706112779355</v>
+        <v>-1.531706112779404</v>
       </c>
       <c r="AE43" s="83" t="n">
         <v>214.1833174083247</v>
@@ -10116,16 +10116,16 @@
         <v>215.5605010986328</v>
       </c>
       <c r="AL43" s="83" t="n">
-        <v>199.43169735769</v>
+        <v>199.4316973576899</v>
       </c>
       <c r="AM43" s="87" t="n">
-        <v>0.3170819878741203</v>
+        <v>0.3170819878741207</v>
       </c>
       <c r="AN43" s="36" t="n">
-        <v>14.96452611562903</v>
+        <v>14.96452611562906</v>
       </c>
       <c r="AO43" s="88" t="n">
-        <v>2.983484378838339</v>
+        <v>2.983484378838338</v>
       </c>
       <c r="AP43" s="83" t="n">
         <v>236.5399932861328</v>
@@ -10274,13 +10274,13 @@
         <v>34.23482138782664</v>
       </c>
       <c r="AB44" s="75" t="n">
-        <v>10.7477119723151</v>
+        <v>10.74771197231502</v>
       </c>
       <c r="AC44" s="75" t="n">
-        <v>11.01957781711873</v>
+        <v>11.01957781711863</v>
       </c>
       <c r="AD44" s="75" t="n">
-        <v>-0.2718658448036297</v>
+        <v>-0.2718658448036173</v>
       </c>
       <c r="AE44" s="72" t="n">
         <v>174.4764956708318</v>
@@ -10307,13 +10307,13 @@
         <v>128.1484131704161</v>
       </c>
       <c r="AM44" s="76" t="n">
-        <v>0.6755108458523159</v>
+        <v>0.675510845852316</v>
       </c>
       <c r="AN44" s="29" t="n">
-        <v>44.36439193079691</v>
+        <v>44.36439193079687</v>
       </c>
       <c r="AO44" s="77" t="n">
-        <v>4.445505934438807</v>
+        <v>4.445505934438808</v>
       </c>
       <c r="AP44" s="72" t="n">
         <v>207.5200042724609</v>
@@ -10462,10 +10462,10 @@
         <v>13.10714546604916</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-3.399321297069093</v>
+        <v>-3.399321297069122</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-4.575819637717718</v>
+        <v>-4.575819637717746</v>
       </c>
       <c r="AD45" s="86" t="n">
         <v>1.176498340648624</v>
@@ -10495,13 +10495,13 @@
         <v>150.6000347062322</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>0.6752104136347088</v>
+        <v>0.6752104136347078</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>12.12043149800886</v>
+        <v>12.12043149800893</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>3.90304460157697</v>
+        <v>3.903044601576971</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -10647,19 +10647,19 @@
         <v>1.806929507728073</v>
       </c>
       <c r="AA46" s="28" t="n">
-        <v>17.97840146440195</v>
+        <v>17.97840146440194</v>
       </c>
       <c r="AB46" s="75" t="n">
-        <v>-2.459811033475333</v>
+        <v>-2.459811033475361</v>
       </c>
       <c r="AC46" s="75" t="n">
-        <v>-1.677461075867471</v>
+        <v>-1.677461075867505</v>
       </c>
       <c r="AD46" s="75" t="n">
-        <v>-0.7823499576078623</v>
+        <v>-0.7823499576078561</v>
       </c>
       <c r="AE46" s="72" t="n">
-        <v>71.30749111525387</v>
+        <v>71.30749111525388</v>
       </c>
       <c r="AF46" s="72" t="n">
         <v>74.13991795472211</v>
@@ -10674,22 +10674,22 @@
         <v>78.92007516860961</v>
       </c>
       <c r="AJ46" s="72" t="n">
-        <v>86.47728159731096</v>
+        <v>86.47728159731095</v>
       </c>
       <c r="AK46" s="72" t="n">
         <v>74.67000007629395</v>
       </c>
       <c r="AL46" s="72" t="n">
-        <v>62.86271855527693</v>
+        <v>62.86271855527694</v>
       </c>
       <c r="AM46" s="76" t="n">
-        <v>0.1404761012936835</v>
+        <v>0.1404761012936833</v>
       </c>
       <c r="AN46" s="29" t="n">
-        <v>31.62523505813029</v>
+        <v>31.62523505813027</v>
       </c>
       <c r="AO46" s="77" t="n">
-        <v>7.947811438417789</v>
+        <v>7.947811438417787</v>
       </c>
       <c r="AP46" s="72" t="n">
         <v>151</v>
@@ -10835,16 +10835,16 @@
         <v>48.94192262355774</v>
       </c>
       <c r="AA47" s="35" t="n">
-        <v>12.8531234605839</v>
+        <v>12.85312346058389</v>
       </c>
       <c r="AB47" s="86" t="n">
-        <v>10.70153133505346</v>
+        <v>10.70153133505323</v>
       </c>
       <c r="AC47" s="86" t="n">
-        <v>-7.520375660028477</v>
+        <v>-7.520375660028678</v>
       </c>
       <c r="AD47" s="86" t="n">
-        <v>18.22190699508194</v>
+        <v>18.22190699508191</v>
       </c>
       <c r="AE47" s="83" t="n">
         <v>1523.303399119648</v>
@@ -10871,10 +10871,10 @@
         <v>1104.141887999234</v>
       </c>
       <c r="AM47" s="87" t="n">
-        <v>0.5967660020016958</v>
+        <v>0.5967660020016957</v>
       </c>
       <c r="AN47" s="36" t="n">
-        <v>46.14302456563419</v>
+        <v>46.14302456563423</v>
       </c>
       <c r="AO47" s="88" t="n">
         <v>9.713763866949355</v>
@@ -11023,22 +11023,22 @@
         <v>54.29835872755525</v>
       </c>
       <c r="AA48" s="28" t="n">
-        <v>19.97757007056276</v>
+        <v>19.97757007056275</v>
       </c>
       <c r="AB48" s="75" t="n">
         <v>-1.459983617632531</v>
       </c>
       <c r="AC48" s="75" t="n">
-        <v>-5.783474316096578</v>
+        <v>-5.78347431609662</v>
       </c>
       <c r="AD48" s="75" t="n">
-        <v>4.323490698464047</v>
+        <v>4.323490698464089</v>
       </c>
       <c r="AE48" s="72" t="n">
         <v>346.6071846843971</v>
       </c>
       <c r="AF48" s="72" t="n">
-        <v>343.9304909480915</v>
+        <v>343.9304909480913</v>
       </c>
       <c r="AG48" s="72" t="n">
         <v>362.4233978271484</v>
@@ -11050,22 +11050,22 @@
         <v>401.7842997741699</v>
       </c>
       <c r="AJ48" s="72" t="n">
-        <v>362.191558973054</v>
+        <v>362.1915589730539</v>
       </c>
       <c r="AK48" s="72" t="n">
         <v>334.6439971923828</v>
       </c>
       <c r="AL48" s="72" t="n">
-        <v>307.0964354117116</v>
+        <v>307.0964354117117</v>
       </c>
       <c r="AM48" s="76" t="n">
-        <v>0.7028493523459056</v>
+        <v>0.702849352345906</v>
       </c>
       <c r="AN48" s="29" t="n">
-        <v>16.46380153942185</v>
+        <v>16.46380153942182</v>
       </c>
       <c r="AO48" s="77" t="n">
-        <v>3.8240534531993</v>
+        <v>3.824053453199301</v>
       </c>
       <c r="AP48" s="72" t="n">
         <v>498.8299865722656</v>
@@ -11640,7 +11640,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 26 Aug 2026, 06:03 PM · Yahoo Finance data</t>
+          <t>Built 26 Aug 2026, 10:05 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -12159,7 +12159,7 @@
         <v>1.06101528897768</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>38.71886971265771</v>
+        <v>38.71886971265772</v>
       </c>
       <c r="Z7" s="28" t="n">
         <v>2.580539307776237</v>
@@ -12168,16 +12168,16 @@
         <v>16.00743503320198</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>-0.3203115482666021</v>
+        <v>-0.3203115482665737</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>0.5997796684754685</v>
+        <v>0.5997796684754774</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-0.9200912167420706</v>
+        <v>-0.9200912167420511</v>
       </c>
       <c r="AE7" s="72" t="n">
-        <v>181.0841226170085</v>
+        <v>181.0841226170084</v>
       </c>
       <c r="AF7" s="72" t="n">
         <v>182.2091852215775</v>
@@ -12349,16 +12349,16 @@
         <v>3.57150517110037</v>
       </c>
       <c r="AC8" s="86" t="n">
-        <v>2.973157486782789</v>
+        <v>2.973157486782793</v>
       </c>
       <c r="AD8" s="86" t="n">
-        <v>0.5983476843175808</v>
+        <v>0.5983476843175763</v>
       </c>
       <c r="AE8" s="83" t="n">
         <v>172.6185119118124</v>
       </c>
       <c r="AF8" s="83" t="n">
-        <v>168.7482306091131</v>
+        <v>168.748230609113</v>
       </c>
       <c r="AG8" s="83" t="n">
         <v>162.5481997680664</v>
@@ -12515,28 +12515,28 @@
         <v>0.7953741222923267</v>
       </c>
       <c r="Y9" s="28" t="n">
-        <v>62.03866188851597</v>
+        <v>62.03866188851595</v>
       </c>
       <c r="Z9" s="28" t="n">
         <v>95.23811995266665</v>
       </c>
       <c r="AA9" s="28" t="n">
-        <v>25.9447377312995</v>
+        <v>25.94473773129948</v>
       </c>
       <c r="AB9" s="75" t="n">
         <v>0.492442421276408</v>
       </c>
       <c r="AC9" s="75" t="n">
-        <v>0.578101934049247</v>
+        <v>0.5781019340492473</v>
       </c>
       <c r="AD9" s="75" t="n">
-        <v>-0.08565951277283901</v>
+        <v>-0.08565951277283923</v>
       </c>
       <c r="AE9" s="72" t="n">
-        <v>57.83320499205568</v>
+        <v>57.83320499205569</v>
       </c>
       <c r="AF9" s="72" t="n">
-        <v>57.45743968175861</v>
+        <v>57.45743968175859</v>
       </c>
       <c r="AG9" s="72" t="n">
         <v>56.19460014343262</v>
@@ -12702,19 +12702,19 @@
         <v>28.34826020131646</v>
       </c>
       <c r="AB10" s="86" t="n">
-        <v>1.53207059408728</v>
+        <v>1.532070594087308</v>
       </c>
       <c r="AC10" s="86" t="n">
-        <v>1.42565916423253</v>
+        <v>1.425659164232551</v>
       </c>
       <c r="AD10" s="86" t="n">
-        <v>0.1064114298547501</v>
+        <v>0.1064114298547569</v>
       </c>
       <c r="AE10" s="83" t="n">
         <v>62.58389416452235</v>
       </c>
       <c r="AF10" s="83" t="n">
-        <v>61.03394826415363</v>
+        <v>61.03394826415364</v>
       </c>
       <c r="AG10" s="83" t="n">
         <v>57.71540031433106</v>
@@ -12741,7 +12741,7 @@
         <v>14.23184172302663</v>
       </c>
       <c r="AO10" s="88" t="n">
-        <v>1.885563251901759</v>
+        <v>1.88556325190176</v>
       </c>
       <c r="AP10" s="83" t="n">
         <v>64.69999694824219</v>
@@ -12877,19 +12877,19 @@
         <v>72.54321303436096</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>17.0746069662052</v>
+        <v>17.07460696620518</v>
       </c>
       <c r="AB11" s="75" t="n">
         <v>0.4492320766756137</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.3325025770910877</v>
+        <v>0.3325025770910808</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>0.1167294995845261</v>
+        <v>0.1167294995845329</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>86.15255432236123</v>
+        <v>86.15255432236125</v>
       </c>
       <c r="AF11" s="72" t="n">
         <v>85.62823719080555</v>
@@ -13058,19 +13058,19 @@
         <v>16.32463068161461</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.6000522748489487</v>
+        <v>0.6000522748489203</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.6191898439528619</v>
+        <v>0.6191898439528407</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.01913756910391318</v>
+        <v>-0.01913756910392039</v>
       </c>
       <c r="AE12" s="83" t="n">
         <v>117.8122357376327</v>
       </c>
       <c r="AF12" s="83" t="n">
-        <v>117.2409708991572</v>
+        <v>117.2409708991573</v>
       </c>
       <c r="AG12" s="83" t="n">
         <v>116.2313998413086</v>
@@ -13097,7 +13097,7 @@
         <v>7.03012096580429</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.446532750178724</v>
+        <v>1.446532750178725</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -13227,7 +13227,7 @@
         <v>0.559475461984041</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>58.09068851355973</v>
+        <v>58.09068851355975</v>
       </c>
       <c r="Z13" s="28" t="n">
         <v>91.12345639820958</v>
@@ -13236,13 +13236,13 @@
         <v>11.49235315796759</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.5241957537753592</v>
+        <v>0.5241957537753734</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.3534767147172825</v>
+        <v>0.3534767147172965</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>0.1707190390580767</v>
+        <v>0.1707190390580769</v>
       </c>
       <c r="AE13" s="72" t="n">
         <v>111.8108182529862</v>
@@ -13269,13 +13269,13 @@
         <v>107.9925263760805</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.861284942060638</v>
+        <v>0.8612849420606363</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>5.425883234817597</v>
+        <v>5.425883234817622</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.501011356246803</v>
+        <v>1.501011356246802</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -13405,28 +13405,28 @@
         <v>0.7171654139555755</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>61.44960602522442</v>
+        <v>61.44960602522443</v>
       </c>
       <c r="Z14" s="35" t="n">
         <v>75.0001172551049</v>
       </c>
       <c r="AA14" s="35" t="n">
-        <v>13.45502192937347</v>
+        <v>13.45502192937346</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.5056969008052405</v>
+        <v>0.5056969008052548</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.4096181129894669</v>
+        <v>0.4096181129894715</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>0.09607878781577367</v>
+        <v>0.09607878781578327</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>52.99681621493925</v>
+        <v>52.99681621493926</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.43027197972937</v>
+        <v>52.43027197972938</v>
       </c>
       <c r="AG14" s="83" t="n">
         <v>51.65659996032715</v>
@@ -13438,7 +13438,7 @@
         <v>49.68829999923706</v>
       </c>
       <c r="AJ14" s="83" t="n">
-        <v>54.02429216524144</v>
+        <v>54.02429216524143</v>
       </c>
       <c r="AK14" s="83" t="n">
         <v>52.40000038146972</v>
@@ -13447,13 +13447,13 @@
         <v>50.77570859769801</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.8632356764265959</v>
+        <v>0.8632356764265976</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>6.199586915828029</v>
+        <v>6.199586915828002</v>
       </c>
       <c r="AO14" s="88" t="n">
-        <v>1.599189254346042</v>
+        <v>1.599189254346041</v>
       </c>
       <c r="AP14" s="83" t="n">
         <v>54.18999862670898</v>
@@ -13592,19 +13592,19 @@
         <v>14.85505707332623</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.597740921948315</v>
+        <v>0.5977409219482865</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>1.271730992963743</v>
+        <v>1.27173099296369</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.6739900710154281</v>
+        <v>-0.6739900710154032</v>
       </c>
       <c r="AE15" s="72" t="n">
         <v>183.5542484068588</v>
       </c>
       <c r="AF15" s="72" t="n">
-        <v>183.5524282709315</v>
+        <v>183.5524282709314</v>
       </c>
       <c r="AG15" s="72" t="n">
         <v>182.9132006835937</v>
@@ -13761,22 +13761,22 @@
         <v>0.5808961755085701</v>
       </c>
       <c r="Y16" s="35" t="n">
-        <v>55.34438024664022</v>
+        <v>55.34438024664021</v>
       </c>
       <c r="Z16" s="35" t="n">
         <v>88.23529411764706</v>
       </c>
       <c r="AA16" s="35" t="n">
-        <v>8.905485611182302</v>
+        <v>8.905485611182307</v>
       </c>
       <c r="AB16" s="86" t="n">
-        <v>0.05898077880414831</v>
+        <v>0.0589807788041341</v>
       </c>
       <c r="AC16" s="86" t="n">
-        <v>0.02126905062596076</v>
+        <v>0.02126905062595848</v>
       </c>
       <c r="AD16" s="86" t="n">
-        <v>0.03771172817818756</v>
+        <v>0.03771172817817563</v>
       </c>
       <c r="AE16" s="83" t="n">
         <v>45.10768704174487</v>
@@ -13951,16 +13951,16 @@
         <v>-0.4164005387462808</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.3699492383955316</v>
+        <v>-0.3699492383955302</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.04645130035074918</v>
+        <v>-0.04645130035075062</v>
       </c>
       <c r="AE17" s="72" t="n">
         <v>43.53027602356346</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>43.96933480740116</v>
+        <v>43.96933480740118</v>
       </c>
       <c r="AG17" s="72" t="n">
         <v>44.78420021057129</v>
@@ -13987,7 +13987,7 @@
         <v>4.786731745731833</v>
       </c>
       <c r="AO17" s="77" t="n">
-        <v>1.525143119610751</v>
+        <v>1.52514311961075</v>
       </c>
       <c r="AP17" s="72" t="n">
         <v>47.79999923706055</v>
@@ -14145,19 +14145,19 @@
         <v>16.67736245364211</v>
       </c>
       <c r="AB19" s="75" t="n">
-        <v>4.535386221418548</v>
+        <v>4.535386221418776</v>
       </c>
       <c r="AC19" s="75" t="n">
-        <v>5.898941091755264</v>
+        <v>5.898941091755504</v>
       </c>
       <c r="AD19" s="75" t="n">
-        <v>-1.363554870336715</v>
+        <v>-1.363554870336729</v>
       </c>
       <c r="AE19" s="72" t="n">
-        <v>766.6776346238021</v>
+        <v>766.6776346238023</v>
       </c>
       <c r="AF19" s="72" t="n">
-        <v>763.5639474660394</v>
+        <v>763.5639474660393</v>
       </c>
       <c r="AG19" s="72" t="n">
         <v>752.7470031738281</v>
@@ -14312,7 +14312,7 @@
         <v>0.6312510470890231</v>
       </c>
       <c r="Y20" s="35" t="n">
-        <v>48.94749559406707</v>
+        <v>48.94749559406706</v>
       </c>
       <c r="Z20" s="35" t="n">
         <v>25.15670410206731</v>
@@ -14321,19 +14321,19 @@
         <v>14.70001626391567</v>
       </c>
       <c r="AB20" s="86" t="n">
-        <v>1.763895400194656</v>
+        <v>1.76389540019477</v>
       </c>
       <c r="AC20" s="86" t="n">
-        <v>2.880489202644569</v>
+        <v>2.88048920264479</v>
       </c>
       <c r="AD20" s="86" t="n">
-        <v>-1.116593802449913</v>
+        <v>-1.116593802450021</v>
       </c>
       <c r="AE20" s="83" t="n">
         <v>714.0300599885434</v>
       </c>
       <c r="AF20" s="83" t="n">
-        <v>713.2346287197892</v>
+        <v>713.234628719789</v>
       </c>
       <c r="AG20" s="83" t="n">
         <v>713.0132006835937</v>
@@ -14494,22 +14494,22 @@
         <v>26.90425934743243</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>14.09731850764592</v>
+        <v>14.09731850764591</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>1.296599616599735</v>
+        <v>1.296599616599792</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>1.785046481194919</v>
+        <v>1.785046481194975</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.4884468645951836</v>
+        <v>-0.4884468645951832</v>
       </c>
       <c r="AE21" s="72" t="n">
         <v>299.8466609254667</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>299.064083654692</v>
+        <v>299.0640836546919</v>
       </c>
       <c r="AG21" s="72" t="n">
         <v>296.95580078125</v>
@@ -14664,28 +14664,28 @@
         <v>0.6895993773390074</v>
       </c>
       <c r="Y22" s="35" t="n">
-        <v>41.20633383052663</v>
+        <v>41.20633383052665</v>
       </c>
       <c r="Z22" s="35" t="n">
         <v>18.99057053549302</v>
       </c>
       <c r="AA22" s="35" t="n">
-        <v>19.56182528470795</v>
+        <v>19.56182528470794</v>
       </c>
       <c r="AB22" s="86" t="n">
-        <v>-10.39522420901102</v>
+        <v>-10.39522420901108</v>
       </c>
       <c r="AC22" s="86" t="n">
-        <v>-10.38170489148928</v>
+        <v>-10.38170489148936</v>
       </c>
       <c r="AD22" s="86" t="n">
-        <v>-0.01351931752174096</v>
+        <v>-0.01351931752171787</v>
       </c>
       <c r="AE22" s="83" t="n">
         <v>123.1452572941707</v>
       </c>
       <c r="AF22" s="83" t="n">
-        <v>132.7696500156955</v>
+        <v>132.7696500156954</v>
       </c>
       <c r="AG22" s="83" t="n">
         <v>167.7311999511719</v>
@@ -14703,13 +14703,13 @@
         <v>127.458500289917</v>
       </c>
       <c r="AL22" s="83" t="n">
-        <v>99.00616237325869</v>
+        <v>99.00616237325872</v>
       </c>
       <c r="AM22" s="87" t="n">
-        <v>0.2928377246976647</v>
+        <v>0.2928377246976644</v>
       </c>
       <c r="AN22" s="36" t="n">
-        <v>44.64564992046925</v>
+        <v>44.6456499204692</v>
       </c>
       <c r="AO22" s="88" t="n">
         <v>15.28505882491378</v>
@@ -14861,7 +14861,7 @@
         <v>0.50751414140136</v>
       </c>
       <c r="Y24" s="28" t="n">
-        <v>47.82170325264422</v>
+        <v>47.82170325264421</v>
       </c>
       <c r="Z24" s="28" t="n">
         <v>47.3363298686861</v>
@@ -14873,16 +14873,16 @@
         <v>-1.438937084806014</v>
       </c>
       <c r="AC24" s="75" t="n">
-        <v>-1.290319543672632</v>
+        <v>-1.29031954367265</v>
       </c>
       <c r="AD24" s="75" t="n">
-        <v>-0.1486175411333814</v>
+        <v>-0.1486175411333641</v>
       </c>
       <c r="AE24" s="72" t="n">
         <v>310.110926620614</v>
       </c>
       <c r="AF24" s="72" t="n">
-        <v>311.7757774077758</v>
+        <v>311.7757774077756</v>
       </c>
       <c r="AG24" s="72" t="n">
         <v>310.8775994873047</v>
@@ -15046,19 +15046,19 @@
         <v>10.15695047802933</v>
       </c>
       <c r="AB25" s="86" t="n">
-        <v>-8.485468367940882</v>
+        <v>-8.485468367940939</v>
       </c>
       <c r="AC25" s="86" t="n">
-        <v>-7.569504275575213</v>
+        <v>-7.569504275575226</v>
       </c>
       <c r="AD25" s="86" t="n">
-        <v>-0.9159640923656696</v>
+        <v>-0.9159640923657131</v>
       </c>
       <c r="AE25" s="83" t="n">
-        <v>475.89679540197</v>
+        <v>475.8967954019701</v>
       </c>
       <c r="AF25" s="83" t="n">
-        <v>484.988021805627</v>
+        <v>484.9880218056269</v>
       </c>
       <c r="AG25" s="83" t="n">
         <v>508.9524005126953</v>
@@ -15070,7 +15070,7 @@
         <v>332.0110004425049</v>
       </c>
       <c r="AJ25" s="83" t="n">
-        <v>518.1562261147191</v>
+        <v>518.1562261147189</v>
       </c>
       <c r="AK25" s="83" t="n">
         <v>480.4335021972656</v>
@@ -15079,10 +15079,10 @@
         <v>442.7107782798122</v>
       </c>
       <c r="AM25" s="87" t="n">
-        <v>0.4833852199508791</v>
+        <v>0.4833852199508798</v>
       </c>
       <c r="AN25" s="36" t="n">
-        <v>15.70361922927036</v>
+        <v>15.70361922927033</v>
       </c>
       <c r="AO25" s="88" t="n">
         <v>5.787231899257232</v>
@@ -15213,22 +15213,22 @@
         <v>0.5473343579437998</v>
       </c>
       <c r="Y26" s="28" t="n">
-        <v>51.59447874058975</v>
+        <v>51.59447874058977</v>
       </c>
       <c r="Z26" s="28" t="n">
         <v>17.40254524460956</v>
       </c>
       <c r="AA26" s="28" t="n">
-        <v>21.15761923206868</v>
+        <v>21.15761923206867</v>
       </c>
       <c r="AB26" s="75" t="n">
-        <v>2.805782602343299</v>
+        <v>2.805782602343243</v>
       </c>
       <c r="AC26" s="75" t="n">
-        <v>4.265794032150819</v>
+        <v>4.265794032150776</v>
       </c>
       <c r="AD26" s="75" t="n">
-        <v>-1.460011429807519</v>
+        <v>-1.460011429807533</v>
       </c>
       <c r="AE26" s="72" t="n">
         <v>262.1181777471069</v>
@@ -15395,16 +15395,16 @@
         <v>96.05312643155295</v>
       </c>
       <c r="AA27" s="35" t="n">
-        <v>22.63240211494755</v>
+        <v>22.63240211494754</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.222947014016185</v>
+        <v>2.222947014016157</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>1.456497417477924</v>
+        <v>1.456497417477911</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.7664495965382614</v>
+        <v>0.7664495965382456</v>
       </c>
       <c r="AE27" s="83" t="n">
         <v>83.52983766862579</v>
@@ -15437,7 +15437,7 @@
         <v>23.17354751872974</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.846624635081089</v>
+        <v>2.84662463508109</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -15574,16 +15574,16 @@
         <v>11.20435963394189</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-11.14393797063926</v>
+        <v>-11.14393797063934</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-9.778178137783959</v>
+        <v>-9.778178137783991</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-1.365759832855298</v>
+        <v>-1.365759832855352</v>
       </c>
       <c r="AE28" s="72" t="n">
-        <v>250.6160482244463</v>
+        <v>250.6160482244464</v>
       </c>
       <c r="AF28" s="72" t="n">
         <v>262.2142445386585</v>
@@ -15607,13 +15607,13 @@
         <v>222.5757648476718</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.2589001414325672</v>
+        <v>0.2589001414325675</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>28.2852763587621</v>
+        <v>28.28527635876211</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>8.007574764528222</v>
+        <v>8.007574764528224</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -15753,10 +15753,10 @@
         <v>-0.9815696685958386</v>
       </c>
       <c r="AC29" s="86" t="n">
-        <v>-0.6695830207175046</v>
+        <v>-0.6695830207175111</v>
       </c>
       <c r="AD29" s="86" t="n">
-        <v>-0.311986647878334</v>
+        <v>-0.3119866478783275</v>
       </c>
       <c r="AE29" s="83" t="n">
         <v>65.78080969071645</v>
@@ -15774,7 +15774,7 @@
         <v>81.57382482528686</v>
       </c>
       <c r="AJ29" s="83" t="n">
-        <v>77.21116098316129</v>
+        <v>77.21116098316131</v>
       </c>
       <c r="AK29" s="83" t="n">
         <v>66.59349937438965</v>
@@ -15783,10 +15783,10 @@
         <v>55.975837765618</v>
       </c>
       <c r="AM29" s="87" t="n">
-        <v>0.2841567558967106</v>
+        <v>0.2841567558967107</v>
       </c>
       <c r="AN29" s="36" t="n">
-        <v>31.88798218600585</v>
+        <v>31.88798218600588</v>
       </c>
       <c r="AO29" s="88" t="n">
         <v>8.401993413382588</v>
@@ -15923,22 +15923,22 @@
         <v>1.847058160376113</v>
       </c>
       <c r="AA30" s="28" t="n">
-        <v>21.27683907191318</v>
+        <v>21.27683907191317</v>
       </c>
       <c r="AB30" s="75" t="n">
-        <v>-8.154650254005389</v>
+        <v>-8.154650254005332</v>
       </c>
       <c r="AC30" s="75" t="n">
-        <v>-1.909894273655249</v>
+        <v>-1.909894273655221</v>
       </c>
       <c r="AD30" s="75" t="n">
-        <v>-6.24475598035014</v>
+        <v>-6.244755980350112</v>
       </c>
       <c r="AE30" s="72" t="n">
         <v>372.2427428881391</v>
       </c>
       <c r="AF30" s="72" t="n">
-        <v>385.3394869817893</v>
+        <v>385.3394869817894</v>
       </c>
       <c r="AG30" s="72" t="n">
         <v>387.46</v>
@@ -15965,7 +15965,7 @@
         <v>24.22054074500931</v>
       </c>
       <c r="AO30" s="77" t="n">
-        <v>4.028286403791032</v>
+        <v>4.028286403791031</v>
       </c>
       <c r="AP30" s="72" t="n">
         <v>495</v>
@@ -16102,19 +16102,19 @@
         <v>18.23166749486843</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>2.267241879695902</v>
+        <v>2.267241879695888</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.038750531250431</v>
+        <v>1.038750531250421</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>1.228491348445471</v>
+        <v>1.228491348445467</v>
       </c>
       <c r="AE31" s="83" t="n">
         <v>100.7234864526285</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>97.39721899003281</v>
+        <v>97.39721899003283</v>
       </c>
       <c r="AG31" s="83" t="n">
         <v>96.32999969482422</v>
@@ -16275,22 +16275,22 @@
         <v>14.03969156397268</v>
       </c>
       <c r="AA32" s="28" t="n">
-        <v>15.71150932782601</v>
+        <v>15.711509327826</v>
       </c>
       <c r="AB32" s="75" t="n">
-        <v>1.319176497937264</v>
+        <v>1.319176497937249</v>
       </c>
       <c r="AC32" s="75" t="n">
-        <v>2.04650255142019</v>
+        <v>2.046502551420173</v>
       </c>
       <c r="AD32" s="75" t="n">
-        <v>-0.7273260534829267</v>
+        <v>-0.727326053482924</v>
       </c>
       <c r="AE32" s="72" t="n">
         <v>90.82779569137334</v>
       </c>
       <c r="AF32" s="72" t="n">
-        <v>90.03476363996919</v>
+        <v>90.0347636399692</v>
       </c>
       <c r="AG32" s="72" t="n">
         <v>89.47580017089844</v>
@@ -16308,16 +16308,16 @@
         <v>89.48850059509277</v>
       </c>
       <c r="AL32" s="72" t="n">
-        <v>66.74210076279022</v>
+        <v>66.74210076279024</v>
       </c>
       <c r="AM32" s="76" t="n">
-        <v>0.4681598035239759</v>
+        <v>0.4681598035239758</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>50.83647548241498</v>
+        <v>50.83647548241491</v>
       </c>
       <c r="AO32" s="77" t="n">
-        <v>8.568871089565452</v>
+        <v>8.56887108956545</v>
       </c>
       <c r="AP32" s="72" t="n">
         <v>153.1999969482422</v>
@@ -16454,19 +16454,19 @@
         <v>10.54981163086536</v>
       </c>
       <c r="AB33" s="86" t="n">
-        <v>7.762734211975499</v>
+        <v>7.762734211975612</v>
       </c>
       <c r="AC33" s="86" t="n">
-        <v>11.99858540046861</v>
+        <v>11.99858540046876</v>
       </c>
       <c r="AD33" s="86" t="n">
-        <v>-4.235851188493116</v>
+        <v>-4.235851188493145</v>
       </c>
       <c r="AE33" s="83" t="n">
         <v>449.4514488175853</v>
       </c>
       <c r="AF33" s="83" t="n">
-        <v>446.0514675340545</v>
+        <v>446.0514675340546</v>
       </c>
       <c r="AG33" s="83" t="n">
         <v>429.9705981445313</v>
@@ -16493,7 +16493,7 @@
         <v>27.0975829974515</v>
       </c>
       <c r="AO33" s="88" t="n">
-        <v>6.605100861605257</v>
+        <v>6.605100861605259</v>
       </c>
       <c r="AP33" s="83" t="n">
         <v>514</v>
@@ -16621,7 +16621,7 @@
         <v>0.8048316283744019</v>
       </c>
       <c r="Y34" s="28" t="n">
-        <v>47.33673639906208</v>
+        <v>47.33673639906207</v>
       </c>
       <c r="Z34" s="28" t="n">
         <v>27.80143086029114</v>
@@ -16630,19 +16630,19 @@
         <v>8.799423763232001</v>
       </c>
       <c r="AB34" s="75" t="n">
-        <v>-2.328252182500705</v>
+        <v>-2.328252182500762</v>
       </c>
       <c r="AC34" s="75" t="n">
-        <v>-2.054104099965501</v>
+        <v>-2.054104099965567</v>
       </c>
       <c r="AD34" s="75" t="n">
-        <v>-0.2741480825352038</v>
+        <v>-0.274148082535195</v>
       </c>
       <c r="AE34" s="72" t="n">
-        <v>343.1807463720263</v>
+        <v>343.1807463720264</v>
       </c>
       <c r="AF34" s="72" t="n">
-        <v>345.5563840975661</v>
+        <v>345.5563840975662</v>
       </c>
       <c r="AG34" s="72" t="n">
         <v>349.6213995361328</v>
@@ -16654,19 +16654,19 @@
         <v>332.6897993469238</v>
       </c>
       <c r="AJ34" s="72" t="n">
-        <v>370.5153731126448</v>
+        <v>370.5153731126447</v>
       </c>
       <c r="AK34" s="72" t="n">
         <v>348.2565017700196</v>
       </c>
       <c r="AL34" s="72" t="n">
-        <v>325.9976304273943</v>
+        <v>325.9976304273944</v>
       </c>
       <c r="AM34" s="76" t="n">
-        <v>0.389560765313515</v>
+        <v>0.3895607653135147</v>
       </c>
       <c r="AN34" s="29" t="n">
-        <v>12.78303275286701</v>
+        <v>12.78303275286698</v>
       </c>
       <c r="AO34" s="77" t="n">
         <v>2.51697052802563</v>
@@ -16806,16 +16806,16 @@
         <v>14.98339587410031</v>
       </c>
       <c r="AB35" s="86" t="n">
-        <v>0.1702280260240414</v>
+        <v>0.1702280260240201</v>
       </c>
       <c r="AC35" s="86" t="n">
-        <v>-0.1061634876109539</v>
+        <v>-0.1061634876109681</v>
       </c>
       <c r="AD35" s="86" t="n">
-        <v>0.2763915136349953</v>
+        <v>0.2763915136349882</v>
       </c>
       <c r="AE35" s="83" t="n">
-        <v>41.88280058684266</v>
+        <v>41.88280058684265</v>
       </c>
       <c r="AF35" s="83" t="n">
         <v>41.39523443846495</v>
@@ -16836,16 +16836,16 @@
         <v>40.51199979782105</v>
       </c>
       <c r="AL35" s="83" t="n">
-        <v>33.64663560515128</v>
+        <v>33.64663560515129</v>
       </c>
       <c r="AM35" s="87" t="n">
-        <v>0.6236641814621127</v>
+        <v>0.6236641814621128</v>
       </c>
       <c r="AN35" s="36" t="n">
-        <v>33.89299085175757</v>
+        <v>33.89299085175753</v>
       </c>
       <c r="AO35" s="88" t="n">
-        <v>8.825994579974203</v>
+        <v>8.825994579974205</v>
       </c>
       <c r="AP35" s="83" t="n">
         <v>76.87000274658203</v>
@@ -16979,16 +16979,16 @@
         <v>10.432474076896</v>
       </c>
       <c r="AA36" s="28" t="n">
-        <v>16.10465277487026</v>
+        <v>16.10465277487027</v>
       </c>
       <c r="AB36" s="75" t="n">
         <v>-3.519050205391409</v>
       </c>
       <c r="AC36" s="75" t="n">
-        <v>-2.773547320627781</v>
+        <v>-2.773547320627762</v>
       </c>
       <c r="AD36" s="75" t="n">
-        <v>-0.7455028847636282</v>
+        <v>-0.7455028847636469</v>
       </c>
       <c r="AE36" s="72" t="n">
         <v>92.29025544093362</v>
@@ -17012,16 +17012,16 @@
         <v>95.53749923706054</v>
       </c>
       <c r="AL36" s="72" t="n">
-        <v>83.01303136579379</v>
+        <v>83.01303136579378</v>
       </c>
       <c r="AM36" s="76" t="n">
-        <v>0.1783298115757792</v>
+        <v>0.1783298115757796</v>
       </c>
       <c r="AN36" s="29" t="n">
-        <v>26.21895689396129</v>
+        <v>26.21895689396132</v>
       </c>
       <c r="AO36" s="77" t="n">
-        <v>7.020044517276306</v>
+        <v>7.020044517276307</v>
       </c>
       <c r="AP36" s="72" t="n">
         <v>142.3500061035156</v>
@@ -17155,22 +17155,22 @@
         <v>39.8031790685044</v>
       </c>
       <c r="AA37" s="35" t="n">
-        <v>34.18974034494999</v>
+        <v>34.18974034494997</v>
       </c>
       <c r="AB37" s="86" t="n">
-        <v>18.24871331969894</v>
+        <v>18.24871331969888</v>
       </c>
       <c r="AC37" s="86" t="n">
-        <v>21.55225737616183</v>
+        <v>21.55225737616176</v>
       </c>
       <c r="AD37" s="86" t="n">
-        <v>-3.30354405646289</v>
+        <v>-3.303544056462883</v>
       </c>
       <c r="AE37" s="83" t="n">
         <v>486.7203624131243</v>
       </c>
       <c r="AF37" s="83" t="n">
-        <v>472.1677468721674</v>
+        <v>472.1677468721675</v>
       </c>
       <c r="AG37" s="83" t="n">
         <v>423.8033978271484</v>
@@ -17197,7 +17197,7 @@
         <v>20.39003921216277</v>
       </c>
       <c r="AO37" s="88" t="n">
-        <v>2.398245679437152</v>
+        <v>2.398245679437153</v>
       </c>
       <c r="AP37" s="83" t="n">
         <v>553.719970703125</v>
@@ -17325,22 +17325,22 @@
         <v>1.380392511806641</v>
       </c>
       <c r="Y38" s="28" t="n">
-        <v>70.18351100612992</v>
+        <v>70.1835110061299</v>
       </c>
       <c r="Z38" s="28" t="n">
         <v>95.05271273508494</v>
       </c>
       <c r="AA38" s="28" t="n">
-        <v>20.54190858102327</v>
+        <v>20.54190858102328</v>
       </c>
       <c r="AB38" s="75" t="n">
-        <v>4.691221774896505</v>
+        <v>4.691221774896519</v>
       </c>
       <c r="AC38" s="75" t="n">
-        <v>0.8377925149367934</v>
+        <v>0.8377925149367832</v>
       </c>
       <c r="AD38" s="75" t="n">
-        <v>3.853429259959711</v>
+        <v>3.853429259959736</v>
       </c>
       <c r="AE38" s="72" t="n">
         <v>112.8025511762749</v>
@@ -17364,16 +17364,16 @@
         <v>101.3014999389648</v>
       </c>
       <c r="AL38" s="72" t="n">
-        <v>81.06869661997001</v>
+        <v>81.06869661996996</v>
       </c>
       <c r="AM38" s="76" t="n">
-        <v>1.130869125983233</v>
+        <v>1.130869125983231</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>39.94571320500741</v>
+        <v>39.94571320500752</v>
       </c>
       <c r="AO38" s="77" t="n">
-        <v>5.635848173286751</v>
+        <v>5.63584817328675</v>
       </c>
       <c r="AP38" s="72" t="n">
         <v>365.2099914550781</v>
@@ -17513,16 +17513,16 @@
         <v>7.907943729131716</v>
       </c>
       <c r="AC39" s="86" t="n">
-        <v>2.585590172410647</v>
+        <v>2.585590172410527</v>
       </c>
       <c r="AD39" s="86" t="n">
-        <v>5.322353556721069</v>
+        <v>5.32235355672119</v>
       </c>
       <c r="AE39" s="83" t="n">
         <v>939.0180003872971</v>
       </c>
       <c r="AF39" s="83" t="n">
-        <v>926.8935605123152</v>
+        <v>926.8935605123153</v>
       </c>
       <c r="AG39" s="83" t="n">
         <v>961.9096032714843</v>
@@ -17534,22 +17534,22 @@
         <v>578.0377505493165</v>
       </c>
       <c r="AJ39" s="83" t="n">
-        <v>1025.059299403799</v>
+        <v>1025.059299403798</v>
       </c>
       <c r="AK39" s="83" t="n">
         <v>902.3759979248047</v>
       </c>
       <c r="AL39" s="83" t="n">
-        <v>779.6926964458107</v>
+        <v>779.6926964458108</v>
       </c>
       <c r="AM39" s="87" t="n">
-        <v>0.6246867846296046</v>
+        <v>0.624686784629605</v>
       </c>
       <c r="AN39" s="36" t="n">
-        <v>27.19117125480485</v>
+        <v>27.19117125480481</v>
       </c>
       <c r="AO39" s="88" t="n">
-        <v>7.008328654811312</v>
+        <v>7.008328654811311</v>
       </c>
       <c r="AP39" s="83" t="n">
         <v>1255</v>
@@ -17689,10 +17689,10 @@
         <v>4.757550469118314</v>
       </c>
       <c r="AC40" s="75" t="n">
-        <v>5.633390193950106</v>
+        <v>5.633390193950094</v>
       </c>
       <c r="AD40" s="75" t="n">
-        <v>-0.875839724831792</v>
+        <v>-0.8758397248317795</v>
       </c>
       <c r="AE40" s="72" t="n">
         <v>225.3612149104927</v>
@@ -17862,19 +17862,19 @@
         <v>22.52455857954936</v>
       </c>
       <c r="AB41" s="86" t="n">
-        <v>1.814932429595444</v>
+        <v>1.814932429595416</v>
       </c>
       <c r="AC41" s="86" t="n">
-        <v>1.068233857434384</v>
+        <v>1.068233857434364</v>
       </c>
       <c r="AD41" s="86" t="n">
-        <v>0.7466985721610604</v>
+        <v>0.7466985721610515</v>
       </c>
       <c r="AE41" s="83" t="n">
-        <v>79.40519615778351</v>
+        <v>79.40519615778349</v>
       </c>
       <c r="AF41" s="83" t="n">
-        <v>76.96620204427563</v>
+        <v>76.96620204427565</v>
       </c>
       <c r="AG41" s="83" t="n">
         <v>74.53299942016602</v>
@@ -17886,19 +17886,19 @@
         <v>88.13284473419189</v>
       </c>
       <c r="AJ41" s="83" t="n">
-        <v>82.19000480529913</v>
+        <v>82.19000480529911</v>
       </c>
       <c r="AK41" s="83" t="n">
         <v>76.25549964904785</v>
       </c>
       <c r="AL41" s="83" t="n">
-        <v>70.32099449279657</v>
+        <v>70.32099449279659</v>
       </c>
       <c r="AM41" s="87" t="n">
-        <v>1.003369998894713</v>
+        <v>1.003369998894714</v>
       </c>
       <c r="AN41" s="36" t="n">
-        <v>15.56479252923071</v>
+        <v>15.56479252923068</v>
       </c>
       <c r="AO41" s="88" t="n">
         <v>2.859696580257904</v>
@@ -18035,16 +18035,16 @@
         <v>61.19404755465597</v>
       </c>
       <c r="AA42" s="28" t="n">
-        <v>16.96020163925633</v>
+        <v>16.96020163925632</v>
       </c>
       <c r="AB42" s="75" t="n">
-        <v>-0.1481756042855817</v>
+        <v>-0.1481756042855853</v>
       </c>
       <c r="AC42" s="75" t="n">
-        <v>-0.2955596102471807</v>
+        <v>-0.2955596102471827</v>
       </c>
       <c r="AD42" s="75" t="n">
-        <v>0.147384005961599</v>
+        <v>0.1473840059615975</v>
       </c>
       <c r="AE42" s="72" t="n">
         <v>10.19247473275511</v>
@@ -18068,13 +18068,13 @@
         <v>9.82350001335144</v>
       </c>
       <c r="AL42" s="72" t="n">
-        <v>8.571952472576923</v>
+        <v>8.571952472576925</v>
       </c>
       <c r="AM42" s="76" t="n">
-        <v>0.7103397397882557</v>
+        <v>0.7103397397882559</v>
       </c>
       <c r="AN42" s="29" t="n">
-        <v>25.48068486941514</v>
+        <v>25.4806848694151</v>
       </c>
       <c r="AO42" s="77" t="n">
         <v>5.363874531321008</v>
@@ -18205,7 +18205,7 @@
         <v>1.063252939910592</v>
       </c>
       <c r="Y43" s="35" t="n">
-        <v>49.60542931840115</v>
+        <v>49.60542931840114</v>
       </c>
       <c r="Z43" s="35" t="n">
         <v>28.06000757402949</v>
@@ -18214,13 +18214,13 @@
         <v>16.95640367617869</v>
       </c>
       <c r="AB43" s="86" t="n">
-        <v>2.193667190699784</v>
+        <v>2.193667190699756</v>
       </c>
       <c r="AC43" s="86" t="n">
-        <v>3.457749553440184</v>
+        <v>3.45774955344016</v>
       </c>
       <c r="AD43" s="86" t="n">
-        <v>-1.2640823627404</v>
+        <v>-1.264082362740404</v>
       </c>
       <c r="AE43" s="83" t="n">
         <v>215.4756927643863</v>
@@ -18387,16 +18387,16 @@
         <v>67.35035332761086</v>
       </c>
       <c r="AA44" s="28" t="n">
-        <v>34.14288292589834</v>
+        <v>34.14288292589833</v>
       </c>
       <c r="AB44" s="75" t="n">
-        <v>11.0177636114114</v>
+        <v>11.01776361141131</v>
       </c>
       <c r="AC44" s="75" t="n">
-        <v>11.08754427831964</v>
+        <v>11.08754427831954</v>
       </c>
       <c r="AD44" s="75" t="n">
-        <v>-0.06978066690824214</v>
+        <v>-0.06978066690822615</v>
       </c>
       <c r="AE44" s="72" t="n">
         <v>173.6126372910695</v>
@@ -18429,7 +18429,7 @@
         <v>49.69256229211258</v>
       </c>
       <c r="AO44" s="77" t="n">
-        <v>4.492596866136232</v>
+        <v>4.492596866136233</v>
       </c>
       <c r="AP44" s="72" t="n">
         <v>207.5200042724609</v>
@@ -18557,22 +18557,22 @@
         <v>1.047450115745411</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>44.09796519135162</v>
+        <v>44.09796519135161</v>
       </c>
       <c r="Z45" s="35" t="n">
         <v>39.12086978490128</v>
       </c>
       <c r="AA45" s="35" t="n">
-        <v>13.74949472711634</v>
+        <v>13.74949472711633</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-3.872920918790726</v>
+        <v>-3.872920918790754</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-4.869944222879874</v>
+        <v>-4.869944222879901</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>0.9970233040891481</v>
+        <v>0.9970233040891472</v>
       </c>
       <c r="AE45" s="83" t="n">
         <v>160.8908389070311</v>
@@ -18590,19 +18590,19 @@
         <v>168.050599822998</v>
       </c>
       <c r="AJ45" s="83" t="n">
-        <v>169.6973282336339</v>
+        <v>169.697328233634</v>
       </c>
       <c r="AK45" s="83" t="n">
         <v>159.9134994506836</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>150.1296706677333</v>
+        <v>150.1296706677332</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>0.5330391159868196</v>
+        <v>0.5330391159868195</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>12.23640132516469</v>
+        <v>12.23640132516476</v>
       </c>
       <c r="AO45" s="88" t="n">
         <v>4.095278023158961</v>
@@ -18742,16 +18742,16 @@
         <v>17.6636249296569</v>
       </c>
       <c r="AB46" s="75" t="n">
-        <v>-2.000396011197012</v>
+        <v>-2.00039601119704</v>
       </c>
       <c r="AC46" s="75" t="n">
-        <v>-1.481873586465505</v>
+        <v>-1.481873586465541</v>
       </c>
       <c r="AD46" s="75" t="n">
-        <v>-0.5185224247315068</v>
+        <v>-0.5185224247314988</v>
       </c>
       <c r="AE46" s="72" t="n">
-        <v>72.77248848956189</v>
+        <v>72.77248848956191</v>
       </c>
       <c r="AF46" s="72" t="n">
         <v>74.93590971967674</v>
@@ -18766,22 +18766,22 @@
         <v>78.8372251701355</v>
       </c>
       <c r="AJ46" s="72" t="n">
-        <v>87.5601485525662</v>
+        <v>87.56014855256619</v>
       </c>
       <c r="AK46" s="72" t="n">
         <v>74.29099998474121</v>
       </c>
       <c r="AL46" s="72" t="n">
-        <v>61.02185141691621</v>
+        <v>61.02185141691622</v>
       </c>
       <c r="AM46" s="76" t="n">
-        <v>0.2218737779253878</v>
+        <v>0.2218737779253877</v>
       </c>
       <c r="AN46" s="29" t="n">
-        <v>35.72208900284119</v>
+        <v>35.72208900284117</v>
       </c>
       <c r="AO46" s="77" t="n">
-        <v>8.250239581420423</v>
+        <v>8.250239581420422</v>
       </c>
       <c r="AP46" s="72" t="n">
         <v>151</v>
@@ -18918,13 +18918,13 @@
         <v>13.77857993538297</v>
       </c>
       <c r="AB47" s="86" t="n">
-        <v>12.63685015587885</v>
+        <v>12.63685015587862</v>
       </c>
       <c r="AC47" s="86" t="n">
-        <v>-12.07585240879896</v>
+        <v>-12.07585240879916</v>
       </c>
       <c r="AD47" s="86" t="n">
-        <v>24.71270256467781</v>
+        <v>24.71270256467778</v>
       </c>
       <c r="AE47" s="83" t="n">
         <v>1530.141514548923</v>
@@ -19085,28 +19085,28 @@
         <v>0.8692681028281307</v>
       </c>
       <c r="Y48" s="28" t="n">
-        <v>51.90591109126196</v>
+        <v>51.90591109126197</v>
       </c>
       <c r="Z48" s="28" t="n">
         <v>68.12476167500641</v>
       </c>
       <c r="AA48" s="28" t="n">
-        <v>20.53622947824116</v>
+        <v>20.53622947824115</v>
       </c>
       <c r="AB48" s="75" t="n">
         <v>-1.733190211387864</v>
       </c>
       <c r="AC48" s="75" t="n">
-        <v>-6.86434699071259</v>
+        <v>-6.864346990712641</v>
       </c>
       <c r="AD48" s="75" t="n">
-        <v>5.131156779324725</v>
+        <v>5.131156779324777</v>
       </c>
       <c r="AE48" s="72" t="n">
         <v>346.8320925015909</v>
       </c>
       <c r="AF48" s="72" t="n">
-        <v>343.7415393104788</v>
+        <v>343.7415393104786</v>
       </c>
       <c r="AG48" s="72" t="n">
         <v>363.7299975585938</v>
@@ -19118,7 +19118,7 @@
         <v>402.2847497558594</v>
       </c>
       <c r="AJ48" s="72" t="n">
-        <v>363.4973731917045</v>
+        <v>363.4973731917044</v>
       </c>
       <c r="AK48" s="72" t="n">
         <v>332.2689971923828</v>
@@ -19127,13 +19127,13 @@
         <v>301.0406211930612</v>
       </c>
       <c r="AM48" s="76" t="n">
-        <v>0.7878952592348666</v>
+        <v>0.7878952592348671</v>
       </c>
       <c r="AN48" s="29" t="n">
-        <v>18.79704472171414</v>
+        <v>18.79704472171411</v>
       </c>
       <c r="AO48" s="77" t="n">
-        <v>3.859678101369739</v>
+        <v>3.85967810136974</v>
       </c>
       <c r="AP48" s="72" t="n">
         <v>498.8299865722656</v>
@@ -19576,7 +19576,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 26 Aug 2026, 06:03 PM · Yahoo Finance data</t>
+          <t>Built 26 Aug 2026, 10:05 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -20101,16 +20101,16 @@
         <v>6.510674165151912</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>15.52801771518155</v>
+        <v>15.52801771518154</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>0.001266297996863841</v>
+        <v>0.001266297996892263</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>0.8298024726609861</v>
+        <v>0.8298024726609901</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-0.8285361746641222</v>
+        <v>-0.8285361746640978</v>
       </c>
       <c r="AE7" s="72" t="n">
         <v>181.8510165371582</v>
@@ -20285,16 +20285,16 @@
         <v>3.440791380822645</v>
       </c>
       <c r="AC8" s="86" t="n">
-        <v>2.823570565703393</v>
+        <v>2.823570565703399</v>
       </c>
       <c r="AD8" s="86" t="n">
-        <v>0.6172208151192522</v>
+        <v>0.617220815119246</v>
       </c>
       <c r="AE8" s="83" t="n">
         <v>171.8552315191494</v>
       </c>
       <c r="AF8" s="83" t="n">
-        <v>168.0940543414111</v>
+        <v>168.094054341411</v>
       </c>
       <c r="AG8" s="83" t="n">
         <v>162.1185998535156</v>
@@ -20321,7 +20321,7 @@
         <v>9.595501221207106</v>
       </c>
       <c r="AO8" s="88" t="n">
-        <v>1.710516517839049</v>
+        <v>1.71051651783905</v>
       </c>
       <c r="AP8" s="83" t="n">
         <v>176.6000061035156</v>
@@ -20451,28 +20451,28 @@
         <v>1.038224318278488</v>
       </c>
       <c r="Y9" s="28" t="n">
-        <v>61.33102900034046</v>
+        <v>61.33102900034044</v>
       </c>
       <c r="Z9" s="28" t="n">
         <v>87.33342488606772</v>
       </c>
       <c r="AA9" s="28" t="n">
-        <v>26.13488787665906</v>
+        <v>26.13488787665904</v>
       </c>
       <c r="AB9" s="75" t="n">
         <v>0.4743883976317136</v>
       </c>
       <c r="AC9" s="75" t="n">
-        <v>0.5995168122424568</v>
+        <v>0.5995168122424571</v>
       </c>
       <c r="AD9" s="75" t="n">
-        <v>-0.1251284146107432</v>
+        <v>-0.1251284146107435</v>
       </c>
       <c r="AE9" s="72" t="n">
         <v>57.69697745455988</v>
       </c>
       <c r="AF9" s="72" t="n">
-        <v>57.37218351260537</v>
+        <v>57.37218351260535</v>
       </c>
       <c r="AG9" s="72" t="n">
         <v>56.09520011901856</v>
@@ -20635,22 +20635,22 @@
         <v>79.05142154083688</v>
       </c>
       <c r="AA10" s="35" t="n">
-        <v>28.6193713834481</v>
+        <v>28.61937138344809</v>
       </c>
       <c r="AB10" s="86" t="n">
-        <v>1.657845939268945</v>
+        <v>1.657845939268974</v>
       </c>
       <c r="AC10" s="86" t="n">
-        <v>1.399056306768842</v>
+        <v>1.399056306768862</v>
       </c>
       <c r="AD10" s="86" t="n">
-        <v>0.2587896325001031</v>
+        <v>0.2587896325001116</v>
       </c>
       <c r="AE10" s="83" t="n">
-        <v>62.73357781915988</v>
+        <v>62.73357781915987</v>
       </c>
       <c r="AF10" s="83" t="n">
-        <v>60.93134295323989</v>
+        <v>60.9313429532399</v>
       </c>
       <c r="AG10" s="83" t="n">
         <v>57.62520027160645</v>
@@ -20662,7 +20662,7 @@
         <v>53.99649990081787</v>
       </c>
       <c r="AJ10" s="83" t="n">
-        <v>65.01290962616201</v>
+        <v>65.01290962616203</v>
       </c>
       <c r="AK10" s="83" t="n">
         <v>60.52300033569336</v>
@@ -20671,10 +20671,10 @@
         <v>56.0330910452247</v>
       </c>
       <c r="AM10" s="87" t="n">
-        <v>0.7880904832698942</v>
+        <v>0.7880904832698928</v>
       </c>
       <c r="AN10" s="36" t="n">
-        <v>14.83703473246596</v>
+        <v>14.83703473246598</v>
       </c>
       <c r="AO10" s="88" t="n">
         <v>1.866402773841495</v>
@@ -20813,19 +20813,19 @@
         <v>99.42184168340651</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>16.66330470751811</v>
+        <v>16.66330470751809</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.4264230586970399</v>
+        <v>0.4264230586970257</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.3033202021949561</v>
+        <v>0.3033202021949475</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>0.1231028565020837</v>
+        <v>0.1231028565020781</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>86.04757080215975</v>
+        <v>86.04757080215977</v>
       </c>
       <c r="AF11" s="72" t="n">
         <v>85.53906124557946</v>
@@ -20994,13 +20994,13 @@
         <v>16.34810254987358</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.6188946513170066</v>
+        <v>0.6188946513169782</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.6239742362288402</v>
+        <v>0.6239742362288208</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.005079584911833579</v>
+        <v>-0.005079584911842572</v>
       </c>
       <c r="AE12" s="83" t="n">
         <v>117.7728753917443</v>
@@ -21033,7 +21033,7 @@
         <v>7.944640234794374</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.49987609050055</v>
+        <v>1.499876090500551</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -21172,13 +21172,13 @@
         <v>10.9981447347795</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.4000286433001037</v>
+        <v>0.4000286433001179</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.3107969549527634</v>
+        <v>0.3107969549527773</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>0.0892316883473403</v>
+        <v>0.08923168834734063</v>
       </c>
       <c r="AE13" s="72" t="n">
         <v>111.419623380932</v>
@@ -21341,28 +21341,28 @@
         <v>1.10760506699593</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>61.44960602522442</v>
+        <v>61.44960602522443</v>
       </c>
       <c r="Z14" s="35" t="n">
         <v>75.0001172551049</v>
       </c>
       <c r="AA14" s="35" t="n">
-        <v>12.97272000214231</v>
+        <v>12.9727200021423</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.4654641226589078</v>
+        <v>0.465464122658922</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.3855984160355234</v>
+        <v>0.3855984160355256</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>0.07986570662338438</v>
+        <v>0.07986570662339637</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>52.83019175319198</v>
+        <v>52.830191753192</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.31529899459684</v>
+        <v>52.31529899459685</v>
       </c>
       <c r="AG14" s="83" t="n">
         <v>51.62859992980957</v>
@@ -21374,7 +21374,7 @@
         <v>49.63344999313355</v>
       </c>
       <c r="AJ14" s="83" t="n">
-        <v>53.86940066273213</v>
+        <v>53.86940066273212</v>
       </c>
       <c r="AK14" s="83" t="n">
         <v>52.33800029754639</v>
@@ -21383,10 +21383,10 @@
         <v>50.80659993236065</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.9055117008404467</v>
+        <v>0.9055117008404486</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>5.851963607625764</v>
+        <v>5.851963607625736</v>
       </c>
       <c r="AO14" s="88" t="n">
         <v>1.630320620815234</v>
@@ -21528,13 +21528,13 @@
         <v>14.59244705880463</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.8640174307540747</v>
+        <v>0.8640174307540462</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>1.4402285107176</v>
+        <v>1.440228510717541</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.5762110799635252</v>
+        <v>-0.5762110799634943</v>
       </c>
       <c r="AE15" s="72" t="n">
         <v>184.0726035250573</v>
@@ -21567,7 +21567,7 @@
         <v>14.12477405031726</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.367366147845958</v>
+        <v>2.367366147845959</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -21697,28 +21697,28 @@
         <v>0.7238578387778541</v>
       </c>
       <c r="Y16" s="35" t="n">
-        <v>54.97425180331379</v>
+        <v>54.97425180331378</v>
       </c>
       <c r="Z16" s="35" t="n">
         <v>86.27459291265356</v>
       </c>
       <c r="AA16" s="35" t="n">
-        <v>8.82492583464386</v>
+        <v>8.824925834643864</v>
       </c>
       <c r="AB16" s="86" t="n">
         <v>0.03333560231789079</v>
       </c>
       <c r="AC16" s="86" t="n">
-        <v>0.01184111858141387</v>
+        <v>0.01184111858141457</v>
       </c>
       <c r="AD16" s="86" t="n">
-        <v>0.02149448373647692</v>
+        <v>0.02149448373647622</v>
       </c>
       <c r="AE16" s="83" t="n">
         <v>45.03559745071438</v>
       </c>
       <c r="AF16" s="83" t="n">
-        <v>44.99080981226599</v>
+        <v>44.99080981226598</v>
       </c>
       <c r="AG16" s="83" t="n">
         <v>44.87600021362304</v>
@@ -21884,19 +21884,19 @@
         <v>12.60132502946572</v>
       </c>
       <c r="AB17" s="75" t="n">
-        <v>-0.4121059616870113</v>
+        <v>-0.4121059616870042</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.3583364133078443</v>
+        <v>-0.3583364133078425</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.05376954837916698</v>
+        <v>-0.0537695483791617</v>
       </c>
       <c r="AE17" s="72" t="n">
-        <v>43.59321163792701</v>
+        <v>43.59321163792702</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>44.03526815081218</v>
+        <v>44.03526815081219</v>
       </c>
       <c r="AG17" s="72" t="n">
         <v>44.80860015869141</v>
@@ -22072,7 +22072,7 @@
         <v>0.70891381373025</v>
       </c>
       <c r="Y19" s="28" t="n">
-        <v>52.13750990307586</v>
+        <v>52.13750990307587</v>
       </c>
       <c r="Z19" s="28" t="n">
         <v>8.251536443200028</v>
@@ -22081,19 +22081,19 @@
         <v>17.95435869078781</v>
       </c>
       <c r="AB19" s="75" t="n">
-        <v>4.944955086365326</v>
+        <v>4.944955086365553</v>
       </c>
       <c r="AC19" s="75" t="n">
-        <v>6.239829809339442</v>
+        <v>6.239829809339686</v>
       </c>
       <c r="AD19" s="75" t="n">
-        <v>-1.294874722974116</v>
+        <v>-1.294874722974133</v>
       </c>
       <c r="AE19" s="72" t="n">
-        <v>766.8969664750223</v>
+        <v>766.8969664750225</v>
       </c>
       <c r="AF19" s="72" t="n">
-        <v>763.3293448981902</v>
+        <v>763.32934489819</v>
       </c>
       <c r="AG19" s="72" t="n">
         <v>752.2638037109375</v>
@@ -22257,16 +22257,16 @@
         <v>14.80645522481141</v>
       </c>
       <c r="AB20" s="86" t="n">
-        <v>2.281379025780325</v>
+        <v>2.281379025780552</v>
       </c>
       <c r="AC20" s="86" t="n">
-        <v>3.159637653257046</v>
+        <v>3.159637653257295</v>
       </c>
       <c r="AD20" s="86" t="n">
-        <v>-0.8782586274767215</v>
+        <v>-0.8782586274767428</v>
       </c>
       <c r="AE20" s="83" t="n">
-        <v>714.9757997843772</v>
+        <v>714.9757997843773</v>
       </c>
       <c r="AF20" s="83" t="n">
         <v>713.4860945214556</v>
@@ -22281,19 +22281,19 @@
         <v>653.2152496337891</v>
       </c>
       <c r="AJ20" s="83" t="n">
-        <v>747.9741017331664</v>
+        <v>747.9741017331665</v>
       </c>
       <c r="AK20" s="83" t="n">
         <v>710.3985015869141</v>
       </c>
       <c r="AL20" s="83" t="n">
-        <v>672.8229014406618</v>
+        <v>672.8229014406617</v>
       </c>
       <c r="AM20" s="87" t="n">
-        <v>0.4457294860651463</v>
+        <v>0.4457294860651465</v>
       </c>
       <c r="AN20" s="36" t="n">
-        <v>10.57873857062327</v>
+        <v>10.5787385706233</v>
       </c>
       <c r="AO20" s="88" t="n">
         <v>1.597328558937709</v>
@@ -22433,19 +22433,19 @@
         <v>13.87344486921295</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>1.461630843610408</v>
+        <v>1.461630843610465</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>1.907158197343715</v>
+        <v>1.907158197343771</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.4455273537333071</v>
+        <v>-0.4455273537333064</v>
       </c>
       <c r="AE21" s="72" t="n">
         <v>300.0228466223634</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>299.0474909215284</v>
+        <v>299.0474909215283</v>
       </c>
       <c r="AG21" s="72" t="n">
         <v>296.830200805664</v>
@@ -22600,22 +22600,22 @@
         <v>0.92526444393878</v>
       </c>
       <c r="Y22" s="35" t="n">
-        <v>39.14760912581253</v>
+        <v>39.14760912581254</v>
       </c>
       <c r="Z22" s="35" t="n">
         <v>10.13355036853932</v>
       </c>
       <c r="AA22" s="35" t="n">
-        <v>19.58392441564625</v>
+        <v>19.58392441564624</v>
       </c>
       <c r="AB22" s="86" t="n">
-        <v>-10.14637804046174</v>
+        <v>-10.1463780404618</v>
       </c>
       <c r="AC22" s="86" t="n">
-        <v>-10.37832506210884</v>
+        <v>-10.37832506210893</v>
       </c>
       <c r="AD22" s="86" t="n">
-        <v>0.2319470216471018</v>
+        <v>0.2319470216471302</v>
       </c>
       <c r="AE22" s="83" t="n">
         <v>125.2810456156637</v>
@@ -22639,13 +22639,13 @@
         <v>127.1520004272461</v>
       </c>
       <c r="AL22" s="83" t="n">
-        <v>98.07313298411459</v>
+        <v>98.07313298411464</v>
       </c>
       <c r="AM22" s="87" t="n">
-        <v>0.2250237342219106</v>
+        <v>0.2250237342219102</v>
       </c>
       <c r="AN22" s="36" t="n">
-        <v>45.7387494422785</v>
+        <v>45.73874944227845</v>
       </c>
       <c r="AO22" s="88" t="n">
         <v>16.52525674855665</v>
@@ -22797,28 +22797,28 @@
         <v>0.6633173923486143</v>
       </c>
       <c r="Y24" s="28" t="n">
-        <v>48.23383138538887</v>
+        <v>48.23383138538886</v>
       </c>
       <c r="Z24" s="28" t="n">
         <v>49.56871257879067</v>
       </c>
       <c r="AA24" s="28" t="n">
-        <v>16.51930729278539</v>
+        <v>16.5193072927854</v>
       </c>
       <c r="AB24" s="75" t="n">
         <v>-1.488307039805818</v>
       </c>
       <c r="AC24" s="75" t="n">
-        <v>-1.253165158389287</v>
+        <v>-1.253165158389309</v>
       </c>
       <c r="AD24" s="75" t="n">
-        <v>-0.2351418814165311</v>
+        <v>-0.2351418814165092</v>
       </c>
       <c r="AE24" s="72" t="n">
         <v>310.1711931132225</v>
       </c>
       <c r="AF24" s="72" t="n">
-        <v>311.9633557589049</v>
+        <v>311.9633557589048</v>
       </c>
       <c r="AG24" s="72" t="n">
         <v>310.5021997070313</v>
@@ -22845,7 +22845,7 @@
         <v>13.78243183760062</v>
       </c>
       <c r="AO24" s="77" t="n">
-        <v>2.37629136440265</v>
+        <v>2.376291364402649</v>
       </c>
       <c r="AP24" s="72" t="n">
         <v>344.5700073242188</v>
@@ -22982,19 +22982,19 @@
         <v>10.29570933916031</v>
       </c>
       <c r="AB25" s="86" t="n">
-        <v>-9.190256584080487</v>
+        <v>-9.19025658408043</v>
       </c>
       <c r="AC25" s="86" t="n">
-        <v>-7.340513252483795</v>
+        <v>-7.340513252483797</v>
       </c>
       <c r="AD25" s="86" t="n">
-        <v>-1.849743331596692</v>
+        <v>-1.849743331596633</v>
       </c>
       <c r="AE25" s="83" t="n">
-        <v>474.9587390380239</v>
+        <v>474.958739038024</v>
       </c>
       <c r="AF25" s="83" t="n">
-        <v>485.5688247186116</v>
+        <v>485.5688247186115</v>
       </c>
       <c r="AG25" s="83" t="n">
         <v>509.6002008056641</v>
@@ -23006,7 +23006,7 @@
         <v>330.8967504119873</v>
       </c>
       <c r="AJ25" s="83" t="n">
-        <v>518.5745909204478</v>
+        <v>518.5745909204477</v>
       </c>
       <c r="AK25" s="83" t="n">
         <v>479.2055023193359</v>
@@ -23015,10 +23015,10 @@
         <v>439.8364137182242</v>
       </c>
       <c r="AM25" s="87" t="n">
-        <v>0.2148079480978662</v>
+        <v>0.2148079480978665</v>
       </c>
       <c r="AN25" s="36" t="n">
-        <v>16.43098353861422</v>
+        <v>16.43098353861419</v>
       </c>
       <c r="AO25" s="88" t="n">
         <v>6.121638726350519</v>
@@ -23158,16 +23158,16 @@
         <v>21.64156825055758</v>
       </c>
       <c r="AB26" s="75" t="n">
-        <v>3.159031902194272</v>
+        <v>3.159031902194215</v>
       </c>
       <c r="AC26" s="75" t="n">
-        <v>4.630796889602698</v>
+        <v>4.630796889602659</v>
       </c>
       <c r="AD26" s="75" t="n">
-        <v>-1.471764987408426</v>
+        <v>-1.471764987408444</v>
       </c>
       <c r="AE26" s="72" t="n">
-        <v>262.420514943825</v>
+        <v>262.4205149438249</v>
       </c>
       <c r="AF26" s="72" t="n">
         <v>260.641665456252</v>
@@ -23197,7 +23197,7 @@
         <v>22.90457774061986</v>
       </c>
       <c r="AO26" s="77" t="n">
-        <v>2.778788248157326</v>
+        <v>2.778788248157327</v>
       </c>
       <c r="AP26" s="72" t="n">
         <v>287.2000122070312</v>
@@ -23334,13 +23334,13 @@
         <v>21.34681728110727</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>1.99662760098785</v>
+        <v>1.996627600987821</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>1.264885018343358</v>
+        <v>1.26488501834335</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.7317425826444917</v>
+        <v>0.7317425826444719</v>
       </c>
       <c r="AE27" s="83" t="n">
         <v>82.71836193206687</v>
@@ -23507,16 +23507,16 @@
         <v>8.318819046905595</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>11.855316937283</v>
+        <v>11.85531693728299</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-10.68280546545407</v>
+        <v>-10.68280546545412</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-9.436738179570133</v>
+        <v>-9.436738179570153</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-1.246067285883933</v>
+        <v>-1.246067285883971</v>
       </c>
       <c r="AE28" s="72" t="n">
         <v>253.2034912718328</v>
@@ -23549,7 +23549,7 @@
         <v>28.05085291131589</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>8.427240984724294</v>
+        <v>8.427240984724296</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -23677,22 +23677,22 @@
         <v>1.024097761438337</v>
       </c>
       <c r="Y29" s="35" t="n">
-        <v>43.18431389434733</v>
+        <v>43.18431389434735</v>
       </c>
       <c r="Z29" s="35" t="n">
         <v>0.3132114283187939</v>
       </c>
       <c r="AA29" s="35" t="n">
-        <v>14.55106175706805</v>
+        <v>14.55106175706804</v>
       </c>
       <c r="AB29" s="86" t="n">
         <v>-0.6188627205917498</v>
       </c>
       <c r="AC29" s="86" t="n">
-        <v>-0.5915863587479211</v>
+        <v>-0.5915863587479292</v>
       </c>
       <c r="AD29" s="86" t="n">
-        <v>-0.02727636184382876</v>
+        <v>-0.02727636184382065</v>
       </c>
       <c r="AE29" s="83" t="n">
         <v>66.85818436762595</v>
@@ -23719,10 +23719,10 @@
         <v>54.98871647308493</v>
       </c>
       <c r="AM29" s="87" t="n">
-        <v>0.3248068744086</v>
+        <v>0.3248068744086002</v>
       </c>
       <c r="AN29" s="36" t="n">
-        <v>34.17279135758569</v>
+        <v>34.1727913575857</v>
       </c>
       <c r="AO29" s="88" t="n">
         <v>8.588127014634134</v>
@@ -23865,16 +23865,16 @@
         <v>-6.561188199296907</v>
       </c>
       <c r="AC30" s="75" t="n">
-        <v>-0.3487052785677137</v>
+        <v>-0.3487052785676928</v>
       </c>
       <c r="AD30" s="75" t="n">
-        <v>-6.212482920729194</v>
+        <v>-6.212482920729214</v>
       </c>
       <c r="AE30" s="72" t="n">
         <v>376.6721007892146</v>
       </c>
       <c r="AF30" s="72" t="n">
-        <v>388.1994366565307</v>
+        <v>388.1994366565309</v>
       </c>
       <c r="AG30" s="72" t="n">
         <v>387.9666003417969</v>
@@ -23901,7 +23901,7 @@
         <v>22.80375221633569</v>
       </c>
       <c r="AO30" s="77" t="n">
-        <v>4.149058753351587</v>
+        <v>4.149058753351586</v>
       </c>
       <c r="AP30" s="72" t="n">
         <v>495</v>
@@ -24035,22 +24035,22 @@
         <v>86.76331944180255</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>17.1794443379402</v>
+        <v>17.17944433794019</v>
       </c>
       <c r="AB31" s="86" t="n">
         <v>1.665747393891223</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>0.7316276941390637</v>
+        <v>0.7316276941390538</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>0.9341196997521596</v>
+        <v>0.9341196997521695</v>
       </c>
       <c r="AE31" s="83" t="n">
         <v>98.94162570067309</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>96.44094098058883</v>
+        <v>96.44094098058885</v>
       </c>
       <c r="AG31" s="83" t="n">
         <v>96.20999969482422</v>
@@ -24205,7 +24205,7 @@
         <v>0.587215510977416</v>
       </c>
       <c r="Y32" s="28" t="n">
-        <v>46.7912006314573</v>
+        <v>46.79120063145731</v>
       </c>
       <c r="Z32" s="28" t="n">
         <v>8.814936156699684</v>
@@ -24214,19 +24214,19 @@
         <v>16.7703150941502</v>
       </c>
       <c r="AB32" s="75" t="n">
-        <v>1.732497281662901</v>
+        <v>1.732497281662887</v>
       </c>
       <c r="AC32" s="75" t="n">
-        <v>2.228334064790922</v>
+        <v>2.228334064790904</v>
       </c>
       <c r="AD32" s="75" t="n">
-        <v>-0.4958367831280204</v>
+        <v>-0.4958367831280173</v>
       </c>
       <c r="AE32" s="72" t="n">
-        <v>91.62430848447219</v>
+        <v>91.62430848447221</v>
       </c>
       <c r="AF32" s="72" t="n">
-        <v>90.23423991241337</v>
+        <v>90.23423991241339</v>
       </c>
       <c r="AG32" s="72" t="n">
         <v>89.72600021362305</v>
@@ -24244,16 +24244,16 @@
         <v>88.45150070190429</v>
       </c>
       <c r="AL32" s="72" t="n">
-        <v>63.730184300894</v>
+        <v>63.73018430089402</v>
       </c>
       <c r="AM32" s="76" t="n">
-        <v>0.4554736352588746</v>
+        <v>0.4554736352588747</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>55.89801462911316</v>
+        <v>55.8980146291131</v>
       </c>
       <c r="AO32" s="77" t="n">
-        <v>9.062785159407174</v>
+        <v>9.062785159407172</v>
       </c>
       <c r="AP32" s="72" t="n">
         <v>153.1999969482422</v>
@@ -24390,16 +24390,16 @@
         <v>11.2192678986343</v>
       </c>
       <c r="AB33" s="86" t="n">
-        <v>8.251866986124924</v>
+        <v>8.251866986125094</v>
       </c>
       <c r="AC33" s="86" t="n">
-        <v>13.05754819759189</v>
+        <v>13.05754819759204</v>
       </c>
       <c r="AD33" s="86" t="n">
-        <v>-4.80568121146697</v>
+        <v>-4.805681211466949</v>
       </c>
       <c r="AE33" s="83" t="n">
-        <v>448.8661484797525</v>
+        <v>448.8661484797526</v>
       </c>
       <c r="AF33" s="83" t="n">
         <v>445.50661428746</v>
@@ -24429,7 +24429,7 @@
         <v>29.32288306485896</v>
       </c>
       <c r="AO33" s="88" t="n">
-        <v>6.973462265728886</v>
+        <v>6.973462265728887</v>
       </c>
       <c r="AP33" s="83" t="n">
         <v>514</v>
@@ -24563,22 +24563,22 @@
         <v>18.44869815470224</v>
       </c>
       <c r="AA34" s="28" t="n">
-        <v>8.951216491266592</v>
+        <v>8.951216491266596</v>
       </c>
       <c r="AB34" s="75" t="n">
-        <v>-2.445818641401104</v>
+        <v>-2.445818641401218</v>
       </c>
       <c r="AC34" s="75" t="n">
-        <v>-1.9855670793317</v>
+        <v>-1.985567079331768</v>
       </c>
       <c r="AD34" s="75" t="n">
-        <v>-0.4602515620694037</v>
+        <v>-0.4602515620694494</v>
       </c>
       <c r="AE34" s="72" t="n">
-        <v>343.1352463817793</v>
+        <v>343.1352463817794</v>
       </c>
       <c r="AF34" s="72" t="n">
-        <v>345.7780228735336</v>
+        <v>345.7780228735338</v>
       </c>
       <c r="AG34" s="72" t="n">
         <v>349.9177996826172</v>
@@ -24590,7 +24590,7 @@
         <v>332.3968493652344</v>
       </c>
       <c r="AJ34" s="72" t="n">
-        <v>370.9249896637275</v>
+        <v>370.9249896637274</v>
       </c>
       <c r="AK34" s="72" t="n">
         <v>347.7195022583008</v>
@@ -24599,10 +24599,10 @@
         <v>324.5140148528741</v>
       </c>
       <c r="AM34" s="76" t="n">
-        <v>0.4325697007407326</v>
+        <v>0.4325697007407324</v>
       </c>
       <c r="AN34" s="29" t="n">
-        <v>13.34724526793363</v>
+        <v>13.3472452679336</v>
       </c>
       <c r="AO34" s="77" t="n">
         <v>2.599068889147551</v>
@@ -24733,7 +24733,7 @@
         <v>0.7000967939287043</v>
       </c>
       <c r="Y35" s="35" t="n">
-        <v>46.60917014066867</v>
+        <v>46.60917014066866</v>
       </c>
       <c r="Z35" s="35" t="n">
         <v>22.55266125959701</v>
@@ -24742,16 +24742,16 @@
         <v>15.47768873756793</v>
       </c>
       <c r="AB35" s="86" t="n">
-        <v>0.1309167012516212</v>
+        <v>0.1309167012515999</v>
       </c>
       <c r="AC35" s="86" t="n">
-        <v>-0.1752613660197027</v>
+        <v>-0.1752613660197151</v>
       </c>
       <c r="AD35" s="86" t="n">
-        <v>0.3061780672713239</v>
+        <v>0.306178067271315</v>
       </c>
       <c r="AE35" s="83" t="n">
-        <v>41.78931530180552</v>
+        <v>41.78931530180551</v>
       </c>
       <c r="AF35" s="83" t="n">
         <v>41.31375797386418</v>
@@ -24766,22 +24766,22 @@
         <v>46.47905006408691</v>
       </c>
       <c r="AJ35" s="83" t="n">
-        <v>47.4828183975126</v>
+        <v>47.48281839751259</v>
       </c>
       <c r="AK35" s="83" t="n">
         <v>40.0979998588562</v>
       </c>
       <c r="AL35" s="83" t="n">
-        <v>32.71318132019979</v>
+        <v>32.71318132019981</v>
       </c>
       <c r="AM35" s="87" t="n">
-        <v>0.4805006389759185</v>
+        <v>0.4805006389759184</v>
       </c>
       <c r="AN35" s="36" t="n">
-        <v>36.83384989102076</v>
+        <v>36.83384989102068</v>
       </c>
       <c r="AO35" s="88" t="n">
-        <v>9.576513849237326</v>
+        <v>9.576513849237328</v>
       </c>
       <c r="AP35" s="83" t="n">
         <v>76.87000274658203</v>
@@ -24915,16 +24915,16 @@
         <v>9.451639401417374</v>
       </c>
       <c r="AA36" s="28" t="n">
-        <v>15.63251842631684</v>
+        <v>15.63251842631685</v>
       </c>
       <c r="AB36" s="75" t="n">
-        <v>-3.151020755259594</v>
+        <v>-3.15102075525958</v>
       </c>
       <c r="AC36" s="75" t="n">
-        <v>-2.587171599436873</v>
+        <v>-2.58717159943685</v>
       </c>
       <c r="AD36" s="75" t="n">
-        <v>-0.5638491558227212</v>
+        <v>-0.5638491558227301</v>
       </c>
       <c r="AE36" s="72" t="n">
         <v>93.66461317921934</v>
@@ -24948,16 +24948,16 @@
         <v>95.47849922180175</v>
       </c>
       <c r="AL36" s="72" t="n">
-        <v>82.79268073680699</v>
+        <v>82.79268073680697</v>
       </c>
       <c r="AM36" s="76" t="n">
-        <v>0.1760754106921673</v>
+        <v>0.1760754106921676</v>
       </c>
       <c r="AN36" s="29" t="n">
-        <v>26.57314178247591</v>
+        <v>26.57314178247594</v>
       </c>
       <c r="AO36" s="77" t="n">
-        <v>7.321699281453084</v>
+        <v>7.321699281453085</v>
       </c>
       <c r="AP36" s="72" t="n">
         <v>142.3500061035156</v>
@@ -25091,16 +25091,16 @@
         <v>27.77476050199683</v>
       </c>
       <c r="AA37" s="35" t="n">
-        <v>34.04642452350934</v>
+        <v>34.04642452350933</v>
       </c>
       <c r="AB37" s="86" t="n">
-        <v>18.90767327113974</v>
+        <v>18.90767327113969</v>
       </c>
       <c r="AC37" s="86" t="n">
-        <v>22.37814339027755</v>
+        <v>22.37814339027748</v>
       </c>
       <c r="AD37" s="86" t="n">
-        <v>-3.470470119137804</v>
+        <v>-3.470470119137797</v>
       </c>
       <c r="AE37" s="83" t="n">
         <v>485.2947541154232</v>
@@ -25267,16 +25267,16 @@
         <v>85.45403316543613</v>
       </c>
       <c r="AA38" s="28" t="n">
-        <v>18.18524406657687</v>
+        <v>18.18524406657689</v>
       </c>
       <c r="AB38" s="75" t="n">
-        <v>3.235248068285046</v>
+        <v>3.23524806828506</v>
       </c>
       <c r="AC38" s="75" t="n">
-        <v>-0.1255648000531346</v>
+        <v>-0.1255648000531507</v>
       </c>
       <c r="AD38" s="75" t="n">
-        <v>3.36081286833818</v>
+        <v>3.36081286833821</v>
       </c>
       <c r="AE38" s="72" t="n">
         <v>108.7947081320521</v>
@@ -25294,19 +25294,19 @@
         <v>143.3328000259399</v>
       </c>
       <c r="AJ38" s="72" t="n">
-        <v>116.348288245455</v>
+        <v>116.3482882454551</v>
       </c>
       <c r="AK38" s="72" t="n">
         <v>99.76800003051758</v>
       </c>
       <c r="AL38" s="72" t="n">
-        <v>83.18771181558014</v>
+        <v>83.18771181558007</v>
       </c>
       <c r="AM38" s="76" t="n">
-        <v>1.189433046233287</v>
+        <v>1.189433046233284</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>33.23768785555643</v>
+        <v>33.23768785555657</v>
       </c>
       <c r="AO38" s="77" t="n">
         <v>5.636796371701839</v>
@@ -25449,16 +25449,16 @@
         <v>8.6148484639657</v>
       </c>
       <c r="AC39" s="86" t="n">
-        <v>1.25500178323038</v>
+        <v>1.255001783230229</v>
       </c>
       <c r="AD39" s="86" t="n">
-        <v>7.35984668073532</v>
+        <v>7.359846680735471</v>
       </c>
       <c r="AE39" s="83" t="n">
         <v>940.7460088684891</v>
       </c>
       <c r="AF39" s="83" t="n">
-        <v>926.2859194932342</v>
+        <v>926.2859194932344</v>
       </c>
       <c r="AG39" s="83" t="n">
         <v>962.8824035644532</v>
@@ -25485,7 +25485,7 @@
         <v>28.27896378781383</v>
       </c>
       <c r="AO39" s="88" t="n">
-        <v>7.428091392184724</v>
+        <v>7.428091392184723</v>
       </c>
       <c r="AP39" s="83" t="n">
         <v>1255</v>
@@ -25625,10 +25625,10 @@
         <v>5.434916180262093</v>
       </c>
       <c r="AC40" s="75" t="n">
-        <v>5.852350125158053</v>
+        <v>5.852350125158037</v>
       </c>
       <c r="AD40" s="75" t="n">
-        <v>-0.4174339448959605</v>
+        <v>-0.4174339448959445</v>
       </c>
       <c r="AE40" s="72" t="n">
         <v>226.3301331075754</v>
@@ -25798,19 +25798,19 @@
         <v>21.80115653752489</v>
       </c>
       <c r="AB41" s="86" t="n">
-        <v>1.570798027465685</v>
+        <v>1.570798027465656</v>
       </c>
       <c r="AC41" s="86" t="n">
-        <v>0.8815592143941187</v>
+        <v>0.8815592143941015</v>
       </c>
       <c r="AD41" s="86" t="n">
-        <v>0.6892388130715661</v>
+        <v>0.6892388130715549</v>
       </c>
       <c r="AE41" s="83" t="n">
-        <v>78.59810838659776</v>
+        <v>78.59810838659774</v>
       </c>
       <c r="AF41" s="83" t="n">
-        <v>76.43982191300984</v>
+        <v>76.43982191300985</v>
       </c>
       <c r="AG41" s="83" t="n">
         <v>74.49519927978515</v>
@@ -25822,19 +25822,19 @@
         <v>88.27092472076416</v>
       </c>
       <c r="AJ41" s="83" t="n">
-        <v>81.24980733566296</v>
+        <v>81.24980733566295</v>
       </c>
       <c r="AK41" s="83" t="n">
         <v>75.7634994506836</v>
       </c>
       <c r="AL41" s="83" t="n">
-        <v>70.27719156570423</v>
+        <v>70.27719156570424</v>
       </c>
       <c r="AM41" s="87" t="n">
-        <v>0.887009148463315</v>
+        <v>0.887009148463316</v>
       </c>
       <c r="AN41" s="36" t="n">
-        <v>14.48272037262626</v>
+        <v>14.48272037262622</v>
       </c>
       <c r="AO41" s="88" t="n">
         <v>2.870929783713489</v>
@@ -25965,22 +25965,22 @@
         <v>0.6030857254328504</v>
       </c>
       <c r="Y42" s="28" t="n">
-        <v>45.52179247622297</v>
+        <v>45.52179247622298</v>
       </c>
       <c r="Z42" s="28" t="n">
         <v>41.79104760874496</v>
       </c>
       <c r="AA42" s="28" t="n">
-        <v>18.13403758358544</v>
+        <v>18.13403758358543</v>
       </c>
       <c r="AB42" s="75" t="n">
-        <v>-0.1810046575677102</v>
+        <v>-0.181004657567712</v>
       </c>
       <c r="AC42" s="75" t="n">
-        <v>-0.3324056117375804</v>
+        <v>-0.3324056117375821</v>
       </c>
       <c r="AD42" s="75" t="n">
-        <v>0.1514009541698702</v>
+        <v>0.1514009541698701</v>
       </c>
       <c r="AE42" s="72" t="n">
         <v>10.14746740455093</v>
@@ -26004,13 +26004,13 @@
         <v>9.752500009536742</v>
       </c>
       <c r="AL42" s="72" t="n">
-        <v>8.467807414855722</v>
+        <v>8.467807414855724</v>
       </c>
       <c r="AM42" s="76" t="n">
-        <v>0.5807586303016524</v>
+        <v>0.5807586303016525</v>
       </c>
       <c r="AN42" s="29" t="n">
-        <v>26.34591322070751</v>
+        <v>26.34591322070747</v>
       </c>
       <c r="AO42" s="77" t="n">
         <v>5.678293464544901</v>
@@ -26141,7 +26141,7 @@
         <v>1.169208088082159</v>
       </c>
       <c r="Y43" s="35" t="n">
-        <v>44.65033667336511</v>
+        <v>44.6503366733651</v>
       </c>
       <c r="Z43" s="35" t="n">
         <v>5.950632977737816</v>
@@ -26150,13 +26150,13 @@
         <v>16.9243929272373</v>
       </c>
       <c r="AB43" s="86" t="n">
-        <v>2.646934448834742</v>
+        <v>2.646934448834713</v>
       </c>
       <c r="AC43" s="86" t="n">
-        <v>3.773770144125284</v>
+        <v>3.773770144125261</v>
       </c>
       <c r="AD43" s="86" t="n">
-        <v>-1.126835695290542</v>
+        <v>-1.126835695290548</v>
       </c>
       <c r="AE43" s="83" t="n">
         <v>216.1687469679944</v>
@@ -26326,13 +26326,13 @@
         <v>33.34956767636059</v>
       </c>
       <c r="AB44" s="75" t="n">
-        <v>11.68786248597888</v>
+        <v>11.68786248597877</v>
       </c>
       <c r="AC44" s="75" t="n">
-        <v>11.1049894450467</v>
+        <v>11.10498944504659</v>
       </c>
       <c r="AD44" s="75" t="n">
-        <v>0.5828730409321849</v>
+        <v>0.5828730409321761</v>
       </c>
       <c r="AE44" s="72" t="n">
         <v>173.8648205949353</v>
@@ -26365,7 +26365,7 @@
         <v>54.18302231141797</v>
       </c>
       <c r="AO44" s="77" t="n">
-        <v>4.415822626488083</v>
+        <v>4.415822626488084</v>
       </c>
       <c r="AP44" s="72" t="n">
         <v>207.5200042724609</v>
@@ -26493,7 +26493,7 @@
         <v>0.9439130811426099</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>41.51927461755136</v>
+        <v>41.51927461755135</v>
       </c>
       <c r="Z45" s="35" t="n">
         <v>24.2490772061536</v>
@@ -26502,13 +26502,13 @@
         <v>13.99677814056725</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-4.099327031554594</v>
+        <v>-4.099327031554651</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-5.119200048902161</v>
+        <v>-5.119200048902188</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.019873017347567</v>
+        <v>1.019873017347537</v>
       </c>
       <c r="AE45" s="83" t="n">
         <v>160.9853650065846</v>
@@ -26526,19 +26526,19 @@
         <v>168.1463998413086</v>
       </c>
       <c r="AJ45" s="83" t="n">
-        <v>169.8959034296253</v>
+        <v>169.8959034296254</v>
       </c>
       <c r="AK45" s="83" t="n">
         <v>160.0294998168945</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>150.1630962041638</v>
+        <v>150.1630962041637</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>0.4240097457769294</v>
+        <v>0.4240097457769298</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>12.33073105148726</v>
+        <v>12.33073105148733</v>
       </c>
       <c r="AO45" s="88" t="n">
         <v>4.308590089375146</v>
@@ -26678,16 +26678,16 @@
         <v>17.44649804763646</v>
       </c>
       <c r="AB46" s="75" t="n">
-        <v>-1.459246328032151</v>
+        <v>-1.459246328032194</v>
       </c>
       <c r="AC46" s="75" t="n">
-        <v>-1.352242980282628</v>
+        <v>-1.352242980282667</v>
       </c>
       <c r="AD46" s="75" t="n">
-        <v>-0.1070033477495231</v>
+        <v>-0.1070033477495271</v>
       </c>
       <c r="AE46" s="72" t="n">
-        <v>74.44748415454832</v>
+        <v>74.44748415454833</v>
       </c>
       <c r="AF46" s="72" t="n">
         <v>75.73850032543348</v>
@@ -26708,16 +26708,16 @@
         <v>74.13999977111817</v>
       </c>
       <c r="AL46" s="72" t="n">
-        <v>60.47546755117597</v>
+        <v>60.47546755117598</v>
       </c>
       <c r="AM46" s="76" t="n">
-        <v>0.28557623131551</v>
+        <v>0.2855762313155098</v>
       </c>
       <c r="AN46" s="29" t="n">
         <v>36.86143043465538</v>
       </c>
       <c r="AO46" s="77" t="n">
-        <v>8.310047221905672</v>
+        <v>8.31004722190567</v>
       </c>
       <c r="AP46" s="72" t="n">
         <v>151</v>
@@ -26851,16 +26851,16 @@
         <v>49.63603807771118</v>
       </c>
       <c r="AA47" s="35" t="n">
-        <v>14.78617484624374</v>
+        <v>14.78617484624373</v>
       </c>
       <c r="AB47" s="86" t="n">
-        <v>16.81702769003323</v>
+        <v>16.817027690033</v>
       </c>
       <c r="AC47" s="86" t="n">
-        <v>-18.25402804996841</v>
+        <v>-18.2540280499686</v>
       </c>
       <c r="AD47" s="86" t="n">
-        <v>35.07105574000164</v>
+        <v>35.0710557400016</v>
       </c>
       <c r="AE47" s="83" t="n">
         <v>1544.247655982544</v>
@@ -26884,13 +26884,13 @@
         <v>1391.875994873047</v>
       </c>
       <c r="AL47" s="83" t="n">
-        <v>993.040226792002</v>
+        <v>993.0402267920019</v>
       </c>
       <c r="AM47" s="87" t="n">
-        <v>0.6269244239693762</v>
+        <v>0.6269244239693761</v>
       </c>
       <c r="AN47" s="36" t="n">
-        <v>57.30909499842659</v>
+        <v>57.30909499842662</v>
       </c>
       <c r="AO47" s="88" t="n">
         <v>10.46563719749731</v>
@@ -27021,28 +27021,28 @@
         <v>1.126156997328464</v>
       </c>
       <c r="Y48" s="28" t="n">
-        <v>51.35058103278162</v>
+        <v>51.35058103278163</v>
       </c>
       <c r="Z48" s="28" t="n">
         <v>65.57476655374727</v>
       </c>
       <c r="AA48" s="28" t="n">
-        <v>20.41690090079842</v>
+        <v>20.41690090079841</v>
       </c>
       <c r="AB48" s="75" t="n">
         <v>-2.507744933149468</v>
       </c>
       <c r="AC48" s="75" t="n">
-        <v>-8.14713618554377</v>
+        <v>-8.147136185543834</v>
       </c>
       <c r="AD48" s="75" t="n">
-        <v>5.639391252394303</v>
+        <v>5.639391252394367</v>
       </c>
       <c r="AE48" s="72" t="n">
         <v>345.8555475020454</v>
       </c>
       <c r="AF48" s="72" t="n">
-        <v>343.0906932415267</v>
+        <v>343.0906932415265</v>
       </c>
       <c r="AG48" s="72" t="n">
         <v>364.8535974121094</v>
@@ -27060,16 +27060,16 @@
         <v>330.1284973144531</v>
       </c>
       <c r="AL48" s="72" t="n">
-        <v>298.261319649642</v>
+        <v>298.2613196496421</v>
       </c>
       <c r="AM48" s="76" t="n">
-        <v>0.7953119207880393</v>
+        <v>0.7953119207880398</v>
       </c>
       <c r="AN48" s="29" t="n">
-        <v>19.30592355646114</v>
+        <v>19.30592355646111</v>
       </c>
       <c r="AO48" s="77" t="n">
-        <v>3.994606270869742</v>
+        <v>3.994606270869743</v>
       </c>
       <c r="AP48" s="72" t="n">
         <v>498.8299865722656</v>
@@ -27512,7 +27512,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 26 Aug 2026, 06:03 PM · Yahoo Finance data</t>
+          <t>Built 26 Aug 2026, 10:05 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -28031,22 +28031,22 @@
         <v>0.8836117786908546</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>43.00505268647656</v>
+        <v>43.00505268647657</v>
       </c>
       <c r="Z7" s="28" t="n">
         <v>8.101817102913829</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>14.62131517250736</v>
+        <v>14.62131517250735</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>0.350606617807955</v>
+        <v>0.3506066178079834</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>1.036936516327017</v>
+        <v>1.036936516327014</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-0.6863298985190616</v>
+        <v>-0.6863298985190309</v>
       </c>
       <c r="AE7" s="72" t="n">
         <v>182.6655926906319</v>
@@ -28221,16 +28221,16 @@
         <v>3.283977531914161</v>
       </c>
       <c r="AC8" s="86" t="n">
-        <v>2.66926536192358</v>
+        <v>2.669265361923588</v>
       </c>
       <c r="AD8" s="86" t="n">
-        <v>0.6147121699905811</v>
+        <v>0.6147121699905731</v>
       </c>
       <c r="AE8" s="83" t="n">
         <v>171.0424413965514</v>
       </c>
       <c r="AF8" s="83" t="n">
-        <v>167.433460080728</v>
+        <v>167.4334600807279</v>
       </c>
       <c r="AG8" s="83" t="n">
         <v>161.7063998413086</v>
@@ -28257,7 +28257,7 @@
         <v>9.044580192481934</v>
       </c>
       <c r="AO8" s="88" t="n">
-        <v>1.77289662167428</v>
+        <v>1.772896621674281</v>
       </c>
       <c r="AP8" s="83" t="n">
         <v>176.6000061035156</v>
@@ -28393,22 +28393,22 @@
         <v>37.99997965494792</v>
       </c>
       <c r="AA9" s="28" t="n">
-        <v>26.33966495627705</v>
+        <v>26.33966495627702</v>
       </c>
       <c r="AB9" s="75" t="n">
         <v>0.4536083553867982</v>
       </c>
       <c r="AC9" s="75" t="n">
-        <v>0.6307989158951426</v>
+        <v>0.6307989158951429</v>
       </c>
       <c r="AD9" s="75" t="n">
-        <v>-0.1771905605083444</v>
+        <v>-0.1771905605083447</v>
       </c>
       <c r="AE9" s="72" t="n">
         <v>57.54754209280467</v>
       </c>
       <c r="AF9" s="72" t="n">
-        <v>57.28740174179559</v>
+        <v>57.28740174179558</v>
       </c>
       <c r="AG9" s="72" t="n">
         <v>55.98320007324219</v>
@@ -28574,19 +28574,19 @@
         <v>28.28720567172498</v>
       </c>
       <c r="AB10" s="86" t="n">
-        <v>1.687357880228923</v>
+        <v>1.687357880228944</v>
       </c>
       <c r="AC10" s="86" t="n">
-        <v>1.334358898643816</v>
+        <v>1.334358898643834</v>
       </c>
       <c r="AD10" s="86" t="n">
-        <v>0.3529989815851069</v>
+        <v>0.3529989815851102</v>
       </c>
       <c r="AE10" s="83" t="n">
         <v>62.62602845024796</v>
       </c>
       <c r="AF10" s="83" t="n">
-        <v>60.71347718752872</v>
+        <v>60.71347718752873</v>
       </c>
       <c r="AG10" s="83" t="n">
         <v>57.50540023803711</v>
@@ -28749,22 +28749,22 @@
         <v>63.96384631246134</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>16.02337359877123</v>
+        <v>16.02337359877121</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.2964170001872617</v>
+        <v>0.2964170001872475</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.2725444880694352</v>
+        <v>0.272544488069428</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>0.02387251211782654</v>
+        <v>0.02387251211781949</v>
       </c>
       <c r="AE11" s="72" t="n">
         <v>85.64687761756478</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.34796767531319</v>
+        <v>85.3479676753132</v>
       </c>
       <c r="AG11" s="72" t="n">
         <v>84.77320007324219</v>
@@ -28930,13 +28930,13 @@
         <v>16.13816638091271</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.5983052863591212</v>
+        <v>0.598305286359107</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.6252441324567986</v>
+        <v>0.6252441324567815</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.02693884609767738</v>
+        <v>-0.0269388460976745</v>
       </c>
       <c r="AE12" s="83" t="n">
         <v>117.6222674888833</v>
@@ -29108,13 +29108,13 @@
         <v>10.70777261424374</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.3232913587176824</v>
+        <v>0.3232913587176967</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.2884890328659283</v>
+        <v>0.2884890328659421</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>0.03480232585175413</v>
+        <v>0.03480232585175458</v>
       </c>
       <c r="AE13" s="72" t="n">
         <v>111.1623730055342</v>
@@ -29147,7 +29147,7 @@
         <v>5.632347650188556</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.598395638838903</v>
+        <v>1.598395638838902</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -29286,19 +29286,19 @@
         <v>12.00378392962904</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.4073420804043693</v>
+        <v>0.4073420804043764</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.3656319893796773</v>
+        <v>0.3656319893796765</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>0.04171009102469198</v>
+        <v>0.04171009102469986</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>52.61596030237407</v>
+        <v>52.61596030237408</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.18882871095106</v>
+        <v>52.18882871095107</v>
       </c>
       <c r="AG14" s="83" t="n">
         <v>51.58139991760254</v>
@@ -29455,22 +29455,22 @@
         <v>0.7235324191609497</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>49.50631906333733</v>
+        <v>49.50631906333732</v>
       </c>
       <c r="Z15" s="28" t="n">
         <v>14.57491629291919</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>13.93292292505813</v>
+        <v>13.93292292505814</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>1.363388533398364</v>
+        <v>1.363388533398336</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>1.584281280708481</v>
+        <v>1.584281280708414</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.2208927473101168</v>
+        <v>-0.2208927473100784</v>
       </c>
       <c r="AE15" s="72" t="n">
         <v>185.221917946</v>
@@ -29639,22 +29639,22 @@
         <v>69.93475133451847</v>
       </c>
       <c r="AA16" s="35" t="n">
-        <v>8.894550421607269</v>
+        <v>8.894550421607271</v>
       </c>
       <c r="AB16" s="86" t="n">
         <v>0.003172571279222325</v>
       </c>
       <c r="AC16" s="86" t="n">
-        <v>0.006467497647294635</v>
+        <v>0.006467497647295513</v>
       </c>
       <c r="AD16" s="86" t="n">
-        <v>-0.00329492636807231</v>
+        <v>-0.003294926368073188</v>
       </c>
       <c r="AE16" s="83" t="n">
-        <v>44.9514819134743</v>
+        <v>44.95148191347429</v>
       </c>
       <c r="AF16" s="83" t="n">
-        <v>44.95689061038712</v>
+        <v>44.95689061038711</v>
       </c>
       <c r="AG16" s="83" t="n">
         <v>44.86780014038086</v>
@@ -29820,19 +29820,19 @@
         <v>11.87727783965133</v>
       </c>
       <c r="AB17" s="75" t="n">
-        <v>-0.3914665992615056</v>
+        <v>-0.3914665992614985</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.3448940262130525</v>
+        <v>-0.344894026213052</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.04657257304845308</v>
+        <v>-0.04657257304844648</v>
       </c>
       <c r="AE17" s="72" t="n">
-        <v>43.69984318570527</v>
+        <v>43.69984318570528</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>44.11679484382309</v>
+        <v>44.1167948438231</v>
       </c>
       <c r="AG17" s="72" t="n">
         <v>44.82520011901855</v>
@@ -30008,7 +30008,7 @@
         <v>0.8482618334990122</v>
       </c>
       <c r="Y19" s="28" t="n">
-        <v>54.22779666041505</v>
+        <v>54.22779666041507</v>
       </c>
       <c r="Z19" s="28" t="n">
         <v>27.58598359010225</v>
@@ -30017,19 +30017,19 @@
         <v>19.05392869432242</v>
       </c>
       <c r="AB19" s="75" t="n">
-        <v>5.644223884948133</v>
+        <v>5.64422388494836</v>
       </c>
       <c r="AC19" s="75" t="n">
-        <v>6.563548490082971</v>
+        <v>6.563548490083219</v>
       </c>
       <c r="AD19" s="75" t="n">
-        <v>-0.9193246051348378</v>
+        <v>-0.9193246051348591</v>
       </c>
       <c r="AE19" s="72" t="n">
-        <v>767.8761081241358</v>
+        <v>767.876108124136</v>
       </c>
       <c r="AF19" s="72" t="n">
-        <v>763.3152823176968</v>
+        <v>763.3152823176965</v>
       </c>
       <c r="AG19" s="72" t="n">
         <v>751.7496044921875</v>
@@ -30056,7 +30056,7 @@
         <v>7.394265152225938</v>
       </c>
       <c r="AO19" s="77" t="n">
-        <v>0.905986938156639</v>
+        <v>0.9059869381566391</v>
       </c>
       <c r="AP19" s="72" t="n">
         <v>779.3699951171875</v>
@@ -30184,7 +30184,7 @@
         <v>0.8465930607525081</v>
       </c>
       <c r="Y20" s="35" t="n">
-        <v>50.14984366773613</v>
+        <v>50.14984366773611</v>
       </c>
       <c r="Z20" s="35" t="n">
         <v>21.84833941428787</v>
@@ -30193,16 +30193,16 @@
         <v>14.43004592012056</v>
       </c>
       <c r="AB20" s="86" t="n">
-        <v>3.356688884277901</v>
+        <v>3.356688884278128</v>
       </c>
       <c r="AC20" s="86" t="n">
-        <v>3.379202310126226</v>
+        <v>3.37920231012648</v>
       </c>
       <c r="AD20" s="86" t="n">
-        <v>-0.0225134258483255</v>
+        <v>-0.02251342584835214</v>
       </c>
       <c r="AE20" s="83" t="n">
-        <v>717.4488833444225</v>
+        <v>717.4488833444226</v>
       </c>
       <c r="AF20" s="83" t="n">
         <v>714.2027032411793</v>
@@ -30369,19 +30369,19 @@
         <v>13.61323729375719</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>1.779302519042346</v>
+        <v>1.779302519042403</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>2.018540035777042</v>
+        <v>2.018540035777098</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.2392375167346952</v>
+        <v>-0.2392375167346943</v>
       </c>
       <c r="AE21" s="72" t="n">
         <v>300.6093738799806</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>299.155239891611</v>
+        <v>299.1552398916108</v>
       </c>
       <c r="AG21" s="72" t="n">
         <v>296.6790008544922</v>
@@ -30536,7 +30536,7 @@
         <v>0.6529201448204961</v>
       </c>
       <c r="Y22" s="35" t="n">
-        <v>42.00648384125834</v>
+        <v>42.00648384125836</v>
       </c>
       <c r="Z22" s="35" t="n">
         <v>9.674209097782809</v>
@@ -30545,13 +30545,13 @@
         <v>19.26591490192905</v>
       </c>
       <c r="AB22" s="86" t="n">
-        <v>-9.22197671859243</v>
+        <v>-9.221976718592487</v>
       </c>
       <c r="AC22" s="86" t="n">
-        <v>-10.43631181752062</v>
+        <v>-10.43631181752071</v>
       </c>
       <c r="AD22" s="86" t="n">
-        <v>1.214335098928188</v>
+        <v>1.214335098928224</v>
       </c>
       <c r="AE22" s="83" t="n">
         <v>129.315629030965</v>
@@ -30569,19 +30569,19 @@
         <v>105.2839499759674</v>
       </c>
       <c r="AJ22" s="83" t="n">
-        <v>156.1394518932076</v>
+        <v>156.1394518932075</v>
       </c>
       <c r="AK22" s="83" t="n">
         <v>128.0014999389649</v>
       </c>
       <c r="AL22" s="83" t="n">
-        <v>99.86354798472215</v>
+        <v>99.86354798472217</v>
       </c>
       <c r="AM22" s="87" t="n">
-        <v>0.3684783193019891</v>
+        <v>0.368478319301989</v>
       </c>
       <c r="AN22" s="36" t="n">
-        <v>43.9650347342176</v>
+        <v>43.96503473421755</v>
       </c>
       <c r="AO22" s="88" t="n">
         <v>15.47216919831381</v>
@@ -30733,7 +30733,7 @@
         <v>0.8841417929801366</v>
       </c>
       <c r="Y24" s="28" t="n">
-        <v>47.28468061563026</v>
+        <v>47.28468061563025</v>
       </c>
       <c r="Z24" s="28" t="n">
         <v>44.5459288975733</v>
@@ -30745,16 +30745,16 @@
         <v>-1.574473201278806</v>
       </c>
       <c r="AC24" s="75" t="n">
-        <v>-1.194379688035154</v>
+        <v>-1.194379688035181</v>
       </c>
       <c r="AD24" s="75" t="n">
-        <v>-0.3800935132436523</v>
+        <v>-0.3800935132436249</v>
       </c>
       <c r="AE24" s="72" t="n">
         <v>310.1229636204602</v>
       </c>
       <c r="AF24" s="72" t="n">
-        <v>312.1256917010064</v>
+        <v>312.1256917010062</v>
       </c>
       <c r="AG24" s="72" t="n">
         <v>310.2079998779297</v>
@@ -30915,22 +30915,22 @@
         <v>18.58002868284747</v>
       </c>
       <c r="AA25" s="35" t="n">
-        <v>9.876288763983844</v>
+        <v>9.876288763983842</v>
       </c>
       <c r="AB25" s="86" t="n">
-        <v>-7.672365102650701</v>
+        <v>-7.672365102650645</v>
       </c>
       <c r="AC25" s="86" t="n">
-        <v>-6.878077419584622</v>
+        <v>-6.878077419584638</v>
       </c>
       <c r="AD25" s="86" t="n">
-        <v>-0.794287683066079</v>
+        <v>-0.7942876830660062</v>
       </c>
       <c r="AE25" s="83" t="n">
-        <v>480.1612359060307</v>
+        <v>480.1612359060308</v>
       </c>
       <c r="AF25" s="83" t="n">
-        <v>488.4507071904728</v>
+        <v>488.4507071904727</v>
       </c>
       <c r="AG25" s="83" t="n">
         <v>510.2342010498047</v>
@@ -31094,16 +31094,16 @@
         <v>22.24155052443415</v>
       </c>
       <c r="AB26" s="75" t="n">
-        <v>3.461119550199442</v>
+        <v>3.461119550199385</v>
       </c>
       <c r="AC26" s="75" t="n">
-        <v>4.998738136454804</v>
+        <v>4.99873813645477</v>
       </c>
       <c r="AD26" s="75" t="n">
-        <v>-1.537618586255363</v>
+        <v>-1.537618586255386</v>
       </c>
       <c r="AE26" s="72" t="n">
-        <v>262.5206599779982</v>
+        <v>262.5206599779981</v>
       </c>
       <c r="AF26" s="72" t="n">
         <v>260.4988312694554</v>
@@ -31133,7 +31133,7 @@
         <v>25.3289999424292</v>
       </c>
       <c r="AO26" s="77" t="n">
-        <v>2.892852088635585</v>
+        <v>2.892852088635586</v>
       </c>
       <c r="AP26" s="72" t="n">
         <v>287.2000122070312</v>
@@ -31261,7 +31261,7 @@
         <v>1.373817140771056</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>66.1063553302954</v>
+        <v>66.10635533029541</v>
       </c>
       <c r="Z27" s="35" t="n">
         <v>97.98659479332146</v>
@@ -31270,16 +31270,16 @@
         <v>20.31792184343016</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>1.928174887522133</v>
+        <v>1.928174887522104</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>1.081949372682235</v>
+        <v>1.081949372682232</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.8462255148398974</v>
+        <v>0.8462255148398725</v>
       </c>
       <c r="AE27" s="83" t="n">
-        <v>82.37503729295874</v>
+        <v>82.37503729295875</v>
       </c>
       <c r="AF27" s="83" t="n">
         <v>79.79080092329698</v>
@@ -31294,19 +31294,19 @@
         <v>76.68595006942749</v>
       </c>
       <c r="AJ27" s="83" t="n">
-        <v>87.14351880532904</v>
+        <v>87.14351880532905</v>
       </c>
       <c r="AK27" s="83" t="n">
         <v>78.0564998626709</v>
       </c>
       <c r="AL27" s="83" t="n">
-        <v>68.96948092001277</v>
+        <v>68.96948092001276</v>
       </c>
       <c r="AM27" s="87" t="n">
-        <v>0.9486344351900675</v>
+        <v>0.9486344351900668</v>
       </c>
       <c r="AN27" s="36" t="n">
-        <v>23.28318322918764</v>
+        <v>23.28318322918768</v>
       </c>
       <c r="AO27" s="88" t="n">
         <v>2.808344737198555</v>
@@ -31449,16 +31449,16 @@
         <v>-9.655792021809987</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-9.12522135809915</v>
+        <v>-9.125221358099159</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-0.5305706637108365</v>
+        <v>-0.5305706637108276</v>
       </c>
       <c r="AE28" s="72" t="n">
-        <v>257.324489126843</v>
+        <v>257.3244891268431</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>266.8296362824018</v>
+        <v>266.8296362824019</v>
       </c>
       <c r="AG28" s="72" t="n">
         <v>302.3635989379883</v>
@@ -31479,10 +31479,10 @@
         <v>225.5529712684579</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.2522112636972847</v>
+        <v>0.252211263697285</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>27.01367818234507</v>
+        <v>27.01367818234509</v>
       </c>
       <c r="AO28" s="77" t="n">
         <v>8.589066018481246</v>
@@ -31619,16 +31619,16 @@
         <v>47.25185383610136</v>
       </c>
       <c r="AA29" s="35" t="n">
-        <v>15.26051751053128</v>
+        <v>15.26051751053127</v>
       </c>
       <c r="AB29" s="86" t="n">
         <v>-0.1815333192850659</v>
       </c>
       <c r="AC29" s="86" t="n">
-        <v>-0.5847672682869639</v>
+        <v>-0.584767268286974</v>
       </c>
       <c r="AD29" s="86" t="n">
-        <v>0.403233949001898</v>
+        <v>0.4032339490019081</v>
       </c>
       <c r="AE29" s="83" t="n">
         <v>68.14623748005592</v>
@@ -31646,22 +31646,22 @@
         <v>81.65417484283448</v>
       </c>
       <c r="AJ29" s="83" t="n">
-        <v>77.86438315671433</v>
+        <v>77.86438315671434</v>
       </c>
       <c r="AK29" s="83" t="n">
         <v>66.11749954223633</v>
       </c>
       <c r="AL29" s="83" t="n">
-        <v>54.37061592775833</v>
+        <v>54.37061592775832</v>
       </c>
       <c r="AM29" s="87" t="n">
-        <v>0.6077946316128168</v>
+        <v>0.6077946316128165</v>
       </c>
       <c r="AN29" s="36" t="n">
-        <v>35.53335711667076</v>
+        <v>35.5333571166708</v>
       </c>
       <c r="AO29" s="88" t="n">
-        <v>7.689591259811926</v>
+        <v>7.689591259811928</v>
       </c>
       <c r="AP29" s="83" t="n">
         <v>133.8600006103516</v>
@@ -31801,16 +31801,16 @@
         <v>-4.637590427933787</v>
       </c>
       <c r="AC30" s="75" t="n">
-        <v>1.204415451614585</v>
+        <v>1.204415451614611</v>
       </c>
       <c r="AD30" s="75" t="n">
-        <v>-5.842005879548372</v>
+        <v>-5.842005879548398</v>
       </c>
       <c r="AE30" s="72" t="n">
         <v>381.7898410816688</v>
       </c>
       <c r="AF30" s="72" t="n">
-        <v>391.1433793456213</v>
+        <v>391.1433793456215</v>
       </c>
       <c r="AG30" s="72" t="n">
         <v>388.5028002929687</v>
@@ -31965,28 +31965,28 @@
         <v>1.32301170337127</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>62.02830001349681</v>
+        <v>62.02830001349682</v>
       </c>
       <c r="Z31" s="35" t="n">
         <v>97.37734715230583</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>16.91966867906344</v>
+        <v>16.91966867906343</v>
       </c>
       <c r="AB31" s="86" t="n">
         <v>1.351320173041671</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>0.4980977692010238</v>
+        <v>0.4980977692010115</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>0.8532224038406473</v>
+        <v>0.8532224038406596</v>
       </c>
       <c r="AE31" s="83" t="n">
         <v>97.99066257427499</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>95.85803541434107</v>
+        <v>95.85803541434109</v>
       </c>
       <c r="AG31" s="83" t="n">
         <v>96.14399978637695</v>
@@ -32004,13 +32004,13 @@
         <v>94.241499710083</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>84.40562931118144</v>
+        <v>84.40562931118146</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.9203238803894195</v>
+        <v>0.92032388038942</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>20.87375610354217</v>
+        <v>20.87375610354214</v>
       </c>
       <c r="AO31" s="88" t="n">
         <v>3.847625512790251</v>
@@ -32141,7 +32141,7 @@
         <v>0.6669506310743233</v>
       </c>
       <c r="Y32" s="28" t="n">
-        <v>48.06399276237421</v>
+        <v>48.06399276237422</v>
       </c>
       <c r="Z32" s="28" t="n">
         <v>8.771925704861937</v>
@@ -32150,19 +32150,19 @@
         <v>17.79327738791554</v>
       </c>
       <c r="AB32" s="75" t="n">
-        <v>2.417099578374945</v>
+        <v>2.417099578374931</v>
       </c>
       <c r="AC32" s="75" t="n">
-        <v>2.352293260572927</v>
+        <v>2.352293260572909</v>
       </c>
       <c r="AD32" s="75" t="n">
-        <v>0.06480631780201795</v>
+        <v>0.06480631780202195</v>
       </c>
       <c r="AE32" s="72" t="n">
         <v>93.1598251943214</v>
       </c>
       <c r="AF32" s="72" t="n">
-        <v>90.63266390365472</v>
+        <v>90.63266390365473</v>
       </c>
       <c r="AG32" s="72" t="n">
         <v>89.91580017089844</v>
@@ -32174,22 +32174,22 @@
         <v>91.95407497406006</v>
       </c>
       <c r="AJ32" s="72" t="n">
-        <v>113.5661380047709</v>
+        <v>113.5661380047708</v>
       </c>
       <c r="AK32" s="72" t="n">
         <v>87.67850074768066</v>
       </c>
       <c r="AL32" s="72" t="n">
-        <v>61.79086349059045</v>
+        <v>61.79086349059047</v>
       </c>
       <c r="AM32" s="76" t="n">
         <v>0.5033123479894532</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>59.05127719186053</v>
+        <v>59.05127719186049</v>
       </c>
       <c r="AO32" s="77" t="n">
-        <v>9.177631233585931</v>
+        <v>9.177631233585929</v>
       </c>
       <c r="AP32" s="72" t="n">
         <v>153.1999969482422</v>
@@ -32326,16 +32326,16 @@
         <v>11.69424712235745</v>
       </c>
       <c r="AB33" s="86" t="n">
-        <v>10.62044177675244</v>
+        <v>10.62044177675261</v>
       </c>
       <c r="AC33" s="86" t="n">
-        <v>14.25896850045864</v>
+        <v>14.25896850045878</v>
       </c>
       <c r="AD33" s="86" t="n">
-        <v>-3.638526723706192</v>
+        <v>-3.638526723706166</v>
       </c>
       <c r="AE33" s="83" t="n">
-        <v>453.3450473478514</v>
+        <v>453.3450473478515</v>
       </c>
       <c r="AF33" s="83" t="n">
         <v>446.7382754720654</v>
@@ -32365,7 +32365,7 @@
         <v>29.46619898169195</v>
       </c>
       <c r="AO33" s="88" t="n">
-        <v>6.879137498822042</v>
+        <v>6.879137498822044</v>
       </c>
       <c r="AP33" s="83" t="n">
         <v>514</v>
@@ -32493,25 +32493,25 @@
         <v>0.8521437261452697</v>
       </c>
       <c r="Y34" s="28" t="n">
-        <v>46.00663174413023</v>
+        <v>46.00663174413022</v>
       </c>
       <c r="Z34" s="28" t="n">
         <v>12.22609227090578</v>
       </c>
       <c r="AA34" s="28" t="n">
-        <v>9.114685582996152</v>
+        <v>9.114685582996159</v>
       </c>
       <c r="AB34" s="75" t="n">
-        <v>-2.687573377795445</v>
+        <v>-2.687573377795559</v>
       </c>
       <c r="AC34" s="75" t="n">
-        <v>-1.870504188814349</v>
+        <v>-1.870504188814406</v>
       </c>
       <c r="AD34" s="75" t="n">
-        <v>-0.8170691889810962</v>
+        <v>-0.8170691889811532</v>
       </c>
       <c r="AE34" s="72" t="n">
-        <v>342.7196035371761</v>
+        <v>342.7196035371762</v>
       </c>
       <c r="AF34" s="72" t="n">
         <v>345.896825527098</v>
@@ -32541,7 +32541,7 @@
         <v>14.39077639394272</v>
       </c>
       <c r="AO34" s="77" t="n">
-        <v>2.631834967170809</v>
+        <v>2.631834967170808</v>
       </c>
       <c r="AP34" s="72" t="n">
         <v>404.4700012207031</v>
@@ -32678,13 +32678,13 @@
         <v>16.36721712385206</v>
       </c>
       <c r="AB35" s="86" t="n">
-        <v>0.3232003162078456</v>
+        <v>0.3232003162078314</v>
       </c>
       <c r="AC35" s="86" t="n">
-        <v>-0.2518058828375336</v>
+        <v>-0.2518058828375438</v>
       </c>
       <c r="AD35" s="86" t="n">
-        <v>0.5750061990453792</v>
+        <v>0.5750061990453752</v>
       </c>
       <c r="AE35" s="83" t="n">
         <v>42.35483356709537</v>
@@ -32702,19 +32702,19 @@
         <v>46.61315004348755</v>
       </c>
       <c r="AJ35" s="83" t="n">
-        <v>47.49136066642113</v>
+        <v>47.49136066642112</v>
       </c>
       <c r="AK35" s="83" t="n">
         <v>39.92199983596802</v>
       </c>
       <c r="AL35" s="83" t="n">
-        <v>32.3526390055149</v>
+        <v>32.35263900551491</v>
       </c>
       <c r="AM35" s="87" t="n">
-        <v>0.6293372898983605</v>
+        <v>0.6293372898983606</v>
       </c>
       <c r="AN35" s="36" t="n">
-        <v>37.92074976982212</v>
+        <v>37.92074976982208</v>
       </c>
       <c r="AO35" s="88" t="n">
         <v>9.384641141618667</v>
@@ -32851,22 +32851,22 @@
         <v>1.795733447274761</v>
       </c>
       <c r="AA36" s="28" t="n">
-        <v>14.84791424946091</v>
+        <v>14.84791424946092</v>
       </c>
       <c r="AB36" s="75" t="n">
-        <v>-2.613048194543254</v>
+        <v>-2.613048194543225</v>
       </c>
       <c r="AC36" s="75" t="n">
-        <v>-2.446209310481192</v>
+        <v>-2.446209310481168</v>
       </c>
       <c r="AD36" s="75" t="n">
-        <v>-0.1668388840620612</v>
+        <v>-0.1668388840620576</v>
       </c>
       <c r="AE36" s="72" t="n">
         <v>95.49450204864473</v>
       </c>
       <c r="AF36" s="72" t="n">
-        <v>98.06947544192391</v>
+        <v>98.0694754419239</v>
       </c>
       <c r="AG36" s="72" t="n">
         <v>108.1813996887207</v>
@@ -32893,7 +32893,7 @@
         <v>25.60666538431192</v>
       </c>
       <c r="AO36" s="77" t="n">
-        <v>7.217874069983048</v>
+        <v>7.217874069983051</v>
       </c>
       <c r="AP36" s="72" t="n">
         <v>142.3500061035156</v>
@@ -33027,16 +33027,16 @@
         <v>16.64843787151077</v>
       </c>
       <c r="AA37" s="35" t="n">
-        <v>34.00527810316554</v>
+        <v>34.00527810316552</v>
       </c>
       <c r="AB37" s="86" t="n">
-        <v>19.92172446740415</v>
+        <v>19.92172446740409</v>
       </c>
       <c r="AC37" s="86" t="n">
-        <v>23.245760920062</v>
+        <v>23.24576092006193</v>
       </c>
       <c r="AD37" s="86" t="n">
-        <v>-3.32403645265785</v>
+        <v>-3.324036452657843</v>
       </c>
       <c r="AE37" s="83" t="n">
         <v>484.7189702745173</v>
@@ -33197,22 +33197,22 @@
         <v>2.220619867148746</v>
       </c>
       <c r="Y38" s="28" t="n">
-        <v>66.07499956826719</v>
+        <v>66.07499956826717</v>
       </c>
       <c r="Z38" s="28" t="n">
         <v>91.20369319142259</v>
       </c>
       <c r="AA38" s="28" t="n">
-        <v>15.43109520963007</v>
+        <v>15.43109520963008</v>
       </c>
       <c r="AB38" s="75" t="n">
         <v>1.757474849667105</v>
       </c>
       <c r="AC38" s="75" t="n">
-        <v>-0.9657680171376797</v>
+        <v>-0.9657680171377033</v>
       </c>
       <c r="AD38" s="75" t="n">
-        <v>2.723242866804784</v>
+        <v>2.723242866804808</v>
       </c>
       <c r="AE38" s="72" t="n">
         <v>104.8417683830904</v>
@@ -33230,19 +33230,19 @@
         <v>143.9546000671387</v>
       </c>
       <c r="AJ38" s="72" t="n">
-        <v>111.409224388086</v>
+        <v>111.4092243880861</v>
       </c>
       <c r="AK38" s="72" t="n">
         <v>98.56900024414062</v>
       </c>
       <c r="AL38" s="72" t="n">
-        <v>85.7287761001952</v>
+        <v>85.72877610019511</v>
       </c>
       <c r="AM38" s="76" t="n">
-        <v>1.305320823219863</v>
+        <v>1.305320823219857</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>26.05327052550419</v>
+        <v>26.05327052550439</v>
       </c>
       <c r="AO38" s="77" t="n">
         <v>5.684479521064557</v>
@@ -33385,16 +33385,16 @@
         <v>11.68678865609854</v>
       </c>
       <c r="AC39" s="86" t="n">
-        <v>-0.5849598869534504</v>
+        <v>-0.5849598869536394</v>
       </c>
       <c r="AD39" s="86" t="n">
-        <v>12.27174854305199</v>
+        <v>12.27174854305218</v>
       </c>
       <c r="AE39" s="83" t="n">
         <v>949.4077277806913</v>
       </c>
       <c r="AF39" s="83" t="n">
-        <v>927.8715121749796</v>
+        <v>927.8715121749797</v>
       </c>
       <c r="AG39" s="83" t="n">
         <v>964.5912036132812</v>
@@ -33406,22 +33406,22 @@
         <v>571.0984007263183</v>
       </c>
       <c r="AJ39" s="83" t="n">
-        <v>1022.896523729269</v>
+        <v>1022.896523729268</v>
       </c>
       <c r="AK39" s="83" t="n">
         <v>896.2425018310547</v>
       </c>
       <c r="AL39" s="83" t="n">
-        <v>769.5884799328409</v>
+        <v>769.588479932841</v>
       </c>
       <c r="AM39" s="87" t="n">
-        <v>0.7784654068171168</v>
+        <v>0.7784654068171171</v>
       </c>
       <c r="AN39" s="36" t="n">
-        <v>28.26333757648298</v>
+        <v>28.26333757648296</v>
       </c>
       <c r="AO39" s="88" t="n">
-        <v>6.903296244410746</v>
+        <v>6.903296244410743</v>
       </c>
       <c r="AP39" s="83" t="n">
         <v>1255</v>
@@ -33549,22 +33549,22 @@
         <v>0.6986982926688237</v>
       </c>
       <c r="Y40" s="28" t="n">
-        <v>49.6637222480617</v>
+        <v>49.66372224806169</v>
       </c>
       <c r="Z40" s="28" t="n">
         <v>38.42255119474325</v>
       </c>
       <c r="AA40" s="28" t="n">
-        <v>13.61692114424372</v>
+        <v>13.61692114424371</v>
       </c>
       <c r="AB40" s="75" t="n">
         <v>7.346536658556801</v>
       </c>
       <c r="AC40" s="75" t="n">
-        <v>5.956708611382044</v>
+        <v>5.956708611382023</v>
       </c>
       <c r="AD40" s="75" t="n">
-        <v>1.389828047174757</v>
+        <v>1.389828047174777</v>
       </c>
       <c r="AE40" s="72" t="n">
         <v>230.7358843777086</v>
@@ -33725,7 +33725,7 @@
         <v>0.706907571518349</v>
       </c>
       <c r="Y41" s="35" t="n">
-        <v>61.61434628104366</v>
+        <v>61.61434628104367</v>
       </c>
       <c r="Z41" s="35" t="n">
         <v>82.27982826113538</v>
@@ -33734,19 +33734,19 @@
         <v>21.74301919281315</v>
       </c>
       <c r="AB41" s="86" t="n">
-        <v>1.462382270819433</v>
+        <v>1.462382270819418</v>
       </c>
       <c r="AC41" s="86" t="n">
-        <v>0.709249511126227</v>
+        <v>0.7092495111262127</v>
       </c>
       <c r="AD41" s="86" t="n">
-        <v>0.7531327596932055</v>
+        <v>0.7531327596932056</v>
       </c>
       <c r="AE41" s="83" t="n">
         <v>78.19471017241698</v>
       </c>
       <c r="AF41" s="83" t="n">
-        <v>76.08280389068777</v>
+        <v>76.08280389068779</v>
       </c>
       <c r="AG41" s="83" t="n">
         <v>74.52039916992187</v>
@@ -33758,19 +33758,19 @@
         <v>88.41735469818116</v>
       </c>
       <c r="AJ41" s="83" t="n">
-        <v>80.87968755491885</v>
+        <v>80.87968755491883</v>
       </c>
       <c r="AK41" s="83" t="n">
         <v>75.28299942016602</v>
       </c>
       <c r="AL41" s="83" t="n">
-        <v>69.6863112854132</v>
+        <v>69.68631128541321</v>
       </c>
       <c r="AM41" s="87" t="n">
-        <v>0.8847808573592086</v>
+        <v>0.8847808573592096</v>
       </c>
       <c r="AN41" s="36" t="n">
-        <v>14.86839838438648</v>
+        <v>14.86839838438644</v>
       </c>
       <c r="AO41" s="88" t="n">
         <v>2.953446900021074</v>
@@ -33907,16 +33907,16 @@
         <v>54.22885713770581</v>
       </c>
       <c r="AA42" s="28" t="n">
-        <v>18.9953208341176</v>
+        <v>18.99532083411759</v>
       </c>
       <c r="AB42" s="75" t="n">
         <v>-0.1805645465085082</v>
       </c>
       <c r="AC42" s="75" t="n">
-        <v>-0.370255850280048</v>
+        <v>-0.3702558502800496</v>
       </c>
       <c r="AD42" s="75" t="n">
-        <v>0.1896913037715398</v>
+        <v>0.1896913037715414</v>
       </c>
       <c r="AE42" s="72" t="n">
         <v>10.20102950923778</v>
@@ -34077,7 +34077,7 @@
         <v>0.8480718345175143</v>
       </c>
       <c r="Y43" s="35" t="n">
-        <v>51.00954196738143</v>
+        <v>51.00954196738142</v>
       </c>
       <c r="Z43" s="35" t="n">
         <v>30.04769282521364</v>
@@ -34086,13 +34086,13 @@
         <v>16.88991981299272</v>
       </c>
       <c r="AB43" s="86" t="n">
-        <v>3.652277266609843</v>
+        <v>3.652277266609815</v>
       </c>
       <c r="AC43" s="86" t="n">
-        <v>4.055479067947919</v>
+        <v>4.055479067947897</v>
       </c>
       <c r="AD43" s="86" t="n">
-        <v>-0.403201801338076</v>
+        <v>-0.4032018013380823</v>
       </c>
       <c r="AE43" s="83" t="n">
         <v>218.3655330366959</v>
@@ -34262,13 +34262,13 @@
         <v>32.58689421101383</v>
       </c>
       <c r="AB44" s="75" t="n">
-        <v>12.05140122230691</v>
+        <v>12.05140122230677</v>
       </c>
       <c r="AC44" s="75" t="n">
-        <v>10.95927118481365</v>
+        <v>10.95927118481355</v>
       </c>
       <c r="AD44" s="75" t="n">
-        <v>1.092130037493257</v>
+        <v>1.092130037493217</v>
       </c>
       <c r="AE44" s="72" t="n">
         <v>173.2861980821602</v>
@@ -34429,22 +34429,22 @@
         <v>0.7578971721450054</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>43.55974205692664</v>
+        <v>43.55974205692663</v>
       </c>
       <c r="Z45" s="35" t="n">
         <v>40.51282968500927</v>
       </c>
       <c r="AA45" s="35" t="n">
-        <v>13.92568138944569</v>
+        <v>13.92568138944568</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-4.121986201131278</v>
+        <v>-4.121986201131364</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-5.374168303239052</v>
+        <v>-5.374168303239071</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.252182102107773</v>
+        <v>1.252182102107708</v>
       </c>
       <c r="AE45" s="83" t="n">
         <v>161.686898214381</v>
@@ -34468,13 +34468,13 @@
         <v>160.6049995422363</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>149.852631629027</v>
+        <v>149.8526316290269</v>
       </c>
       <c r="AM45" s="87" t="n">
         <v>0.5067427221117284</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>13.38982963650726</v>
+        <v>13.38982963650733</v>
       </c>
       <c r="AO45" s="88" t="n">
         <v>4.359646137232569</v>
@@ -34614,16 +34614,16 @@
         <v>17.51374260141473</v>
       </c>
       <c r="AB46" s="75" t="n">
-        <v>-0.8868075614076361</v>
+        <v>-0.8868075614076787</v>
       </c>
       <c r="AC46" s="75" t="n">
-        <v>-1.325492143345247</v>
+        <v>-1.325492143345285</v>
       </c>
       <c r="AD46" s="75" t="n">
-        <v>0.4386845819376111</v>
+        <v>0.4386845819376062</v>
       </c>
       <c r="AE46" s="72" t="n">
-        <v>76.20962283319159</v>
+        <v>76.2096228331916</v>
       </c>
       <c r="AF46" s="72" t="n">
         <v>76.48435048004714</v>
@@ -34644,16 +34644,16 @@
         <v>74.07299995422363</v>
       </c>
       <c r="AL46" s="72" t="n">
-        <v>60.28164197639109</v>
+        <v>60.2816419763911</v>
       </c>
       <c r="AM46" s="76" t="n">
-        <v>0.4455093449892589</v>
+        <v>0.4455093449892587</v>
       </c>
       <c r="AN46" s="29" t="n">
-        <v>37.23720650265402</v>
+        <v>37.23720650265401</v>
       </c>
       <c r="AO46" s="77" t="n">
-        <v>7.953848355766797</v>
+        <v>7.953848355766796</v>
       </c>
       <c r="AP46" s="72" t="n">
         <v>151</v>
@@ -34790,13 +34790,13 @@
         <v>15.65927819323035</v>
       </c>
       <c r="AB47" s="86" t="n">
-        <v>20.6503909166579</v>
+        <v>20.65039091665767</v>
       </c>
       <c r="AC47" s="86" t="n">
-        <v>-27.02179198496882</v>
+        <v>-27.021791984969</v>
       </c>
       <c r="AD47" s="86" t="n">
-        <v>47.67218290162672</v>
+        <v>47.67218290162667</v>
       </c>
       <c r="AE47" s="83" t="n">
         <v>1558.855559086931</v>
@@ -34820,13 +34820,13 @@
         <v>1381.131494140625</v>
       </c>
       <c r="AL47" s="83" t="n">
-        <v>982.2064303532638</v>
+        <v>982.2064303532637</v>
       </c>
       <c r="AM47" s="87" t="n">
         <v>0.7694095726567791</v>
       </c>
       <c r="AN47" s="36" t="n">
-        <v>57.7678614208392</v>
+        <v>57.76786142083922</v>
       </c>
       <c r="AO47" s="88" t="n">
         <v>9.678440353879001</v>
@@ -34957,28 +34957,28 @@
         <v>1.687935199294433</v>
       </c>
       <c r="Y48" s="28" t="n">
-        <v>58.00529603381864</v>
+        <v>58.00529603381865</v>
       </c>
       <c r="Z48" s="28" t="n">
         <v>92.85991788151304</v>
       </c>
       <c r="AA48" s="28" t="n">
-        <v>20.28839320201394</v>
+        <v>20.28839320201393</v>
       </c>
       <c r="AB48" s="75" t="n">
-        <v>-3.327519730977144</v>
+        <v>-3.327519730977201</v>
       </c>
       <c r="AC48" s="75" t="n">
-        <v>-9.556983998642346</v>
+        <v>-9.556983998642426</v>
       </c>
       <c r="AD48" s="75" t="n">
-        <v>6.229464267665202</v>
+        <v>6.229464267665225</v>
       </c>
       <c r="AE48" s="72" t="n">
         <v>344.9714147291923</v>
       </c>
       <c r="AF48" s="72" t="n">
-        <v>342.5047613449763</v>
+        <v>342.504761344976</v>
       </c>
       <c r="AG48" s="72" t="n">
         <v>365.8575970458984</v>
@@ -34990,22 +34990,22 @@
         <v>403.3203997802734</v>
       </c>
       <c r="AJ48" s="72" t="n">
-        <v>360.0216992700388</v>
+        <v>360.0216992700387</v>
       </c>
       <c r="AK48" s="72" t="n">
         <v>328.1419967651367</v>
       </c>
       <c r="AL48" s="72" t="n">
-        <v>296.2622942602346</v>
+        <v>296.2622942602347</v>
       </c>
       <c r="AM48" s="76" t="n">
-        <v>1.04451556724984</v>
+        <v>1.044515567249841</v>
       </c>
       <c r="AN48" s="29" t="n">
-        <v>19.43043122744179</v>
+        <v>19.43043122744175</v>
       </c>
       <c r="AO48" s="77" t="n">
-        <v>3.81941188977447</v>
+        <v>3.819411889774471</v>
       </c>
       <c r="AP48" s="72" t="n">
         <v>498.8299865722656</v>
@@ -35448,7 +35448,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 26 Aug 2026, 06:03 PM · Yahoo Finance data</t>
+          <t>Built 26 Aug 2026, 10:05 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35976,13 +35976,13 @@
         <v>14.15447154482318</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>0.6641194388350868</v>
+        <v>0.6641194388351153</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>1.208518990956782</v>
+        <v>1.208518990956772</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-0.5443995521216951</v>
+        <v>-0.5443995521216567</v>
       </c>
       <c r="AE7" s="72" t="n">
         <v>183.3557620308125</v>
@@ -36000,7 +36000,7 @@
         <v>169.4420997619629</v>
       </c>
       <c r="AJ7" s="72" t="n">
-        <v>189.1056752762148</v>
+        <v>189.1056752762147</v>
       </c>
       <c r="AK7" s="72" t="n">
         <v>183.4590003967285</v>
@@ -36009,10 +36009,10 @@
         <v>177.8123255172423</v>
       </c>
       <c r="AM7" s="76" t="n">
-        <v>0.173347925726225</v>
+        <v>0.1733479257262233</v>
       </c>
       <c r="AN7" s="29" t="n">
-        <v>6.155789432271342</v>
+        <v>6.155789432271311</v>
       </c>
       <c r="AO7" s="77" t="n">
         <v>1.454636049402259</v>
@@ -36154,13 +36154,13 @@
         <v>26.83292850747817</v>
       </c>
       <c r="AB8" s="86" t="n">
-        <v>3.044204732550497</v>
+        <v>3.044204732550526</v>
       </c>
       <c r="AC8" s="86" t="n">
-        <v>2.515587319425934</v>
+        <v>2.515587319425944</v>
       </c>
       <c r="AD8" s="86" t="n">
-        <v>0.5286174131245631</v>
+        <v>0.5286174131245813</v>
       </c>
       <c r="AE8" s="83" t="n">
         <v>170.0202831906554</v>
@@ -36323,22 +36323,22 @@
         <v>1.007730235681439</v>
       </c>
       <c r="Y9" s="28" t="n">
-        <v>49.32158697919547</v>
+        <v>49.32158697919546</v>
       </c>
       <c r="Z9" s="28" t="n">
         <v>2.666727701822917</v>
       </c>
       <c r="AA9" s="28" t="n">
-        <v>27.7082968736361</v>
+        <v>27.70829687363607</v>
       </c>
       <c r="AB9" s="75" t="n">
         <v>0.4958331508324605</v>
       </c>
       <c r="AC9" s="75" t="n">
-        <v>0.6750965560222286</v>
+        <v>0.6750965560222291</v>
       </c>
       <c r="AD9" s="75" t="n">
-        <v>-0.1792634051897681</v>
+        <v>-0.1792634051897686</v>
       </c>
       <c r="AE9" s="72" t="n">
         <v>57.56683996439563</v>
@@ -36510,19 +36510,19 @@
         <v>26.89712426028244</v>
       </c>
       <c r="AB10" s="86" t="n">
-        <v>1.646518949086094</v>
+        <v>1.646518949086115</v>
       </c>
       <c r="AC10" s="86" t="n">
-        <v>1.246109153247539</v>
+        <v>1.246109153247557</v>
       </c>
       <c r="AD10" s="86" t="n">
-        <v>0.4004097958385544</v>
+        <v>0.4004097958385584</v>
       </c>
       <c r="AE10" s="83" t="n">
-        <v>62.33632246756212</v>
+        <v>62.33632246756211</v>
       </c>
       <c r="AF10" s="83" t="n">
-        <v>60.42082496731675</v>
+        <v>60.42082496731676</v>
       </c>
       <c r="AG10" s="83" t="n">
         <v>57.39760025024414</v>
@@ -36685,22 +36685,22 @@
         <v>43.84379224230761</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>16.28768411895964</v>
+        <v>16.28768411895962</v>
       </c>
       <c r="AB11" s="75" t="n">
         <v>0.2748249268329062</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.2665763600399785</v>
+        <v>0.2665763600399731</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>0.008248566792927681</v>
+        <v>0.00824856679293301</v>
       </c>
       <c r="AE11" s="72" t="n">
         <v>85.54884326150628</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.28376465646755</v>
+        <v>85.28376465646757</v>
       </c>
       <c r="AG11" s="72" t="n">
         <v>84.76320007324219</v>
@@ -36712,19 +36712,19 @@
         <v>82.82620025634766</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>87.02177445129659</v>
+        <v>87.02177445129658</v>
       </c>
       <c r="AK11" s="72" t="n">
         <v>85.45750045776367</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>83.89322646423075</v>
+        <v>83.89322646423076</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.4560496551410067</v>
+        <v>0.4560496551410063</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.660940198703905</v>
+        <v>3.660940198703871</v>
       </c>
       <c r="AO11" s="77" t="n">
         <v>1.587518985729019</v>
@@ -36857,7 +36857,7 @@
         <v>0.7782354903520596</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>49.70279104840946</v>
+        <v>49.70279104840947</v>
       </c>
       <c r="Z12" s="35" t="n">
         <v>13.95881526227118</v>
@@ -36866,13 +36866,13 @@
         <v>16.08831772726856</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.5918328907144286</v>
+        <v>0.5918328907144144</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.6319788439812178</v>
+        <v>0.6319788439812001</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.04014595326678927</v>
+        <v>-0.04014595326678572</v>
       </c>
       <c r="AE12" s="83" t="n">
         <v>117.5086305876881</v>
@@ -36902,10 +36902,10 @@
         <v>0.5234546827304895</v>
       </c>
       <c r="AN12" s="36" t="n">
-        <v>10.71498473957781</v>
+        <v>10.71498473957784</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.593612721626003</v>
+        <v>1.593612721626004</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -37044,13 +37044,13 @@
         <v>10.81669286471324</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.3143168001982701</v>
+        <v>0.3143168001982843</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.2797884514029897</v>
+        <v>0.2797884514030034</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>0.03452834879528038</v>
+        <v>0.03452834879528094</v>
       </c>
       <c r="AE13" s="72" t="n">
         <v>111.0944791425786</v>
@@ -37083,7 +37083,7 @@
         <v>6.535621689108432</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.639416635752044</v>
+        <v>1.639416635752043</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -37213,7 +37213,7 @@
         <v>0.8312317311463656</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>54.05114607743119</v>
+        <v>54.0511460774312</v>
       </c>
       <c r="Z14" s="35" t="n">
         <v>63.69229830228365</v>
@@ -37225,16 +37225,16 @@
         <v>0.3313050639745754</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.3552044666235043</v>
+        <v>0.3552044666235015</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>-0.02389940264892892</v>
+        <v>-0.02389940264892609</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>52.35194869861599</v>
+        <v>52.351948698616</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.05371149049343</v>
+        <v>52.05371149049345</v>
       </c>
       <c r="AG14" s="83" t="n">
         <v>51.50259986877441</v>
@@ -37252,13 +37252,13 @@
         <v>52.11450004577637</v>
       </c>
       <c r="AL14" s="83" t="n">
-        <v>50.7144779867765</v>
+        <v>50.71447798677651</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.6091047534590933</v>
+        <v>0.6091047534590939</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>5.37286957668255</v>
+        <v>5.372869576682524</v>
       </c>
       <c r="AO14" s="88" t="n">
         <v>1.598051105562417</v>
@@ -37400,13 +37400,13 @@
         <v>13.9078178571306</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>1.649009830500717</v>
+        <v>1.649009830500688</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>1.63950446753601</v>
+        <v>1.639504467535934</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>0.00950536296470661</v>
+        <v>0.009505362964754349</v>
       </c>
       <c r="AE15" s="72" t="n">
         <v>185.7681809138304</v>
@@ -37578,19 +37578,19 @@
         <v>9.317036453397709</v>
       </c>
       <c r="AB16" s="86" t="n">
-        <v>-0.009918025737832181</v>
+        <v>-0.009918025737825076</v>
       </c>
       <c r="AC16" s="86" t="n">
-        <v>0.007291229239312712</v>
+        <v>0.00729122923931381</v>
       </c>
       <c r="AD16" s="86" t="n">
-        <v>-0.01720925497714489</v>
+        <v>-0.01720925497713888</v>
       </c>
       <c r="AE16" s="83" t="n">
         <v>44.91476193702275</v>
       </c>
       <c r="AF16" s="83" t="n">
-        <v>44.94457948832036</v>
+        <v>44.94457948832035</v>
       </c>
       <c r="AG16" s="83" t="n">
         <v>44.8660001373291</v>
@@ -37617,7 +37617,7 @@
         <v>4.486387199614589</v>
       </c>
       <c r="AO16" s="88" t="n">
-        <v>1.294694383981368</v>
+        <v>1.294694383981369</v>
       </c>
       <c r="AP16" s="83" t="n">
         <v>46.45500183105469</v>
@@ -37756,19 +37756,19 @@
         <v>11.17206171522052</v>
       </c>
       <c r="AB17" s="75" t="n">
-        <v>-0.3136109484589511</v>
+        <v>-0.313610948458944</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.3332508829509392</v>
+        <v>-0.3332508829509404</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>0.01963993449198814</v>
+        <v>0.01963993449199641</v>
       </c>
       <c r="AE17" s="72" t="n">
-        <v>43.96551253654572</v>
+        <v>43.96551253654573</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>44.25147428242903</v>
+        <v>44.25147428242905</v>
       </c>
       <c r="AG17" s="72" t="n">
         <v>44.84980010986328</v>
@@ -37953,19 +37953,19 @@
         <v>20.45565099589324</v>
       </c>
       <c r="AB19" s="75" t="n">
-        <v>6.225556440449054</v>
+        <v>6.225556440449395</v>
       </c>
       <c r="AC19" s="75" t="n">
-        <v>6.79337964136668</v>
+        <v>6.793379641366933</v>
       </c>
       <c r="AD19" s="75" t="n">
-        <v>-0.5678232009176254</v>
+        <v>-0.5678232009175375</v>
       </c>
       <c r="AE19" s="72" t="n">
         <v>768.4921473872819</v>
       </c>
       <c r="AF19" s="72" t="n">
-        <v>763.0748134791539</v>
+        <v>763.0748134791538</v>
       </c>
       <c r="AG19" s="72" t="n">
         <v>750.9438049316407</v>
@@ -37977,22 +37977,22 @@
         <v>707.1325009155273</v>
       </c>
       <c r="AJ19" s="72" t="n">
-        <v>790.8932869772848</v>
+        <v>790.8932869772847</v>
       </c>
       <c r="AK19" s="72" t="n">
         <v>760.9875030517578</v>
       </c>
       <c r="AL19" s="72" t="n">
-        <v>731.0817191262308</v>
+        <v>731.081719126231</v>
       </c>
       <c r="AM19" s="76" t="n">
-        <v>0.5269592085964901</v>
+        <v>0.5269592085964903</v>
       </c>
       <c r="AN19" s="29" t="n">
-        <v>7.859730627795333</v>
+        <v>7.859730627795303</v>
       </c>
       <c r="AO19" s="77" t="n">
-        <v>0.9267135082935865</v>
+        <v>0.9267135082935866</v>
       </c>
       <c r="AP19" s="72" t="n">
         <v>779.3699951171875</v>
@@ -38120,25 +38120,25 @@
         <v>0.8364699118268181</v>
       </c>
       <c r="Y20" s="35" t="n">
-        <v>48.80395267781023</v>
+        <v>48.80395267781022</v>
       </c>
       <c r="Z20" s="35" t="n">
         <v>51.49708843837153</v>
       </c>
       <c r="AA20" s="35" t="n">
-        <v>14.56182599759823</v>
+        <v>14.56182599759822</v>
       </c>
       <c r="AB20" s="86" t="n">
-        <v>3.955405762511646</v>
+        <v>3.955405762511987</v>
       </c>
       <c r="AC20" s="86" t="n">
-        <v>3.384830666588307</v>
+        <v>3.384830666588568</v>
       </c>
       <c r="AD20" s="86" t="n">
-        <v>0.5705750959233384</v>
+        <v>0.5705750959234184</v>
       </c>
       <c r="AE20" s="83" t="n">
-        <v>718.5942778881414</v>
+        <v>718.5942778881415</v>
       </c>
       <c r="AF20" s="83" t="n">
         <v>714.2789733211566</v>
@@ -38305,19 +38305,19 @@
         <v>13.5840952341048</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>1.956269142453095</v>
+        <v>1.956269142453152</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>2.078349414960715</v>
+        <v>2.078349414960771</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.12208027250762</v>
+        <v>-0.1220802725076187</v>
       </c>
       <c r="AE21" s="72" t="n">
         <v>300.794911715667</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>299.0747647352642</v>
+        <v>299.0747647352641</v>
       </c>
       <c r="AG21" s="72" t="n">
         <v>296.32080078125</v>
@@ -38344,7 +38344,7 @@
         <v>6.447098227373758</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.245993808028674</v>
+        <v>1.245993808028673</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -38478,22 +38478,22 @@
         <v>36.69524361603511</v>
       </c>
       <c r="AA22" s="35" t="n">
-        <v>19.41314022389118</v>
+        <v>19.41314022389117</v>
       </c>
       <c r="AB22" s="86" t="n">
-        <v>-8.869129750904563</v>
+        <v>-8.869129750904648</v>
       </c>
       <c r="AC22" s="86" t="n">
-        <v>-10.73989559225267</v>
+        <v>-10.73989559225276</v>
       </c>
       <c r="AD22" s="86" t="n">
-        <v>1.870765841348103</v>
+        <v>1.870765841348117</v>
       </c>
       <c r="AE22" s="83" t="n">
         <v>131.8058091900632</v>
       </c>
       <c r="AF22" s="83" t="n">
-        <v>138.4327341422042</v>
+        <v>138.4327341422041</v>
       </c>
       <c r="AG22" s="83" t="n">
         <v>173.568999786377</v>
@@ -38505,7 +38505,7 @@
         <v>104.9238499927521</v>
       </c>
       <c r="AJ22" s="83" t="n">
-        <v>156.9842944527779</v>
+        <v>156.9842944527778</v>
       </c>
       <c r="AK22" s="83" t="n">
         <v>128.8119998931885</v>
@@ -38514,10 +38514,10 @@
         <v>100.6397053335991</v>
       </c>
       <c r="AM22" s="87" t="n">
-        <v>0.3828281311138606</v>
+        <v>0.3828281311138605</v>
       </c>
       <c r="AN22" s="36" t="n">
-        <v>43.74172372597274</v>
+        <v>43.74172372597266</v>
       </c>
       <c r="AO22" s="88" t="n">
         <v>15.80835645386891</v>
@@ -38678,13 +38678,13 @@
         <v>19.00495703277948</v>
       </c>
       <c r="AB24" s="75" t="n">
-        <v>-1.560752122403926</v>
+        <v>-1.560752122403983</v>
       </c>
       <c r="AC24" s="75" t="n">
-        <v>-1.099356309724241</v>
+        <v>-1.099356309724275</v>
       </c>
       <c r="AD24" s="75" t="n">
-        <v>-0.4613958126796851</v>
+        <v>-0.4613958126797078</v>
       </c>
       <c r="AE24" s="72" t="n">
         <v>310.3438086253014</v>
@@ -38702,19 +38702,19 @@
         <v>281.3000494384765</v>
       </c>
       <c r="AJ24" s="72" t="n">
-        <v>340.6267756646938</v>
+        <v>340.6267756646939</v>
       </c>
       <c r="AK24" s="72" t="n">
         <v>315.5219985961914</v>
       </c>
       <c r="AL24" s="72" t="n">
-        <v>290.417221527689</v>
+        <v>290.4172215276889</v>
       </c>
       <c r="AM24" s="76" t="n">
-        <v>0.4159122028508317</v>
+        <v>0.4159122028508319</v>
       </c>
       <c r="AN24" s="29" t="n">
-        <v>15.9131706696824</v>
+        <v>15.91317066968243</v>
       </c>
       <c r="AO24" s="77" t="n">
         <v>2.508032895576729</v>
@@ -38854,19 +38854,19 @@
         <v>9.796929843118427</v>
       </c>
       <c r="AB25" s="86" t="n">
-        <v>-7.303385573950834</v>
+        <v>-7.303385573950777</v>
       </c>
       <c r="AC25" s="86" t="n">
-        <v>-6.679505498818102</v>
+        <v>-6.679505498818137</v>
       </c>
       <c r="AD25" s="86" t="n">
-        <v>-0.6238800751327318</v>
+        <v>-0.6238800751326403</v>
       </c>
       <c r="AE25" s="83" t="n">
-        <v>482.1358747363252</v>
+        <v>482.1358747363253</v>
       </c>
       <c r="AF25" s="83" t="n">
-        <v>489.9707779095201</v>
+        <v>489.97077790952</v>
       </c>
       <c r="AG25" s="83" t="n">
         <v>509.8172009277343</v>
@@ -39027,19 +39027,19 @@
         <v>8.075922180696777</v>
       </c>
       <c r="AA26" s="28" t="n">
-        <v>23.19066374928627</v>
+        <v>23.19066374928626</v>
       </c>
       <c r="AB26" s="75" t="n">
-        <v>4.14660447604814</v>
+        <v>4.146604476048083</v>
       </c>
       <c r="AC26" s="75" t="n">
-        <v>5.383142783018645</v>
+        <v>5.383142783018616</v>
       </c>
       <c r="AD26" s="75" t="n">
-        <v>-1.236538306970505</v>
+        <v>-1.236538306970534</v>
       </c>
       <c r="AE26" s="72" t="n">
-        <v>263.6322757194798</v>
+        <v>263.6322757194797</v>
       </c>
       <c r="AF26" s="72" t="n">
         <v>260.6857139081197</v>
@@ -39203,16 +39203,16 @@
         <v>94.71395013767165</v>
       </c>
       <c r="AA27" s="35" t="n">
-        <v>18.98248015623538</v>
+        <v>18.98248015623537</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>1.57959442348097</v>
+        <v>1.579594423480955</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>0.8703929939722608</v>
+        <v>0.8703929939722633</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.7092014295087088</v>
+        <v>0.709201429508692</v>
       </c>
       <c r="AE27" s="83" t="n">
         <v>81.27933392395477</v>
@@ -39245,7 +39245,7 @@
         <v>22.37011521072027</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.837390559371579</v>
+        <v>2.83739055937158</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -39373,7 +39373,7 @@
         <v>0.5223567345089022</v>
       </c>
       <c r="Y28" s="28" t="n">
-        <v>41.39273257620361</v>
+        <v>41.39273257620362</v>
       </c>
       <c r="Z28" s="28" t="n">
         <v>39.21396852825984</v>
@@ -39385,16 +39385,16 @@
         <v>-8.6667569398154</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-8.99257869217144</v>
+        <v>-8.992578692171451</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>0.3258217523560401</v>
+        <v>0.3258217523560507</v>
       </c>
       <c r="AE28" s="72" t="n">
         <v>261.3257696418786</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>269.1805991782201</v>
+        <v>269.1805991782202</v>
       </c>
       <c r="AG28" s="72" t="n">
         <v>303.6457986450195</v>
@@ -39555,16 +39555,16 @@
         <v>48.19025753151218</v>
       </c>
       <c r="AA29" s="35" t="n">
-        <v>16.24819573658247</v>
+        <v>16.24819573658246</v>
       </c>
       <c r="AB29" s="86" t="n">
         <v>-0.2621563458793617</v>
       </c>
       <c r="AC29" s="86" t="n">
-        <v>-0.6855757555374384</v>
+        <v>-0.685575755537451</v>
       </c>
       <c r="AD29" s="86" t="n">
-        <v>0.4234194096580768</v>
+        <v>0.4234194096580893</v>
       </c>
       <c r="AE29" s="83" t="n">
         <v>68.00230489553506</v>
@@ -39591,13 +39591,13 @@
         <v>53.05201382499448</v>
       </c>
       <c r="AM29" s="87" t="n">
-        <v>0.482520194239778</v>
+        <v>0.4825201942397782</v>
       </c>
       <c r="AN29" s="36" t="n">
-        <v>37.99675020477849</v>
+        <v>37.9967502047785</v>
       </c>
       <c r="AO29" s="88" t="n">
-        <v>8.123231676163808</v>
+        <v>8.12323167616381</v>
       </c>
       <c r="AP29" s="83" t="n">
         <v>133.8600006103516</v>
@@ -39737,16 +39737,16 @@
         <v>-3.101542751203567</v>
       </c>
       <c r="AC30" s="75" t="n">
-        <v>2.664916921501678</v>
+        <v>2.66491692150171</v>
       </c>
       <c r="AD30" s="75" t="n">
-        <v>-5.766459672705246</v>
+        <v>-5.766459672705277</v>
       </c>
       <c r="AE30" s="72" t="n">
         <v>385.6012207601366</v>
       </c>
       <c r="AF30" s="72" t="n">
-        <v>393.4127160594804</v>
+        <v>393.4127160594805</v>
       </c>
       <c r="AG30" s="72" t="n">
         <v>388.5758001708984</v>
@@ -39907,22 +39907,22 @@
         <v>67.62633648596935</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>16.86075198106713</v>
+        <v>16.86075198106712</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>0.9059042129727573</v>
+        <v>0.9059042129727288</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>0.284792168240862</v>
+        <v>0.2847921682408465</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>0.6211120447318953</v>
+        <v>0.6211120447318823</v>
       </c>
       <c r="AE31" s="83" t="n">
         <v>96.69942269943057</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>95.19283874215213</v>
+        <v>95.19283874215216</v>
       </c>
       <c r="AG31" s="83" t="n">
         <v>95.99439971923829</v>
@@ -39949,7 +39949,7 @@
         <v>20.18553954799183</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>3.861750297063762</v>
+        <v>3.861750297063761</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -40077,28 +40077,28 @@
         <v>0.5279058940218972</v>
       </c>
       <c r="Y32" s="28" t="n">
-        <v>49.55829908126501</v>
+        <v>49.55829908126502</v>
       </c>
       <c r="Z32" s="28" t="n">
         <v>41.74370458726978</v>
       </c>
       <c r="AA32" s="28" t="n">
-        <v>18.86733456807689</v>
+        <v>18.86733456807688</v>
       </c>
       <c r="AB32" s="75" t="n">
-        <v>3.092834307673257</v>
+        <v>3.092834307673243</v>
       </c>
       <c r="AC32" s="75" t="n">
-        <v>2.336091681122422</v>
+        <v>2.336091681122403</v>
       </c>
       <c r="AD32" s="75" t="n">
-        <v>0.7567426265508352</v>
+        <v>0.7567426265508401</v>
       </c>
       <c r="AE32" s="72" t="n">
         <v>94.67691854295006</v>
       </c>
       <c r="AF32" s="72" t="n">
-        <v>90.91093044660808</v>
+        <v>90.91093044660809</v>
       </c>
       <c r="AG32" s="72" t="n">
         <v>90.07100021362305</v>
@@ -40116,16 +40116,16 @@
         <v>86.8800006866455</v>
       </c>
       <c r="AL32" s="72" t="n">
-        <v>60.09321264473191</v>
+        <v>60.09321264473192</v>
       </c>
       <c r="AM32" s="76" t="n">
-        <v>0.5537578720725791</v>
+        <v>0.5537578720725792</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>61.66387622055128</v>
+        <v>61.66387622055125</v>
       </c>
       <c r="AO32" s="77" t="n">
-        <v>9.321068919838295</v>
+        <v>9.321068919838291</v>
       </c>
       <c r="AP32" s="72" t="n">
         <v>153.1999969482422</v>
@@ -40262,13 +40262,13 @@
         <v>11.93498744893341</v>
       </c>
       <c r="AB33" s="86" t="n">
-        <v>12.58396333580407</v>
+        <v>12.58396333580424</v>
       </c>
       <c r="AC33" s="86" t="n">
-        <v>15.16860018138518</v>
+        <v>15.16860018138532</v>
       </c>
       <c r="AD33" s="86" t="n">
-        <v>-2.584636845581111</v>
+        <v>-2.584636845581079</v>
       </c>
       <c r="AE33" s="83" t="n">
         <v>456.563636140876</v>
@@ -40286,7 +40286,7 @@
         <v>235.663949432373</v>
       </c>
       <c r="AJ33" s="83" t="n">
-        <v>509.2885707731979</v>
+        <v>509.2885707731978</v>
       </c>
       <c r="AK33" s="83" t="n">
         <v>443.8099990844727</v>
@@ -40298,10 +40298,10 @@
         <v>0.4310461417202027</v>
       </c>
       <c r="AN33" s="36" t="n">
-        <v>29.50747924733544</v>
+        <v>29.50747924733542</v>
       </c>
       <c r="AO33" s="88" t="n">
-        <v>7.267655835129472</v>
+        <v>7.267655835129474</v>
       </c>
       <c r="AP33" s="83" t="n">
         <v>514</v>
@@ -40429,25 +40429,25 @@
         <v>0.7734646092116633</v>
       </c>
       <c r="Y34" s="28" t="n">
-        <v>43.10031208947679</v>
+        <v>43.10031208947678</v>
       </c>
       <c r="Z34" s="28" t="n">
         <v>4.447851632630818</v>
       </c>
       <c r="AA34" s="28" t="n">
-        <v>9.762805716661694</v>
+        <v>9.762805716661699</v>
       </c>
       <c r="AB34" s="75" t="n">
-        <v>-2.667885092349252</v>
+        <v>-2.667885092349366</v>
       </c>
       <c r="AC34" s="75" t="n">
-        <v>-1.666236891569075</v>
+        <v>-1.666236891569117</v>
       </c>
       <c r="AD34" s="75" t="n">
-        <v>-1.001648200780177</v>
+        <v>-1.001648200780248</v>
       </c>
       <c r="AE34" s="72" t="n">
-        <v>342.9966331192264</v>
+        <v>342.9966331192265</v>
       </c>
       <c r="AF34" s="72" t="n">
         <v>346.3115080798078</v>
@@ -40471,13 +40471,13 @@
         <v>318.0042775103381</v>
       </c>
       <c r="AM34" s="76" t="n">
-        <v>0.3647912007758704</v>
+        <v>0.3647912007758701</v>
       </c>
       <c r="AN34" s="29" t="n">
-        <v>16.01526526511088</v>
+        <v>16.01526526511084</v>
       </c>
       <c r="AO34" s="77" t="n">
-        <v>2.73939245486919</v>
+        <v>2.739392454869189</v>
       </c>
       <c r="AP34" s="72" t="n">
         <v>404.4700012207031</v>
@@ -40611,16 +40611,16 @@
         <v>52.0218448011869</v>
       </c>
       <c r="AA35" s="35" t="n">
-        <v>16.88360421817563</v>
+        <v>16.88360421817562</v>
       </c>
       <c r="AB35" s="86" t="n">
-        <v>0.3531594294068441</v>
+        <v>0.3531594294068299</v>
       </c>
       <c r="AC35" s="86" t="n">
-        <v>-0.3955574325988784</v>
+        <v>-0.3955574325988876</v>
       </c>
       <c r="AD35" s="86" t="n">
-        <v>0.7487168620057225</v>
+        <v>0.7487168620057175</v>
       </c>
       <c r="AE35" s="83" t="n">
         <v>42.49049999537541</v>
@@ -40644,16 +40644,16 @@
         <v>39.68149976730346</v>
       </c>
       <c r="AL35" s="83" t="n">
-        <v>32.07072520452169</v>
+        <v>32.0707252045217</v>
       </c>
       <c r="AM35" s="87" t="n">
-        <v>0.6917346705478362</v>
+        <v>0.6917346705478363</v>
       </c>
       <c r="AN35" s="36" t="n">
-        <v>38.35930903525402</v>
+        <v>38.35930903525399</v>
       </c>
       <c r="AO35" s="88" t="n">
-        <v>9.020229584569961</v>
+        <v>9.020229584569959</v>
       </c>
       <c r="AP35" s="83" t="n">
         <v>76.87000274658203</v>
@@ -40787,22 +40787,22 @@
         <v>29.65829344845205</v>
       </c>
       <c r="AA36" s="28" t="n">
-        <v>14.62974814664449</v>
+        <v>14.6297481466445</v>
       </c>
       <c r="AB36" s="75" t="n">
-        <v>-2.174500449274234</v>
+        <v>-2.174500449274205</v>
       </c>
       <c r="AC36" s="75" t="n">
-        <v>-2.404499589465677</v>
+        <v>-2.404499589465653</v>
       </c>
       <c r="AD36" s="75" t="n">
-        <v>0.2299991401914432</v>
+        <v>0.2299991401914472</v>
       </c>
       <c r="AE36" s="72" t="n">
         <v>97.04435986402203</v>
       </c>
       <c r="AF36" s="72" t="n">
-        <v>98.86942301663389</v>
+        <v>98.86942301663387</v>
       </c>
       <c r="AG36" s="72" t="n">
         <v>108.5207997131348</v>
@@ -40829,7 +40829,7 @@
         <v>25.22456653274561</v>
       </c>
       <c r="AO36" s="77" t="n">
-        <v>7.347139420013754</v>
+        <v>7.347139420013756</v>
       </c>
       <c r="AP36" s="72" t="n">
         <v>142.3500061035156</v>
@@ -40963,22 +40963,22 @@
         <v>15.87915568779233</v>
       </c>
       <c r="AA37" s="35" t="n">
-        <v>34.22372488959985</v>
+        <v>34.22372488959984</v>
       </c>
       <c r="AB37" s="86" t="n">
-        <v>21.34065274775799</v>
+        <v>21.34065274775793</v>
       </c>
       <c r="AC37" s="86" t="n">
-        <v>24.07677003322646</v>
+        <v>24.0767700332264</v>
       </c>
       <c r="AD37" s="86" t="n">
-        <v>-2.736117285468474</v>
+        <v>-2.736117285468467</v>
       </c>
       <c r="AE37" s="83" t="n">
-        <v>485.1415360002722</v>
+        <v>485.1415360002723</v>
       </c>
       <c r="AF37" s="83" t="n">
-        <v>467.0302633659076</v>
+        <v>467.0302633659077</v>
       </c>
       <c r="AG37" s="83" t="n">
         <v>418.1269976806641</v>
@@ -41133,28 +41133,28 @@
         <v>2.458946520407303</v>
       </c>
       <c r="Y38" s="28" t="n">
-        <v>61.8364210170222</v>
+        <v>61.83642101702218</v>
       </c>
       <c r="Z38" s="28" t="n">
         <v>94.08154923886663</v>
       </c>
       <c r="AA38" s="28" t="n">
-        <v>12.9078618918056</v>
+        <v>12.90786189180561</v>
       </c>
       <c r="AB38" s="75" t="n">
-        <v>0.1898807549839603</v>
+        <v>0.1898807549839461</v>
       </c>
       <c r="AC38" s="75" t="n">
-        <v>-1.646578733838876</v>
+        <v>-1.646578733838905</v>
       </c>
       <c r="AD38" s="75" t="n">
-        <v>1.836459488822836</v>
+        <v>1.836459488822851</v>
       </c>
       <c r="AE38" s="72" t="n">
         <v>100.7251307782591</v>
       </c>
       <c r="AF38" s="72" t="n">
-        <v>98.73177204480621</v>
+        <v>98.73177204480623</v>
       </c>
       <c r="AG38" s="72" t="n">
         <v>99.70239959716797</v>
@@ -41166,22 +41166,22 @@
         <v>144.6817001342773</v>
       </c>
       <c r="AJ38" s="72" t="n">
-        <v>106.2035059523912</v>
+        <v>106.2035059523913</v>
       </c>
       <c r="AK38" s="72" t="n">
         <v>97.19000015258788</v>
       </c>
       <c r="AL38" s="72" t="n">
-        <v>88.1764943527846</v>
+        <v>88.17649435278446</v>
       </c>
       <c r="AM38" s="76" t="n">
-        <v>1.343179090060179</v>
+        <v>1.343179090060165</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>18.54821645365185</v>
+        <v>18.54821645365215</v>
       </c>
       <c r="AO38" s="77" t="n">
-        <v>5.843825538502213</v>
+        <v>5.843825538502212</v>
       </c>
       <c r="AP38" s="72" t="n">
         <v>365.2099914550781</v>
@@ -41321,13 +41321,13 @@
         <v>9.70025348309332</v>
       </c>
       <c r="AC39" s="86" t="n">
-        <v>-3.652897022716449</v>
+        <v>-3.652897022716685</v>
       </c>
       <c r="AD39" s="86" t="n">
-        <v>13.35315050580977</v>
+        <v>13.35315050581</v>
       </c>
       <c r="AE39" s="83" t="n">
-        <v>944.4442130617816</v>
+        <v>944.4442130617817</v>
       </c>
       <c r="AF39" s="83" t="n">
         <v>923.9806604627901</v>
@@ -41348,13 +41348,13 @@
         <v>893.9510009765625</v>
       </c>
       <c r="AL39" s="83" t="n">
-        <v>770.8769540945077</v>
+        <v>770.8769540945078</v>
       </c>
       <c r="AM39" s="87" t="n">
-        <v>0.8265473840732268</v>
+        <v>0.826547384073227</v>
       </c>
       <c r="AN39" s="36" t="n">
-        <v>27.53485297239048</v>
+        <v>27.53485297239046</v>
       </c>
       <c r="AO39" s="88" t="n">
         <v>7.126440530878421</v>
@@ -41494,19 +41494,19 @@
         <v>14.49458876896328</v>
       </c>
       <c r="AB40" s="75" t="n">
-        <v>8.842655229711426</v>
+        <v>8.842655229711397</v>
       </c>
       <c r="AC40" s="75" t="n">
-        <v>5.609251599588354</v>
+        <v>5.609251599588329</v>
       </c>
       <c r="AD40" s="75" t="n">
-        <v>3.233403630123072</v>
+        <v>3.233403630123068</v>
       </c>
       <c r="AE40" s="72" t="n">
         <v>234.0518499476789</v>
       </c>
       <c r="AF40" s="72" t="n">
-        <v>222.7234950335359</v>
+        <v>222.7234950335358</v>
       </c>
       <c r="AG40" s="72" t="n">
         <v>222.9508004760742</v>
@@ -41670,19 +41670,19 @@
         <v>21.58112097660603</v>
       </c>
       <c r="AB41" s="86" t="n">
-        <v>1.345497553319078</v>
+        <v>1.345497553319063</v>
       </c>
       <c r="AC41" s="86" t="n">
-        <v>0.5209663212029256</v>
+        <v>0.5209663212029113</v>
       </c>
       <c r="AD41" s="86" t="n">
-        <v>0.824531232116152</v>
+        <v>0.8245312321161521</v>
       </c>
       <c r="AE41" s="83" t="n">
         <v>77.79605698228166</v>
       </c>
       <c r="AF41" s="83" t="n">
-        <v>75.73208464596749</v>
+        <v>75.7320846459675</v>
       </c>
       <c r="AG41" s="83" t="n">
         <v>74.56859924316406</v>
@@ -41694,22 +41694,22 @@
         <v>88.56944972991943</v>
       </c>
       <c r="AJ41" s="83" t="n">
-        <v>80.47402358092724</v>
+        <v>80.47402358092722</v>
       </c>
       <c r="AK41" s="83" t="n">
         <v>74.80799942016601</v>
       </c>
       <c r="AL41" s="83" t="n">
-        <v>69.14197525940479</v>
+        <v>69.1419752594048</v>
       </c>
       <c r="AM41" s="87" t="n">
-        <v>0.970523935143799</v>
+        <v>0.9705239351438001</v>
       </c>
       <c r="AN41" s="36" t="n">
-        <v>15.14817721280709</v>
+        <v>15.14817721280705</v>
       </c>
       <c r="AO41" s="88" t="n">
-        <v>3.032105014274704</v>
+        <v>3.032105014274705</v>
       </c>
       <c r="AP41" s="83" t="n">
         <v>126.7099990844727</v>
@@ -41837,7 +41837,7 @@
         <v>0.8547039591262054</v>
       </c>
       <c r="Y42" s="28" t="n">
-        <v>47.63396033878345</v>
+        <v>47.63396033878346</v>
       </c>
       <c r="Z42" s="28" t="n">
         <v>58.47454921707772</v>
@@ -41846,13 +41846,13 @@
         <v>20.44512399218472</v>
       </c>
       <c r="AB42" s="75" t="n">
-        <v>-0.2028309568073645</v>
+        <v>-0.2028309568073663</v>
       </c>
       <c r="AC42" s="75" t="n">
-        <v>-0.4176786762229329</v>
+        <v>-0.4176786762229349</v>
       </c>
       <c r="AD42" s="75" t="n">
-        <v>0.2148477194155684</v>
+        <v>0.2148477194155686</v>
       </c>
       <c r="AE42" s="72" t="n">
         <v>10.19846650097801</v>
@@ -41870,19 +41870,19 @@
         <v>9.426949989795684</v>
       </c>
       <c r="AJ42" s="72" t="n">
-        <v>10.9659673985187</v>
+        <v>10.96596739851869</v>
       </c>
       <c r="AK42" s="72" t="n">
         <v>9.663000011444092</v>
       </c>
       <c r="AL42" s="72" t="n">
-        <v>8.360032624369488</v>
+        <v>8.36003262436949</v>
       </c>
       <c r="AM42" s="76" t="n">
-        <v>0.68688096567773</v>
+        <v>0.6868809656777303</v>
       </c>
       <c r="AN42" s="29" t="n">
-        <v>26.96817521538803</v>
+        <v>26.968175215388</v>
       </c>
       <c r="AO42" s="77" t="n">
         <v>5.875732725396289</v>
@@ -42025,16 +42025,16 @@
         <v>4.246990234479028</v>
       </c>
       <c r="AC43" s="86" t="n">
-        <v>4.156279518282438</v>
+        <v>4.156279518282417</v>
       </c>
       <c r="AD43" s="86" t="n">
-        <v>0.09071071619659055</v>
+        <v>0.09071071619661097</v>
       </c>
       <c r="AE43" s="83" t="n">
         <v>219.407113555551</v>
       </c>
       <c r="AF43" s="83" t="n">
-        <v>215.2399868944047</v>
+        <v>215.2399868944048</v>
       </c>
       <c r="AG43" s="83" t="n">
         <v>207.2909991455078</v>
@@ -42198,13 +42198,13 @@
         <v>31.5170009954653</v>
       </c>
       <c r="AB44" s="75" t="n">
-        <v>11.9277517899894</v>
+        <v>11.92775178998926</v>
       </c>
       <c r="AC44" s="75" t="n">
-        <v>10.68623867544033</v>
+        <v>10.68623867544024</v>
       </c>
       <c r="AD44" s="75" t="n">
-        <v>1.241513114549067</v>
+        <v>1.241513114549015</v>
       </c>
       <c r="AE44" s="72" t="n">
         <v>171.3851111223755</v>
@@ -42365,22 +42365,22 @@
         <v>0.7522743084254828</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>43.54814409687217</v>
+        <v>43.54814409687216</v>
       </c>
       <c r="Z45" s="35" t="n">
         <v>68.70673225167022</v>
       </c>
       <c r="AA45" s="35" t="n">
-        <v>14.34089696523808</v>
+        <v>14.34089696523807</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-4.316987866209786</v>
+        <v>-4.316987866209843</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-5.687213828765994</v>
+        <v>-5.687213828765998</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.370225962556209</v>
+        <v>1.370225962556155</v>
       </c>
       <c r="AE45" s="83" t="n">
         <v>161.9545834184899</v>
@@ -42410,10 +42410,10 @@
         <v>0.4920760337229503</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>13.80245334386981</v>
+        <v>13.80245334386984</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>4.496216031886696</v>
+        <v>4.496216031886697</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -42550,19 +42550,19 @@
         <v>18.21088368262421</v>
       </c>
       <c r="AB46" s="75" t="n">
-        <v>-0.5800686097855561</v>
+        <v>-0.5800686097855987</v>
       </c>
       <c r="AC46" s="75" t="n">
-        <v>-1.43516328882965</v>
+        <v>-1.435163288829686</v>
       </c>
       <c r="AD46" s="75" t="n">
-        <v>0.8550946790440936</v>
+        <v>0.8550946790440876</v>
       </c>
       <c r="AE46" s="72" t="n">
-        <v>77.24951515843941</v>
+        <v>77.24951515843942</v>
       </c>
       <c r="AF46" s="72" t="n">
-        <v>76.87578555856943</v>
+        <v>76.87578555856945</v>
       </c>
       <c r="AG46" s="72" t="n">
         <v>82.70220024108886</v>
@@ -42574,22 +42574,22 @@
         <v>78.67007514953613</v>
       </c>
       <c r="AJ46" s="72" t="n">
-        <v>88.11954108639881</v>
+        <v>88.1195410863988</v>
       </c>
       <c r="AK46" s="72" t="n">
         <v>73.63999996185302</v>
       </c>
       <c r="AL46" s="72" t="n">
-        <v>59.16045883730724</v>
+        <v>59.16045883730725</v>
       </c>
       <c r="AM46" s="76" t="n">
-        <v>0.4761731740089076</v>
+        <v>0.4761731740089077</v>
       </c>
       <c r="AN46" s="29" t="n">
-        <v>39.32520676818706</v>
+        <v>39.32520676818703</v>
       </c>
       <c r="AO46" s="77" t="n">
-        <v>8.152002047685572</v>
+        <v>8.152002047685569</v>
       </c>
       <c r="AP46" s="72" t="n">
         <v>151</v>
@@ -42717,7 +42717,7 @@
         <v>0.6532640256435032</v>
       </c>
       <c r="Y47" s="35" t="n">
-        <v>53.88456461879663</v>
+        <v>53.88456461879665</v>
       </c>
       <c r="Z47" s="35" t="n">
         <v>67.82765531546728</v>
@@ -42726,19 +42726,19 @@
         <v>16.08589152481968</v>
       </c>
       <c r="AB47" s="86" t="n">
-        <v>14.75959099894385</v>
+        <v>14.75959099894362</v>
       </c>
       <c r="AC47" s="86" t="n">
-        <v>-38.9398377103755</v>
+        <v>-38.93983771037566</v>
       </c>
       <c r="AD47" s="86" t="n">
-        <v>53.69942870931935</v>
+        <v>53.69942870931929</v>
       </c>
       <c r="AE47" s="83" t="n">
         <v>1548.220017096143</v>
       </c>
       <c r="AF47" s="83" t="n">
-        <v>1487.432932977266</v>
+        <v>1487.432932977265</v>
       </c>
       <c r="AG47" s="83" t="n">
         <v>1655.117795410156</v>
@@ -42899,22 +42899,22 @@
         <v>84.2437731252695</v>
       </c>
       <c r="AA48" s="28" t="n">
-        <v>20.15000029563065</v>
+        <v>20.15000029563064</v>
       </c>
       <c r="AB48" s="75" t="n">
-        <v>-5.741738360651595</v>
+        <v>-5.741738360651709</v>
       </c>
       <c r="AC48" s="75" t="n">
-        <v>-11.11435006555865</v>
+        <v>-11.11435006555873</v>
       </c>
       <c r="AD48" s="75" t="n">
-        <v>5.372611704907051</v>
+        <v>5.372611704907024</v>
       </c>
       <c r="AE48" s="72" t="n">
-        <v>339.8603945513723</v>
+        <v>339.8603945513722</v>
       </c>
       <c r="AF48" s="72" t="n">
-        <v>340.4692389443176</v>
+        <v>340.4692389443175</v>
       </c>
       <c r="AG48" s="72" t="n">
         <v>366.232197265625</v>
@@ -42932,16 +42932,16 @@
         <v>325.6504974365234</v>
       </c>
       <c r="AL48" s="72" t="n">
-        <v>297.4353967542557</v>
+        <v>297.4353967542558</v>
       </c>
       <c r="AM48" s="76" t="n">
-        <v>0.8451964900931813</v>
+        <v>0.845196490093182</v>
       </c>
       <c r="AN48" s="29" t="n">
-        <v>17.32845544801751</v>
+        <v>17.32845544801748</v>
       </c>
       <c r="AO48" s="77" t="n">
-        <v>3.848218761996399</v>
+        <v>3.8482187619964</v>
       </c>
       <c r="AP48" s="72" t="n">
         <v>498.8299865722656</v>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'08-24'!$5:$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'08-21'!$A$6:$AZ$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'08-21'!$5:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -855,12 +855,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$C$14:$C$23</f>
+              <f>'Dashboard'!$C$14:$C$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$14:$E$23</f>
+              <f>'Dashboard'!$E$14:$E$24</f>
             </numRef>
           </val>
         </ser>
@@ -1215,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:S51"/>
+  <dimension ref="B2:S52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 28 Aug 2026, 01:35 AM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 28 Aug 2026, 04:22 AM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1376,14 +1376,14 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
@@ -1397,14 +1397,14 @@
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="O8" s="10" t="n"/>
       <c r="P8" s="10" t="n"/>
       <c r="Q8" s="16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="R8" s="12" t="n"/>
@@ -1413,14 +1413,14 @@
     <row r="9" ht="15" customHeight="1">
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>of 39 names</t>
+          <t>of 40 names</t>
         </is>
       </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>of 39 names</t>
+          <t>of 40 names</t>
         </is>
       </c>
       <c r="F9" s="8" t="n"/>
@@ -1441,7 +1441,7 @@
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>of 39 names</t>
+          <t>of 40 names</t>
         </is>
       </c>
       <c r="O9" s="10" t="n"/>
@@ -1547,31 +1547,31 @@
       </c>
       <c r="C15" s="31" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>State Street Financial Select Sector SPDR ETF</t>
+          <t>State Street Energy Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E15" s="33" t="n">
-        <v>-0.006522438454611534</v>
+        <v>-0.002242501825469811</v>
       </c>
       <c r="F15" s="34" t="n">
         <v>6</v>
       </c>
       <c r="G15" s="35" t="n">
-        <v>56.3701733921237</v>
+        <v>60.14216437335956</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>2.69840758955866</v>
+        <v>7.412108906110726</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>0.01633011927509909</v>
+        <v>-0.02290194642310051</v>
       </c>
       <c r="J15" s="33" t="n">
-        <v>0.02117150240787624</v>
+        <v>0.06206307408265466</v>
       </c>
     </row>
     <row r="16">
@@ -1580,31 +1580,31 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>State Street Utilities Select Sector SPDR ETF</t>
+          <t>State Street Financial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>-0.007584418043843133</v>
+        <v>-0.006522438454611534</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>39.75511151129263</v>
+        <v>56.3701733921237</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>-3.44796702447473</v>
+        <v>2.69840758955866</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>-0.01347955554986158</v>
+        <v>0.01633011927509909</v>
       </c>
       <c r="J16" s="26" t="n">
-        <v>-0.0385214773572532</v>
+        <v>0.02117150240787624</v>
       </c>
     </row>
     <row r="17">
@@ -1613,31 +1613,31 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D17" s="32" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>State Street Utilities Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E17" s="33" t="n">
-        <v>-0.008198223248004122</v>
+        <v>-0.007584418043843133</v>
       </c>
       <c r="F17" s="34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G17" s="35" t="n">
-        <v>57.40881785747306</v>
+        <v>39.75511151129263</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>2.978900556338204</v>
+        <v>-3.44796702447473</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>0.01545214424999508</v>
+        <v>-0.01347955554986158</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>0.0287977931084924</v>
+        <v>-0.0385214773572532</v>
       </c>
     </row>
     <row r="18">
@@ -1646,31 +1646,31 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>State Street Industrial Select Sector SPDR ETF</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>-0.008539388474021248</v>
+        <v>-0.008198223248004122</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>41.45211287326175</v>
+        <v>57.40881785747306</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>-1.721736673768559</v>
+        <v>2.978900556338204</v>
       </c>
       <c r="I18" s="26" t="n">
-        <v>-0.005395790163263192</v>
+        <v>0.01545214424999508</v>
       </c>
       <c r="J18" s="26" t="n">
-        <v>0.01211366096052813</v>
+        <v>0.0287977931084924</v>
       </c>
     </row>
     <row r="19">
@@ -1679,31 +1679,31 @@
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="D19" s="32" t="inlineStr">
         <is>
-          <t>State Street Real Estate Select Sector SPDR ETF</t>
+          <t>State Street Industrial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>-0.009536489326250397</v>
+        <v>-0.008539388474021248</v>
       </c>
       <c r="F19" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="35" t="n">
-        <v>45.5010127355274</v>
+        <v>41.45211287326175</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>-0.466244912272562</v>
+        <v>-1.721736673768559</v>
       </c>
       <c r="I19" s="33" t="n">
-        <v>-0.009316813810625213</v>
+        <v>-0.005395790163263192</v>
       </c>
       <c r="J19" s="33" t="n">
-        <v>-0.02828544958565382</v>
+        <v>0.01211366096052813</v>
       </c>
     </row>
     <row r="20">
@@ -1712,31 +1712,31 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>State Street Communication Services Select Sector SPDR ETF</t>
+          <t>State Street Real Estate Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.01065622006694034</v>
+        <v>-0.009536489326250397</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>51.01216980941457</v>
+        <v>45.5010127355274</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>1.261017306224188</v>
+        <v>-0.466244912272562</v>
       </c>
       <c r="I20" s="26" t="n">
-        <v>0.006595621204560587</v>
+        <v>-0.009316813810625213</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.01735002729262392</v>
+        <v>-0.02828544958565382</v>
       </c>
     </row>
     <row r="21">
@@ -1745,31 +1745,31 @@
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D21" s="32" t="inlineStr">
         <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>-0.01092528481292099</v>
+        <v>-0.01065622006694034</v>
       </c>
       <c r="F21" s="34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>46.11854978280344</v>
+        <v>51.01216980941457</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>-0.233834601405758</v>
+        <v>1.261017306224188</v>
       </c>
       <c r="I21" s="33" t="n">
-        <v>-0.006856385410228039</v>
+        <v>0.006595621204560587</v>
       </c>
       <c r="J21" s="33" t="n">
-        <v>0.03825819030297883</v>
+        <v>0.01735002729262392</v>
       </c>
     </row>
     <row r="22">
@@ -1778,31 +1778,31 @@
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
-          <t>State Street Health Care Select Sector SPDR ETF</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>-0.01129417731304438</v>
+        <v>-0.01092528481292099</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>58.26336947672519</v>
+        <v>46.11854978280344</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>5.048552178820076</v>
+        <v>-0.233834601405758</v>
       </c>
       <c r="I22" s="26" t="n">
-        <v>-0.004698634268006097</v>
+        <v>-0.006856385410228039</v>
       </c>
       <c r="J22" s="26" t="n">
-        <v>0.03212220982578229</v>
+        <v>0.03825819030297883</v>
       </c>
     </row>
     <row r="23">
@@ -1811,969 +1811,1002 @@
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
+          <t>XLV</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>State Street Health Care Select Sector SPDR ETF</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>-0.01129417731304438</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>58.26336947672519</v>
+      </c>
+      <c r="H23" s="36" t="n">
+        <v>5.048552178820076</v>
+      </c>
+      <c r="I23" s="33" t="n">
+        <v>-0.004698634268006097</v>
+      </c>
+      <c r="J23" s="33" t="n">
+        <v>0.03212220982578229</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
           <t>XLP</t>
         </is>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>State Street Consumer Staples Select Sector SPDR ETF</t>
         </is>
       </c>
-      <c r="E23" s="33" t="n">
+      <c r="E24" s="26" t="n">
         <v>-0.01379384326320543</v>
       </c>
-      <c r="F23" s="34" t="n">
+      <c r="F24" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="35" t="n">
+      <c r="G24" s="28" t="n">
         <v>47.94394812605086</v>
       </c>
-      <c r="H23" s="36" t="n">
+      <c r="H24" s="29" t="n">
         <v>0.287143062619033</v>
       </c>
-      <c r="I23" s="33" t="n">
+      <c r="I24" s="26" t="n">
         <v>-0.002812914493998675</v>
       </c>
-      <c r="J23" s="33" t="n">
+      <c r="J24" s="26" t="n">
         <v>-0.02609888694330786</v>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="21" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>STRONGEST TODAY</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>WEAKEST TODAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>% Change</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>RSI</t>
-        </is>
-      </c>
-      <c r="H27" s="22" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="I27" s="22" t="inlineStr">
-        <is>
-          <t>% Change</t>
-        </is>
-      </c>
-      <c r="J27" s="22" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="K27" s="22" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="L27" s="22" t="inlineStr">
-        <is>
-          <t>RSI</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="n">
-        <v>0.04749291648327469</v>
-      </c>
-      <c r="D28" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>Very Strong</t>
-        </is>
-      </c>
-      <c r="F28" s="28" t="n">
-        <v>69.09787260511135</v>
-      </c>
-      <c r="H28" s="24" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
-      </c>
-      <c r="I28" s="26" t="n">
-        <v>-0.01374842694128908</v>
-      </c>
-      <c r="J28" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-      <c r="L28" s="28" t="n">
-        <v>47.26430761025513</v>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="31" t="inlineStr">
-        <is>
-          <t>MSTR</t>
-        </is>
-      </c>
-      <c r="C29" s="33" t="n">
-        <v>0.1153502002878597</v>
-      </c>
-      <c r="D29" s="34" t="n">
-        <v>8</v>
-      </c>
-      <c r="E29" s="30" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="n">
+        <v>0.04749291648327469</v>
+      </c>
+      <c r="D29" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>Very Strong</t>
         </is>
       </c>
-      <c r="F29" s="35" t="n">
-        <v>72.85353721955366</v>
-      </c>
-      <c r="H29" s="31" t="inlineStr">
-        <is>
-          <t>XLY</t>
-        </is>
-      </c>
-      <c r="I29" s="33" t="n">
-        <v>-0.01092528481292099</v>
-      </c>
-      <c r="J29" s="34" t="n">
+      <c r="F29" s="28" t="n">
+        <v>69.09787260511135</v>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="I29" s="26" t="n">
+        <v>-0.01374842694128908</v>
+      </c>
+      <c r="J29" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="K29" s="30" t="inlineStr">
+      <c r="K29" s="23" t="inlineStr">
         <is>
           <t>Very Weak</t>
         </is>
       </c>
-      <c r="L29" s="35" t="n">
-        <v>46.11854978280344</v>
+      <c r="L29" s="28" t="n">
+        <v>47.26430761025513</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="n">
-        <v>0.0873795275466771</v>
-      </c>
-      <c r="D30" s="27" t="n">
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>0.1153502002878597</v>
+      </c>
+      <c r="D30" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>Very Strong</t>
         </is>
       </c>
-      <c r="F30" s="28" t="n">
-        <v>61.31941960626309</v>
-      </c>
-      <c r="H30" s="24" t="inlineStr">
-        <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="I30" s="26" t="n">
-        <v>-0.008539388474021248</v>
-      </c>
-      <c r="J30" s="27" t="n">
+      <c r="F30" s="35" t="n">
+        <v>72.85353721955366</v>
+      </c>
+      <c r="H30" s="31" t="inlineStr">
+        <is>
+          <t>XLY</t>
+        </is>
+      </c>
+      <c r="I30" s="33" t="n">
+        <v>-0.01092528481292099</v>
+      </c>
+      <c r="J30" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="23" t="inlineStr">
+      <c r="K30" s="30" t="inlineStr">
         <is>
           <t>Very Weak</t>
         </is>
       </c>
-      <c r="L30" s="28" t="n">
-        <v>41.45211287326175</v>
+      <c r="L30" s="35" t="n">
+        <v>46.11854978280344</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="31" t="inlineStr">
-        <is>
-          <t>XLK</t>
-        </is>
-      </c>
-      <c r="C31" s="33" t="n">
-        <v>0.03155767002859644</v>
-      </c>
-      <c r="D31" s="34" t="n">
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="n">
+        <v>0.0873795275466771</v>
+      </c>
+      <c r="D31" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="E31" s="30" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>Very Strong</t>
         </is>
       </c>
-      <c r="F31" s="35" t="n">
-        <v>57.83612648825964</v>
-      </c>
-      <c r="H31" s="31" t="inlineStr">
-        <is>
-          <t>XLU</t>
-        </is>
-      </c>
-      <c r="I31" s="33" t="n">
-        <v>-0.007584418043843133</v>
-      </c>
-      <c r="J31" s="34" t="n">
+      <c r="F31" s="28" t="n">
+        <v>61.31941960626309</v>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="I31" s="26" t="n">
+        <v>-0.008539388474021248</v>
+      </c>
+      <c r="J31" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="K31" s="30" t="inlineStr">
+      <c r="K31" s="23" t="inlineStr">
         <is>
           <t>Very Weak</t>
         </is>
       </c>
-      <c r="L31" s="35" t="n">
-        <v>39.75511151129263</v>
+      <c r="L31" s="28" t="n">
+        <v>41.45211287326175</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>ARKK</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="n">
-        <v>0.01865234899615387</v>
-      </c>
-      <c r="D32" s="27" t="n">
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>XLK</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="n">
+        <v>0.03155767002859644</v>
+      </c>
+      <c r="D32" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="30" t="inlineStr">
         <is>
           <t>Very Strong</t>
         </is>
       </c>
-      <c r="F32" s="28" t="n">
-        <v>64.75266026536364</v>
-      </c>
-      <c r="H32" s="24" t="inlineStr">
-        <is>
-          <t>ASTS</t>
-        </is>
-      </c>
-      <c r="I32" s="26" t="n">
-        <v>0.02605206297206331</v>
-      </c>
-      <c r="J32" s="27" t="n">
+      <c r="F32" s="35" t="n">
+        <v>57.83612648825964</v>
+      </c>
+      <c r="H32" s="31" t="inlineStr">
+        <is>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="I32" s="33" t="n">
+        <v>-0.007584418043843133</v>
+      </c>
+      <c r="J32" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="K32" s="23" t="inlineStr">
+      <c r="K32" s="30" t="inlineStr">
         <is>
           <t>Very Weak</t>
         </is>
       </c>
-      <c r="L32" s="28" t="n">
-        <v>42.94026409835578</v>
+      <c r="L32" s="35" t="n">
+        <v>39.75511151129263</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="31" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-      <c r="C33" s="33" t="n">
-        <v>0.01819671921894161</v>
-      </c>
-      <c r="D33" s="34" t="n">
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>ARKK</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>0.01865234899615387</v>
+      </c>
+      <c r="D33" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="E33" s="30" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>Very Strong</t>
         </is>
       </c>
-      <c r="F33" s="35" t="n">
-        <v>56.91722587993239</v>
-      </c>
-      <c r="H33" s="31" t="inlineStr">
-        <is>
-          <t>XLRE</t>
-        </is>
-      </c>
-      <c r="I33" s="33" t="n">
-        <v>-0.009536489326250397</v>
-      </c>
-      <c r="J33" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" s="30" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="L33" s="35" t="n">
-        <v>45.5010127355274</v>
+      <c r="F33" s="28" t="n">
+        <v>64.75266026536364</v>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="I33" s="26" t="n">
+        <v>0.02605206297206331</v>
+      </c>
+      <c r="J33" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+      <c r="L33" s="28" t="n">
+        <v>42.94026409835578</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="n">
-        <v>0.01750710664804522</v>
-      </c>
-      <c r="D34" s="27" t="n">
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="n">
+        <v>0.01819671921894161</v>
+      </c>
+      <c r="D34" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>Very Strong</t>
         </is>
       </c>
-      <c r="F34" s="28" t="n">
-        <v>70.45128335913824</v>
-      </c>
-      <c r="H34" s="24" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="I34" s="26" t="n">
-        <v>-0.004099128939600072</v>
-      </c>
-      <c r="J34" s="27" t="n">
+      <c r="F34" s="35" t="n">
+        <v>56.91722587993239</v>
+      </c>
+      <c r="H34" s="31" t="inlineStr">
+        <is>
+          <t>XLRE</t>
+        </is>
+      </c>
+      <c r="I34" s="33" t="n">
+        <v>-0.009536489326250397</v>
+      </c>
+      <c r="J34" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="K34" s="23" t="inlineStr">
+      <c r="K34" s="30" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="L34" s="28" t="n">
-        <v>43.15833149859111</v>
+      <c r="L34" s="35" t="n">
+        <v>45.5010127355274</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="31" t="inlineStr">
-        <is>
-          <t>NOK</t>
-        </is>
-      </c>
-      <c r="C35" s="33" t="n">
-        <v>0.01729109585150757</v>
-      </c>
-      <c r="D35" s="34" t="n">
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>0.01750710664804522</v>
+      </c>
+      <c r="D35" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="E35" s="30" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>Very Strong</t>
         </is>
       </c>
-      <c r="F35" s="35" t="n">
-        <v>53.35085497285271</v>
-      </c>
-      <c r="H35" s="31" t="inlineStr">
-        <is>
-          <t>RKLB</t>
-        </is>
-      </c>
-      <c r="I35" s="33" t="n">
-        <v>0.02039888890746222</v>
-      </c>
-      <c r="J35" s="34" t="n">
+      <c r="F35" s="28" t="n">
+        <v>70.45128335913824</v>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="I35" s="26" t="n">
+        <v>-0.004099128939600072</v>
+      </c>
+      <c r="J35" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="K35" s="30" t="inlineStr">
+      <c r="K35" s="23" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="L35" s="35" t="n">
-        <v>38.76198658715374</v>
+      <c r="L35" s="28" t="n">
+        <v>43.15833149859111</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C36" s="26" t="n">
-        <v>0.01369187666225713</v>
-      </c>
-      <c r="D36" s="27" t="n">
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="n">
+        <v>0.01729109585150757</v>
+      </c>
+      <c r="D36" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>Very Strong</t>
         </is>
       </c>
-      <c r="F36" s="28" t="n">
-        <v>54.76175538399814</v>
-      </c>
-      <c r="H36" s="24" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="I36" s="26" t="n">
-        <v>-0.01544486334918349</v>
-      </c>
-      <c r="J36" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="K36" s="23" t="inlineStr">
+      <c r="F36" s="35" t="n">
+        <v>53.35085497285271</v>
+      </c>
+      <c r="H36" s="31" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="I36" s="33" t="n">
+        <v>0.02039888890746222</v>
+      </c>
+      <c r="J36" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="30" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="L36" s="28" t="n">
-        <v>47.22910999363603</v>
+      <c r="L36" s="35" t="n">
+        <v>38.76198658715374</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="31" t="inlineStr">
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="n">
+        <v>0.01369187666225713</v>
+      </c>
+      <c r="D37" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>Very Strong</t>
+        </is>
+      </c>
+      <c r="F37" s="28" t="n">
+        <v>54.76175538399814</v>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="I37" s="26" t="n">
+        <v>-0.01544486334918349</v>
+      </c>
+      <c r="J37" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="L37" s="28" t="n">
+        <v>47.22910999363603</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="C37" s="33" t="n">
+      <c r="C38" s="33" t="n">
         <v>0.006552786111251541</v>
       </c>
-      <c r="D37" s="34" t="n">
+      <c r="D38" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="E37" s="30" t="inlineStr">
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>Very Strong</t>
         </is>
       </c>
-      <c r="F37" s="35" t="n">
+      <c r="F38" s="35" t="n">
         <v>58.58959203233157</v>
       </c>
-      <c r="H37" s="31" t="inlineStr">
+      <c r="H38" s="31" t="inlineStr">
         <is>
           <t>XLP</t>
         </is>
       </c>
-      <c r="I37" s="33" t="n">
+      <c r="I38" s="33" t="n">
         <v>-0.01379384326320543</v>
       </c>
-      <c r="J37" s="34" t="n">
+      <c r="J38" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="30" t="inlineStr">
+      <c r="K38" s="30" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="L37" s="35" t="n">
+      <c r="L38" s="35" t="n">
         <v>47.94394812605086</v>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="21" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>BIGGEST GAINERS</t>
         </is>
       </c>
-      <c r="H40" s="21" t="inlineStr">
+      <c r="H41" s="21" t="inlineStr">
         <is>
           <t>BIGGEST LOSERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C41" s="22" t="inlineStr">
-        <is>
-          <t>% Change</t>
-        </is>
-      </c>
-      <c r="D41" s="22" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="E41" s="22" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="F41" s="22" t="inlineStr">
-        <is>
-          <t>RSI</t>
-        </is>
-      </c>
-      <c r="H41" s="22" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="I41" s="22" t="inlineStr">
-        <is>
-          <t>% Change</t>
-        </is>
-      </c>
-      <c r="J41" s="22" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="K41" s="22" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="L41" s="22" t="inlineStr">
-        <is>
-          <t>RSI</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>MSTR</t>
-        </is>
-      </c>
-      <c r="C42" s="26" t="n">
-        <v>0.1153502002878597</v>
-      </c>
-      <c r="D42" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>Very Strong</t>
-        </is>
-      </c>
-      <c r="F42" s="28" t="n">
-        <v>72.85353721955366</v>
-      </c>
-      <c r="H42" s="24" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="I42" s="26" t="n">
-        <v>-0.01988709507475095</v>
-      </c>
-      <c r="J42" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="K42" s="23" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="L42" s="28" t="n">
-        <v>58.35199284044167</v>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="I42" s="22" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="K42" s="22" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="L42" s="22" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="31" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="C43" s="33" t="n">
-        <v>0.0873795275466771</v>
-      </c>
-      <c r="D43" s="34" t="n">
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="n">
+        <v>0.1153502002878597</v>
+      </c>
+      <c r="D43" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="E43" s="30" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>Very Strong</t>
         </is>
       </c>
-      <c r="F43" s="35" t="n">
-        <v>61.31941960626309</v>
-      </c>
-      <c r="H43" s="31" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="I43" s="33" t="n">
-        <v>-0.01544486334918349</v>
-      </c>
-      <c r="J43" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" s="30" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="L43" s="35" t="n">
-        <v>47.22910999363603</v>
+      <c r="F43" s="28" t="n">
+        <v>72.85353721955366</v>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="I43" s="26" t="n">
+        <v>-0.01988709507475095</v>
+      </c>
+      <c r="J43" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="L43" s="28" t="n">
+        <v>58.35199284044167</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>SOXL</t>
-        </is>
-      </c>
-      <c r="C44" s="26" t="n">
-        <v>0.0553173641684761</v>
-      </c>
-      <c r="D44" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E44" s="23" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F44" s="28" t="n">
-        <v>44.72343474073616</v>
-      </c>
-      <c r="H44" s="24" t="inlineStr">
-        <is>
-          <t>XLP</t>
-        </is>
-      </c>
-      <c r="I44" s="26" t="n">
-        <v>-0.01379384326320543</v>
-      </c>
-      <c r="J44" s="27" t="n">
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C44" s="33" t="n">
+        <v>0.0873795275466771</v>
+      </c>
+      <c r="D44" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" s="30" t="inlineStr">
+        <is>
+          <t>Very Strong</t>
+        </is>
+      </c>
+      <c r="F44" s="35" t="n">
+        <v>61.31941960626309</v>
+      </c>
+      <c r="H44" s="31" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="I44" s="33" t="n">
+        <v>-0.01544486334918349</v>
+      </c>
+      <c r="J44" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="K44" s="23" t="inlineStr">
+      <c r="K44" s="30" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="L44" s="28" t="n">
-        <v>47.94394812605086</v>
+      <c r="L44" s="35" t="n">
+        <v>47.22910999363603</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="31" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="C45" s="33" t="n">
-        <v>0.04749291648327469</v>
-      </c>
-      <c r="D45" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="E45" s="30" t="inlineStr">
-        <is>
-          <t>Very Strong</t>
-        </is>
-      </c>
-      <c r="F45" s="35" t="n">
-        <v>69.09787260511135</v>
-      </c>
-      <c r="H45" s="31" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
-      </c>
-      <c r="I45" s="33" t="n">
-        <v>-0.01374842694128908</v>
-      </c>
-      <c r="J45" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="30" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-      <c r="L45" s="35" t="n">
-        <v>47.26430761025513</v>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="n">
+        <v>0.0553173641684761</v>
+      </c>
+      <c r="D45" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F45" s="28" t="n">
+        <v>44.72343474073616</v>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>XLP</t>
+        </is>
+      </c>
+      <c r="I45" s="26" t="n">
+        <v>-0.01379384326320543</v>
+      </c>
+      <c r="J45" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="L45" s="28" t="n">
+        <v>47.94394812605086</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="C46" s="26" t="n">
-        <v>0.04485506445989884</v>
-      </c>
-      <c r="D46" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="23" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F46" s="28" t="n">
-        <v>43.89340665362339</v>
-      </c>
-      <c r="H46" s="24" t="inlineStr">
-        <is>
-          <t>XLV</t>
-        </is>
-      </c>
-      <c r="I46" s="26" t="n">
-        <v>-0.01129417731304438</v>
-      </c>
-      <c r="J46" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K46" s="23" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="L46" s="28" t="n">
-        <v>58.26336947672519</v>
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="n">
+        <v>0.04749291648327469</v>
+      </c>
+      <c r="D46" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>Very Strong</t>
+        </is>
+      </c>
+      <c r="F46" s="35" t="n">
+        <v>69.09787260511135</v>
+      </c>
+      <c r="H46" s="31" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="I46" s="33" t="n">
+        <v>-0.01374842694128908</v>
+      </c>
+      <c r="J46" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="30" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+      <c r="L46" s="35" t="n">
+        <v>47.26430761025513</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="31" t="inlineStr">
-        <is>
-          <t>INTC</t>
-        </is>
-      </c>
-      <c r="C47" s="33" t="n">
-        <v>0.04363099011023275</v>
-      </c>
-      <c r="D47" s="34" t="n">
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>0.04485506445989884</v>
+      </c>
+      <c r="D47" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E47" s="30" t="inlineStr">
+      <c r="E47" s="23" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="F47" s="35" t="n">
-        <v>44.27592621645633</v>
-      </c>
-      <c r="H47" s="31" t="inlineStr">
-        <is>
-          <t>XLY</t>
-        </is>
-      </c>
-      <c r="I47" s="33" t="n">
-        <v>-0.01092528481292099</v>
-      </c>
-      <c r="J47" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="30" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-      <c r="L47" s="35" t="n">
-        <v>46.11854978280344</v>
+      <c r="F47" s="28" t="n">
+        <v>43.89340665362339</v>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>XLV</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="n">
+        <v>-0.01129417731304438</v>
+      </c>
+      <c r="J47" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K47" s="23" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="L47" s="28" t="n">
+        <v>58.26336947672519</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>XLK</t>
-        </is>
-      </c>
-      <c r="C48" s="26" t="n">
-        <v>0.03155767002859644</v>
-      </c>
-      <c r="D48" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="E48" s="23" t="inlineStr">
-        <is>
-          <t>Very Strong</t>
-        </is>
-      </c>
-      <c r="F48" s="28" t="n">
-        <v>57.83612648825964</v>
-      </c>
-      <c r="H48" s="24" t="inlineStr">
-        <is>
-          <t>XLC</t>
-        </is>
-      </c>
-      <c r="I48" s="26" t="n">
-        <v>-0.01065622006694034</v>
-      </c>
-      <c r="J48" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="K48" s="23" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="L48" s="28" t="n">
-        <v>51.01216980941457</v>
+      <c r="B48" s="31" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="C48" s="33" t="n">
+        <v>0.04363099011023275</v>
+      </c>
+      <c r="D48" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="30" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="F48" s="35" t="n">
+        <v>44.27592621645633</v>
+      </c>
+      <c r="H48" s="31" t="inlineStr">
+        <is>
+          <t>XLY</t>
+        </is>
+      </c>
+      <c r="I48" s="33" t="n">
+        <v>-0.01092528481292099</v>
+      </c>
+      <c r="J48" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="30" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+      <c r="L48" s="35" t="n">
+        <v>46.11854978280344</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="31" t="inlineStr">
-        <is>
-          <t>ASTS</t>
-        </is>
-      </c>
-      <c r="C49" s="33" t="n">
-        <v>0.02605206297206331</v>
-      </c>
-      <c r="D49" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="30" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-      <c r="F49" s="35" t="n">
-        <v>42.94026409835578</v>
-      </c>
-      <c r="H49" s="31" t="inlineStr">
-        <is>
-          <t>SNDK</t>
-        </is>
-      </c>
-      <c r="I49" s="33" t="n">
-        <v>-0.009617401970342554</v>
-      </c>
-      <c r="J49" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="K49" s="30" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="L49" s="35" t="n">
-        <v>49.32206344808555</v>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>XLK</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="n">
+        <v>0.03155767002859644</v>
+      </c>
+      <c r="D49" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>Very Strong</t>
+        </is>
+      </c>
+      <c r="F49" s="28" t="n">
+        <v>57.83612648825964</v>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>XLC</t>
+        </is>
+      </c>
+      <c r="I49" s="26" t="n">
+        <v>-0.01065622006694034</v>
+      </c>
+      <c r="J49" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="23" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="L49" s="28" t="n">
+        <v>51.01216980941457</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="C50" s="26" t="n">
-        <v>0.02599615419574763</v>
-      </c>
-      <c r="D50" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="E50" s="23" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="F50" s="28" t="n">
-        <v>53.87218957306972</v>
-      </c>
-      <c r="H50" s="24" t="inlineStr">
-        <is>
-          <t>CCJ</t>
-        </is>
-      </c>
-      <c r="I50" s="26" t="n">
-        <v>-0.00959387829211289</v>
-      </c>
-      <c r="J50" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K50" s="23" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="L50" s="28" t="n">
-        <v>65.28503598146888</v>
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="C50" s="33" t="n">
+        <v>0.02605206297206331</v>
+      </c>
+      <c r="D50" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="30" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+      <c r="F50" s="35" t="n">
+        <v>42.94026409835578</v>
+      </c>
+      <c r="H50" s="31" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="I50" s="33" t="n">
+        <v>-0.009617401970342554</v>
+      </c>
+      <c r="J50" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" s="30" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="L50" s="35" t="n">
+        <v>49.32206344808555</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="31" t="inlineStr">
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="n">
+        <v>0.02599615419574763</v>
+      </c>
+      <c r="D51" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="F51" s="28" t="n">
+        <v>53.87218957306972</v>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>CCJ</t>
+        </is>
+      </c>
+      <c r="I51" s="26" t="n">
+        <v>-0.00959387829211289</v>
+      </c>
+      <c r="J51" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K51" s="23" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="L51" s="28" t="n">
+        <v>65.28503598146888</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>IREN</t>
         </is>
       </c>
-      <c r="C51" s="33" t="n">
+      <c r="C52" s="33" t="n">
         <v>0.02400194300892666</v>
       </c>
-      <c r="D51" s="34" t="n">
+      <c r="D52" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="E51" s="30" t="inlineStr">
+      <c r="E52" s="30" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="F51" s="35" t="n">
+      <c r="F52" s="35" t="n">
         <v>48.35559646321695</v>
       </c>
-      <c r="H51" s="31" t="inlineStr">
+      <c r="H52" s="31" t="inlineStr">
         <is>
           <t>XLRE</t>
         </is>
       </c>
-      <c r="I51" s="33" t="n">
+      <c r="I52" s="33" t="n">
         <v>-0.009536489326250397</v>
       </c>
-      <c r="J51" s="34" t="n">
+      <c r="J52" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="K51" s="30" t="inlineStr">
+      <c r="K52" s="30" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="L51" s="35" t="n">
+      <c r="L52" s="35" t="n">
         <v>45.5010127355274</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H26:L26"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="N8:P8"/>
+    <mergeCell ref="H41:L41"/>
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="H7:J7"/>
-    <mergeCell ref="H40:L40"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="Q9:S9"/>
     <mergeCell ref="B9:D9"/>
@@ -2784,7 +2817,7 @@
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="H27:L27"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="K9:M9"/>
     <mergeCell ref="E8:G8"/>
@@ -2792,9 +2825,9 @@
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="B5:R5"/>
     <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
-  <conditionalFormatting sqref="E14:E23">
+  <conditionalFormatting sqref="E14:E24">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.02"/>
@@ -2806,7 +2839,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F23">
+  <conditionalFormatting sqref="F14:F24">
     <cfRule type="dataBar" priority="2">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -2815,7 +2848,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:I23">
+  <conditionalFormatting sqref="I14:I24">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="percentile" val="10"/>
@@ -2827,7 +2860,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J14:J23">
+  <conditionalFormatting sqref="J14:J24">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="percentile" val="10"/>
@@ -2839,7 +2872,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28:C37">
+  <conditionalFormatting sqref="C29:C38">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-0.03"/>
@@ -2851,7 +2884,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D28:D37">
+  <conditionalFormatting sqref="D29:D38">
     <cfRule type="dataBar" priority="6">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -2860,7 +2893,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I28:I37">
+  <conditionalFormatting sqref="I29:I38">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-0.03"/>
@@ -2872,7 +2905,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J28:J37">
+  <conditionalFormatting sqref="J29:J38">
     <cfRule type="dataBar" priority="8">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -2881,7 +2914,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C42:C51">
+  <conditionalFormatting sqref="C43:C52">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-0.03"/>
@@ -2893,7 +2926,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D42:D51">
+  <conditionalFormatting sqref="D43:D52">
     <cfRule type="dataBar" priority="10">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -2902,7 +2935,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I42:I51">
+  <conditionalFormatting sqref="I43:I52">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-0.03"/>
@@ -2914,7 +2947,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J42:J51">
+  <conditionalFormatting sqref="J43:J52">
     <cfRule type="dataBar" priority="12">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -3074,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 28 Aug 2026, 01:35 AM · Yahoo Finance data</t>
+          <t>Built 28 Aug 2026, 04:22 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -3099,12 +3132,12 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>22 of 39</t>
+          <t>22 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>17 of 39</t>
+          <t>18 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
@@ -3114,7 +3147,7 @@
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>21 of 39</t>
+          <t>22 of 40</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3539,7 @@
         <v>-0.008539388474021248</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
@@ -3587,10 +3620,10 @@
         <v>178.1799926757812</v>
       </c>
       <c r="W7" s="73" t="n">
-        <v>5462671</v>
+        <v>5464700</v>
       </c>
       <c r="X7" s="74" t="n">
-        <v>0.9069031731909785</v>
+        <v>0.9072247442739189</v>
       </c>
       <c r="Y7" s="28" t="n">
         <v>41.45211287326175</v>
@@ -3696,7 +3729,7 @@
         <v>-0.01129417731304438</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
@@ -3777,10 +3810,10 @@
         <v>171.4299926757812</v>
       </c>
       <c r="W8" s="84" t="n">
-        <v>7087785</v>
+        <v>7091200</v>
       </c>
       <c r="X8" s="85" t="n">
-        <v>0.8048951099179901</v>
+        <v>0.8052673057749131</v>
       </c>
       <c r="Y8" s="35" t="n">
         <v>58.26336947672519</v>
@@ -3886,7 +3919,7 @@
         <v>-0.006522438454611534</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
@@ -3967,10 +4000,10 @@
         <v>57.72999954223633</v>
       </c>
       <c r="W9" s="73" t="n">
-        <v>26065932</v>
+        <v>26082100</v>
       </c>
       <c r="X9" s="74" t="n">
-        <v>0.9318109772495536</v>
+        <v>0.932362010451051</v>
       </c>
       <c r="Y9" s="28" t="n">
         <v>56.3701733921237</v>
@@ -4072,57 +4105,171 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
-      <c r="I10" s="30" t="n"/>
-      <c r="J10" s="30" t="n"/>
-      <c r="K10" s="30" t="n"/>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="30" t="n"/>
-      <c r="N10" s="80" t="n"/>
-      <c r="O10" s="30" t="n"/>
-      <c r="P10" s="32" t="n"/>
+      <c r="C10" s="33" t="n">
+        <v>-0.002242501825469811</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" s="80" t="n">
+        <v>6</v>
+      </c>
+      <c r="O10" s="30" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="P10" s="32" t="inlineStr">
+        <is>
+          <t>Long-term up, short-term mixed</t>
+        </is>
+      </c>
       <c r="Q10" s="32" t="inlineStr">
         <is>
           <t>State Street Energy Select Sector SPDR ETF</t>
         </is>
       </c>
-      <c r="R10" s="81" t="n"/>
-      <c r="S10" s="82" t="n"/>
-      <c r="T10" s="83" t="n"/>
-      <c r="U10" s="83" t="n"/>
-      <c r="V10" s="83" t="n"/>
-      <c r="W10" s="84" t="n"/>
-      <c r="X10" s="85" t="n"/>
-      <c r="Y10" s="35" t="n"/>
-      <c r="Z10" s="35" t="n"/>
-      <c r="AA10" s="35" t="n"/>
-      <c r="AB10" s="86" t="n"/>
-      <c r="AC10" s="86" t="n"/>
-      <c r="AD10" s="86" t="n"/>
-      <c r="AE10" s="83" t="n"/>
-      <c r="AF10" s="83" t="n"/>
-      <c r="AG10" s="83" t="n"/>
-      <c r="AH10" s="83" t="n"/>
-      <c r="AI10" s="83" t="n"/>
-      <c r="AJ10" s="83" t="n"/>
-      <c r="AK10" s="83" t="n"/>
-      <c r="AL10" s="83" t="n"/>
-      <c r="AM10" s="87" t="n"/>
-      <c r="AN10" s="36" t="n"/>
-      <c r="AO10" s="88" t="n"/>
-      <c r="AP10" s="83" t="n"/>
-      <c r="AQ10" s="83" t="n"/>
-      <c r="AR10" s="36" t="n"/>
-      <c r="AS10" s="89" t="n"/>
-      <c r="AT10" s="33" t="n"/>
-      <c r="AU10" s="33" t="n"/>
-      <c r="AV10" s="33" t="n"/>
-      <c r="AW10" s="33" t="n"/>
+      <c r="R10" s="81" t="n">
+        <v>62.29000091552734</v>
+      </c>
+      <c r="S10" s="82" t="n">
+        <v>-0.1399993896484375</v>
+      </c>
+      <c r="T10" s="83" t="n">
+        <v>62.22999954223633</v>
+      </c>
+      <c r="U10" s="83" t="n">
+        <v>62.72000122070312</v>
+      </c>
+      <c r="V10" s="83" t="n">
+        <v>61.54999923706055</v>
+      </c>
+      <c r="W10" s="84" t="n">
+        <v>29599300</v>
+      </c>
+      <c r="X10" s="85" t="n">
+        <v>1.134761262244737</v>
+      </c>
+      <c r="Y10" s="35" t="n">
+        <v>60.14216437335956</v>
+      </c>
+      <c r="Z10" s="35" t="n">
+        <v>63.48490015316591</v>
+      </c>
+      <c r="AA10" s="35" t="n">
+        <v>26.4101387878838</v>
+      </c>
+      <c r="AB10" s="86" t="n">
+        <v>1.35018323806527</v>
+      </c>
+      <c r="AC10" s="86" t="n">
+        <v>1.413752072296182</v>
+      </c>
+      <c r="AD10" s="86" t="n">
+        <v>-0.06356883423091242</v>
+      </c>
+      <c r="AE10" s="83" t="n">
+        <v>62.49198561498208</v>
+      </c>
+      <c r="AF10" s="83" t="n">
+        <v>61.26351107056134</v>
+      </c>
+      <c r="AG10" s="83" t="n">
+        <v>57.99160034179688</v>
+      </c>
+      <c r="AH10" s="83" t="n">
+        <v>57.81500015258789</v>
+      </c>
+      <c r="AI10" s="83" t="n">
+        <v>54.26732492446899</v>
+      </c>
+      <c r="AJ10" s="83" t="n">
+        <v>65.31057520080981</v>
+      </c>
+      <c r="AK10" s="83" t="n">
+        <v>61.10300045013427</v>
+      </c>
+      <c r="AL10" s="83" t="n">
+        <v>56.89542569945874</v>
+      </c>
+      <c r="AM10" s="87" t="n">
+        <v>0.6410551844863237</v>
+      </c>
+      <c r="AN10" s="36" t="n">
+        <v>13.77207246674999</v>
+      </c>
+      <c r="AO10" s="88" t="n">
+        <v>1.936060513686391</v>
+      </c>
+      <c r="AP10" s="83" t="n">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="AQ10" s="83" t="n">
+        <v>42.34999847412109</v>
+      </c>
+      <c r="AR10" s="36" t="n">
+        <v>-3.724878124248998</v>
+      </c>
+      <c r="AS10" s="89" t="n">
+        <v>89.21701925167753</v>
+      </c>
+      <c r="AT10" s="33" t="n">
+        <v>-0.02290194642310051</v>
+      </c>
+      <c r="AU10" s="33" t="n">
+        <v>0.06206307408265466</v>
+      </c>
+      <c r="AV10" s="33" t="n">
+        <v>0.09376646323177806</v>
+      </c>
+      <c r="AW10" s="33" t="n">
+        <v>0.3932006752637141</v>
+      </c>
       <c r="AX10" s="90" t="inlineStr">
         <is>
           <t>Sector Update: Energy Stocks Mixed Late Afternoon</t>
@@ -4152,7 +4299,7 @@
         <v>-0.01379384326320543</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
@@ -4227,16 +4374,16 @@
         <v>85.30999755859375</v>
       </c>
       <c r="U11" s="72" t="n">
-        <v>85.85500335693359</v>
+        <v>85.86000061035156</v>
       </c>
       <c r="V11" s="72" t="n">
         <v>85.06999969482422</v>
       </c>
       <c r="W11" s="73" t="n">
-        <v>8487958</v>
+        <v>8492100</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>0.9224479259104591</v>
+        <v>0.9228772958231383</v>
       </c>
       <c r="Y11" s="28" t="n">
         <v>47.94394812605086</v>
@@ -4342,7 +4489,7 @@
         <v>-0.01092528481292099</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
@@ -4423,10 +4570,10 @@
         <v>115.8099975585938</v>
       </c>
       <c r="W12" s="84" t="n">
-        <v>5220236</v>
+        <v>5231500</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>0.8733110768412422</v>
+        <v>0.8751130169611171</v>
       </c>
       <c r="Y12" s="35" t="n">
         <v>46.11854978280344</v>
@@ -4532,7 +4679,7 @@
         <v>-0.01065622006694034</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
@@ -4607,16 +4754,16 @@
         <v>112.0299987792969</v>
       </c>
       <c r="U13" s="72" t="n">
-        <v>112.3600006103516</v>
+        <v>112.370002746582</v>
       </c>
       <c r="V13" s="72" t="n">
         <v>111.370002746582</v>
       </c>
       <c r="W13" s="73" t="n">
-        <v>4419088</v>
+        <v>4425600</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>1.010448085816363</v>
+        <v>1.011861756125221</v>
       </c>
       <c r="Y13" s="28" t="n">
         <v>51.01216980941457</v>
@@ -4722,7 +4869,7 @@
         <v>-0.008198223248004122</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
@@ -4797,16 +4944,16 @@
         <v>53.22000122070312</v>
       </c>
       <c r="U14" s="83" t="n">
-        <v>53.48500061035156</v>
+        <v>53.4900016784668</v>
       </c>
       <c r="V14" s="83" t="n">
         <v>53.09999847412109</v>
       </c>
       <c r="W14" s="84" t="n">
-        <v>7591921</v>
+        <v>7784600</v>
       </c>
       <c r="X14" s="85" t="n">
-        <v>0.6956996904062925</v>
+        <v>0.7127269730893976</v>
       </c>
       <c r="Y14" s="35" t="n">
         <v>57.40881785747306</v>
@@ -4987,16 +5134,16 @@
         <v>186.4700012207031</v>
       </c>
       <c r="U15" s="72" t="n">
-        <v>188.7299957275391</v>
+        <v>188.7400054931641</v>
       </c>
       <c r="V15" s="72" t="n">
         <v>185.6699981689453</v>
       </c>
       <c r="W15" s="73" t="n">
-        <v>8125501</v>
+        <v>8136000</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>1.189706770443892</v>
+        <v>1.191152442916625</v>
       </c>
       <c r="Y15" s="28" t="n">
         <v>57.83612648825964</v>
@@ -5005,7 +5152,7 @@
         <v>75.71538152894806</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>14.19922552255718</v>
+        <v>14.20148561688027</v>
       </c>
       <c r="AB15" s="75" t="n">
         <v>0.8249471787323728</v>
@@ -5047,7 +5194,7 @@
         <v>8.659718434645153</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.222303017077061</v>
+        <v>2.222682097325518</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -5102,7 +5249,7 @@
         <v>-0.009536489326250397</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
@@ -5183,10 +5330,10 @@
         <v>44.63000106811523</v>
       </c>
       <c r="W16" s="84" t="n">
-        <v>4635340</v>
+        <v>4637800</v>
       </c>
       <c r="X16" s="85" t="n">
-        <v>0.8917353069729933</v>
+        <v>0.8921874443921831</v>
       </c>
       <c r="Y16" s="35" t="n">
         <v>45.5010127355274</v>
@@ -5292,7 +5439,7 @@
         <v>-0.007584418043843133</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
@@ -5367,16 +5514,16 @@
         <v>43.22000122070312</v>
       </c>
       <c r="U17" s="72" t="n">
-        <v>43.31999969482422</v>
+        <v>43.33000183105469</v>
       </c>
       <c r="V17" s="72" t="n">
         <v>42.91999816894531</v>
       </c>
       <c r="W17" s="73" t="n">
-        <v>16005821</v>
+        <v>16033500</v>
       </c>
       <c r="X17" s="74" t="n">
-        <v>0.8127698695212767</v>
+        <v>0.8141181858825758</v>
       </c>
       <c r="Y17" s="28" t="n">
         <v>39.75511151129263</v>
@@ -5576,16 +5723,16 @@
         <v>768.5</v>
       </c>
       <c r="U19" s="72" t="n">
-        <v>772.35498046875</v>
+        <v>772.3599853515625</v>
       </c>
       <c r="V19" s="72" t="n">
         <v>767.1599731445312</v>
       </c>
       <c r="W19" s="73" t="n">
-        <v>34017770</v>
+        <v>34502700</v>
       </c>
       <c r="X19" s="74" t="n">
-        <v>0.8293910194640869</v>
+        <v>0.840717156025259</v>
       </c>
       <c r="Y19" s="28" t="n">
         <v>58.58959203233157</v>
@@ -5594,7 +5741,7 @@
         <v>52.27921883529682</v>
       </c>
       <c r="AA19" s="28" t="n">
-        <v>15.34861286576076</v>
+        <v>15.34931751324575</v>
       </c>
       <c r="AB19" s="75" t="n">
         <v>4.247962904467045</v>
@@ -5636,7 +5783,7 @@
         <v>3.500163842191669</v>
       </c>
       <c r="AO19" s="77" t="n">
-        <v>0.8132032363213794</v>
+        <v>0.8132495975768304</v>
       </c>
       <c r="AP19" s="72" t="n">
         <v>779.3699951171875</v>
@@ -5761,19 +5908,19 @@
         <v>9.739990234375</v>
       </c>
       <c r="T20" s="83" t="n">
-        <v>716.97998046875</v>
+        <v>716.9299926757812</v>
       </c>
       <c r="U20" s="83" t="n">
         <v>721.3499755859375</v>
       </c>
       <c r="V20" s="83" t="n">
-        <v>714.5250244140625</v>
+        <v>714.530029296875</v>
       </c>
       <c r="W20" s="84" t="n">
-        <v>28443051</v>
+        <v>28627600</v>
       </c>
       <c r="X20" s="85" t="n">
-        <v>0.835194840148926</v>
+        <v>0.8403861873314151</v>
       </c>
       <c r="Y20" s="35" t="n">
         <v>54.76175538399814</v>
@@ -5952,16 +6099,16 @@
         <v>298.7699890136719</v>
       </c>
       <c r="U21" s="72" t="n">
-        <v>300.3150024414062</v>
+        <v>300.3200073242188</v>
       </c>
       <c r="V21" s="72" t="n">
         <v>298.1400146484375</v>
       </c>
       <c r="W21" s="73" t="n">
-        <v>13640283</v>
+        <v>13658700</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>0.7944010841392982</v>
+        <v>0.7954310193463625</v>
       </c>
       <c r="Y21" s="28" t="n">
         <v>52.41279782132757</v>
@@ -5970,7 +6117,7 @@
         <v>34.0294154035339</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>14.1636283452161</v>
+        <v>14.16121708747646</v>
       </c>
       <c r="AB21" s="75" t="n">
         <v>1.054301356064684</v>
@@ -6012,7 +6159,7 @@
         <v>3.97162331000525</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.079258834026428</v>
+        <v>1.07937807342217</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -6143,13 +6290,13 @@
         <v>124.879997253418</v>
       </c>
       <c r="V22" s="83" t="n">
-        <v>117.6901016235352</v>
+        <v>117.6900024414062</v>
       </c>
       <c r="W22" s="84" t="n">
-        <v>54871327</v>
+        <v>55366200</v>
       </c>
       <c r="X22" s="85" t="n">
-        <v>0.9074170960061452</v>
+        <v>0.9152263989444337</v>
       </c>
       <c r="Y22" s="35" t="n">
         <v>44.72343474073616</v>
@@ -6346,19 +6493,19 @@
         <v>1.129974365234375</v>
       </c>
       <c r="T24" s="72" t="n">
-        <v>310.5450134277344</v>
+        <v>310.5499877929688</v>
       </c>
       <c r="U24" s="72" t="n">
         <v>315.3999938964844</v>
       </c>
       <c r="V24" s="72" t="n">
-        <v>309.4000854492188</v>
+        <v>309.3999938964844</v>
       </c>
       <c r="W24" s="73" t="n">
-        <v>32248789</v>
+        <v>32364000</v>
       </c>
       <c r="X24" s="74" t="n">
-        <v>0.6754834573968823</v>
+        <v>0.677814882648429</v>
       </c>
       <c r="Y24" s="28" t="n">
         <v>52.5517714023335</v>
@@ -6409,7 +6556,7 @@
         <v>4.862699022324679</v>
       </c>
       <c r="AO24" s="77" t="n">
-        <v>2.258300811281256</v>
+        <v>2.258302890078798</v>
       </c>
       <c r="AP24" s="72" t="n">
         <v>344.5700073242188</v>
@@ -6534,19 +6681,19 @@
         <v>-4.259979248046875</v>
       </c>
       <c r="T25" s="83" t="n">
-        <v>482</v>
+        <v>481.5</v>
       </c>
       <c r="U25" s="83" t="n">
         <v>483</v>
       </c>
       <c r="V25" s="83" t="n">
-        <v>469.697509765625</v>
+        <v>469.6300048828125</v>
       </c>
       <c r="W25" s="84" t="n">
-        <v>16373484</v>
+        <v>16403600</v>
       </c>
       <c r="X25" s="85" t="n">
-        <v>0.712015081314737</v>
+        <v>0.7132779953981925</v>
       </c>
       <c r="Y25" s="35" t="n">
         <v>47.42782678682413</v>
@@ -6555,7 +6702,7 @@
         <v>38.6888061390259</v>
       </c>
       <c r="AA25" s="35" t="n">
-        <v>9.36227543576255</v>
+        <v>9.364686578479947</v>
       </c>
       <c r="AB25" s="86" t="n">
         <v>-7.331334950120549</v>
@@ -6597,7 +6744,7 @@
         <v>12.33059629009582</v>
       </c>
       <c r="AO25" s="88" t="n">
-        <v>5.445770391486151</v>
+        <v>5.446781946064355</v>
       </c>
       <c r="AP25" s="83" t="n">
         <v>584.72998046875</v>
@@ -6731,10 +6878,10 @@
         <v>255.0200042724609</v>
       </c>
       <c r="W26" s="73" t="n">
-        <v>35779842</v>
+        <v>35852900</v>
       </c>
       <c r="X26" s="74" t="n">
-        <v>0.8477289202844398</v>
+        <v>0.8493863650282022</v>
       </c>
       <c r="Y26" s="28" t="n">
         <v>47.22910999363603</v>
@@ -6916,13 +7063,13 @@
         <v>87.83000183105469</v>
       </c>
       <c r="V27" s="83" t="n">
-        <v>86.02749633789062</v>
+        <v>86.02799987792969</v>
       </c>
       <c r="W27" s="84" t="n">
-        <v>2907411</v>
+        <v>2907800</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>0.5831516991680312</v>
+        <v>0.5832274472717499</v>
       </c>
       <c r="Y27" s="35" t="n">
         <v>64.75266026536364</v>
@@ -7098,19 +7245,19 @@
         <v>4.150009155273438</v>
       </c>
       <c r="T28" s="72" t="n">
-        <v>255.1950073242188</v>
+        <v>255.4600067138672</v>
       </c>
       <c r="U28" s="72" t="n">
         <v>267.6900024414062</v>
       </c>
       <c r="V28" s="72" t="n">
-        <v>249.4653930664062</v>
+        <v>249.4649963378906</v>
       </c>
       <c r="W28" s="73" t="n">
-        <v>4862183</v>
+        <v>4869000</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>1.091339292819676</v>
+        <v>1.092785795804591</v>
       </c>
       <c r="Y28" s="28" t="n">
         <v>45.7149076110599</v>
@@ -7161,7 +7308,7 @@
         <v>24.76500843313769</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>7.422114751324922</v>
+        <v>7.422125855023981</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -7286,7 +7433,7 @@
         <v>1.55999755859375</v>
       </c>
       <c r="T29" s="83" t="n">
-        <v>60.52000045776367</v>
+        <v>60.54999923706055</v>
       </c>
       <c r="U29" s="83" t="n">
         <v>61.63000106811523</v>
@@ -7295,10 +7442,10 @@
         <v>59.95000076293945</v>
       </c>
       <c r="W29" s="84" t="n">
-        <v>6551514</v>
+        <v>6578100</v>
       </c>
       <c r="X29" s="85" t="n">
-        <v>0.5944071123582731</v>
+        <v>0.5967472417415538</v>
       </c>
       <c r="Y29" s="35" t="n">
         <v>42.94026409835578</v>
@@ -7377,17 +7524,17 @@
       </c>
       <c r="AX29" s="90" t="inlineStr">
         <is>
+          <t>ASTS Stock Takes Flight After 3-Day Skid As BlueBirds Deploy, New Zealand Gateway Opens</t>
+        </is>
+      </c>
+      <c r="AY29" s="90" t="inlineStr">
+        <is>
           <t>AST SpaceMobile vs. Firefly Aerospace: Which Outer Space Upstart Is a Better Buy in 2026?</t>
         </is>
       </c>
-      <c r="AY29" s="90" t="inlineStr">
+      <c r="AZ29" s="90" t="inlineStr">
         <is>
           <t>1,000 Reasons to Buy AST SpaceMobile Stock Now</t>
-        </is>
-      </c>
-      <c r="AZ29" s="90" t="inlineStr">
-        <is>
-          <t>Why Did Rocket Lab Hike Its Iridium Bid By 30%? Analyst Says ASTS May Have Been Mystery Rival</t>
         </is>
       </c>
     </row>
@@ -7474,19 +7621,19 @@
         <v>15.95001220703125</v>
       </c>
       <c r="T30" s="72" t="n">
-        <v>361.7650146484375</v>
+        <v>361.7900085449219</v>
       </c>
       <c r="U30" s="72" t="n">
         <v>371.7200012207031</v>
       </c>
       <c r="V30" s="72" t="n">
-        <v>360.75</v>
+        <v>360.6099853515625</v>
       </c>
       <c r="W30" s="73" t="n">
-        <v>21123328</v>
+        <v>21271000</v>
       </c>
       <c r="X30" s="74" t="n">
-        <v>1.07805790743324</v>
+        <v>1.085185616941364</v>
       </c>
       <c r="Y30" s="28" t="n">
         <v>43.89340665362339</v>
@@ -7565,17 +7712,17 @@
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
+          <t>Spicy Stocks: Why BNP Thinks Jalapeño Could Benefit Broadcom Stock</t>
+        </is>
+      </c>
+      <c r="AY30" s="79" t="inlineStr">
+        <is>
           <t>Cathie Wood Sends a $20 Million Signal on Broadcom Stock</t>
         </is>
       </c>
-      <c r="AY30" s="79" t="inlineStr">
+      <c r="AZ30" s="79" t="inlineStr">
         <is>
           <t>Broadcom Faces New AI Challenge as Google Deepens Marvell Partnership</t>
-        </is>
-      </c>
-      <c r="AZ30" s="79" t="inlineStr">
-        <is>
-          <t>Broadcom Urges Enterprises to Prepare Now for Post-Quantum Cyber Threats</t>
         </is>
       </c>
     </row>
@@ -7665,16 +7812,16 @@
         <v>108.129997253418</v>
       </c>
       <c r="U31" s="83" t="n">
-        <v>108.8300018310547</v>
+        <v>108.9700012207031</v>
       </c>
       <c r="V31" s="83" t="n">
-        <v>105.1900024414062</v>
+        <v>105.1399993896484</v>
       </c>
       <c r="W31" s="84" t="n">
-        <v>1873073</v>
+        <v>2313900</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>0.6515719482457752</v>
+        <v>0.7987945069284782</v>
       </c>
       <c r="Y31" s="35" t="n">
         <v>65.28503598146888</v>
@@ -7683,7 +7830,7 @@
         <v>70.448100418946</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>20.71088267501756</v>
+        <v>20.69494291305339</v>
       </c>
       <c r="AB31" s="86" t="n">
         <v>3.005102164700801</v>
@@ -7725,7 +7872,7 @@
         <v>21.40250557551872</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>3.794736892955154</v>
+        <v>3.807500555819707</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -7850,7 +7997,7 @@
         <v>-1.209999084472656</v>
       </c>
       <c r="T32" s="72" t="n">
-        <v>90.61000061035156</v>
+        <v>90.75</v>
       </c>
       <c r="U32" s="72" t="n">
         <v>91.80999755859375</v>
@@ -7859,10 +8006,10 @@
         <v>86.51000213623047</v>
       </c>
       <c r="W32" s="73" t="n">
-        <v>19456096</v>
+        <v>19738000</v>
       </c>
       <c r="X32" s="74" t="n">
-        <v>0.644747464242209</v>
+        <v>0.6537839843128942</v>
       </c>
       <c r="Y32" s="28" t="n">
         <v>47.26430761025513</v>
@@ -8047,10 +8194,10 @@
         <v>459.1300048828125</v>
       </c>
       <c r="W33" s="84" t="n">
-        <v>4635914</v>
+        <v>4642600</v>
       </c>
       <c r="X33" s="85" t="n">
-        <v>0.8731569637810371</v>
+        <v>0.8743611933242995</v>
       </c>
       <c r="Y33" s="35" t="n">
         <v>56.91722587993239</v>
@@ -8226,7 +8373,7 @@
         <v>-1.3900146484375</v>
       </c>
       <c r="T34" s="72" t="n">
-        <v>336.3219909667969</v>
+        <v>336.2999877929688</v>
       </c>
       <c r="U34" s="72" t="n">
         <v>338.8099975585938</v>
@@ -8235,10 +8382,10 @@
         <v>335.3999938964844</v>
       </c>
       <c r="W34" s="73" t="n">
-        <v>16991240</v>
+        <v>17899600</v>
       </c>
       <c r="X34" s="74" t="n">
-        <v>0.9870466408531271</v>
+        <v>1.037078409514915</v>
       </c>
       <c r="Y34" s="28" t="n">
         <v>43.15833149859111</v>
@@ -8414,19 +8561,19 @@
         <v>0.9499969482421875</v>
       </c>
       <c r="T35" s="83" t="n">
-        <v>40.61199951171875</v>
+        <v>40.65000152587891</v>
       </c>
       <c r="U35" s="83" t="n">
-        <v>41.5099983215332</v>
+        <v>41.52000045776367</v>
       </c>
       <c r="V35" s="83" t="n">
         <v>40.31000137329102</v>
       </c>
       <c r="W35" s="84" t="n">
-        <v>42523265</v>
+        <v>46872400</v>
       </c>
       <c r="X35" s="85" t="n">
-        <v>0.9741019588935911</v>
+        <v>1.068407638985605</v>
       </c>
       <c r="Y35" s="35" t="n">
         <v>48.35559646321695</v>
@@ -8477,7 +8624,7 @@
         <v>21.53582671938426</v>
       </c>
       <c r="AO35" s="88" t="n">
-        <v>8.732148257900167</v>
+        <v>8.733910997410886</v>
       </c>
       <c r="AP35" s="83" t="n">
         <v>76.87000274658203</v>
@@ -8505,17 +8652,17 @@
       </c>
       <c r="AX35" s="90" t="inlineStr">
         <is>
+          <t>Nasdaq Futures Sink While S&amp;P 500, Dow Futures Gain Ahead Of Fed Chief Warsh’s Jackson Hole Speech: PYPL, M...</t>
+        </is>
+      </c>
+      <c r="AY35" s="90" t="inlineStr">
+        <is>
+          <t>IREN Stock Falls 8% After Q4 Miss; AI Cloud Shift Gains Momentum</t>
+        </is>
+      </c>
+      <c r="AZ35" s="90" t="inlineStr">
+        <is>
           <t>IREN Q4 Earnings Call Highlights</t>
-        </is>
-      </c>
-      <c r="AY35" s="90" t="inlineStr">
-        <is>
-          <t>IREN Limited (IREN) Reports Q4 Loss, Beats Revenue Estimates</t>
-        </is>
-      </c>
-      <c r="AZ35" s="90" t="inlineStr">
-        <is>
-          <t>Bitcoin Price Tests $80,000 In 'Powerful Setup.' IREN Tops Sales Views.</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8749,7 @@
         <v>3.849998474121094</v>
       </c>
       <c r="T36" s="72" t="n">
-        <v>89.94999694824219</v>
+        <v>89.91000366210938</v>
       </c>
       <c r="U36" s="72" t="n">
         <v>92.94999694824219</v>
@@ -8611,10 +8758,10 @@
         <v>88.45999908447266</v>
       </c>
       <c r="W36" s="73" t="n">
-        <v>99979854</v>
+        <v>100251700</v>
       </c>
       <c r="X36" s="74" t="n">
-        <v>0.9693495011668117</v>
+        <v>0.9718570953210842</v>
       </c>
       <c r="Y36" s="28" t="n">
         <v>44.27592621645633</v>
@@ -8693,17 +8840,17 @@
       </c>
       <c r="AX36" s="79" t="inlineStr">
         <is>
+          <t>Amkor, FormFactor, Vishay Intertechnology, Allegro MicroSystems, and Intel Shares Skyrocket, What You Need ...</t>
+        </is>
+      </c>
+      <c r="AY36" s="79" t="inlineStr">
+        <is>
+          <t>Nancy Pelosi Buys Intel. What Comes Next and If You Should Buy INTC Stock Too.</t>
+        </is>
+      </c>
+      <c r="AZ36" s="79" t="inlineStr">
+        <is>
           <t>Intel Jumps 3.6% as Nvidia's $5 Billion Entry Price Looks Tiny</t>
-        </is>
-      </c>
-      <c r="AY36" s="79" t="inlineStr">
-        <is>
-          <t>Which Turnaround Is Better for Retirees: CVS or INTC?</t>
-        </is>
-      </c>
-      <c r="AZ36" s="79" t="inlineStr">
-        <is>
-          <t>Kasm Technologies Expands Intel Partnership to Deliver Private AI Through Kasm AI Workspaces on Intel Xeon ...</t>
         </is>
       </c>
     </row>
@@ -8790,19 +8937,19 @@
         <v>8.69000244140625</v>
       </c>
       <c r="T37" s="83" t="n">
-        <v>494.6549987792969</v>
+        <v>494.8800048828125</v>
       </c>
       <c r="U37" s="83" t="n">
-        <v>506.4700012207031</v>
+        <v>506.4800109863281</v>
       </c>
       <c r="V37" s="83" t="n">
         <v>490.0799865722656</v>
       </c>
       <c r="W37" s="84" t="n">
-        <v>28615865</v>
+        <v>28649300</v>
       </c>
       <c r="X37" s="85" t="n">
-        <v>0.9513321542966903</v>
+        <v>0.9523907670024605</v>
       </c>
       <c r="Y37" s="35" t="n">
         <v>70.45128335913824</v>
@@ -8811,7 +8958,7 @@
         <v>76.29856180228973</v>
       </c>
       <c r="AA37" s="35" t="n">
-        <v>35.45290493703252</v>
+        <v>35.45336133350031</v>
       </c>
       <c r="AB37" s="86" t="n">
         <v>18.10930597592107</v>
@@ -8853,7 +9000,7 @@
         <v>8.081783650034183</v>
       </c>
       <c r="AO37" s="88" t="n">
-        <v>2.377519170833559</v>
+        <v>2.377660734858107</v>
       </c>
       <c r="AP37" s="83" t="n">
         <v>553.719970703125</v>
@@ -8978,19 +9125,19 @@
         <v>14.20999145507812</v>
       </c>
       <c r="T38" s="72" t="n">
-        <v>126.6999969482422</v>
+        <v>126.7699966430664</v>
       </c>
       <c r="U38" s="72" t="n">
         <v>139.7799987792969</v>
       </c>
       <c r="V38" s="72" t="n">
-        <v>124.4649963378906</v>
+        <v>124.4700012207031</v>
       </c>
       <c r="W38" s="73" t="n">
-        <v>43908722</v>
+        <v>44091800</v>
       </c>
       <c r="X38" s="74" t="n">
-        <v>1.781865833073854</v>
+        <v>1.788630913493065</v>
       </c>
       <c r="Y38" s="28" t="n">
         <v>72.85353721955366</v>
@@ -9166,19 +9313,19 @@
         <v>-3.010009765625</v>
       </c>
       <c r="T39" s="83" t="n">
-        <v>966.9849853515625</v>
+        <v>967.010009765625</v>
       </c>
       <c r="U39" s="83" t="n">
-        <v>968.6845092773438</v>
+        <v>968.7100219726562</v>
       </c>
       <c r="V39" s="83" t="n">
         <v>906.8900146484375</v>
       </c>
       <c r="W39" s="84" t="n">
-        <v>28499670</v>
+        <v>28691600</v>
       </c>
       <c r="X39" s="85" t="n">
-        <v>0.8914281574793949</v>
+        <v>0.8971621519996861</v>
       </c>
       <c r="Y39" s="35" t="n">
         <v>50.99257728699911</v>
@@ -9187,7 +9334,7 @@
         <v>47.39701054912835</v>
       </c>
       <c r="AA39" s="35" t="n">
-        <v>10.69202942977481</v>
+        <v>10.69162354786665</v>
       </c>
       <c r="AB39" s="86" t="n">
         <v>7.20416427576663</v>
@@ -9229,7 +9376,7 @@
         <v>21.13814610071091</v>
       </c>
       <c r="AO39" s="88" t="n">
-        <v>6.649109012411817</v>
+        <v>6.649303833326186</v>
       </c>
       <c r="AP39" s="83" t="n">
         <v>1255</v>
@@ -9354,7 +9501,7 @@
         <v>4.550003051757812</v>
       </c>
       <c r="T40" s="72" t="n">
-        <v>223.2879943847656</v>
+        <v>223.3699951171875</v>
       </c>
       <c r="U40" s="72" t="n">
         <v>228.5</v>
@@ -9363,10 +9510,10 @@
         <v>215.4100036621094</v>
       </c>
       <c r="W40" s="73" t="n">
-        <v>15908149</v>
+        <v>15974300</v>
       </c>
       <c r="X40" s="74" t="n">
-        <v>0.6274094069855621</v>
+        <v>0.6299361952158242</v>
       </c>
       <c r="Y40" s="28" t="n">
         <v>49.72579556929819</v>
@@ -9548,13 +9695,13 @@
         <v>81.15000152587891</v>
       </c>
       <c r="V41" s="83" t="n">
-        <v>79.29000091552734</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="W41" s="84" t="n">
-        <v>27058234</v>
+        <v>27120400</v>
       </c>
       <c r="X41" s="85" t="n">
-        <v>0.9190274871244796</v>
+        <v>0.921041705898944</v>
       </c>
       <c r="Y41" s="35" t="n">
         <v>58.35199284044167</v>
@@ -9563,7 +9710,7 @@
         <v>70.52865099594071</v>
       </c>
       <c r="AA41" s="35" t="n">
-        <v>22.56731843355563</v>
+        <v>22.56191693415193</v>
       </c>
       <c r="AB41" s="86" t="n">
         <v>1.858468529673502</v>
@@ -9605,7 +9752,7 @@
         <v>15.97759109296075</v>
       </c>
       <c r="AO41" s="88" t="n">
-        <v>2.826752123858149</v>
+        <v>2.82764696145202</v>
       </c>
       <c r="AP41" s="83" t="n">
         <v>126.7099990844727</v>
@@ -9736,13 +9883,13 @@
         <v>10.65999984741211</v>
       </c>
       <c r="V42" s="72" t="n">
-        <v>10.36050033569336</v>
+        <v>10.35999965667725</v>
       </c>
       <c r="W42" s="73" t="n">
-        <v>68696632</v>
+        <v>70406900</v>
       </c>
       <c r="X42" s="74" t="n">
-        <v>0.9579107995913652</v>
+        <v>0.9805896401247483</v>
       </c>
       <c r="Y42" s="28" t="n">
         <v>53.35085497285271</v>
@@ -9793,7 +9940,7 @@
         <v>21.19724663048639</v>
       </c>
       <c r="AO42" s="77" t="n">
-        <v>4.922587854694093</v>
+        <v>4.92292555805906</v>
       </c>
       <c r="AP42" s="72" t="n">
         <v>17.45000076293945</v>
@@ -9918,7 +10065,7 @@
         <v>18.31999206542969</v>
       </c>
       <c r="T43" s="83" t="n">
-        <v>222.5850067138672</v>
+        <v>222.8600006103516</v>
       </c>
       <c r="U43" s="83" t="n">
         <v>230.4700012207031</v>
@@ -9927,10 +10074,10 @@
         <v>220.8999938964844</v>
       </c>
       <c r="W43" s="84" t="n">
-        <v>297197891</v>
+        <v>298231200</v>
       </c>
       <c r="X43" s="85" t="n">
-        <v>2.376572047743667</v>
+        <v>2.383850121871779</v>
       </c>
       <c r="Y43" s="35" t="n">
         <v>61.31941960626309</v>
@@ -10009,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
-          <t>Nvidia Just Guided for 70% Revenue Growth in Fiscal Year 2028. Here's What That Means for AI Stocks.</t>
+          <t>Amkor, FormFactor, Vishay Intertechnology, Allegro MicroSystems, and Intel Shares Skyrocket, What You Need ...</t>
         </is>
       </c>
       <c r="AY43" s="90" t="inlineStr">
         <is>
-          <t>Dow Jones Futures: Fed Chief Warsh Due; Nvidia, These 7 Stocks Are In Buy Zones</t>
+          <t>Nasdaq Futures Sink While S&amp;P 500, Dow Futures Gain Ahead Of Fed Chief Warsh’s Jackson Hole Speech: PYPL, M...</t>
         </is>
       </c>
       <c r="AZ43" s="90" t="inlineStr">
         <is>
-          <t>NVDA Q2 Deep Dive: AI Infrastructure Demand and Supply Constraints Drive Results</t>
+          <t>Asian shares mostly gain after upbeat results for Nvidia and others lift US stocks</t>
         </is>
       </c>
     </row>
@@ -10106,28 +10253,28 @@
         <v>8.42999267578125</v>
       </c>
       <c r="T44" s="72" t="n">
-        <v>178.9299926757812</v>
+        <v>178.75</v>
       </c>
       <c r="U44" s="72" t="n">
-        <v>186.8500061035156</v>
+        <v>186.8600006103516</v>
       </c>
       <c r="V44" s="72" t="n">
         <v>178.0099945068359</v>
       </c>
       <c r="W44" s="73" t="n">
-        <v>40613863</v>
+        <v>40651900</v>
       </c>
       <c r="X44" s="74" t="n">
-        <v>0.8588940225195333</v>
+        <v>0.8596638459097615</v>
       </c>
       <c r="Y44" s="28" t="n">
         <v>69.09787260511135</v>
       </c>
       <c r="Z44" s="28" t="n">
-        <v>95.02964374744451</v>
+        <v>94.97836004307393</v>
       </c>
       <c r="AA44" s="28" t="n">
-        <v>34.9918981467595</v>
+        <v>34.99258410853557</v>
       </c>
       <c r="AB44" s="75" t="n">
         <v>11.08613005288802</v>
@@ -10169,7 +10316,7 @@
         <v>38.13274643460484</v>
       </c>
       <c r="AO44" s="77" t="n">
-        <v>4.300007681457641</v>
+        <v>4.300391639599709</v>
       </c>
       <c r="AP44" s="72" t="n">
         <v>207.5200042724609</v>
@@ -10294,19 +10441,19 @@
         <v>1.05999755859375</v>
       </c>
       <c r="T45" s="83" t="n">
-        <v>165.1199951171875</v>
+        <v>165.1600036621094</v>
       </c>
       <c r="U45" s="83" t="n">
         <v>166.9499969482422</v>
       </c>
       <c r="V45" s="83" t="n">
-        <v>161.9234008789062</v>
+        <v>161.9199981689453</v>
       </c>
       <c r="W45" s="84" t="n">
-        <v>15050965</v>
+        <v>15065100</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>1.504956802384819</v>
+        <v>1.506263725880818</v>
       </c>
       <c r="Y45" s="35" t="n">
         <v>49.20875651303803</v>
@@ -10357,7 +10504,7 @@
         <v>11.21274275152781</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>3.818793735654197</v>
+        <v>3.81894123578364</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -10482,19 +10629,19 @@
         <v>1.349998474121094</v>
       </c>
       <c r="T46" s="72" t="n">
-        <v>67.01670074462891</v>
+        <v>66.91000366210938</v>
       </c>
       <c r="U46" s="72" t="n">
-        <v>67.55999755859375</v>
+        <v>67.56999969482422</v>
       </c>
       <c r="V46" s="72" t="n">
         <v>65.41999816894531</v>
       </c>
       <c r="W46" s="73" t="n">
-        <v>11320659</v>
+        <v>11397800</v>
       </c>
       <c r="X46" s="74" t="n">
-        <v>0.6401699807959338</v>
+        <v>0.6443916644853003</v>
       </c>
       <c r="Y46" s="28" t="n">
         <v>38.76198658715374</v>
@@ -10545,7 +10692,7 @@
         <v>30.43002575697768</v>
       </c>
       <c r="AO46" s="77" t="n">
-        <v>7.458928508912822</v>
+        <v>7.45998646584321</v>
       </c>
       <c r="AP46" s="72" t="n">
         <v>151</v>
@@ -10573,17 +10720,17 @@
       </c>
       <c r="AX46" s="79" t="inlineStr">
         <is>
+          <t>RKLB Stock Heads For Third Weekly Loss After 7 Bruising Sessions: SpaceX Raises Red Flag Over Iridium Deal</t>
+        </is>
+      </c>
+      <c r="AY46" s="79" t="inlineStr">
+        <is>
           <t>Rocket Lab CFO Sells Nearly 10,000 Shares Amid a Rising Stock Price</t>
         </is>
       </c>
-      <c r="AY46" s="79" t="inlineStr">
+      <c r="AZ46" s="79" t="inlineStr">
         <is>
           <t>Rocket Lab Stock: Bull vs. Bear</t>
-        </is>
-      </c>
-      <c r="AZ46" s="79" t="inlineStr">
-        <is>
-          <t>Is RKLB Stock A Buy Or A High-Beta Trap?</t>
         </is>
       </c>
     </row>
@@ -10670,7 +10817,7 @@
         <v>-14.4200439453125</v>
       </c>
       <c r="T47" s="83" t="n">
-        <v>1548.489990234375</v>
+        <v>1549.420043945312</v>
       </c>
       <c r="U47" s="83" t="n">
         <v>1557.890014648438</v>
@@ -10679,10 +10826,10 @@
         <v>1456</v>
       </c>
       <c r="W47" s="84" t="n">
-        <v>8754429</v>
+        <v>8799100</v>
       </c>
       <c r="X47" s="85" t="n">
-        <v>0.6072467982714458</v>
+        <v>0.6102508352795738</v>
       </c>
       <c r="Y47" s="35" t="n">
         <v>49.32206344808555</v>
@@ -10761,17 +10908,17 @@
       </c>
       <c r="AX47" s="90" t="inlineStr">
         <is>
+          <t>After Surging 3,110%, Has Sandisk Already Had Its "Nvidia Moment"?</t>
+        </is>
+      </c>
+      <c r="AY47" s="90" t="inlineStr">
+        <is>
           <t>The Peer-Group Mispricing Sitting On SNDK Stock</t>
         </is>
       </c>
-      <c r="AY47" s="90" t="inlineStr">
+      <c r="AZ47" s="90" t="inlineStr">
         <is>
           <t>AI Bubble Could Be Ready to Pop and Jim Cramer May Be the Warning Sign</t>
-        </is>
-      </c>
-      <c r="AZ47" s="90" t="inlineStr">
-        <is>
-          <t>Nvidia, Micron, Salesforce, Marvell, Veeva, Okta, Hormel, and More Stocks That Explain Today’s Market</t>
         </is>
       </c>
     </row>
@@ -10858,7 +11005,7 @@
         <v>8.989990234375</v>
       </c>
       <c r="T48" s="72" t="n">
-        <v>346.2999877929688</v>
+        <v>346.1600036621094</v>
       </c>
       <c r="U48" s="72" t="n">
         <v>355.739990234375</v>
@@ -10867,10 +11014,10 @@
         <v>345.4500122070312</v>
       </c>
       <c r="W48" s="73" t="n">
-        <v>29998173</v>
+        <v>30062000</v>
       </c>
       <c r="X48" s="74" t="n">
-        <v>0.8993521486493352</v>
+        <v>0.9011794743199673</v>
       </c>
       <c r="Y48" s="28" t="n">
         <v>53.87218957306972</v>
@@ -10949,17 +11096,17 @@
       </c>
       <c r="AX48" s="79" t="inlineStr">
         <is>
+          <t>Tesla Stock Sits Nearly 30% Below Its High and Still Trades at 330 Times Earnings</t>
+        </is>
+      </c>
+      <c r="AY48" s="79" t="inlineStr">
+        <is>
           <t>Optimus Just Entered Production at Fremont. Here's What Changes for Tesla Investors.</t>
         </is>
       </c>
-      <c r="AY48" s="79" t="inlineStr">
+      <c r="AZ48" s="79" t="inlineStr">
         <is>
           <t>What Is Tesla (TSLA) Really Building With Optimus Robots And Its New Starbase?</t>
-        </is>
-      </c>
-      <c r="AZ48" s="79" t="inlineStr">
-        <is>
-          <t>Ford Motor vs. Tesla: Analyzing Revenue Trends Between These Automotive Giants</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 28 Aug 2026, 01:35 AM · Yahoo Finance data</t>
+          <t>Built 28 Aug 2026, 04:22 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -11521,22 +11668,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>19 of 39</t>
+          <t>20 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>20 of 39</t>
+          <t>20 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.5 / 9</t>
+          <t>4.6 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>17 of 39</t>
+          <t>18 of 40</t>
         </is>
       </c>
     </row>
@@ -12106,7 +12253,7 @@
         <v>-0.009983456369602406</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
@@ -12284,7 +12431,7 @@
         <v>-0.0008575381680699934</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
@@ -12458,57 +12605,171 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
-      <c r="I10" s="30" t="n"/>
-      <c r="J10" s="30" t="n"/>
-      <c r="K10" s="30" t="n"/>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="30" t="n"/>
-      <c r="N10" s="80" t="n"/>
-      <c r="O10" s="30" t="n"/>
-      <c r="P10" s="32" t="n"/>
+      <c r="C10" s="33" t="n">
+        <v>0.005961954941947623</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" s="80" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" s="30" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="P10" s="32" t="inlineStr">
+        <is>
+          <t>Long-term up, short-term mixed</t>
+        </is>
+      </c>
       <c r="Q10" s="32" t="inlineStr">
         <is>
           <t>State Street Energy Select Sector SPDR ETF</t>
         </is>
       </c>
-      <c r="R10" s="81" t="n"/>
-      <c r="S10" s="82" t="n"/>
-      <c r="T10" s="83" t="n"/>
-      <c r="U10" s="83" t="n"/>
-      <c r="V10" s="83" t="n"/>
-      <c r="W10" s="84" t="n"/>
-      <c r="X10" s="85" t="n"/>
-      <c r="Y10" s="35" t="n"/>
-      <c r="Z10" s="35" t="n"/>
-      <c r="AA10" s="35" t="n"/>
-      <c r="AB10" s="86" t="n"/>
-      <c r="AC10" s="86" t="n"/>
-      <c r="AD10" s="86" t="n"/>
-      <c r="AE10" s="83" t="n"/>
-      <c r="AF10" s="83" t="n"/>
-      <c r="AG10" s="83" t="n"/>
-      <c r="AH10" s="83" t="n"/>
-      <c r="AI10" s="83" t="n"/>
-      <c r="AJ10" s="83" t="n"/>
-      <c r="AK10" s="83" t="n"/>
-      <c r="AL10" s="83" t="n"/>
-      <c r="AM10" s="87" t="n"/>
-      <c r="AN10" s="36" t="n"/>
-      <c r="AO10" s="88" t="n"/>
-      <c r="AP10" s="83" t="n"/>
-      <c r="AQ10" s="83" t="n"/>
-      <c r="AR10" s="36" t="n"/>
-      <c r="AS10" s="89" t="n"/>
-      <c r="AT10" s="33" t="n"/>
-      <c r="AU10" s="33" t="n"/>
-      <c r="AV10" s="33" t="n"/>
-      <c r="AW10" s="33" t="n"/>
+      <c r="R10" s="81" t="n">
+        <v>62.43000030517578</v>
+      </c>
+      <c r="S10" s="82" t="n">
+        <v>0.3699989318847656</v>
+      </c>
+      <c r="T10" s="83" t="n">
+        <v>61.43000030517578</v>
+      </c>
+      <c r="U10" s="83" t="n">
+        <v>63.02000045776367</v>
+      </c>
+      <c r="V10" s="83" t="n">
+        <v>61.31000137329102</v>
+      </c>
+      <c r="W10" s="84" t="n">
+        <v>24394100</v>
+      </c>
+      <c r="X10" s="85" t="n">
+        <v>0.9471051659417036</v>
+      </c>
+      <c r="Y10" s="35" t="n">
+        <v>61.17888562652035</v>
+      </c>
+      <c r="Z10" s="35" t="n">
+        <v>70.09225641211214</v>
+      </c>
+      <c r="AA10" s="35" t="n">
+        <v>27.34330835731434</v>
+      </c>
+      <c r="AB10" s="86" t="n">
+        <v>1.445584747339346</v>
+      </c>
+      <c r="AC10" s="86" t="n">
+        <v>1.42964428085391</v>
+      </c>
+      <c r="AD10" s="86" t="n">
+        <v>0.01594046648543568</v>
+      </c>
+      <c r="AE10" s="83" t="n">
+        <v>62.549695529112</v>
+      </c>
+      <c r="AF10" s="83" t="n">
+        <v>61.16086208606474</v>
+      </c>
+      <c r="AG10" s="83" t="n">
+        <v>57.85300033569336</v>
+      </c>
+      <c r="AH10" s="83" t="n">
+        <v>57.78890014648437</v>
+      </c>
+      <c r="AI10" s="83" t="n">
+        <v>54.17972492218018</v>
+      </c>
+      <c r="AJ10" s="83" t="n">
+        <v>65.20610140671835</v>
+      </c>
+      <c r="AK10" s="83" t="n">
+        <v>60.93650035858154</v>
+      </c>
+      <c r="AL10" s="83" t="n">
+        <v>56.66689931044473</v>
+      </c>
+      <c r="AM10" s="87" t="n">
+        <v>0.6748992387996045</v>
+      </c>
+      <c r="AN10" s="36" t="n">
+        <v>14.01327947293425</v>
+      </c>
+      <c r="AO10" s="88" t="n">
+        <v>1.936150951015984</v>
+      </c>
+      <c r="AP10" s="83" t="n">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="AQ10" s="83" t="n">
+        <v>42.34999847412109</v>
+      </c>
+      <c r="AR10" s="36" t="n">
+        <v>-3.508495749825657</v>
+      </c>
+      <c r="AS10" s="89" t="n">
+        <v>89.84341477385415</v>
+      </c>
+      <c r="AT10" s="33" t="n">
+        <v>-0.01808747236174513</v>
+      </c>
+      <c r="AU10" s="33" t="n">
+        <v>0.08441897926201469</v>
+      </c>
+      <c r="AV10" s="33" t="n">
+        <v>0.0954553161342413</v>
+      </c>
+      <c r="AW10" s="33" t="n">
+        <v>0.3963319522155193</v>
+      </c>
       <c r="AX10" s="32" t="n"/>
       <c r="AY10" s="32" t="n"/>
       <c r="AZ10" s="32" t="n"/>
@@ -12526,7 +12787,7 @@
         <v>-0.002889505428801176</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
@@ -12704,7 +12965,7 @@
         <v>-0.006697696537283249</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
@@ -12882,7 +13143,7 @@
         <v>-0.00503622277157878</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
@@ -13060,7 +13321,7 @@
         <v>0.0016796628371607</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
@@ -13416,7 +13677,7 @@
         <v>-0.005952390964078957</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
@@ -13594,7 +13855,7 @@
         <v>0.004617800551849571</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
@@ -19318,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 28 Aug 2026, 01:35 AM · Yahoo Finance data</t>
+          <t>Built 28 Aug 2026, 04:22 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19343,22 +19604,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>27 of 39</t>
+          <t>27 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>11 of 39</t>
+          <t>12 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.7 / 9</t>
+          <t>4.8 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>19 of 39</t>
+          <t>20 of 40</t>
         </is>
       </c>
     </row>
@@ -20280,57 +20541,171 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
-      <c r="I10" s="30" t="n"/>
-      <c r="J10" s="30" t="n"/>
-      <c r="K10" s="30" t="n"/>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="30" t="n"/>
-      <c r="N10" s="80" t="n"/>
-      <c r="O10" s="30" t="n"/>
-      <c r="P10" s="32" t="n"/>
+      <c r="C10" s="33" t="n">
+        <v>-0.01663760460950336</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" s="80" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" s="30" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="P10" s="32" t="inlineStr">
+        <is>
+          <t>Long-term up, short-term mixed</t>
+        </is>
+      </c>
       <c r="Q10" s="32" t="inlineStr">
         <is>
           <t>State Street Energy Select Sector SPDR ETF</t>
         </is>
       </c>
-      <c r="R10" s="81" t="n"/>
-      <c r="S10" s="82" t="n"/>
-      <c r="T10" s="83" t="n"/>
-      <c r="U10" s="83" t="n"/>
-      <c r="V10" s="83" t="n"/>
-      <c r="W10" s="84" t="n"/>
-      <c r="X10" s="85" t="n"/>
-      <c r="Y10" s="35" t="n"/>
-      <c r="Z10" s="35" t="n"/>
-      <c r="AA10" s="35" t="n"/>
-      <c r="AB10" s="86" t="n"/>
-      <c r="AC10" s="86" t="n"/>
-      <c r="AD10" s="86" t="n"/>
-      <c r="AE10" s="83" t="n"/>
-      <c r="AF10" s="83" t="n"/>
-      <c r="AG10" s="83" t="n"/>
-      <c r="AH10" s="83" t="n"/>
-      <c r="AI10" s="83" t="n"/>
-      <c r="AJ10" s="83" t="n"/>
-      <c r="AK10" s="83" t="n"/>
-      <c r="AL10" s="83" t="n"/>
-      <c r="AM10" s="87" t="n"/>
-      <c r="AN10" s="36" t="n"/>
-      <c r="AO10" s="88" t="n"/>
-      <c r="AP10" s="83" t="n"/>
-      <c r="AQ10" s="83" t="n"/>
-      <c r="AR10" s="36" t="n"/>
-      <c r="AS10" s="89" t="n"/>
-      <c r="AT10" s="33" t="n"/>
-      <c r="AU10" s="33" t="n"/>
-      <c r="AV10" s="33" t="n"/>
-      <c r="AW10" s="33" t="n"/>
+      <c r="R10" s="81" t="n">
+        <v>62.06000137329102</v>
+      </c>
+      <c r="S10" s="82" t="n">
+        <v>-1.049999237060547</v>
+      </c>
+      <c r="T10" s="83" t="n">
+        <v>62.20000076293945</v>
+      </c>
+      <c r="U10" s="83" t="n">
+        <v>62.79000091552734</v>
+      </c>
+      <c r="V10" s="83" t="n">
+        <v>62.04000091552734</v>
+      </c>
+      <c r="W10" s="84" t="n">
+        <v>27426400</v>
+      </c>
+      <c r="X10" s="85" t="n">
+        <v>1.045009510339446</v>
+      </c>
+      <c r="Y10" s="35" t="n">
+        <v>59.46408936893629</v>
+      </c>
+      <c r="Z10" s="35" t="n">
+        <v>65.21743282309848</v>
+      </c>
+      <c r="AA10" s="35" t="n">
+        <v>28.34826020131646</v>
+      </c>
+      <c r="AB10" s="86" t="n">
+        <v>1.532070594087308</v>
+      </c>
+      <c r="AC10" s="86" t="n">
+        <v>1.425659164232551</v>
+      </c>
+      <c r="AD10" s="86" t="n">
+        <v>0.1064114298547569</v>
+      </c>
+      <c r="AE10" s="83" t="n">
+        <v>62.58389416452235</v>
+      </c>
+      <c r="AF10" s="83" t="n">
+        <v>61.03394826415364</v>
+      </c>
+      <c r="AG10" s="83" t="n">
+        <v>57.71540031433106</v>
+      </c>
+      <c r="AH10" s="83" t="n">
+        <v>57.75710014343262</v>
+      </c>
+      <c r="AI10" s="83" t="n">
+        <v>54.08824991226196</v>
+      </c>
+      <c r="AJ10" s="83" t="n">
+        <v>65.07024447482409</v>
+      </c>
+      <c r="AK10" s="83" t="n">
+        <v>60.7475004196167</v>
+      </c>
+      <c r="AL10" s="83" t="n">
+        <v>56.4247563644093</v>
+      </c>
+      <c r="AM10" s="87" t="n">
+        <v>0.6518134010378445</v>
+      </c>
+      <c r="AN10" s="36" t="n">
+        <v>14.23184172302663</v>
+      </c>
+      <c r="AO10" s="88" t="n">
+        <v>1.88556325190176</v>
+      </c>
+      <c r="AP10" s="83" t="n">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="AQ10" s="83" t="n">
+        <v>42.34999847412109</v>
+      </c>
+      <c r="AR10" s="36" t="n">
+        <v>-4.080364295941274</v>
+      </c>
+      <c r="AS10" s="89" t="n">
+        <v>88.18793845553053</v>
+      </c>
+      <c r="AT10" s="33" t="n">
+        <v>-0.02543968159738053</v>
+      </c>
+      <c r="AU10" s="33" t="n">
+        <v>0.0633996011693525</v>
+      </c>
+      <c r="AV10" s="33" t="n">
+        <v>0.07277446862947179</v>
+      </c>
+      <c r="AW10" s="33" t="n">
+        <v>0.3880564223684775</v>
+      </c>
       <c r="AX10" s="32" t="n"/>
       <c r="AY10" s="32" t="n"/>
       <c r="AZ10" s="32" t="n"/>
@@ -27140,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 28 Aug 2026, 01:35 AM · Yahoo Finance data</t>
+          <t>Built 28 Aug 2026, 04:22 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27165,22 +27540,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>14 of 39</t>
+          <t>14 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>25 of 39</t>
+          <t>26 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.0 / 9</t>
+          <t>4.1 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>13 of 39</t>
+          <t>14 of 40</t>
         </is>
       </c>
     </row>
@@ -28102,57 +28477,171 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
-      <c r="I10" s="30" t="n"/>
-      <c r="J10" s="30" t="n"/>
-      <c r="K10" s="30" t="n"/>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="30" t="n"/>
-      <c r="N10" s="80" t="n"/>
-      <c r="O10" s="30" t="n"/>
-      <c r="P10" s="32" t="n"/>
+      <c r="C10" s="33" t="n">
+        <v>-0.008328076435888287</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" s="80" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" s="30" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="P10" s="32" t="inlineStr">
+        <is>
+          <t>Above every average</t>
+        </is>
+      </c>
       <c r="Q10" s="32" t="inlineStr">
         <is>
           <t>State Street Energy Select Sector SPDR ETF</t>
         </is>
       </c>
-      <c r="R10" s="81" t="n"/>
-      <c r="S10" s="82" t="n"/>
-      <c r="T10" s="83" t="n"/>
-      <c r="U10" s="83" t="n"/>
-      <c r="V10" s="83" t="n"/>
-      <c r="W10" s="84" t="n"/>
-      <c r="X10" s="85" t="n"/>
-      <c r="Y10" s="35" t="n"/>
-      <c r="Z10" s="35" t="n"/>
-      <c r="AA10" s="35" t="n"/>
-      <c r="AB10" s="86" t="n"/>
-      <c r="AC10" s="86" t="n"/>
-      <c r="AD10" s="86" t="n"/>
-      <c r="AE10" s="83" t="n"/>
-      <c r="AF10" s="83" t="n"/>
-      <c r="AG10" s="83" t="n"/>
-      <c r="AH10" s="83" t="n"/>
-      <c r="AI10" s="83" t="n"/>
-      <c r="AJ10" s="83" t="n"/>
-      <c r="AK10" s="83" t="n"/>
-      <c r="AL10" s="83" t="n"/>
-      <c r="AM10" s="87" t="n"/>
-      <c r="AN10" s="36" t="n"/>
-      <c r="AO10" s="88" t="n"/>
-      <c r="AP10" s="83" t="n"/>
-      <c r="AQ10" s="83" t="n"/>
-      <c r="AR10" s="36" t="n"/>
-      <c r="AS10" s="89" t="n"/>
-      <c r="AT10" s="33" t="n"/>
-      <c r="AU10" s="33" t="n"/>
-      <c r="AV10" s="33" t="n"/>
-      <c r="AW10" s="33" t="n"/>
+      <c r="R10" s="81" t="n">
+        <v>63.11000061035156</v>
+      </c>
+      <c r="S10" s="82" t="n">
+        <v>-0.529998779296875</v>
+      </c>
+      <c r="T10" s="83" t="n">
+        <v>63.2400016784668</v>
+      </c>
+      <c r="U10" s="83" t="n">
+        <v>63.72000122070312</v>
+      </c>
+      <c r="V10" s="83" t="n">
+        <v>62.56000137329102</v>
+      </c>
+      <c r="W10" s="84" t="n">
+        <v>23007900</v>
+      </c>
+      <c r="X10" s="85" t="n">
+        <v>0.876029552418839</v>
+      </c>
+      <c r="Y10" s="35" t="n">
+        <v>67.29742645360218</v>
+      </c>
+      <c r="Z10" s="35" t="n">
+        <v>79.05142154083688</v>
+      </c>
+      <c r="AA10" s="35" t="n">
+        <v>28.6193713834481</v>
+      </c>
+      <c r="AB10" s="86" t="n">
+        <v>1.657845939268974</v>
+      </c>
+      <c r="AC10" s="86" t="n">
+        <v>1.399056306768862</v>
+      </c>
+      <c r="AD10" s="86" t="n">
+        <v>0.2587896325001116</v>
+      </c>
+      <c r="AE10" s="83" t="n">
+        <v>62.73357781915987</v>
+      </c>
+      <c r="AF10" s="83" t="n">
+        <v>60.9313429532399</v>
+      </c>
+      <c r="AG10" s="83" t="n">
+        <v>57.62520027160645</v>
+      </c>
+      <c r="AH10" s="83" t="n">
+        <v>57.72620014190674</v>
+      </c>
+      <c r="AI10" s="83" t="n">
+        <v>53.99649990081787</v>
+      </c>
+      <c r="AJ10" s="83" t="n">
+        <v>65.01290962616201</v>
+      </c>
+      <c r="AK10" s="83" t="n">
+        <v>60.52300033569336</v>
+      </c>
+      <c r="AL10" s="83" t="n">
+        <v>56.0330910452247</v>
+      </c>
+      <c r="AM10" s="87" t="n">
+        <v>0.7880904832698942</v>
+      </c>
+      <c r="AN10" s="36" t="n">
+        <v>14.83703473246596</v>
+      </c>
+      <c r="AO10" s="88" t="n">
+        <v>1.866402773841495</v>
+      </c>
+      <c r="AP10" s="83" t="n">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="AQ10" s="83" t="n">
+        <v>42.34999847412109</v>
+      </c>
+      <c r="AR10" s="36" t="n">
+        <v>-2.457490591788691</v>
+      </c>
+      <c r="AS10" s="89" t="n">
+        <v>92.88592193985306</v>
+      </c>
+      <c r="AT10" s="33" t="n">
+        <v>0.008469139721786867</v>
+      </c>
+      <c r="AU10" s="33" t="n">
+        <v>0.05853743275732182</v>
+      </c>
+      <c r="AV10" s="33" t="n">
+        <v>0.06085054344846452</v>
+      </c>
+      <c r="AW10" s="33" t="n">
+        <v>0.4115410848279137</v>
+      </c>
       <c r="AX10" s="32" t="n"/>
       <c r="AY10" s="32" t="n"/>
       <c r="AZ10" s="32" t="n"/>
@@ -28882,7 +29371,7 @@
         <v>-0.01778405188071586</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
@@ -34962,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 28 Aug 2026, 01:35 AM · Yahoo Finance data</t>
+          <t>Built 28 Aug 2026, 04:22 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -34987,12 +35476,12 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>24 of 39</t>
+          <t>24 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>14 of 39</t>
+          <t>15 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
@@ -35002,7 +35491,7 @@
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>19 of 39</t>
+          <t>20 of 40</t>
         </is>
       </c>
     </row>
@@ -35924,57 +36413,171 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
-      <c r="I10" s="30" t="n"/>
-      <c r="J10" s="30" t="n"/>
-      <c r="K10" s="30" t="n"/>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="30" t="n"/>
-      <c r="N10" s="80" t="n"/>
-      <c r="O10" s="30" t="n"/>
-      <c r="P10" s="32" t="n"/>
+      <c r="C10" s="33" t="n">
+        <v>-0.001725499770220629</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M10" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" s="80" t="n">
+        <v>8</v>
+      </c>
+      <c r="O10" s="30" t="inlineStr">
+        <is>
+          <t>Very Strong</t>
+        </is>
+      </c>
+      <c r="P10" s="32" t="inlineStr">
+        <is>
+          <t>Above every average</t>
+        </is>
+      </c>
       <c r="Q10" s="32" t="inlineStr">
         <is>
           <t>State Street Energy Select Sector SPDR ETF</t>
         </is>
       </c>
-      <c r="R10" s="81" t="n"/>
-      <c r="S10" s="82" t="n"/>
-      <c r="T10" s="83" t="n"/>
-      <c r="U10" s="83" t="n"/>
-      <c r="V10" s="83" t="n"/>
-      <c r="W10" s="84" t="n"/>
-      <c r="X10" s="85" t="n"/>
-      <c r="Y10" s="35" t="n"/>
-      <c r="Z10" s="35" t="n"/>
-      <c r="AA10" s="35" t="n"/>
-      <c r="AB10" s="86" t="n"/>
-      <c r="AC10" s="86" t="n"/>
-      <c r="AD10" s="86" t="n"/>
-      <c r="AE10" s="83" t="n"/>
-      <c r="AF10" s="83" t="n"/>
-      <c r="AG10" s="83" t="n"/>
-      <c r="AH10" s="83" t="n"/>
-      <c r="AI10" s="83" t="n"/>
-      <c r="AJ10" s="83" t="n"/>
-      <c r="AK10" s="83" t="n"/>
-      <c r="AL10" s="83" t="n"/>
-      <c r="AM10" s="87" t="n"/>
-      <c r="AN10" s="36" t="n"/>
-      <c r="AO10" s="88" t="n"/>
-      <c r="AP10" s="83" t="n"/>
-      <c r="AQ10" s="83" t="n"/>
-      <c r="AR10" s="36" t="n"/>
-      <c r="AS10" s="89" t="n"/>
-      <c r="AT10" s="33" t="n"/>
-      <c r="AU10" s="33" t="n"/>
-      <c r="AV10" s="33" t="n"/>
-      <c r="AW10" s="33" t="n"/>
+      <c r="R10" s="81" t="n">
+        <v>63.63999938964844</v>
+      </c>
+      <c r="S10" s="82" t="n">
+        <v>-0.1100006103515625</v>
+      </c>
+      <c r="T10" s="83" t="n">
+        <v>63.90999984741211</v>
+      </c>
+      <c r="U10" s="83" t="n">
+        <v>64.30000305175781</v>
+      </c>
+      <c r="V10" s="83" t="n">
+        <v>63.34999847412109</v>
+      </c>
+      <c r="W10" s="84" t="n">
+        <v>27791900</v>
+      </c>
+      <c r="X10" s="85" t="n">
+        <v>1.036840192774177</v>
+      </c>
+      <c r="Y10" s="35" t="n">
+        <v>71.72606516455384</v>
+      </c>
+      <c r="Z10" s="35" t="n">
+        <v>86.03428102722459</v>
+      </c>
+      <c r="AA10" s="35" t="n">
+        <v>28.28720567172499</v>
+      </c>
+      <c r="AB10" s="86" t="n">
+        <v>1.687357880228944</v>
+      </c>
+      <c r="AC10" s="86" t="n">
+        <v>1.334358898643834</v>
+      </c>
+      <c r="AD10" s="86" t="n">
+        <v>0.3529989815851102</v>
+      </c>
+      <c r="AE10" s="83" t="n">
+        <v>62.62602845024796</v>
+      </c>
+      <c r="AF10" s="83" t="n">
+        <v>60.71347718752873</v>
+      </c>
+      <c r="AG10" s="83" t="n">
+        <v>57.50540023803711</v>
+      </c>
+      <c r="AH10" s="83" t="n">
+        <v>57.70770011901855</v>
+      </c>
+      <c r="AI10" s="83" t="n">
+        <v>53.89892490386963</v>
+      </c>
+      <c r="AJ10" s="83" t="n">
+        <v>64.70487358478495</v>
+      </c>
+      <c r="AK10" s="83" t="n">
+        <v>60.28550033569336</v>
+      </c>
+      <c r="AL10" s="83" t="n">
+        <v>55.86612708660177</v>
+      </c>
+      <c r="AM10" s="87" t="n">
+        <v>0.8795220345605117</v>
+      </c>
+      <c r="AN10" s="36" t="n">
+        <v>14.66147987321257</v>
+      </c>
+      <c r="AO10" s="88" t="n">
+        <v>1.853021264697937</v>
+      </c>
+      <c r="AP10" s="83" t="n">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="AQ10" s="83" t="n">
+        <v>42.34999847412109</v>
+      </c>
+      <c r="AR10" s="36" t="n">
+        <v>-1.638327061192468</v>
+      </c>
+      <c r="AS10" s="89" t="n">
+        <v>95.25728129323538</v>
+      </c>
+      <c r="AT10" s="33" t="n">
+        <v>0.02794378204652248</v>
+      </c>
+      <c r="AU10" s="33" t="n">
+        <v>0.0717412974891416</v>
+      </c>
+      <c r="AV10" s="33" t="n">
+        <v>0.07627258988779451</v>
+      </c>
+      <c r="AW10" s="33" t="n">
+        <v>0.4233952290942897</v>
+      </c>
       <c r="AX10" s="32" t="n"/>
       <c r="AY10" s="32" t="n"/>
       <c r="AZ10" s="32" t="n"/>
@@ -37060,7 +37663,7 @@
         <v>-0.02284669841310516</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
@@ -42645,7 +43248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M17"/>
+  <dimension ref="B2:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -42781,262 +43384,262 @@
     <row r="7">
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
+          <t>State Street Energy Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>-0.01092528481292099</v>
+        <v>-0.002242501825469811</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>-0.006856385410228039</v>
+        <v>-0.02290194642310051</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.03825819030297883</v>
+        <v>0.06206307408265466</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>-0.05063084080604807</v>
+        <v>0.09376646323177806</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>-0.009995777597908151</v>
+        <v>0.1315168352190041</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>-0.02956206599473987</v>
+        <v>0.3932006752637141</v>
       </c>
       <c r="J7" s="34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K7" s="102" t="inlineStr">
         <is>
-          <t>Below every average</t>
+          <t>Long-term up, short-term mixed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>State Street Health Care Select Sector SPDR ETF</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>-0.01129417731304438</v>
+        <v>-0.01092528481292099</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>-0.004698634268006097</v>
+        <v>-0.006856385410228039</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>0.03212220982578229</v>
+        <v>0.03825819030297883</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>0.1371950972848903</v>
+        <v>-0.05063084080604807</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>0.08995047533231881</v>
+        <v>-0.009995777597908151</v>
       </c>
       <c r="I8" s="26" t="n">
-        <v>0.1083979227938803</v>
+        <v>-0.02956206599473987</v>
       </c>
       <c r="J8" s="27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K8" s="101" t="inlineStr">
         <is>
-          <t>Long-term up, short-term mixed</t>
+          <t>Below every average</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>State Street Health Care Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D9" s="33" t="n">
-        <v>-0.008198223248004122</v>
+        <v>-0.01129417731304438</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>0.01545214424999508</v>
+        <v>-0.004698634268006097</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.0287977931084924</v>
+        <v>0.03212220982578229</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>0.03640963609155157</v>
+        <v>0.1371950972848903</v>
       </c>
       <c r="H9" s="33" t="n">
-        <v>0.004339614004458925</v>
+        <v>0.08995047533231881</v>
       </c>
       <c r="I9" s="33" t="n">
-        <v>0.1737596765876839</v>
+        <v>0.1083979227938803</v>
       </c>
       <c r="J9" s="34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K9" s="102" t="inlineStr">
         <is>
-          <t>Above every average</t>
+          <t>Long-term up, short-term mixed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>State Street Financial Select Sector SPDR ETF</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>-0.006522438454611534</v>
+        <v>-0.008198223248004122</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>0.01633011927509909</v>
+        <v>0.01545214424999508</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>0.02117150240787624</v>
+        <v>0.0287977931084924</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>0.1289253081984443</v>
+        <v>0.03640963609155157</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>0.1024762108212425</v>
+        <v>0.004339614004458925</v>
       </c>
       <c r="I10" s="26" t="n">
-        <v>0.05678292102169813</v>
+        <v>0.1737596765876839</v>
       </c>
       <c r="J10" s="27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K10" s="101" t="inlineStr">
         <is>
-          <t>Long-term up, short-term mixed</t>
+          <t>Above every average</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>State Street Communication Services Select Sector SPDR ETF</t>
+          <t>State Street Financial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D11" s="33" t="n">
-        <v>-0.01065622006694034</v>
+        <v>-0.006522438454611534</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>0.006595621204560587</v>
+        <v>0.01633011927509909</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.01735002729262392</v>
+        <v>0.02117150240787624</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>-0.04508437978390245</v>
+        <v>0.1289253081984443</v>
       </c>
       <c r="H11" s="33" t="n">
-        <v>-0.04549346729831849</v>
+        <v>0.1024762108212425</v>
       </c>
       <c r="I11" s="33" t="n">
-        <v>-0.05360174560959852</v>
+        <v>0.05678292102169813</v>
       </c>
       <c r="J11" s="34" t="n">
         <v>6</v>
       </c>
       <c r="K11" s="102" t="inlineStr">
         <is>
-          <t>Long-term down, short-term mixed</t>
+          <t>Long-term up, short-term mixed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>State Street Industrial Select Sector SPDR ETF</t>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>-0.008539388474021248</v>
+        <v>-0.01065622006694034</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>-0.005395790163263192</v>
+        <v>0.006595621204560587</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>0.01211366096052813</v>
+        <v>0.01735002729262392</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>0.02876869914962543</v>
+        <v>-0.04508437978390245</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>0.01188458483183075</v>
+        <v>-0.04549346729831849</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0.152656064208105</v>
+        <v>-0.05360174560959852</v>
       </c>
       <c r="J12" s="27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K12" s="101" t="inlineStr">
         <is>
-          <t>Long-term up, short-term mixed</t>
+          <t>Long-term down, short-term mixed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
+          <t>State Street Industrial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D13" s="33" t="n">
-        <v>-0.01379384326320543</v>
+        <v>-0.008539388474021248</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>-0.002812914493998675</v>
+        <v>-0.005395790163263192</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.02609888694330786</v>
+        <v>0.01211366096052813</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>0.007698703346315838</v>
+        <v>0.02876869914962543</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>-0.0425388110886028</v>
+        <v>0.01188458483183075</v>
       </c>
       <c r="I13" s="33" t="n">
-        <v>0.09526263512882416</v>
+        <v>0.152656064208105</v>
       </c>
       <c r="J13" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" s="102" t="inlineStr">
         <is>
@@ -43047,34 +43650,34 @@
     <row r="14">
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>State Street Real Estate Select Sector SPDR ETF</t>
+          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>-0.009536489326250397</v>
+        <v>-0.01379384326320543</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.009316813810625213</v>
+        <v>-0.002812914493998675</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.02828544958565382</v>
+        <v>-0.02609888694330786</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>0.005629362775477986</v>
+        <v>0.007698703346315838</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.02360758088657477</v>
+        <v>-0.0425388110886028</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0.1068154036252389</v>
+        <v>0.09526263512882416</v>
       </c>
       <c r="J14" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="101" t="inlineStr">
         <is>
@@ -43085,43 +43688,81 @@
     <row r="15">
       <c r="B15" s="31" t="inlineStr">
         <is>
+          <t>XLRE</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>State Street Real Estate Select Sector SPDR ETF</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>-0.009536489326250397</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>-0.009316813810625213</v>
+      </c>
+      <c r="F15" s="33" t="n">
+        <v>-0.02828544958565382</v>
+      </c>
+      <c r="G15" s="33" t="n">
+        <v>0.005629362775477986</v>
+      </c>
+      <c r="H15" s="33" t="n">
+        <v>0.02360758088657477</v>
+      </c>
+      <c r="I15" s="33" t="n">
+        <v>0.1068154036252389</v>
+      </c>
+      <c r="J15" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="102" t="inlineStr">
+        <is>
+          <t>Long-term up, short-term mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
           <t>XLU</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>State Street Utilities Select Sector SPDR ETF</t>
         </is>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D16" s="26" t="n">
         <v>-0.007584418043843133</v>
       </c>
-      <c r="E15" s="33" t="n">
+      <c r="E16" s="26" t="n">
         <v>-0.01347955554986158</v>
       </c>
-      <c r="F15" s="33" t="n">
+      <c r="F16" s="26" t="n">
         <v>-0.0385214773572532</v>
       </c>
-      <c r="G15" s="33" t="n">
+      <c r="G16" s="26" t="n">
         <v>-0.03248937325200674</v>
       </c>
-      <c r="H15" s="33" t="n">
+      <c r="H16" s="26" t="n">
         <v>-0.08478168660717855</v>
       </c>
-      <c r="I15" s="33" t="n">
+      <c r="I16" s="26" t="n">
         <v>0.01147813760200567</v>
       </c>
-      <c r="J15" s="34" t="n">
+      <c r="J16" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="102" t="inlineStr">
+      <c r="K16" s="101" t="inlineStr">
         <is>
           <t>Below every average</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="100" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="100" t="inlineStr">
         <is>
           <t>Read it left to right: a sector green in every column is in a real trend. Green today but red over a month is a bounce, not a trend.</t>
         </is>
@@ -43131,7 +43772,7 @@
   <mergeCells count="1">
     <mergeCell ref="B2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D15">
+  <conditionalFormatting sqref="D6:D16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -43143,7 +43784,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E15">
+  <conditionalFormatting sqref="E6:E16">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -43155,7 +43796,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F15">
+  <conditionalFormatting sqref="F6:F16">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -43167,7 +43808,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G15">
+  <conditionalFormatting sqref="G6:G16">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -43179,7 +43820,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H6:H15">
+  <conditionalFormatting sqref="H6:H16">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -43191,7 +43832,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:I15">
+  <conditionalFormatting sqref="I6:I16">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -43203,7 +43844,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J15">
+  <conditionalFormatting sqref="J6:J16">
     <cfRule type="dataBar" priority="7">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -43223,7 +43864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G52"/>
+  <dimension ref="B2:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -43411,7 +44052,7 @@
       </c>
       <c r="D10" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 2.8% at the open</t>
+          <t>Gapped up 2.9% at the open</t>
         </is>
       </c>
       <c r="E10" s="26" t="n">
@@ -43495,7 +44136,7 @@
       </c>
       <c r="D13" s="107" t="inlineStr">
         <is>
-          <t>Gapped up 6.2% at the open</t>
+          <t>Gapped up 6.3% at the open</t>
         </is>
       </c>
       <c r="E13" s="33" t="n">
@@ -43793,21 +44434,21 @@
     <row r="24">
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C24" s="101" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>State Street Energy Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D24" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 3.0% at the open</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>-0.003207597706004428</v>
+        <v>-0.002242501825469811</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>6</v>
@@ -43831,7 +44472,7 @@
       </c>
       <c r="D25" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped up 3.0% at the open</t>
         </is>
       </c>
       <c r="E25" s="33" t="n">
@@ -43849,28 +44490,28 @@
     <row r="26">
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>SOXL</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C26" s="101" t="inlineStr">
         <is>
-          <t>Direxion Daily Semiconductor Bull 3X Shares</t>
-        </is>
-      </c>
-      <c r="D26" s="104" t="inlineStr">
-        <is>
-          <t>MACD crossed up</t>
+          <t>Micron Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="D26" s="106" t="inlineStr">
+        <is>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>0.0553173641684761</v>
+        <v>-0.003207597706004428</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -43885,9 +44526,9 @@
           <t>Direxion Daily Semiconductor Bull 3X Shares</t>
         </is>
       </c>
-      <c r="D27" s="107" t="inlineStr">
-        <is>
-          <t>Gapped up 5.8% at the open</t>
+      <c r="D27" s="105" t="inlineStr">
+        <is>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E27" s="33" t="n">
@@ -43915,7 +44556,7 @@
       </c>
       <c r="D28" s="106" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped up 5.8% at the open</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
@@ -43933,21 +44574,21 @@
     <row r="29">
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>SOXL</t>
         </is>
       </c>
       <c r="C29" s="102" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
-        </is>
-      </c>
-      <c r="D29" s="105" t="inlineStr">
-        <is>
-          <t>MACD crossed up</t>
+          <t>Direxion Daily Semiconductor Bull 3X Shares</t>
+        </is>
+      </c>
+      <c r="D29" s="107" t="inlineStr">
+        <is>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E29" s="33" t="n">
-        <v>0.01652994979538658</v>
+        <v>0.0553173641684761</v>
       </c>
       <c r="F29" s="34" t="n">
         <v>5</v>
@@ -43969,9 +44610,9 @@
           <t>Arm Holdings plc</t>
         </is>
       </c>
-      <c r="D30" s="106" t="inlineStr">
-        <is>
-          <t>Gapped up 1.6% at the open</t>
+      <c r="D30" s="104" t="inlineStr">
+        <is>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E30" s="26" t="n">
@@ -43989,24 +44630,24 @@
     <row r="31">
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C31" s="102" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="D31" s="107" t="inlineStr">
         <is>
-          <t>Reclaimed the 200 DMA</t>
+          <t>Gapped up 1.8% at the open</t>
         </is>
       </c>
       <c r="E31" s="33" t="n">
-        <v>0.04485506445989884</v>
+        <v>0.01652994979538658</v>
       </c>
       <c r="F31" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="30" t="inlineStr">
         <is>
@@ -44027,7 +44668,7 @@
       </c>
       <c r="D32" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 1.7% at the open</t>
+          <t>Reclaimed the 200 DMA</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
@@ -44045,21 +44686,21 @@
     <row r="33">
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C33" s="102" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="D33" s="107" t="inlineStr">
         <is>
-          <t>Gapped up 1.9% at the open</t>
+          <t>Gapped up 1.7% at the open</t>
         </is>
       </c>
       <c r="E33" s="33" t="n">
-        <v>0.04363099011023275</v>
+        <v>0.04485506445989884</v>
       </c>
       <c r="F33" s="34" t="n">
         <v>4</v>
@@ -44073,28 +44714,28 @@
     <row r="34">
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C34" s="101" t="inlineStr">
         <is>
-          <t>IREN Limited</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="D34" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 2.6% at the open</t>
+          <t>Gapped up 1.9% at the open</t>
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>0.02400194300892666</v>
+        <v>0.04363099011023275</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -44111,7 +44752,7 @@
       </c>
       <c r="D35" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped up 2.7% at the open</t>
         </is>
       </c>
       <c r="E35" s="33" t="n">
@@ -44129,21 +44770,21 @@
     <row r="36">
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C36" s="101" t="inlineStr">
         <is>
-          <t>Nebius Group N.V.</t>
+          <t>IREN Limited</t>
         </is>
       </c>
       <c r="D36" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 4.4% at the open</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>0.02126865426791058</v>
+        <v>0.02400194300892666</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>3</v>
@@ -44157,21 +44798,21 @@
     <row r="37">
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C37" s="102" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
-        </is>
-      </c>
-      <c r="D37" s="105" t="inlineStr">
-        <is>
-          <t>MACD crossed up</t>
+          <t>Nebius Group N.V.</t>
+        </is>
+      </c>
+      <c r="D37" s="107" t="inlineStr">
+        <is>
+          <t>Gapped up 4.4% at the open</t>
         </is>
       </c>
       <c r="E37" s="33" t="n">
-        <v>-0.008857794924257756</v>
+        <v>0.02126865426791058</v>
       </c>
       <c r="F37" s="34" t="n">
         <v>3</v>
@@ -44185,21 +44826,21 @@
     <row r="38">
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C38" s="101" t="inlineStr">
         <is>
-          <t>Sandisk Corporation</t>
-        </is>
-      </c>
-      <c r="D38" s="106" t="inlineStr">
-        <is>
-          <t>Gapped up 3.3% at the open</t>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="D38" s="104" t="inlineStr">
+        <is>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>-0.009617401970342554</v>
+        <v>-0.008857794924257756</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>3</v>
@@ -44213,21 +44854,21 @@
     <row r="39">
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C39" s="102" t="inlineStr">
         <is>
-          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
+          <t>Sandisk Corporation</t>
         </is>
       </c>
       <c r="D39" s="107" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Gapped up 3.3% at the open</t>
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>-0.01379384326320543</v>
+        <v>-0.009617401970342554</v>
       </c>
       <c r="F39" s="34" t="n">
         <v>3</v>
@@ -44251,7 +44892,7 @@
       </c>
       <c r="D40" s="106" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E40" s="26" t="n">
@@ -44279,7 +44920,7 @@
       </c>
       <c r="D41" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E41" s="33" t="n">
@@ -44297,21 +44938,21 @@
     <row r="42">
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C42" s="101" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D42" s="106" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>-0.01544486334918349</v>
+        <v>-0.01379384326320543</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>3</v>
@@ -44325,24 +44966,24 @@
     <row r="43">
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C43" s="102" t="inlineStr">
         <is>
-          <t>State Street Real Estate Select Sector SPDR ETF</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D43" s="107" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>-0.009536489326250397</v>
+        <v>-0.01544486334918349</v>
       </c>
       <c r="F43" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="30" t="inlineStr">
         <is>
@@ -44363,7 +45004,7 @@
       </c>
       <c r="D44" s="106" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E44" s="26" t="n">
@@ -44391,7 +45032,7 @@
       </c>
       <c r="D45" s="107" t="inlineStr">
         <is>
-          <t>Lost the 50 DMA</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E45" s="33" t="n">
@@ -44419,7 +45060,7 @@
       </c>
       <c r="D46" s="106" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Lost the 50 DMA</t>
         </is>
       </c>
       <c r="E46" s="26" t="n">
@@ -44437,28 +45078,28 @@
     <row r="47">
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="C47" s="102" t="inlineStr">
         <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
+          <t>State Street Real Estate Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D47" s="107" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E47" s="33" t="n">
-        <v>-0.01092528481292099</v>
+        <v>-0.009536489326250397</v>
       </c>
       <c r="F47" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -44475,7 +45116,7 @@
       </c>
       <c r="D48" s="106" t="inlineStr">
         <is>
-          <t>Lost the 50 DMA</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E48" s="26" t="n">
@@ -44503,7 +45144,7 @@
       </c>
       <c r="D49" s="107" t="inlineStr">
         <is>
-          <t>Lost the 200 DMA</t>
+          <t>Lost the 50 DMA</t>
         </is>
       </c>
       <c r="E49" s="33" t="n">
@@ -44531,7 +45172,7 @@
       </c>
       <c r="D50" s="106" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Lost the 200 DMA</t>
         </is>
       </c>
       <c r="E50" s="26" t="n">
@@ -44549,21 +45190,21 @@
     <row r="51">
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C51" s="102" t="inlineStr">
         <is>
-          <t>CoreWeave, Inc.</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D51" s="107" t="inlineStr">
         <is>
-          <t>8 EMA crossed below 21</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E51" s="33" t="n">
-        <v>-0.01374842694128908</v>
+        <v>-0.01092528481292099</v>
       </c>
       <c r="F51" s="34" t="n">
         <v>1</v>
@@ -44587,7 +45228,7 @@
       </c>
       <c r="D52" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 3.0% at the open</t>
+          <t>8 EMA crossed below 21</t>
         </is>
       </c>
       <c r="E52" s="26" t="n">
@@ -44602,12 +45243,40 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="C53" s="102" t="inlineStr">
+        <is>
+          <t>CoreWeave, Inc.</t>
+        </is>
+      </c>
+      <c r="D53" s="107" t="inlineStr">
+        <is>
+          <t>Gapped up 3.1% at the open</t>
+        </is>
+      </c>
+      <c r="E53" s="33" t="n">
+        <v>-0.01374842694128908</v>
+      </c>
+      <c r="F53" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="30" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B5:G52"/>
+  <autoFilter ref="B5:G53"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E52">
+  <conditionalFormatting sqref="E6:E53">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 28 Aug 2026, 04:22 AM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 28 Aug 2026, 05:21 AM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 28 Aug 2026, 04:22 AM · Yahoo Finance data</t>
+          <t>Built 28 Aug 2026, 05:21 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
+          <t>YouTube Faces Potential Lawsuit from FTC As Regulator Probes Whether It Broke Its Own Policies on Suspended...</t>
+        </is>
+      </c>
+      <c r="AY34" s="79" t="inlineStr">
+        <is>
           <t>FTC Probes YouTube Over Suspended Social Media Accounts, Says Report — GOOGL Stock In Focus</t>
         </is>
       </c>
-      <c r="AY34" s="79" t="inlineStr">
+      <c r="AZ34" s="79" t="inlineStr">
         <is>
           <t>Market Chatter: Alphabet's YouTube Investigated by FTC on Consumer Protection</t>
-        </is>
-      </c>
-      <c r="AZ34" s="79" t="inlineStr">
-        <is>
-          <t>Should SpaceX Join the "Magnificent Seven"? Here's 1 Stock I'd Kick Out to Make Room.</t>
         </is>
       </c>
     </row>
@@ -9592,17 +9592,17 @@
       </c>
       <c r="AX40" s="79" t="inlineStr">
         <is>
+          <t>Is Nebius Group (NasdaqGS:NBIS) Priced For Perfection On AI Growth?</t>
+        </is>
+      </c>
+      <c r="AY40" s="79" t="inlineStr">
+        <is>
           <t>What's Going On With Nebius Stock Thursday</t>
         </is>
       </c>
-      <c r="AY40" s="79" t="inlineStr">
+      <c r="AZ40" s="79" t="inlineStr">
         <is>
           <t>George Soros Is Betting Big on Utility Stocks as AI Power Demand Surges</t>
-        </is>
-      </c>
-      <c r="AZ40" s="79" t="inlineStr">
-        <is>
-          <t>Nebius Group stock surges as funding concerns ease</t>
         </is>
       </c>
     </row>
@@ -9780,17 +9780,17 @@
       </c>
       <c r="AX41" s="90" t="inlineStr">
         <is>
+          <t>The GTA 6 Leak Saga May Be Over — the Money Trail Shows Where It Went</t>
+        </is>
+      </c>
+      <c r="AY41" s="90" t="inlineStr">
+        <is>
           <t>Netflix (NFLX) Stock Falls Amid Market Uptick: What Investors Need to Know</t>
         </is>
       </c>
-      <c r="AY41" s="90" t="inlineStr">
+      <c r="AZ41" s="90" t="inlineStr">
         <is>
           <t>NFLX Has Bounced From This Price Before. Now What?</t>
-        </is>
-      </c>
-      <c r="AZ41" s="90" t="inlineStr">
-        <is>
-          <t>Unusual Options Activity: NFLX, HONA, and MSFT Lead the Way With These 3 Options Strategies</t>
         </is>
       </c>
     </row>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
+          <t>Dow Jones Futures Rise With Fed Chief Warsh Due; Nvidia, These 7 Stocks Are In Buy Zones</t>
+        </is>
+      </c>
+      <c r="AY43" s="90" t="inlineStr">
+        <is>
+          <t>Bill Ackman Just Made His Biggest Portfolio Overhaul in Years, Adding Netflix, Visa, and Mastercard to Pers...</t>
+        </is>
+      </c>
+      <c r="AZ43" s="90" t="inlineStr">
+        <is>
           <t>Amkor, FormFactor, Vishay Intertechnology, Allegro MicroSystems, and Intel Shares Skyrocket, What You Need ...</t>
-        </is>
-      </c>
-      <c r="AY43" s="90" t="inlineStr">
-        <is>
-          <t>Nasdaq Futures Sink While S&amp;P 500, Dow Futures Gain Ahead Of Fed Chief Warsh’s Jackson Hole Speech: PYPL, M...</t>
-        </is>
-      </c>
-      <c r="AZ43" s="90" t="inlineStr">
-        <is>
-          <t>Asian shares mostly gain after upbeat results for Nvidia and others lift US stocks</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 28 Aug 2026, 04:22 AM · Yahoo Finance data</t>
+          <t>Built 28 Aug 2026, 05:21 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 28 Aug 2026, 04:22 AM · Yahoo Finance data</t>
+          <t>Built 28 Aug 2026, 05:21 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 28 Aug 2026, 04:22 AM · Yahoo Finance data</t>
+          <t>Built 28 Aug 2026, 05:21 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 28 Aug 2026, 04:22 AM · Yahoo Finance data</t>
+          <t>Built 28 Aug 2026, 05:21 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'08-25'!$5:$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'08-24'!$A$6:$AZ$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'08-24'!$5:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 29 Aug 2026, 01:05 AM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 29 Aug 2026, 02:50 AM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1376,35 +1376,35 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="L8" s="10" t="n"/>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O8" s="10" t="n"/>
       <c r="P8" s="10" t="n"/>
       <c r="Q8" s="16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R8" s="12" t="n"/>
@@ -1413,14 +1413,14 @@
     <row r="9" ht="15" customHeight="1">
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>of 39 names</t>
+          <t>of 40 names</t>
         </is>
       </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>of 39 names</t>
+          <t>of 40 names</t>
         </is>
       </c>
       <c r="F9" s="8" t="n"/>
@@ -1441,7 +1441,7 @@
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>of 39 names</t>
+          <t>of 40 names</t>
         </is>
       </c>
       <c r="O9" s="10" t="n"/>
@@ -2197,11 +2197,11 @@
       </c>
       <c r="H35" s="24" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>-0.02845037703741871</v>
+        <v>-0.04256684013924827</v>
       </c>
       <c r="J35" s="27" t="n">
         <v>1</v>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="L35" s="28" t="n">
-        <v>41.50443800949344</v>
+        <v>47.15991440223318</v>
       </c>
     </row>
     <row r="36">
@@ -2237,11 +2237,11 @@
       </c>
       <c r="H36" s="31" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="I36" s="33" t="n">
-        <v>-0.02326562725379</v>
+        <v>-0.02845037703741871</v>
       </c>
       <c r="J36" s="34" t="n">
         <v>1</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="L36" s="35" t="n">
-        <v>44.83215501734773</v>
+        <v>41.50443800949344</v>
       </c>
     </row>
     <row r="37">
@@ -2277,11 +2277,11 @@
       </c>
       <c r="H37" s="24" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>-0.01042150902637939</v>
+        <v>-0.02326562725379</v>
       </c>
       <c r="J37" s="27" t="n">
         <v>1</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="L37" s="28" t="n">
-        <v>35.78398855531299</v>
+        <v>44.83215501734773</v>
       </c>
     </row>
     <row r="38">
@@ -2317,11 +2317,11 @@
       </c>
       <c r="H38" s="31" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I38" s="33" t="n">
-        <v>-0.004030459153398613</v>
+        <v>-0.01042150902637939</v>
       </c>
       <c r="J38" s="34" t="n">
         <v>1</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="L38" s="35" t="n">
-        <v>43.30756864961271</v>
+        <v>35.78398855531299</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -2741,22 +2741,22 @@
       </c>
       <c r="H51" s="24" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="I51" s="26" t="n">
-        <v>-0.03588291869363736</v>
+        <v>-0.04256684013924827</v>
       </c>
       <c r="J51" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K51" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Very Weak</t>
         </is>
       </c>
       <c r="L51" s="28" t="n">
-        <v>48.37686691688126</v>
+        <v>47.15991440223318</v>
       </c>
     </row>
     <row r="52">
@@ -2781,22 +2781,22 @@
       </c>
       <c r="H52" s="31" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="I52" s="33" t="n">
-        <v>-0.03392203277851213</v>
+        <v>-0.03588291869363736</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52" s="30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="L52" s="35" t="n">
-        <v>52.59366691435373</v>
+        <v>48.37686691688126</v>
       </c>
     </row>
   </sheetData>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 29 Aug 2026, 01:05 AM · Yahoo Finance data</t>
+          <t>Built 29 Aug 2026, 02:50 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -3132,22 +3132,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>12 of 39</t>
+          <t>12 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>27 of 39</t>
+          <t>28 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.3 / 9</t>
+          <t>4.2 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>16 of 39</t>
+          <t>16 of 40</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
         <v>-0.06332041548914424</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>-0.05517577254916717</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" s="30" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>-0.05943759603113641</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
+          <t>AppLovin vs. Alphabet: Which High-Growth Digital Media Stock Is the Better Investment in 2026?</t>
+        </is>
+      </c>
+      <c r="AY34" s="79" t="inlineStr">
+        <is>
+          <t>Alphabet (GOOGL) Faces FTC Heat, AI Turmoil And UK Play Store Settlement</t>
+        </is>
+      </c>
+      <c r="AZ34" s="79" t="inlineStr">
+        <is>
           <t>Stock Market Today, Aug. 28: Marvell Slides 10% on Softer Fiscal 2028 Guidance and Google Deal Timing</t>
-        </is>
-      </c>
-      <c r="AY34" s="79" t="inlineStr">
-        <is>
-          <t>Sector Update: Tech Stocks Fall Late Afternoon</t>
-        </is>
-      </c>
-      <c r="AZ34" s="79" t="inlineStr">
-        <is>
-          <t>$353M Settlement Barely Dents Alphabet’s (GOOGL) Bigger Bet</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
         <v>-0.1253392097053883</v>
       </c>
       <c r="D35" s="34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E35" s="30" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>-0.07343520222782773</v>
       </c>
       <c r="D38" s="27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
@@ -9425,57 +9425,171 @@
           <t>NBIS</t>
         </is>
       </c>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="23" t="n"/>
-      <c r="I40" s="23" t="n"/>
-      <c r="J40" s="23" t="n"/>
-      <c r="K40" s="23" t="n"/>
-      <c r="L40" s="23" t="n"/>
-      <c r="M40" s="23" t="n"/>
-      <c r="N40" s="69" t="n"/>
-      <c r="O40" s="23" t="n"/>
-      <c r="P40" s="25" t="n"/>
+      <c r="C40" s="26" t="n">
+        <v>-0.04256684013924827</v>
+      </c>
+      <c r="D40" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="23" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+      <c r="P40" s="25" t="inlineStr">
+        <is>
+          <t>Long-term up, short-term mixed</t>
+        </is>
+      </c>
       <c r="Q40" s="25" t="inlineStr">
         <is>
           <t>Nebius Group N.V.</t>
         </is>
       </c>
-      <c r="R40" s="70" t="n"/>
-      <c r="S40" s="71" t="n"/>
-      <c r="T40" s="72" t="n"/>
-      <c r="U40" s="72" t="n"/>
-      <c r="V40" s="72" t="n"/>
-      <c r="W40" s="73" t="n"/>
-      <c r="X40" s="74" t="n"/>
-      <c r="Y40" s="28" t="n"/>
-      <c r="Z40" s="28" t="n"/>
-      <c r="AA40" s="28" t="n"/>
-      <c r="AB40" s="75" t="n"/>
-      <c r="AC40" s="75" t="n"/>
-      <c r="AD40" s="75" t="n"/>
-      <c r="AE40" s="72" t="n"/>
-      <c r="AF40" s="72" t="n"/>
-      <c r="AG40" s="72" t="n"/>
-      <c r="AH40" s="72" t="n"/>
-      <c r="AI40" s="72" t="n"/>
-      <c r="AJ40" s="72" t="n"/>
-      <c r="AK40" s="72" t="n"/>
-      <c r="AL40" s="72" t="n"/>
-      <c r="AM40" s="76" t="n"/>
-      <c r="AN40" s="29" t="n"/>
-      <c r="AO40" s="77" t="n"/>
-      <c r="AP40" s="72" t="n"/>
-      <c r="AQ40" s="72" t="n"/>
-      <c r="AR40" s="29" t="n"/>
-      <c r="AS40" s="78" t="n"/>
-      <c r="AT40" s="26" t="n"/>
-      <c r="AU40" s="26" t="n"/>
-      <c r="AV40" s="26" t="n"/>
-      <c r="AW40" s="26" t="n"/>
+      <c r="R40" s="70" t="n">
+        <v>209.1799926757812</v>
+      </c>
+      <c r="S40" s="71" t="n">
+        <v>-9.300003051757812</v>
+      </c>
+      <c r="T40" s="72" t="n">
+        <v>211.9700012207031</v>
+      </c>
+      <c r="U40" s="72" t="n">
+        <v>214.2799987792969</v>
+      </c>
+      <c r="V40" s="72" t="n">
+        <v>205.4799957275391</v>
+      </c>
+      <c r="W40" s="73" t="n">
+        <v>13064528</v>
+      </c>
+      <c r="X40" s="74" t="n">
+        <v>0.5282577481795031</v>
+      </c>
+      <c r="Y40" s="28" t="n">
+        <v>47.15991440223318</v>
+      </c>
+      <c r="Z40" s="28" t="n">
+        <v>23.38536963898732</v>
+      </c>
+      <c r="AA40" s="28" t="n">
+        <v>10.26259211559968</v>
+      </c>
+      <c r="AB40" s="75" t="n">
+        <v>1.618478299991892</v>
+      </c>
+      <c r="AC40" s="75" t="n">
+        <v>4.122908923924964</v>
+      </c>
+      <c r="AD40" s="75" t="n">
+        <v>-2.504430623933072</v>
+      </c>
+      <c r="AE40" s="72" t="n">
+        <v>219.0393337059973</v>
+      </c>
+      <c r="AF40" s="72" t="n">
+        <v>219.4930636158715</v>
+      </c>
+      <c r="AG40" s="72" t="n">
+        <v>219.3753997802734</v>
+      </c>
+      <c r="AH40" s="72" t="n">
+        <v>206.6682002258301</v>
+      </c>
+      <c r="AI40" s="72" t="n">
+        <v>151.8271253585816</v>
+      </c>
+      <c r="AJ40" s="72" t="n">
+        <v>274.7259626096215</v>
+      </c>
+      <c r="AK40" s="72" t="n">
+        <v>222.9654998779297</v>
+      </c>
+      <c r="AL40" s="72" t="n">
+        <v>171.2050371462378</v>
+      </c>
+      <c r="AM40" s="76" t="n">
+        <v>0.3668336170639773</v>
+      </c>
+      <c r="AN40" s="29" t="n">
+        <v>46.42912267595656</v>
+      </c>
+      <c r="AO40" s="77" t="n">
+        <v>10.08548385902063</v>
+      </c>
+      <c r="AP40" s="72" t="n">
+        <v>299.8599853515625</v>
+      </c>
+      <c r="AQ40" s="72" t="n">
+        <v>63.2599983215332</v>
+      </c>
+      <c r="AR40" s="29" t="n">
+        <v>-30.24077806495789</v>
+      </c>
+      <c r="AS40" s="78" t="n">
+        <v>61.67371189911682</v>
+      </c>
+      <c r="AT40" s="26" t="n">
+        <v>-0.04540689081968652</v>
+      </c>
+      <c r="AU40" s="26" t="n">
+        <v>0.110120473420084</v>
+      </c>
+      <c r="AV40" s="26" t="n">
+        <v>-0.09481156263498935</v>
+      </c>
+      <c r="AW40" s="26" t="n">
+        <v>1.499014253628212</v>
+      </c>
       <c r="AX40" s="79" t="inlineStr">
         <is>
           <t>Zacks Investment Ideas feature highlights: QQQ, NVIDIA, CoreWeave, Nebius, TeraWulf, Cipher and IREN</t>
@@ -9671,12 +9785,12 @@
       </c>
       <c r="AY41" s="90" t="inlineStr">
         <is>
+          <t>Netflix Stock Is Up 25% From Its 2026 Lows. More Gains for NFLX Could Be in Store.</t>
+        </is>
+      </c>
+      <c r="AZ41" s="90" t="inlineStr">
+        <is>
           <t>Netflix Stock Price Prediction: The Road Back to $100</t>
-        </is>
-      </c>
-      <c r="AZ41" s="90" t="inlineStr">
-        <is>
-          <t>Where Will Netflix Stock Be in 5 Years?</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9993,7 @@
         <v>-0.04574959589106331</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
@@ -9957,7 +10071,7 @@
         <v>229.2599945068359</v>
       </c>
       <c r="V43" s="83" t="n">
-        <v>216.8099975585938</v>
+        <v>216.8200073242188</v>
       </c>
       <c r="W43" s="84" t="n">
         <v>194036188</v>
@@ -9972,7 +10086,7 @@
         <v>44.35832261100078</v>
       </c>
       <c r="AA43" s="35" t="n">
-        <v>16.84031568016377</v>
+        <v>16.84184550764452</v>
       </c>
       <c r="AB43" s="86" t="n">
         <v>2.348894281795168</v>
@@ -10014,7 +10128,7 @@
         <v>10.81203662259366</v>
       </c>
       <c r="AO43" s="88" t="n">
-        <v>3.522423226324357</v>
+        <v>3.5220945739461</v>
       </c>
       <c r="AP43" s="83" t="n">
         <v>236.5399932861328</v>
@@ -10042,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
+          <t>Why Elastic Stock Snapped Back Today</t>
+        </is>
+      </c>
+      <c r="AY43" s="90" t="inlineStr">
+        <is>
           <t>This AI Energy Stock Is Up Nearly 2,000% in the Last Two Years. Could It Be Nvidia's Next Big Investment?</t>
         </is>
       </c>
-      <c r="AY43" s="90" t="inlineStr">
+      <c r="AZ43" s="90" t="inlineStr">
         <is>
           <t>Nvidia Drops 3.3% as $315 Target Meets a $108 Billion Test</t>
-        </is>
-      </c>
-      <c r="AZ43" s="90" t="inlineStr">
-        <is>
-          <t>Nvidia Quietly Became Its Own Market Category</t>
         </is>
       </c>
     </row>
@@ -10230,17 +10344,17 @@
       </c>
       <c r="AX44" s="79" t="inlineStr">
         <is>
+          <t>Expert ranks top 5 U.S. tech companies to recruit from</t>
+        </is>
+      </c>
+      <c r="AY44" s="79" t="inlineStr">
+        <is>
           <t>Can PLTR Stock Live Up To Its Multiple?</t>
         </is>
       </c>
-      <c r="AY44" s="79" t="inlineStr">
+      <c r="AZ44" s="79" t="inlineStr">
         <is>
           <t>Palantir’s Pentagon AI surge comes with a question investors can’t ignore</t>
-        </is>
-      </c>
-      <c r="AZ44" s="79" t="inlineStr">
-        <is>
-          <t>NVIDIA (NVDA), Palantir Technologies (PLTR), and the AI Achilles’ Heel: Steve Eisman’s Concentration Warnin...</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10557,7 @@
         <v>-0.04649784460844808</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -11529,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 29 Aug 2026, 01:05 AM · Yahoo Finance data</t>
+          <t>Built 29 Aug 2026, 02:50 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -11554,22 +11668,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>21 of 39</t>
+          <t>22 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>18 of 39</t>
+          <t>18 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>5.3 / 9</t>
+          <t>5.2 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>22 of 39</t>
+          <t>22 of 40</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14777,7 @@
         <v>0.003604958753321119</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
@@ -14839,7 +14953,7 @@
         <v>-0.008857794924257756</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -15015,7 +15129,7 @@
         <v>-0.01544486334918349</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
@@ -15191,7 +15305,7 @@
         <v>0.01865234899615387</v>
       </c>
       <c r="D27" s="34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
@@ -15367,7 +15481,7 @@
         <v>0.01652994979538658</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
@@ -15895,7 +16009,7 @@
         <v>-0.00959387829211289</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -16071,7 +16185,7 @@
         <v>-0.01374842694128908</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -16247,7 +16361,7 @@
         <v>0.01819671921894161</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -16423,7 +16537,7 @@
         <v>-0.004099128939600072</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
@@ -16951,7 +17065,7 @@
         <v>0.01750710664804522</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -17303,7 +17417,7 @@
         <v>-0.003207597706004428</v>
       </c>
       <c r="D39" s="34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E39" s="30" t="inlineStr">
         <is>
@@ -17475,57 +17589,171 @@
           <t>NBIS</t>
         </is>
       </c>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="23" t="n"/>
-      <c r="I40" s="23" t="n"/>
-      <c r="J40" s="23" t="n"/>
-      <c r="K40" s="23" t="n"/>
-      <c r="L40" s="23" t="n"/>
-      <c r="M40" s="23" t="n"/>
-      <c r="N40" s="69" t="n"/>
-      <c r="O40" s="23" t="n"/>
-      <c r="P40" s="25" t="n"/>
+      <c r="C40" s="26" t="n">
+        <v>0.02126865426791058</v>
+      </c>
+      <c r="D40" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" s="23" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="P40" s="25" t="inlineStr">
+        <is>
+          <t>Long-term up, short-term mixed</t>
+        </is>
+      </c>
       <c r="Q40" s="25" t="inlineStr">
         <is>
           <t>Nebius Group N.V.</t>
         </is>
       </c>
-      <c r="R40" s="70" t="n"/>
-      <c r="S40" s="71" t="n"/>
-      <c r="T40" s="72" t="n"/>
-      <c r="U40" s="72" t="n"/>
-      <c r="V40" s="72" t="n"/>
-      <c r="W40" s="73" t="n"/>
-      <c r="X40" s="74" t="n"/>
-      <c r="Y40" s="28" t="n"/>
-      <c r="Z40" s="28" t="n"/>
-      <c r="AA40" s="28" t="n"/>
-      <c r="AB40" s="75" t="n"/>
-      <c r="AC40" s="75" t="n"/>
-      <c r="AD40" s="75" t="n"/>
-      <c r="AE40" s="72" t="n"/>
-      <c r="AF40" s="72" t="n"/>
-      <c r="AG40" s="72" t="n"/>
-      <c r="AH40" s="72" t="n"/>
-      <c r="AI40" s="72" t="n"/>
-      <c r="AJ40" s="72" t="n"/>
-      <c r="AK40" s="72" t="n"/>
-      <c r="AL40" s="72" t="n"/>
-      <c r="AM40" s="76" t="n"/>
-      <c r="AN40" s="29" t="n"/>
-      <c r="AO40" s="77" t="n"/>
-      <c r="AP40" s="72" t="n"/>
-      <c r="AQ40" s="72" t="n"/>
-      <c r="AR40" s="29" t="n"/>
-      <c r="AS40" s="78" t="n"/>
-      <c r="AT40" s="26" t="n"/>
-      <c r="AU40" s="26" t="n"/>
-      <c r="AV40" s="26" t="n"/>
-      <c r="AW40" s="26" t="n"/>
+      <c r="R40" s="70" t="n">
+        <v>218.4799957275391</v>
+      </c>
+      <c r="S40" s="71" t="n">
+        <v>4.550003051757812</v>
+      </c>
+      <c r="T40" s="72" t="n">
+        <v>223.3699951171875</v>
+      </c>
+      <c r="U40" s="72" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="V40" s="72" t="n">
+        <v>215.4100036621094</v>
+      </c>
+      <c r="W40" s="73" t="n">
+        <v>16068200</v>
+      </c>
+      <c r="X40" s="74" t="n">
+        <v>0.6335217880799794</v>
+      </c>
+      <c r="Y40" s="28" t="n">
+        <v>49.72579556929819</v>
+      </c>
+      <c r="Z40" s="28" t="n">
+        <v>36.19525194259934</v>
+      </c>
+      <c r="AA40" s="28" t="n">
+        <v>10.83636146691733</v>
+      </c>
+      <c r="AB40" s="75" t="n">
+        <v>2.893221850498094</v>
+      </c>
+      <c r="AC40" s="75" t="n">
+        <v>4.749016579908232</v>
+      </c>
+      <c r="AD40" s="75" t="n">
+        <v>-1.855794729410138</v>
+      </c>
+      <c r="AE40" s="72" t="n">
+        <v>221.8562882860591</v>
+      </c>
+      <c r="AF40" s="72" t="n">
+        <v>220.5243707098805</v>
+      </c>
+      <c r="AG40" s="72" t="n">
+        <v>220.81</v>
+      </c>
+      <c r="AH40" s="72" t="n">
+        <v>205.750400314331</v>
+      </c>
+      <c r="AI40" s="72" t="n">
+        <v>151.3309753799439</v>
+      </c>
+      <c r="AJ40" s="72" t="n">
+        <v>275.408517849765</v>
+      </c>
+      <c r="AK40" s="72" t="n">
+        <v>222.0270004272461</v>
+      </c>
+      <c r="AL40" s="72" t="n">
+        <v>168.6454830047272</v>
+      </c>
+      <c r="AM40" s="76" t="n">
+        <v>0.4667768464538746</v>
+      </c>
+      <c r="AN40" s="29" t="n">
+        <v>48.08560879514382</v>
+      </c>
+      <c r="AO40" s="77" t="n">
+        <v>9.941251693103386</v>
+      </c>
+      <c r="AP40" s="72" t="n">
+        <v>299.8599853515625</v>
+      </c>
+      <c r="AQ40" s="72" t="n">
+        <v>63.2599983215332</v>
+      </c>
+      <c r="AR40" s="29" t="n">
+        <v>-27.13932955362874</v>
+      </c>
+      <c r="AS40" s="78" t="n">
+        <v>65.60439810434366</v>
+      </c>
+      <c r="AT40" s="26" t="n">
+        <v>-0.007405410377959165</v>
+      </c>
+      <c r="AU40" s="26" t="n">
+        <v>0.474025056862718</v>
+      </c>
+      <c r="AV40" s="26" t="n">
+        <v>-0.0347265208868246</v>
+      </c>
+      <c r="AW40" s="26" t="n">
+        <v>1.610118761702035</v>
+      </c>
       <c r="AX40" s="25" t="n"/>
       <c r="AY40" s="25" t="n"/>
       <c r="AZ40" s="25" t="n"/>
@@ -17541,7 +17769,7 @@
         <v>-0.01988709507475095</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E41" s="30" t="inlineStr">
         <is>
@@ -17717,7 +17945,7 @@
         <v>0.01729109585150757</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -18245,7 +18473,7 @@
         <v>0.006474453644578437</v>
       </c>
       <c r="D45" s="34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
@@ -18421,7 +18649,7 @@
         <v>0.02039888890746222</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -18597,7 +18825,7 @@
         <v>-0.009617401970342554</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
@@ -19351,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 29 Aug 2026, 01:05 AM · Yahoo Finance data</t>
+          <t>Built 29 Aug 2026, 02:50 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19376,22 +19604,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>20 of 39</t>
+          <t>20 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>19 of 39</t>
+          <t>20 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.7 / 9</t>
+          <t>4.6 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>18 of 39</t>
+          <t>18 of 40</t>
         </is>
       </c>
     </row>
@@ -24421,7 +24649,7 @@
         <v>-0.06230744635067853</v>
       </c>
       <c r="D35" s="34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E35" s="30" t="inlineStr">
         <is>
@@ -25297,57 +25525,171 @@
           <t>NBIS</t>
         </is>
       </c>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="23" t="n"/>
-      <c r="I40" s="23" t="n"/>
-      <c r="J40" s="23" t="n"/>
-      <c r="K40" s="23" t="n"/>
-      <c r="L40" s="23" t="n"/>
-      <c r="M40" s="23" t="n"/>
-      <c r="N40" s="69" t="n"/>
-      <c r="O40" s="23" t="n"/>
-      <c r="P40" s="25" t="n"/>
+      <c r="C40" s="26" t="n">
+        <v>-0.03622114925758713</v>
+      </c>
+      <c r="D40" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="23" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+      <c r="P40" s="25" t="inlineStr">
+        <is>
+          <t>Long-term up, short-term mixed</t>
+        </is>
+      </c>
       <c r="Q40" s="25" t="inlineStr">
         <is>
           <t>Nebius Group N.V.</t>
         </is>
       </c>
-      <c r="R40" s="70" t="n"/>
-      <c r="S40" s="71" t="n"/>
-      <c r="T40" s="72" t="n"/>
-      <c r="U40" s="72" t="n"/>
-      <c r="V40" s="72" t="n"/>
-      <c r="W40" s="73" t="n"/>
-      <c r="X40" s="74" t="n"/>
-      <c r="Y40" s="28" t="n"/>
-      <c r="Z40" s="28" t="n"/>
-      <c r="AA40" s="28" t="n"/>
-      <c r="AB40" s="75" t="n"/>
-      <c r="AC40" s="75" t="n"/>
-      <c r="AD40" s="75" t="n"/>
-      <c r="AE40" s="72" t="n"/>
-      <c r="AF40" s="72" t="n"/>
-      <c r="AG40" s="72" t="n"/>
-      <c r="AH40" s="72" t="n"/>
-      <c r="AI40" s="72" t="n"/>
-      <c r="AJ40" s="72" t="n"/>
-      <c r="AK40" s="72" t="n"/>
-      <c r="AL40" s="72" t="n"/>
-      <c r="AM40" s="76" t="n"/>
-      <c r="AN40" s="29" t="n"/>
-      <c r="AO40" s="77" t="n"/>
-      <c r="AP40" s="72" t="n"/>
-      <c r="AQ40" s="72" t="n"/>
-      <c r="AR40" s="29" t="n"/>
-      <c r="AS40" s="78" t="n"/>
-      <c r="AT40" s="26" t="n"/>
-      <c r="AU40" s="26" t="n"/>
-      <c r="AV40" s="26" t="n"/>
-      <c r="AW40" s="26" t="n"/>
+      <c r="R40" s="70" t="n">
+        <v>213.9299926757812</v>
+      </c>
+      <c r="S40" s="71" t="n">
+        <v>-8.040008544921875</v>
+      </c>
+      <c r="T40" s="72" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="U40" s="72" t="n">
+        <v>221.4700012207031</v>
+      </c>
+      <c r="V40" s="72" t="n">
+        <v>213.6000061035156</v>
+      </c>
+      <c r="W40" s="73" t="n">
+        <v>10562800</v>
+      </c>
+      <c r="X40" s="74" t="n">
+        <v>0.3959811816342677</v>
+      </c>
+      <c r="Y40" s="28" t="n">
+        <v>48.45164047982113</v>
+      </c>
+      <c r="Z40" s="28" t="n">
+        <v>33.23286593556736</v>
+      </c>
+      <c r="AA40" s="28" t="n">
+        <v>11.40910369743057</v>
+      </c>
+      <c r="AB40" s="75" t="n">
+        <v>3.531265535503451</v>
+      </c>
+      <c r="AC40" s="75" t="n">
+        <v>5.212965262260766</v>
+      </c>
+      <c r="AD40" s="75" t="n">
+        <v>-1.681699726757315</v>
+      </c>
+      <c r="AE40" s="72" t="n">
+        <v>222.820943302779</v>
+      </c>
+      <c r="AF40" s="72" t="n">
+        <v>220.7288082081147</v>
+      </c>
+      <c r="AG40" s="72" t="n">
+        <v>221.7424002075195</v>
+      </c>
+      <c r="AH40" s="72" t="n">
+        <v>204.6910003662109</v>
+      </c>
+      <c r="AI40" s="72" t="n">
+        <v>150.7949753952026</v>
+      </c>
+      <c r="AJ40" s="72" t="n">
+        <v>275.876030632897</v>
+      </c>
+      <c r="AK40" s="72" t="n">
+        <v>220.5245002746582</v>
+      </c>
+      <c r="AL40" s="72" t="n">
+        <v>165.1729699164194</v>
+      </c>
+      <c r="AM40" s="76" t="n">
+        <v>0.4404306659978788</v>
+      </c>
+      <c r="AN40" s="29" t="n">
+        <v>50.19989188439358</v>
+      </c>
+      <c r="AO40" s="77" t="n">
+        <v>10.4097692066209</v>
+      </c>
+      <c r="AP40" s="72" t="n">
+        <v>299.8599853515625</v>
+      </c>
+      <c r="AQ40" s="72" t="n">
+        <v>63.2599983215332</v>
+      </c>
+      <c r="AR40" s="29" t="n">
+        <v>-28.65670542037645</v>
+      </c>
+      <c r="AS40" s="78" t="n">
+        <v>63.68131978600869</v>
+      </c>
+      <c r="AT40" s="26" t="n">
+        <v>-0.04452881416920695</v>
+      </c>
+      <c r="AU40" s="26" t="n">
+        <v>0.2607106464604538</v>
+      </c>
+      <c r="AV40" s="26" t="n">
+        <v>0.02668329264713387</v>
+      </c>
+      <c r="AW40" s="26" t="n">
+        <v>1.555761161173679</v>
+      </c>
       <c r="AX40" s="25" t="n"/>
       <c r="AY40" s="25" t="n"/>
       <c r="AZ40" s="25" t="n"/>
@@ -27173,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 29 Aug 2026, 01:05 AM · Yahoo Finance data</t>
+          <t>Built 29 Aug 2026, 02:50 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27198,22 +27540,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>26 of 39</t>
+          <t>27 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>12 of 39</t>
+          <t>12 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.7 / 9</t>
+          <t>4.8 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>20 of 39</t>
+          <t>20 of 40</t>
         </is>
       </c>
     </row>
@@ -30307,7 +30649,7 @@
         <v>-0.001417807716048269</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
@@ -30483,7 +30825,7 @@
         <v>0.04910781100335249</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -30659,7 +31001,7 @@
         <v>-0.003853969311243932</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
@@ -30835,7 +31177,7 @@
         <v>0.02919452610931228</v>
       </c>
       <c r="D27" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
@@ -31011,7 +31353,7 @@
         <v>0.01164251107089753</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
@@ -31187,7 +31529,7 @@
         <v>-0.005453089990515525</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" s="30" t="inlineStr">
         <is>
@@ -31363,7 +31705,7 @@
         <v>-0.005630559360753851</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
@@ -31539,7 +31881,7 @@
         <v>0.04585902606191405</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -31715,7 +32057,7 @@
         <v>0.02075363380321549</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -31891,7 +32233,7 @@
         <v>0.04226782117639094</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -32067,7 +32409,7 @@
         <v>-0.003627499385601141</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
@@ -32419,7 +32761,7 @@
         <v>0.002521214936021421</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -32595,7 +32937,7 @@
         <v>0.009029147603226262</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -32771,7 +33113,7 @@
         <v>0.0342494061135572</v>
       </c>
       <c r="D38" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
@@ -32947,7 +33289,7 @@
         <v>0.0247575082199325</v>
       </c>
       <c r="D39" s="34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39" s="30" t="inlineStr">
         <is>
@@ -33119,57 +33461,171 @@
           <t>NBIS</t>
         </is>
       </c>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="23" t="n"/>
-      <c r="I40" s="23" t="n"/>
-      <c r="J40" s="23" t="n"/>
-      <c r="K40" s="23" t="n"/>
-      <c r="L40" s="23" t="n"/>
-      <c r="M40" s="23" t="n"/>
-      <c r="N40" s="69" t="n"/>
-      <c r="O40" s="23" t="n"/>
-      <c r="P40" s="25" t="n"/>
+      <c r="C40" s="26" t="n">
+        <v>0.0524394166542832</v>
+      </c>
+      <c r="D40" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N40" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="O40" s="23" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="P40" s="25" t="inlineStr">
+        <is>
+          <t>Long-term up, short-term mixed</t>
+        </is>
+      </c>
       <c r="Q40" s="25" t="inlineStr">
         <is>
           <t>Nebius Group N.V.</t>
         </is>
       </c>
-      <c r="R40" s="70" t="n"/>
-      <c r="S40" s="71" t="n"/>
-      <c r="T40" s="72" t="n"/>
-      <c r="U40" s="72" t="n"/>
-      <c r="V40" s="72" t="n"/>
-      <c r="W40" s="73" t="n"/>
-      <c r="X40" s="74" t="n"/>
-      <c r="Y40" s="28" t="n"/>
-      <c r="Z40" s="28" t="n"/>
-      <c r="AA40" s="28" t="n"/>
-      <c r="AB40" s="75" t="n"/>
-      <c r="AC40" s="75" t="n"/>
-      <c r="AD40" s="75" t="n"/>
-      <c r="AE40" s="72" t="n"/>
-      <c r="AF40" s="72" t="n"/>
-      <c r="AG40" s="72" t="n"/>
-      <c r="AH40" s="72" t="n"/>
-      <c r="AI40" s="72" t="n"/>
-      <c r="AJ40" s="72" t="n"/>
-      <c r="AK40" s="72" t="n"/>
-      <c r="AL40" s="72" t="n"/>
-      <c r="AM40" s="76" t="n"/>
-      <c r="AN40" s="29" t="n"/>
-      <c r="AO40" s="77" t="n"/>
-      <c r="AP40" s="72" t="n"/>
-      <c r="AQ40" s="72" t="n"/>
-      <c r="AR40" s="29" t="n"/>
-      <c r="AS40" s="78" t="n"/>
-      <c r="AT40" s="26" t="n"/>
-      <c r="AU40" s="26" t="n"/>
-      <c r="AV40" s="26" t="n"/>
-      <c r="AW40" s="26" t="n"/>
+      <c r="R40" s="70" t="n">
+        <v>221.9700012207031</v>
+      </c>
+      <c r="S40" s="71" t="n">
+        <v>11.05999755859375</v>
+      </c>
+      <c r="T40" s="72" t="n">
+        <v>217.9600067138672</v>
+      </c>
+      <c r="U40" s="72" t="n">
+        <v>223.4400024414062</v>
+      </c>
+      <c r="V40" s="72" t="n">
+        <v>213.5500030517578</v>
+      </c>
+      <c r="W40" s="73" t="n">
+        <v>13547900</v>
+      </c>
+      <c r="X40" s="74" t="n">
+        <v>0.4815206041016987</v>
+      </c>
+      <c r="Y40" s="28" t="n">
+        <v>50.5539280953977</v>
+      </c>
+      <c r="Z40" s="28" t="n">
+        <v>41.25690745085653</v>
+      </c>
+      <c r="AA40" s="28" t="n">
+        <v>12.2225942722081</v>
+      </c>
+      <c r="AB40" s="75" t="n">
+        <v>4.757550469118314</v>
+      </c>
+      <c r="AC40" s="75" t="n">
+        <v>5.633390193950094</v>
+      </c>
+      <c r="AD40" s="75" t="n">
+        <v>-0.8758397248317795</v>
+      </c>
+      <c r="AE40" s="72" t="n">
+        <v>225.3612149104927</v>
+      </c>
+      <c r="AF40" s="72" t="n">
+        <v>221.408689761348</v>
+      </c>
+      <c r="AG40" s="72" t="n">
+        <v>222.6652005004883</v>
+      </c>
+      <c r="AH40" s="72" t="n">
+        <v>203.6399004364014</v>
+      </c>
+      <c r="AI40" s="72" t="n">
+        <v>150.2725254440307</v>
+      </c>
+      <c r="AJ40" s="72" t="n">
+        <v>280.9375445928216</v>
+      </c>
+      <c r="AK40" s="72" t="n">
+        <v>217.2390007019043</v>
+      </c>
+      <c r="AL40" s="72" t="n">
+        <v>153.540456810987</v>
+      </c>
+      <c r="AM40" s="76" t="n">
+        <v>0.5371358608047665</v>
+      </c>
+      <c r="AN40" s="29" t="n">
+        <v>58.64374599874407</v>
+      </c>
+      <c r="AO40" s="77" t="n">
+        <v>10.51440292459219</v>
+      </c>
+      <c r="AP40" s="72" t="n">
+        <v>299.8599853515625</v>
+      </c>
+      <c r="AQ40" s="72" t="n">
+        <v>63.2599983215332</v>
+      </c>
+      <c r="AR40" s="29" t="n">
+        <v>-25.97545118917398</v>
+      </c>
+      <c r="AS40" s="78" t="n">
+        <v>67.07946390505357</v>
+      </c>
+      <c r="AT40" s="26" t="n">
+        <v>-0.1065088444840486</v>
+      </c>
+      <c r="AU40" s="26" t="n">
+        <v>0.1814455793694161</v>
+      </c>
+      <c r="AV40" s="26" t="n">
+        <v>0.0668557330833961</v>
+      </c>
+      <c r="AW40" s="26" t="n">
+        <v>1.65181287097651</v>
+      </c>
       <c r="AX40" s="25" t="n"/>
       <c r="AY40" s="25" t="n"/>
       <c r="AZ40" s="25" t="n"/>
@@ -33185,7 +33641,7 @@
         <v>0.02774654619960137</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E41" s="30" t="inlineStr">
         <is>
@@ -33361,7 +33817,7 @@
         <v>0.0391566608262095</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -33537,7 +33993,7 @@
         <v>0.02192060350092895</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
@@ -33713,7 +34169,7 @@
         <v>-0.01796579494613015</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
@@ -33889,7 +34345,7 @@
         <v>0.0128051396891955</v>
       </c>
       <c r="D45" s="34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
@@ -34065,7 +34521,7 @@
         <v>-0.02006436938605949</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -34241,7 +34697,7 @@
         <v>-0.008271254571852515</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
@@ -34417,7 +34873,7 @@
         <v>0.003725426988085312</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
@@ -34995,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 29 Aug 2026, 01:05 AM · Yahoo Finance data</t>
+          <t>Built 29 Aug 2026, 02:50 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35020,22 +35476,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>14 of 39</t>
+          <t>14 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>25 of 39</t>
+          <t>26 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.2 / 9</t>
+          <t>4.1 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>14 of 39</t>
+          <t>14 of 40</t>
         </is>
       </c>
     </row>
@@ -39009,7 +39465,7 @@
         <v>-0.09176988946435649</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E29" s="30" t="inlineStr">
         <is>
@@ -40065,7 +40521,7 @@
         <v>-0.04942692554991801</v>
       </c>
       <c r="D35" s="34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E35" s="30" t="inlineStr">
         <is>
@@ -40769,7 +41225,7 @@
         <v>-0.05828630599876616</v>
       </c>
       <c r="D39" s="34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E39" s="30" t="inlineStr">
         <is>
@@ -40941,57 +41397,171 @@
           <t>NBIS</t>
         </is>
       </c>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="23" t="n"/>
-      <c r="I40" s="23" t="n"/>
-      <c r="J40" s="23" t="n"/>
-      <c r="K40" s="23" t="n"/>
-      <c r="L40" s="23" t="n"/>
-      <c r="M40" s="23" t="n"/>
-      <c r="N40" s="69" t="n"/>
-      <c r="O40" s="23" t="n"/>
-      <c r="P40" s="25" t="n"/>
+      <c r="C40" s="26" t="n">
+        <v>-0.03751198392524591</v>
+      </c>
+      <c r="D40" s="27" t="n">
+        <v>19</v>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="23" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+      <c r="P40" s="25" t="inlineStr">
+        <is>
+          <t>Long-term up, short-term mixed</t>
+        </is>
+      </c>
       <c r="Q40" s="25" t="inlineStr">
         <is>
           <t>Nebius Group N.V.</t>
         </is>
       </c>
-      <c r="R40" s="70" t="n"/>
-      <c r="S40" s="71" t="n"/>
-      <c r="T40" s="72" t="n"/>
-      <c r="U40" s="72" t="n"/>
-      <c r="V40" s="72" t="n"/>
-      <c r="W40" s="73" t="n"/>
-      <c r="X40" s="74" t="n"/>
-      <c r="Y40" s="28" t="n"/>
-      <c r="Z40" s="28" t="n"/>
-      <c r="AA40" s="28" t="n"/>
-      <c r="AB40" s="75" t="n"/>
-      <c r="AC40" s="75" t="n"/>
-      <c r="AD40" s="75" t="n"/>
-      <c r="AE40" s="72" t="n"/>
-      <c r="AF40" s="72" t="n"/>
-      <c r="AG40" s="72" t="n"/>
-      <c r="AH40" s="72" t="n"/>
-      <c r="AI40" s="72" t="n"/>
-      <c r="AJ40" s="72" t="n"/>
-      <c r="AK40" s="72" t="n"/>
-      <c r="AL40" s="72" t="n"/>
-      <c r="AM40" s="76" t="n"/>
-      <c r="AN40" s="29" t="n"/>
-      <c r="AO40" s="77" t="n"/>
-      <c r="AP40" s="72" t="n"/>
-      <c r="AQ40" s="72" t="n"/>
-      <c r="AR40" s="29" t="n"/>
-      <c r="AS40" s="78" t="n"/>
-      <c r="AT40" s="26" t="n"/>
-      <c r="AU40" s="26" t="n"/>
-      <c r="AV40" s="26" t="n"/>
-      <c r="AW40" s="26" t="n"/>
+      <c r="R40" s="70" t="n">
+        <v>210.9100036621094</v>
+      </c>
+      <c r="S40" s="71" t="n">
+        <v>-8.220001220703125</v>
+      </c>
+      <c r="T40" s="72" t="n">
+        <v>211.2019958496094</v>
+      </c>
+      <c r="U40" s="72" t="n">
+        <v>213.75</v>
+      </c>
+      <c r="V40" s="72" t="n">
+        <v>201.8910064697266</v>
+      </c>
+      <c r="W40" s="73" t="n">
+        <v>16882300</v>
+      </c>
+      <c r="X40" s="74" t="n">
+        <v>0.5840942159542905</v>
+      </c>
+      <c r="Y40" s="28" t="n">
+        <v>47.65263001805049</v>
+      </c>
+      <c r="Z40" s="28" t="n">
+        <v>30.21887445956007</v>
+      </c>
+      <c r="AA40" s="28" t="n">
+        <v>13.09866104504544</v>
+      </c>
+      <c r="AB40" s="75" t="n">
+        <v>5.434916180262093</v>
+      </c>
+      <c r="AC40" s="75" t="n">
+        <v>5.852350125158037</v>
+      </c>
+      <c r="AD40" s="75" t="n">
+        <v>-0.4174339448959445</v>
+      </c>
+      <c r="AE40" s="72" t="n">
+        <v>226.3301331075754</v>
+      </c>
+      <c r="AF40" s="72" t="n">
+        <v>221.3525586154125</v>
+      </c>
+      <c r="AG40" s="72" t="n">
+        <v>222.8730004882813</v>
+      </c>
+      <c r="AH40" s="72" t="n">
+        <v>202.4397003936768</v>
+      </c>
+      <c r="AI40" s="72" t="n">
+        <v>149.7476754379273</v>
+      </c>
+      <c r="AJ40" s="72" t="n">
+        <v>281.5419454408989</v>
+      </c>
+      <c r="AK40" s="72" t="n">
+        <v>214.6250007629395</v>
+      </c>
+      <c r="AL40" s="72" t="n">
+        <v>147.7080560849801</v>
+      </c>
+      <c r="AM40" s="76" t="n">
+        <v>0.4722417310091736</v>
+      </c>
+      <c r="AN40" s="29" t="n">
+        <v>62.3570827630388</v>
+      </c>
+      <c r="AO40" s="77" t="n">
+        <v>11.45999131841995</v>
+      </c>
+      <c r="AP40" s="72" t="n">
+        <v>299.8599853515625</v>
+      </c>
+      <c r="AQ40" s="72" t="n">
+        <v>63.2599983215332</v>
+      </c>
+      <c r="AR40" s="29" t="n">
+        <v>-29.6638384695331</v>
+      </c>
+      <c r="AS40" s="78" t="n">
+        <v>62.40490846765617</v>
+      </c>
+      <c r="AT40" s="26" t="n">
+        <v>-0.2155105119063957</v>
+      </c>
+      <c r="AU40" s="26" t="n">
+        <v>0.1232358676206422</v>
+      </c>
+      <c r="AV40" s="26" t="n">
+        <v>-0.01797271748178908</v>
+      </c>
+      <c r="AW40" s="26" t="n">
+        <v>1.519682205942697</v>
+      </c>
       <c r="AX40" s="25" t="n"/>
       <c r="AY40" s="25" t="n"/>
       <c r="AZ40" s="25" t="n"/>
@@ -41887,7 +42457,7 @@
         <v>-0.05911534978045907</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -42063,7 +42633,7 @@
         <v>-0.06450802201163175</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
@@ -42239,7 +42809,7 @@
         <v>-0.03833427136104406</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
@@ -43294,7 +43864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G48"/>
+  <dimension ref="B2:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -44284,21 +44854,21 @@
     <row r="39">
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C39" s="102" t="inlineStr">
         <is>
-          <t>AST SpaceMobile, Inc.</t>
+          <t>Nebius Group N.V.</t>
         </is>
       </c>
       <c r="D39" s="107" t="inlineStr">
         <is>
-          <t>Closed below lower band</t>
+          <t>8 EMA crossed below 21</t>
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>-0.05517577254916717</v>
+        <v>-0.04256684013924827</v>
       </c>
       <c r="F39" s="34" t="n">
         <v>1</v>
@@ -44312,21 +44882,21 @@
     <row r="40">
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C40" s="101" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>Nebius Group N.V.</t>
         </is>
       </c>
       <c r="D40" s="106" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Gapped down 3.0% at the open</t>
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>-0.06332041548914424</v>
+        <v>-0.04256684013924827</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>1</v>
@@ -44340,21 +44910,21 @@
     <row r="41">
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="C41" s="102" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>AST SpaceMobile, Inc.</t>
         </is>
       </c>
       <c r="D41" s="107" t="inlineStr">
         <is>
-          <t>Gapped down 1.7% at the open</t>
+          <t>Closed below lower band</t>
         </is>
       </c>
       <c r="E41" s="33" t="n">
-        <v>-0.06332041548914424</v>
+        <v>-0.05517577254916717</v>
       </c>
       <c r="F41" s="34" t="n">
         <v>1</v>
@@ -44368,12 +44938,12 @@
     <row r="42">
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C42" s="101" t="inlineStr">
         <is>
-          <t>IREN Limited</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="D42" s="106" t="inlineStr">
@@ -44382,7 +44952,7 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>-0.1253392097053883</v>
+        <v>-0.06332041548914424</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>1</v>
@@ -44396,21 +44966,21 @@
     <row r="43">
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C43" s="102" t="inlineStr">
         <is>
-          <t>IREN Limited</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="D43" s="107" t="inlineStr">
         <is>
-          <t>8 EMA crossed below 21</t>
+          <t>Gapped down 1.7% at the open</t>
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>-0.1253392097053883</v>
+        <v>-0.06332041548914424</v>
       </c>
       <c r="F43" s="34" t="n">
         <v>1</v>
@@ -44434,7 +45004,7 @@
       </c>
       <c r="D44" s="106" t="inlineStr">
         <is>
-          <t>Closed below lower band</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E44" s="26" t="n">
@@ -44462,7 +45032,7 @@
       </c>
       <c r="D45" s="107" t="inlineStr">
         <is>
-          <t>Volume 2.0x its 20-day average</t>
+          <t>8 EMA crossed below 21</t>
         </is>
       </c>
       <c r="E45" s="33" t="n">
@@ -44490,7 +45060,7 @@
       </c>
       <c r="D46" s="106" t="inlineStr">
         <is>
-          <t>Gapped down 7.3% at the open</t>
+          <t>Closed below lower band</t>
         </is>
       </c>
       <c r="E46" s="26" t="n">
@@ -44508,24 +45078,24 @@
     <row r="47">
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C47" s="102" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>IREN Limited</t>
         </is>
       </c>
       <c r="D47" s="107" t="inlineStr">
         <is>
-          <t>Lost the 200 DMA</t>
+          <t>Volume 2.0x its 20-day average</t>
         </is>
       </c>
       <c r="E47" s="33" t="n">
-        <v>-0.007401625495918829</v>
+        <v>-0.1253392097053883</v>
       </c>
       <c r="F47" s="34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="30" t="inlineStr">
         <is>
@@ -44536,37 +45106,93 @@
     <row r="48">
       <c r="B48" s="24" t="inlineStr">
         <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="C48" s="101" t="inlineStr">
+        <is>
+          <t>IREN Limited</t>
+        </is>
+      </c>
+      <c r="D48" s="106" t="inlineStr">
+        <is>
+          <t>Gapped down 7.3% at the open</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="n">
+        <v>-0.1253392097053883</v>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="31" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C49" s="102" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="D49" s="107" t="inlineStr">
+        <is>
+          <t>Lost the 200 DMA</t>
+        </is>
+      </c>
+      <c r="E49" s="33" t="n">
+        <v>-0.007401625495918829</v>
+      </c>
+      <c r="F49" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="30" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="24" t="inlineStr">
+        <is>
           <t>CRWV</t>
         </is>
       </c>
-      <c r="C48" s="101" t="inlineStr">
+      <c r="C50" s="101" t="inlineStr">
         <is>
           <t>CoreWeave, Inc.</t>
         </is>
       </c>
-      <c r="D48" s="106" t="inlineStr">
+      <c r="D50" s="106" t="inlineStr">
         <is>
           <t>Gapped down 2.0% at the open</t>
         </is>
       </c>
-      <c r="E48" s="26" t="n">
+      <c r="E50" s="26" t="n">
         <v>-0.02960829037404245</v>
       </c>
-      <c r="F48" s="27" t="n">
+      <c r="F50" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="23" t="inlineStr">
+      <c r="G50" s="23" t="inlineStr">
         <is>
           <t>Very Weak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:G48"/>
+  <autoFilter ref="B5:G50"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E48">
+  <conditionalFormatting sqref="E6:E50">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 29 Aug 2026, 02:50 AM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 29 Aug 2026, 03:09 AM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 29 Aug 2026, 02:50 AM · Yahoo Finance data</t>
+          <t>Built 29 Aug 2026, 03:09 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -8088,17 +8088,17 @@
       </c>
       <c r="AX32" s="79" t="inlineStr">
         <is>
+          <t>Wall Street Sees CoreWeave Anywhere From $74 to $250. Somebody Is Very Wrong</t>
+        </is>
+      </c>
+      <c r="AY32" s="79" t="inlineStr">
+        <is>
           <t>Could CoreWeave (CRWV) Stock Win as AI Demand Continues to Outpace GPU Supply?</t>
         </is>
       </c>
-      <c r="AY32" s="79" t="inlineStr">
+      <c r="AZ32" s="79" t="inlineStr">
         <is>
           <t>CoreWeave (CRWV) Enters Next Generation Engineering AI Workloads</t>
-        </is>
-      </c>
-      <c r="AZ32" s="79" t="inlineStr">
-        <is>
-          <t>Nvidia’s GPU Price Hikes Look Bad for CoreWeave. Truist Says the Opposite May Be True</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 29 Aug 2026, 02:50 AM · Yahoo Finance data</t>
+          <t>Built 29 Aug 2026, 03:09 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 29 Aug 2026, 02:50 AM · Yahoo Finance data</t>
+          <t>Built 29 Aug 2026, 03:09 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 29 Aug 2026, 02:50 AM · Yahoo Finance data</t>
+          <t>Built 29 Aug 2026, 03:09 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 29 Aug 2026, 02:50 AM · Yahoo Finance data</t>
+          <t>Built 29 Aug 2026, 03:09 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 31 Aug 2026, 09:59 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 31 Aug 2026, 11:53 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 31 Aug 2026, 09:59 PM · Yahoo Finance data</t>
+          <t>Built 31 Aug 2026, 11:53 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AZ24" s="79" t="inlineStr">
         <is>
-          <t>What Tim Cook told employees on his last day at Apple</t>
+          <t>Apple To Begin New Chapter With CEO John Ternus</t>
         </is>
       </c>
     </row>
@@ -6772,17 +6772,17 @@
       </c>
       <c r="AX25" s="90" t="inlineStr">
         <is>
+          <t>AMD Expands Global AI Footprint With New Saudi Platform</t>
+        </is>
+      </c>
+      <c r="AY25" s="90" t="inlineStr">
+        <is>
           <t>Not Nvidia, Not AMD. Micron Could Be September's Biggest AI Winner or Loser.</t>
         </is>
       </c>
-      <c r="AY25" s="90" t="inlineStr">
+      <c r="AZ25" s="90" t="inlineStr">
         <is>
           <t>Wall Street Is Looking Here. I’m Looking Somewhere Else</t>
-        </is>
-      </c>
-      <c r="AZ25" s="90" t="inlineStr">
-        <is>
-          <t>AMD Enters a Sovereign AI Showcase, Not a Revenue Windfall</t>
         </is>
       </c>
     </row>
@@ -6960,17 +6960,17 @@
       </c>
       <c r="AX26" s="79" t="inlineStr">
         <is>
+          <t>US regulator, 22 states accuse Amazon of 'manipulating' ad auctions: lawsuit</t>
+        </is>
+      </c>
+      <c r="AY26" s="79" t="inlineStr">
+        <is>
           <t>FTC, 22 states sue Amazon over deceptive advertising practices</t>
         </is>
       </c>
-      <c r="AY26" s="79" t="inlineStr">
-        <is>
-          <t>FTC sues Amazon for manipulating ad auction prices</t>
-        </is>
-      </c>
       <c r="AZ26" s="79" t="inlineStr">
         <is>
-          <t>FTC sues Amazon, alleging it overcharged advertisers</t>
+          <t>FTC, 22 States File Suit Against Amazon Alleging It Secretly Upcharged Companies for Ads</t>
         </is>
       </c>
     </row>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
+          <t>Broadcom's Next Earnings Report on September 2 Could Send the Stock Soaring. Here's Why.</t>
+        </is>
+      </c>
+      <c r="AY30" s="79" t="inlineStr">
+        <is>
           <t>Is Broadcom (AVGO) Stock a Buy Before Its Q3 Earnings?</t>
         </is>
       </c>
-      <c r="AY30" s="79" t="inlineStr">
+      <c r="AZ30" s="79" t="inlineStr">
         <is>
           <t>VGT’s $58 Billion AI Chip Concentration Could Derail Your 2027 Returns</t>
-        </is>
-      </c>
-      <c r="AZ30" s="79" t="inlineStr">
-        <is>
-          <t>Broadcom Has Trailed the S&amp;P 500 This Year. That Shouldn't Last Much Longer.</t>
         </is>
       </c>
     </row>
@@ -8276,17 +8276,17 @@
       </c>
       <c r="AX33" s="90" t="inlineStr">
         <is>
+          <t>Dell Earnings Could Swing the Stock 11% This Week, a $52 Straddle Shows</t>
+        </is>
+      </c>
+      <c r="AY33" s="90" t="inlineStr">
+        <is>
           <t>Buy Dell Technologies Stock Before Q2 Earnings as AI Server Demand Soars?</t>
         </is>
       </c>
-      <c r="AY33" s="90" t="inlineStr">
+      <c r="AZ33" s="90" t="inlineStr">
         <is>
           <t>Back-to-School Success with Dell and Waterdrop Filter: The Simple Habits Helping Kids Learn, Focus and Thri...</t>
-        </is>
-      </c>
-      <c r="AZ33" s="90" t="inlineStr">
-        <is>
-          <t>Dell Stock Flashes Major Last-Minute Signal Before Earnings</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="AZ35" s="90" t="inlineStr">
         <is>
-          <t>Investors Freaked Out Over IREN’s $30 Billion Capex — CEO Explains Why They’re Dead Wrong</t>
+          <t>A $4 Billion Reason to Buy the Recent Dip in IREN Stock Today</t>
         </is>
       </c>
     </row>
@@ -9216,17 +9216,17 @@
       </c>
       <c r="AX38" s="79" t="inlineStr">
         <is>
+          <t>Strategy Just Bought Bitcoin for the First Time in Over Two Months. Here's Why the Timing Matters.</t>
+        </is>
+      </c>
+      <c r="AY38" s="79" t="inlineStr">
+        <is>
           <t>Stock Market Today, Aug. 31: Stocks Edge Lower as Oil Prices Surge Again</t>
         </is>
       </c>
-      <c r="AY38" s="79" t="inlineStr">
+      <c r="AZ38" s="79" t="inlineStr">
         <is>
           <t>Bitcoin is back—and so is Michael Saylor’s Strategy, which made its first buy in two months</t>
-        </is>
-      </c>
-      <c r="AZ38" s="79" t="inlineStr">
-        <is>
-          <t>Bitcoin Bulls Rejoice as Strategy Buys $370 Million Worth of Coins</t>
         </is>
       </c>
     </row>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
-          <t>JPMorgan Built a Version of JEPI Designed to Keep the IRS Waiting</t>
+          <t>Nvidia (NVDA) Invests $3.5 Billion in MediaTek. Is This the Next Leg of Its AI Growth?</t>
         </is>
       </c>
       <c r="AY43" s="90" t="inlineStr">
         <is>
-          <t>S&amp;P500, Dow End Lower On US-Iran Flare-Up, While Dow Records Fifth Straight Month Of Gains — NVDA, META, AO...</t>
+          <t>Nvidia stock flashes unusual signal for investors</t>
         </is>
       </c>
       <c r="AZ43" s="90" t="inlineStr">
         <is>
-          <t>You Could Buy Nvidia for Its 106% Revenue Growth and 75% Gross Margin. But There's an Even Better Reason th...</t>
+          <t>Jensen Huang Told Investors in June to 'Buy at a Discount' During Nvidia's Sell-Off. Nearly Three Months La...</t>
         </is>
       </c>
     </row>
@@ -10908,17 +10908,17 @@
       </c>
       <c r="AX47" s="90" t="inlineStr">
         <is>
+          <t>The Ceiling SanDisk Wrote Into Its Own Contracts</t>
+        </is>
+      </c>
+      <c r="AY47" s="90" t="inlineStr">
+        <is>
           <t>Qualcomm vs. Sandisk: Comparing Gradual Revenue Contraction Against Rapid Revenue Acceleration</t>
         </is>
       </c>
-      <c r="AY47" s="90" t="inlineStr">
+      <c r="AZ47" s="90" t="inlineStr">
         <is>
           <t>Can SanDisk Avoid the Memory Trap That’s Burned Investors Before?</t>
-        </is>
-      </c>
-      <c r="AZ47" s="90" t="inlineStr">
-        <is>
-          <t>Sandisk (SNDK) Backs $31 Billion Japan Flash Memory Expansion Through 2032</t>
         </is>
       </c>
     </row>
@@ -11101,12 +11101,12 @@
       </c>
       <c r="AY48" s="79" t="inlineStr">
         <is>
-          <t>Elon Musk’s SpaceX Blade Plan Knocks Howmet As HWM Suffers Steepest Slide In 16 Months</t>
+          <t>Dow Jones Futures: Trump's Iran Warning Sparks Stock Market Losses; Elon Musk-Led SpaceX, Tesla Rally</t>
         </is>
       </c>
       <c r="AZ48" s="79" t="inlineStr">
         <is>
-          <t>Stock Market Today, Aug. 31: Tesla Stock Surges on Cybercab Event Anticipation</t>
+          <t>Why Tesla (TSLA) Stock Is Up Today</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 31 Aug 2026, 09:59 PM · Yahoo Finance data</t>
+          <t>Built 31 Aug 2026, 11:53 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 31 Aug 2026, 09:59 PM · Yahoo Finance data</t>
+          <t>Built 31 Aug 2026, 11:53 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 31 Aug 2026, 09:59 PM · Yahoo Finance data</t>
+          <t>Built 31 Aug 2026, 11:53 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 31 Aug 2026, 09:59 PM · Yahoo Finance data</t>
+          <t>Built 31 Aug 2026, 11:53 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 31 Aug 2026, 11:53 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 1 Sep 2026, 12:36 AM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 31 Aug 2026, 11:53 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 12:36 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AZ24" s="79" t="inlineStr">
         <is>
-          <t>Apple To Begin New Chapter With CEO John Ternus</t>
+          <t>Apple shares ‘shocking evidence’ against former employee accused of stealing company data for OpenAI</t>
         </is>
       </c>
     </row>
@@ -6772,17 +6772,17 @@
       </c>
       <c r="AX25" s="90" t="inlineStr">
         <is>
+          <t>Here's What September Has Done to AMD Stock Over the Past 10 Years</t>
+        </is>
+      </c>
+      <c r="AY25" s="90" t="inlineStr">
+        <is>
           <t>AMD Expands Global AI Footprint With New Saudi Platform</t>
         </is>
       </c>
-      <c r="AY25" s="90" t="inlineStr">
+      <c r="AZ25" s="90" t="inlineStr">
         <is>
           <t>Not Nvidia, Not AMD. Micron Could Be September's Biggest AI Winner or Loser.</t>
-        </is>
-      </c>
-      <c r="AZ25" s="90" t="inlineStr">
-        <is>
-          <t>Wall Street Is Looking Here. I’m Looking Somewhere Else</t>
         </is>
       </c>
     </row>
@@ -6960,17 +6960,17 @@
       </c>
       <c r="AX26" s="79" t="inlineStr">
         <is>
+          <t>FTC Lawsuit Puts Amazon’s (AMZN) High-Margin Advertising Business in Focus</t>
+        </is>
+      </c>
+      <c r="AY26" s="79" t="inlineStr">
+        <is>
           <t>US regulator, 22 states accuse Amazon of 'manipulating' ad auctions: lawsuit</t>
         </is>
       </c>
-      <c r="AY26" s="79" t="inlineStr">
+      <c r="AZ26" s="79" t="inlineStr">
         <is>
           <t>FTC, 22 states sue Amazon over deceptive advertising practices</t>
-        </is>
-      </c>
-      <c r="AZ26" s="79" t="inlineStr">
-        <is>
-          <t>FTC, 22 States File Suit Against Amazon Alleging It Secretly Upcharged Companies for Ads</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="AZ34" s="79" t="inlineStr">
         <is>
-          <t>Marvell and Google: Misplaced Fear Should Drive Your Purchase Decision</t>
+          <t>Meta just turned teen safety into a competitive advantage</t>
         </is>
       </c>
     </row>
@@ -9780,17 +9780,17 @@
       </c>
       <c r="AX41" s="90" t="inlineStr">
         <is>
+          <t>Duolingo Stock Gets an Upgrade. This Analyst Sees a Netflix-Like Comeback.</t>
+        </is>
+      </c>
+      <c r="AY41" s="90" t="inlineStr">
+        <is>
           <t>Netflix vs. Meta: The Better Media Stock May Surprise You</t>
         </is>
       </c>
-      <c r="AY41" s="90" t="inlineStr">
+      <c r="AZ41" s="90" t="inlineStr">
         <is>
           <t>Jim Cramer Calls Netflix “A Buy, Not a Huge Buy” After Shares Fall 35% in a Year</t>
-        </is>
-      </c>
-      <c r="AZ41" s="90" t="inlineStr">
-        <is>
-          <t>The Bull Case for Netflix Stock Is Stronger Than You Think</t>
         </is>
       </c>
     </row>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
-          <t>Nvidia (NVDA) Invests $3.5 Billion in MediaTek. Is This the Next Leg of Its AI Growth?</t>
+          <t>Dow Jones Futures: Trump's Iran Warning Sparks Stock Market Losses; Elon Musk-Led SpaceX, Tesla Rally</t>
         </is>
       </c>
       <c r="AY43" s="90" t="inlineStr">
         <is>
-          <t>Nvidia stock flashes unusual signal for investors</t>
+          <t>Anthropic Seals $35 Billion Cloud Deal With Nvidia-Backed Lambda</t>
         </is>
       </c>
       <c r="AZ43" s="90" t="inlineStr">
         <is>
-          <t>Jensen Huang Told Investors in June to 'Buy at a Discount' During Nvidia's Sell-Off. Nearly Three Months La...</t>
+          <t>Why Deere Stock Rallied Today</t>
         </is>
       </c>
     </row>
@@ -10913,12 +10913,12 @@
       </c>
       <c r="AY47" s="90" t="inlineStr">
         <is>
-          <t>Qualcomm vs. Sandisk: Comparing Gradual Revenue Contraction Against Rapid Revenue Acceleration</t>
+          <t>Dear Sandisk Stock Fans, Mark Your Calendars for August 31</t>
         </is>
       </c>
       <c r="AZ47" s="90" t="inlineStr">
         <is>
-          <t>Can SanDisk Avoid the Memory Trap That’s Burned Investors Before?</t>
+          <t>A $31 Billion Reason to Buy Sandisk Stock Now</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 31 Aug 2026, 11:53 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 12:36 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 31 Aug 2026, 11:53 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 12:36 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 31 Aug 2026, 11:53 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 12:36 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 31 Aug 2026, 11:53 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 12:36 AM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 1 Sep 2026, 08:01 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 1 Sep 2026, 10:38 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1390,7 +1390,7 @@
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="L8" s="10" t="n"/>
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>0.01282050823267267</v>
+        <v>0.01266412711363518</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>9</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>70.57352081545743</v>
+        <v>70.54063344819689</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>10.60269496630397</v>
+        <v>10.58599543251328</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0.04382851024519119</v>
+        <v>0.04366734144066098</v>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.1018880382801199</v>
+        <v>0.101717904990875</v>
       </c>
     </row>
     <row r="15">
@@ -1556,22 +1556,22 @@
         </is>
       </c>
       <c r="E15" s="33" t="n">
-        <v>0.008169576709516013</v>
+        <v>0.007814393431963884</v>
       </c>
       <c r="F15" s="34" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="35" t="n">
-        <v>36.89377856884519</v>
+        <v>36.70361122725726</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>-4.612432777944464</v>
+        <v>-4.645397415474628</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>-0.01492365662994721</v>
+        <v>-0.01527070404375552</v>
       </c>
       <c r="J15" s="33" t="n">
-        <v>-0.04002249768322719</v>
+        <v>-0.04036070264747738</v>
       </c>
     </row>
     <row r="16">
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>0.006567435323498572</v>
+        <v>0.006626040385240062</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>57.87053016049415</v>
+        <v>57.89146377987348</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>4.290582251469788</v>
+        <v>4.296527670171058</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>-0.02070848173345563</v>
+        <v>-0.02065146474892288</v>
       </c>
       <c r="J16" s="26" t="n">
-        <v>0.05806211692554597</v>
+        <v>0.05812372014606826</v>
       </c>
     </row>
     <row r="17">
@@ -1622,22 +1622,22 @@
         </is>
       </c>
       <c r="E17" s="33" t="n">
-        <v>0.00341248852291498</v>
+        <v>0.003177178540842984</v>
       </c>
       <c r="F17" s="34" t="n">
         <v>4</v>
       </c>
       <c r="G17" s="35" t="n">
-        <v>49.03665155406308</v>
+        <v>48.9318172316673</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>0.4336736283873988</v>
+        <v>0.4105939432430761</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>-0.02492853494856073</v>
+        <v>-0.02515719868514421</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>0.002586638252966456</v>
+        <v>0.002351521940810342</v>
       </c>
     </row>
     <row r="18">
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>-0.001360266888704942</v>
+        <v>-0.001586934796092287</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>38.4836624963454</v>
+        <v>38.37775641324347</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>-1.860311713687723</v>
+        <v>-1.882150008747119</v>
       </c>
       <c r="I18" s="26" t="n">
-        <v>-0.02888010043350975</v>
+        <v>-0.02910052198109947</v>
       </c>
       <c r="J18" s="26" t="n">
-        <v>-0.02501109031612336</v>
+        <v>-0.02523239003869238</v>
       </c>
     </row>
     <row r="19">
@@ -1688,22 +1688,22 @@
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>-0.005113939525445588</v>
+        <v>-0.005203676976662464</v>
       </c>
       <c r="F19" s="34" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="35" t="n">
-        <v>48.92684741256794</v>
+        <v>48.88880247143053</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>0.7206395657435749</v>
+        <v>0.7117376834417488</v>
       </c>
       <c r="I19" s="33" t="n">
-        <v>-0.012731484233094</v>
+        <v>-0.01282053459151322</v>
       </c>
       <c r="J19" s="33" t="n">
-        <v>0.02448264577032044</v>
+        <v>0.02439023874493351</v>
       </c>
     </row>
     <row r="20">
@@ -1721,22 +1721,22 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.008664009841139131</v>
+        <v>-0.008837260953456161</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>47.94944345826823</v>
+        <v>47.84953486775056</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>1.089881841691609</v>
+        <v>1.072571970000347</v>
       </c>
       <c r="I20" s="26" t="n">
-        <v>-0.01886472754092949</v>
+        <v>-0.01903619592195727</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>-0.002962739290310767</v>
+        <v>-0.003136986786774432</v>
       </c>
     </row>
     <row r="21">
@@ -1754,22 +1754,22 @@
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>-0.01138733136760706</v>
+        <v>-0.01176691873304558</v>
       </c>
       <c r="F21" s="34" t="n">
         <v>3</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>47.18285975703026</v>
+        <v>47.03073809436141</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>0.7364266411873821</v>
+        <v>0.698526897038132</v>
       </c>
       <c r="I21" s="33" t="n">
-        <v>-0.02780891428792742</v>
+        <v>-0.02818219642828157</v>
       </c>
       <c r="J21" s="33" t="n">
-        <v>0.03291691131006669</v>
+        <v>0.03252031290351032</v>
       </c>
     </row>
     <row r="22">
@@ -1787,22 +1787,22 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>-0.01364700121631179</v>
+        <v>-0.01370415741653974</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>2</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>30.43426095596647</v>
+        <v>30.42030144051444</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>-4.920527360029014</v>
+        <v>-4.925932167064273</v>
       </c>
       <c r="I22" s="26" t="n">
-        <v>-0.03497203635103874</v>
+        <v>-0.03502795682939075</v>
       </c>
       <c r="J22" s="26" t="n">
-        <v>-0.0394794872625932</v>
+        <v>-0.03953514654767343</v>
       </c>
     </row>
     <row r="23">
@@ -1820,22 +1820,22 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>-0.0151206827035858</v>
+        <v>-0.01533512391609415</v>
       </c>
       <c r="F23" s="34" t="n">
         <v>3</v>
       </c>
       <c r="G23" s="35" t="n">
-        <v>49.61734486031943</v>
+        <v>49.77037300465658</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>0.642600428488338</v>
+        <v>0.5499468890449499</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>0.0106745192251585</v>
+        <v>0.01993888518212716</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>0.03167827231145903</v>
+        <v>0.04727683488781254</v>
       </c>
     </row>
     <row r="24">
@@ -1853,22 +1853,22 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>-0.01723985393232841</v>
+        <v>-0.01715413039557678</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>42.46508287194265</v>
+        <v>42.47758893926807</v>
       </c>
       <c r="H24" s="29" t="n">
-        <v>-1.366474520494299</v>
+        <v>-1.319474978088842</v>
       </c>
       <c r="I24" s="26" t="n">
-        <v>-0.028571387913357</v>
+        <v>-0.03136100268944209</v>
       </c>
       <c r="J24" s="26" t="n">
-        <v>-0.03070803892675766</v>
+        <v>-0.01292100996914591</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C30" s="33" t="n">
-        <v>0.01282050823267267</v>
+        <v>0.01266412711363518</v>
       </c>
       <c r="D30" s="34" t="n">
         <v>9</v>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="F30" s="35" t="n">
-        <v>70.57352081545743</v>
+        <v>70.54063344819689</v>
       </c>
       <c r="H30" s="31" t="inlineStr">
         <is>
@@ -2018,11 +2018,11 @@
     <row r="31">
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
-        <v>-0.02781345403653102</v>
+        <v>0.006626040385240062</v>
       </c>
       <c r="D31" s="27" t="n">
         <v>7</v>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="F31" s="28" t="n">
-        <v>53.35848226617453</v>
+        <v>57.89146377987348</v>
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
@@ -2058,14 +2058,14 @@
     <row r="32">
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>ARKK</t>
         </is>
       </c>
       <c r="C32" s="33" t="n">
-        <v>0.006567435323498572</v>
+        <v>-0.02909895842760113</v>
       </c>
       <c r="D32" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="F32" s="35" t="n">
-        <v>57.87053016049415</v>
+        <v>53.6361945639654</v>
       </c>
       <c r="H32" s="31" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>-0.06246119435907782</v>
+        <v>-0.06099829060707829</v>
       </c>
       <c r="J33" s="27" t="n">
         <v>1</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="L33" s="28" t="n">
-        <v>38.77524195456882</v>
+        <v>38.83029725769804</v>
       </c>
     </row>
     <row r="34">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="H35" s="24" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>-0.03286164112737533</v>
+        <v>-0.01715413039557678</v>
       </c>
       <c r="J35" s="27" t="n">
         <v>1</v>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="L35" s="28" t="n">
-        <v>44.46037894215243</v>
+        <v>42.47758893926807</v>
       </c>
     </row>
     <row r="36">
@@ -2237,11 +2237,11 @@
       </c>
       <c r="H36" s="31" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="I36" s="33" t="n">
-        <v>-0.02490886017883343</v>
+        <v>-0.001586934796092287</v>
       </c>
       <c r="J36" s="34" t="n">
         <v>1</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="L36" s="35" t="n">
-        <v>46.57663423637104</v>
+        <v>38.37775641324347</v>
       </c>
     </row>
     <row r="37">
@@ -2277,11 +2277,11 @@
       </c>
       <c r="H37" s="24" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>-0.01723985393232841</v>
+        <v>0.007814393431963884</v>
       </c>
       <c r="J37" s="27" t="n">
         <v>1</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="L37" s="28" t="n">
-        <v>42.46508287194265</v>
+        <v>36.70361122725726</v>
       </c>
     </row>
     <row r="38">
@@ -2313,26 +2313,26 @@
         </is>
       </c>
       <c r="F38" s="35" t="n">
-        <v>51.00490620595838</v>
+        <v>50.88260328192964</v>
       </c>
       <c r="H38" s="31" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I38" s="33" t="n">
-        <v>-0.01272391734043543</v>
+        <v>-0.06800291463242925</v>
       </c>
       <c r="J38" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="L38" s="35" t="n">
-        <v>46.56322527453447</v>
+        <v>44.88638752206839</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I43" s="26" t="n">
-        <v>-0.06940642471933811</v>
+        <v>-0.06800291463242925</v>
       </c>
       <c r="J43" s="27" t="n">
         <v>2</v>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L43" s="28" t="n">
-        <v>44.75196031726701</v>
+        <v>44.88638752206839</v>
       </c>
     </row>
     <row r="44">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="C44" s="33" t="n">
-        <v>0.01282050823267267</v>
+        <v>0.01266412711363518</v>
       </c>
       <c r="D44" s="34" t="n">
         <v>9</v>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="F44" s="35" t="n">
-        <v>70.57352081545743</v>
+        <v>70.54063344819689</v>
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I44" s="33" t="n">
-        <v>-0.06246119435907782</v>
+        <v>-0.06099829060707829</v>
       </c>
       <c r="J44" s="34" t="n">
         <v>1</v>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="L44" s="35" t="n">
-        <v>38.77524195456882</v>
+        <v>38.83029725769804</v>
       </c>
     </row>
     <row r="45">
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="C45" s="26" t="n">
-        <v>0.008169576709516013</v>
+        <v>0.007814393431963884</v>
       </c>
       <c r="D45" s="27" t="n">
         <v>1</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F45" s="28" t="n">
-        <v>36.89377856884519</v>
+        <v>36.70361122725726</v>
       </c>
       <c r="H45" s="24" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="C46" s="33" t="n">
-        <v>0.006567435323498572</v>
+        <v>0.006626040385240062</v>
       </c>
       <c r="D46" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="F46" s="35" t="n">
-        <v>57.87053016049415</v>
+        <v>57.89146377987348</v>
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="C47" s="26" t="n">
-        <v>0.00341248852291498</v>
+        <v>0.003177178540842984</v>
       </c>
       <c r="D47" s="27" t="n">
         <v>4</v>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="F47" s="28" t="n">
-        <v>49.03665155406308</v>
+        <v>48.9318172316673</v>
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="C48" s="33" t="n">
-        <v>-0.001360266888704942</v>
+        <v>-0.001586934796092287</v>
       </c>
       <c r="D48" s="34" t="n">
         <v>1</v>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="F48" s="35" t="n">
-        <v>38.4836624963454</v>
+        <v>38.37775641324347</v>
       </c>
       <c r="H48" s="31" t="inlineStr">
         <is>
@@ -2668,11 +2668,11 @@
         <v>-0.03286164112737533</v>
       </c>
       <c r="J49" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="L49" s="28" t="n">
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="C51" s="26" t="n">
-        <v>-0.005113939525445588</v>
+        <v>-0.005203676976662464</v>
       </c>
       <c r="D51" s="27" t="n">
         <v>2</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="F51" s="28" t="n">
-        <v>48.92684741256794</v>
+        <v>48.88880247143053</v>
       </c>
       <c r="H51" s="24" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="I52" s="33" t="n">
-        <v>-0.02781345403653102</v>
+        <v>-0.02909895842760113</v>
       </c>
       <c r="J52" s="34" t="n">
         <v>7</v>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L52" s="35" t="n">
-        <v>53.35848226617453</v>
+        <v>53.6361945639654</v>
       </c>
     </row>
   </sheetData>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 1 Sep 2026, 08:01 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 10:38 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>3.1 / 9</t>
+          <t>3.2 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="C7" s="26" t="n">
-        <v>-0.01364700121631179</v>
+        <v>-0.01370415741653974</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>9</v>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="R7" s="70" t="n">
-        <v>172.7400054931641</v>
+        <v>172.7299957275391</v>
       </c>
       <c r="S7" s="71" t="n">
-        <v>-2.389999389648438</v>
+        <v>-2.400009155273438</v>
       </c>
       <c r="T7" s="72" t="n">
         <v>174.3399963378906</v>
@@ -3620,61 +3620,61 @@
         <v>172.1450042724609</v>
       </c>
       <c r="W7" s="73" t="n">
-        <v>8708436</v>
+        <v>9112323</v>
       </c>
       <c r="X7" s="74" t="n">
-        <v>1.445131288118034</v>
+        <v>1.507104205474665</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>30.43426095596647</v>
+        <v>30.42030144051444</v>
       </c>
       <c r="Z7" s="28" t="n">
-        <v>3.897813589868923</v>
+        <v>3.83224027820677</v>
       </c>
       <c r="AA7" s="28" t="n">
         <v>20.96062964897961</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>-1.561366895951664</v>
+        <v>-1.562165395773604</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>-0.3530339179165644</v>
+        <v>-0.3531936178809524</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-1.2083329780351</v>
+        <v>-1.208971777892652</v>
       </c>
       <c r="AE7" s="72" t="n">
-        <v>177.8159079605279</v>
+        <v>177.8136835681667</v>
       </c>
       <c r="AF7" s="72" t="n">
-        <v>180.3794894563351</v>
+        <v>180.3785794776419</v>
       </c>
       <c r="AG7" s="72" t="n">
-        <v>181.6795999145508</v>
+        <v>181.6793997192383</v>
       </c>
       <c r="AH7" s="72" t="n">
-        <v>177.573399810791</v>
+        <v>177.5732997131348</v>
       </c>
       <c r="AI7" s="72" t="n">
-        <v>170.2925498199463</v>
+        <v>170.2924997711182</v>
       </c>
       <c r="AJ7" s="72" t="n">
-        <v>190.3784790304786</v>
+        <v>190.3803877683187</v>
       </c>
       <c r="AK7" s="72" t="n">
-        <v>182.3720001220703</v>
+        <v>182.3714996337891</v>
       </c>
       <c r="AL7" s="72" t="n">
-        <v>174.365521213662</v>
+        <v>174.3626114992594</v>
       </c>
       <c r="AM7" s="76" t="n">
-        <v>-0.1015125212401939</v>
+        <v>-0.1019252450712531</v>
       </c>
       <c r="AN7" s="29" t="n">
-        <v>8.780381750541975</v>
+        <v>8.783047954984051</v>
       </c>
       <c r="AO7" s="77" t="n">
-        <v>1.539207145484353</v>
+        <v>1.53929634309424</v>
       </c>
       <c r="AP7" s="72" t="n">
         <v>188.1900024414062</v>
@@ -3683,22 +3683,22 @@
         <v>147.1399993896484</v>
       </c>
       <c r="AR7" s="29" t="n">
-        <v>-8.209786252089879</v>
+        <v>-8.21510521988581</v>
       </c>
       <c r="AS7" s="78" t="n">
-        <v>62.36298221765759</v>
+        <v>62.33859789395273</v>
       </c>
       <c r="AT7" s="26" t="n">
-        <v>-0.03497203635103874</v>
+        <v>-0.03502795682939075</v>
       </c>
       <c r="AU7" s="26" t="n">
-        <v>-0.0394794872625932</v>
+        <v>-0.03953514654767343</v>
       </c>
       <c r="AV7" s="26" t="n">
-        <v>0.001972225108568315</v>
+        <v>0.001914163820984971</v>
       </c>
       <c r="AW7" s="26" t="n">
-        <v>0.1135895495784749</v>
+        <v>0.1135250204014502</v>
       </c>
       <c r="AX7" s="79" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>0.006567435323498572</v>
+        <v>0.006626040385240062</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>3</v>
@@ -3738,19 +3738,19 @@
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
           <t>Same</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" s="30" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
       <c r="I8" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="N8" s="80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O8" s="30" t="inlineStr">
         <is>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="R8" s="81" t="n">
-        <v>171.6600036621094</v>
+        <v>171.6699981689453</v>
       </c>
       <c r="S8" s="82" t="n">
-        <v>1.120010375976562</v>
+        <v>1.1300048828125</v>
       </c>
       <c r="T8" s="83" t="n">
         <v>172.6199951171875</v>
@@ -3810,61 +3810,61 @@
         <v>171.0299987792969</v>
       </c>
       <c r="W8" s="84" t="n">
-        <v>7216844</v>
+        <v>7813853</v>
       </c>
       <c r="X8" s="85" t="n">
-        <v>0.9028958498821944</v>
+        <v>0.9739500662211876</v>
       </c>
       <c r="Y8" s="35" t="n">
-        <v>57.87053016049415</v>
+        <v>57.89146377987348</v>
       </c>
       <c r="Z8" s="35" t="n">
-        <v>54.0037251884971</v>
+        <v>54.09678386376778</v>
       </c>
       <c r="AA8" s="35" t="n">
         <v>28.18882692755856</v>
       </c>
       <c r="AB8" s="86" t="n">
-        <v>2.495093923330984</v>
+        <v>2.495891205927592</v>
       </c>
       <c r="AC8" s="86" t="n">
-        <v>2.897253065784638</v>
+        <v>2.897412522303959</v>
       </c>
       <c r="AD8" s="86" t="n">
-        <v>-0.4021591424536539</v>
+        <v>-0.4015213163763676</v>
       </c>
       <c r="AE8" s="83" t="n">
-        <v>171.8165448588302</v>
+        <v>171.8187658603493</v>
       </c>
       <c r="AF8" s="83" t="n">
-        <v>169.8331614363222</v>
+        <v>169.8340700278527</v>
       </c>
       <c r="AG8" s="83" t="n">
-        <v>164.5977996826172</v>
+        <v>164.5979995727539</v>
       </c>
       <c r="AH8" s="83" t="n">
-        <v>156.2629000854492</v>
+        <v>156.2630000305176</v>
       </c>
       <c r="AI8" s="83" t="n">
-        <v>155.0679000091553</v>
+        <v>155.0679499816895</v>
       </c>
       <c r="AJ8" s="83" t="n">
-        <v>177.0589340229605</v>
+        <v>177.0598734512753</v>
       </c>
       <c r="AK8" s="83" t="n">
-        <v>170.1434982299805</v>
+        <v>170.1439979553223</v>
       </c>
       <c r="AL8" s="83" t="n">
-        <v>163.2280624370005</v>
+        <v>163.2281224593692</v>
       </c>
       <c r="AM8" s="87" t="n">
-        <v>0.6096464111248293</v>
+        <v>0.6103258882057666</v>
       </c>
       <c r="AN8" s="36" t="n">
-        <v>8.128945113885605</v>
+        <v>8.129438098391322</v>
       </c>
       <c r="AO8" s="88" t="n">
-        <v>1.534428650068773</v>
+        <v>1.534339316709444</v>
       </c>
       <c r="AP8" s="83" t="n">
         <v>176.6000061035156</v>
@@ -3873,22 +3873,22 @@
         <v>133.7299957275391</v>
       </c>
       <c r="AR8" s="36" t="n">
-        <v>-2.797283278977136</v>
+        <v>-2.791623875528382</v>
       </c>
       <c r="AS8" s="89" t="n">
-        <v>88.47678739034194</v>
+        <v>88.50010090659323</v>
       </c>
       <c r="AT8" s="33" t="n">
-        <v>-0.02070848173345563</v>
+        <v>-0.02065146474892288</v>
       </c>
       <c r="AU8" s="33" t="n">
-        <v>0.05806211692554597</v>
+        <v>0.05812372014606826</v>
       </c>
       <c r="AV8" s="33" t="n">
-        <v>0.1725410575050004</v>
+        <v>0.1726093259971631</v>
       </c>
       <c r="AW8" s="33" t="n">
-        <v>0.1089147304778435</v>
+        <v>0.1089792944742189</v>
       </c>
       <c r="AX8" s="90" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="C9" s="26" t="n">
-        <v>-0.008664009841139131</v>
+        <v>-0.008837260953456161</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>7</v>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="R9" s="70" t="n">
-        <v>57.20999908447266</v>
+        <v>57.20000076293945</v>
       </c>
       <c r="S9" s="71" t="n">
-        <v>-0.5</v>
+        <v>-0.5099983215332031</v>
       </c>
       <c r="T9" s="72" t="n">
         <v>57.61000061035156</v>
@@ -4000,61 +4000,61 @@
         <v>57.13000106811523</v>
       </c>
       <c r="W9" s="73" t="n">
-        <v>28912954</v>
+        <v>32355532</v>
       </c>
       <c r="X9" s="74" t="n">
-        <v>1.063510636725195</v>
+        <v>1.182651732142717</v>
       </c>
       <c r="Y9" s="28" t="n">
-        <v>47.94944345826823</v>
+        <v>47.84953486775056</v>
       </c>
       <c r="Z9" s="28" t="n">
-        <v>19.99994913736979</v>
+        <v>19.33339436848959</v>
       </c>
       <c r="AA9" s="28" t="n">
         <v>22.21145834162404</v>
       </c>
       <c r="AB9" s="75" t="n">
-        <v>0.3239031542812967</v>
+        <v>0.3231055673783629</v>
       </c>
       <c r="AC9" s="75" t="n">
-        <v>0.4650610385653203</v>
+        <v>0.4649015211847335</v>
       </c>
       <c r="AD9" s="75" t="n">
-        <v>-0.1411578842840236</v>
+        <v>-0.1417959538063706</v>
       </c>
       <c r="AE9" s="72" t="n">
-        <v>57.74888586370943</v>
+        <v>57.74666401447983</v>
       </c>
       <c r="AF9" s="72" t="n">
-        <v>57.58278824153479</v>
+        <v>57.58187930321359</v>
       </c>
       <c r="AG9" s="72" t="n">
-        <v>56.59320007324219</v>
+        <v>56.59300010681152</v>
       </c>
       <c r="AH9" s="72" t="n">
-        <v>54.2881999206543</v>
+        <v>54.28809993743896</v>
       </c>
       <c r="AI9" s="72" t="n">
-        <v>53.40055002212524</v>
+        <v>53.40050003051758</v>
       </c>
       <c r="AJ9" s="72" t="n">
-        <v>58.52703638067054</v>
+        <v>58.52826772459009</v>
       </c>
       <c r="AK9" s="72" t="n">
-        <v>57.8189998626709</v>
+        <v>57.81849994659424</v>
       </c>
       <c r="AL9" s="72" t="n">
-        <v>57.11096334467126</v>
+        <v>57.10873216859839</v>
       </c>
       <c r="AM9" s="76" t="n">
-        <v>0.0699368869286519</v>
+        <v>0.06429468705861716</v>
       </c>
       <c r="AN9" s="29" t="n">
-        <v>2.449148271956742</v>
+        <v>2.455158050283035</v>
       </c>
       <c r="AO9" s="77" t="n">
-        <v>1.067566997421766</v>
+        <v>1.067753603679739</v>
       </c>
       <c r="AP9" s="72" t="n">
         <v>58.40999984741211</v>
@@ -4063,22 +4063,22 @@
         <v>47.66999816894531</v>
       </c>
       <c r="AR9" s="29" t="n">
-        <v>-2.054444043955295</v>
+        <v>-2.071561526508492</v>
       </c>
       <c r="AS9" s="78" t="n">
-        <v>88.82681028490528</v>
+        <v>88.73371605799049</v>
       </c>
       <c r="AT9" s="26" t="n">
-        <v>-0.01886472754092949</v>
+        <v>-0.01903619592195727</v>
       </c>
       <c r="AU9" s="26" t="n">
-        <v>-0.002962739290310767</v>
+        <v>-0.003136986786774432</v>
       </c>
       <c r="AV9" s="26" t="n">
-        <v>0.1117372736552376</v>
+        <v>0.1115429805788466</v>
       </c>
       <c r="AW9" s="26" t="n">
-        <v>0.04454991065027669</v>
+        <v>0.04436735959222227</v>
       </c>
       <c r="AX9" s="79" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>0.01282050823267267</v>
+        <v>0.01266412711363518</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>1</v>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="R10" s="81" t="n">
-        <v>64.77999877929688</v>
+        <v>64.76999664306641</v>
       </c>
       <c r="S10" s="82" t="n">
-        <v>0.8199996948242188</v>
+        <v>0.80999755859375</v>
       </c>
       <c r="T10" s="83" t="n">
         <v>64.87000274658203</v>
@@ -4190,61 +4190,61 @@
         <v>64.05000305175781</v>
       </c>
       <c r="W10" s="84" t="n">
-        <v>30527530</v>
+        <v>33074746</v>
       </c>
       <c r="X10" s="85" t="n">
-        <v>1.190789115306871</v>
+        <v>1.283770781279166</v>
       </c>
       <c r="Y10" s="35" t="n">
-        <v>70.57352081545743</v>
+        <v>70.54063344819689</v>
       </c>
       <c r="Z10" s="35" t="n">
-        <v>96.39834189889592</v>
+        <v>96.18643211653584</v>
       </c>
       <c r="AA10" s="35" t="n">
         <v>26.648779566004</v>
       </c>
       <c r="AB10" s="86" t="n">
-        <v>1.414788187481598</v>
+        <v>1.413990296272331</v>
       </c>
       <c r="AC10" s="86" t="n">
-        <v>1.385238071042228</v>
+        <v>1.385078492800375</v>
       </c>
       <c r="AD10" s="86" t="n">
-        <v>0.02955011643936989</v>
+        <v>0.02891180347195643</v>
       </c>
       <c r="AE10" s="83" t="n">
-        <v>63.27943865944544</v>
+        <v>63.27721596250534</v>
       </c>
       <c r="AF10" s="83" t="n">
-        <v>61.91246495316741</v>
+        <v>61.91155566805555</v>
       </c>
       <c r="AG10" s="83" t="n">
-        <v>58.57000030517578</v>
+        <v>58.56980026245117</v>
       </c>
       <c r="AH10" s="83" t="n">
-        <v>57.97380012512207</v>
+        <v>57.97370010375977</v>
       </c>
       <c r="AI10" s="83" t="n">
-        <v>54.54409992218017</v>
+        <v>54.54404991149902</v>
       </c>
       <c r="AJ10" s="83" t="n">
-        <v>66.01799848531138</v>
+        <v>66.01609146541506</v>
       </c>
       <c r="AK10" s="83" t="n">
-        <v>61.83100032806396</v>
+        <v>61.83050022125244</v>
       </c>
       <c r="AL10" s="83" t="n">
-        <v>57.64400217081655</v>
+        <v>57.64490897708983</v>
       </c>
       <c r="AM10" s="87" t="n">
-        <v>0.8521614221549619</v>
+        <v>0.8511447069650548</v>
       </c>
       <c r="AN10" s="36" t="n">
-        <v>13.54336218088651</v>
+        <v>13.53892085357555</v>
       </c>
       <c r="AO10" s="88" t="n">
-        <v>1.838843887668827</v>
+        <v>1.839127851973663</v>
       </c>
       <c r="AP10" s="83" t="n">
         <v>64.94999694824219</v>
@@ -4253,36 +4253,36 @@
         <v>42.34999847412109</v>
       </c>
       <c r="AR10" s="36" t="n">
-        <v>-0.2617369929682756</v>
+        <v>-0.277136741544759</v>
       </c>
       <c r="AS10" s="89" t="n">
-        <v>99.24779566184496</v>
+        <v>99.20353841889903</v>
       </c>
       <c r="AT10" s="33" t="n">
-        <v>0.04382851024519119</v>
+        <v>0.04366734144066098</v>
       </c>
       <c r="AU10" s="33" t="n">
-        <v>0.1018880382801199</v>
+        <v>0.101717904990875</v>
       </c>
       <c r="AV10" s="33" t="n">
-        <v>0.1176673533911645</v>
+        <v>0.1174947837502318</v>
       </c>
       <c r="AW10" s="33" t="n">
-        <v>0.4488928674971575</v>
+        <v>0.4486691561029441</v>
       </c>
       <c r="AX10" s="90" t="inlineStr">
         <is>
+          <t>Sector Update: Energy Stocks Rise Late Afternoon</t>
+        </is>
+      </c>
+      <c r="AY10" s="90" t="inlineStr">
+        <is>
           <t>The Energy Sector Stands Out in Today's Selloff</t>
         </is>
       </c>
-      <c r="AY10" s="90" t="inlineStr">
+      <c r="AZ10" s="90" t="inlineStr">
         <is>
           <t>Sector Update: Energy Stocks Advance Premarket Tuesday</t>
-        </is>
-      </c>
-      <c r="AZ10" s="90" t="inlineStr">
-        <is>
-          <t>Buy These 3 Mutual Funds Powered by Energy Sector Gains</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>0.00341248852291498</v>
+        <v>0.003177178540842984</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>4</v>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="R11" s="70" t="n">
-        <v>85.26999664306641</v>
+        <v>85.25</v>
       </c>
       <c r="S11" s="71" t="n">
-        <v>0.2899932861328125</v>
+        <v>0.2699966430664062</v>
       </c>
       <c r="T11" s="72" t="n">
         <v>85.51000213623047</v>
@@ -4380,61 +4380,61 @@
         <v>85.15229797363281</v>
       </c>
       <c r="W11" s="73" t="n">
-        <v>8973359</v>
+        <v>9238776</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>1.019434260024259</v>
+        <v>1.048007388931834</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>49.03665155406308</v>
+        <v>48.9318172316673</v>
       </c>
       <c r="Z11" s="28" t="n">
-        <v>36.41603584493362</v>
+        <v>35.83809803113058</v>
       </c>
       <c r="AA11" s="28" t="n">
         <v>15.76101063524304</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.1881940621548353</v>
+        <v>0.1865988883489678</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.3008637557649711</v>
+        <v>0.3005447210037976</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.1126696936101358</v>
+        <v>-0.1139458326548298</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>85.62186269661281</v>
+        <v>85.61741899815361</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.5447401242465</v>
+        <v>85.5429222476041</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>84.90179992675782</v>
+        <v>84.90139999389649</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.26720008850097</v>
+        <v>84.26700012207031</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.16510021209717</v>
+        <v>83.16500022888184</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>86.98117310424932</v>
+        <v>86.98105359710452</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.57099990844726</v>
+        <v>85.57000007629395</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>84.1608267126452</v>
+        <v>84.15894655548338</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.3932743629375057</v>
+        <v>0.3866095185000036</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.295913796288016</v>
+        <v>3.298009862223858</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.395097012783363</v>
+        <v>1.395424253334772</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -4443,22 +4443,22 @@
         <v>75.16000366210938</v>
       </c>
       <c r="AR11" s="29" t="n">
-        <v>-5.40270998397776</v>
+        <v>-5.424893968004618</v>
       </c>
       <c r="AS11" s="78" t="n">
-        <v>67.48995904164998</v>
+        <v>67.35647006454938</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-0.02492853494856073</v>
+        <v>-0.02515719868514421</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>0.002586638252966456</v>
+        <v>0.002351521940810342</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.03949771927324774</v>
+        <v>0.03925394695380402</v>
       </c>
       <c r="AW11" s="26" t="n">
-        <v>0.09770850036138468</v>
+        <v>0.09745107704794687</v>
       </c>
       <c r="AX11" s="79" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>-0.01723985393232841</v>
+        <v>-0.01715413039557678</v>
       </c>
       <c r="D12" s="34" t="n">
         <v>11</v>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="R12" s="81" t="n">
-        <v>114.5800018310547</v>
+        <v>114.5899963378906</v>
       </c>
       <c r="S12" s="82" t="n">
-        <v>-2.009994506835938</v>
+        <v>-2</v>
       </c>
       <c r="T12" s="83" t="n">
         <v>115.4199981689453</v>
@@ -4570,61 +4570,61 @@
         <v>114.3199996948242</v>
       </c>
       <c r="W12" s="84" t="n">
-        <v>5641885</v>
+        <v>5870171</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>1.118073006879549</v>
+        <v>1.095742612368982</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>42.46508287194265</v>
+        <v>42.47758893926807</v>
       </c>
       <c r="Z12" s="35" t="n">
-        <v>5.349837522173907</v>
+        <v>5.399932861328125</v>
       </c>
       <c r="AA12" s="35" t="n">
-        <v>13.20986958843927</v>
+        <v>13.66989746612066</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.001466741259548598</v>
+        <v>0.02922968977189555</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.3559337053239918</v>
+        <v>0.397090944492239</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.3544669640644432</v>
+        <v>-0.3678612547203434</v>
       </c>
       <c r="AE12" s="83" t="n">
-        <v>116.5466806559738</v>
+        <v>116.5569834786755</v>
       </c>
       <c r="AF12" s="83" t="n">
-        <v>116.8449543518037</v>
+        <v>116.8383915256486</v>
       </c>
       <c r="AG12" s="83" t="n">
-        <v>116.1673997497559</v>
+        <v>116.1221997070313</v>
       </c>
       <c r="AH12" s="83" t="n">
-        <v>116.960299911499</v>
+        <v>116.9156998443603</v>
       </c>
       <c r="AI12" s="83" t="n">
-        <v>116.9664999389648</v>
+        <v>116.9753499221802</v>
       </c>
       <c r="AJ12" s="83" t="n">
-        <v>120.262389170877</v>
+        <v>120.3158424554142</v>
       </c>
       <c r="AK12" s="83" t="n">
-        <v>117.7059989929199</v>
+        <v>117.7604988098145</v>
       </c>
       <c r="AL12" s="83" t="n">
-        <v>115.1496088149629</v>
+        <v>115.2051551642147</v>
       </c>
       <c r="AM12" s="87" t="n">
-        <v>-0.1114084596357261</v>
+        <v>-0.1203671426704948</v>
       </c>
       <c r="AN12" s="36" t="n">
-        <v>4.343687152446342</v>
+        <v>4.339899493338025</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.4366076135326</v>
+        <v>1.453860177755761</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -4633,22 +4633,22 @@
         <v>105.1900024414062</v>
       </c>
       <c r="AR12" s="36" t="n">
-        <v>-8.343332634943579</v>
+        <v>-8.33533766920872</v>
       </c>
       <c r="AS12" s="89" t="n">
-        <v>47.37638513738492</v>
+        <v>47.42681150968475</v>
       </c>
       <c r="AT12" s="33" t="n">
-        <v>-0.028571387913357</v>
+        <v>-0.03136100268944209</v>
       </c>
       <c r="AU12" s="33" t="n">
-        <v>-0.03070803892675766</v>
+        <v>-0.01292100996914591</v>
       </c>
       <c r="AV12" s="33" t="n">
-        <v>-0.0255973688287805</v>
+        <v>-0.03045948074415483</v>
       </c>
       <c r="AW12" s="33" t="n">
-        <v>-0.04044888772235522</v>
+        <v>-0.04036518864749195</v>
       </c>
       <c r="AX12" s="90" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>-0.005113939525445588</v>
+        <v>-0.005203676976662464</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>6</v>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="R13" s="70" t="n">
-        <v>110.8899993896484</v>
+        <v>110.879997253418</v>
       </c>
       <c r="S13" s="71" t="n">
-        <v>-0.5699996948242188</v>
+        <v>-0.5800018310546875</v>
       </c>
       <c r="T13" s="72" t="n">
         <v>110.5599975585938</v>
@@ -4760,61 +4760,61 @@
         <v>110.3099975585938</v>
       </c>
       <c r="W13" s="73" t="n">
-        <v>5041247</v>
+        <v>5136085</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>1.214488389550337</v>
+        <v>1.235923956079946</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>48.92684741256794</v>
+        <v>48.88880247143053</v>
       </c>
       <c r="Z13" s="28" t="n">
-        <v>24.23878033866678</v>
+        <v>23.9951231388846</v>
       </c>
       <c r="AA13" s="28" t="n">
         <v>11.83810281460942</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.3573463785588018</v>
+        <v>0.3565484873495421</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.4111048514841529</v>
+        <v>0.410945273242301</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>-0.05375847292535113</v>
+        <v>-0.05439678589275887</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>111.5752349254688</v>
+        <v>111.5730122285287</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.2679344005431</v>
+        <v>111.2670251154313</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.0965997314453</v>
+        <v>110.0963996887207</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.6251998901367</v>
+        <v>112.6250998687744</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0090000152588</v>
+        <v>114.0089500045776</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.1532481522125</v>
+        <v>113.1535579924061</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.5390003204346</v>
+        <v>111.5385002136231</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.9247524886566</v>
+        <v>109.92344243484</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.298977295180473</v>
+        <v>0.2961364079800141</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>2.894499371772179</v>
+        <v>2.895964668145748</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.452207818008357</v>
+        <v>1.452338817113611</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -4823,22 +4823,22 @@
         <v>105.0299987792969</v>
       </c>
       <c r="AR13" s="29" t="n">
-        <v>-7.902495316734726</v>
+        <v>-7.910802393958982</v>
       </c>
       <c r="AS13" s="78" t="n">
-        <v>38.11382510797765</v>
+        <v>38.04877056338923</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>-0.012731484233094</v>
+        <v>-0.01282053459151322</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>0.02448264577032044</v>
+        <v>0.02439023874493351</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>-0.04082692842993119</v>
+        <v>-0.04091344461518909</v>
       </c>
       <c r="AW13" s="26" t="n">
-        <v>-0.05801904315520434</v>
+        <v>-0.05810400863368514</v>
       </c>
       <c r="AX13" s="79" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C14" s="33" t="n">
-        <v>-0.01138733136760706</v>
+        <v>-0.01176691873304558</v>
       </c>
       <c r="D14" s="34" t="n">
         <v>8</v>
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="R14" s="81" t="n">
-        <v>52.09000015258789</v>
+        <v>52.06999969482422</v>
       </c>
       <c r="S14" s="82" t="n">
-        <v>-0.5999984741210938</v>
+        <v>-0.6199989318847656</v>
       </c>
       <c r="T14" s="83" t="n">
         <v>52.43999862670898</v>
@@ -4950,61 +4950,61 @@
         <v>52.02000045776367</v>
       </c>
       <c r="W14" s="84" t="n">
-        <v>13826995</v>
+        <v>15475252</v>
       </c>
       <c r="X14" s="85" t="n">
-        <v>1.291684835418839</v>
+        <v>1.434616226152872</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>47.18285975703026</v>
+        <v>47.03073809436141</v>
       </c>
       <c r="Z14" s="35" t="n">
-        <v>13.93444032575032</v>
+        <v>13.11474897245443</v>
       </c>
       <c r="AA14" s="35" t="n">
         <v>13.16409788156925</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.3610497115706721</v>
+        <v>0.3594542334584645</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.4360472324549198</v>
+        <v>0.4357281368324782</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>-0.07499752088424766</v>
+        <v>-0.07627390337401374</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>52.84400438003036</v>
+        <v>52.83955983386065</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.56556287166938</v>
+        <v>52.56374464823632</v>
       </c>
       <c r="AG14" s="83" t="n">
-        <v>51.70919982910156</v>
+        <v>51.70879981994629</v>
       </c>
       <c r="AH14" s="83" t="n">
-        <v>51.53899997711181</v>
+        <v>51.53879997253418</v>
       </c>
       <c r="AI14" s="83" t="n">
-        <v>49.88474998474121</v>
+        <v>49.88464998245239</v>
       </c>
       <c r="AJ14" s="83" t="n">
-        <v>53.88268679929241</v>
+        <v>53.88400966406964</v>
       </c>
       <c r="AK14" s="83" t="n">
-        <v>52.74300022125244</v>
+        <v>52.74200019836426</v>
       </c>
       <c r="AL14" s="83" t="n">
-        <v>51.60331364321248</v>
+        <v>51.59999073265887</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.2135176980904763</v>
+        <v>0.2057815527277763</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>4.321660024113435</v>
+        <v>4.330550458497035</v>
       </c>
       <c r="AO14" s="88" t="n">
-        <v>1.532658534383017</v>
+        <v>1.533247239442797</v>
       </c>
       <c r="AP14" s="83" t="n">
         <v>54.18999862670898</v>
@@ -5013,22 +5013,22 @@
         <v>42.03499984741211</v>
       </c>
       <c r="AR14" s="36" t="n">
-        <v>-3.875251019264747</v>
+        <v>-3.912159043384567</v>
       </c>
       <c r="AS14" s="89" t="n">
-        <v>82.72317001217691</v>
+        <v>82.5586248885876</v>
       </c>
       <c r="AT14" s="33" t="n">
-        <v>-0.02780891428792742</v>
+        <v>-0.02818219642828157</v>
       </c>
       <c r="AU14" s="33" t="n">
-        <v>0.03291691131006669</v>
+        <v>0.03252031290351032</v>
       </c>
       <c r="AV14" s="33" t="n">
-        <v>0.02297725894963065</v>
+        <v>0.02258447696842736</v>
       </c>
       <c r="AW14" s="33" t="n">
-        <v>0.1486218722215167</v>
+        <v>0.1481808477796946</v>
       </c>
       <c r="AX14" s="90" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>-0.0151206827035858</v>
+        <v>-0.01533512391609415</v>
       </c>
       <c r="D15" s="27" t="n">
         <v>10</v>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="R15" s="70" t="n">
-        <v>183.6799926757812</v>
+        <v>183.6399993896484</v>
       </c>
       <c r="S15" s="71" t="n">
-        <v>-2.82000732421875</v>
+        <v>-2.860000610351562</v>
       </c>
       <c r="T15" s="72" t="n">
         <v>183.6999969482422</v>
@@ -5140,61 +5140,61 @@
         <v>182.6300048828125</v>
       </c>
       <c r="W15" s="73" t="n">
-        <v>7271912</v>
+        <v>7555296</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>1.181764541421381</v>
+        <v>1.157476727892616</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>49.61734486031943</v>
+        <v>49.77037300465658</v>
       </c>
       <c r="Z15" s="28" t="n">
-        <v>37.58691496141046</v>
+        <v>37.27760862895041</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>12.2697100887299</v>
+        <v>12.89589537992149</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.7725997734760597</v>
+        <v>0.7651872183634794</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>0.9553384405854923</v>
+        <v>0.9757095145848074</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.1827386671094327</v>
+        <v>-0.210522296221328</v>
       </c>
       <c r="AE15" s="72" t="n">
-        <v>184.848975637664</v>
+        <v>184.6874146564698</v>
       </c>
       <c r="AF15" s="72" t="n">
-        <v>184.2694276936688</v>
+        <v>184.1353130869622</v>
       </c>
       <c r="AG15" s="72" t="n">
-        <v>182.5072006225586</v>
+        <v>182.6356005859375</v>
       </c>
       <c r="AH15" s="72" t="n">
-        <v>177.8116007995606</v>
+        <v>177.3750009155274</v>
       </c>
       <c r="AI15" s="72" t="n">
-        <v>159.7170250701904</v>
+        <v>159.5231751251221</v>
       </c>
       <c r="AJ15" s="72" t="n">
-        <v>191.59549774262</v>
+        <v>191.6757393950913</v>
       </c>
       <c r="AK15" s="72" t="n">
-        <v>185.818000793457</v>
+        <v>185.8765007019043</v>
       </c>
       <c r="AL15" s="72" t="n">
-        <v>180.0405038442941</v>
+        <v>180.0772620087173</v>
       </c>
       <c r="AM15" s="76" t="n">
-        <v>0.3149710734173969</v>
+        <v>0.307172852284619</v>
       </c>
       <c r="AN15" s="29" t="n">
-        <v>6.218447001358994</v>
+        <v>6.239883655317391</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.133290058002839</v>
+        <v>2.239163245725061</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -5203,22 +5203,22 @@
         <v>126.6800003051758</v>
       </c>
       <c r="AR15" s="29" t="n">
-        <v>-7.573090814328564</v>
+        <v>-7.593215247978558</v>
       </c>
       <c r="AS15" s="78" t="n">
-        <v>79.11172240395936</v>
+        <v>79.05621471669531</v>
       </c>
       <c r="AT15" s="26" t="n">
-        <v>0.0106745192251585</v>
+        <v>0.01993888518212716</v>
       </c>
       <c r="AU15" s="26" t="n">
-        <v>0.03167827231145903</v>
+        <v>0.04727683488781254</v>
       </c>
       <c r="AV15" s="26" t="n">
-        <v>-0.07330615784227901</v>
+        <v>-0.06191252276912107</v>
       </c>
       <c r="AW15" s="26" t="n">
-        <v>0.2758212899797334</v>
+        <v>0.2755435009556748</v>
       </c>
       <c r="AX15" s="79" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="C16" s="33" t="n">
-        <v>-0.001360266888704942</v>
+        <v>-0.001586934796092287</v>
       </c>
       <c r="D16" s="34" t="n">
         <v>5</v>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="R16" s="81" t="n">
-        <v>44.04999923706055</v>
+        <v>44.04000091552734</v>
       </c>
       <c r="S16" s="82" t="n">
-        <v>-0.06000137329101562</v>
+        <v>-0.06999969482421875</v>
       </c>
       <c r="T16" s="83" t="n">
         <v>44.13000106811523</v>
@@ -5330,61 +5330,61 @@
         <v>43.89500045776367</v>
       </c>
       <c r="W16" s="84" t="n">
-        <v>5988215</v>
+        <v>6730934</v>
       </c>
       <c r="X16" s="85" t="n">
-        <v>1.185688708586722</v>
+        <v>1.323021565580911</v>
       </c>
       <c r="Y16" s="35" t="n">
-        <v>38.4836624963454</v>
+        <v>38.37775641324347</v>
       </c>
       <c r="Z16" s="35" t="n">
-        <v>11.56235843883366</v>
+        <v>10.93746274706149</v>
       </c>
       <c r="AA16" s="35" t="n">
         <v>11.8079868885479</v>
       </c>
       <c r="AB16" s="86" t="n">
-        <v>-0.1394617207556763</v>
+        <v>-0.1402593076586101</v>
       </c>
       <c r="AC16" s="86" t="n">
-        <v>-0.03092550312459823</v>
+        <v>-0.03108502050518498</v>
       </c>
       <c r="AD16" s="86" t="n">
-        <v>-0.1085362176310781</v>
+        <v>-0.1091742871534251</v>
       </c>
       <c r="AE16" s="83" t="n">
-        <v>44.56757791809318</v>
+        <v>44.56535606886358</v>
       </c>
       <c r="AF16" s="83" t="n">
-        <v>44.7985135296971</v>
+        <v>44.79760459137591</v>
       </c>
       <c r="AG16" s="83" t="n">
-        <v>44.88500015258789</v>
+        <v>44.88480018615723</v>
       </c>
       <c r="AH16" s="83" t="n">
-        <v>44.51450019836426</v>
+        <v>44.51440021514892</v>
       </c>
       <c r="AI16" s="83" t="n">
-        <v>43.02115009307861</v>
+        <v>43.02110010147095</v>
       </c>
       <c r="AJ16" s="83" t="n">
-        <v>45.62079517155712</v>
+        <v>45.62214131550767</v>
       </c>
       <c r="AK16" s="83" t="n">
-        <v>44.80200080871582</v>
+        <v>44.80150089263916</v>
       </c>
       <c r="AL16" s="83" t="n">
-        <v>43.98320644587452</v>
+        <v>43.98086046977065</v>
       </c>
       <c r="AM16" s="87" t="n">
-        <v>0.04078728079798557</v>
+        <v>0.0360331054312235</v>
       </c>
       <c r="AN16" s="36" t="n">
-        <v>3.655168733812502</v>
+        <v>3.663450583207303</v>
       </c>
       <c r="AO16" s="88" t="n">
-        <v>1.19581712798806</v>
+        <v>1.196088612181793</v>
       </c>
       <c r="AP16" s="83" t="n">
         <v>46.45500183105469</v>
@@ -5393,22 +5393,22 @@
         <v>39.72499847412109</v>
       </c>
       <c r="AR16" s="36" t="n">
-        <v>-5.177058441931692</v>
+        <v>-5.198581036139238</v>
       </c>
       <c r="AS16" s="89" t="n">
-        <v>64.26446665117361</v>
+        <v>64.1159032552445</v>
       </c>
       <c r="AT16" s="33" t="n">
-        <v>-0.02888010043350975</v>
+        <v>-0.02910052198109947</v>
       </c>
       <c r="AU16" s="33" t="n">
-        <v>-0.02501109031612336</v>
+        <v>-0.02523239003869238</v>
       </c>
       <c r="AV16" s="33" t="n">
-        <v>0.01287646670455334</v>
+        <v>0.01264656739097969</v>
       </c>
       <c r="AW16" s="33" t="n">
-        <v>0.09169766797667878</v>
+        <v>0.09144987809040117</v>
       </c>
       <c r="AX16" s="90" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>0.008169576709516013</v>
+        <v>0.007814393431963884</v>
       </c>
       <c r="D17" s="27" t="n">
         <v>2</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="R17" s="70" t="n">
-        <v>42.57500076293945</v>
+        <v>42.56000137329102</v>
       </c>
       <c r="S17" s="71" t="n">
-        <v>0.345001220703125</v>
+        <v>0.3300018310546875</v>
       </c>
       <c r="T17" s="72" t="n">
         <v>42.29999923706055</v>
@@ -5520,61 +5520,61 @@
         <v>42.09000015258789</v>
       </c>
       <c r="W17" s="73" t="n">
-        <v>28481037</v>
+        <v>30607780</v>
       </c>
       <c r="X17" s="74" t="n">
-        <v>1.398396390862473</v>
+        <v>1.495012226677681</v>
       </c>
       <c r="Y17" s="28" t="n">
-        <v>36.89377856884519</v>
+        <v>36.70361122725726</v>
       </c>
       <c r="Z17" s="28" t="n">
-        <v>25.62723720299379</v>
+        <v>25.08962484720707</v>
       </c>
       <c r="AA17" s="28" t="n">
         <v>15.44436840277224</v>
       </c>
       <c r="AB17" s="75" t="n">
-        <v>-0.5125470726422492</v>
+        <v>-0.5137436051498128</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.4246063314813189</v>
+        <v>-0.4248456379828316</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.08794074116093031</v>
+        <v>-0.08889796716698117</v>
       </c>
       <c r="AE17" s="72" t="n">
-        <v>43.04404548751325</v>
+        <v>43.0407122898136</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>43.60815328138903</v>
+        <v>43.6067897005119</v>
       </c>
       <c r="AG17" s="72" t="n">
-        <v>44.63370018005371</v>
+        <v>44.63340019226074</v>
       </c>
       <c r="AH17" s="72" t="n">
-        <v>44.89364990234375</v>
+        <v>44.89349990844727</v>
       </c>
       <c r="AI17" s="72" t="n">
-        <v>44.69784996032715</v>
+        <v>44.6977749633789</v>
       </c>
       <c r="AJ17" s="72" t="n">
-        <v>44.61319673958235</v>
+        <v>44.61508083450245</v>
       </c>
       <c r="AK17" s="72" t="n">
-        <v>43.52475051879883</v>
+        <v>43.5240005493164</v>
       </c>
       <c r="AL17" s="72" t="n">
-        <v>42.4363042980153</v>
+        <v>42.43292026413036</v>
       </c>
       <c r="AM17" s="76" t="n">
-        <v>0.06371305365198042</v>
+        <v>0.05823636944323803</v>
       </c>
       <c r="AN17" s="29" t="n">
-        <v>5.001504697027095</v>
+        <v>5.0136948415381</v>
       </c>
       <c r="AO17" s="77" t="n">
-        <v>1.589458094040938</v>
+        <v>1.59001826557555</v>
       </c>
       <c r="AP17" s="72" t="n">
         <v>47.79999923706055</v>
@@ -5583,22 +5583,22 @@
         <v>41.15000152587891</v>
       </c>
       <c r="AR17" s="29" t="n">
-        <v>-10.93095932535083</v>
+        <v>-10.96233880210363</v>
       </c>
       <c r="AS17" s="78" t="n">
-        <v>21.42856733115083</v>
+        <v>21.2030125219632</v>
       </c>
       <c r="AT17" s="26" t="n">
-        <v>-0.01492365662994721</v>
+        <v>-0.01527070404375552</v>
       </c>
       <c r="AU17" s="26" t="n">
-        <v>-0.04002249768322719</v>
+        <v>-0.04036070264747738</v>
       </c>
       <c r="AV17" s="26" t="n">
-        <v>-0.01218092180436781</v>
+        <v>-0.01252893549762679</v>
       </c>
       <c r="AW17" s="26" t="n">
-        <v>-0.002693789352749776</v>
+        <v>-0.00304514541109957</v>
       </c>
       <c r="AX17" s="79" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="C19" s="26" t="n">
-        <v>-0.006948721953806136</v>
+        <v>-0.006870423805438008</v>
       </c>
       <c r="D19" s="27" t="n">
         <v>1</v>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="N19" s="69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" s="23" t="inlineStr">
         <is>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="R19" s="70" t="n">
-        <v>761.719970703125</v>
+        <v>761.780029296875</v>
       </c>
       <c r="S19" s="71" t="n">
-        <v>-5.33001708984375</v>
+        <v>-5.26995849609375</v>
       </c>
       <c r="T19" s="72" t="n">
         <v>762.010009765625</v>
@@ -5729,61 +5729,61 @@
         <v>759.47998046875</v>
       </c>
       <c r="W19" s="73" t="n">
-        <v>35097486</v>
+        <v>40112421</v>
       </c>
       <c r="X19" s="74" t="n">
-        <v>0.9486180244123822</v>
+        <v>1.07686401188567</v>
       </c>
       <c r="Y19" s="28" t="n">
-        <v>48.52095844592502</v>
+        <v>48.57682306948648</v>
       </c>
       <c r="Z19" s="28" t="n">
-        <v>11.26188328147344</v>
+        <v>11.56383677327098</v>
       </c>
       <c r="AA19" s="28" t="n">
         <v>14.23855992927188</v>
       </c>
       <c r="AB19" s="75" t="n">
-        <v>3.052525888640275</v>
+        <v>3.057316887571801</v>
       </c>
       <c r="AC19" s="75" t="n">
-        <v>4.452610319700631</v>
+        <v>4.453568519486936</v>
       </c>
       <c r="AD19" s="75" t="n">
-        <v>-1.400084431060356</v>
+        <v>-1.396251631915135</v>
       </c>
       <c r="AE19" s="72" t="n">
-        <v>766.4133217097304</v>
+        <v>766.4266680638971</v>
       </c>
       <c r="AF19" s="72" t="n">
-        <v>764.7900775662763</v>
+        <v>764.7955374384353</v>
       </c>
       <c r="AG19" s="72" t="n">
-        <v>754.7080004882813</v>
+        <v>754.7092016601563</v>
       </c>
       <c r="AH19" s="72" t="n">
-        <v>742.8282006835938</v>
+        <v>742.8288012695313</v>
       </c>
       <c r="AI19" s="72" t="n">
-        <v>710.6582000732421</v>
+        <v>710.6585003662109</v>
       </c>
       <c r="AJ19" s="72" t="n">
-        <v>777.6814909098458</v>
+        <v>777.673922270429</v>
       </c>
       <c r="AK19" s="72" t="n">
-        <v>769.2044921875</v>
+        <v>769.2074951171875</v>
       </c>
       <c r="AL19" s="72" t="n">
-        <v>760.7274934651542</v>
+        <v>760.741067963946</v>
       </c>
       <c r="AM19" s="76" t="n">
-        <v>0.05853942359071935</v>
+        <v>0.061357719975849</v>
       </c>
       <c r="AN19" s="29" t="n">
-        <v>2.204094960038132</v>
+        <v>2.201337664280473</v>
       </c>
       <c r="AO19" s="77" t="n">
-        <v>0.8269706371284882</v>
+        <v>0.8269054389195192</v>
       </c>
       <c r="AP19" s="72" t="n">
         <v>779.3699951171875</v>
@@ -5792,36 +5792,36 @@
         <v>629.280029296875</v>
       </c>
       <c r="AR19" s="29" t="n">
-        <v>-2.264652799651157</v>
+        <v>-2.256946755779021</v>
       </c>
       <c r="AS19" s="78" t="n">
-        <v>88.24037015559516</v>
+        <v>88.28038521817562</v>
       </c>
       <c r="AT19" s="26" t="n">
-        <v>-0.00547062003149501</v>
+        <v>-0.005392205340661982</v>
       </c>
       <c r="AU19" s="26" t="n">
-        <v>0.005345319049611774</v>
+        <v>0.005424586534275022</v>
       </c>
       <c r="AV19" s="26" t="n">
-        <v>0.002830500622951204</v>
+        <v>0.002909569824171454</v>
       </c>
       <c r="AW19" s="26" t="n">
-        <v>0.1170225096680917</v>
+        <v>0.1171105824555965</v>
       </c>
       <c r="AX19" s="79" t="inlineStr">
         <is>
-          <t>Target Stock Is Up 66% in 2026: What Will It Take to Break Through $200?</t>
+          <t>These ETFs Generate the Most Revenue</t>
         </is>
       </c>
       <c r="AY19" s="79" t="inlineStr">
         <is>
-          <t>Nio Falls 4% as Memory Chip Costs and Revenue Miss Overshadow Doubled Vehicle Margin, XPeng Holds Steady</t>
+          <t>SPYI’s Monthly Check Hides the Real Cost: Part of That Payout Is Your Own Capital, and It Quietly Shrinks Y...</t>
         </is>
       </c>
       <c r="AZ19" s="79" t="inlineStr">
         <is>
-          <t>Novavax Jumps 6% on Matrix-M Oncology Speculation: Is the Royalty Model the Real Story?</t>
+          <t>Most Investors Fear Bear Markets. My 7-Year Track Record Shows They Should Welcome Them.</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G20" s="30" t="inlineStr">
@@ -5884,11 +5884,11 @@
         </is>
       </c>
       <c r="N20" s="80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="P20" s="32" t="inlineStr">
@@ -5917,10 +5917,10 @@
         <v>704.6599731445312</v>
       </c>
       <c r="W20" s="84" t="n">
-        <v>31446012</v>
+        <v>34409539</v>
       </c>
       <c r="X20" s="85" t="n">
-        <v>1.008052020003596</v>
+        <v>1.097837838433686</v>
       </c>
       <c r="Y20" s="35" t="n">
         <v>46.56322527453447</v>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="AZ20" s="90" t="inlineStr">
         <is>
-          <t>Forget Diversification — Investors Are Betting Everything on Tech ETFs (And the Numbers Are Jaw-Dropping)</t>
+          <t>Oracle Falls 4% as Bond Selloff Tests Its Debt-Funded AI Buildout, Nebius Slips</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>-0.01122712167930684</v>
+        <v>-0.01143124361340264</v>
       </c>
       <c r="D21" s="27" t="n">
         <v>2</v>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="R21" s="70" t="n">
-        <v>290.6300048828125</v>
+        <v>290.5700073242188</v>
       </c>
       <c r="S21" s="71" t="n">
-        <v>-3.29998779296875</v>
+        <v>-3.3599853515625</v>
       </c>
       <c r="T21" s="72" t="n">
         <v>291.9800109863281</v>
@@ -6105,61 +6105,61 @@
         <v>289.9750061035156</v>
       </c>
       <c r="W21" s="73" t="n">
-        <v>20943590</v>
+        <v>22700723</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>1.261546191134435</v>
+        <v>1.353301231328082</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>38.0004733461348</v>
+        <v>38.37419555412637</v>
       </c>
       <c r="Z21" s="28" t="n">
-        <v>4.307789264948207</v>
+        <v>3.913197935922061</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>18.49162150024266</v>
+        <v>17.69275325367105</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>-0.4283309241486108</v>
+        <v>-0.1813943103584279</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>0.8159764612656106</v>
+        <v>1.027797981449304</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-1.244307385414221</v>
+        <v>-1.209192291807732</v>
       </c>
       <c r="AE21" s="72" t="n">
-        <v>296.146785030254</v>
+        <v>296.6617753509157</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>297.6666730996729</v>
+        <v>297.9144728791328</v>
       </c>
       <c r="AG21" s="72" t="n">
-        <v>297.1294006347656</v>
+        <v>297.1768005371094</v>
       </c>
       <c r="AH21" s="72" t="n">
-        <v>289.6053009033203</v>
+        <v>289.2668008422851</v>
       </c>
       <c r="AI21" s="72" t="n">
-        <v>271.7901502227783</v>
+        <v>271.5293002319336</v>
       </c>
       <c r="AJ21" s="72" t="n">
-        <v>306.2525021286297</v>
+        <v>306.3822615727421</v>
       </c>
       <c r="AK21" s="72" t="n">
-        <v>299.5869995117188</v>
+        <v>299.881999206543</v>
       </c>
       <c r="AL21" s="72" t="n">
-        <v>292.9214968948078</v>
+        <v>293.3817368403438</v>
       </c>
       <c r="AM21" s="76" t="n">
-        <v>-0.1718919145108144</v>
+        <v>-0.2162781559976599</v>
       </c>
       <c r="AN21" s="29" t="n">
-        <v>4.449794302005559</v>
+        <v>4.335213439551667</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.158112198829347</v>
+        <v>1.219573288255476</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -6168,22 +6168,22 @@
         <v>228.8999938964844</v>
       </c>
       <c r="AR21" s="29" t="n">
-        <v>-4.76767420609595</v>
+        <v>-4.787333934791704</v>
       </c>
       <c r="AS21" s="78" t="n">
-        <v>80.92555319112333</v>
+        <v>80.84689881310302</v>
       </c>
       <c r="AT21" s="26" t="n">
-        <v>-0.02874045312222562</v>
+        <v>-0.02483469431878571</v>
       </c>
       <c r="AU21" s="26" t="n">
-        <v>-0.01887109687007837</v>
+        <v>-0.00216347821566909</v>
       </c>
       <c r="AV21" s="26" t="n">
-        <v>-0.003531505061935558</v>
+        <v>0.005502097991012533</v>
       </c>
       <c r="AW21" s="26" t="n">
-        <v>0.1806548608999239</v>
+        <v>0.1804111269151125</v>
       </c>
       <c r="AX21" s="79" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="C22" s="33" t="n">
-        <v>-0.06246119435907782</v>
+        <v>-0.06099829060707829</v>
       </c>
       <c r="D22" s="34" t="n">
         <v>4</v>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="R22" s="81" t="n">
-        <v>105.745002746582</v>
+        <v>105.9100036621094</v>
       </c>
       <c r="S22" s="82" t="n">
-        <v>-7.044998168945312</v>
+        <v>-6.879997253417969</v>
       </c>
       <c r="T22" s="83" t="n">
         <v>106.3550033569336</v>
@@ -6293,61 +6293,61 @@
         <v>102.3099975585938</v>
       </c>
       <c r="W22" s="84" t="n">
-        <v>60954710</v>
+        <v>63167537</v>
       </c>
       <c r="X22" s="85" t="n">
-        <v>1.103729310941075</v>
+        <v>1.141510852062677</v>
       </c>
       <c r="Y22" s="35" t="n">
-        <v>38.77524195456882</v>
+        <v>38.83029725769804</v>
       </c>
       <c r="Z22" s="35" t="n">
-        <v>6.290066195928885</v>
+        <v>6.592210333784959</v>
       </c>
       <c r="AA22" s="35" t="n">
         <v>19.21602059627059</v>
       </c>
       <c r="AB22" s="86" t="n">
-        <v>-10.5885504605328</v>
+        <v>-10.57538799433689</v>
       </c>
       <c r="AC22" s="86" t="n">
-        <v>-10.28291846060971</v>
+        <v>-10.28028596737052</v>
       </c>
       <c r="AD22" s="86" t="n">
-        <v>-0.3056319999230936</v>
+        <v>-0.2951020269663687</v>
       </c>
       <c r="AE22" s="83" t="n">
-        <v>115.3595118828787</v>
+        <v>115.3961787529959</v>
       </c>
       <c r="AF22" s="83" t="n">
-        <v>125.3837385236164</v>
+        <v>125.3987386068462</v>
       </c>
       <c r="AG22" s="83" t="n">
-        <v>152.8694999694824</v>
+        <v>152.872799987793</v>
       </c>
       <c r="AH22" s="83" t="n">
-        <v>162.9066500854492</v>
+        <v>162.9083000946045</v>
       </c>
       <c r="AI22" s="83" t="n">
-        <v>107.7414249897003</v>
+        <v>107.742249994278</v>
       </c>
       <c r="AJ22" s="83" t="n">
-        <v>152.6255892171121</v>
+        <v>152.6064766265304</v>
       </c>
       <c r="AK22" s="83" t="n">
-        <v>127.0327507019043</v>
+        <v>127.0410007476807</v>
       </c>
       <c r="AL22" s="83" t="n">
-        <v>101.4399121866965</v>
+        <v>101.4755248688309</v>
       </c>
       <c r="AM22" s="87" t="n">
-        <v>0.0841073286444437</v>
+        <v>0.08672787501184563</v>
       </c>
       <c r="AN22" s="36" t="n">
-        <v>40.29329188543522</v>
+        <v>40.24759837908707</v>
       </c>
       <c r="AO22" s="88" t="n">
-        <v>13.98629072722896</v>
+        <v>13.96450099353971</v>
       </c>
       <c r="AP22" s="83" t="n">
         <v>302</v>
@@ -6356,22 +6356,22 @@
         <v>23.79999923706055</v>
       </c>
       <c r="AR22" s="36" t="n">
-        <v>-64.98509842828409</v>
+        <v>-64.93046236353995</v>
       </c>
       <c r="AS22" s="89" t="n">
-        <v>29.45542893055154</v>
+        <v>29.51473910850799</v>
       </c>
       <c r="AT22" s="33" t="n">
-        <v>-0.08580440545928802</v>
+        <v>-0.08437792566211233</v>
       </c>
       <c r="AU22" s="33" t="n">
-        <v>-0.09395078762663989</v>
+        <v>-0.09253701916788148</v>
       </c>
       <c r="AV22" s="33" t="n">
-        <v>-0.6029400727004045</v>
+        <v>-0.6023205138576981</v>
       </c>
       <c r="AW22" s="33" t="n">
-        <v>1.515941132947876</v>
+        <v>1.519866922153671</v>
       </c>
       <c r="AX22" s="90" t="inlineStr">
         <is>
@@ -6502,10 +6502,10 @@
         <v>314.7369995117188</v>
       </c>
       <c r="W24" s="73" t="n">
-        <v>50793068</v>
+        <v>52432411</v>
       </c>
       <c r="X24" s="74" t="n">
-        <v>1.253918753155005</v>
+        <v>1.29177498401736</v>
       </c>
       <c r="Y24" s="28" t="n">
         <v>61.06205449589036</v>
@@ -6584,17 +6584,17 @@
       </c>
       <c r="AX24" s="79" t="inlineStr">
         <is>
-          <t>Tim Cook Just Handed Apple to John Ternus -- but He's Not Leaving. Here's What It Means for AAPL Stock.</t>
+          <t>Average household is spending over $3,300 a year on streaming: Sooth</t>
         </is>
       </c>
       <c r="AY24" s="79" t="inlineStr">
         <is>
-          <t>Apple's New CEO Inherits a 33x Valuation and an $840 Billion Legacy</t>
+          <t>Are you willing to pay $2,000 for an iPhone? These customers may.</t>
         </is>
       </c>
       <c r="AZ24" s="79" t="inlineStr">
         <is>
-          <t>AAPL Stock Sees Best Day In Over A Month – CEO John Ternus Reportedly Touts 'Phenomenal' iPhone Launch In F...</t>
+          <t>John Ternus Takes Over Apple with Just Eight Days Until His First Big Test</t>
         </is>
       </c>
     </row>
@@ -6690,10 +6690,10 @@
         <v>452.2999877929688</v>
       </c>
       <c r="W25" s="84" t="n">
-        <v>15608228</v>
+        <v>16112953</v>
       </c>
       <c r="X25" s="85" t="n">
-        <v>0.7728157265346534</v>
+        <v>0.7968107143972365</v>
       </c>
       <c r="Y25" s="35" t="n">
         <v>43.60040584568678</v>
@@ -6878,10 +6878,10 @@
         <v>251.9299926757812</v>
       </c>
       <c r="W26" s="73" t="n">
-        <v>28562976</v>
+        <v>31415716</v>
       </c>
       <c r="X26" s="74" t="n">
-        <v>0.8415123137103976</v>
+        <v>0.9216855139992844</v>
       </c>
       <c r="Y26" s="28" t="n">
         <v>46.32660631265332</v>
@@ -6960,17 +6960,17 @@
       </c>
       <c r="AX26" s="79" t="inlineStr">
         <is>
-          <t>Amazon Stock Drops 4.6% as FTC Alleges More Than $20 Billion in Ad Overcharges</t>
+          <t>AMAZON TEAMSTERS AT DJT6 TO LAUNCH UNFAIR LABOR PRACTICE STRIKE</t>
         </is>
       </c>
       <c r="AY26" s="79" t="inlineStr">
         <is>
-          <t>Sector Update: Tech Stocks Fall Late Afternoon</t>
+          <t>FTC alleges Amazon overcharged advertisers for years</t>
         </is>
       </c>
       <c r="AZ26" s="79" t="inlineStr">
         <is>
-          <t>Anthropic Raises AI Stakes With Stunning $35 Billion Bet</t>
+          <t>Amazon's $69 Billion Ad Machine Just Ran Into a $20 Billion Problem</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="C27" s="33" t="n">
-        <v>-0.02781345403653102</v>
+        <v>-0.02909895842760113</v>
       </c>
       <c r="D27" s="34" t="n">
         <v>17</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="R27" s="81" t="n">
-        <v>83.19000244140625</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="S27" s="82" t="n">
-        <v>-2.379997253417969</v>
+        <v>-2.489997863769531</v>
       </c>
       <c r="T27" s="83" t="n">
         <v>84.04000091552734</v>
@@ -7066,61 +7066,61 @@
         <v>82.76999664306641</v>
       </c>
       <c r="W27" s="84" t="n">
-        <v>3438394</v>
+        <v>4144823</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>0.7361246817208965</v>
+        <v>0.8663744494616298</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>53.35848226617453</v>
+        <v>53.6361945639654</v>
       </c>
       <c r="Z27" s="35" t="n">
-        <v>47.1225232729097</v>
+        <v>45.86895528175718</v>
       </c>
       <c r="AA27" s="35" t="n">
-        <v>24.87642762391344</v>
+        <v>24.74561915002105</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.127011849178274</v>
+        <v>2.231843511365867</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>2.037390319051627</v>
+        <v>1.999838541378428</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.08962153012664675</v>
+        <v>0.2320049699874389</v>
       </c>
       <c r="AE27" s="83" t="n">
-        <v>84.53500751459066</v>
+        <v>84.5353451160023</v>
       </c>
       <c r="AF27" s="83" t="n">
-        <v>82.41151591743721</v>
+        <v>82.18829583584916</v>
       </c>
       <c r="AG27" s="83" t="n">
-        <v>79.21819961547851</v>
+        <v>79.09279968261718</v>
       </c>
       <c r="AH27" s="83" t="n">
-        <v>78.19009994506835</v>
+        <v>78.03229995727538</v>
       </c>
       <c r="AI27" s="83" t="n">
-        <v>76.78790006637573</v>
+        <v>76.77120008468628</v>
       </c>
       <c r="AJ27" s="83" t="n">
-        <v>88.70074799082411</v>
+        <v>88.66825938281181</v>
       </c>
       <c r="AK27" s="83" t="n">
-        <v>82.39649963378906</v>
+        <v>81.99949989318847</v>
       </c>
       <c r="AL27" s="83" t="n">
-        <v>76.09225127675401</v>
+        <v>75.33074040356513</v>
       </c>
       <c r="AM27" s="87" t="n">
-        <v>0.5629339742565583</v>
+        <v>0.5810122137068737</v>
       </c>
       <c r="AN27" s="36" t="n">
-        <v>15.30222372322674</v>
+        <v>16.26536624811123</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.913456522139206</v>
+        <v>2.986319148685328</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -7129,22 +7129,22 @@
         <v>62.94499969482422</v>
       </c>
       <c r="AR27" s="36" t="n">
-        <v>-10.21046835258853</v>
+        <v>-10.32919539904286</v>
       </c>
       <c r="AS27" s="89" t="n">
-        <v>68.15351455530688</v>
+        <v>67.78320449447206</v>
       </c>
       <c r="AT27" s="33" t="n">
-        <v>-0.03681834206380896</v>
+        <v>-0.01000948946876246</v>
       </c>
       <c r="AU27" s="33" t="n">
-        <v>0.1312211232763445</v>
+        <v>0.1661988254116249</v>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>0.04104615979203285</v>
+        <v>0.02239723907185032</v>
       </c>
       <c r="AW27" s="33" t="n">
-        <v>0.08151331801503225</v>
+        <v>0.08008325284381423</v>
       </c>
       <c r="AX27" s="90" t="inlineStr">
         <is>
@@ -7254,10 +7254,10 @@
         <v>229.3300018310547</v>
       </c>
       <c r="W28" s="73" t="n">
-        <v>2908936</v>
+        <v>2944972</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>0.7191202027088462</v>
+        <v>0.7277045514164107</v>
       </c>
       <c r="Y28" s="28" t="n">
         <v>38.52933689785394</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="F29" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G29" s="30" t="inlineStr">
@@ -7442,10 +7442,10 @@
         <v>55.70000076293945</v>
       </c>
       <c r="W29" s="84" t="n">
-        <v>8020538</v>
+        <v>8308720</v>
       </c>
       <c r="X29" s="85" t="n">
-        <v>0.787878533664651</v>
+        <v>0.8150337746703411</v>
       </c>
       <c r="Y29" s="35" t="n">
         <v>37.39675453818472</v>
@@ -7630,10 +7630,10 @@
         <v>362</v>
       </c>
       <c r="W30" s="73" t="n">
-        <v>17781814</v>
+        <v>18744535</v>
       </c>
       <c r="X30" s="74" t="n">
-        <v>0.9330863904673026</v>
+        <v>0.98112617366597</v>
       </c>
       <c r="Y30" s="28" t="n">
         <v>43.32701006182213</v>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
+          <t>28 Analysts Share Their Broadcom Stock Forecast Before Q3 Earnings</t>
+        </is>
+      </c>
+      <c r="AY30" s="79" t="inlineStr">
+        <is>
+          <t>Two Stocks That Will Benefit From OpenAI Announcement</t>
+        </is>
+      </c>
+      <c r="AZ30" s="79" t="inlineStr">
+        <is>
           <t>Broadcom Faces Crucial Earnings Test After AI Chip Sales Surge 143%</t>
-        </is>
-      </c>
-      <c r="AY30" s="79" t="inlineStr">
-        <is>
-          <t>Broadcom Boosts VMware AI Push to Challenge Nutanix &amp; Microsoft</t>
-        </is>
-      </c>
-      <c r="AZ30" s="79" t="inlineStr">
-        <is>
-          <t>Morgan Stanley delivers bold pre-earnings verdict on Broadcom</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>-0.02490886017883343</v>
+        <v>-0.02531389171652176</v>
       </c>
       <c r="D31" s="34" t="n">
         <v>15</v>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="G31" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" s="30" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="N31" s="80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="P31" s="32" t="inlineStr">
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="R31" s="81" t="n">
-        <v>96.30000305175781</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="S31" s="82" t="n">
-        <v>-2.459999084472656</v>
+        <v>-2.5</v>
       </c>
       <c r="T31" s="83" t="n">
         <v>96</v>
@@ -7818,61 +7818,61 @@
         <v>94.69000244140625</v>
       </c>
       <c r="W31" s="84" t="n">
-        <v>1939748</v>
+        <v>2136391</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>0.7093760687736557</v>
+        <v>0.7812531226349684</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>46.57663423637104</v>
+        <v>46.90485088138379</v>
       </c>
       <c r="Z31" s="35" t="n">
-        <v>13.55643653991542</v>
+        <v>13.32954532176966</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>17.7806217290446</v>
+        <v>18.41821041137974</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>1.749387266910276</v>
+        <v>2.002343329639928</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.929279305695919</v>
+        <v>1.903014257259686</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>-0.1798920387856429</v>
+        <v>0.09932907238024158</v>
       </c>
       <c r="AE31" s="83" t="n">
-        <v>100.4311065360988</v>
+        <v>100.8398168790675</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>98.83513249971004</v>
+        <v>98.75806693210856</v>
       </c>
       <c r="AG31" s="83" t="n">
-        <v>95.82260009765625</v>
+        <v>95.96300003051758</v>
       </c>
       <c r="AH31" s="83" t="n">
-        <v>104.3805998229981</v>
+        <v>104.5354998016357</v>
       </c>
       <c r="AI31" s="83" t="n">
-        <v>105.1492498016357</v>
+        <v>105.1118497848511</v>
       </c>
       <c r="AJ31" s="83" t="n">
-        <v>106.9589753222431</v>
+        <v>107.0492177214587</v>
       </c>
       <c r="AK31" s="83" t="n">
-        <v>99.22600021362305</v>
+        <v>98.87799987792968</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>91.49302510500297</v>
+        <v>90.70678203440062</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.3108103853455069</v>
+        <v>0.3398036992874659</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>15.58659039359</v>
+        <v>16.52787850404919</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>4.282553973126682</v>
+        <v>4.534801159407194</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -7881,22 +7881,22 @@
         <v>73.19999694824219</v>
       </c>
       <c r="AR31" s="36" t="n">
-        <v>-28.79325706872626</v>
+        <v>-28.82283479270038</v>
       </c>
       <c r="AS31" s="89" t="n">
-        <v>37.23404726288745</v>
+        <v>37.16957126350331</v>
       </c>
       <c r="AT31" s="33" t="n">
-        <v>-0.09966338934143049</v>
+        <v>-0.05876595975466281</v>
       </c>
       <c r="AU31" s="33" t="n">
-        <v>0.07333929716372256</v>
+        <v>0.1143783884806915</v>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>-0.2008961800291438</v>
+        <v>-0.1450394771543706</v>
       </c>
       <c r="AW31" s="33" t="n">
-        <v>0.05257410974203403</v>
+        <v>0.05213689347291894</v>
       </c>
       <c r="AX31" s="90" t="inlineStr">
         <is>
@@ -8006,10 +8006,10 @@
         <v>80.38999938964844</v>
       </c>
       <c r="W32" s="73" t="n">
-        <v>15006220</v>
+        <v>15591995</v>
       </c>
       <c r="X32" s="74" t="n">
-        <v>0.5507452605259213</v>
+        <v>0.5716294043480932</v>
       </c>
       <c r="Y32" s="28" t="n">
         <v>42.64953739692996</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>-0.06940642471933811</v>
+        <v>-0.06800291463242925</v>
       </c>
       <c r="D33" s="34" t="n">
         <v>25</v>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="R33" s="81" t="n">
-        <v>424.3599853515625</v>
+        <v>425</v>
       </c>
       <c r="S33" s="82" t="n">
-        <v>-31.6500244140625</v>
+        <v>-31.010009765625</v>
       </c>
       <c r="T33" s="83" t="n">
         <v>455.6900024414062</v>
@@ -8194,61 +8194,61 @@
         <v>421.8901062011719</v>
       </c>
       <c r="W33" s="84" t="n">
-        <v>9912016</v>
+        <v>14731371</v>
       </c>
       <c r="X33" s="85" t="n">
-        <v>1.794482872039855</v>
+        <v>2.555500571243471</v>
       </c>
       <c r="Y33" s="35" t="n">
-        <v>44.75196031726701</v>
+        <v>44.88638752206839</v>
       </c>
       <c r="Z33" s="35" t="n">
-        <v>2.681448266333847</v>
+        <v>3.376286379854333</v>
       </c>
       <c r="AA33" s="35" t="n">
         <v>9.151884588042073</v>
       </c>
       <c r="AB33" s="86" t="n">
-        <v>4.951762235882939</v>
+        <v>5.002817535473412</v>
       </c>
       <c r="AC33" s="86" t="n">
-        <v>8.938986673228641</v>
+        <v>8.949197733146736</v>
       </c>
       <c r="AD33" s="86" t="n">
-        <v>-3.987224437345702</v>
+        <v>-3.946380197673324</v>
       </c>
       <c r="AE33" s="83" t="n">
-        <v>449.4750191480409</v>
+        <v>449.6172446254715</v>
       </c>
       <c r="AF33" s="83" t="n">
-        <v>448.5613786404192</v>
+        <v>448.6195617902771</v>
       </c>
       <c r="AG33" s="83" t="n">
-        <v>434.2107983398437</v>
+        <v>434.2235986328125</v>
       </c>
       <c r="AH33" s="83" t="n">
-        <v>360.6437983703613</v>
+        <v>360.6501985168457</v>
       </c>
       <c r="AI33" s="83" t="n">
-        <v>247.7352494049072</v>
+        <v>247.7384494781494</v>
       </c>
       <c r="AJ33" s="83" t="n">
-        <v>496.3313736274868</v>
+        <v>496.2570886322646</v>
       </c>
       <c r="AK33" s="83" t="n">
-        <v>457.1519989013672</v>
+        <v>457.1839996337891</v>
       </c>
       <c r="AL33" s="83" t="n">
-        <v>417.9726241752475</v>
+        <v>418.1109106353135</v>
       </c>
       <c r="AM33" s="87" t="n">
-        <v>0.08151433274478384</v>
+        <v>0.08815644656294322</v>
       </c>
       <c r="AN33" s="36" t="n">
-        <v>17.14063367119731</v>
+        <v>17.09293808609823</v>
       </c>
       <c r="AO33" s="88" t="n">
-        <v>6.574662520354218</v>
+        <v>6.56476162547996</v>
       </c>
       <c r="AP33" s="83" t="n">
         <v>514</v>
@@ -8257,36 +8257,36 @@
         <v>110.2200012207031</v>
       </c>
       <c r="AR33" s="36" t="n">
-        <v>-17.43969156584387</v>
+        <v>-17.31517509727627</v>
       </c>
       <c r="AS33" s="89" t="n">
-        <v>77.7997882709802</v>
+        <v>77.95829405392448</v>
       </c>
       <c r="AT33" s="33" t="n">
-        <v>-0.06011077441514401</v>
+        <v>-0.05869324473975635</v>
       </c>
       <c r="AU33" s="33" t="n">
-        <v>-0.0108619732913211</v>
+        <v>-0.00937016716380501</v>
       </c>
       <c r="AV33" s="33" t="n">
-        <v>-0.02515451578976735</v>
+        <v>-0.02368426550370228</v>
       </c>
       <c r="AW33" s="33" t="n">
-        <v>2.371147081432273</v>
+        <v>2.376231405092918</v>
       </c>
       <c r="AX33" s="90" t="inlineStr">
         <is>
-          <t>John Ternus's first day as Apple CEO, JOLTS data, Dell earnings: What to Watch</t>
+          <t>Dell stock surges on record orders for AI servers</t>
         </is>
       </c>
       <c r="AY33" s="90" t="inlineStr">
         <is>
-          <t>Dell Stock Is Up 248% This Year. Now It Has to Prove the AI Boom Isn’t Slowing Down.</t>
+          <t>Dell and GitLab stocks soar, MongoDB sinks on Q2 earnings</t>
         </is>
       </c>
       <c r="AZ33" s="90" t="inlineStr">
         <is>
-          <t>Dell Falls 4% Ahead of Earnings as Its 266% Rally Raises the Bar, Super Micro and Hewlett Packard Enterpris...</t>
+          <t>CEO Michael Dell Just Delivered Fantastic News for Dell Shareholders</t>
         </is>
       </c>
     </row>
@@ -8382,10 +8382,10 @@
         <v>329.2900085449219</v>
       </c>
       <c r="W34" s="73" t="n">
-        <v>13257268</v>
+        <v>14313571</v>
       </c>
       <c r="X34" s="74" t="n">
-        <v>0.823772363209048</v>
+        <v>0.8864989914285322</v>
       </c>
       <c r="Y34" s="28" t="n">
         <v>40.11764624992139</v>
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
-          <t>Alphabet Drops as Google Signs 396-Megawatt Geothermal Deal</t>
+          <t>Stock Market Today, Sept. 1: Fervo Energy Surges 28% on 396-Megawatt Google Power Deal</t>
         </is>
       </c>
       <c r="AY34" s="79" t="inlineStr">
         <is>
-          <t>Google Just Locked Up the Largest Geothermal Power Deal Ever Made.</t>
+          <t>FRVO Stock Clocks Best Day In A Month After Google Deal: Analyst Says Agreement Arrived Earlier Than Expected</t>
         </is>
       </c>
       <c r="AZ34" s="79" t="inlineStr">
         <is>
-          <t>What Is a Small Modular Reactor, and Why Is Big Tech Signing Multi-Decade Deals for Them?</t>
+          <t>Google Just Locked In Nearly 1 Gigawatt of Geothermal Power</t>
         </is>
       </c>
     </row>
@@ -8570,10 +8570,10 @@
         <v>35.13999938964844</v>
       </c>
       <c r="W35" s="84" t="n">
-        <v>32910050</v>
+        <v>33277422</v>
       </c>
       <c r="X35" s="85" t="n">
-        <v>0.7372535666211251</v>
+        <v>0.7451768270631552</v>
       </c>
       <c r="Y35" s="35" t="n">
         <v>43.12264643388389</v>
@@ -8758,10 +8758,10 @@
         <v>85.72000122070312</v>
       </c>
       <c r="W36" s="73" t="n">
-        <v>70053072</v>
+        <v>73437030</v>
       </c>
       <c r="X36" s="74" t="n">
-        <v>0.7167338240852963</v>
+        <v>0.7500576699095257</v>
       </c>
       <c r="Y36" s="28" t="n">
         <v>40.95245215668395</v>
@@ -8840,17 +8840,17 @@
       </c>
       <c r="AX36" s="79" t="inlineStr">
         <is>
+          <t>Stock Market Today, Sept. 1: Intel Falls on Chip Stock Pressure</t>
+        </is>
+      </c>
+      <c r="AY36" s="79" t="inlineStr">
+        <is>
           <t>Billionaires Were Buying These Two Nancy Pelosi AI Stocks</t>
         </is>
       </c>
-      <c r="AY36" s="79" t="inlineStr">
+      <c r="AZ36" s="79" t="inlineStr">
         <is>
           <t>Semiconductor Stocks Slide as Global Bond Selloff Lifts Yields: Intel Drops 3%, NVIDIA and AMD Slip</t>
-        </is>
-      </c>
-      <c r="AZ36" s="79" t="inlineStr">
-        <is>
-          <t>Archive Intel Partners With Zocks to Streamline AI Compliance Reviews</t>
         </is>
       </c>
     </row>
@@ -8946,10 +8946,10 @@
         <v>496.7799987792969</v>
       </c>
       <c r="W37" s="84" t="n">
-        <v>17754528</v>
+        <v>19129792</v>
       </c>
       <c r="X37" s="85" t="n">
-        <v>0.7133545089205314</v>
+        <v>0.7664931977136088</v>
       </c>
       <c r="Y37" s="35" t="n">
         <v>63.74452013366422</v>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="AX37" s="90" t="inlineStr">
         <is>
-          <t>Microsoft's AI strategy accelerates cloud growth and efficiency: analysts</t>
+          <t>MDB Stock Dives After-Hours Despite Raised Full-Year Forecast — What’s Driving The Selloff?</t>
         </is>
       </c>
       <c r="AY37" s="90" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT) Extends HUMAIN Tie Up As Valuation Questions Come Back Into Focus</t>
+          <t>MongoDB Inc. Q2 2027 Earnings: Recap of $MDB Earnings, Forecast</t>
         </is>
       </c>
       <c r="AZ37" s="90" t="inlineStr">
         <is>
-          <t>Dow Jones Software Giant Microsoft, AI Leader Palantir Eye Latest Entries</t>
+          <t>Box (BOX) Q2 2027 Earnings Call Transcript</t>
         </is>
       </c>
     </row>
@@ -9134,10 +9134,10 @@
         <v>123.5914993286133</v>
       </c>
       <c r="W38" s="73" t="n">
-        <v>20837386</v>
+        <v>22002128</v>
       </c>
       <c r="X38" s="74" t="n">
-        <v>0.8016452932980436</v>
+        <v>0.8445624387074909</v>
       </c>
       <c r="Y38" s="28" t="n">
         <v>59.00188766296943</v>
@@ -9216,17 +9216,17 @@
       </c>
       <c r="AX38" s="79" t="inlineStr">
         <is>
+          <t>Why Strategy (MSTR) Stock Is Trading Lower Today</t>
+        </is>
+      </c>
+      <c r="AY38" s="79" t="inlineStr">
+        <is>
           <t>Go Brewing Names Performance Chef and Ultra-Endurance Athlete Dan Churchill Partner and Head of Strategy</t>
         </is>
       </c>
-      <c r="AY38" s="79" t="inlineStr">
+      <c r="AZ38" s="79" t="inlineStr">
         <is>
           <t>Strategy resumes bitcoin buying after 10-week pause, spends $370M</t>
-        </is>
-      </c>
-      <c r="AZ38" s="79" t="inlineStr">
-        <is>
-          <t>Saylor Urges MSCI to Drop 'Discriminatory' Rule That Would Delete Strategy</t>
         </is>
       </c>
     </row>
@@ -9322,10 +9322,10 @@
         <v>922.3900146484375</v>
       </c>
       <c r="W39" s="84" t="n">
-        <v>27048449</v>
+        <v>27573310</v>
       </c>
       <c r="X39" s="85" t="n">
-        <v>0.9365181408625137</v>
+        <v>0.9538241100383713</v>
       </c>
       <c r="Y39" s="35" t="n">
         <v>50.44717781168542</v>
@@ -9404,17 +9404,17 @@
       </c>
       <c r="AX39" s="90" t="inlineStr">
         <is>
-          <t>Micron's AI Memory Boom Just Ran Into a Labor Risk</t>
+          <t>Stock Market Today: Nasdaq Ends Lower As Oil Prices Top $90; Micron, Nvidia Shares Wrapped in Red</t>
         </is>
       </c>
       <c r="AY39" s="90" t="inlineStr">
         <is>
-          <t>Micron Stock Is Down 23% From Its Highs. Did Nvidia's CFO Just Give It the Green Light for a Turnaround?</t>
+          <t>Micron Stock Drops as Nearly 10,000 Taiwan Workers Push for Strike</t>
         </is>
       </c>
       <c r="AZ39" s="90" t="inlineStr">
         <is>
-          <t>Micron Faces New Taiwan Risk as AI Demand Soars</t>
+          <t>Prediction: This Could Be Micron's Stock Price by the End of 2027 (Hint: It's Above $2,000)</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr">
@@ -9477,11 +9477,11 @@
         </is>
       </c>
       <c r="N40" s="69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="P40" s="25" t="inlineStr">
@@ -9510,10 +9510,10 @@
         <v>194.8000030517578</v>
       </c>
       <c r="W40" s="73" t="n">
-        <v>9875607</v>
+        <v>10776181</v>
       </c>
       <c r="X40" s="74" t="n">
-        <v>0.4246392068345846</v>
+        <v>0.4624673841461251</v>
       </c>
       <c r="Y40" s="28" t="n">
         <v>44.46037894215243</v>
@@ -9592,17 +9592,17 @@
       </c>
       <c r="AX40" s="79" t="inlineStr">
         <is>
+          <t>Nebius Raised Its Year-End Power Target From More Than 3 Gigawatts to 5 in 6 Months</t>
+        </is>
+      </c>
+      <c r="AY40" s="79" t="inlineStr">
+        <is>
           <t>Oracle Falls 4% as Bond Selloff Tests Its Debt-Funded AI Buildout, Nebius Slips</t>
         </is>
       </c>
-      <c r="AY40" s="79" t="inlineStr">
+      <c r="AZ40" s="79" t="inlineStr">
         <is>
           <t>What to Understand Before Buying Nebius</t>
-        </is>
-      </c>
-      <c r="AZ40" s="79" t="inlineStr">
-        <is>
-          <t>Nebius vs. CoreWeave: Which Is the Better Artificial Intelligence (AI) Infrastructure Stock to Buy Right Now</t>
         </is>
       </c>
     </row>
@@ -9698,10 +9698,10 @@
         <v>79.59999847412109</v>
       </c>
       <c r="W41" s="84" t="n">
-        <v>20247214</v>
+        <v>20847239</v>
       </c>
       <c r="X41" s="85" t="n">
-        <v>0.7278011571488335</v>
+        <v>0.7485622393595779</v>
       </c>
       <c r="Y41" s="35" t="n">
         <v>59.38896004331443</v>
@@ -9780,17 +9780,17 @@
       </c>
       <c r="AX41" s="90" t="inlineStr">
         <is>
+          <t>GTA VI Gameplay Peek Tops Netflix’s Viewership Charts — But TTWO Stock Fails To Gather Steam</t>
+        </is>
+      </c>
+      <c r="AY41" s="90" t="inlineStr">
+        <is>
           <t>Does This News Make Netflix Stock a Buy?</t>
         </is>
       </c>
-      <c r="AY41" s="90" t="inlineStr">
+      <c r="AZ41" s="90" t="inlineStr">
         <is>
           <t>EverPass Media Expands NFL Offering Through Multi-Year Agreement with Netflix</t>
-        </is>
-      </c>
-      <c r="AZ41" s="90" t="inlineStr">
-        <is>
-          <t>Netflix Is Down 46% From Its High. Is This a Once-in-a-Lifetime Buying Opportunity Before the Stock Goes Pa...</t>
         </is>
       </c>
     </row>
@@ -9886,10 +9886,10 @@
         <v>9.75</v>
       </c>
       <c r="W42" s="73" t="n">
-        <v>58458068</v>
+        <v>61333827</v>
       </c>
       <c r="X42" s="74" t="n">
-        <v>0.8674237123114569</v>
+        <v>0.9081577219498613</v>
       </c>
       <c r="Y42" s="28" t="n">
         <v>44.86611781971846</v>
@@ -10074,10 +10074,10 @@
         <v>215.1000061035156</v>
       </c>
       <c r="W43" s="84" t="n">
-        <v>99321017</v>
+        <v>106942626</v>
       </c>
       <c r="X43" s="85" t="n">
-        <v>0.7886922158900688</v>
+        <v>0.8466521339052876</v>
       </c>
       <c r="Y43" s="35" t="n">
         <v>51.87096875315195</v>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
-          <t>Two deals, one Nvidia strategy: What's behind the chip giant's recent partnerships</t>
+          <t>Nvidia Shareholders Should Brace Themselves for 1 Particular Thing in the Months to Come. Here’s What It Me...</t>
         </is>
       </c>
       <c r="AY43" s="90" t="inlineStr">
         <is>
-          <t>Sector Update: Tech Stocks Fall Late Afternoon</t>
+          <t>CEO Michael Dell Just Delivered Fantastic News for Dell Shareholders</t>
         </is>
       </c>
       <c r="AZ43" s="90" t="inlineStr">
         <is>
-          <t>Symbotic's Backlog Sits at $22.5 Billion. Here's The Customer Concentration Risk Nobody Talks About</t>
+          <t>28 Analysts Share Their Broadcom Stock Forecast Before Q3 Earnings</t>
         </is>
       </c>
     </row>
@@ -10262,10 +10262,10 @@
         <v>179.75</v>
       </c>
       <c r="W44" s="73" t="n">
-        <v>23826751</v>
+        <v>24387438</v>
       </c>
       <c r="X44" s="74" t="n">
-        <v>0.6445972944126216</v>
+        <v>0.6592658414766648</v>
       </c>
       <c r="Y44" s="28" t="n">
         <v>61.92113102167345</v>
@@ -10344,17 +10344,17 @@
       </c>
       <c r="AX44" s="79" t="inlineStr">
         <is>
+          <t>As AI Models Become Commoditized, Palantir Is Betting Its Ontology Is the New Moat</t>
+        </is>
+      </c>
+      <c r="AY44" s="79" t="inlineStr">
+        <is>
+          <t>Palantir to Deliver Eight TITAN Systems to the U.S. Army</t>
+        </is>
+      </c>
+      <c r="AZ44" s="79" t="inlineStr">
+        <is>
           <t>Prediction: Palantir's Commercial Revenue Passes Its Government Revenue Before 2027, and the Stock's Growth...</t>
-        </is>
-      </c>
-      <c r="AY44" s="79" t="inlineStr">
-        <is>
-          <t>Dow Jones Software Giant Microsoft, AI Leader Palantir Eye Latest Entries</t>
-        </is>
-      </c>
-      <c r="AZ44" s="79" t="inlineStr">
-        <is>
-          <t>Big Software Names Bounced Back in August. Can They Sustain Their Recent Rally?</t>
         </is>
       </c>
     </row>
@@ -10450,61 +10450,61 @@
         <v>162.2100067138672</v>
       </c>
       <c r="W45" s="84" t="n">
-        <v>8402246</v>
+        <v>8835110</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>0.9080650207826999</v>
+        <v>0.9104113333516409</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>51.00490620595838</v>
+        <v>50.88260328192964</v>
       </c>
       <c r="Z45" s="35" t="n">
         <v>68.51484231083393</v>
       </c>
       <c r="AA45" s="35" t="n">
-        <v>12.10331854086442</v>
+        <v>12.17585872366302</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-1.352837224149567</v>
+        <v>-1.629804958922534</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-3.039697872971139</v>
+        <v>-3.365393359595412</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.686860648821571</v>
+        <v>1.735588400672877</v>
       </c>
       <c r="AE45" s="83" t="n">
-        <v>164.8993715663237</v>
+        <v>164.6377808293622</v>
       </c>
       <c r="AF45" s="83" t="n">
-        <v>164.540679412096</v>
+        <v>164.5017637102231</v>
       </c>
       <c r="AG45" s="83" t="n">
-        <v>171.2947998046875</v>
+        <v>172.4489996337891</v>
       </c>
       <c r="AH45" s="83" t="n">
-        <v>182.3026002502442</v>
+        <v>181.9382002258301</v>
       </c>
       <c r="AI45" s="83" t="n">
-        <v>167.8679498291016</v>
+        <v>167.9303498077392</v>
       </c>
       <c r="AJ45" s="83" t="n">
-        <v>169.1431788250064</v>
+        <v>169.0415188676768</v>
       </c>
       <c r="AK45" s="83" t="n">
-        <v>162.9459991455078</v>
+        <v>162.8699989318848</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>156.7488194660093</v>
+        <v>156.6984789960927</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>0.7956184631022526</v>
+        <v>0.8030049094370144</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>7.606421405860468</v>
+        <v>7.578461320397125</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>3.797560385044389</v>
+        <v>3.897473344923669</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -10519,13 +10519,13 @@
         <v>32.34974096402502</v>
       </c>
       <c r="AT45" s="33" t="n">
-        <v>0.03768063741748606</v>
+        <v>0.05096828293239031</v>
       </c>
       <c r="AU45" s="33" t="n">
-        <v>0.0992280303448243</v>
+        <v>0.1287175660282978</v>
       </c>
       <c r="AV45" s="33" t="n">
-        <v>-0.3082129083883427</v>
+        <v>-0.2724136573055574</v>
       </c>
       <c r="AW45" s="33" t="n">
         <v>-0.02595733623028795</v>
@@ -10638,10 +10638,10 @@
         <v>61.93000030517578</v>
       </c>
       <c r="W46" s="73" t="n">
-        <v>13754838</v>
+        <v>14156543</v>
       </c>
       <c r="X46" s="74" t="n">
-        <v>0.7821260613392276</v>
+        <v>0.8040494731248466</v>
       </c>
       <c r="Y46" s="28" t="n">
         <v>33.3105767782444</v>
@@ -10826,10 +10826,10 @@
         <v>1513</v>
       </c>
       <c r="W47" s="84" t="n">
-        <v>11465539</v>
+        <v>11580091</v>
       </c>
       <c r="X47" s="85" t="n">
-        <v>0.8166447699465091</v>
+        <v>0.8244675086191331</v>
       </c>
       <c r="Y47" s="35" t="n">
         <v>51.66385839684092</v>
@@ -10908,17 +10908,17 @@
       </c>
       <c r="AX47" s="90" t="inlineStr">
         <is>
-          <t>Apple, Tesla, Nvidia, Medtronic, Alumis, Robinhood, Fervo, and More Stocks That Explain Today’s Market</t>
+          <t>Down More Than 30% From Its Peak, Is Now the Perfect Time to Buy Sandisk Stock?</t>
         </is>
       </c>
       <c r="AY47" s="90" t="inlineStr">
         <is>
-          <t>The Ceiling SanDisk Wrote Into Its Own Contracts</t>
+          <t>Tesla, Apple, Nvidia, Medtronic, Alumis, Robinhood, Fervo, and More Stocks That Explain Today’s Market</t>
         </is>
       </c>
       <c r="AZ47" s="90" t="inlineStr">
         <is>
-          <t>Dear Sandisk Stock Fans, Mark Your Calendars for August 31</t>
+          <t>Sandisk (SNDK) Joins The Strong Buy List, Is The Upside Already Priced In?</t>
         </is>
       </c>
     </row>
@@ -11014,10 +11014,10 @@
         <v>352.9599914550781</v>
       </c>
       <c r="W48" s="73" t="n">
-        <v>34877274</v>
+        <v>35998050</v>
       </c>
       <c r="X48" s="74" t="n">
-        <v>1.012997038811336</v>
+        <v>1.043850549910684</v>
       </c>
       <c r="Y48" s="28" t="n">
         <v>53.08184013406564</v>
@@ -11096,17 +11096,17 @@
       </c>
       <c r="AX48" s="79" t="inlineStr">
         <is>
-          <t>Tesla Stock Jumps 2.7% as France Registrations Soar 279%</t>
+          <t>Tesla stock investors stand to gain from U.S. power grid</t>
         </is>
       </c>
       <c r="AY48" s="79" t="inlineStr">
         <is>
-          <t>Tesla Just Posted a 279% Surge and a 79% Plunge</t>
+          <t>Tesla, Apple, Nvidia, Medtronic, Alumis, Robinhood, Fervo, and More Stocks That Explain Today’s Market</t>
         </is>
       </c>
       <c r="AZ48" s="79" t="inlineStr">
         <is>
-          <t>Tesla Stock Faces Crucial Test After Mixed Europe Sales</t>
+          <t>Tesla's French Registrations Nearly Quadrupled While Norway Fell 79%</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 1 Sep 2026, 08:01 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 10:38 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -11668,12 +11668,12 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>19 of 40</t>
+          <t>18 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>21 of 40</t>
+          <t>22 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
@@ -12431,7 +12431,7 @@
         <v>-0.006712554214991062</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
@@ -12962,19 +12962,19 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>-0.005289674527982902</v>
+        <v>0.006127020204530709</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" s="30" t="inlineStr">
@@ -13034,7 +13034,7 @@
         <v>116.5899963378906</v>
       </c>
       <c r="S12" s="82" t="n">
-        <v>-0.6200027465820312</v>
+        <v>0.7099990844726562</v>
       </c>
       <c r="T12" s="83" t="n">
         <v>116.5599975585938</v>
@@ -13049,58 +13049,58 @@
         <v>4912700</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>0.9288479445644519</v>
+        <v>0.8826552062409492</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>48.6875434606039</v>
+        <v>48.73504905390154</v>
       </c>
       <c r="Z12" s="35" t="n">
-        <v>22.22217391965883</v>
+        <v>18.79514439772846</v>
       </c>
       <c r="AA12" s="35" t="n">
-        <v>13.42405384927395</v>
+        <v>13.78987054065863</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.2269600721638056</v>
+        <v>0.2573574278493851</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.4445504463401025</v>
+        <v>0.4890562581723248</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.2175903741762969</v>
+        <v>-0.2316988303229398</v>
       </c>
       <c r="AE12" s="83" t="n">
-        <v>117.108588891665</v>
+        <v>117.1189798046141</v>
       </c>
       <c r="AF12" s="83" t="n">
-        <v>117.0714496038786</v>
+        <v>117.0632310444245</v>
       </c>
       <c r="AG12" s="83" t="n">
-        <v>116.1745997619629</v>
+        <v>116.1735998535156</v>
       </c>
       <c r="AH12" s="83" t="n">
-        <v>116.9418998718262</v>
+        <v>116.8779998779297</v>
       </c>
       <c r="AI12" s="83" t="n">
-        <v>116.9884499359131</v>
+        <v>117.0012749481201</v>
       </c>
       <c r="AJ12" s="83" t="n">
-        <v>120.0154880732483</v>
+        <v>120.0459537132867</v>
       </c>
       <c r="AK12" s="83" t="n">
-        <v>117.8914989471436</v>
+        <v>117.9414989471436</v>
       </c>
       <c r="AL12" s="83" t="n">
-        <v>115.7675098210388</v>
+        <v>115.8370441810004</v>
       </c>
       <c r="AM12" s="87" t="n">
-        <v>0.1936183445440202</v>
+        <v>0.1788948303864417</v>
       </c>
       <c r="AN12" s="36" t="n">
-        <v>3.603294800852466</v>
+        <v>3.568641716324644</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.370675307154388</v>
+        <v>1.389068897616946</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -13115,13 +13115,13 @@
         <v>57.51762902126261</v>
       </c>
       <c r="AT12" s="33" t="n">
-        <v>-0.01445483237324208</v>
+        <v>-0.01211659333884407</v>
       </c>
       <c r="AU12" s="33" t="n">
-        <v>0.004307003323048564</v>
+        <v>0.0373698458141376</v>
       </c>
       <c r="AV12" s="33" t="n">
-        <v>-0.01353757568715541</v>
+        <v>-0.03540999678526469</v>
       </c>
       <c r="AW12" s="33" t="n">
         <v>-0.02361617316584663</v>
@@ -13321,7 +13321,7 @@
         <v>-0.01014467255628793</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
@@ -13496,14 +13496,14 @@
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>0.004362095686057943</v>
+        <v>-0.01118710886762897</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -13547,7 +13547,7 @@
         </is>
       </c>
       <c r="N15" s="69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O15" s="23" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>186.5</v>
       </c>
       <c r="S15" s="71" t="n">
-        <v>0.80999755859375</v>
+        <v>-2.110000610351562</v>
       </c>
       <c r="T15" s="72" t="n">
         <v>185.7799987792969</v>
@@ -13583,58 +13583,58 @@
         <v>4874800</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>0.7540725455285144</v>
+        <v>0.736731859406147</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>54.14795211299604</v>
+        <v>54.26111161887398</v>
       </c>
       <c r="Z15" s="28" t="n">
         <v>59.39672874035261</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>12.63520409915696</v>
+        <v>13.36314976897932</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.9434473341411547</v>
+        <v>0.9252752490141916</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>1.00102310736285</v>
+        <v>1.028340088640139</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.05757577322169571</v>
+        <v>-0.1030648396259477</v>
       </c>
       <c r="AE15" s="72" t="n">
-        <v>185.1829707696305</v>
+        <v>184.9866761612759</v>
       </c>
       <c r="AF15" s="72" t="n">
-        <v>184.3283711954575</v>
+        <v>184.1848444566936</v>
       </c>
       <c r="AG15" s="72" t="n">
-        <v>182.6766006469726</v>
+        <v>182.7916006469727</v>
       </c>
       <c r="AH15" s="72" t="n">
-        <v>177.3955009460449</v>
+        <v>176.9555009460449</v>
       </c>
       <c r="AI15" s="72" t="n">
-        <v>159.5334251403809</v>
+        <v>159.3375001525879</v>
       </c>
       <c r="AJ15" s="72" t="n">
-        <v>191.6882663932217</v>
+        <v>192.2747749349986</v>
       </c>
       <c r="AK15" s="72" t="n">
-        <v>185.9790008544922</v>
+        <v>185.5965003967285</v>
       </c>
       <c r="AL15" s="72" t="n">
-        <v>180.2697353157627</v>
+        <v>178.9182258584584</v>
       </c>
       <c r="AM15" s="76" t="n">
-        <v>0.5456275104016038</v>
+        <v>0.5676446886163441</v>
       </c>
       <c r="AN15" s="29" t="n">
-        <v>6.139688365350884</v>
+        <v>7.196552223770107</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.103030859761249</v>
+        <v>2.214807014797722</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -13649,13 +13649,13 @@
         <v>83.02568146486927</v>
       </c>
       <c r="AT15" s="26" t="n">
-        <v>0.03582336483708937</v>
+        <v>0.017402228377569</v>
       </c>
       <c r="AU15" s="26" t="n">
-        <v>0.06358707447037171</v>
+        <v>0.0612872277602472</v>
       </c>
       <c r="AV15" s="26" t="n">
-        <v>-0.04730279304596419</v>
+        <v>-0.02366246556048568</v>
       </c>
       <c r="AW15" s="26" t="n">
         <v>0.2954087547314752</v>
@@ -13677,7 +13677,7 @@
         <v>-0.008318321395966555</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>-0.006153870918744753</v>
+        <v>-0.01961243764615728</v>
       </c>
       <c r="D21" s="27" t="n">
         <v>4</v>
@@ -14473,7 +14473,7 @@
         <v>293.9299926757812</v>
       </c>
       <c r="S21" s="71" t="n">
-        <v>-1.82000732421875</v>
+        <v>-5.8800048828125</v>
       </c>
       <c r="T21" s="72" t="n">
         <v>295.0899963378906</v>
@@ -14488,58 +14488,58 @@
         <v>20883400</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>1.258647650198726</v>
+        <v>1.243201603992837</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>42.54763745691413</v>
+        <v>42.73469720129305</v>
       </c>
       <c r="Z21" s="28" t="n">
         <v>9.78348918424833</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>16.47959107866174</v>
+        <v>15.69992067893879</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>0.1987337049282019</v>
+        <v>0.5150209965044041</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>1.127053307619166</v>
+        <v>1.330096054401237</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.9283196026909641</v>
+        <v>-0.8150750578968331</v>
       </c>
       <c r="AE21" s="72" t="n">
-        <v>297.723007929523</v>
+        <v>298.4022805014006</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>298.370339921359</v>
+        <v>298.6489194346242</v>
       </c>
       <c r="AG21" s="72" t="n">
-        <v>297.280400390625</v>
+        <v>297.2772003173828</v>
       </c>
       <c r="AH21" s="72" t="n">
-        <v>289.318600769043</v>
+        <v>288.96580078125</v>
       </c>
       <c r="AI21" s="72" t="n">
-        <v>271.5552001953125</v>
+        <v>271.2976502227783</v>
       </c>
       <c r="AJ21" s="72" t="n">
-        <v>305.4378972265099</v>
+        <v>305.3869115435745</v>
       </c>
       <c r="AK21" s="72" t="n">
-        <v>300.140998840332</v>
+        <v>300.1644989013672</v>
       </c>
       <c r="AL21" s="72" t="n">
-        <v>294.8441004541542</v>
+        <v>294.9420862591599</v>
       </c>
       <c r="AM21" s="76" t="n">
-        <v>-0.08628707894022007</v>
+        <v>-0.09689904386326761</v>
       </c>
       <c r="AN21" s="29" t="n">
-        <v>3.529606689285191</v>
+        <v>3.479700405159083</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.129691163083167</v>
+        <v>1.194868827155104</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -14554,13 +14554,13 @@
         <v>85.2517040114933</v>
       </c>
       <c r="AT21" s="26" t="n">
-        <v>-0.01355844054223931</v>
+        <v>-0.02010267686049028</v>
       </c>
       <c r="AU21" s="26" t="n">
-        <v>0.00937493253540489</v>
+        <v>0.004579774956978255</v>
       </c>
       <c r="AV21" s="26" t="n">
-        <v>0.01712914908044394</v>
+        <v>0.01205109695370621</v>
       </c>
       <c r="AW21" s="26" t="n">
         <v>0.1940607259627896</v>
@@ -14777,7 +14777,7 @@
         <v>-0.008914626195478559</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>0.01104002490802869</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>-0.02499719943397638</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
@@ -15302,19 +15302,19 @@
         </is>
       </c>
       <c r="C27" s="33" t="n">
-        <v>0.01158533395626371</v>
+        <v>-0.02071409493576004</v>
       </c>
       <c r="D27" s="34" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G27" s="30" t="inlineStr">
@@ -15374,7 +15374,7 @@
         <v>85.56999969482422</v>
       </c>
       <c r="S27" s="82" t="n">
-        <v>0.9800033569335938</v>
+        <v>-1.80999755859375</v>
       </c>
       <c r="T27" s="83" t="n">
         <v>83.83999633789062</v>
@@ -15389,58 +15389,58 @@
         <v>3100100</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>0.6418512878537703</v>
+        <v>0.6417024852749554</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>59.13045381552157</v>
+        <v>59.76137193386293</v>
       </c>
       <c r="Z27" s="35" t="n">
         <v>74.24499437902826</v>
       </c>
       <c r="AA27" s="35" t="n">
-        <v>25.45544121663947</v>
+        <v>25.25744420442534</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.370117011846517</v>
+        <v>2.481783084916216</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>2.014984936519965</v>
+        <v>1.941837298881568</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.3551320753265519</v>
+        <v>0.5399457860346484</v>
       </c>
       <c r="AE27" s="83" t="n">
-        <v>84.91929467835763</v>
+        <v>84.9511574831302</v>
       </c>
       <c r="AF27" s="83" t="n">
-        <v>82.3336672650403</v>
+        <v>82.0991252363286</v>
       </c>
       <c r="AG27" s="83" t="n">
-        <v>79.12299957275391</v>
+        <v>79.03499969482422</v>
       </c>
       <c r="AH27" s="83" t="n">
-        <v>78.04739990234376</v>
+        <v>77.90509994506836</v>
       </c>
       <c r="AI27" s="83" t="n">
-        <v>76.77875005722046</v>
+        <v>76.76605009078979</v>
       </c>
       <c r="AJ27" s="83" t="n">
-        <v>88.82468033503761</v>
+        <v>89.11469087891429</v>
       </c>
       <c r="AK27" s="83" t="n">
-        <v>82.07499961853027</v>
+        <v>81.52249984741211</v>
       </c>
       <c r="AL27" s="83" t="n">
-        <v>75.32531890202293</v>
+        <v>73.93030881590992</v>
       </c>
       <c r="AM27" s="87" t="n">
-        <v>0.7589011408899986</v>
+        <v>0.7665567706751498</v>
       </c>
       <c r="AN27" s="36" t="n">
-        <v>16.44759244076426</v>
+        <v>18.62600152280093</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.798595912103206</v>
+        <v>2.870746677021745</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -15455,13 +15455,13 @@
         <v>76.16562398709232</v>
       </c>
       <c r="AT27" s="33" t="n">
-        <v>0.01966160107102444</v>
+        <v>-0.007423725744635901</v>
       </c>
       <c r="AU27" s="33" t="n">
-        <v>0.2011510704766948</v>
+        <v>0.1737996968964064</v>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>0.05303959445346984</v>
+        <v>0.04417331154836224</v>
       </c>
       <c r="AW27" s="33" t="n">
         <v>0.1124545206940883</v>
@@ -15481,7 +15481,7 @@
         <v>-0.05211395596517232</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>0.004202900721427705</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>-0.01249874985801214</v>
+        <v>-0.07119345024419377</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -16053,15 +16053,15 @@
       </c>
       <c r="M31" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N31" s="80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O31" s="30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="P31" s="32" t="inlineStr">
@@ -16078,7 +16078,7 @@
         <v>98.76000213623047</v>
       </c>
       <c r="S31" s="82" t="n">
-        <v>-1.25</v>
+        <v>-7.569999694824219</v>
       </c>
       <c r="T31" s="83" t="n">
         <v>99.59999847412109</v>
@@ -16093,58 +16093,58 @@
         <v>3128400</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>1.10259948295824</v>
+        <v>1.128085114822434</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>50.50174829706862</v>
+        <v>50.64559111168269</v>
       </c>
       <c r="Z31" s="35" t="n">
         <v>27.50992189281716</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>18.7041232745334</v>
+        <v>19.4645964776505</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>2.278761540531065</v>
+        <v>2.57110225722883</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.974252315392329</v>
+        <v>1.878181989164625</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>0.3045092251387356</v>
+        <v>0.6929202680642046</v>
       </c>
       <c r="AE31" s="83" t="n">
-        <v>101.6114218173391</v>
+        <v>102.148335377021</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>99.08864544450526</v>
+        <v>99.00787341169638</v>
       </c>
       <c r="AG31" s="83" t="n">
-        <v>96.03800003051758</v>
+        <v>96.16759994506836</v>
       </c>
       <c r="AH31" s="83" t="n">
-        <v>104.5729998016357</v>
+        <v>104.7318997955322</v>
       </c>
       <c r="AI31" s="83" t="n">
-        <v>105.1305997848511</v>
+        <v>105.0931497573852</v>
       </c>
       <c r="AJ31" s="83" t="n">
-        <v>107.1595519801748</v>
+        <v>107.5922436831232</v>
       </c>
       <c r="AK31" s="83" t="n">
-        <v>99.06549987792968</v>
+        <v>98.55099983215332</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>90.97144777568455</v>
+        <v>89.50975598118343</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.4811282570312048</v>
+        <v>0.5115582716008</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>16.34080908534004</v>
+        <v>18.3483554025194</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>4.180094217506338</v>
+        <v>4.443000496321981</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -16159,13 +16159,13 @@
         <v>41.19922899346607</v>
       </c>
       <c r="AT31" s="33" t="n">
-        <v>-0.03432086263859191</v>
+        <v>-0.03658179613552681</v>
       </c>
       <c r="AU31" s="33" t="n">
-        <v>0.1433202740964736</v>
+        <v>0.1193471424533201</v>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>-0.122835017776849</v>
+        <v>-0.1236911729324509</v>
       </c>
       <c r="AW31" s="33" t="n">
         <v>0.0794622848640365</v>
@@ -16185,7 +16185,7 @@
         <v>0.007835640584247017</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>-0.0005040778398927026</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>-0.02178605084672747</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>0.0004470874592776841</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>-0.01215122854742678</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>-0.01367236567406971</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>-0.008198704832808712</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E41" s="30" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>-0.00685599359086031</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>0.0004831799877809129</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         </is>
       </c>
       <c r="C45" s="33" t="n">
-        <v>0.03830923437849076</v>
+        <v>0.03459155838371286</v>
       </c>
       <c r="D45" s="34" t="n">
         <v>5</v>
@@ -18482,7 +18482,7 @@
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
@@ -18521,11 +18521,11 @@
         </is>
       </c>
       <c r="N45" s="80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O45" s="30" t="inlineStr">
         <is>
-          <t>Very Strong</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="P45" s="32" t="inlineStr">
@@ -18542,7 +18542,7 @@
         <v>170.4799957275391</v>
       </c>
       <c r="S45" s="82" t="n">
-        <v>6.289993286132812</v>
+        <v>5.699996948242188</v>
       </c>
       <c r="T45" s="83" t="n">
         <v>164.7899932861328</v>
@@ -18557,58 +18557,58 @@
         <v>12734600</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>1.31959638874137</v>
+        <v>1.280141699601068</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>55.780846199514</v>
+        <v>55.46586429173728</v>
       </c>
       <c r="Z45" s="35" t="n">
         <v>94.05934909973199</v>
       </c>
       <c r="AA45" s="35" t="n">
-        <v>12.1523068230342</v>
+        <v>12.49227043299314</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-1.70849065987835</v>
+        <v>-2.029853019445795</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-3.461413035176531</v>
+        <v>-3.799290459763631</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.752922375298181</v>
+        <v>1.769437440317836</v>
       </c>
       <c r="AE45" s="83" t="n">
-        <v>164.4106204108871</v>
+        <v>164.0742894633653</v>
       </c>
       <c r="AF45" s="83" t="n">
-        <v>164.3337472922705</v>
+        <v>164.2909400202102</v>
       </c>
       <c r="AG45" s="83" t="n">
-        <v>172.4005996704101</v>
+        <v>173.6389996337891</v>
       </c>
       <c r="AH45" s="83" t="n">
-        <v>181.9140002441406</v>
+        <v>181.5472002410889</v>
       </c>
       <c r="AI45" s="83" t="n">
-        <v>167.9182498168945</v>
+        <v>167.9671997833252</v>
       </c>
       <c r="AJ45" s="83" t="n">
-        <v>168.7139008456425</v>
+        <v>169.7708473578702</v>
       </c>
       <c r="AK45" s="83" t="n">
-        <v>162.7489990234375</v>
+        <v>162.1179992675781</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>156.7840972012325</v>
+        <v>154.465151177286</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>1.148040565841508</v>
+        <v>1.046332317151862</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>7.330185571643363</v>
+        <v>9.44108380915921</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>3.623688243548068</v>
+        <v>3.728844265518225</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -18623,13 +18623,13 @@
         <v>35.15550815064062</v>
       </c>
       <c r="AT45" s="33" t="n">
-        <v>0.07538003557849504</v>
+        <v>0.06052874480584181</v>
       </c>
       <c r="AU45" s="33" t="n">
-        <v>0.1549352687664962</v>
+        <v>0.1245381851180916</v>
       </c>
       <c r="AV45" s="33" t="n">
-        <v>-0.2555133777110271</v>
+        <v>-0.3208509567926806</v>
       </c>
       <c r="AW45" s="33" t="n">
         <v>-0.003332401719082556</v>
@@ -18649,7 +18649,7 @@
         <v>-0.007299289100143769</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 1 Sep 2026, 08:01 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 10:38 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19604,22 +19604,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>11 of 40</t>
+          <t>14 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>29 of 40</t>
+          <t>26 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.3 / 9</t>
+          <t>4.5 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>16 of 40</t>
+          <t>18 of 40</t>
         </is>
       </c>
     </row>
@@ -20723,7 +20723,7 @@
         <v>-0.01379384326320543</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
@@ -20898,67 +20898,67 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>0.01147740647720341</v>
+        <v>-0.01092528481292099</v>
       </c>
       <c r="D12" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M12" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F12" s="30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G12" s="30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" s="30" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="I12" s="30" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="J12" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K12" s="30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L12" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M12" s="30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N12" s="80" t="n">
-        <v>5</v>
-      </c>
       <c r="O12" s="30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Very Weak</t>
         </is>
       </c>
       <c r="P12" s="32" t="inlineStr">
         <is>
-          <t>Long-term up, short-term mixed</t>
+          <t>Below every average</t>
         </is>
       </c>
       <c r="Q12" s="32" t="inlineStr">
@@ -20967,76 +20967,76 @@
         </is>
       </c>
       <c r="R12" s="81" t="n">
-        <v>117.2099990844727</v>
+        <v>115.879997253418</v>
       </c>
       <c r="S12" s="82" t="n">
-        <v>1.330001831054688</v>
+        <v>-1.280006408691406</v>
       </c>
       <c r="T12" s="83" t="n">
-        <v>116.7099990844727</v>
+        <v>116.5400009155273</v>
       </c>
       <c r="U12" s="83" t="n">
-        <v>117.5699996948242</v>
+        <v>116.620002746582</v>
       </c>
       <c r="V12" s="83" t="n">
-        <v>116.379997253418</v>
+        <v>115.8099975585938</v>
       </c>
       <c r="W12" s="84" t="n">
-        <v>4505600</v>
+        <v>5231500</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>0.8124837141700471</v>
+        <v>0.8751130169611171</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>50.82050597356402</v>
+        <v>46.11854978280344</v>
       </c>
       <c r="Z12" s="35" t="n">
-        <v>33.73496412347481</v>
+        <v>1.686739014135516</v>
       </c>
       <c r="AA12" s="35" t="n">
-        <v>14.02483206422039</v>
+        <v>14.60964167370293</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.3068163364086445</v>
+        <v>0.341151632772295</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.4989480398841767</v>
+        <v>0.5469809657530598</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.1921317034755323</v>
+        <v>-0.2058293329807648</v>
       </c>
       <c r="AE12" s="83" t="n">
-        <v>117.2567581927434</v>
+        <v>117.2701179379637</v>
       </c>
       <c r="AF12" s="83" t="n">
-        <v>117.1195949304774</v>
+        <v>117.1105545150778</v>
       </c>
       <c r="AG12" s="83" t="n">
-        <v>116.1859999084473</v>
+        <v>116.1515998840332</v>
       </c>
       <c r="AH12" s="83" t="n">
-        <v>116.8841999053955</v>
+        <v>116.7897998809814</v>
       </c>
       <c r="AI12" s="83" t="n">
-        <v>117.004374961853</v>
+        <v>117.0157249832153</v>
       </c>
       <c r="AJ12" s="83" t="n">
-        <v>120.0137223397632</v>
+        <v>120.0951522891402</v>
       </c>
       <c r="AK12" s="83" t="n">
-        <v>117.9724990844727</v>
+        <v>117.9164989471436</v>
       </c>
       <c r="AL12" s="83" t="n">
-        <v>115.9312758291821</v>
+        <v>115.7378456051469</v>
       </c>
       <c r="AM12" s="87" t="n">
-        <v>0.3132247420698089</v>
+        <v>0.03262374181585737</v>
       </c>
       <c r="AN12" s="36" t="n">
-        <v>3.46050693361846</v>
+        <v>3.695247673479995</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.407925686600866</v>
+        <v>1.421444839978871</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -21045,22 +21045,22 @@
         <v>105.1900024414062</v>
       </c>
       <c r="AR12" s="36" t="n">
-        <v>-6.239503174520156</v>
+        <v>-7.303419507875075</v>
       </c>
       <c r="AS12" s="89" t="n">
-        <v>60.64579630748077</v>
+        <v>53.93539342386214</v>
       </c>
       <c r="AT12" s="33" t="n">
-        <v>-0.006863223026886356</v>
+        <v>-0.006856385410228039</v>
       </c>
       <c r="AU12" s="33" t="n">
-        <v>0.04288637530919104</v>
+        <v>0.03825819030297883</v>
       </c>
       <c r="AV12" s="33" t="n">
-        <v>-0.03028049622686779</v>
+        <v>-0.05063084080604807</v>
       </c>
       <c r="AW12" s="33" t="n">
-        <v>-0.01842395536526409</v>
+        <v>-0.02956206599473987</v>
       </c>
       <c r="AX12" s="32" t="n"/>
       <c r="AY12" s="32" t="n"/>
@@ -21432,19 +21432,19 @@
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>-0.01548167201896</v>
+        <v>0.03155767002859644</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -21479,15 +21479,15 @@
       </c>
       <c r="M15" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N15" s="69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O15" s="23" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Very Strong</t>
         </is>
       </c>
       <c r="P15" s="25" t="inlineStr">
@@ -21501,76 +21501,76 @@
         </is>
       </c>
       <c r="R15" s="70" t="n">
-        <v>185.6900024414062</v>
+        <v>188.6100006103516</v>
       </c>
       <c r="S15" s="71" t="n">
-        <v>-2.919998168945312</v>
+        <v>5.770004272460938</v>
       </c>
       <c r="T15" s="72" t="n">
-        <v>188.0700073242188</v>
+        <v>186.4700012207031</v>
       </c>
       <c r="U15" s="72" t="n">
-        <v>188.6699981689453</v>
+        <v>188.7400054931641</v>
       </c>
       <c r="V15" s="72" t="n">
-        <v>185.5099945068359</v>
+        <v>185.6699981689453</v>
       </c>
       <c r="W15" s="73" t="n">
-        <v>6300200</v>
+        <v>8136000</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>0.9420070992186075</v>
+        <v>1.191152442916625</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>53.00339310126717</v>
+        <v>57.83612648825964</v>
       </c>
       <c r="Z15" s="28" t="n">
-        <v>53.13224291345087</v>
+        <v>75.71538152894806</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>13.42241089458476</v>
+        <v>14.2014856168803</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.860660059154867</v>
+        <v>0.8249471787323728</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>1.015417050668274</v>
+        <v>1.054106298546626</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.1547569915134073</v>
+        <v>-0.2291591198142533</v>
       </c>
       <c r="AE15" s="72" t="n">
-        <v>184.8066767038106</v>
+        <v>184.5542979216405</v>
       </c>
       <c r="AF15" s="72" t="n">
-        <v>184.1112083150033</v>
+        <v>183.953328902363</v>
       </c>
       <c r="AG15" s="72" t="n">
-        <v>182.7754006958008</v>
+        <v>182.7776007080078</v>
       </c>
       <c r="AH15" s="72" t="n">
-        <v>176.947400970459</v>
+        <v>176.4648008728027</v>
       </c>
       <c r="AI15" s="72" t="n">
-        <v>159.3334501647949</v>
+        <v>159.1438251495361</v>
       </c>
       <c r="AJ15" s="72" t="n">
-        <v>192.2216794840587</v>
+        <v>193.0509289294371</v>
       </c>
       <c r="AK15" s="72" t="n">
-        <v>185.5560005187988</v>
+        <v>185.0390007019043</v>
       </c>
       <c r="AL15" s="72" t="n">
-        <v>178.890321553539</v>
+        <v>177.0270724743714</v>
       </c>
       <c r="AM15" s="76" t="n">
-        <v>0.5100516333974229</v>
+        <v>0.7228552108202617</v>
       </c>
       <c r="AN15" s="29" t="n">
-        <v>7.184546925589225</v>
+        <v>8.659718434645001</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.217928968762917</v>
+        <v>2.222682097325518</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -21579,22 +21579,22 @@
         <v>126.6800003051758</v>
       </c>
       <c r="AR15" s="29" t="n">
-        <v>-6.561663345482471</v>
+        <v>-5.092333988202824</v>
       </c>
       <c r="AS15" s="78" t="n">
-        <v>81.90146548977381</v>
+        <v>85.95420435787231</v>
       </c>
       <c r="AT15" s="26" t="n">
-        <v>0.01298349743336691</v>
+        <v>0.03009281443563072</v>
       </c>
       <c r="AU15" s="26" t="n">
-        <v>0.05667789766130582</v>
+        <v>0.1323166975866985</v>
       </c>
       <c r="AV15" s="26" t="n">
-        <v>-0.02790284636080442</v>
+        <v>0.009419290603934538</v>
       </c>
       <c r="AW15" s="26" t="n">
-        <v>0.2897825996177301</v>
+        <v>0.3100645899225647</v>
       </c>
       <c r="AX15" s="25" t="n"/>
       <c r="AY15" s="25" t="n"/>
@@ -21988,7 +21988,7 @@
         <v>-0.002269485222937795</v>
       </c>
       <c r="D19" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>-0.006489984566639517</v>
       </c>
       <c r="D20" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
@@ -22337,14 +22337,14 @@
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>-0.01354190184335091</v>
+        <v>0.002943849410811605</v>
       </c>
       <c r="D21" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -22359,17 +22359,17 @@
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K21" s="23" t="inlineStr">
@@ -22384,20 +22384,20 @@
       </c>
       <c r="M21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="N21" s="69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O21" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="P21" s="25" t="inlineStr">
         <is>
-          <t>Long-term up, short-term mixed</t>
+          <t>Above every average</t>
         </is>
       </c>
       <c r="Q21" s="25" t="inlineStr">
@@ -22406,76 +22406,76 @@
         </is>
       </c>
       <c r="R21" s="70" t="n">
-        <v>295.75</v>
+        <v>299.8099975585938</v>
       </c>
       <c r="S21" s="71" t="n">
-        <v>-4.05999755859375</v>
+        <v>0.8800048828125</v>
       </c>
       <c r="T21" s="72" t="n">
-        <v>299.7000122070312</v>
+        <v>298.7699890136719</v>
       </c>
       <c r="U21" s="72" t="n">
-        <v>300.3900146484375</v>
+        <v>300.3200073242188</v>
       </c>
       <c r="V21" s="72" t="n">
-        <v>295.6700134277344</v>
+        <v>298.1400146484375</v>
       </c>
       <c r="W21" s="73" t="n">
-        <v>19052800</v>
+        <v>13658700</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>1.140438929641368</v>
+        <v>0.7954310193463625</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>45.32522468665713</v>
+        <v>52.41279782132757</v>
       </c>
       <c r="Z21" s="28" t="n">
-        <v>0.8410804080571717</v>
+        <v>34.0294154035339</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>14.94790355833013</v>
+        <v>14.16121708747648</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>0.6602067659577529</v>
+        <v>1.054301356064684</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>1.359133208291907</v>
+        <v>1.533864818875446</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.6989264423341541</v>
+        <v>-0.4795634628107615</v>
       </c>
       <c r="AE21" s="72" t="n">
-        <v>298.8067265734492</v>
+        <v>299.680077023006</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>298.8143746459168</v>
+        <v>299.1208121105085</v>
       </c>
       <c r="AG21" s="72" t="n">
-        <v>297.3136004638672</v>
+        <v>297.1962005615234</v>
       </c>
       <c r="AH21" s="72" t="n">
-        <v>288.9840008544922</v>
+        <v>288.5556008911133</v>
       </c>
       <c r="AI21" s="72" t="n">
-        <v>271.3067502593994</v>
+        <v>271.0481502532959</v>
       </c>
       <c r="AJ21" s="72" t="n">
-        <v>305.0891537932497</v>
+        <v>305.9859908677769</v>
       </c>
       <c r="AK21" s="72" t="n">
-        <v>300.2554992675781</v>
+        <v>300.0279998779297</v>
       </c>
       <c r="AL21" s="72" t="n">
-        <v>295.4218447419065</v>
+        <v>294.0700088880825</v>
       </c>
       <c r="AM21" s="76" t="n">
-        <v>0.03394483990846393</v>
+        <v>0.4817050479173745</v>
       </c>
       <c r="AN21" s="29" t="n">
-        <v>3.21969425203699</v>
+        <v>3.97162331000525</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.130034660141968</v>
+        <v>1.07937807342217</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -22484,22 +22484,22 @@
         <v>228.8999938964844</v>
       </c>
       <c r="AR21" s="29" t="n">
-        <v>-3.089977358312457</v>
+        <v>-1.759615717303098</v>
       </c>
       <c r="AS21" s="78" t="n">
-        <v>87.63766016427803</v>
+        <v>92.96015311598961</v>
       </c>
       <c r="AT21" s="26" t="n">
-        <v>-0.01403517660690634</v>
+        <v>0.007189115578747796</v>
       </c>
       <c r="AU21" s="26" t="n">
-        <v>0.0108001083484075</v>
+        <v>0.0389506530446404</v>
       </c>
       <c r="AV21" s="26" t="n">
-        <v>0.01831769258816762</v>
+        <v>0.02664109444857621</v>
       </c>
       <c r="AW21" s="26" t="n">
-        <v>0.2014543207675612</v>
+        <v>0.2179476482707843</v>
       </c>
       <c r="AX21" s="25" t="n"/>
       <c r="AY21" s="25" t="n"/>
@@ -22713,7 +22713,7 @@
         <v>0.01627575132974779</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>-0.02326562725379</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -23238,19 +23238,19 @@
         </is>
       </c>
       <c r="C27" s="33" t="n">
-        <v>-0.03192951480000428</v>
+        <v>0.01865234899615387</v>
       </c>
       <c r="D27" s="34" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G27" s="30" t="inlineStr">
@@ -23260,7 +23260,7 @@
       </c>
       <c r="H27" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I27" s="30" t="inlineStr">
@@ -23289,16 +23289,16 @@
         </is>
       </c>
       <c r="N27" s="80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O27" s="30" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Very Strong</t>
         </is>
       </c>
       <c r="P27" s="32" t="inlineStr">
         <is>
-          <t>Long-term up, short-term mixed</t>
+          <t>Above every average</t>
         </is>
       </c>
       <c r="Q27" s="32" t="inlineStr">
@@ -23307,76 +23307,76 @@
         </is>
       </c>
       <c r="R27" s="81" t="n">
-        <v>84.58999633789062</v>
+        <v>87.37999725341797</v>
       </c>
       <c r="S27" s="82" t="n">
-        <v>-2.790000915527344</v>
+        <v>1.599998474121094</v>
       </c>
       <c r="T27" s="83" t="n">
-        <v>86.70999908447266</v>
+        <v>86.5</v>
       </c>
       <c r="U27" s="83" t="n">
-        <v>87.19000244140625</v>
+        <v>87.83000183105469</v>
       </c>
       <c r="V27" s="83" t="n">
-        <v>84.18000030517578</v>
+        <v>86.02799987792969</v>
       </c>
       <c r="W27" s="84" t="n">
-        <v>5061500</v>
+        <v>2907800</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>1.026855679253417</v>
+        <v>0.5832274472717499</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>57.36713154759599</v>
+        <v>64.75266026536364</v>
       </c>
       <c r="Z27" s="35" t="n">
-        <v>63.07686689730184</v>
+        <v>94.87174359674376</v>
       </c>
       <c r="AA27" s="35" t="n">
-        <v>25.57602069893318</v>
+        <v>25.33738466636874</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.403606178950014</v>
+        <v>2.511171149610618</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>1.926201917688327</v>
+        <v>1.806850852372906</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.4774042612616864</v>
+        <v>0.7043202972377125</v>
       </c>
       <c r="AE27" s="83" t="n">
-        <v>84.73337895936719</v>
+        <v>84.77434542264621</v>
       </c>
       <c r="AF27" s="83" t="n">
-        <v>82.01003402206192</v>
+        <v>81.75203779047905</v>
       </c>
       <c r="AG27" s="83" t="n">
-        <v>79.01539962768555</v>
+        <v>78.89339965820312</v>
       </c>
       <c r="AH27" s="83" t="n">
-        <v>77.89529991149902</v>
+        <v>77.73699996948243</v>
       </c>
       <c r="AI27" s="83" t="n">
-        <v>76.76115007400513</v>
+        <v>76.75240007400512</v>
       </c>
       <c r="AJ27" s="83" t="n">
-        <v>88.97264740006578</v>
+        <v>89.37672863617078</v>
       </c>
       <c r="AK27" s="83" t="n">
-        <v>81.47349967956544</v>
+        <v>80.80599975585938</v>
       </c>
       <c r="AL27" s="83" t="n">
-        <v>73.97435195906509</v>
+        <v>72.23527087554797</v>
       </c>
       <c r="AM27" s="87" t="n">
-        <v>0.7077900565824069</v>
+        <v>0.8835144938874636</v>
       </c>
       <c r="AN27" s="36" t="n">
-        <v>18.40880224857022</v>
+        <v>21.21310028019282</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.854184757973381</v>
+        <v>2.693889727016816</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -23385,22 +23385,22 @@
         <v>62.94499969482422</v>
       </c>
       <c r="AR27" s="36" t="n">
-        <v>-8.699411824334369</v>
+        <v>-5.688077912215606</v>
       </c>
       <c r="AS27" s="89" t="n">
-        <v>72.86650499525619</v>
+        <v>82.25886568722078</v>
       </c>
       <c r="AT27" s="33" t="n">
-        <v>-0.01879135557111744</v>
+        <v>0.04935752102847935</v>
       </c>
       <c r="AU27" s="33" t="n">
-        <v>0.160356578426982</v>
+        <v>0.2380276988739238</v>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>0.03221475885247194</v>
+        <v>0.07863220527355863</v>
       </c>
       <c r="AW27" s="33" t="n">
-        <v>0.09971396712853675</v>
+        <v>0.1359854307523325</v>
       </c>
       <c r="AX27" s="32" t="n"/>
       <c r="AY27" s="32" t="n"/>
@@ -23417,7 +23417,7 @@
         <v>0.01652994979538658</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>-0.05517577254916717</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E29" s="30" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>-0.007401625495918829</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
@@ -23942,10 +23942,10 @@
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>-0.05943759603113641</v>
+        <v>-0.00959387829211289</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -23964,7 +23964,7 @@
       </c>
       <c r="H31" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I31" s="30" t="inlineStr">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="N31" s="80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O31" s="30" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
       </c>
       <c r="P31" s="32" t="inlineStr">
         <is>
-          <t>Long-term down, short-term mixed</t>
+          <t>Above every average</t>
         </is>
       </c>
       <c r="Q31" s="32" t="inlineStr">
@@ -24011,76 +24011,76 @@
         </is>
       </c>
       <c r="R31" s="81" t="n">
-        <v>100.0100021362305</v>
+        <v>106.3300018310547</v>
       </c>
       <c r="S31" s="82" t="n">
-        <v>-6.319999694824219</v>
+        <v>-1.029998779296875</v>
       </c>
       <c r="T31" s="83" t="n">
-        <v>105.7399978637695</v>
+        <v>108.129997253418</v>
       </c>
       <c r="U31" s="83" t="n">
-        <v>106.4700012207031</v>
+        <v>108.9700012207031</v>
       </c>
       <c r="V31" s="83" t="n">
-        <v>99.52999877929688</v>
+        <v>105.1399993896484</v>
       </c>
       <c r="W31" s="84" t="n">
-        <v>4190900</v>
+        <v>2313900</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>1.482811571230434</v>
+        <v>0.7987945069284782</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>52.59298094718957</v>
+        <v>65.28503598146889</v>
       </c>
       <c r="Z31" s="35" t="n">
-        <v>34.60011017834091</v>
+        <v>70.448100418946</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>19.91066925997254</v>
+        <v>20.69494291305342</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>2.670817356943928</v>
+        <v>3.005102164700801</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.898125009107645</v>
+        <v>1.704951922148574</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>0.772692347836283</v>
+        <v>1.300150242552227</v>
       </c>
       <c r="AE31" s="83" t="n">
-        <v>102.4261131547987</v>
+        <v>103.1164305886754</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>99.12150977533274</v>
+        <v>99.03266053924297</v>
       </c>
       <c r="AG31" s="83" t="n">
-        <v>96.19259994506837</v>
+        <v>96.30579986572266</v>
       </c>
       <c r="AH31" s="83" t="n">
-        <v>104.7443997955322</v>
+        <v>104.8465998077393</v>
       </c>
       <c r="AI31" s="83" t="n">
-        <v>105.0993997573853</v>
+        <v>105.070549736023</v>
       </c>
       <c r="AJ31" s="83" t="n">
-        <v>107.6769134564309</v>
+        <v>108.4119504240334</v>
       </c>
       <c r="AK31" s="83" t="n">
-        <v>98.61349983215332</v>
+        <v>97.9319995880127</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>89.55008620787579</v>
+        <v>87.45204875199201</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.5770406362309468</v>
+        <v>0.9006699255771874</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>18.38168940298044</v>
+        <v>21.40250557551872</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>4.254624645273521</v>
+        <v>3.807500555819707</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -24089,22 +24089,22 @@
         <v>73.19999694824219</v>
       </c>
       <c r="AR31" s="36" t="n">
-        <v>-26.04998663558495</v>
+        <v>-21.37681343378138</v>
       </c>
       <c r="AS31" s="89" t="n">
-        <v>43.21405785844745</v>
+        <v>53.40103210789172</v>
       </c>
       <c r="AT31" s="33" t="n">
-        <v>-0.02438786409035121</v>
+        <v>0.1123549106038293</v>
       </c>
       <c r="AU31" s="33" t="n">
-        <v>0.1335146586319509</v>
+        <v>0.2573016697972415</v>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>-0.1125997795531408</v>
+        <v>-0.03886825932494031</v>
       </c>
       <c r="AW31" s="33" t="n">
-        <v>0.09312498055959506</v>
+        <v>0.1622035666607209</v>
       </c>
       <c r="AX31" s="32" t="n"/>
       <c r="AY31" s="32" t="n"/>
@@ -24121,7 +24121,7 @@
         <v>-0.02960829037404245</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>-0.03392203277851213</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>0.01530903307141895</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>-0.02845037703741871</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>0.01677034764032892</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>-0.002704785444845648</v>
       </c>
       <c r="D39" s="34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E39" s="30" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>-0.04256684013924827</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>-0.03588291869363736</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>-0.04574959589106331</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>0.00193621591207882</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
@@ -26406,19 +26406,19 @@
         </is>
       </c>
       <c r="C45" s="33" t="n">
-        <v>-0.003580509420204936</v>
+        <v>0.006474453644578437</v>
       </c>
       <c r="D45" s="34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
@@ -26457,11 +26457,11 @@
         </is>
       </c>
       <c r="N45" s="80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O45" s="30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="P45" s="32" t="inlineStr">
@@ -26475,76 +26475,76 @@
         </is>
       </c>
       <c r="R45" s="81" t="n">
-        <v>164.1900024414062</v>
+        <v>164.7799987792969</v>
       </c>
       <c r="S45" s="82" t="n">
-        <v>-0.589996337890625</v>
+        <v>1.05999755859375</v>
       </c>
       <c r="T45" s="83" t="n">
-        <v>164.5899963378906</v>
+        <v>165.1600036621094</v>
       </c>
       <c r="U45" s="83" t="n">
-        <v>165.4900054931641</v>
+        <v>166.9499969482422</v>
       </c>
       <c r="V45" s="83" t="n">
-        <v>161.8999938964844</v>
+        <v>161.9199981689453</v>
       </c>
       <c r="W45" s="84" t="n">
-        <v>7752100</v>
+        <v>15065100</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>0.7992943369613185</v>
+        <v>1.506263725880818</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>48.50336989918072</v>
+        <v>49.20875651303804</v>
       </c>
       <c r="Z45" s="35" t="n">
-        <v>74.11548084340996</v>
+        <v>67.64243247321564</v>
       </c>
       <c r="AA45" s="35" t="n">
-        <v>11.75275876428061</v>
+        <v>12.40692899222806</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-2.531618865633021</v>
+        <v>-2.904970548344465</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-3.899643629001076</v>
+        <v>-4.24164981984309</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.368024763368055</v>
+        <v>1.336679271498625</v>
       </c>
       <c r="AE45" s="83" t="n">
-        <v>162.676513177558</v>
+        <v>162.2440876736013</v>
       </c>
       <c r="AF45" s="83" t="n">
-        <v>163.7191224487436</v>
+        <v>163.6720344494773</v>
       </c>
       <c r="AG45" s="83" t="n">
-        <v>173.5131997680664</v>
+        <v>174.4887997436524</v>
       </c>
       <c r="AH45" s="83" t="n">
-        <v>181.4843003082275</v>
+        <v>181.0831002807617</v>
       </c>
       <c r="AI45" s="83" t="n">
-        <v>167.9357498168945</v>
+        <v>167.9726498413086</v>
       </c>
       <c r="AJ45" s="83" t="n">
-        <v>168.5150185229261</v>
+        <v>169.9993277746179</v>
       </c>
       <c r="AK45" s="83" t="n">
-        <v>161.8034996032715</v>
+        <v>160.9744995117188</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>155.0919806836168</v>
+        <v>151.9496712488196</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>0.6777915600554963</v>
+        <v>0.7108349963412831</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>8.295888452488022</v>
+        <v>11.21274275152156</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>3.715080851846692</v>
+        <v>3.81894123578364</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -26553,22 +26553,22 @@
         <v>121.9899978637695</v>
       </c>
       <c r="AR45" s="36" t="n">
-        <v>-36.83056557433734</v>
+        <v>-36.60357407410234</v>
       </c>
       <c r="AS45" s="89" t="n">
-        <v>30.59522933067932</v>
+        <v>31.02297983551198</v>
       </c>
       <c r="AT45" s="33" t="n">
-        <v>0.02139970414560644</v>
+        <v>0.0251337137493417</v>
       </c>
       <c r="AU45" s="33" t="n">
-        <v>0.08304746590375411</v>
+        <v>0.05845327936562317</v>
       </c>
       <c r="AV45" s="33" t="n">
-        <v>-0.3459086939414122</v>
+        <v>-0.3227012892984074</v>
       </c>
       <c r="AW45" s="33" t="n">
-        <v>-0.04010523524092424</v>
+        <v>-0.03665597287691191</v>
       </c>
       <c r="AX45" s="32" t="n"/>
       <c r="AY45" s="32" t="n"/>
@@ -26585,7 +26585,7 @@
         <v>-0.04649784460844808</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>2.022243029231596e-05</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>-0.01707955694679375</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 1 Sep 2026, 08:01 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 10:38 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 1 Sep 2026, 08:01 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 10:38 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -43355,22 +43355,22 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>0.01282050823267267</v>
+        <v>0.01266412711363518</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>0.04382851024519119</v>
+        <v>0.04366734144066098</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>0.1018880382801199</v>
+        <v>0.101717904990875</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>0.1176673533911645</v>
+        <v>0.1174947837502318</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>0.1461429273643715</v>
+        <v>0.1459659610489175</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0.4488928674971575</v>
+        <v>0.4486691561029441</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>9</v>
@@ -43393,25 +43393,25 @@
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.006567435323498572</v>
+        <v>0.006626040385240062</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>-0.02070848173345563</v>
+        <v>-0.02065146474892288</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.05806211692554597</v>
+        <v>0.05812372014606826</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.1725410575050004</v>
+        <v>0.1726093259971631</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>0.09518947075445916</v>
+        <v>0.09525323562931987</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>0.1089147304778435</v>
+        <v>0.1089792944742189</v>
       </c>
       <c r="J7" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" s="102" t="inlineStr">
         <is>
@@ -43422,31 +43422,31 @@
     <row r="8">
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>State Street Technology Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>-0.01138733136760706</v>
+        <v>-0.01533512391609415</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>-0.02780891428792742</v>
+        <v>0.01993888518212716</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>0.03291691131006669</v>
+        <v>0.04727683488781254</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>0.02297725894963065</v>
+        <v>-0.06191252276912107</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>-0.02178403469318513</v>
+        <v>0.316038470871119</v>
       </c>
       <c r="I8" s="26" t="n">
-        <v>0.1486218722215167</v>
+        <v>0.2755435009556748</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>3</v>
@@ -43460,31 +43460,31 @@
     <row r="9">
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>State Street Technology Select Sector SPDR ETF</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D9" s="33" t="n">
-        <v>-0.0151206827035858</v>
+        <v>-0.01176691873304558</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>0.0106745192251585</v>
+        <v>-0.02818219642828157</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.03167827231145903</v>
+        <v>0.03252031290351032</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>-0.07330615784227901</v>
+        <v>0.02258447696842736</v>
       </c>
       <c r="H9" s="33" t="n">
-        <v>0.3358544921875</v>
+        <v>-0.02215963014414613</v>
       </c>
       <c r="I9" s="33" t="n">
-        <v>0.2758212899797334</v>
+        <v>0.1481808477796946</v>
       </c>
       <c r="J9" s="34" t="n">
         <v>3</v>
@@ -43507,22 +43507,22 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>-0.005113939525445588</v>
+        <v>-0.005203676976662464</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>-0.012731484233094</v>
+        <v>-0.01282053459151322</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>0.02448264577032044</v>
+        <v>0.02439023874493351</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>-0.04082692842993119</v>
+        <v>-0.04091344461518909</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>-0.05921780940262167</v>
+        <v>-0.05930266675391893</v>
       </c>
       <c r="I10" s="26" t="n">
-        <v>-0.05801904315520434</v>
+        <v>-0.05810400863368514</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>2</v>
@@ -43545,22 +43545,22 @@
         </is>
       </c>
       <c r="D11" s="33" t="n">
-        <v>0.00341248852291498</v>
+        <v>0.003177178540842984</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>-0.02492853494856073</v>
+        <v>-0.02515719868514421</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.002586638252966456</v>
+        <v>0.002351521940810342</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>0.03949771927324774</v>
+        <v>0.03925394695380402</v>
       </c>
       <c r="H11" s="33" t="n">
-        <v>-0.03877806872853828</v>
+        <v>-0.03900348461482828</v>
       </c>
       <c r="I11" s="33" t="n">
-        <v>0.09770850036138468</v>
+        <v>0.09745107704794687</v>
       </c>
       <c r="J11" s="34" t="n">
         <v>4</v>
@@ -43583,22 +43583,22 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>-0.008664009841139131</v>
+        <v>-0.008837260953456161</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>-0.01886472754092949</v>
+        <v>-0.01903619592195727</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>-0.002962739290310767</v>
+        <v>-0.003136986786774432</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>0.1117372736552376</v>
+        <v>0.1115429805788466</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>0.1171646183805393</v>
+        <v>0.1169693767927253</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0.04454991065027669</v>
+        <v>0.04436735959222227</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>3</v>
@@ -43612,76 +43612,76 @@
     <row r="13">
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>State Street Real Estate Select Sector SPDR ETF</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D13" s="33" t="n">
-        <v>-0.001360266888704942</v>
+        <v>-0.01715413039557678</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>-0.02888010043350975</v>
+        <v>-0.03136100268944209</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.02501109031612336</v>
+        <v>-0.01292100996914591</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>0.01287646670455334</v>
+        <v>-0.03045948074415483</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>0.008009118261112613</v>
+        <v>-0.007191144032421271</v>
       </c>
       <c r="I13" s="33" t="n">
-        <v>0.09169766797667878</v>
+        <v>-0.04036518864749195</v>
       </c>
       <c r="J13" s="34" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="102" t="inlineStr">
         <is>
-          <t>Long-term up, short-term mixed</t>
+          <t>Below every average</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
+          <t>State Street Real Estate Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>-0.01723985393232841</v>
+        <v>-0.001586934796092287</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.028571387913357</v>
+        <v>-0.02910052198109947</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.03070803892675766</v>
+        <v>-0.02523239003869238</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-0.0255973688287805</v>
+        <v>0.01264656739097969</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.001923760226731019</v>
+        <v>0.007780323722013094</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>-0.04044888772235522</v>
+        <v>0.09144987809040117</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="101" t="inlineStr">
         <is>
-          <t>Below every average</t>
+          <t>Long-term up, short-term mixed</t>
         </is>
       </c>
     </row>
@@ -43697,22 +43697,22 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-0.01364700121631179</v>
+        <v>-0.01370415741653974</v>
       </c>
       <c r="E15" s="33" t="n">
-        <v>-0.03497203635103874</v>
+        <v>-0.03502795682939075</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>-0.0394794872625932</v>
+        <v>-0.03953514654767343</v>
       </c>
       <c r="G15" s="33" t="n">
-        <v>0.001972225108568315</v>
+        <v>0.001914163820984971</v>
       </c>
       <c r="H15" s="33" t="n">
-        <v>-0.03443258028775908</v>
+        <v>-0.03448853202597324</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>0.1135895495784749</v>
+        <v>0.1135250204014502</v>
       </c>
       <c r="J15" s="34" t="n">
         <v>2</v>
@@ -43735,22 +43735,22 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>0.008169576709516013</v>
+        <v>0.007814393431963884</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>-0.01492365662994721</v>
+        <v>-0.01527070404375552</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>-0.04002249768322719</v>
+        <v>-0.04036070264747738</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>-0.01218092180436781</v>
+        <v>-0.01252893549762679</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>-0.1012243672591219</v>
+        <v>-0.1015410104929544</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>-0.002693789352749776</v>
+        <v>-0.00304514541109957</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>1</v>
@@ -43972,7 +43972,7 @@
         </is>
       </c>
       <c r="E7" s="33" t="n">
-        <v>0.01282050823267267</v>
+        <v>0.01266412711363518</v>
       </c>
       <c r="F7" s="34" t="n">
         <v>9</v>
@@ -44000,7 +44000,7 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>0.01282050823267267</v>
+        <v>0.01266412711363518</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>9</v>
@@ -44028,7 +44028,7 @@
         </is>
       </c>
       <c r="E9" s="33" t="n">
-        <v>-0.02781345403653102</v>
+        <v>-0.02909895842760113</v>
       </c>
       <c r="F9" s="34" t="n">
         <v>7</v>
@@ -44218,9 +44218,9 @@
           <t>QUALCOMM Incorporated</t>
         </is>
       </c>
-      <c r="D16" s="106" t="inlineStr">
-        <is>
-          <t>Lost the 200 DMA</t>
+      <c r="D16" s="104" t="inlineStr">
+        <is>
+          <t>8 EMA crossed above 21</t>
         </is>
       </c>
       <c r="E16" s="26" t="n">
@@ -44248,7 +44248,7 @@
       </c>
       <c r="D17" s="107" t="inlineStr">
         <is>
-          <t>Gapped down 2.8% at the open</t>
+          <t>Lost the 200 DMA</t>
         </is>
       </c>
       <c r="E17" s="33" t="n">
@@ -44276,7 +44276,7 @@
       </c>
       <c r="D18" s="106" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped down 2.8% at the open</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
@@ -44294,21 +44294,21 @@
     <row r="19">
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="C19" s="102" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>QUALCOMM Incorporated</t>
         </is>
       </c>
       <c r="D19" s="107" t="inlineStr">
         <is>
-          <t>Lost the 50 DMA</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>-0.03223268236356913</v>
+        <v>-0.02270058196958502</v>
       </c>
       <c r="F19" s="34" t="n">
         <v>5</v>
@@ -44332,7 +44332,7 @@
       </c>
       <c r="D20" s="106" t="inlineStr">
         <is>
-          <t>Gapped down 1.9% at the open</t>
+          <t>Lost the 50 DMA</t>
         </is>
       </c>
       <c r="E20" s="26" t="n">
@@ -44350,21 +44350,21 @@
     <row r="21">
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C21" s="102" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="D21" s="107" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Gapped down 1.9% at the open</t>
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>-0.03466040639889967</v>
+        <v>-0.03223268236356913</v>
       </c>
       <c r="F21" s="34" t="n">
         <v>5</v>
@@ -44388,7 +44388,7 @@
       </c>
       <c r="D22" s="106" t="inlineStr">
         <is>
-          <t>Gapped down 1.9% at the open</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E22" s="26" t="n">
@@ -44406,24 +44406,24 @@
     <row r="23">
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C23" s="102" t="inlineStr">
         <is>
-          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="D23" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped down 1.9% at the open</t>
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>0.00341248852291498</v>
+        <v>-0.03466040639889967</v>
       </c>
       <c r="F23" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="30" t="inlineStr">
         <is>
@@ -44434,21 +44434,21 @@
     <row r="24">
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C24" s="101" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D24" s="106" t="inlineStr">
         <is>
-          <t>Gapped down 1.9% at the open</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>-0.0151281653970361</v>
+        <v>0.003177178540842984</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>4</v>
@@ -44472,7 +44472,7 @@
       </c>
       <c r="D25" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped down 1.9% at the open</t>
         </is>
       </c>
       <c r="E25" s="33" t="n">
@@ -44490,49 +44490,49 @@
     <row r="26">
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C26" s="101" t="inlineStr">
         <is>
-          <t>State Street Financial Select Sector SPDR ETF</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D26" s="106" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>-0.008664009841139131</v>
+        <v>-0.0151281653970361</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C27" s="102" t="inlineStr">
         <is>
-          <t>State Street Financial Select Sector SPDR ETF</t>
+          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
         </is>
       </c>
       <c r="D27" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E27" s="33" t="n">
-        <v>-0.008664009841139131</v>
+        <v>-0.006870423805438008</v>
       </c>
       <c r="F27" s="34" t="n">
         <v>3</v>
@@ -44546,21 +44546,21 @@
     <row r="28">
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C28" s="101" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
         </is>
       </c>
       <c r="D28" s="106" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>-0.01138733136760706</v>
+        <v>-0.006870423805438008</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>3</v>
@@ -44574,12 +44574,12 @@
     <row r="29">
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C29" s="102" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>State Street Financial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D29" s="107" t="inlineStr">
@@ -44588,7 +44588,7 @@
         </is>
       </c>
       <c r="E29" s="33" t="n">
-        <v>-0.01138733136760706</v>
+        <v>-0.008837260953456161</v>
       </c>
       <c r="F29" s="34" t="n">
         <v>3</v>
@@ -44602,12 +44602,12 @@
     <row r="30">
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C30" s="101" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>State Street Financial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D30" s="106" t="inlineStr">
@@ -44616,7 +44616,7 @@
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>-0.01138733136760706</v>
+        <v>-0.008837260953456161</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>3</v>
@@ -44630,21 +44630,21 @@
     <row r="31">
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C31" s="102" t="inlineStr">
         <is>
-          <t>State Street Technology Select Sector SPDR ETF</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D31" s="107" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E31" s="33" t="n">
-        <v>-0.0151206827035858</v>
+        <v>-0.01176691873304558</v>
       </c>
       <c r="F31" s="34" t="n">
         <v>3</v>
@@ -44658,21 +44658,21 @@
     <row r="32">
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C32" s="101" t="inlineStr">
         <is>
-          <t>State Street Technology Select Sector SPDR ETF</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D32" s="106" t="inlineStr">
         <is>
-          <t>Gapped down 1.5% at the open</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>-0.0151206827035858</v>
+        <v>-0.01176691873304558</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>3</v>
@@ -44686,21 +44686,21 @@
     <row r="33">
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C33" s="102" t="inlineStr">
         <is>
-          <t>Nokia Oyj</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D33" s="107" t="inlineStr">
         <is>
-          <t>8 EMA crossed below 21</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E33" s="33" t="n">
-        <v>-0.02071006223241978</v>
+        <v>-0.01176691873304558</v>
       </c>
       <c r="F33" s="34" t="n">
         <v>3</v>
@@ -44714,24 +44714,24 @@
     <row r="34">
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C34" s="101" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>State Street Technology Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D34" s="106" t="inlineStr">
         <is>
-          <t>Gapped down 1.6% at the open</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>-0.001782156042112182</v>
+        <v>-0.01533512391609415</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
@@ -44742,24 +44742,24 @@
     <row r="35">
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C35" s="102" t="inlineStr">
         <is>
-          <t>State Street Communication Services Select Sector SPDR ETF</t>
+          <t>State Street Technology Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D35" s="107" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Gapped down 1.5% at the open</t>
         </is>
       </c>
       <c r="E35" s="33" t="n">
-        <v>-0.005113939525445588</v>
+        <v>-0.01533512391609415</v>
       </c>
       <c r="F35" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="30" t="inlineStr">
         <is>
@@ -44770,24 +44770,24 @@
     <row r="36">
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C36" s="101" t="inlineStr">
         <is>
-          <t>State Street Communication Services Select Sector SPDR ETF</t>
+          <t>Nokia Oyj</t>
         </is>
       </c>
       <c r="D36" s="106" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>8 EMA crossed below 21</t>
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>-0.005113939525445588</v>
+        <v>-0.02071006223241978</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
@@ -44798,21 +44798,21 @@
     <row r="37">
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C37" s="102" t="inlineStr">
         <is>
-          <t>State Street Communication Services Select Sector SPDR ETF</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="D37" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped down 1.6% at the open</t>
         </is>
       </c>
       <c r="E37" s="33" t="n">
-        <v>-0.005113939525445588</v>
+        <v>-0.001782156042112182</v>
       </c>
       <c r="F37" s="34" t="n">
         <v>2</v>
@@ -44826,21 +44826,21 @@
     <row r="38">
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C38" s="101" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D38" s="106" t="inlineStr">
         <is>
-          <t>Gapped down 2.9% at the open</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>-0.006032855576357687</v>
+        <v>-0.005203676976662464</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>2</v>
@@ -44854,12 +44854,12 @@
     <row r="39">
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C39" s="102" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D39" s="107" t="inlineStr">
@@ -44868,7 +44868,7 @@
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>-0.006948721953806136</v>
+        <v>-0.005203676976662464</v>
       </c>
       <c r="F39" s="34" t="n">
         <v>2</v>
@@ -44882,12 +44882,12 @@
     <row r="40">
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C40" s="101" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D40" s="106" t="inlineStr">
@@ -44896,7 +44896,7 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>-0.006948721953806136</v>
+        <v>-0.005203676976662464</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>2</v>
@@ -44910,21 +44910,21 @@
     <row r="41">
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C41" s="102" t="inlineStr">
         <is>
-          <t>iShares Russell 2000 ETF</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="D41" s="107" t="inlineStr">
         <is>
-          <t>Closed below lower band</t>
+          <t>Gapped down 2.9% at the open</t>
         </is>
       </c>
       <c r="E41" s="33" t="n">
-        <v>-0.01122712167930684</v>
+        <v>-0.006032855576357687</v>
       </c>
       <c r="F41" s="34" t="n">
         <v>2</v>
@@ -44938,12 +44938,12 @@
     <row r="42">
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C42" s="101" t="inlineStr">
         <is>
-          <t>State Street Industrial Select Sector SPDR ETF</t>
+          <t>iShares Russell 2000 ETF</t>
         </is>
       </c>
       <c r="D42" s="106" t="inlineStr">
@@ -44952,7 +44952,7 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>-0.01364700121631179</v>
+        <v>-0.01143124361340264</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>2</v>
@@ -44966,21 +44966,21 @@
     <row r="43">
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C43" s="102" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Invesco QQQ Trust</t>
         </is>
       </c>
       <c r="D43" s="107" t="inlineStr">
         <is>
-          <t>8 EMA crossed below 21</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>-0.01867032778937106</v>
+        <v>-0.01272391734043543</v>
       </c>
       <c r="F43" s="34" t="n">
         <v>2</v>
@@ -44994,21 +44994,21 @@
     <row r="44">
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C44" s="101" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Invesco QQQ Trust</t>
         </is>
       </c>
       <c r="D44" s="106" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>Lost the 50 DMA</t>
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>-0.01867032778937106</v>
+        <v>-0.01272391734043543</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>2</v>
@@ -45022,21 +45022,21 @@
     <row r="45">
       <c r="B45" s="31" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C45" s="102" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Invesco QQQ Trust</t>
         </is>
       </c>
       <c r="D45" s="107" t="inlineStr">
         <is>
-          <t>Gapped down 1.9% at the open</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E45" s="33" t="n">
-        <v>-0.01867032778937106</v>
+        <v>-0.01272391734043543</v>
       </c>
       <c r="F45" s="34" t="n">
         <v>2</v>
@@ -45050,21 +45050,21 @@
     <row r="46">
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C46" s="101" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>State Street Industrial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D46" s="106" t="inlineStr">
         <is>
-          <t>Gapped down 2.4% at the open</t>
+          <t>Closed below lower band</t>
         </is>
       </c>
       <c r="E46" s="26" t="n">
-        <v>-0.02360217505168549</v>
+        <v>-0.01370415741653974</v>
       </c>
       <c r="F46" s="27" t="n">
         <v>2</v>
@@ -45078,21 +45078,21 @@
     <row r="47">
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C47" s="102" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D47" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>8 EMA crossed below 21</t>
         </is>
       </c>
       <c r="E47" s="33" t="n">
-        <v>-0.02360217505168549</v>
+        <v>-0.01867032778937106</v>
       </c>
       <c r="F47" s="34" t="n">
         <v>2</v>
@@ -45106,21 +45106,21 @@
     <row r="48">
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C48" s="101" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D48" s="106" t="inlineStr">
         <is>
-          <t>Gapped down 3.4% at the open</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E48" s="26" t="n">
-        <v>-0.02930840490496478</v>
+        <v>-0.01867032778937106</v>
       </c>
       <c r="F48" s="27" t="n">
         <v>2</v>
@@ -45134,21 +45134,21 @@
     <row r="49">
       <c r="B49" s="31" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C49" s="102" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D49" s="107" t="inlineStr">
         <is>
-          <t>Volume 1.8x its 20-day average</t>
+          <t>Gapped down 1.9% at the open</t>
         </is>
       </c>
       <c r="E49" s="33" t="n">
-        <v>-0.06940642471933811</v>
+        <v>-0.01867032778937106</v>
       </c>
       <c r="F49" s="34" t="n">
         <v>2</v>
@@ -45162,21 +45162,21 @@
     <row r="50">
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C50" s="101" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="D50" s="106" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>Gapped down 2.4% at the open</t>
         </is>
       </c>
       <c r="E50" s="26" t="n">
-        <v>-0.06940642471933811</v>
+        <v>-0.02360217505168549</v>
       </c>
       <c r="F50" s="27" t="n">
         <v>2</v>
@@ -45190,21 +45190,21 @@
     <row r="51">
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C51" s="102" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="D51" s="107" t="inlineStr">
         <is>
-          <t>Lost the 50 DMA</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E51" s="33" t="n">
-        <v>-0.06940642471933811</v>
+        <v>-0.02360217505168549</v>
       </c>
       <c r="F51" s="34" t="n">
         <v>2</v>
@@ -45218,12 +45218,12 @@
     <row r="52">
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C52" s="101" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
+          <t>Cameco Corporation</t>
         </is>
       </c>
       <c r="D52" s="106" t="inlineStr">
@@ -45232,203 +45232,203 @@
         </is>
       </c>
       <c r="E52" s="26" t="n">
-        <v>-0.01272391734043543</v>
+        <v>-0.02531389171652176</v>
       </c>
       <c r="F52" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="31" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C53" s="102" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
+          <t>Cameco Corporation</t>
         </is>
       </c>
       <c r="D53" s="107" t="inlineStr">
         <is>
-          <t>Lost the 50 DMA</t>
+          <t>Gapped down 2.8% at the open</t>
         </is>
       </c>
       <c r="E53" s="33" t="n">
-        <v>-0.01272391734043543</v>
+        <v>-0.02531389171652176</v>
       </c>
       <c r="F53" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C54" s="101" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="D54" s="106" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped down 3.4% at the open</t>
         </is>
       </c>
       <c r="E54" s="26" t="n">
-        <v>-0.01272391734043543</v>
+        <v>-0.02930840490496478</v>
       </c>
       <c r="F54" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="31" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C55" s="102" t="inlineStr">
         <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
+          <t>Nebius Group N.V.</t>
         </is>
       </c>
       <c r="D55" s="107" t="inlineStr">
         <is>
-          <t>8 EMA crossed below 21</t>
+          <t>Gapped down 3.5% at the open</t>
         </is>
       </c>
       <c r="E55" s="33" t="n">
-        <v>-0.01723985393232841</v>
+        <v>-0.03286164112737533</v>
       </c>
       <c r="F55" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C56" s="101" t="inlineStr">
         <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D56" s="106" t="inlineStr">
         <is>
-          <t>Closed below lower band</t>
+          <t>Volume 2.6x its 20-day average</t>
         </is>
       </c>
       <c r="E56" s="26" t="n">
-        <v>-0.01723985393232841</v>
+        <v>-0.06800291463242925</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="31" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C57" s="102" t="inlineStr">
         <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D57" s="107" t="inlineStr">
         <is>
-          <t>Lost the 50 DMA</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E57" s="33" t="n">
-        <v>-0.01723985393232841</v>
+        <v>-0.06800291463242925</v>
       </c>
       <c r="F57" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C58" s="101" t="inlineStr">
         <is>
-          <t>Cameco Corporation</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D58" s="106" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Lost the 50 DMA</t>
         </is>
       </c>
       <c r="E58" s="26" t="n">
-        <v>-0.02490886017883343</v>
+        <v>-0.06800291463242925</v>
       </c>
       <c r="F58" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="31" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C59" s="102" t="inlineStr">
         <is>
-          <t>Cameco Corporation</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D59" s="107" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>8 EMA crossed below 21</t>
         </is>
       </c>
       <c r="E59" s="33" t="n">
-        <v>-0.02490886017883343</v>
+        <v>-0.01715413039557678</v>
       </c>
       <c r="F59" s="34" t="n">
         <v>1</v>
@@ -45442,21 +45442,21 @@
     <row r="60">
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C60" s="101" t="inlineStr">
         <is>
-          <t>Cameco Corporation</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D60" s="106" t="inlineStr">
         <is>
-          <t>Gapped down 2.8% at the open</t>
+          <t>Closed below lower band</t>
         </is>
       </c>
       <c r="E60" s="26" t="n">
-        <v>-0.02490886017883343</v>
+        <v>-0.01715413039557678</v>
       </c>
       <c r="F60" s="27" t="n">
         <v>1</v>
@@ -45470,21 +45470,21 @@
     <row r="61">
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C61" s="102" t="inlineStr">
         <is>
-          <t>Nebius Group N.V.</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D61" s="107" t="inlineStr">
         <is>
-          <t>Gapped down 3.5% at the open</t>
+          <t>Lost the 50 DMA</t>
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>-0.03286164112737533</v>
+        <v>-0.01715413039557678</v>
       </c>
       <c r="F61" s="34" t="n">
         <v>1</v>
@@ -45540,7 +45540,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>-0.06246119435907782</v>
+        <v>-0.06099829060707829</v>
       </c>
       <c r="F63" s="34" t="n">
         <v>1</v>
@@ -45568,7 +45568,7 @@
         </is>
       </c>
       <c r="E64" s="26" t="n">
-        <v>-0.06246119435907782</v>
+        <v>-0.06099829060707829</v>
       </c>
       <c r="F64" s="27" t="n">
         <v>1</v>
@@ -45596,7 +45596,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>-0.06246119435907782</v>
+        <v>-0.06099829060707829</v>
       </c>
       <c r="F65" s="34" t="n">
         <v>1</v>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 1 Sep 2026, 10:38 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 1 Sep 2026, 11:17 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1628,16 +1628,16 @@
         <v>4</v>
       </c>
       <c r="G17" s="35" t="n">
-        <v>48.9318172316673</v>
+        <v>48.94633859203591</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>0.4105939432430761</v>
+        <v>0.3333067427351732</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>-0.02515719868514421</v>
+        <v>-0.01467864877879865</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>0.002351521940810342</v>
+        <v>0.004595797629547427</v>
       </c>
     </row>
     <row r="18">
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="F47" s="28" t="n">
-        <v>48.9318172316673</v>
+        <v>48.94633859203591</v>
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 1 Sep 2026, 10:38 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 11:17 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -4383,58 +4383,58 @@
         <v>9238776</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>1.048007388931834</v>
+        <v>1.087833876780699</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>48.9318172316673</v>
+        <v>48.94633859203591</v>
       </c>
       <c r="Z11" s="28" t="n">
-        <v>35.83809803113058</v>
+        <v>22.9167549696944</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>15.76101063524304</v>
+        <v>14.9702235353203</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.1865988883489678</v>
+        <v>0.1464442725417143</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.3005447210037976</v>
+        <v>0.2757090788078762</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.1139458326548298</v>
+        <v>-0.1292648062661618</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>85.61741899815361</v>
+        <v>85.55228582561726</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.5429222476041</v>
+        <v>85.52929049436101</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>84.90139999389649</v>
+        <v>84.96679992675782</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.26700012207031</v>
+        <v>84.28700012207031</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.16500022888184</v>
+        <v>83.20565021514892</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>86.98105359710452</v>
+        <v>86.98321531696089</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.57000007629395</v>
+        <v>85.57399978637696</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>84.15894655548338</v>
+        <v>84.16478425579302</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.3866095185000036</v>
+        <v>0.3850425008292723</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.298009862223858</v>
+        <v>3.293560039502272</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.395424253334772</v>
+        <v>1.351383848292627</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -4449,13 +4449,13 @@
         <v>67.35647006454938</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-0.02515719868514421</v>
+        <v>-0.01467864877879865</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>0.002351521940810342</v>
+        <v>0.004595797629547427</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.03925394695380402</v>
+        <v>0.04179393978269985</v>
       </c>
       <c r="AW11" s="26" t="n">
         <v>0.09745107704794687</v>
@@ -5222,17 +5222,17 @@
       </c>
       <c r="AX15" s="79" t="inlineStr">
         <is>
+          <t>Better Tech ETF for Artificial Intelligence: Vanguard's VGT with Broad Exposure or State Street XLK's Conce...</t>
+        </is>
+      </c>
+      <c r="AY15" s="79" t="inlineStr">
+        <is>
           <t>Stock Market News for Sep 1, 2026</t>
         </is>
       </c>
-      <c r="AY15" s="79" t="inlineStr">
+      <c r="AZ15" s="79" t="inlineStr">
         <is>
           <t>Sector Update: Tech Stocks Gain Late Afternoon</t>
-        </is>
-      </c>
-      <c r="AZ15" s="79" t="inlineStr">
-        <is>
-          <t>Sector Update: Tech Stocks Gain Thursday Afternoon</t>
         </is>
       </c>
     </row>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="AY26" s="79" t="inlineStr">
         <is>
-          <t>FTC alleges Amazon overcharged advertisers for years</t>
+          <t>Suzelle Snowden Started With One Class on the Beach 30 years ago, Now She's Running the World's Largest Fit...</t>
         </is>
       </c>
       <c r="AZ26" s="79" t="inlineStr">
         <is>
-          <t>Amazon's $69 Billion Ad Machine Just Ran Into a $20 Billion Problem</t>
+          <t>Whirlpool (WHR) Dips More Than Broader Market: What You Should Know</t>
         </is>
       </c>
     </row>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
+          <t>Broadcom's earnings loom, but this reveal came first</t>
+        </is>
+      </c>
+      <c r="AY30" s="79" t="inlineStr">
+        <is>
           <t>28 Analysts Share Their Broadcom Stock Forecast Before Q3 Earnings</t>
         </is>
       </c>
-      <c r="AY30" s="79" t="inlineStr">
+      <c r="AZ30" s="79" t="inlineStr">
         <is>
           <t>Two Stocks That Will Benefit From OpenAI Announcement</t>
-        </is>
-      </c>
-      <c r="AZ30" s="79" t="inlineStr">
-        <is>
-          <t>Broadcom Faces Crucial Earnings Test After AI Chip Sales Surge 143%</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="AZ33" s="90" t="inlineStr">
         <is>
-          <t>CEO Michael Dell Just Delivered Fantastic News for Dell Shareholders</t>
+          <t>Dow Jones Futures: Market Breaks Key Levels As Oil Prices Jump; Dell, Credo, Palo Alto Are Earnings Movers</t>
         </is>
       </c>
     </row>
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
+          <t>Google prepares Gemini 3.8 Flash to narrow AI coding gap, WSJ reports</t>
+        </is>
+      </c>
+      <c r="AY34" s="79" t="inlineStr">
+        <is>
           <t>Stock Market Today, Sept. 1: Fervo Energy Surges 28% on 396-Megawatt Google Power Deal</t>
         </is>
       </c>
-      <c r="AY34" s="79" t="inlineStr">
+      <c r="AZ34" s="79" t="inlineStr">
         <is>
           <t>FRVO Stock Clocks Best Day In A Month After Google Deal: Analyst Says Agreement Arrived Earlier Than Expected</t>
-        </is>
-      </c>
-      <c r="AZ34" s="79" t="inlineStr">
-        <is>
-          <t>Google Just Locked In Nearly 1 Gigawatt of Geothermal Power</t>
         </is>
       </c>
     </row>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="AX37" s="90" t="inlineStr">
         <is>
-          <t>MDB Stock Dives After-Hours Despite Raised Full-Year Forecast — What’s Driving The Selloff?</t>
+          <t>Dow Jones Futures: Market Breaks Key Levels As Oil Prices Jump; Dell, Credo, Palo Alto Are Earnings Movers</t>
         </is>
       </c>
       <c r="AY37" s="90" t="inlineStr">
         <is>
-          <t>MongoDB Inc. Q2 2027 Earnings: Recap of $MDB Earnings, Forecast</t>
+          <t>Market Chatter: Dropbox Accounts Breached In Hack Affecting About 5,000 Users</t>
         </is>
       </c>
       <c r="AZ37" s="90" t="inlineStr">
         <is>
-          <t>Box (BOX) Q2 2027 Earnings Call Transcript</t>
+          <t>MongoDB Q2 Earnings Call Highlights</t>
         </is>
       </c>
     </row>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
+          <t>Not Nvidia. Not OpenAI. This Artificial Intelligence (AI) Stock Will Be the Ultimate Winner.</t>
+        </is>
+      </c>
+      <c r="AY43" s="90" t="inlineStr">
+        <is>
+          <t>Nvidia was just the beginning — Here are AI’s next big winners</t>
+        </is>
+      </c>
+      <c r="AZ43" s="90" t="inlineStr">
+        <is>
           <t>Nvidia Shareholders Should Brace Themselves for 1 Particular Thing in the Months to Come. Here’s What It Me...</t>
-        </is>
-      </c>
-      <c r="AY43" s="90" t="inlineStr">
-        <is>
-          <t>CEO Michael Dell Just Delivered Fantastic News for Dell Shareholders</t>
-        </is>
-      </c>
-      <c r="AZ43" s="90" t="inlineStr">
-        <is>
-          <t>28 Analysts Share Their Broadcom Stock Forecast Before Q3 Earnings</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 1 Sep 2026, 10:38 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 11:17 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -12253,7 +12253,7 @@
         <v>-0.003622402212613562</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
@@ -12784,10 +12784,10 @@
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>-0.001175346403020305</v>
+        <v>-0.005500217765873949</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
@@ -12835,7 +12835,7 @@
         </is>
       </c>
       <c r="N11" s="69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" s="23" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>84.98000335693359</v>
       </c>
       <c r="S11" s="71" t="n">
-        <v>-0.09999847412109375</v>
+        <v>-0.4699935913085938</v>
       </c>
       <c r="T11" s="72" t="n">
         <v>85.34999847412109</v>
@@ -12871,58 +12871,58 @@
         <v>7012600</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>0.7806306180947875</v>
+        <v>0.8066036460840454</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>47.47290145839173</v>
+        <v>47.48693481569663</v>
       </c>
       <c r="Z11" s="28" t="n">
         <v>28.03472477944208</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>15.92319707054252</v>
+        <v>15.16847015679679</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.2418924086119318</v>
+        <v>0.1940077921954639</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.329031179167505</v>
+        <v>0.3080252803744166</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.08713877055557318</v>
+        <v>-0.1140174881789527</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>85.72239585476893</v>
+        <v>85.63865320436504</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.57221447236451</v>
+        <v>85.55721954379712</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>84.86240005493164</v>
+        <v>84.90539993286133</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.24230010986328</v>
+        <v>84.26900009155274</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.12590023040771</v>
+        <v>83.16600021362305</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>86.98921164214956</v>
+        <v>86.98466080490893</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.55050010681153</v>
+        <v>85.57999992370605</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>84.1117885714735</v>
+        <v>84.17533904250318</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.3017334483441489</v>
+        <v>0.286426540810812</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.363420514296864</v>
+        <v>3.282684932122265</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.400726645825778</v>
+        <v>1.353147829686729</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -12937,13 +12937,13 @@
         <v>65.55408875565456</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-0.01174548821871158</v>
+        <v>-0.02824463896517315</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>-0.005732980657204401</v>
+        <v>-0.0008230416497647663</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.02496682672045547</v>
+        <v>0.03596250910077115</v>
       </c>
       <c r="AW11" s="26" t="n">
         <v>0.09397532213026283</v>
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 1 Sep 2026, 10:38 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 11:17 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19604,12 +19604,12 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>14 of 40</t>
+          <t>15 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>26 of 40</t>
+          <t>25 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
@@ -20011,7 +20011,7 @@
         <v>-0.008539388474021248</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>-0.002447827045478523</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>0.003800922632101411</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
@@ -20720,19 +20720,19 @@
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>-0.01379384326320543</v>
+        <v>0.004348790658493584</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -20789,76 +20789,76 @@
         </is>
       </c>
       <c r="R11" s="70" t="n">
-        <v>85.08000183105469</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="S11" s="71" t="n">
-        <v>-1.189994812011719</v>
+        <v>0.3699951171875</v>
       </c>
       <c r="T11" s="72" t="n">
-        <v>85.30999755859375</v>
+        <v>85.5</v>
       </c>
       <c r="U11" s="72" t="n">
-        <v>85.86000061035156</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="V11" s="72" t="n">
-        <v>85.06999969482422</v>
+        <v>85.20999908447266</v>
       </c>
       <c r="W11" s="73" t="n">
-        <v>8492100</v>
+        <v>6807200</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>0.9228772958231383</v>
+        <v>0.758633140829468</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>47.94394812605087</v>
+        <v>49.78740689917412</v>
       </c>
       <c r="Z11" s="28" t="n">
-        <v>30.92485485403817</v>
+        <v>41.61835818032277</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>16.73591344057998</v>
+        <v>16.06676903557024</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.3364391794618058</v>
+        <v>0.2793847748701808</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.3508158718063983</v>
+        <v>0.3365296524191548</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.01437669234459249</v>
+        <v>-0.05714487754897402</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>85.9345079970076</v>
+        <v>85.82683887505974</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.6314355839076</v>
+        <v>85.61494116248348</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>84.83639999389648</v>
+        <v>84.87179992675782</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.20510009765626</v>
+        <v>84.24700004577636</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.08315021514892</v>
+        <v>83.12825019836426</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>86.9874742051806</v>
+        <v>86.98984187178345</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.55400009155274</v>
+        <v>85.57399978637696</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>84.12052597792487</v>
+        <v>84.15815770097046</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.3346680083052058</v>
+        <v>0.4562088034347526</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.351039371844408</v>
+        <v>3.309047348355667</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.466016456168893</v>
+        <v>1.399709783339811</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -20867,22 +20867,22 @@
         <v>75.16000366210938</v>
       </c>
       <c r="AR11" s="29" t="n">
-        <v>-5.613487456019262</v>
+        <v>-5.203020271980218</v>
       </c>
       <c r="AS11" s="78" t="n">
-        <v>66.22163550226182</v>
+        <v>68.6915635577639</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-0.002812914493998675</v>
+        <v>-0.006279810779654227</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>-0.02609888694330786</v>
+        <v>-0.0002340502185004256</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.007698703346315838</v>
+        <v>0.03063554666435997</v>
       </c>
       <c r="AW11" s="26" t="n">
-        <v>0.09526263512882416</v>
+        <v>0.1000257030450693</v>
       </c>
       <c r="AX11" s="25" t="n"/>
       <c r="AY11" s="25" t="n"/>
@@ -20901,7 +20901,7 @@
         <v>-0.01092528481292099</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>-0.01065622006694034</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>-0.008198223248004122</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>-0.004030459153398613</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>-0.007584418043843133</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 1 Sep 2026, 10:38 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 11:17 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 1 Sep 2026, 10:38 PM · Yahoo Finance data</t>
+          <t>Built 1 Sep 2026, 11:17 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -43548,16 +43548,16 @@
         <v>0.003177178540842984</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>-0.02515719868514421</v>
+        <v>-0.01467864877879865</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.002351521940810342</v>
+        <v>0.004595797629547427</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>0.03925394695380402</v>
+        <v>0.04179393978269985</v>
       </c>
       <c r="H11" s="33" t="n">
-        <v>-0.03900348461482828</v>
+        <v>-0.0283792788282905</v>
       </c>
       <c r="I11" s="33" t="n">
         <v>0.09745107704794687</v>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'08-28'!$5:$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'08-27'!$A$6:$AZ$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'08-27'!$5:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1299,7 +1299,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 2 Sep 2026, 07:58 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 2 Sep 2026, 10:41 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1366,21 +1366,21 @@
     <row r="8" ht="32" customHeight="1">
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="P8" s="10" t="n"/>
       <c r="Q8" s="16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R8" s="12" t="n"/>
@@ -1520,22 +1520,22 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>0.0181486402988813</v>
+        <v>0.01690034709569455</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>7</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>54.4958190400969</v>
+        <v>54.05040407002677</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>2.470779088672836</v>
+        <v>2.347717249193892</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>-0.01054502467520968</v>
+        <v>-0.01175813823414407</v>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.03930604066044152</v>
+        <v>0.03803180759147962</v>
       </c>
     </row>
     <row r="15">
@@ -1553,22 +1553,22 @@
         </is>
       </c>
       <c r="E15" s="33" t="n">
-        <v>0.01424965611645512</v>
+        <v>0.0138888974898479</v>
       </c>
       <c r="F15" s="34" t="n">
         <v>6</v>
       </c>
       <c r="G15" s="35" t="n">
-        <v>53.93611763104145</v>
+        <v>54.72608401943974</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>1.937223681780997</v>
+        <v>2.007482729214516</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>-0.001332044446016312</v>
+        <v>-0.006714986165234249</v>
       </c>
       <c r="J15" s="33" t="n">
-        <v>0.003748644818933666</v>
+        <v>0.00970003472765657</v>
       </c>
     </row>
     <row r="16">
@@ -1586,22 +1586,22 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>0.008216737757639647</v>
+        <v>0.008041941928971008</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>5</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>52.82552367269125</v>
+        <v>52.72957425128689</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>1.766753697368784</v>
+        <v>1.749469306764473</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>-0.01012701973199037</v>
+        <v>-0.0102986352799006</v>
       </c>
       <c r="J16" s="26" t="n">
-        <v>-0.003628246290506842</v>
+        <v>-0.003800988539102157</v>
       </c>
     </row>
     <row r="17">
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="E17" s="33" t="n">
-        <v>0.007805652427233634</v>
+        <v>0.007456158868465623</v>
       </c>
       <c r="F17" s="34" t="n">
         <v>7</v>
       </c>
       <c r="G17" s="35" t="n">
-        <v>60.71026441711535</v>
+        <v>60.59214890511474</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>4.845265156166634</v>
+        <v>4.809668370252562</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>-0.003054044023287572</v>
+        <v>-0.003399771584166378</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>0.06730405917661275</v>
+        <v>0.06693393236393752</v>
       </c>
     </row>
     <row r="18">
@@ -1652,22 +1652,22 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>0.004863400613437818</v>
+        <v>0.005094979900543306</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>8</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>71.61650998925876</v>
+        <v>71.66578309253622</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>10.72210307164094</v>
+        <v>10.74705473555622</v>
       </c>
       <c r="I18" s="26" t="n">
-        <v>0.04252761118562365</v>
+        <v>0.04276787050926778</v>
       </c>
       <c r="J18" s="26" t="n">
-        <v>0.1121838444182381</v>
+        <v>0.1124401566111826</v>
       </c>
     </row>
     <row r="19">
@@ -1685,22 +1685,22 @@
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>0.003636334998167179</v>
+        <v>0.003284443158907635</v>
       </c>
       <c r="F19" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="35" t="n">
-        <v>50.6273939748334</v>
+        <v>50.46824785757966</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>0.6955449870581498</v>
+        <v>0.6609502075595408</v>
       </c>
       <c r="I19" s="33" t="n">
-        <v>-0.01109569026491164</v>
+        <v>-0.0114424168074545</v>
       </c>
       <c r="J19" s="33" t="n">
-        <v>0.008248844487479312</v>
+        <v>0.007895335424539018</v>
       </c>
     </row>
     <row r="20">
@@ -1709,31 +1709,31 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
+          <t>State Street Utilities Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0.002399873764442839</v>
+        <v>0.002584511092692976</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>43.55084638096561</v>
+        <v>38.17497212155799</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>-1.081376322970073</v>
+        <v>-4.311052907273593</v>
       </c>
       <c r="I20" s="26" t="n">
-        <v>-0.0261551434022198</v>
+        <v>-0.01477726123417744</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>-0.0282971089299543</v>
+        <v>-0.03809743954358469</v>
       </c>
     </row>
     <row r="21">
@@ -1742,31 +1742,31 @@
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="D21" s="32" t="inlineStr">
         <is>
-          <t>State Street Utilities Select Sector SPDR ETF</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>0.001409717026733981</v>
+        <v>0.002356263906883926</v>
       </c>
       <c r="F21" s="34" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>37.51473300697274</v>
+        <v>43.53170083284979</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>-4.421034567480464</v>
+        <v>-1.085594686590152</v>
       </c>
       <c r="I21" s="33" t="n">
-        <v>-0.01593171137213978</v>
+        <v>-0.02619751096090783</v>
       </c>
       <c r="J21" s="33" t="n">
-        <v>-0.03922456389824214</v>
+        <v>-0.02833938330146835</v>
       </c>
     </row>
     <row r="22">
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>0.0002316247664648774</v>
+        <v>0.0002894867885985253</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>30.5574044727401</v>
+        <v>30.59156978165758</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>-4.809285506857286</v>
+        <v>-4.803883697477406</v>
       </c>
       <c r="I22" s="26" t="n">
-        <v>-0.03155823888250919</v>
+        <v>-0.03150221586021174</v>
       </c>
       <c r="J22" s="26" t="n">
-        <v>-0.0567263550006023</v>
+        <v>-0.05667178791916472</v>
       </c>
     </row>
     <row r="23">
@@ -1817,22 +1817,22 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>-0.0005717475925072213</v>
+        <v>-0.0002177809097458905</v>
       </c>
       <c r="F23" s="34" t="n">
         <v>2</v>
       </c>
       <c r="G23" s="35" t="n">
-        <v>49.60805321927165</v>
+        <v>49.7084196689224</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>0.5873525669384927</v>
+        <v>0.622260574529121</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>0.009876736627549176</v>
+        <v>0.01023440384137952</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>0.03086391026282165</v>
+        <v>0.03122901048668969</v>
       </c>
     </row>
     <row r="24">
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>-0.006244357860173189</v>
+        <v>-0.007039086440657094</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>35.48518388683048</v>
+        <v>35.14802343309778</v>
       </c>
       <c r="H24" s="29" t="n">
-        <v>-2.456802151979887</v>
+        <v>-2.533288999343486</v>
       </c>
       <c r="I24" s="26" t="n">
-        <v>-0.0293856899191739</v>
+        <v>-0.03016191185959682</v>
       </c>
       <c r="J24" s="26" t="n">
-        <v>-0.0311046897553966</v>
+        <v>-0.03187953697326018</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C29" s="26" t="n">
-        <v>0.1560941090303309</v>
+        <v>0.1581176757812499</v>
       </c>
       <c r="D29" s="27" t="n">
         <v>8</v>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="F29" s="28" t="n">
-        <v>58.72595100645445</v>
+        <v>58.85987553832133</v>
       </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>-0.01246177962225503</v>
+        <v>-0.01124005114350968</v>
       </c>
       <c r="J29" s="27" t="n">
         <v>0</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="L29" s="28" t="n">
-        <v>41.6720250020694</v>
+        <v>41.76587281159821</v>
       </c>
     </row>
     <row r="30">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="C30" s="33" t="n">
-        <v>0.03136493740275537</v>
+        <v>0.03205482497444945</v>
       </c>
       <c r="D30" s="34" t="n">
         <v>8</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F30" s="35" t="n">
-        <v>56.57742953109358</v>
+        <v>56.67062689432778</v>
       </c>
       <c r="H30" s="31" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="I30" s="33" t="n">
-        <v>-0.007425327774216117</v>
+        <v>-0.006600309699600682</v>
       </c>
       <c r="J30" s="34" t="n">
         <v>1</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="L30" s="35" t="n">
-        <v>41.98284966517424</v>
+        <v>42.128064745238</v>
       </c>
     </row>
     <row r="31">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="C31" s="26" t="n">
-        <v>0.02398656002515054</v>
+        <v>0.02425438655856049</v>
       </c>
       <c r="D31" s="27" t="n">
         <v>8</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="F31" s="28" t="n">
-        <v>53.19994723339119</v>
+        <v>53.2289583279718</v>
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>-0.006331396699976732</v>
+        <v>-0.005548155771720742</v>
       </c>
       <c r="J31" s="27" t="n">
         <v>1</v>
@@ -2049,17 +2049,17 @@
         </is>
       </c>
       <c r="L31" s="28" t="n">
-        <v>42.89514686212071</v>
+        <v>42.98115350769675</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C32" s="33" t="n">
-        <v>0.004863400613437818</v>
+        <v>0.0237595081839681</v>
       </c>
       <c r="D32" s="34" t="n">
         <v>8</v>
@@ -2070,15 +2070,15 @@
         </is>
       </c>
       <c r="F32" s="35" t="n">
-        <v>71.61650998925876</v>
+        <v>63.8893141682433</v>
       </c>
       <c r="H32" s="31" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="I32" s="33" t="n">
-        <v>-0.006244357860173189</v>
+        <v>0.002356263906883926</v>
       </c>
       <c r="J32" s="34" t="n">
         <v>1</v>
@@ -2089,28 +2089,28 @@
         </is>
       </c>
       <c r="L32" s="35" t="n">
-        <v>35.48518388683048</v>
+        <v>43.53170083284979</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
-        <v>0.02394512122816539</v>
+        <v>0.005094979900543306</v>
       </c>
       <c r="D33" s="27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Very Strong</t>
         </is>
       </c>
       <c r="F33" s="28" t="n">
-        <v>63.92054859576306</v>
+        <v>71.66578309253622</v>
       </c>
       <c r="H33" s="24" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>0.001409717026733981</v>
+        <v>0.002584511092692976</v>
       </c>
       <c r="J33" s="27" t="n">
         <v>1</v>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="L33" s="28" t="n">
-        <v>37.51473300697274</v>
+        <v>38.17497212155799</v>
       </c>
     </row>
     <row r="34">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C34" s="33" t="n">
-        <v>0.0201668603207652</v>
+        <v>0.02010687288424085</v>
       </c>
       <c r="D34" s="34" t="n">
         <v>7</v>
@@ -2150,15 +2150,15 @@
         </is>
       </c>
       <c r="F34" s="35" t="n">
-        <v>54.40531156514164</v>
+        <v>54.39558251894007</v>
       </c>
       <c r="H34" s="31" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>SOXL</t>
         </is>
       </c>
       <c r="I34" s="33" t="n">
-        <v>0.002399873764442839</v>
+        <v>0.004154421648548512</v>
       </c>
       <c r="J34" s="34" t="n">
         <v>1</v>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="L34" s="35" t="n">
-        <v>43.55084638096561</v>
+        <v>39.07870188155146</v>
       </c>
     </row>
     <row r="35">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="C35" s="26" t="n">
-        <v>0.0181486402988813</v>
+        <v>0.01690034709569455</v>
       </c>
       <c r="D35" s="27" t="n">
         <v>7</v>
@@ -2190,15 +2190,15 @@
         </is>
       </c>
       <c r="F35" s="28" t="n">
-        <v>54.4958190400969</v>
+        <v>54.05040407002677</v>
       </c>
       <c r="H35" s="24" t="inlineStr">
         <is>
-          <t>SOXL</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>0.003021430306481054</v>
+        <v>0.005270608096960672</v>
       </c>
       <c r="J35" s="27" t="n">
         <v>1</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="L35" s="28" t="n">
-        <v>39.0111574244058</v>
+        <v>41.85444003414893</v>
       </c>
     </row>
     <row r="36">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C36" s="33" t="n">
-        <v>0.012089478038948</v>
+        <v>0.01075564579267785</v>
       </c>
       <c r="D36" s="34" t="n">
         <v>7</v>
@@ -2230,26 +2230,26 @@
         </is>
       </c>
       <c r="F36" s="35" t="n">
-        <v>52.59881195474022</v>
+        <v>52.49743744689197</v>
       </c>
       <c r="H36" s="31" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="I36" s="33" t="n">
-        <v>0.005270608096960672</v>
+        <v>-0.009063459196570256</v>
       </c>
       <c r="J36" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="L36" s="35" t="n">
-        <v>41.85444003414893</v>
+        <v>43.74717551038872</v>
       </c>
     </row>
     <row r="37">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="C37" s="26" t="n">
-        <v>0.007805652427233634</v>
+        <v>0.007456158868465623</v>
       </c>
       <c r="D37" s="27" t="n">
         <v>7</v>
@@ -2270,15 +2270,15 @@
         </is>
       </c>
       <c r="F37" s="28" t="n">
-        <v>60.71026441711535</v>
+        <v>60.59214890511474</v>
       </c>
       <c r="H37" s="24" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>-0.007552946690279616</v>
+        <v>-0.007039086440657094</v>
       </c>
       <c r="J37" s="27" t="n">
         <v>2</v>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="L37" s="28" t="n">
-        <v>43.9297661187968</v>
+        <v>35.14802343309778</v>
       </c>
     </row>
     <row r="38">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="C38" s="33" t="n">
-        <v>0.003911855333165182</v>
+        <v>0.003731313815136028</v>
       </c>
       <c r="D38" s="34" t="n">
         <v>7</v>
@@ -2310,15 +2310,15 @@
         </is>
       </c>
       <c r="F38" s="35" t="n">
-        <v>54.29465561037647</v>
+        <v>54.26467799669614</v>
       </c>
       <c r="H38" s="31" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="I38" s="33" t="n">
-        <v>-0.0006668687045597865</v>
+        <v>-0.0002177809097458905</v>
       </c>
       <c r="J38" s="34" t="n">
         <v>2</v>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="L38" s="35" t="n">
-        <v>46.19588710679039</v>
+        <v>49.7084196689224</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="C43" s="26" t="n">
-        <v>0.1560941090303309</v>
+        <v>0.1581176757812499</v>
       </c>
       <c r="D43" s="27" t="n">
         <v>8</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="F43" s="28" t="n">
-        <v>58.72595100645445</v>
+        <v>58.85987553832133</v>
       </c>
       <c r="H43" s="24" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="I43" s="26" t="n">
-        <v>-0.05844263837627894</v>
+        <v>-0.0581369028542128</v>
       </c>
       <c r="J43" s="27" t="n">
         <v>4</v>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="L43" s="28" t="n">
-        <v>52.15864999100307</v>
+        <v>52.20170484253993</v>
       </c>
     </row>
     <row r="44">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="C44" s="33" t="n">
-        <v>0.1177867782454238</v>
+        <v>0.1182796125279308</v>
       </c>
       <c r="D44" s="34" t="n">
         <v>3</v>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="F44" s="35" t="n">
-        <v>47.19011437480498</v>
+        <v>47.22465818876867</v>
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="I44" s="33" t="n">
-        <v>-0.01485422620385501</v>
+        <v>-0.01353295042585745</v>
       </c>
       <c r="J44" s="34" t="n">
         <v>5</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="L44" s="35" t="n">
-        <v>57.52674939889583</v>
+        <v>57.65496680563243</v>
       </c>
     </row>
     <row r="45">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="C45" s="26" t="n">
-        <v>0.07509504108000065</v>
+        <v>0.07550241179626238</v>
       </c>
       <c r="D45" s="27" t="n">
         <v>3</v>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="F45" s="28" t="n">
-        <v>48.59992158304607</v>
+        <v>48.62675899852136</v>
       </c>
       <c r="H45" s="24" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="I45" s="26" t="n">
-        <v>-0.01246177962225503</v>
+        <v>-0.01124005114350968</v>
       </c>
       <c r="J45" s="27" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="L45" s="28" t="n">
-        <v>41.6720250020694</v>
+        <v>41.76587281159821</v>
       </c>
     </row>
     <row r="46">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="C46" s="33" t="n">
-        <v>0.03136493740275537</v>
+        <v>0.03205482497444945</v>
       </c>
       <c r="D46" s="34" t="n">
         <v>8</v>
@@ -2534,26 +2534,26 @@
         </is>
       </c>
       <c r="F46" s="35" t="n">
-        <v>56.57742953109358</v>
+        <v>56.67062689432778</v>
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="I46" s="33" t="n">
-        <v>-0.008682239593875374</v>
+        <v>-0.009063459196570256</v>
       </c>
       <c r="J46" s="34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K46" s="30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="L46" s="35" t="n">
-        <v>60.7354146789976</v>
+        <v>43.74717551038872</v>
       </c>
     </row>
     <row r="47">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="C47" s="26" t="n">
-        <v>0.02398656002515054</v>
+        <v>0.02425438655856049</v>
       </c>
       <c r="D47" s="27" t="n">
         <v>8</v>
@@ -2574,26 +2574,26 @@
         </is>
       </c>
       <c r="F47" s="28" t="n">
-        <v>53.19994723339119</v>
+        <v>53.2289583279718</v>
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="I47" s="26" t="n">
-        <v>-0.007552946690279616</v>
+        <v>-0.008382862523551915</v>
       </c>
       <c r="J47" s="27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K47" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="L47" s="28" t="n">
-        <v>43.9297661187968</v>
+        <v>60.83443647725979</v>
       </c>
     </row>
     <row r="48">
@@ -2603,37 +2603,37 @@
         </is>
       </c>
       <c r="C48" s="33" t="n">
-        <v>0.02394512122816539</v>
+        <v>0.0237595081839681</v>
       </c>
       <c r="D48" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Very Strong</t>
         </is>
       </c>
       <c r="F48" s="35" t="n">
-        <v>63.92054859576306</v>
+        <v>63.8893141682433</v>
       </c>
       <c r="H48" s="31" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="I48" s="33" t="n">
-        <v>-0.007425327774216117</v>
+        <v>-0.007039086440657094</v>
       </c>
       <c r="J48" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="L48" s="35" t="n">
-        <v>41.98284966517424</v>
+        <v>35.14802343309778</v>
       </c>
     </row>
     <row r="49">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="C49" s="26" t="n">
-        <v>0.02272729184472988</v>
+        <v>0.02280246168613065</v>
       </c>
       <c r="D49" s="27" t="n">
         <v>2</v>
@@ -2654,15 +2654,15 @@
         </is>
       </c>
       <c r="F49" s="28" t="n">
-        <v>46.05856038939699</v>
+        <v>46.06369373280975</v>
       </c>
       <c r="H49" s="24" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="I49" s="26" t="n">
-        <v>-0.006331396699976732</v>
+        <v>-0.006600309699600682</v>
       </c>
       <c r="J49" s="27" t="n">
         <v>1</v>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="L49" s="28" t="n">
-        <v>42.89514686212071</v>
+        <v>42.128064745238</v>
       </c>
     </row>
     <row r="50">
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="C50" s="33" t="n">
-        <v>0.0201668603207652</v>
+        <v>0.02010687288424085</v>
       </c>
       <c r="D50" s="34" t="n">
         <v>7</v>
@@ -2694,15 +2694,15 @@
         </is>
       </c>
       <c r="F50" s="35" t="n">
-        <v>54.40531156514164</v>
+        <v>54.39558251894007</v>
       </c>
       <c r="H50" s="31" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I50" s="33" t="n">
-        <v>-0.006244357860173189</v>
+        <v>-0.005548155771720742</v>
       </c>
       <c r="J50" s="34" t="n">
         <v>1</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="L50" s="35" t="n">
-        <v>35.48518388683048</v>
+        <v>42.98115350769675</v>
       </c>
     </row>
     <row r="51">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="C51" s="26" t="n">
-        <v>0.0181486402988813</v>
+        <v>0.01690034709569455</v>
       </c>
       <c r="D51" s="27" t="n">
         <v>7</v>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="F51" s="28" t="n">
-        <v>54.4958190400969</v>
+        <v>54.05040407002677</v>
       </c>
       <c r="H51" s="24" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="I51" s="26" t="n">
-        <v>-0.0006766561603024357</v>
+        <v>-0.000522909067699362</v>
       </c>
       <c r="J51" s="27" t="n">
         <v>7</v>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="L51" s="28" t="n">
-        <v>60.79744354811776</v>
+        <v>60.85736584032756</v>
       </c>
     </row>
     <row r="52">
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="C52" s="33" t="n">
-        <v>0.01424965611645512</v>
+        <v>0.0138888974898479</v>
       </c>
       <c r="D52" s="34" t="n">
         <v>6</v>
@@ -2774,15 +2774,15 @@
         </is>
       </c>
       <c r="F52" s="35" t="n">
-        <v>53.93611763104145</v>
+        <v>54.72608401943974</v>
       </c>
       <c r="H52" s="31" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="I52" s="33" t="n">
-        <v>-0.0006668687045597865</v>
+        <v>-0.0002177809097458905</v>
       </c>
       <c r="J52" s="34" t="n">
         <v>2</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="L52" s="35" t="n">
-        <v>46.19588710679039</v>
+        <v>49.7084196689224</v>
       </c>
     </row>
   </sheetData>
@@ -3104,7 +3104,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 2 Sep 2026, 07:58 PM · Yahoo Finance data</t>
+          <t>Built 2 Sep 2026, 10:41 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>29 of 40</t>
+          <t>30 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>11 of 40</t>
+          <t>10 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="C7" s="26" t="n">
-        <v>0.0002316247664648774</v>
+        <v>0.0002894867885985253</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>9</v>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="R7" s="70" t="n">
-        <v>172.7700042724609</v>
+        <v>172.7799987792969</v>
       </c>
       <c r="S7" s="71" t="n">
-        <v>0.040008544921875</v>
+        <v>0.0500030517578125</v>
       </c>
       <c r="T7" s="72" t="n">
         <v>173.3399963378906</v>
@@ -3617,61 +3617,61 @@
         <v>171.6150054931641</v>
       </c>
       <c r="W7" s="73" t="n">
-        <v>10039755</v>
+        <v>10797498</v>
       </c>
       <c r="X7" s="74" t="n">
-        <v>1.666442656893948</v>
+        <v>1.781015938524481</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>30.5574044727401</v>
+        <v>30.59156978165758</v>
       </c>
       <c r="Z7" s="28" t="n">
-        <v>7.32170666357138</v>
+        <v>7.385063308280859</v>
       </c>
       <c r="AA7" s="28" t="n">
         <v>23.06108551951775</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>-1.949407267585542</v>
+        <v>-1.948609984988963</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>-0.6724363478218705</v>
+        <v>-0.6722768913025545</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-1.276970919763672</v>
+        <v>-1.276333093686408</v>
       </c>
       <c r="AE7" s="72" t="n">
-        <v>176.6928659468988</v>
+        <v>176.6950869484179</v>
       </c>
       <c r="AF7" s="72" t="n">
-        <v>179.6868908226255</v>
+        <v>179.687799414156</v>
       </c>
       <c r="AG7" s="72" t="n">
-        <v>181.4987997436523</v>
+        <v>181.4989996337891</v>
       </c>
       <c r="AH7" s="72" t="n">
-        <v>177.5790997314453</v>
+        <v>177.5791996765137</v>
       </c>
       <c r="AI7" s="72" t="n">
-        <v>170.3843997955322</v>
+        <v>170.3844497680664</v>
       </c>
       <c r="AJ7" s="72" t="n">
-        <v>190.4920744768428</v>
+        <v>190.4905493667063</v>
       </c>
       <c r="AK7" s="72" t="n">
-        <v>181.6900001525879</v>
+        <v>181.6904998779297</v>
       </c>
       <c r="AL7" s="72" t="n">
-        <v>172.887925828333</v>
+        <v>172.890450389153</v>
       </c>
       <c r="AM7" s="76" t="n">
-        <v>-0.006698509438117885</v>
+        <v>-0.006275624358533936</v>
       </c>
       <c r="AN7" s="29" t="n">
-        <v>9.689112572912839</v>
+        <v>9.686857039513958</v>
       </c>
       <c r="AO7" s="77" t="n">
-        <v>1.500140621499647</v>
+        <v>1.500053845450322</v>
       </c>
       <c r="AP7" s="72" t="n">
         <v>188.1900024414062</v>
@@ -3680,22 +3680,22 @@
         <v>147.1399993896484</v>
       </c>
       <c r="AR7" s="29" t="n">
-        <v>-8.19384556506736</v>
+        <v>-8.188534705454053</v>
       </c>
       <c r="AS7" s="78" t="n">
-        <v>62.43606084632189</v>
+        <v>62.46040799880161</v>
       </c>
       <c r="AT7" s="26" t="n">
-        <v>-0.03155823888250919</v>
+        <v>-0.03150221586021174</v>
       </c>
       <c r="AU7" s="26" t="n">
-        <v>-0.0567263550006023</v>
+        <v>-0.05667178791916472</v>
       </c>
       <c r="AV7" s="26" t="n">
-        <v>-0.008152007285395002</v>
+        <v>-0.008094630244830925</v>
       </c>
       <c r="AW7" s="26" t="n">
-        <v>0.1137829403742534</v>
+        <v>0.1138473711836303</v>
       </c>
       <c r="AX7" s="79" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>0.007805652427233634</v>
+        <v>0.007456158868465623</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>4</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G8" s="30" t="inlineStr">
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="R8" s="81" t="n">
-        <v>173.0099945068359</v>
+        <v>172.9499969482422</v>
       </c>
       <c r="S8" s="82" t="n">
-        <v>1.339996337890625</v>
+        <v>1.279998779296875</v>
       </c>
       <c r="T8" s="83" t="n">
         <v>172.0899963378906</v>
@@ -3807,61 +3807,61 @@
         <v>172.0899963378906</v>
       </c>
       <c r="W8" s="84" t="n">
-        <v>7045049</v>
+        <v>7797812</v>
       </c>
       <c r="X8" s="85" t="n">
-        <v>0.9251945730079125</v>
+        <v>1.019014713683155</v>
       </c>
       <c r="Y8" s="35" t="n">
-        <v>60.71026441711535</v>
+        <v>60.59214890511474</v>
       </c>
       <c r="Z8" s="35" t="n">
-        <v>66.57346591708259</v>
+        <v>66.01482971683168</v>
       </c>
       <c r="AA8" s="35" t="n">
         <v>28.09164824563776</v>
       </c>
       <c r="AB8" s="86" t="n">
-        <v>2.43928733581302</v>
+        <v>2.434501205782738</v>
       </c>
       <c r="AC8" s="86" t="n">
-        <v>2.805787485005772</v>
+        <v>2.804830258999715</v>
       </c>
       <c r="AD8" s="86" t="n">
-        <v>-0.3665001491927513</v>
+        <v>-0.3703290532169774</v>
       </c>
       <c r="AE8" s="83" t="n">
-        <v>172.0834833373464</v>
+        <v>172.0701505465478</v>
       </c>
       <c r="AF8" s="83" t="n">
-        <v>170.122790435033</v>
+        <v>170.1173361115245</v>
       </c>
       <c r="AG8" s="83" t="n">
-        <v>165.014599609375</v>
+        <v>165.0133996582031</v>
       </c>
       <c r="AH8" s="83" t="n">
-        <v>156.52</v>
+        <v>156.5194000244141</v>
       </c>
       <c r="AI8" s="83" t="n">
-        <v>155.1692999267578</v>
+        <v>155.1689999389648</v>
       </c>
       <c r="AJ8" s="83" t="n">
-        <v>177.0306623156264</v>
+        <v>177.0232012296744</v>
       </c>
       <c r="AK8" s="83" t="n">
-        <v>170.5864974975586</v>
+        <v>170.5834976196289</v>
       </c>
       <c r="AL8" s="83" t="n">
-        <v>164.1423326794908</v>
+        <v>164.1437940095834</v>
       </c>
       <c r="AM8" s="87" t="n">
-        <v>0.6880380994044786</v>
+        <v>0.6837428763741311</v>
       </c>
       <c r="AN8" s="36" t="n">
-        <v>7.555304684252671</v>
+        <v>7.550207024603218</v>
       </c>
       <c r="AO8" s="88" t="n">
-        <v>1.530008744468707</v>
+        <v>1.530539515159167</v>
       </c>
       <c r="AP8" s="83" t="n">
         <v>176.6000061035156</v>
@@ -3870,22 +3870,22 @@
         <v>133.7299957275391</v>
       </c>
       <c r="AR8" s="36" t="n">
-        <v>-2.032849078484955</v>
+        <v>-2.066822779798749</v>
       </c>
       <c r="AS8" s="89" t="n">
-        <v>91.62582055568744</v>
+        <v>91.48586827187049</v>
       </c>
       <c r="AT8" s="33" t="n">
-        <v>-0.003054044023287572</v>
+        <v>-0.003399771584166378</v>
       </c>
       <c r="AU8" s="33" t="n">
-        <v>0.06730405917661275</v>
+        <v>0.06693393236393752</v>
       </c>
       <c r="AV8" s="33" t="n">
-        <v>0.1725516159165867</v>
+        <v>0.1721449906549615</v>
       </c>
       <c r="AW8" s="33" t="n">
-        <v>0.1176356013958835</v>
+        <v>0.1172480202756576</v>
       </c>
       <c r="AX8" s="90" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="C9" s="26" t="n">
-        <v>0.008216737757639647</v>
+        <v>0.008041941928971008</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>3</v>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="R9" s="70" t="n">
-        <v>57.66999816894531</v>
+        <v>57.65999984741211</v>
       </c>
       <c r="S9" s="71" t="n">
-        <v>0.4699974060058594</v>
+        <v>0.4599990844726562</v>
       </c>
       <c r="T9" s="72" t="n">
         <v>57.38000106811523</v>
@@ -3997,61 +3997,61 @@
         <v>57.31999969482422</v>
       </c>
       <c r="W9" s="73" t="n">
-        <v>28275349</v>
+        <v>31253512</v>
       </c>
       <c r="X9" s="74" t="n">
-        <v>1.044894489676772</v>
+        <v>1.148629620539903</v>
       </c>
       <c r="Y9" s="28" t="n">
-        <v>52.82552367269125</v>
+        <v>52.72957425128689</v>
       </c>
       <c r="Z9" s="28" t="n">
-        <v>50.66655476888021</v>
+        <v>50</v>
       </c>
       <c r="AA9" s="28" t="n">
         <v>20.72273183268819</v>
       </c>
       <c r="AB9" s="75" t="n">
-        <v>0.2928512532733976</v>
+        <v>0.2920536663704709</v>
       </c>
       <c r="AC9" s="75" t="n">
-        <v>0.4304914676024663</v>
+        <v>0.430331950221881</v>
       </c>
       <c r="AD9" s="75" t="n">
-        <v>-0.1376402143290688</v>
+        <v>-0.1382782838514101</v>
       </c>
       <c r="AE9" s="72" t="n">
-        <v>57.7296271599166</v>
+        <v>57.727405310687</v>
       </c>
       <c r="AF9" s="72" t="n">
-        <v>57.5898901091892</v>
+        <v>57.588981170868</v>
       </c>
       <c r="AG9" s="72" t="n">
-        <v>56.66880004882812</v>
+        <v>56.66860008239746</v>
       </c>
       <c r="AH9" s="72" t="n">
-        <v>54.35709991455078</v>
+        <v>54.35699993133545</v>
       </c>
       <c r="AI9" s="72" t="n">
-        <v>53.42395002365112</v>
+        <v>53.42390003204346</v>
       </c>
       <c r="AJ9" s="72" t="n">
-        <v>58.50946249597167</v>
+        <v>58.50934900483585</v>
       </c>
       <c r="AK9" s="72" t="n">
-        <v>57.8019998550415</v>
+        <v>57.80149993896485</v>
       </c>
       <c r="AL9" s="72" t="n">
-        <v>57.09453721411133</v>
+        <v>57.09365087309384</v>
       </c>
       <c r="AM9" s="76" t="n">
-        <v>0.4067076630911325</v>
+        <v>0.4000492489323132</v>
       </c>
       <c r="AN9" s="29" t="n">
-        <v>2.447882919983303</v>
+        <v>2.449241167161608</v>
       </c>
       <c r="AO9" s="77" t="n">
-        <v>1.110495224829556</v>
+        <v>1.110687786195292</v>
       </c>
       <c r="AP9" s="72" t="n">
         <v>58.40999984741211</v>
@@ -4060,22 +4060,22 @@
         <v>47.66999816894531</v>
       </c>
       <c r="AR9" s="29" t="n">
-        <v>-1.266909228556667</v>
+        <v>-1.284026711109865</v>
       </c>
       <c r="AS9" s="78" t="n">
-        <v>93.10985509480444</v>
+        <v>93.01676086788967</v>
       </c>
       <c r="AT9" s="26" t="n">
-        <v>-0.01012701973199037</v>
+        <v>-0.0102986352799006</v>
       </c>
       <c r="AU9" s="26" t="n">
-        <v>-0.003628246290506842</v>
+        <v>-0.003800988539102157</v>
       </c>
       <c r="AV9" s="26" t="n">
-        <v>0.1336740589707066</v>
+        <v>0.1334775124453844</v>
       </c>
       <c r="AW9" s="26" t="n">
-        <v>0.05294865230863022</v>
+        <v>0.05276610125057579</v>
       </c>
       <c r="AX9" s="79" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>0.004863400613437818</v>
+        <v>0.005094979900543306</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>5</v>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="R10" s="81" t="n">
-        <v>65.08499908447266</v>
+        <v>65.09999847412109</v>
       </c>
       <c r="S10" s="82" t="n">
-        <v>0.31500244140625</v>
+        <v>0.3300018310546875</v>
       </c>
       <c r="T10" s="83" t="n">
         <v>64.26999664306641</v>
@@ -4187,61 +4187,61 @@
         <v>64.26999664306641</v>
       </c>
       <c r="W10" s="84" t="n">
-        <v>25141602</v>
+        <v>27292645</v>
       </c>
       <c r="X10" s="85" t="n">
-        <v>0.9909891128572088</v>
+        <v>1.071233993479942</v>
       </c>
       <c r="Y10" s="35" t="n">
-        <v>71.61650998925876</v>
+        <v>71.66578309253622</v>
       </c>
       <c r="Z10" s="35" t="n">
-        <v>93.65074337668145</v>
+        <v>94.01702872899355</v>
       </c>
       <c r="AA10" s="35" t="n">
         <v>27.49577802958462</v>
       </c>
       <c r="AB10" s="86" t="n">
-        <v>1.486994822044394</v>
+        <v>1.488191354551958</v>
       </c>
       <c r="AC10" s="86" t="n">
-        <v>1.405461758649179</v>
+        <v>1.405701065150692</v>
       </c>
       <c r="AD10" s="86" t="n">
-        <v>0.0815330633952156</v>
+        <v>0.08249028940126646</v>
       </c>
       <c r="AE10" s="83" t="n">
-        <v>63.67894554516474</v>
+        <v>63.6822787428644</v>
       </c>
       <c r="AF10" s="83" t="n">
-        <v>62.20005052409346</v>
+        <v>62.2014141049706</v>
       </c>
       <c r="AG10" s="83" t="n">
-        <v>58.78230026245117</v>
+        <v>58.78260025024414</v>
       </c>
       <c r="AH10" s="83" t="n">
-        <v>58.0551501083374</v>
+        <v>58.05530010223389</v>
       </c>
       <c r="AI10" s="83" t="n">
-        <v>54.64327489852905</v>
+        <v>54.64334989547729</v>
       </c>
       <c r="AJ10" s="83" t="n">
-        <v>66.08526081196719</v>
+        <v>66.08823938030804</v>
       </c>
       <c r="AK10" s="83" t="n">
-        <v>62.21925010681152</v>
+        <v>62.22000007629394</v>
       </c>
       <c r="AL10" s="83" t="n">
-        <v>58.35323940165586</v>
+        <v>58.35176077227985</v>
       </c>
       <c r="AM10" s="87" t="n">
-        <v>0.8706338647535823</v>
+        <v>0.8722621807340821</v>
       </c>
       <c r="AN10" s="36" t="n">
-        <v>12.42705657338814</v>
+        <v>12.43407039302756</v>
       </c>
       <c r="AO10" s="88" t="n">
-        <v>1.817474339533456</v>
+        <v>1.81705558367426</v>
       </c>
       <c r="AP10" s="83" t="n">
         <v>65.34500122070312</v>
@@ -4250,22 +4250,22 @@
         <v>42.34999847412109</v>
       </c>
       <c r="AR10" s="36" t="n">
-        <v>-0.3978913939450601</v>
+        <v>-0.3749372438674126</v>
       </c>
       <c r="AS10" s="89" t="n">
-        <v>98.869310262339</v>
+        <v>98.93453917234932</v>
       </c>
       <c r="AT10" s="33" t="n">
-        <v>0.04252761118562365</v>
+        <v>0.04276787050926778</v>
       </c>
       <c r="AU10" s="33" t="n">
-        <v>0.1121838444182381</v>
+        <v>0.1124401566111826</v>
       </c>
       <c r="AV10" s="33" t="n">
-        <v>0.1085845699099326</v>
+        <v>0.1088400526195619</v>
       </c>
       <c r="AW10" s="33" t="n">
-        <v>0.4557146145654034</v>
+        <v>0.4560500963358258</v>
       </c>
       <c r="AX10" s="90" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>0.003636334998167179</v>
+        <v>0.003284443158907635</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>6</v>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="N11" s="69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O11" s="23" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="R11" s="70" t="n">
-        <v>85.55999755859375</v>
+        <v>85.52999877929688</v>
       </c>
       <c r="S11" s="71" t="n">
-        <v>0.30999755859375</v>
+        <v>0.279998779296875</v>
       </c>
       <c r="T11" s="72" t="n">
         <v>85.37000274658203</v>
@@ -4377,61 +4377,61 @@
         <v>85.05000305175781</v>
       </c>
       <c r="W11" s="73" t="n">
-        <v>6911907</v>
+        <v>8426913</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>0.812804993022889</v>
+        <v>0.9822125668524383</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>50.6273939748334</v>
+        <v>50.46824785757966</v>
       </c>
       <c r="Z11" s="28" t="n">
-        <v>33.68054083838427</v>
+        <v>32.63891832323147</v>
       </c>
       <c r="AA11" s="28" t="n">
         <v>15.51690569335987</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.1658804211549949</v>
+        <v>0.1634873561398535</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.2736118610340371</v>
+        <v>0.2731332480310088</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.1077314398790422</v>
+        <v>-0.1096458918911553</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>85.60465867825143</v>
+        <v>85.59799228285212</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.54447454860315</v>
+        <v>85.54174738684888</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>84.96899993896484</v>
+        <v>84.9683999633789</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.28810012817382</v>
+        <v>84.28780014038085</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.20620021820068</v>
+        <v>83.20605022430419</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>86.98759472917838</v>
+        <v>86.98623859549889</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.57949981689453</v>
+        <v>85.57799987792968</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>84.17140490461067</v>
+        <v>84.16976116036048</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.4930749489503006</v>
+        <v>0.4829570448412093</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.290729474457342</v>
+        <v>3.291123231620153</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.377044391366874</v>
+        <v>1.377527375715853</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -4440,22 +4440,22 @@
         <v>75.16000366210938</v>
       </c>
       <c r="AR11" s="29" t="n">
-        <v>-5.080987199985099</v>
+        <v>-5.114267407994866</v>
       </c>
       <c r="AS11" s="78" t="n">
-        <v>69.42588025819752</v>
+        <v>69.22562132727056</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-0.01109569026491164</v>
+        <v>-0.0114424168074545</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>0.008248844487479312</v>
+        <v>0.007895335424539018</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.04558225154681006</v>
+        <v>0.04521565276121042</v>
       </c>
       <c r="AW11" s="26" t="n">
-        <v>0.1014417768081926</v>
+        <v>0.1010555927301928</v>
       </c>
       <c r="AX11" s="79" t="inlineStr">
         <is>
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>0.002399873764442839</v>
+        <v>0.002356263906883926</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="R12" s="81" t="n">
-        <v>114.8649978637695</v>
+        <v>114.8600006103516</v>
       </c>
       <c r="S12" s="82" t="n">
-        <v>0.2750015258789062</v>
+        <v>0.2700042724609375</v>
       </c>
       <c r="T12" s="83" t="n">
         <v>114.9899978637695</v>
@@ -4567,61 +4567,61 @@
         <v>114.25</v>
       </c>
       <c r="W12" s="84" t="n">
-        <v>3869688</v>
+        <v>4221465</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>0.7698796567150139</v>
+        <v>0.8369374496828449</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>43.55084638096561</v>
+        <v>43.53170083284979</v>
       </c>
       <c r="Z12" s="35" t="n">
-        <v>12.47460092697911</v>
+        <v>12.37323676656066</v>
       </c>
       <c r="AA12" s="35" t="n">
         <v>13.59380012353222</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>-0.1278985267688029</v>
+        <v>-0.1282971680671068</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.2920930502400306</v>
+        <v>0.2920133219803698</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.4199915770088335</v>
+        <v>-0.4203104900474766</v>
       </c>
       <c r="AE12" s="83" t="n">
-        <v>116.1809866753631</v>
+        <v>116.1798761746035</v>
       </c>
       <c r="AF12" s="83" t="n">
-        <v>116.6589921018414</v>
+        <v>116.6585378060762</v>
       </c>
       <c r="AG12" s="83" t="n">
-        <v>116.1206996154785</v>
+        <v>116.1205996704102</v>
       </c>
       <c r="AH12" s="83" t="n">
-        <v>116.9369498443604</v>
+        <v>116.9368998718262</v>
       </c>
       <c r="AI12" s="83" t="n">
-        <v>116.9548249053955</v>
+        <v>116.9547999191284</v>
       </c>
       <c r="AJ12" s="83" t="n">
-        <v>120.4235361052071</v>
+        <v>120.4242475651574</v>
       </c>
       <c r="AK12" s="83" t="n">
-        <v>117.5892486572266</v>
+        <v>117.5889987945557</v>
       </c>
       <c r="AL12" s="83" t="n">
-        <v>114.754961209246</v>
+        <v>114.7537500239539</v>
       </c>
       <c r="AM12" s="87" t="n">
-        <v>0.01941169633339902</v>
+        <v>0.01873743628766048</v>
       </c>
       <c r="AN12" s="36" t="n">
-        <v>4.8206574671508</v>
+        <v>4.822302765848549</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.399949132425546</v>
+        <v>1.400010040492322</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -4630,22 +4630,22 @@
         <v>105.1900024414062</v>
       </c>
       <c r="AR12" s="36" t="n">
-        <v>-8.115354050954537</v>
+        <v>-8.119351533821973</v>
       </c>
       <c r="AS12" s="89" t="n">
-        <v>48.8143066162095</v>
+        <v>48.78909343005958</v>
       </c>
       <c r="AT12" s="33" t="n">
-        <v>-0.0261551434022198</v>
+        <v>-0.02619751096090783</v>
       </c>
       <c r="AU12" s="33" t="n">
-        <v>-0.0282971089299543</v>
+        <v>-0.02833938330146835</v>
       </c>
       <c r="AV12" s="33" t="n">
-        <v>-0.0231737270089788</v>
+        <v>-0.02321622427552861</v>
       </c>
       <c r="AW12" s="33" t="n">
-        <v>-0.03806218624028102</v>
+        <v>-0.0381040357777126</v>
       </c>
       <c r="AX12" s="90" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>0.01424965611645512</v>
+        <v>0.0138888974898479</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>2</v>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="R13" s="70" t="n">
-        <v>112.4599990844727</v>
+        <v>112.4199981689453</v>
       </c>
       <c r="S13" s="71" t="n">
-        <v>1.580001831054688</v>
+        <v>1.540000915527344</v>
       </c>
       <c r="T13" s="72" t="n">
         <v>110.9300003051758</v>
@@ -4757,61 +4757,61 @@
         <v>110.9049987792969</v>
       </c>
       <c r="W13" s="73" t="n">
-        <v>4864119</v>
+        <v>5098194</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>1.20849449977645</v>
+        <v>1.231947836219613</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>53.93611763104145</v>
+        <v>54.72608401943974</v>
       </c>
       <c r="Z13" s="28" t="n">
-        <v>58.93330891927084</v>
+        <v>57.86661783854166</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>12.70478720520246</v>
+        <v>12.10741423181737</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.4212377709385322</v>
+        <v>0.4021011784522983</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.4395490192292572</v>
+        <v>0.4091764542843005</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>-0.01831124829072495</v>
+        <v>-0.007075275832002181</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>111.8882825580179</v>
+        <v>111.7612313263991</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.4915688920322</v>
+        <v>111.3718408475689</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.3227996826172</v>
+        <v>110.2075996398926</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.5973999023438</v>
+        <v>112.6065998840332</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0088499832153</v>
+        <v>114.0033499908447</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.3962276802872</v>
+        <v>113.2043378909943</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.6654998779297</v>
+        <v>111.5575000762939</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.9347720755722</v>
+        <v>109.9106622615936</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.729527487066634</v>
+        <v>0.7618649161903897</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>3.099843379109088</v>
+        <v>2.952446610177032</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.513657591402044</v>
+        <v>1.468637558676278</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -4820,22 +4820,22 @@
         <v>105.0299987792969</v>
       </c>
       <c r="AR13" s="29" t="n">
-        <v>-6.598562996032631</v>
+        <v>-6.631784968486332</v>
       </c>
       <c r="AS13" s="78" t="n">
-        <v>48.32520523691565</v>
+        <v>48.06503668064025</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>-0.001332044446016312</v>
+        <v>-0.006714986165234249</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>0.003748644818933666</v>
+        <v>0.00970003472765657</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>0.003390410842344149</v>
+        <v>-0.01012592699629389</v>
       </c>
       <c r="AW13" s="26" t="n">
-        <v>-0.04468231465924755</v>
+        <v>-0.04502211176349968</v>
       </c>
       <c r="AX13" s="79" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="C14" s="33" t="n">
-        <v>0.0181486402988813</v>
+        <v>0.01690034709569455</v>
       </c>
       <c r="D14" s="34" t="n">
         <v>1</v>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="R14" s="81" t="n">
-        <v>53.01499938964844</v>
+        <v>52.95000076293945</v>
       </c>
       <c r="S14" s="82" t="n">
-        <v>0.9449996948242188</v>
+        <v>0.8800010681152344</v>
       </c>
       <c r="T14" s="83" t="n">
         <v>52.36000061035156</v>
@@ -4947,61 +4947,61 @@
         <v>52.27000045776367</v>
       </c>
       <c r="W14" s="84" t="n">
-        <v>10946626</v>
+        <v>12839941</v>
       </c>
       <c r="X14" s="85" t="n">
-        <v>1.04335148183895</v>
+        <v>1.2128647893584</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>54.4958190400969</v>
+        <v>54.05040407002677</v>
       </c>
       <c r="Z14" s="35" t="n">
-        <v>51.84426645988077</v>
+        <v>49.18038681677405</v>
       </c>
       <c r="AA14" s="35" t="n">
         <v>12.83321990595936</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.3503435360309766</v>
+        <v>0.345158460396064</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.418651216672178</v>
+        <v>0.4176142015451955</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>-0.06830768064120141</v>
+        <v>-0.07245574114913145</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>52.87854640181349</v>
+        <v>52.86410226254483</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.6047678065465</v>
+        <v>52.59885884048205</v>
       </c>
       <c r="AG14" s="83" t="n">
-        <v>51.73669982910156</v>
+        <v>51.73539985656738</v>
       </c>
       <c r="AH14" s="83" t="n">
-        <v>51.55224998474121</v>
+        <v>51.55159999847412</v>
       </c>
       <c r="AI14" s="83" t="n">
-        <v>49.92934997558594</v>
+        <v>49.92902498245239</v>
       </c>
       <c r="AJ14" s="83" t="n">
-        <v>53.88759090282354</v>
+        <v>53.88206629554979</v>
       </c>
       <c r="AK14" s="83" t="n">
-        <v>52.79275016784668</v>
+        <v>52.78950023651123</v>
       </c>
       <c r="AL14" s="83" t="n">
-        <v>51.69790943286981</v>
+        <v>51.69693417747267</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.6014984256164242</v>
+        <v>0.5734511772082048</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>4.147693505248278</v>
+        <v>4.139330943250339</v>
       </c>
       <c r="AO14" s="88" t="n">
-        <v>1.549251949172213</v>
+        <v>1.551153729109351</v>
       </c>
       <c r="AP14" s="83" t="n">
         <v>54.18999862670898</v>
@@ -5010,22 +5010,22 @@
         <v>42.03499984741211</v>
       </c>
       <c r="AR14" s="36" t="n">
-        <v>-2.168295380766838</v>
+        <v>-2.288241179541872</v>
       </c>
       <c r="AS14" s="89" t="n">
-        <v>90.33320152148534</v>
+        <v>89.79845340765011</v>
       </c>
       <c r="AT14" s="33" t="n">
-        <v>-0.01054502467520968</v>
+        <v>-0.01175813823414407</v>
       </c>
       <c r="AU14" s="33" t="n">
-        <v>0.03930604066044152</v>
+        <v>0.03803180759147962</v>
       </c>
       <c r="AV14" s="33" t="n">
-        <v>0.02901783615297848</v>
+        <v>0.02775621685694873</v>
       </c>
       <c r="AW14" s="33" t="n">
-        <v>0.1690187689841129</v>
+        <v>0.1675855026358002</v>
       </c>
       <c r="AX14" s="90" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>-0.0005717475925072213</v>
+        <v>-0.0002177809097458905</v>
       </c>
       <c r="D15" s="27" t="n">
         <v>10</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="R15" s="70" t="n">
-        <v>183.5350036621094</v>
+        <v>183.6000061035156</v>
       </c>
       <c r="S15" s="71" t="n">
-        <v>-0.1049957275390625</v>
+        <v>-0.0399932861328125</v>
       </c>
       <c r="T15" s="72" t="n">
         <v>183.4600067138672</v>
@@ -5137,61 +5137,61 @@
         <v>182.2700042724609</v>
       </c>
       <c r="W15" s="73" t="n">
-        <v>5179835</v>
+        <v>5668731</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>0.8468962654322842</v>
+        <v>0.9231406141208736</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>49.60805321927165</v>
+        <v>49.7084196689224</v>
       </c>
       <c r="Z15" s="28" t="n">
-        <v>36.4655762467842</v>
+        <v>36.96830229649036</v>
       </c>
       <c r="AA15" s="28" t="n">
         <v>12.54910890277319</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.6226663133107877</v>
+        <v>0.6278516932520404</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>0.9051008743300035</v>
+        <v>0.9061379503182541</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.2824345610192158</v>
+        <v>-0.2782862570662137</v>
       </c>
       <c r="AE15" s="72" t="n">
-        <v>184.4313233243897</v>
+        <v>184.4457683113689</v>
       </c>
       <c r="AF15" s="72" t="n">
-        <v>184.0807395028847</v>
+        <v>184.0866488157398</v>
       </c>
       <c r="AG15" s="72" t="n">
-        <v>182.46330078125</v>
+        <v>182.4646008300781</v>
       </c>
       <c r="AH15" s="72" t="n">
-        <v>177.7896508789063</v>
+        <v>177.7903009033203</v>
       </c>
       <c r="AI15" s="72" t="n">
-        <v>159.7060501098633</v>
+        <v>159.7063751220703</v>
       </c>
       <c r="AJ15" s="72" t="n">
-        <v>191.5738246354155</v>
+        <v>191.5723244706226</v>
       </c>
       <c r="AK15" s="72" t="n">
-        <v>185.7082511901855</v>
+        <v>185.7115013122558</v>
       </c>
       <c r="AL15" s="72" t="n">
-        <v>179.8426777449556</v>
+        <v>179.8506781538891</v>
       </c>
       <c r="AM15" s="76" t="n">
-        <v>0.3147455190554714</v>
+        <v>0.3198635966582695</v>
       </c>
       <c r="AN15" s="29" t="n">
-        <v>6.316976663813326</v>
+        <v>6.311750340666694</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.13878982691616</v>
+        <v>2.138032601666799</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -5200,22 +5200,22 @@
         <v>126.6800003051758</v>
       </c>
       <c r="AR15" s="29" t="n">
-        <v>-7.646048604691858</v>
+        <v>-7.613339681628539</v>
       </c>
       <c r="AS15" s="78" t="n">
-        <v>78.91048850682732</v>
+        <v>79.00070702943125</v>
       </c>
       <c r="AT15" s="26" t="n">
-        <v>0.009876736627549176</v>
+        <v>0.01023440384137952</v>
       </c>
       <c r="AU15" s="26" t="n">
-        <v>0.03086391026282165</v>
+        <v>0.03122901048668969</v>
       </c>
       <c r="AV15" s="26" t="n">
-        <v>-0.07403764973855442</v>
+        <v>-0.07370970241397712</v>
       </c>
       <c r="AW15" s="26" t="n">
-        <v>0.2748142120298651</v>
+        <v>0.2752657119316162</v>
       </c>
       <c r="AX15" s="79" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="C16" s="33" t="n">
-        <v>-0.006244357860173189</v>
+        <v>-0.007039086440657094</v>
       </c>
       <c r="D16" s="34" t="n">
         <v>11</v>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G16" s="30" t="inlineStr">
@@ -5294,11 +5294,11 @@
         </is>
       </c>
       <c r="N16" s="80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="P16" s="32" t="inlineStr">
@@ -5312,10 +5312,10 @@
         </is>
       </c>
       <c r="R16" s="81" t="n">
-        <v>43.76499938964844</v>
+        <v>43.72999954223633</v>
       </c>
       <c r="S16" s="82" t="n">
-        <v>-0.2750015258789062</v>
+        <v>-0.3100013732910156</v>
       </c>
       <c r="T16" s="83" t="n">
         <v>44.0099983215332</v>
@@ -5327,61 +5327,61 @@
         <v>43.56499862670898</v>
       </c>
       <c r="W16" s="84" t="n">
-        <v>5645848</v>
+        <v>7636281</v>
       </c>
       <c r="X16" s="85" t="n">
-        <v>1.113202403588181</v>
+        <v>1.476683039821955</v>
       </c>
       <c r="Y16" s="35" t="n">
-        <v>35.48518388683048</v>
+        <v>35.14802343309778</v>
       </c>
       <c r="Z16" s="35" t="n">
-        <v>10.52634749053354</v>
+        <v>8.684251737693597</v>
       </c>
       <c r="AA16" s="35" t="n">
         <v>13.41052189102336</v>
       </c>
       <c r="AB16" s="86" t="n">
-        <v>-0.2029713558790291</v>
+        <v>-0.2057633664987932</v>
       </c>
       <c r="AC16" s="86" t="n">
-        <v>-0.06546228757995382</v>
+        <v>-0.06602068970390663</v>
       </c>
       <c r="AD16" s="86" t="n">
-        <v>-0.1375090682990753</v>
+        <v>-0.1397426767948866</v>
       </c>
       <c r="AE16" s="83" t="n">
-        <v>44.38749902903799</v>
+        <v>44.37972128516863</v>
       </c>
       <c r="AF16" s="83" t="n">
-        <v>44.70373139121887</v>
+        <v>44.70054958690867</v>
       </c>
       <c r="AG16" s="83" t="n">
-        <v>44.86730018615722</v>
+        <v>44.86660018920898</v>
       </c>
       <c r="AH16" s="83" t="n">
-        <v>44.52385021209717</v>
+        <v>44.52350021362304</v>
       </c>
       <c r="AI16" s="83" t="n">
-        <v>43.03577508926391</v>
+        <v>43.03560009002685</v>
       </c>
       <c r="AJ16" s="83" t="n">
-        <v>45.64406207188032</v>
+        <v>45.64979487975917</v>
       </c>
       <c r="AK16" s="83" t="n">
-        <v>44.72975082397461</v>
+        <v>44.72800083160401</v>
       </c>
       <c r="AL16" s="83" t="n">
-        <v>43.8154395760689</v>
+        <v>43.80620678344884</v>
       </c>
       <c r="AM16" s="87" t="n">
-        <v>-0.02758370660757118</v>
+        <v>-0.04133637083306877</v>
       </c>
       <c r="AN16" s="36" t="n">
-        <v>4.088157126132025</v>
+        <v>4.121776207372275</v>
       </c>
       <c r="AO16" s="88" t="n">
-        <v>1.19678924408549</v>
+        <v>1.197747109197906</v>
       </c>
       <c r="AP16" s="83" t="n">
         <v>46.45500183105469</v>
@@ -5390,22 +5390,22 @@
         <v>39.72499847412109</v>
       </c>
       <c r="AR16" s="36" t="n">
-        <v>-5.790555021801791</v>
+        <v>-5.8658964189228</v>
       </c>
       <c r="AS16" s="89" t="n">
-        <v>60.02970134279544</v>
+        <v>59.50964443411574</v>
       </c>
       <c r="AT16" s="33" t="n">
-        <v>-0.0293856899191739</v>
+        <v>-0.03016191185959682</v>
       </c>
       <c r="AU16" s="33" t="n">
-        <v>-0.0311046897553966</v>
+        <v>-0.03187953697326018</v>
       </c>
       <c r="AV16" s="33" t="n">
-        <v>0.005860746447995835</v>
+        <v>0.00505633714525433</v>
       </c>
       <c r="AW16" s="33" t="n">
-        <v>0.08463447446516237</v>
+        <v>0.08376706805287815</v>
       </c>
       <c r="AX16" s="90" t="inlineStr">
         <is>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>0.001409717026733981</v>
+        <v>0.002584511092692976</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="R17" s="70" t="n">
-        <v>42.61999893188477</v>
+        <v>42.66999816894531</v>
       </c>
       <c r="S17" s="71" t="n">
-        <v>0.05999755859375</v>
+        <v>0.1099967956542969</v>
       </c>
       <c r="T17" s="72" t="n">
         <v>42.40000152587891</v>
@@ -5517,61 +5517,61 @@
         <v>42.02000045776367</v>
       </c>
       <c r="W17" s="73" t="n">
-        <v>24865325</v>
+        <v>29748425</v>
       </c>
       <c r="X17" s="74" t="n">
-        <v>1.220185450797487</v>
+        <v>1.442524741063707</v>
       </c>
       <c r="Y17" s="28" t="n">
-        <v>37.51473300697274</v>
+        <v>38.17497212155799</v>
       </c>
       <c r="Z17" s="28" t="n">
-        <v>27.24007427035393</v>
+        <v>29.03216103212822</v>
       </c>
       <c r="AA17" s="28" t="n">
         <v>16.2096219818047</v>
       </c>
       <c r="AB17" s="75" t="n">
-        <v>-0.5257601892416659</v>
+        <v>-0.521771646114324</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.4450285482345985</v>
+        <v>-0.4442308396091301</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.08073164100706742</v>
+        <v>-0.0775408065051939</v>
       </c>
       <c r="AE17" s="72" t="n">
-        <v>42.94722043249607</v>
+        <v>42.95833137406509</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>43.51708144881852</v>
+        <v>43.52162683400584</v>
       </c>
       <c r="AG17" s="72" t="n">
-        <v>44.59140014648438</v>
+        <v>44.59240013122559</v>
       </c>
       <c r="AH17" s="72" t="n">
-        <v>44.84819988250732</v>
+        <v>44.84869987487793</v>
       </c>
       <c r="AI17" s="72" t="n">
-        <v>44.68607496261597</v>
+        <v>44.68632495880127</v>
       </c>
       <c r="AJ17" s="72" t="n">
-        <v>44.57334196189532</v>
+        <v>44.56864939502348</v>
       </c>
       <c r="AK17" s="72" t="n">
-        <v>43.44950046539306</v>
+        <v>43.45200042724609</v>
       </c>
       <c r="AL17" s="72" t="n">
-        <v>42.32565896889081</v>
+        <v>42.3353514594687</v>
       </c>
       <c r="AM17" s="76" t="n">
-        <v>0.1309526138294572</v>
+        <v>0.1498441852065223</v>
       </c>
       <c r="AN17" s="29" t="n">
-        <v>5.173092829444071</v>
+        <v>5.139689573772587</v>
       </c>
       <c r="AO17" s="77" t="n">
-        <v>1.59000673863903</v>
+        <v>1.588143623399645</v>
       </c>
       <c r="AP17" s="72" t="n">
         <v>47.79999923706055</v>
@@ -5580,22 +5580,22 @@
         <v>41.15000152587891</v>
       </c>
       <c r="AR17" s="29" t="n">
-        <v>-10.83682089509239</v>
+        <v>-10.73221997907025</v>
       </c>
       <c r="AS17" s="78" t="n">
-        <v>22.10523175871372</v>
+        <v>22.85710024396862</v>
       </c>
       <c r="AT17" s="26" t="n">
-        <v>-0.01593171137213978</v>
+        <v>-0.01477726123417744</v>
       </c>
       <c r="AU17" s="26" t="n">
-        <v>-0.03922456389824214</v>
+        <v>-0.03809743954358469</v>
       </c>
       <c r="AV17" s="26" t="n">
-        <v>-0.0291572334738891</v>
+        <v>-0.02801829872849804</v>
       </c>
       <c r="AW17" s="26" t="n">
-        <v>-0.001639721177700504</v>
+        <v>-0.0004685045305005131</v>
       </c>
       <c r="AX17" s="79" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="C19" s="26" t="n">
-        <v>0.004200623603678011</v>
+        <v>0.004436902672253051</v>
       </c>
       <c r="D19" s="27" t="n">
         <v>2</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="R19" s="70" t="n">
-        <v>764.97998046875</v>
+        <v>765.1599731445312</v>
       </c>
       <c r="S19" s="71" t="n">
-        <v>3.199951171875</v>
+        <v>3.37994384765625</v>
       </c>
       <c r="T19" s="72" t="n">
         <v>762.4500122070312</v>
@@ -5726,61 +5726,61 @@
         <v>761.72998046875</v>
       </c>
       <c r="W19" s="73" t="n">
-        <v>22134124</v>
+        <v>29174572</v>
       </c>
       <c r="X19" s="74" t="n">
-        <v>0.6119091968110061</v>
+        <v>0.7987724629679409</v>
       </c>
       <c r="Y19" s="28" t="n">
-        <v>51.76348715123333</v>
+        <v>51.93104068165</v>
       </c>
       <c r="Z19" s="28" t="n">
-        <v>28.46789811050139</v>
+        <v>29.39953686591542</v>
       </c>
       <c r="AA19" s="28" t="n">
         <v>13.26091923453281</v>
       </c>
       <c r="AB19" s="75" t="n">
-        <v>2.709740062813921</v>
+        <v>2.724098452904741</v>
       </c>
       <c r="AC19" s="75" t="n">
-        <v>4.104802828152334</v>
+        <v>4.107674506170497</v>
       </c>
       <c r="AD19" s="75" t="n">
-        <v>-1.395062765338412</v>
+        <v>-1.383576053265756</v>
       </c>
       <c r="AE19" s="72" t="n">
-        <v>766.1051819316422</v>
+        <v>766.145180304038</v>
       </c>
       <c r="AF19" s="72" t="n">
-        <v>764.8123049866458</v>
+        <v>764.8286679571713</v>
       </c>
       <c r="AG19" s="72" t="n">
-        <v>755.3372009277343</v>
+        <v>755.34080078125</v>
       </c>
       <c r="AH19" s="72" t="n">
-        <v>743.6840008544922</v>
+        <v>743.68580078125</v>
       </c>
       <c r="AI19" s="72" t="n">
-        <v>711.123200378418</v>
+        <v>711.1241003417969</v>
       </c>
       <c r="AJ19" s="72" t="n">
-        <v>777.6246823858597</v>
+        <v>777.6174443373843</v>
       </c>
       <c r="AK19" s="72" t="n">
-        <v>768.9669952392578</v>
+        <v>768.9759948730468</v>
       </c>
       <c r="AL19" s="72" t="n">
-        <v>760.3093080926559</v>
+        <v>760.3345454087093</v>
       </c>
       <c r="AM19" s="76" t="n">
-        <v>0.2697413464476659</v>
+        <v>0.2792024506846929</v>
       </c>
       <c r="AN19" s="29" t="n">
-        <v>2.25177080426141</v>
+        <v>2.247521254747135</v>
       </c>
       <c r="AO19" s="77" t="n">
-        <v>0.8085143295153746</v>
+        <v>0.8083241383623025</v>
       </c>
       <c r="AP19" s="72" t="n">
         <v>779.3699951171875</v>
@@ -5789,22 +5789,22 @@
         <v>629.280029296875</v>
       </c>
       <c r="AR19" s="29" t="n">
-        <v>-1.84636497922579</v>
+        <v>-1.823270341645578</v>
       </c>
       <c r="AS19" s="78" t="n">
-        <v>90.41240727200565</v>
+        <v>90.53233046260503</v>
       </c>
       <c r="AT19" s="26" t="n">
-        <v>-0.001435929141282877</v>
+        <v>-0.0012009763011539</v>
       </c>
       <c r="AU19" s="26" t="n">
-        <v>-0.00823258071175792</v>
+        <v>-0.007999227060540792</v>
       </c>
       <c r="AV19" s="26" t="n">
-        <v>0.01423948660032948</v>
+        <v>0.01447812772001522</v>
       </c>
       <c r="AW19" s="26" t="n">
-        <v>0.1218031435361779</v>
+        <v>0.1220670933840957</v>
       </c>
       <c r="AX19" s="79" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="C20" s="33" t="n">
-        <v>0.002077286010819135</v>
+        <v>0.002261002137834645</v>
       </c>
       <c r="D20" s="34" t="n">
         <v>4</v>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="R20" s="81" t="n">
-        <v>709.1099853515625</v>
+        <v>709.239990234375</v>
       </c>
       <c r="S20" s="82" t="n">
-        <v>1.469970703125</v>
+        <v>1.5999755859375</v>
       </c>
       <c r="T20" s="83" t="n">
         <v>707.1099853515625</v>
@@ -5914,61 +5914,61 @@
         <v>705.1099853515625</v>
       </c>
       <c r="W20" s="84" t="n">
-        <v>21103985</v>
+        <v>23119119</v>
       </c>
       <c r="X20" s="85" t="n">
-        <v>0.6860290406760102</v>
+        <v>0.7490817012440798</v>
       </c>
       <c r="Y20" s="35" t="n">
-        <v>47.52711002373304</v>
+        <v>47.61068544462786</v>
       </c>
       <c r="Z20" s="35" t="n">
-        <v>20.10656261846141</v>
+        <v>20.51435704412221</v>
       </c>
       <c r="AA20" s="35" t="n">
         <v>11.88075282716057</v>
       </c>
       <c r="AB20" s="86" t="n">
-        <v>0.5631868606510579</v>
+        <v>0.5735576205336201</v>
       </c>
       <c r="AC20" s="86" t="n">
-        <v>1.699550908455062</v>
+        <v>1.701625060431574</v>
       </c>
       <c r="AD20" s="86" t="n">
-        <v>-1.136364047804004</v>
+        <v>-1.128067439897954</v>
       </c>
       <c r="AE20" s="83" t="n">
-        <v>712.8576821070443</v>
+        <v>712.8865720810027</v>
       </c>
       <c r="AF20" s="83" t="n">
-        <v>713.2641550752619</v>
+        <v>713.275973700972</v>
       </c>
       <c r="AG20" s="83" t="n">
-        <v>710.8897998046875</v>
+        <v>710.8923999023438</v>
       </c>
       <c r="AH20" s="83" t="n">
-        <v>704.3402996826172</v>
+        <v>704.3415997314453</v>
       </c>
       <c r="AI20" s="83" t="n">
-        <v>656.5860992431641</v>
+        <v>656.5867492675782</v>
       </c>
       <c r="AJ20" s="83" t="n">
-        <v>732.3303006364529</v>
+        <v>732.3220368305624</v>
       </c>
       <c r="AK20" s="83" t="n">
-        <v>717.5565032958984</v>
+        <v>717.5630035400391</v>
       </c>
       <c r="AL20" s="83" t="n">
-        <v>702.782705955344</v>
+        <v>702.8039702495157</v>
       </c>
       <c r="AM20" s="87" t="n">
-        <v>0.2141385606681487</v>
+        <v>0.2180366375686611</v>
       </c>
       <c r="AN20" s="36" t="n">
-        <v>4.117807384559979</v>
+        <v>4.113655028955186</v>
       </c>
       <c r="AO20" s="88" t="n">
-        <v>1.378498839659858</v>
+        <v>1.378246158504573</v>
       </c>
       <c r="AP20" s="83" t="n">
         <v>748.6500244140625</v>
@@ -5977,22 +5977,22 @@
         <v>555.5999755859375</v>
       </c>
       <c r="AR20" s="36" t="n">
-        <v>-5.281511757572755</v>
+        <v>-5.264146516328793</v>
       </c>
       <c r="AS20" s="89" t="n">
-        <v>79.5182444643135</v>
+        <v>79.58558704392</v>
       </c>
       <c r="AT20" s="33" t="n">
-        <v>-0.003176982134666329</v>
+        <v>-0.002994229300410156</v>
       </c>
       <c r="AU20" s="33" t="n">
-        <v>-0.02036332214067338</v>
+        <v>-0.02018372016899783</v>
       </c>
       <c r="AV20" s="33" t="n">
-        <v>-0.04716415472080726</v>
+        <v>-0.04698946628746969</v>
       </c>
       <c r="AW20" s="33" t="n">
-        <v>0.1543194611348102</v>
+        <v>0.1545310886247244</v>
       </c>
       <c r="AX20" s="90" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -6102,10 +6102,10 @@
         <v>291.1900024414062</v>
       </c>
       <c r="W21" s="73" t="n">
-        <v>18861944</v>
+        <v>22223877</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>1.13048110102929</v>
+        <v>1.31869132441236</v>
       </c>
       <c r="Y21" s="28" t="n">
         <v>44.60613909456504</v>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="C22" s="33" t="n">
-        <v>0.003021430306481054</v>
+        <v>0.004154421648548512</v>
       </c>
       <c r="D22" s="34" t="n">
         <v>3</v>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="R22" s="81" t="n">
-        <v>106.2300033569336</v>
+        <v>106.3499984741211</v>
       </c>
       <c r="S22" s="82" t="n">
-        <v>0.3199996948242188</v>
+        <v>0.4399948120117188</v>
       </c>
       <c r="T22" s="83" t="n">
         <v>104.5</v>
@@ -6290,61 +6290,61 @@
         <v>101.3399963378906</v>
       </c>
       <c r="W22" s="84" t="n">
-        <v>41232447</v>
+        <v>45335726</v>
       </c>
       <c r="X22" s="85" t="n">
-        <v>0.7626886854949689</v>
+        <v>0.8354178503828386</v>
       </c>
       <c r="Y22" s="35" t="n">
-        <v>39.0111574244058</v>
+        <v>39.07870188155146</v>
       </c>
       <c r="Z22" s="35" t="n">
-        <v>8.798141162188184</v>
+        <v>9.014037371677789</v>
       </c>
       <c r="AA22" s="35" t="n">
         <v>19.57800783152739</v>
       </c>
       <c r="AB22" s="86" t="n">
-        <v>-10.78524316844376</v>
+        <v>-10.77567090838322</v>
       </c>
       <c r="AC22" s="86" t="n">
-        <v>-10.38127740758517</v>
+        <v>-10.37936295557306</v>
       </c>
       <c r="AD22" s="86" t="n">
-        <v>-0.4039657608585863</v>
+        <v>-0.3963079528101563</v>
       </c>
       <c r="AE22" s="83" t="n">
-        <v>113.3592508872043</v>
+        <v>113.3859164688015</v>
       </c>
       <c r="AF22" s="83" t="n">
-        <v>123.6561263113996</v>
+        <v>123.6670349584166</v>
       </c>
       <c r="AG22" s="83" t="n">
-        <v>150.3690000915527</v>
+        <v>150.3713999938965</v>
       </c>
       <c r="AH22" s="83" t="n">
-        <v>163.2067001342774</v>
+        <v>163.2079000854492</v>
       </c>
       <c r="AI22" s="83" t="n">
-        <v>108.0773000049591</v>
+        <v>108.077899980545</v>
       </c>
       <c r="AJ22" s="83" t="n">
-        <v>152.739329185921</v>
+        <v>152.7280183407437</v>
       </c>
       <c r="AK22" s="83" t="n">
-        <v>125.7490005493164</v>
+        <v>125.7550003051758</v>
       </c>
       <c r="AL22" s="83" t="n">
-        <v>98.75867191271179</v>
+        <v>98.78198226960782</v>
       </c>
       <c r="AM22" s="87" t="n">
-        <v>0.1384075671107075</v>
+        <v>0.1402886431643227</v>
       </c>
       <c r="AN22" s="36" t="n">
-        <v>42.92730521706136</v>
+        <v>42.89772648421331</v>
       </c>
       <c r="AO22" s="88" t="n">
-        <v>13.38049802624919</v>
+        <v>13.36540075824992</v>
       </c>
       <c r="AP22" s="83" t="n">
         <v>302</v>
@@ -6353,22 +6353,22 @@
         <v>23.97999954223633</v>
       </c>
       <c r="AR22" s="36" t="n">
-        <v>-64.82450219969087</v>
+        <v>-64.78476871717844</v>
       </c>
       <c r="AS22" s="89" t="n">
-        <v>29.58420389873805</v>
+        <v>29.62736450480593</v>
       </c>
       <c r="AT22" s="33" t="n">
-        <v>-0.08893649445020435</v>
+        <v>-0.08790737679361926</v>
       </c>
       <c r="AU22" s="33" t="n">
-        <v>-0.2406718513830964</v>
+        <v>-0.239814130708167</v>
       </c>
       <c r="AV22" s="33" t="n">
-        <v>-0.621337420256322</v>
+        <v>-0.620909691185485</v>
       </c>
       <c r="AW22" s="33" t="n">
-        <v>1.527480524440565</v>
+        <v>1.530335511846528</v>
       </c>
       <c r="AX22" s="90" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="C24" s="26" t="n">
-        <v>-0.0006766561603024357</v>
+        <v>-0.000522909067699362</v>
       </c>
       <c r="D24" s="27" t="n">
         <v>18</v>
@@ -6484,10 +6484,10 @@
         </is>
       </c>
       <c r="R24" s="70" t="n">
-        <v>324.9100036621094</v>
+        <v>324.9599914550781</v>
       </c>
       <c r="S24" s="71" t="n">
-        <v>-0.220001220703125</v>
+        <v>-0.170013427734375</v>
       </c>
       <c r="T24" s="72" t="n">
         <v>326.9700012207031</v>
@@ -6499,61 +6499,61 @@
         <v>323.5299987792969</v>
       </c>
       <c r="W24" s="73" t="n">
-        <v>27408987</v>
+        <v>33660931</v>
       </c>
       <c r="X24" s="74" t="n">
-        <v>0.6934649569864361</v>
+        <v>0.8449604356901161</v>
       </c>
       <c r="Y24" s="28" t="n">
-        <v>60.79744354811776</v>
+        <v>60.85736584032756</v>
       </c>
       <c r="Z24" s="28" t="n">
-        <v>86.29225685117461</v>
+        <v>86.48859545975958</v>
       </c>
       <c r="AA24" s="28" t="n">
         <v>14.39910545869981</v>
       </c>
       <c r="AB24" s="75" t="n">
-        <v>1.892230991609949</v>
+        <v>1.896218621818321</v>
       </c>
       <c r="AC24" s="75" t="n">
-        <v>0.1366330328525921</v>
+        <v>0.1374305588942664</v>
       </c>
       <c r="AD24" s="75" t="n">
-        <v>1.755597958757357</v>
+        <v>1.758788062924054</v>
       </c>
       <c r="AE24" s="72" t="n">
-        <v>318.4786816811892</v>
+        <v>318.4897900796267</v>
       </c>
       <c r="AF24" s="72" t="n">
-        <v>315.2645488670926</v>
+        <v>315.269093211908</v>
       </c>
       <c r="AG24" s="72" t="n">
-        <v>313.5513995361328</v>
+        <v>313.5523992919922</v>
       </c>
       <c r="AH24" s="72" t="n">
-        <v>301.8491000366211</v>
+        <v>301.8495999145508</v>
       </c>
       <c r="AI24" s="72" t="n">
-        <v>283.3282495117188</v>
+        <v>283.3284994506836</v>
       </c>
       <c r="AJ24" s="72" t="n">
-        <v>324.3210715861197</v>
+        <v>324.334061826194</v>
       </c>
       <c r="AK24" s="72" t="n">
-        <v>312.0154998779297</v>
+        <v>312.0179992675781</v>
       </c>
       <c r="AL24" s="72" t="n">
-        <v>299.7099281697397</v>
+        <v>299.7019367089623</v>
       </c>
       <c r="AM24" s="76" t="n">
-        <v>1.023929488607087</v>
+        <v>1.025411109512683</v>
       </c>
       <c r="AN24" s="29" t="n">
-        <v>7.887795133898384</v>
+        <v>7.894456465669454</v>
       </c>
       <c r="AO24" s="77" t="n">
-        <v>2.286358865593482</v>
+        <v>2.286007160655548</v>
       </c>
       <c r="AP24" s="72" t="n">
         <v>344.5700073242188</v>
@@ -6562,22 +6562,22 @@
         <v>225.9499969482422</v>
       </c>
       <c r="AR24" s="29" t="n">
-        <v>-5.705663071136236</v>
+        <v>-5.691155774532874</v>
       </c>
       <c r="AS24" s="78" t="n">
-        <v>83.42606479311942</v>
+        <v>83.4682059064192</v>
       </c>
       <c r="AT24" s="26" t="n">
-        <v>0.0365608263160917</v>
+        <v>0.03672030243994584</v>
       </c>
       <c r="AU24" s="26" t="n">
-        <v>0.05019716379272587</v>
+        <v>0.05035873788342271</v>
       </c>
       <c r="AV24" s="26" t="n">
-        <v>0.04721844077666093</v>
+        <v>0.04737955658725634</v>
       </c>
       <c r="AW24" s="26" t="n">
-        <v>0.1951372808394143</v>
+        <v>0.1953211541406068</v>
       </c>
       <c r="AX24" s="79" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="C25" s="33" t="n">
-        <v>-0.006331396699976732</v>
+        <v>-0.005548155771720742</v>
       </c>
       <c r="D25" s="34" t="n">
         <v>19</v>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="R25" s="81" t="n">
-        <v>456.7000122070312</v>
+        <v>457.0599975585938</v>
       </c>
       <c r="S25" s="82" t="n">
-        <v>-2.90997314453125</v>
+        <v>-2.54998779296875</v>
       </c>
       <c r="T25" s="83" t="n">
         <v>458.4500122070312</v>
@@ -6687,61 +6687,61 @@
         <v>452.3699951171875</v>
       </c>
       <c r="W25" s="84" t="n">
-        <v>10117521</v>
+        <v>11852873</v>
       </c>
       <c r="X25" s="85" t="n">
-        <v>0.554327425247102</v>
+        <v>0.6463327802692866</v>
       </c>
       <c r="Y25" s="35" t="n">
-        <v>42.89514686212071</v>
+        <v>42.98115350769675</v>
       </c>
       <c r="Z25" s="35" t="n">
-        <v>8.590827889075117</v>
+        <v>9.133383253087635</v>
       </c>
       <c r="AA25" s="35" t="n">
         <v>9.981757858089708</v>
       </c>
       <c r="AB25" s="86" t="n">
-        <v>-9.174014923238644</v>
+        <v>-9.145298143057062</v>
       </c>
       <c r="AC25" s="86" t="n">
-        <v>-8.07508505522207</v>
+        <v>-8.069341699185754</v>
       </c>
       <c r="AD25" s="86" t="n">
-        <v>-1.098929868016574</v>
+        <v>-1.075956443871307</v>
       </c>
       <c r="AE25" s="83" t="n">
-        <v>467.4224551616498</v>
+        <v>467.5024519064415</v>
       </c>
       <c r="AF25" s="83" t="n">
-        <v>477.1759057177553</v>
+        <v>477.2086316588064</v>
       </c>
       <c r="AG25" s="83" t="n">
-        <v>501.6390008544922</v>
+        <v>501.6462005615234</v>
       </c>
       <c r="AH25" s="83" t="n">
-        <v>462.2411009216308</v>
+        <v>462.2447007751465</v>
       </c>
       <c r="AI25" s="83" t="n">
-        <v>338.7641003417968</v>
+        <v>338.7659002685547</v>
       </c>
       <c r="AJ25" s="83" t="n">
-        <v>505.8168074202796</v>
+        <v>505.7839355910621</v>
       </c>
       <c r="AK25" s="83" t="n">
-        <v>477.1255004882813</v>
+        <v>477.1434997558594</v>
       </c>
       <c r="AL25" s="83" t="n">
-        <v>448.4341935562829</v>
+        <v>448.5030639206566</v>
       </c>
       <c r="AM25" s="87" t="n">
-        <v>0.1440474404031034</v>
+        <v>0.1493855346191973</v>
       </c>
       <c r="AN25" s="36" t="n">
-        <v>12.02673380594256</v>
+        <v>12.00495693637543</v>
       </c>
       <c r="AO25" s="88" t="n">
-        <v>4.980114835650419</v>
+        <v>4.976192443842977</v>
       </c>
       <c r="AP25" s="83" t="n">
         <v>584.72998046875</v>
@@ -6750,36 +6750,36 @@
         <v>149.2200012207031</v>
       </c>
       <c r="AR25" s="36" t="n">
-        <v>-21.89557103931686</v>
+        <v>-21.83400666540295</v>
       </c>
       <c r="AS25" s="89" t="n">
-        <v>70.60228826839381</v>
+        <v>70.68494661578325</v>
       </c>
       <c r="AT25" s="33" t="n">
-        <v>-0.05038151256472923</v>
+        <v>-0.04963299332690907</v>
       </c>
       <c r="AU25" s="33" t="n">
-        <v>-0.1193258568466818</v>
+        <v>-0.1186316817151705</v>
       </c>
       <c r="AV25" s="33" t="n">
-        <v>-0.1581877243873309</v>
+        <v>-0.1575241814053161</v>
       </c>
       <c r="AW25" s="33" t="n">
-        <v>1.132517764276793</v>
+        <v>1.134198682027105</v>
       </c>
       <c r="AX25" s="90" t="inlineStr">
         <is>
+          <t>Stanley Druckenmiller Increased Amazon More Than 10-Fold and Opened an AMD Position. What’s the Common Bet?</t>
+        </is>
+      </c>
+      <c r="AY25" s="90" t="inlineStr">
+        <is>
+          <t>Top Stock Reports for AMD, Costco &amp; AstraZeneca</t>
+        </is>
+      </c>
+      <c r="AZ25" s="90" t="inlineStr">
+        <is>
           <t>Advanced Micro Devices (AMD) Dropped, So What Is Driving Attention Now?</t>
-        </is>
-      </c>
-      <c r="AY25" s="90" t="inlineStr">
-        <is>
-          <t>Can AMD's Saudi AI Buildout Challenge NVIDIA and Broadcom?</t>
-        </is>
-      </c>
-      <c r="AZ25" s="90" t="inlineStr">
-        <is>
-          <t>Prediction: AMD Will Join the $2 Trillion Club in 2030 Amid Historic Growth in This Market</t>
         </is>
       </c>
     </row>
@@ -6791,10 +6791,10 @@
         </is>
       </c>
       <c r="C26" s="26" t="n">
-        <v>-0.0006668687045597865</v>
+        <v>0.0002353583831189443</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="N26" s="69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" s="23" t="inlineStr">
         <is>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="R26" s="70" t="n">
-        <v>254.75</v>
+        <v>254.9799957275391</v>
       </c>
       <c r="S26" s="71" t="n">
-        <v>-0.1699981689453125</v>
+        <v>0.05999755859375</v>
       </c>
       <c r="T26" s="72" t="n">
         <v>254.2550048828125</v>
@@ -6875,61 +6875,61 @@
         <v>253.3999938964844</v>
       </c>
       <c r="W26" s="73" t="n">
-        <v>18796021</v>
+        <v>23785257</v>
       </c>
       <c r="X26" s="74" t="n">
-        <v>0.5733448147975007</v>
+        <v>0.7200548473337726</v>
       </c>
       <c r="Y26" s="28" t="n">
-        <v>46.19588710679039</v>
+        <v>46.38015526474356</v>
       </c>
       <c r="Z26" s="28" t="n">
-        <v>18.04226771112378</v>
+        <v>19.51376902710851</v>
       </c>
       <c r="AA26" s="28" t="n">
         <v>17.00119561087406</v>
       </c>
       <c r="AB26" s="75" t="n">
-        <v>0.5483792847347218</v>
+        <v>0.5667265222591595</v>
       </c>
       <c r="AC26" s="75" t="n">
-        <v>2.148345949479042</v>
+        <v>2.152015396983929</v>
       </c>
       <c r="AD26" s="75" t="n">
-        <v>-1.59996666474432</v>
+        <v>-1.58528887472477</v>
       </c>
       <c r="AE26" s="72" t="n">
-        <v>258.7791721277338</v>
+        <v>258.8302822894091</v>
       </c>
       <c r="AF26" s="72" t="n">
-        <v>259.6920402023566</v>
+        <v>259.7129489048601</v>
       </c>
       <c r="AG26" s="72" t="n">
-        <v>252.8221994018555</v>
+        <v>252.8267993164062</v>
       </c>
       <c r="AH26" s="72" t="n">
-        <v>254.9098999023437</v>
+        <v>254.9121998596191</v>
       </c>
       <c r="AI26" s="72" t="n">
-        <v>238.8724499511719</v>
+        <v>238.8735999298096</v>
       </c>
       <c r="AJ26" s="72" t="n">
-        <v>276.3770075324142</v>
+        <v>276.3566829408193</v>
       </c>
       <c r="AK26" s="72" t="n">
-        <v>263.6519996643066</v>
+        <v>263.6634994506836</v>
       </c>
       <c r="AL26" s="72" t="n">
-        <v>250.926991796199</v>
+        <v>250.9703159605479</v>
       </c>
       <c r="AM26" s="76" t="n">
-        <v>0.1502163394877932</v>
+        <v>0.1579461830874498</v>
       </c>
       <c r="AN26" s="29" t="n">
-        <v>9.652881741317827</v>
+        <v>9.628320580270412</v>
       </c>
       <c r="AO26" s="77" t="n">
-        <v>2.720516068307137</v>
+        <v>2.718062122574544</v>
       </c>
       <c r="AP26" s="72" t="n">
         <v>287.2000122070312</v>
@@ -6938,36 +6938,36 @@
         <v>196</v>
       </c>
       <c r="AR26" s="29" t="n">
-        <v>-11.29875028822747</v>
+        <v>-11.2186682137973</v>
       </c>
       <c r="AS26" s="78" t="n">
-        <v>64.41885102672229</v>
+        <v>64.67103929070733</v>
       </c>
       <c r="AT26" s="26" t="n">
-        <v>-0.02124634549420756</v>
+        <v>-0.02036269815819358</v>
       </c>
       <c r="AU26" s="26" t="n">
-        <v>-0.08171729626723456</v>
+        <v>-0.08088824386868088</v>
       </c>
       <c r="AV26" s="26" t="n">
-        <v>0.01891846910931383</v>
+        <v>0.01983837841100478</v>
       </c>
       <c r="AW26" s="26" t="n">
-        <v>0.1036738233968091</v>
+        <v>0.1046702523034939</v>
       </c>
       <c r="AX26" s="79" t="inlineStr">
         <is>
+          <t>Stanley Druckenmiller Increased Amazon More Than 10-Fold and Opened an AMD Position. What’s the Common Bet?</t>
+        </is>
+      </c>
+      <c r="AY26" s="79" t="inlineStr">
+        <is>
           <t>How Could Amazon.com (AMZN) Gain From New Creator Shopping Tools?</t>
         </is>
       </c>
-      <c r="AY26" s="79" t="inlineStr">
+      <c r="AZ26" s="79" t="inlineStr">
         <is>
           <t>DoJ requests beef price data from major retailers including Amazon and Walmart</t>
-        </is>
-      </c>
-      <c r="AZ26" s="79" t="inlineStr">
-        <is>
-          <t>What's Wrong With Amazon Stock? Here's the Honest Answer.</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="C27" s="33" t="n">
-        <v>0.003911855333165182</v>
+        <v>0.003731313815136028</v>
       </c>
       <c r="D27" s="34" t="n">
         <v>13</v>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="R27" s="81" t="n">
-        <v>83.40499877929688</v>
+        <v>83.38999938964844</v>
       </c>
       <c r="S27" s="82" t="n">
-        <v>0.3249969482421875</v>
+        <v>0.30999755859375</v>
       </c>
       <c r="T27" s="83" t="n">
         <v>82.98999786376953</v>
@@ -7063,61 +7063,61 @@
         <v>82.58000183105469</v>
       </c>
       <c r="W27" s="84" t="n">
-        <v>2826609</v>
+        <v>3715137</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>0.6152123936978083</v>
+        <v>0.8008569866919399</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>54.29465561037647</v>
+        <v>54.26467799669614</v>
       </c>
       <c r="Z27" s="35" t="n">
-        <v>49.57262356356567</v>
+        <v>49.40169037792232</v>
       </c>
       <c r="AA27" s="35" t="n">
         <v>24.16780966287277</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.036513476548123</v>
+        <v>2.035316944040559</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>2.007173528412367</v>
+        <v>2.006934221910854</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.02933994813575591</v>
+        <v>0.02838272212970505</v>
       </c>
       <c r="AE27" s="83" t="n">
-        <v>84.28415704117887</v>
+        <v>84.28082384347923</v>
       </c>
       <c r="AF27" s="83" t="n">
-        <v>82.29890519434441</v>
+        <v>82.29754161346727</v>
       </c>
       <c r="AG27" s="83" t="n">
-        <v>79.19229965209961</v>
+        <v>79.19199966430664</v>
       </c>
       <c r="AH27" s="83" t="n">
-        <v>78.17714996337891</v>
+        <v>78.17699996948242</v>
       </c>
       <c r="AI27" s="83" t="n">
-        <v>76.781425075531</v>
+        <v>76.78135007858276</v>
       </c>
       <c r="AJ27" s="83" t="n">
-        <v>88.57157435439305</v>
+        <v>88.57031181052821</v>
       </c>
       <c r="AK27" s="83" t="n">
-        <v>82.33174972534179</v>
+        <v>82.33099975585938</v>
       </c>
       <c r="AL27" s="83" t="n">
-        <v>76.09192509629054</v>
+        <v>76.09168770119055</v>
       </c>
       <c r="AM27" s="87" t="n">
-        <v>0.5859999373186122</v>
+        <v>0.584865096064286</v>
       </c>
       <c r="AN27" s="36" t="n">
-        <v>15.1577602804927</v>
+        <v>15.15665320030269</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.885527362136531</v>
+        <v>2.886046382997098</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -7126,36 +7126,36 @@
         <v>62.94499969482422</v>
       </c>
       <c r="AR27" s="36" t="n">
-        <v>-9.978416183835382</v>
+        <v>-9.994605487020936</v>
       </c>
       <c r="AS27" s="89" t="n">
-        <v>68.8772860572021</v>
+        <v>68.82679156562203</v>
       </c>
       <c r="AT27" s="33" t="n">
-        <v>-0.03432909428039232</v>
+        <v>-0.03450275862184715</v>
       </c>
       <c r="AU27" s="33" t="n">
-        <v>0.1341446524470551</v>
+        <v>0.133940690120951</v>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>0.04373664068350824</v>
+        <v>0.0435489371550255</v>
       </c>
       <c r="AW27" s="33" t="n">
-        <v>0.08430838227671367</v>
+        <v>0.08411338240664756</v>
       </c>
       <c r="AX27" s="90" t="inlineStr">
         <is>
+          <t>Nvidia Blew Wall Street Away with Its Q2 Results. Cathie Wood Is Celebrating by Buying More Than 243,000 Sh...</t>
+        </is>
+      </c>
+      <c r="AY27" s="90" t="inlineStr">
+        <is>
           <t>Cathie Wood's Ark Has Delivered Just a 13.8% Annualized Return Since 2014, Roughly Matching the S&amp;P 500. Sh...</t>
         </is>
       </c>
-      <c r="AY27" s="90" t="inlineStr">
+      <c r="AZ27" s="90" t="inlineStr">
         <is>
           <t>Cathie Wood buys $53 million of popular semiconductor stock</t>
-        </is>
-      </c>
-      <c r="AZ27" s="90" t="inlineStr">
-        <is>
-          <t>Cathie Wood sells $4 million of surging AI stock</t>
         </is>
       </c>
     </row>
@@ -7167,10 +7167,10 @@
         </is>
       </c>
       <c r="C28" s="26" t="n">
-        <v>0.0007665133726562079</v>
+        <v>0.0001703146447720183</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="R28" s="70" t="n">
-        <v>235</v>
+        <v>234.8600006103516</v>
       </c>
       <c r="S28" s="71" t="n">
-        <v>0.17999267578125</v>
+        <v>0.0399932861328125</v>
       </c>
       <c r="T28" s="72" t="n">
         <v>233.375</v>
@@ -7251,61 +7251,61 @@
         <v>229.3899993896484</v>
       </c>
       <c r="W28" s="73" t="n">
-        <v>2116120</v>
+        <v>2423600</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>0.5828871717279394</v>
+        <v>0.6596615954523741</v>
       </c>
       <c r="Y28" s="28" t="n">
-        <v>39.031859921825</v>
+        <v>38.55073600426524</v>
       </c>
       <c r="Z28" s="28" t="n">
-        <v>9.853064564074659</v>
+        <v>9.128219696542685</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>9.232053722506933</v>
+        <v>9.470357924200014</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-11.03853766879146</v>
+        <v>-11.09515337438438</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-10.36383271832425</v>
+        <v>-10.28828006087829</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-0.6747049504672162</v>
+        <v>-0.8068733135060899</v>
       </c>
       <c r="AE28" s="72" t="n">
-        <v>242.437633132584</v>
+        <v>243.7305990629119</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>253.3040630054915</v>
+        <v>254.7670310276704</v>
       </c>
       <c r="AG28" s="72" t="n">
-        <v>277.8237991333008</v>
+        <v>280.3677993774414</v>
       </c>
       <c r="AH28" s="72" t="n">
-        <v>275.9315995788574</v>
+        <v>275.0289994812012</v>
       </c>
       <c r="AI28" s="72" t="n">
-        <v>200.6999249649048</v>
+        <v>200.2055249404907</v>
       </c>
       <c r="AJ28" s="72" t="n">
-        <v>290.6307946936363</v>
+        <v>292.1762327516705</v>
       </c>
       <c r="AK28" s="72" t="n">
-        <v>257.0755004882812</v>
+        <v>258.8449996948242</v>
       </c>
       <c r="AL28" s="72" t="n">
-        <v>223.5202062829262</v>
+        <v>225.5137666379779</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.1710578611949969</v>
+        <v>0.1402023434961691</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>26.10540027472176</v>
+        <v>25.75381645088256</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>7.112505803819667</v>
+        <v>7.476826938691822</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -7314,22 +7314,22 @@
         <v>100.0199966430664</v>
       </c>
       <c r="AR28" s="29" t="n">
-        <v>-48.08924372360553</v>
+        <v>-48.12016914571142</v>
       </c>
       <c r="AS28" s="78" t="n">
-        <v>38.27265436094793</v>
+        <v>38.23295849402318</v>
       </c>
       <c r="AT28" s="26" t="n">
-        <v>-0.06396876330266665</v>
+        <v>-0.02773636784218381</v>
       </c>
       <c r="AU28" s="26" t="n">
-        <v>-0.1623894994120776</v>
+        <v>-0.01756879859087579</v>
       </c>
       <c r="AV28" s="26" t="n">
-        <v>-0.4293761803118153</v>
+        <v>-0.4168011581690544</v>
       </c>
       <c r="AW28" s="26" t="n">
-        <v>1.149849101167826</v>
+        <v>1.148568345584848</v>
       </c>
       <c r="AX28" s="79" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="C29" s="33" t="n">
-        <v>0.1177867782454238</v>
+        <v>0.1182796125279308</v>
       </c>
       <c r="D29" s="34" t="n">
         <v>2</v>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="R29" s="81" t="n">
-        <v>62.37250137329102</v>
+        <v>62.40000152587891</v>
       </c>
       <c r="S29" s="82" t="n">
-        <v>6.572502136230469</v>
+        <v>6.600002288818359</v>
       </c>
       <c r="T29" s="83" t="n">
         <v>58.32500076293945</v>
@@ -7439,61 +7439,61 @@
         <v>58</v>
       </c>
       <c r="W29" s="84" t="n">
-        <v>17053589</v>
+        <v>19740307</v>
       </c>
       <c r="X29" s="85" t="n">
-        <v>1.631387788907778</v>
+        <v>1.864445959054976</v>
       </c>
       <c r="Y29" s="35" t="n">
-        <v>47.19011437480498</v>
+        <v>47.22465818876867</v>
       </c>
       <c r="Z29" s="35" t="n">
-        <v>35.56770366387878</v>
+        <v>35.71429297650321</v>
       </c>
       <c r="AA29" s="35" t="n">
         <v>15.17849151015382</v>
       </c>
       <c r="AB29" s="86" t="n">
-        <v>-2.433098703539329</v>
+        <v>-2.430904959173347</v>
       </c>
       <c r="AC29" s="86" t="n">
-        <v>-1.81484074275798</v>
+        <v>-1.814401993884784</v>
       </c>
       <c r="AD29" s="86" t="n">
-        <v>-0.618257960781349</v>
+        <v>-0.6165029652885632</v>
       </c>
       <c r="AE29" s="83" t="n">
-        <v>60.86567623038943</v>
+        <v>60.87178737540896</v>
       </c>
       <c r="AF29" s="83" t="n">
-        <v>63.61404269809417</v>
+        <v>63.61654271196579</v>
       </c>
       <c r="AG29" s="83" t="n">
-        <v>66.9180493927002</v>
+        <v>66.91859939575195</v>
       </c>
       <c r="AH29" s="83" t="n">
-        <v>77.26612495422363</v>
+        <v>77.26639995574951</v>
       </c>
       <c r="AI29" s="83" t="n">
-        <v>81.37208734512329</v>
+        <v>81.37222484588624</v>
       </c>
       <c r="AJ29" s="83" t="n">
-        <v>76.29092835361851</v>
+        <v>76.29051826036167</v>
       </c>
       <c r="AK29" s="83" t="n">
-        <v>65.79262466430664</v>
+        <v>65.79399967193604</v>
       </c>
       <c r="AL29" s="83" t="n">
-        <v>55.29432097499478</v>
+        <v>55.29748108351041</v>
       </c>
       <c r="AM29" s="87" t="n">
-        <v>0.3371106708173439</v>
+        <v>0.3383274360224711</v>
       </c>
       <c r="AN29" s="36" t="n">
-        <v>31.91331473057142</v>
+        <v>31.90722145108575</v>
       </c>
       <c r="AO29" s="88" t="n">
-        <v>7.562864142814421</v>
+        <v>7.559531131390654</v>
       </c>
       <c r="AP29" s="83" t="n">
         <v>133.8600006103516</v>
@@ -7502,36 +7502,36 @@
         <v>36.08000183105469</v>
       </c>
       <c r="AR29" s="36" t="n">
-        <v>-53.40467571425689</v>
+        <v>-53.38413174857446</v>
       </c>
       <c r="AS29" s="89" t="n">
-        <v>26.88944556195196</v>
+        <v>26.91757007916531</v>
       </c>
       <c r="AT29" s="33" t="n">
-        <v>0.04162492085363345</v>
+        <v>0.04208417523067665</v>
       </c>
       <c r="AU29" s="33" t="n">
-        <v>-0.1128928525233971</v>
+        <v>-0.1125017253218213</v>
       </c>
       <c r="AV29" s="33" t="n">
-        <v>-0.4210294307089458</v>
+        <v>-0.4207741615013809</v>
       </c>
       <c r="AW29" s="33" t="n">
-        <v>-0.1412294680989298</v>
+        <v>-0.1408508345641943</v>
       </c>
       <c r="AX29" s="90" t="inlineStr">
         <is>
+          <t>AST SpaceMobile Stock Soars on New Buy Call</t>
+        </is>
+      </c>
+      <c r="AY29" s="90" t="inlineStr">
+        <is>
           <t>Why Is AST SpaceMobile Stock Up 13% Today?</t>
         </is>
       </c>
-      <c r="AY29" s="90" t="inlineStr">
+      <c r="AZ29" s="90" t="inlineStr">
         <is>
           <t>ASTS Stock Pops 10% To Best Day In A Month After Berenberg’s Bullish Ratings, Early Investor Cisnero’s Stoc...</t>
-        </is>
-      </c>
-      <c r="AZ29" s="90" t="inlineStr">
-        <is>
-          <t>AST SpaceMobile Stock Soars on New Buy Call</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="C30" s="26" t="n">
-        <v>-0.007425327774216117</v>
+        <v>-0.006600309699600682</v>
       </c>
       <c r="D30" s="27" t="n">
         <v>20</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="R30" s="70" t="n">
-        <v>366.9349975585938</v>
+        <v>367.239990234375</v>
       </c>
       <c r="S30" s="71" t="n">
-        <v>-2.7449951171875</v>
+        <v>-2.44000244140625</v>
       </c>
       <c r="T30" s="72" t="n">
         <v>369.6799926757812</v>
@@ -7627,61 +7627,61 @@
         <v>364.6499938964844</v>
       </c>
       <c r="W30" s="73" t="n">
-        <v>19893110</v>
+        <v>30822042</v>
       </c>
       <c r="X30" s="74" t="n">
-        <v>1.031641097091058</v>
+        <v>1.5543590652599</v>
       </c>
       <c r="Y30" s="28" t="n">
-        <v>41.98284966517424</v>
+        <v>42.128064745238</v>
       </c>
       <c r="Z30" s="28" t="n">
-        <v>27.02594385039545</v>
+        <v>27.51440103145891</v>
       </c>
       <c r="AA30" s="28" t="n">
         <v>21.5747155555884</v>
       </c>
       <c r="AB30" s="75" t="n">
-        <v>-7.94129012974787</v>
+        <v>-7.916960229685571</v>
       </c>
       <c r="AC30" s="75" t="n">
-        <v>-6.714560407106689</v>
+        <v>-6.70969442709423</v>
       </c>
       <c r="AD30" s="75" t="n">
-        <v>-1.22672972264118</v>
+        <v>-1.207265802591341</v>
       </c>
       <c r="AE30" s="72" t="n">
-        <v>368.8930581312652</v>
+        <v>368.9608342814388</v>
       </c>
       <c r="AF30" s="72" t="n">
-        <v>377.5787726877589</v>
+        <v>377.6064992946481</v>
       </c>
       <c r="AG30" s="72" t="n">
-        <v>384.5739001464844</v>
+        <v>384.58</v>
       </c>
       <c r="AH30" s="72" t="n">
-        <v>398.5821508789062</v>
+        <v>398.585200805664</v>
       </c>
       <c r="AI30" s="72" t="n">
-        <v>369.6823753356933</v>
+        <v>369.6839002990723</v>
       </c>
       <c r="AJ30" s="72" t="n">
-        <v>434.8445013691686</v>
+        <v>434.8378629372111</v>
       </c>
       <c r="AK30" s="72" t="n">
-        <v>384.9717498779297</v>
+        <v>384.9869995117188</v>
       </c>
       <c r="AL30" s="72" t="n">
-        <v>335.0989983866908</v>
+        <v>335.1361360862264</v>
       </c>
       <c r="AM30" s="76" t="n">
-        <v>0.3191722756412942</v>
+        <v>0.3219989779728829</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>25.90982403620681</v>
+        <v>25.89742692024329</v>
       </c>
       <c r="AO30" s="77" t="n">
-        <v>3.449206560447345</v>
+        <v>3.446341995677256</v>
       </c>
       <c r="AP30" s="72" t="n">
         <v>495</v>
@@ -7690,36 +7690,36 @@
         <v>289.9599914550781</v>
       </c>
       <c r="AR30" s="29" t="n">
-        <v>-25.87171766493056</v>
+        <v>-25.81010298295454</v>
       </c>
       <c r="AS30" s="78" t="n">
-        <v>37.54145673801575</v>
+        <v>37.69020462285327</v>
       </c>
       <c r="AT30" s="26" t="n">
-        <v>0.0319047254915541</v>
+        <v>0.03276243431048109</v>
       </c>
       <c r="AU30" s="26" t="n">
-        <v>-0.1225009700949485</v>
+        <v>-0.1217716017356836</v>
       </c>
       <c r="AV30" s="26" t="n">
-        <v>-0.2343238337611916</v>
+        <v>-0.2336874114404076</v>
       </c>
       <c r="AW30" s="26" t="n">
-        <v>0.06019933859477189</v>
+        <v>0.06108056561124875</v>
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
-          <t>Marvell vs. Broadcom: One AI Stock Looks More Attractive Right Now</t>
+          <t>Broadcom stock sinks as chipmaker results 'not enough to keep investors happy'</t>
         </is>
       </c>
       <c r="AY30" s="79" t="inlineStr">
         <is>
-          <t>Broadcom Earnings Prediction Market Preview: Will Hock Tan Talk ‘Competition’?</t>
+          <t>Broadcom's Q3 earnings beat just isn't 'enough' to keep investors happy</t>
         </is>
       </c>
       <c r="AZ30" s="79" t="inlineStr">
         <is>
-          <t>Jensen Huang Says the $3.5 Billion MediaTek Deal Is Not Circular. The Decade Long Roadmap Is the Real Tell.</t>
+          <t>Broadcom's price sinks over 6% after releasing Q3 earnings</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>0.001651740894481168</v>
+        <v>0.001246572974491267</v>
       </c>
       <c r="D31" s="34" t="n">
         <v>15</v>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="N31" s="80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O31" s="30" t="inlineStr">
         <is>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="R31" s="81" t="n">
-        <v>96.41899871826172</v>
+        <v>96.37999725341797</v>
       </c>
       <c r="S31" s="82" t="n">
-        <v>0.15899658203125</v>
+        <v>0.1199951171875</v>
       </c>
       <c r="T31" s="83" t="n">
         <v>96</v>
@@ -7815,61 +7815,61 @@
         <v>95.12999725341797</v>
       </c>
       <c r="W31" s="84" t="n">
-        <v>2124169</v>
+        <v>2386914</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>0.8031967409444173</v>
+        <v>0.8980853837940804</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>47.17209720471838</v>
+        <v>47.10679167818135</v>
       </c>
       <c r="Z31" s="35" t="n">
-        <v>14.23139788445468</v>
+        <v>14.01017570113195</v>
       </c>
       <c r="AA31" s="35" t="n">
         <v>17.23665722789432</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>1.546599243860342</v>
+        <v>1.543488015895591</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.831731254579817</v>
+        <v>1.831109008986867</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>-0.2851320107194752</v>
+        <v>-0.2876209930912765</v>
       </c>
       <c r="AE31" s="83" t="n">
-        <v>99.85741284333288</v>
+        <v>99.84874585114538</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>98.54542436721339</v>
+        <v>98.54187877950032</v>
       </c>
       <c r="AG31" s="83" t="n">
-        <v>95.74998001098633</v>
+        <v>95.74919998168946</v>
       </c>
       <c r="AH31" s="83" t="n">
-        <v>104.3442897796631</v>
+        <v>104.3438997650147</v>
       </c>
       <c r="AI31" s="83" t="n">
-        <v>105.1310947799683</v>
+        <v>105.130899772644</v>
       </c>
       <c r="AJ31" s="83" t="n">
-        <v>106.8653910415203</v>
+        <v>106.8660775204759</v>
       </c>
       <c r="AK31" s="83" t="n">
-        <v>99.04444999694825</v>
+        <v>99.04249992370606</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>91.22350895237622</v>
+        <v>91.21892232693625</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.3321524696501407</v>
+        <v>0.3298411029125995</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>15.79279009538243</v>
+        <v>15.79842512617599</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>4.443967201081712</v>
+        <v>4.445765512302909</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -7878,22 +7878,22 @@
         <v>73.19999694824219</v>
       </c>
       <c r="AR31" s="36" t="n">
-        <v>-28.70526855817425</v>
+        <v>-28.73410726215205</v>
       </c>
       <c r="AS31" s="89" t="n">
-        <v>37.42585198583127</v>
+        <v>37.36298696411627</v>
       </c>
       <c r="AT31" s="33" t="n">
-        <v>-0.0985508644019909</v>
+        <v>-0.09891550038906627</v>
       </c>
       <c r="AU31" s="33" t="n">
-        <v>0.07466559748566715</v>
+        <v>0.07423089547593587</v>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>-0.1999087460867778</v>
+        <v>-0.2002323828318811</v>
       </c>
       <c r="AW31" s="33" t="n">
-        <v>0.05387475100646055</v>
+        <v>0.05344845888978766</v>
       </c>
       <c r="AX31" s="90" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="C32" s="26" t="n">
-        <v>-0.01246177962225503</v>
+        <v>-0.01124005114350968</v>
       </c>
       <c r="D32" s="27" t="n">
         <v>23</v>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="R32" s="70" t="n">
-        <v>80.83000183105469</v>
+        <v>80.93000030517578</v>
       </c>
       <c r="S32" s="71" t="n">
-        <v>-1.019996643066406</v>
+        <v>-0.9199981689453125</v>
       </c>
       <c r="T32" s="72" t="n">
         <v>80.09999847412109</v>
@@ -8003,61 +8003,61 @@
         <v>79.58000183105469</v>
       </c>
       <c r="W32" s="73" t="n">
-        <v>13883601</v>
+        <v>15457881</v>
       </c>
       <c r="X32" s="74" t="n">
-        <v>0.5152854397147413</v>
+        <v>0.5720431490458409</v>
       </c>
       <c r="Y32" s="28" t="n">
-        <v>41.6720250020694</v>
+        <v>41.76587281159821</v>
       </c>
       <c r="Z32" s="28" t="n">
-        <v>4.069010254978727</v>
+        <v>4.394526108323491</v>
       </c>
       <c r="AA32" s="28" t="n">
         <v>11.9401643986182</v>
       </c>
       <c r="AB32" s="75" t="n">
-        <v>-1.229322460242884</v>
+        <v>-1.221345373988214</v>
       </c>
       <c r="AC32" s="75" t="n">
-        <v>0.2612076917350954</v>
+        <v>0.2628031089860293</v>
       </c>
       <c r="AD32" s="75" t="n">
-        <v>-1.490530151977979</v>
+        <v>-1.484148482974244</v>
       </c>
       <c r="AE32" s="72" t="n">
-        <v>85.06049984477102</v>
+        <v>85.08272172790905</v>
       </c>
       <c r="AF32" s="72" t="n">
-        <v>87.42338785722086</v>
+        <v>87.43247862759551</v>
       </c>
       <c r="AG32" s="72" t="n">
-        <v>86.12980041503906</v>
+        <v>86.13180038452148</v>
       </c>
       <c r="AH32" s="72" t="n">
-        <v>98.98254981994629</v>
+        <v>98.9835498046875</v>
       </c>
       <c r="AI32" s="72" t="n">
-        <v>91.36417503356934</v>
+        <v>91.36467502593995</v>
       </c>
       <c r="AJ32" s="72" t="n">
-        <v>107.4067135947167</v>
+        <v>107.3991371176112</v>
       </c>
       <c r="AK32" s="72" t="n">
-        <v>91.11700096130372</v>
+        <v>91.12200088500977</v>
       </c>
       <c r="AL32" s="72" t="n">
-        <v>74.82728832789073</v>
+        <v>74.84486465240829</v>
       </c>
       <c r="AM32" s="76" t="n">
-        <v>0.1842486002746103</v>
+        <v>0.1869227966704478</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>35.75559437109005</v>
+        <v>35.72602900399915</v>
       </c>
       <c r="AO32" s="77" t="n">
-        <v>7.705982610809676</v>
+        <v>7.696460968652518</v>
       </c>
       <c r="AP32" s="72" t="n">
         <v>153.1999969482422</v>
@@ -8066,22 +8066,22 @@
         <v>60.54999923706055</v>
       </c>
       <c r="AR32" s="29" t="n">
-        <v>-47.23890114804462</v>
+        <v>-47.17362799131285</v>
       </c>
       <c r="AS32" s="78" t="n">
-        <v>21.88883226658365</v>
+        <v>21.99676370381133</v>
       </c>
       <c r="AT32" s="26" t="n">
-        <v>-0.08158163993749112</v>
+        <v>-0.08044542278382827</v>
       </c>
       <c r="AU32" s="26" t="n">
-        <v>-0.1204570131775996</v>
+        <v>-0.1193688905175262</v>
       </c>
       <c r="AV32" s="26" t="n">
-        <v>-0.2713422734275128</v>
+        <v>-0.2704408177902101</v>
       </c>
       <c r="AW32" s="26" t="n">
-        <v>0.1287529834117935</v>
+        <v>0.1301494151010658</v>
       </c>
       <c r="AX32" s="79" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>0.1560941090303309</v>
+        <v>0.1581176757812499</v>
       </c>
       <c r="D33" s="34" t="n">
         <v>1</v>
@@ -8176,10 +8176,10 @@
         </is>
       </c>
       <c r="R33" s="81" t="n">
-        <v>491.3399963378906</v>
+        <v>492.2000122070312</v>
       </c>
       <c r="S33" s="82" t="n">
-        <v>66.33999633789062</v>
+        <v>67.20001220703125</v>
       </c>
       <c r="T33" s="83" t="n">
         <v>462.0499877929688</v>
@@ -8191,61 +8191,61 @@
         <v>432.2651062011719</v>
       </c>
       <c r="W33" s="84" t="n">
-        <v>34570821</v>
+        <v>36411468</v>
       </c>
       <c r="X33" s="85" t="n">
-        <v>4.798346637556556</v>
+        <v>4.990081362593337</v>
       </c>
       <c r="Y33" s="35" t="n">
-        <v>58.72595100645445</v>
+        <v>58.85987553832133</v>
       </c>
       <c r="Z33" s="35" t="n">
-        <v>88.05627740468624</v>
+        <v>89.14669952004557</v>
       </c>
       <c r="AA33" s="35" t="n">
         <v>8.695768462542427</v>
       </c>
       <c r="AB33" s="86" t="n">
-        <v>7.860057960771655</v>
+        <v>7.928663215289987</v>
       </c>
       <c r="AC33" s="86" t="n">
-        <v>8.73136977867172</v>
+        <v>8.745090829575387</v>
       </c>
       <c r="AD33" s="86" t="n">
-        <v>-0.8713118179000645</v>
+        <v>-0.8164276142854003</v>
       </c>
       <c r="AE33" s="83" t="n">
-        <v>458.8889672282313</v>
+        <v>459.0800818658181</v>
       </c>
       <c r="AF33" s="83" t="n">
-        <v>452.5032376582419</v>
+        <v>452.5814209190729</v>
       </c>
       <c r="AG33" s="83" t="n">
-        <v>435.4947985839844</v>
+        <v>435.5119989013672</v>
       </c>
       <c r="AH33" s="83" t="n">
-        <v>363.785598449707</v>
+        <v>363.7941986083985</v>
       </c>
       <c r="AI33" s="83" t="n">
-        <v>249.5254494476318</v>
+        <v>249.5297495269775</v>
       </c>
       <c r="AJ33" s="83" t="n">
-        <v>500.3981115226883</v>
+        <v>500.5772860043821</v>
       </c>
       <c r="AK33" s="83" t="n">
-        <v>458.6159988403321</v>
+        <v>458.6589996337891</v>
       </c>
       <c r="AL33" s="83" t="n">
-        <v>416.8338861579758</v>
+        <v>416.740713263196</v>
       </c>
       <c r="AM33" s="87" t="n">
-        <v>0.8916029539523175</v>
+        <v>0.9000761419098976</v>
       </c>
       <c r="AN33" s="36" t="n">
-        <v>18.22095730982239</v>
+        <v>18.27862808930477</v>
       </c>
       <c r="AO33" s="88" t="n">
-        <v>6.336184666461129</v>
+        <v>6.325113518090922</v>
       </c>
       <c r="AP33" s="83" t="n">
         <v>514</v>
@@ -8254,36 +8254,36 @@
         <v>110.2200012207031</v>
       </c>
       <c r="AR33" s="36" t="n">
-        <v>-4.408561023756685</v>
+        <v>-4.241242761277963</v>
       </c>
       <c r="AS33" s="89" t="n">
-        <v>94.38803216340213</v>
+        <v>94.60102336448703</v>
       </c>
       <c r="AT33" s="33" t="n">
-        <v>0.05933333745655966</v>
+        <v>0.06118753920629039</v>
       </c>
       <c r="AU33" s="33" t="n">
-        <v>0.05151199069092049</v>
+        <v>0.05335250236374578</v>
       </c>
       <c r="AV33" s="33" t="n">
-        <v>0.1668566828301801</v>
+        <v>0.1688990878281982</v>
       </c>
       <c r="AW33" s="33" t="n">
-        <v>2.903241238151119</v>
+        <v>2.910073267765874</v>
       </c>
       <c r="AX33" s="90" t="inlineStr">
         <is>
-          <t>Dell Print Showed 'Broad-Based Strength' But Computer Maker Faces AI Growth Slowdown Concerns, UBS Says</t>
+          <t>Stock Market Today, Sept. 2: Dell Helps Stocks Edge Higher Despite Geopolitical Tensions</t>
         </is>
       </c>
       <c r="AY33" s="90" t="inlineStr">
         <is>
-          <t>Dell Stock Is Surging Thanks to Massive AI Demand Driven by Tech Infrastructure Spending</t>
+          <t>Stock Market Today, Sept. 2: Dell Surges 16% on Soaring AI Backlog</t>
         </is>
       </c>
       <c r="AZ33" s="90" t="inlineStr">
         <is>
-          <t>DELL Q2 Earnings Beat Estimates, Strong AI Demand Aids Revenue Growth</t>
+          <t>Stock Market Today: Dow Rises Nearly 300 Points; Dell Retakes A Breakout Point (Live Coverage)</t>
         </is>
       </c>
     </row>
@@ -8379,10 +8379,10 @@
         <v>329.5201110839844</v>
       </c>
       <c r="W34" s="73" t="n">
-        <v>9483467</v>
+        <v>12897448</v>
       </c>
       <c r="X34" s="74" t="n">
-        <v>0.6219267054712201</v>
+        <v>0.8364522855405842</v>
       </c>
       <c r="Y34" s="28" t="n">
         <v>41.85444003414893</v>
@@ -8461,17 +8461,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
-          <t>US judge rejects bid to break up Google's ad business</t>
+          <t>Google Dodges Major Breakup Threat</t>
         </is>
       </c>
       <c r="AY34" s="79" t="inlineStr">
         <is>
-          <t>Sector Update: Tech Stocks Mixed Late Afternoon</t>
+          <t>Stock Market Today, Sept. 2: Eos Energy Surges 19% on Google Partnership for $350M West Virginia Project</t>
         </is>
       </c>
       <c r="AZ34" s="79" t="inlineStr">
         <is>
-          <t>The $277 Billion That GOOGL Stock Quietly Paid Its Owners</t>
+          <t>Google spared from ad-business breakup, but judge orders changes to how it operates</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="C35" s="33" t="n">
-        <v>0.07509504108000065</v>
+        <v>0.07550241179626238</v>
       </c>
       <c r="D35" s="34" t="n">
         <v>3</v>
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="R35" s="81" t="n">
-        <v>39.58499908447266</v>
+        <v>39.59999847412109</v>
       </c>
       <c r="S35" s="82" t="n">
-        <v>2.764999389648438</v>
+        <v>2.779998779296875</v>
       </c>
       <c r="T35" s="83" t="n">
         <v>35.79499816894531</v>
@@ -8567,61 +8567,61 @@
         <v>35.7599983215332</v>
       </c>
       <c r="W35" s="84" t="n">
-        <v>34952380</v>
+        <v>40267008</v>
       </c>
       <c r="X35" s="85" t="n">
-        <v>0.7819274705279278</v>
+        <v>0.8954986925525983</v>
       </c>
       <c r="Y35" s="35" t="n">
-        <v>48.59992158304607</v>
+        <v>48.62675899852136</v>
       </c>
       <c r="Z35" s="35" t="n">
-        <v>40.5347895245423</v>
+        <v>40.6621188216794</v>
       </c>
       <c r="AA35" s="35" t="n">
         <v>14.03012261147245</v>
       </c>
       <c r="AB35" s="86" t="n">
-        <v>-0.8514513879848664</v>
+        <v>-0.8502548554773028</v>
       </c>
       <c r="AC35" s="86" t="n">
-        <v>-0.5056500188779449</v>
+        <v>-0.5054107123764322</v>
       </c>
       <c r="AD35" s="86" t="n">
-        <v>-0.3458013691069215</v>
+        <v>-0.3448441431008706</v>
       </c>
       <c r="AE35" s="83" t="n">
-        <v>38.92792509645874</v>
+        <v>38.9312582941584</v>
       </c>
       <c r="AF35" s="83" t="n">
-        <v>39.96871185687949</v>
+        <v>39.97007543775663</v>
       </c>
       <c r="AG35" s="83" t="n">
-        <v>40.45759998321533</v>
+        <v>40.4578999710083</v>
       </c>
       <c r="AH35" s="83" t="n">
-        <v>47.56729997634888</v>
+        <v>47.56744997024536</v>
       </c>
       <c r="AI35" s="83" t="n">
-        <v>45.69725004196167</v>
+        <v>45.69732503890991</v>
       </c>
       <c r="AJ35" s="83" t="n">
-        <v>46.04870353323724</v>
+        <v>46.04878198840085</v>
       </c>
       <c r="AK35" s="83" t="n">
-        <v>40.77300014495849</v>
+        <v>40.77375011444092</v>
       </c>
       <c r="AL35" s="83" t="n">
-        <v>35.49729675667975</v>
+        <v>35.49871824048098</v>
       </c>
       <c r="AM35" s="87" t="n">
-        <v>0.3874082778113274</v>
+        <v>0.3887445926048316</v>
       </c>
       <c r="AN35" s="36" t="n">
-        <v>25.87841644972046</v>
+        <v>25.87464660059151</v>
       </c>
       <c r="AO35" s="88" t="n">
-        <v>8.833043149281368</v>
+        <v>8.829697435617662</v>
       </c>
       <c r="AP35" s="83" t="n">
         <v>76.87000274658203</v>
@@ -8630,36 +8630,36 @@
         <v>25.30999946594238</v>
       </c>
       <c r="AR35" s="36" t="n">
-        <v>-48.50397076871084</v>
+        <v>-48.48445809912258</v>
       </c>
       <c r="AS35" s="89" t="n">
-        <v>27.68618834415477</v>
+        <v>27.71527947816188</v>
       </c>
       <c r="AT35" s="33" t="n">
-        <v>0.0001262570284685793</v>
+        <v>0.0005052208726963325</v>
       </c>
       <c r="AU35" s="33" t="n">
-        <v>-0.03096693847980991</v>
+        <v>-0.03059975634495771</v>
       </c>
       <c r="AV35" s="33" t="n">
-        <v>-0.3954643088716175</v>
+        <v>-0.3952352406236109</v>
       </c>
       <c r="AW35" s="33" t="n">
-        <v>0.04805397417822665</v>
+        <v>0.04845109860148988</v>
       </c>
       <c r="AX35" s="90" t="inlineStr">
         <is>
+          <t>IREN's AI Cloud Revenue Just Jumped 687%</t>
+        </is>
+      </c>
+      <c r="AY35" s="90" t="inlineStr">
+        <is>
           <t>IREN (IREN) Gains A Clearer Path To Texas Power Expansion</t>
         </is>
       </c>
-      <c r="AY35" s="90" t="inlineStr">
+      <c r="AZ35" s="90" t="inlineStr">
         <is>
           <t>NBIS, IREN, CRWV At Risk? OpenAI Co-Founder Warns AI Agents Could Turn Neoclouds Into Cybersecurity Targets...</t>
-        </is>
-      </c>
-      <c r="AZ35" s="90" t="inlineStr">
-        <is>
-          <t>What PUCT’s transmission approval means for CORZ, IREN, CIFR, and others in West Texas</t>
         </is>
       </c>
     </row>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="C36" s="26" t="n">
-        <v>0.01050913280617305</v>
+        <v>0.01213894364658463</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="R36" s="70" t="n">
-        <v>89.90499877929688</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="S36" s="71" t="n">
-        <v>0.93499755859375</v>
+        <v>1.080001831054688</v>
       </c>
       <c r="T36" s="72" t="n">
         <v>88.75</v>
@@ -8755,61 +8755,61 @@
         <v>87.5</v>
       </c>
       <c r="W36" s="73" t="n">
-        <v>47274914</v>
+        <v>60998770</v>
       </c>
       <c r="X36" s="74" t="n">
-        <v>0.4922978407417118</v>
+        <v>0.630704556638145</v>
       </c>
       <c r="Y36" s="28" t="n">
-        <v>42.53062891024699</v>
+        <v>42.76785590832485</v>
       </c>
       <c r="Z36" s="28" t="n">
-        <v>21.92820365178648</v>
+        <v>22.59550346798586</v>
       </c>
       <c r="AA36" s="28" t="n">
         <v>15.63461355409994</v>
       </c>
       <c r="AB36" s="75" t="n">
-        <v>-3.323007006506131</v>
+        <v>-3.311439714116091</v>
       </c>
       <c r="AC36" s="75" t="n">
-        <v>-3.279916294192609</v>
+        <v>-3.277602835714601</v>
       </c>
       <c r="AD36" s="75" t="n">
-        <v>-0.0430907123135218</v>
+        <v>-0.0338368784014893</v>
       </c>
       <c r="AE36" s="72" t="n">
-        <v>90.2452308171634</v>
+        <v>90.27745398882139</v>
       </c>
       <c r="AF36" s="72" t="n">
-        <v>93.37098181371297</v>
+        <v>93.38416402030032</v>
       </c>
       <c r="AG36" s="72" t="n">
-        <v>102.144899597168</v>
+        <v>102.1477996826172</v>
       </c>
       <c r="AH36" s="72" t="n">
-        <v>103.2763497543335</v>
+        <v>103.2777997970581</v>
       </c>
       <c r="AI36" s="72" t="n">
-        <v>73.56802492141723</v>
+        <v>73.56874994277955</v>
       </c>
       <c r="AJ36" s="72" t="n">
-        <v>106.1944109199716</v>
+        <v>106.1899426291852</v>
       </c>
       <c r="AK36" s="72" t="n">
-        <v>94.64024963378907</v>
+        <v>94.64749984741211</v>
       </c>
       <c r="AL36" s="72" t="n">
-        <v>83.08608834760651</v>
+        <v>83.10505706563902</v>
       </c>
       <c r="AM36" s="76" t="n">
-        <v>0.2950846133611185</v>
+        <v>0.3008438559074212</v>
       </c>
       <c r="AN36" s="29" t="n">
-        <v>24.41701354527582</v>
+        <v>24.39038072929866</v>
       </c>
       <c r="AO36" s="77" t="n">
-        <v>5.807846856566285</v>
+        <v>5.798494690220251</v>
       </c>
       <c r="AP36" s="72" t="n">
         <v>142.3500061035156</v>
@@ -8818,36 +8818,36 @@
         <v>23.71999931335449</v>
       </c>
       <c r="AR36" s="29" t="n">
-        <v>-36.84229369549954</v>
+        <v>-36.7404290897787</v>
       </c>
       <c r="AS36" s="78" t="n">
-        <v>55.7911115886673</v>
+        <v>55.91334396172736</v>
       </c>
       <c r="AT36" s="26" t="n">
-        <v>0.01886900448590079</v>
+        <v>0.0205122986378885</v>
       </c>
       <c r="AU36" s="26" t="n">
-        <v>-0.1086159207293356</v>
+        <v>-0.1071782420501421</v>
       </c>
       <c r="AV36" s="26" t="n">
-        <v>-0.2023334264077505</v>
+        <v>-0.2010469010449719</v>
       </c>
       <c r="AW36" s="26" t="n">
-        <v>1.436449730665843</v>
+        <v>1.440379385583588</v>
       </c>
       <c r="AX36" s="79" t="inlineStr">
         <is>
+          <t>Prediction: Intel Stock Could Have a Major Catalyst Ahead</t>
+        </is>
+      </c>
+      <c r="AY36" s="79" t="inlineStr">
+        <is>
           <t>Prediction: This Is What a $1,000 Investment in Intel Will Be Worth by 2030</t>
         </is>
       </c>
-      <c r="AY36" s="79" t="inlineStr">
+      <c r="AZ36" s="79" t="inlineStr">
         <is>
           <t>What Is Intel (INTC) Doing In Open Source 5G And NextG Networks?</t>
-        </is>
-      </c>
-      <c r="AZ36" s="79" t="inlineStr">
-        <is>
-          <t>Stock Market Today, Sept. 1: Intel Falls on Chip Stock Pressure</t>
         </is>
       </c>
     </row>
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="C37" s="33" t="n">
-        <v>-0.008682239593875374</v>
+        <v>-0.008382862523551915</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="R37" s="81" t="n">
-        <v>496.6700134277344</v>
+        <v>496.8200073242188</v>
       </c>
       <c r="S37" s="82" t="n">
-        <v>-4.3499755859375</v>
+        <v>-4.199981689453125</v>
       </c>
       <c r="T37" s="83" t="n">
         <v>500.1700134277344</v>
@@ -8943,61 +8943,61 @@
         <v>493.8099975585938</v>
       </c>
       <c r="W37" s="84" t="n">
-        <v>11093253</v>
+        <v>15280048</v>
       </c>
       <c r="X37" s="85" t="n">
-        <v>0.4634039795100743</v>
+        <v>0.6327675911902199</v>
       </c>
       <c r="Y37" s="35" t="n">
-        <v>60.7354146789976</v>
+        <v>60.83443647725979</v>
       </c>
       <c r="Z37" s="35" t="n">
-        <v>48.04332395699151</v>
+        <v>48.4124939441851</v>
       </c>
       <c r="AA37" s="35" t="n">
         <v>37.33157980111926</v>
       </c>
       <c r="AB37" s="86" t="n">
-        <v>16.41822818416591</v>
+        <v>16.43019350924158</v>
       </c>
       <c r="AC37" s="86" t="n">
-        <v>18.70623867160624</v>
+        <v>18.70863173662137</v>
       </c>
       <c r="AD37" s="86" t="n">
-        <v>-2.288010487440324</v>
+        <v>-2.278438227379791</v>
       </c>
       <c r="AE37" s="83" t="n">
-        <v>499.0730403241845</v>
+        <v>499.1063723011811</v>
       </c>
       <c r="AF37" s="83" t="n">
-        <v>485.6520993189758</v>
+        <v>485.6657351277472</v>
       </c>
       <c r="AG37" s="83" t="n">
-        <v>438.3385986328125</v>
+        <v>438.3415985107422</v>
       </c>
       <c r="AH37" s="83" t="n">
-        <v>425.6305987548828</v>
+        <v>425.6320986938476</v>
       </c>
       <c r="AI37" s="83" t="n">
-        <v>431.0849992370606</v>
+        <v>431.085749206543</v>
       </c>
       <c r="AJ37" s="83" t="n">
-        <v>514.1886623101284</v>
+        <v>514.1985916928444</v>
       </c>
       <c r="AK37" s="83" t="n">
-        <v>495.203498840332</v>
+        <v>495.2109985351562</v>
       </c>
       <c r="AL37" s="83" t="n">
-        <v>476.2183353705356</v>
+        <v>476.2234053774681</v>
       </c>
       <c r="AM37" s="87" t="n">
-        <v>0.5386226484100455</v>
+        <v>0.542370003815123</v>
       </c>
       <c r="AN37" s="36" t="n">
-        <v>7.667620892928205</v>
+        <v>7.668486044879377</v>
       </c>
       <c r="AO37" s="88" t="n">
-        <v>2.278808331880465</v>
+        <v>2.278120341590217</v>
       </c>
       <c r="AP37" s="83" t="n">
         <v>553.719970703125</v>
@@ -9006,36 +9006,36 @@
         <v>349.2000122070312</v>
       </c>
       <c r="AR37" s="36" t="n">
-        <v>-10.30303407748639</v>
+        <v>-10.2759456746076</v>
       </c>
       <c r="AS37" s="89" t="n">
-        <v>72.10543279252609</v>
+        <v>72.17877228349182</v>
       </c>
       <c r="AT37" s="33" t="n">
-        <v>0.0006044247506862277</v>
+        <v>0.0009066063852731787</v>
       </c>
       <c r="AU37" s="33" t="n">
-        <v>0.007832665506510406</v>
+        <v>0.008137030063291695</v>
       </c>
       <c r="AV37" s="33" t="n">
-        <v>0.1622361999437696</v>
+        <v>0.1625871942288113</v>
       </c>
       <c r="AW37" s="33" t="n">
-        <v>0.02698403383297809</v>
+        <v>0.02729418208573597</v>
       </c>
       <c r="AX37" s="90" t="inlineStr">
         <is>
-          <t>Sector Update: Tech Stocks Mixed Late Afternoon</t>
+          <t>Steve Ballmer banned, Clippers fined $30M over Kawhi Leonard scandal</t>
         </is>
       </c>
       <c r="AY37" s="90" t="inlineStr">
         <is>
-          <t>Is Microsoft Stock Winning The Move To The Cloud Or Just The AI Boom?</t>
+          <t>Microsoft Discloses Exact Azure Sales Figures For The First Time Following Longstanding Investor Demand</t>
         </is>
       </c>
       <c r="AZ37" s="90" t="inlineStr">
         <is>
-          <t>Update: Microsoft's Edge Remains Exempt From Gatekeeper Designation in European Court Ruling</t>
+          <t>Microsoft to detail quarterly Azure sales in sweeping reportable segment revamp</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="C38" s="26" t="n">
-        <v>-0.01485422620385501</v>
+        <v>-0.01353295042585745</v>
       </c>
       <c r="D38" s="27" t="n">
         <v>24</v>
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="R38" s="70" t="n">
-        <v>123.0250015258789</v>
+        <v>123.1900024414062</v>
       </c>
       <c r="S38" s="71" t="n">
-        <v>-1.854995727539062</v>
+        <v>-1.689994812011719</v>
       </c>
       <c r="T38" s="72" t="n">
         <v>123.3499984741211</v>
@@ -9131,61 +9131,61 @@
         <v>121.3800964355469</v>
       </c>
       <c r="W38" s="73" t="n">
-        <v>12563870</v>
+        <v>14665180</v>
       </c>
       <c r="X38" s="74" t="n">
-        <v>0.4830535699225836</v>
+        <v>0.5615758762984344</v>
       </c>
       <c r="Y38" s="28" t="n">
-        <v>57.52674939889583</v>
+        <v>57.65496680563243</v>
       </c>
       <c r="Z38" s="28" t="n">
-        <v>65.17356674110519</v>
+        <v>65.51653268048172</v>
       </c>
       <c r="AA38" s="28" t="n">
         <v>33.37893841346034</v>
       </c>
       <c r="AB38" s="75" t="n">
-        <v>7.765674235555451</v>
+        <v>7.778836701751374</v>
       </c>
       <c r="AC38" s="75" t="n">
-        <v>5.872333131653799</v>
+        <v>5.874965624892983</v>
       </c>
       <c r="AD38" s="75" t="n">
-        <v>1.893341103901652</v>
+        <v>1.90387107685839</v>
       </c>
       <c r="AE38" s="72" t="n">
-        <v>124.042950954668</v>
+        <v>124.0796178247852</v>
       </c>
       <c r="AF38" s="72" t="n">
-        <v>114.8318262038044</v>
+        <v>114.8468262870342</v>
       </c>
       <c r="AG38" s="72" t="n">
-        <v>101.3352996826172</v>
+        <v>101.3385997009277</v>
       </c>
       <c r="AH38" s="72" t="n">
-        <v>127.4553497314453</v>
+        <v>127.4569997406006</v>
       </c>
       <c r="AI38" s="72" t="n">
-        <v>139.623125038147</v>
+        <v>139.6239500427246</v>
       </c>
       <c r="AJ38" s="72" t="n">
-        <v>140.8367073671269</v>
+        <v>140.8583560039526</v>
       </c>
       <c r="AK38" s="72" t="n">
-        <v>110.9772495269775</v>
+        <v>110.9854995727539</v>
       </c>
       <c r="AL38" s="72" t="n">
-        <v>81.11779168682816</v>
+        <v>81.11264314155524</v>
       </c>
       <c r="AM38" s="76" t="n">
-        <v>0.7017409703719035</v>
+        <v>0.7042741191616709</v>
       </c>
       <c r="AN38" s="29" t="n">
-        <v>53.81185417267137</v>
+        <v>53.83199885786203</v>
       </c>
       <c r="AO38" s="77" t="n">
-        <v>6.283518926962516</v>
+        <v>6.275102770171097</v>
       </c>
       <c r="AP38" s="72" t="n">
         <v>365.2099914550781</v>
@@ -9194,36 +9194,36 @@
         <v>81.80999755859375</v>
       </c>
       <c r="AR38" s="29" t="n">
-        <v>-66.31390038489367</v>
+        <v>-66.2687206473761</v>
       </c>
       <c r="AS38" s="78" t="n">
-        <v>14.54305040752382</v>
+        <v>14.60127232674786</v>
       </c>
       <c r="AT38" s="26" t="n">
-        <v>-0.001339401836653265</v>
+        <v>0</v>
       </c>
       <c r="AU38" s="26" t="n">
-        <v>0.2598566267638531</v>
+        <v>0.2615463442543706</v>
       </c>
       <c r="AV38" s="26" t="n">
-        <v>-0.02785461430954861</v>
+        <v>-0.02655077462919819</v>
       </c>
       <c r="AW38" s="26" t="n">
-        <v>-0.1903586443125486</v>
+        <v>-0.1892727547512375</v>
       </c>
       <c r="AX38" s="79" t="inlineStr">
         <is>
+          <t>MicroStrategy Reserve Capital Beats All S&amp;P 500 Financials But Berkshire, MSTR Still Slips</t>
+        </is>
+      </c>
+      <c r="AY38" s="79" t="inlineStr">
+        <is>
           <t>Stocks making big moves yesterday: Myriad Genetics, Greenbrier, Tidewater, Strategy, and Charter</t>
         </is>
       </c>
-      <c r="AY38" s="79" t="inlineStr">
+      <c r="AZ38" s="79" t="inlineStr">
         <is>
           <t>MicroStrategy Resumes Bitcoin Accumulation After Extended Buying Gap</t>
-        </is>
-      </c>
-      <c r="AZ38" s="79" t="inlineStr">
-        <is>
-          <t>Strategy CEO Defends Bitcoin Purchases And Sales</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="C39" s="33" t="n">
-        <v>0.02398656002515054</v>
+        <v>0.02425438655856049</v>
       </c>
       <c r="D39" s="34" t="n">
         <v>5</v>
@@ -9304,10 +9304,10 @@
         </is>
       </c>
       <c r="R39" s="81" t="n">
-        <v>955.8300170898438</v>
+        <v>956.0800170898438</v>
       </c>
       <c r="S39" s="82" t="n">
-        <v>22.3900146484375</v>
+        <v>22.6400146484375</v>
       </c>
       <c r="T39" s="83" t="n">
         <v>930.8250122070312</v>
@@ -9319,61 +9319,61 @@
         <v>927.1569213867188</v>
       </c>
       <c r="W39" s="84" t="n">
-        <v>18959627</v>
+        <v>21231828</v>
       </c>
       <c r="X39" s="85" t="n">
-        <v>0.6740102799290327</v>
+        <v>0.7517503138827293</v>
       </c>
       <c r="Y39" s="35" t="n">
-        <v>53.19994723339119</v>
+        <v>53.2289583279718</v>
       </c>
       <c r="Z39" s="35" t="n">
-        <v>45.93322297801551</v>
+        <v>46.10155045385953</v>
       </c>
       <c r="AA39" s="35" t="n">
         <v>8.568580024037685</v>
       </c>
       <c r="AB39" s="86" t="n">
-        <v>7.989402619236671</v>
+        <v>8.009345639179742</v>
       </c>
       <c r="AC39" s="86" t="n">
-        <v>6.189012000214057</v>
+        <v>6.193000604202672</v>
       </c>
       <c r="AD39" s="86" t="n">
-        <v>1.800390619022614</v>
+        <v>1.81634503497707</v>
       </c>
       <c r="AE39" s="83" t="n">
-        <v>943.4618129849189</v>
+        <v>943.5173685404745</v>
       </c>
       <c r="AF39" s="83" t="n">
-        <v>934.0416807734882</v>
+        <v>934.0644080462155</v>
       </c>
       <c r="AG39" s="83" t="n">
-        <v>944.0210046386719</v>
+        <v>944.0260046386719</v>
       </c>
       <c r="AH39" s="83" t="n">
-        <v>852.6206024169921</v>
+        <v>852.6231024169922</v>
       </c>
       <c r="AI39" s="83" t="n">
-        <v>599.0484506988525</v>
+        <v>599.0497006988526</v>
       </c>
       <c r="AJ39" s="83" t="n">
-        <v>1007.565242341031</v>
+        <v>1007.593356893206</v>
       </c>
       <c r="AK39" s="83" t="n">
-        <v>932.5059997558594</v>
+        <v>932.5184997558594</v>
       </c>
       <c r="AL39" s="83" t="n">
-        <v>857.4467571706882</v>
+        <v>857.443642618513</v>
       </c>
       <c r="AM39" s="87" t="n">
-        <v>0.6553707213839661</v>
+        <v>0.6569201609726647</v>
       </c>
       <c r="AN39" s="36" t="n">
-        <v>16.09839349126388</v>
+        <v>16.10152659856112</v>
       </c>
       <c r="AO39" s="88" t="n">
-        <v>5.808442861652312</v>
+        <v>5.806924044514147</v>
       </c>
       <c r="AP39" s="83" t="n">
         <v>1255</v>
@@ -9382,36 +9382,36 @@
         <v>117.3000030517578</v>
       </c>
       <c r="AR39" s="36" t="n">
-        <v>-23.83824565021165</v>
+        <v>-23.81832533148656</v>
       </c>
       <c r="AS39" s="89" t="n">
-        <v>73.70396556977697</v>
+        <v>73.72593972822563</v>
       </c>
       <c r="AT39" s="33" t="n">
-        <v>0.0185741605097085</v>
+        <v>0.01884057141496842</v>
       </c>
       <c r="AU39" s="33" t="n">
-        <v>0.07075406968853382</v>
+        <v>0.07103412839419909</v>
       </c>
       <c r="AV39" s="33" t="n">
-        <v>-0.1146196498194166</v>
+        <v>-0.1143880761257812</v>
       </c>
       <c r="AW39" s="33" t="n">
-        <v>2.348971671719783</v>
+        <v>2.349847604577048</v>
       </c>
       <c r="AX39" s="90" t="inlineStr">
         <is>
-          <t>Micron Rises as Taiwan Workers Demand 15% Profit Pool</t>
+          <t>Billionaire David Tepper Cut Micron 41% and Kept Buying This AI Chip Stock for a Sixth Quarter</t>
         </is>
       </c>
       <c r="AY39" s="90" t="inlineStr">
         <is>
-          <t>Dell Called Out the Memory Chip Shortage. Micron Stock Shrugs.</t>
+          <t>Micron (MU) Exceeds Market Returns: Some Facts to Consider</t>
         </is>
       </c>
       <c r="AZ39" s="90" t="inlineStr">
         <is>
-          <t>The Memory Crunch Is Bigger Than Expected. 1 Top Stock to Buy on the Dip (Hint: Not Micron or Sandisk)</t>
+          <t>Billionaire Philippe Laffont Just Bought Micron Stock in Q2: Is the Artificial Intelligence (AI) Memory Win...</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="C40" s="26" t="n">
-        <v>0.02272729184472988</v>
+        <v>0.02280246168613065</v>
       </c>
       <c r="D40" s="27" t="n">
         <v>7</v>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr">
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="R40" s="70" t="n">
-        <v>204.0749969482422</v>
+        <v>204.0899963378906</v>
       </c>
       <c r="S40" s="71" t="n">
-        <v>4.535003662109375</v>
+        <v>4.550003051757812</v>
       </c>
       <c r="T40" s="72" t="n">
         <v>195.5169982910156</v>
@@ -9507,61 +9507,61 @@
         <v>195.1999969482422</v>
       </c>
       <c r="W40" s="73" t="n">
-        <v>8608841</v>
+        <v>10712561</v>
       </c>
       <c r="X40" s="74" t="n">
-        <v>0.3751542209635244</v>
+        <v>0.4646996010943736</v>
       </c>
       <c r="Y40" s="28" t="n">
-        <v>46.05856038939699</v>
+        <v>46.06369373280975</v>
       </c>
       <c r="Z40" s="28" t="n">
-        <v>10.78111783465982</v>
+        <v>10.79855290675287</v>
       </c>
       <c r="AA40" s="28" t="n">
         <v>9.704849071674941</v>
       </c>
       <c r="AB40" s="75" t="n">
-        <v>-1.964286786531432</v>
+        <v>-1.963090254023854</v>
       </c>
       <c r="AC40" s="75" t="n">
-        <v>1.582215005044439</v>
+        <v>1.582454311545954</v>
       </c>
       <c r="AD40" s="75" t="n">
-        <v>-3.54650179157587</v>
+        <v>-3.545544565569808</v>
       </c>
       <c r="AE40" s="72" t="n">
-        <v>210.6338008759924</v>
+        <v>210.6371340736921</v>
       </c>
       <c r="AF40" s="72" t="n">
-        <v>215.4526958982008</v>
+        <v>215.4540594790779</v>
       </c>
       <c r="AG40" s="72" t="n">
-        <v>214.6630999755859</v>
+        <v>214.6633999633789</v>
       </c>
       <c r="AH40" s="72" t="n">
-        <v>208.7045501708984</v>
+        <v>208.7047001647949</v>
       </c>
       <c r="AI40" s="72" t="n">
-        <v>153.4507503509521</v>
+        <v>153.4508253479004</v>
       </c>
       <c r="AJ40" s="72" t="n">
-        <v>274.1407959981618</v>
+        <v>274.1406207052227</v>
       </c>
       <c r="AK40" s="72" t="n">
-        <v>220.5967491149902</v>
+        <v>220.5974990844726</v>
       </c>
       <c r="AL40" s="72" t="n">
-        <v>167.0527022318187</v>
+        <v>167.0543774637226</v>
       </c>
       <c r="AM40" s="76" t="n">
-        <v>0.3457181224759022</v>
+        <v>0.3458485212768699</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>48.54472887563789</v>
+        <v>48.54372496784012</v>
       </c>
       <c r="AO40" s="77" t="n">
-        <v>9.233554279557081</v>
+        <v>9.2328756687434</v>
       </c>
       <c r="AP40" s="72" t="n">
         <v>299.8599853515625</v>
@@ -9570,22 +9570,22 @@
         <v>63.2599983215332</v>
       </c>
       <c r="AR40" s="29" t="n">
-        <v>-31.94323787184204</v>
+        <v>-31.93823574072047</v>
       </c>
       <c r="AS40" s="78" t="n">
-        <v>59.516063544347</v>
+        <v>59.52240310075895</v>
       </c>
       <c r="AT40" s="26" t="n">
-        <v>-0.04606645194661729</v>
+        <v>-0.04599633840404749</v>
       </c>
       <c r="AU40" s="26" t="n">
-        <v>-0.09597327907205155</v>
+        <v>-0.09590683365128672</v>
       </c>
       <c r="AV40" s="26" t="n">
-        <v>-0.1891489077912708</v>
+        <v>-0.1890893107232283</v>
       </c>
       <c r="AW40" s="26" t="n">
-        <v>1.438026312455441</v>
+        <v>1.438205505924413</v>
       </c>
       <c r="AX40" s="79" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="C41" s="33" t="n">
-        <v>0.02394512122816539</v>
+        <v>0.0237595081839681</v>
       </c>
       <c r="D41" s="34" t="n">
         <v>6</v>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F41" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
@@ -9662,11 +9662,11 @@
         </is>
       </c>
       <c r="N41" s="80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O41" s="30" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Very Strong</t>
         </is>
       </c>
       <c r="P41" s="32" t="inlineStr">
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="R41" s="81" t="n">
-        <v>82.74500274658203</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="S41" s="82" t="n">
-        <v>1.935005187988281</v>
+        <v>1.920005798339844</v>
       </c>
       <c r="T41" s="83" t="n">
         <v>80.54000091552734</v>
@@ -9695,61 +9695,61 @@
         <v>80.30000305175781</v>
       </c>
       <c r="W41" s="84" t="n">
-        <v>17150669</v>
+        <v>21992669</v>
       </c>
       <c r="X41" s="85" t="n">
-        <v>0.6288134524400346</v>
+        <v>0.7992465041329213</v>
       </c>
       <c r="Y41" s="35" t="n">
-        <v>63.92054859576306</v>
+        <v>63.8893141682433</v>
       </c>
       <c r="Z41" s="35" t="n">
-        <v>95.09804019343753</v>
+        <v>94.90196977962523</v>
       </c>
       <c r="AA41" s="35" t="n">
         <v>21.38131953874219</v>
       </c>
       <c r="AB41" s="86" t="n">
-        <v>1.960032288470373</v>
+        <v>1.958835755962809</v>
       </c>
       <c r="AC41" s="86" t="n">
-        <v>1.693413976523572</v>
+        <v>1.693174670022059</v>
       </c>
       <c r="AD41" s="86" t="n">
-        <v>0.2666183119468011</v>
+        <v>0.2656610859407502</v>
       </c>
       <c r="AE41" s="83" t="n">
-        <v>81.01864938852982</v>
+        <v>81.01531619083016</v>
       </c>
       <c r="AF41" s="83" t="n">
-        <v>78.87283265079688</v>
+        <v>78.87146906991975</v>
       </c>
       <c r="AG41" s="83" t="n">
-        <v>75.0768995666504</v>
+        <v>75.07659957885743</v>
       </c>
       <c r="AH41" s="83" t="n">
-        <v>81.558949508667</v>
+        <v>81.55879951477051</v>
       </c>
       <c r="AI41" s="83" t="n">
-        <v>87.18650974273682</v>
+        <v>87.18643474578857</v>
       </c>
       <c r="AJ41" s="83" t="n">
-        <v>84.30230328901148</v>
+        <v>84.29938424005178</v>
       </c>
       <c r="AK41" s="83" t="n">
-        <v>78.65625</v>
+        <v>78.65550003051757</v>
       </c>
       <c r="AL41" s="83" t="n">
-        <v>73.01019671098852</v>
+        <v>73.01161582098337</v>
       </c>
       <c r="AM41" s="87" t="n">
-        <v>0.8620894576517448</v>
+        <v>0.8609662401943832</v>
       </c>
       <c r="AN41" s="36" t="n">
-        <v>14.35627375831285</v>
+        <v>14.35089525168471</v>
       </c>
       <c r="AO41" s="88" t="n">
-        <v>2.728553229312712</v>
+        <v>2.729047930526326</v>
       </c>
       <c r="AP41" s="83" t="n">
         <v>126.7099990844727</v>
@@ -9758,36 +9758,36 @@
         <v>65.08000183105469</v>
       </c>
       <c r="AR41" s="36" t="n">
-        <v>-34.69733774410405</v>
+        <v>-34.70917531789998</v>
       </c>
       <c r="AS41" s="89" t="n">
-        <v>28.66299156706136</v>
+        <v>28.63865376028399</v>
       </c>
       <c r="AT41" s="33" t="n">
-        <v>0.0157746584403573</v>
+        <v>0.01559052647599435</v>
       </c>
       <c r="AU41" s="33" t="n">
-        <v>0.1247112014383125</v>
+        <v>0.1245073222795432</v>
       </c>
       <c r="AV41" s="33" t="n">
-        <v>0.0150270627325868</v>
+        <v>0.01484306628673182</v>
       </c>
       <c r="AW41" s="33" t="n">
-        <v>-0.1174807928613736</v>
+        <v>-0.11764076928316</v>
       </c>
       <c r="AX41" s="90" t="inlineStr">
         <is>
+          <t>Netflix (NFLX) Rises Higher Than Market: Key Facts</t>
+        </is>
+      </c>
+      <c r="AY41" s="90" t="inlineStr">
+        <is>
           <t>Where Will Netflix Stock Be in 3 Years?</t>
         </is>
       </c>
-      <c r="AY41" s="90" t="inlineStr">
+      <c r="AZ41" s="90" t="inlineStr">
         <is>
           <t>Netflix, MercadoLibre, and Tesla Are All Underperforming the S&amp;P 500. Here's the 1 Stock I'd Buy in September.</t>
-        </is>
-      </c>
-      <c r="AZ41" s="90" t="inlineStr">
-        <is>
-          <t>Netflix (NFLX) Unveils New Partnership, Is It Still Below Fair Value?</t>
         </is>
       </c>
     </row>
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="C42" s="26" t="n">
-        <v>-0.007552946690279616</v>
+        <v>-0.009063459196570256</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -9868,10 +9868,10 @@
         </is>
       </c>
       <c r="R42" s="70" t="n">
-        <v>9.854999542236328</v>
+        <v>9.840000152587891</v>
       </c>
       <c r="S42" s="71" t="n">
-        <v>-0.07500076293945312</v>
+        <v>-0.09000015258789062</v>
       </c>
       <c r="T42" s="72" t="n">
         <v>9.975000381469727</v>
@@ -9883,61 +9883,61 @@
         <v>9.729999542236328</v>
       </c>
       <c r="W42" s="73" t="n">
-        <v>45213094</v>
+        <v>48017229</v>
       </c>
       <c r="X42" s="74" t="n">
-        <v>0.6809538334698534</v>
+        <v>0.7216629739083738</v>
       </c>
       <c r="Y42" s="28" t="n">
-        <v>43.9297661187968</v>
+        <v>43.74717551038872</v>
       </c>
       <c r="Z42" s="28" t="n">
-        <v>8.928567779308954</v>
+        <v>7.857183242314239</v>
       </c>
       <c r="AA42" s="28" t="n">
         <v>12.90178238462082</v>
       </c>
       <c r="AB42" s="75" t="n">
-        <v>-0.1122939999047023</v>
+        <v>-0.1134905324122695</v>
       </c>
       <c r="AC42" s="75" t="n">
-        <v>-0.1456578643168484</v>
+        <v>-0.1458971708183618</v>
       </c>
       <c r="AD42" s="75" t="n">
-        <v>0.033363864412146</v>
+        <v>0.03240663840609231</v>
       </c>
       <c r="AE42" s="72" t="n">
-        <v>10.11297881028626</v>
+        <v>10.10964561258661</v>
       </c>
       <c r="AF42" s="72" t="n">
-        <v>10.17133931119703</v>
+        <v>10.1699757303199</v>
       </c>
       <c r="AG42" s="72" t="n">
-        <v>10.69029996871948</v>
+        <v>10.68999998092651</v>
       </c>
       <c r="AH42" s="72" t="n">
-        <v>12.02084999084473</v>
+        <v>12.02069999694824</v>
       </c>
       <c r="AI42" s="72" t="n">
-        <v>9.574074993133545</v>
+        <v>9.573999996185302</v>
       </c>
       <c r="AJ42" s="72" t="n">
-        <v>11.01640038935856</v>
+        <v>11.0164974101138</v>
       </c>
       <c r="AK42" s="72" t="n">
-        <v>10.10525002479553</v>
+        <v>10.10450005531311</v>
       </c>
       <c r="AL42" s="72" t="n">
-        <v>9.194099660232503</v>
+        <v>9.192502700512421</v>
       </c>
       <c r="AM42" s="76" t="n">
-        <v>0.3626733345603062</v>
+        <v>0.3549886678218358</v>
       </c>
       <c r="AN42" s="29" t="n">
-        <v>18.03320773513401</v>
+        <v>18.05131079832389</v>
       </c>
       <c r="AO42" s="77" t="n">
-        <v>4.766955347496203</v>
+        <v>4.774221751925577</v>
       </c>
       <c r="AP42" s="72" t="n">
         <v>17.45000076293945</v>
@@ -9946,22 +9946,22 @@
         <v>4.349999904632568</v>
       </c>
       <c r="AR42" s="29" t="n">
-        <v>-43.52436039334445</v>
+        <v>-43.61031677725645</v>
       </c>
       <c r="AS42" s="78" t="n">
-        <v>42.02289524365158</v>
+        <v>41.90839609353186</v>
       </c>
       <c r="AT42" s="26" t="n">
-        <v>-0.05331415113457016</v>
+        <v>-0.05475501471461774</v>
       </c>
       <c r="AU42" s="26" t="n">
-        <v>-0.006552473140897463</v>
+        <v>-0.008064508376086854</v>
       </c>
       <c r="AV42" s="26" t="n">
-        <v>-0.4109384451950204</v>
+        <v>-0.4118350016838936</v>
       </c>
       <c r="AW42" s="26" t="n">
-        <v>0.5231839044533275</v>
+        <v>0.520865606132642</v>
       </c>
       <c r="AX42" s="79" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="C43" s="33" t="n">
-        <v>0.03136493740275537</v>
+        <v>0.03205482497444945</v>
       </c>
       <c r="D43" s="34" t="n">
         <v>4</v>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="R43" s="81" t="n">
-        <v>224.2599945068359</v>
+        <v>224.4100036621094</v>
       </c>
       <c r="S43" s="82" t="n">
-        <v>6.819992065429688</v>
+        <v>6.970001220703125</v>
       </c>
       <c r="T43" s="83" t="n">
         <v>218.7850036621094</v>
@@ -10071,61 +10071,61 @@
         <v>218.4799957275391</v>
       </c>
       <c r="W43" s="84" t="n">
-        <v>133222090</v>
+        <v>155979384</v>
       </c>
       <c r="X43" s="85" t="n">
-        <v>1.064033666864424</v>
+        <v>1.234574417318901</v>
       </c>
       <c r="Y43" s="35" t="n">
-        <v>56.57742953109358</v>
+        <v>56.67062689432778</v>
       </c>
       <c r="Z43" s="35" t="n">
-        <v>73.25578644530691</v>
+        <v>73.90182067178097</v>
       </c>
       <c r="AA43" s="35" t="n">
         <v>15.9364085022822</v>
       </c>
       <c r="AB43" s="86" t="n">
-        <v>2.653723142705559</v>
+        <v>2.665689685006555</v>
       </c>
       <c r="AC43" s="86" t="n">
-        <v>2.664966465274222</v>
+        <v>2.667359773734421</v>
       </c>
       <c r="AD43" s="86" t="n">
-        <v>-0.01124332256866323</v>
+        <v>-0.001670088727866226</v>
       </c>
       <c r="AE43" s="83" t="n">
-        <v>219.3462483217779</v>
+        <v>219.3795836896164</v>
       </c>
       <c r="AF43" s="83" t="n">
-        <v>216.8421005207994</v>
+        <v>216.8557377167334</v>
       </c>
       <c r="AG43" s="83" t="n">
-        <v>209.2819995117187</v>
+        <v>209.2849996948242</v>
       </c>
       <c r="AH43" s="83" t="n">
-        <v>209.6581999206543</v>
+        <v>209.659700012207</v>
       </c>
       <c r="AI43" s="83" t="n">
-        <v>196.2685001373291</v>
+        <v>196.2692501831055</v>
       </c>
       <c r="AJ43" s="83" t="n">
-        <v>229.6922271091762</v>
+        <v>229.7142698708132</v>
       </c>
       <c r="AK43" s="83" t="n">
-        <v>219.2815010070801</v>
+        <v>219.2890014648438</v>
       </c>
       <c r="AL43" s="83" t="n">
-        <v>208.8707749049839</v>
+        <v>208.8637330588743</v>
       </c>
       <c r="AM43" s="87" t="n">
-        <v>0.7391040476395533</v>
+        <v>0.7456052927296024</v>
       </c>
       <c r="AN43" s="36" t="n">
-        <v>9.495307223166078</v>
+        <v>9.508245590366156</v>
       </c>
       <c r="AO43" s="88" t="n">
-        <v>3.378394680301623</v>
+        <v>3.376136357927834</v>
       </c>
       <c r="AP43" s="83" t="n">
         <v>236.5399932861328</v>
@@ -10134,36 +10134,36 @@
         <v>164.0700073242188</v>
       </c>
       <c r="AR43" s="36" t="n">
-        <v>-5.191510580810011</v>
+        <v>-5.128092486816927</v>
       </c>
       <c r="AS43" s="89" t="n">
-        <v>83.05505566711368</v>
+        <v>83.26205053993215</v>
       </c>
       <c r="AT43" s="33" t="n">
-        <v>0.06963650953787104</v>
+        <v>0.07035199724488828</v>
       </c>
       <c r="AU43" s="33" t="n">
-        <v>0.05812962123012011</v>
+        <v>0.05883741189514535</v>
       </c>
       <c r="AV43" s="33" t="n">
-        <v>0.04428402564300793</v>
+        <v>0.04498255488758729</v>
       </c>
       <c r="AW43" s="33" t="n">
-        <v>0.202466458481694</v>
+        <v>0.203270797115868</v>
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
-          <t>Is BioNTech Stock a No-Brainer Buy on the Dip?</t>
+          <t>Broadcom's Q3 earnings beat just isn't 'enough' to keep investors happy</t>
         </is>
       </c>
       <c r="AY43" s="90" t="inlineStr">
         <is>
-          <t>Jensen Huang Says the $3.5 Billion MediaTek Deal Is Not Circular. The Decade Long Roadmap Is the Real Tell.</t>
+          <t>Nscale doubles contracted revenue to $103 billion after Anthropic win - report</t>
         </is>
       </c>
       <c r="AZ43" s="90" t="inlineStr">
         <is>
-          <t>NVIDIA &amp; 4 Stocks Beyond Pure Plays to Gain From Quantum Boom in 2026</t>
+          <t>Nvidia’s $1 Billion Nokia Bet Was Worth About $2.2 Billion by June. Is 6G the Hidden AI Trade?</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
         </is>
       </c>
       <c r="C44" s="26" t="n">
-        <v>-0.05844263837627894</v>
+        <v>-0.0581369028542128</v>
       </c>
       <c r="D44" s="27" t="n">
         <v>25</v>
@@ -10244,10 +10244,10 @@
         </is>
       </c>
       <c r="R44" s="70" t="n">
-        <v>169.4049987792969</v>
+        <v>169.4600067138672</v>
       </c>
       <c r="S44" s="71" t="n">
-        <v>-10.51499938964844</v>
+        <v>-10.45999145507812</v>
       </c>
       <c r="T44" s="72" t="n">
         <v>176.9949951171875</v>
@@ -10259,61 +10259,61 @@
         <v>165.7100067138672</v>
       </c>
       <c r="W44" s="73" t="n">
-        <v>35433086</v>
+        <v>39578542</v>
       </c>
       <c r="X44" s="74" t="n">
-        <v>0.9954048131702068</v>
+        <v>1.105424451411023</v>
       </c>
       <c r="Y44" s="28" t="n">
-        <v>52.15864999100307</v>
+        <v>52.20170484253993</v>
       </c>
       <c r="Z44" s="28" t="n">
-        <v>16.30623987825285</v>
+        <v>16.5489934648445</v>
       </c>
       <c r="AA44" s="28" t="n">
         <v>33.87108551880625</v>
       </c>
       <c r="AB44" s="75" t="n">
-        <v>9.170137231055264</v>
+        <v>9.174525328399909</v>
       </c>
       <c r="AC44" s="75" t="n">
-        <v>10.64774342834305</v>
+        <v>10.64862104781198</v>
       </c>
       <c r="AD44" s="75" t="n">
-        <v>-1.477606197287782</v>
+        <v>-1.474095719412066</v>
       </c>
       <c r="AE44" s="72" t="n">
-        <v>178.0571572790616</v>
+        <v>178.0693812645217</v>
       </c>
       <c r="AF44" s="72" t="n">
-        <v>170.6347690428985</v>
+        <v>170.6397697642231</v>
       </c>
       <c r="AG44" s="72" t="n">
-        <v>147.1660989379883</v>
+        <v>147.1671990966797</v>
       </c>
       <c r="AH44" s="72" t="n">
-        <v>142.5764992523193</v>
+        <v>142.5770493316651</v>
       </c>
       <c r="AI44" s="72" t="n">
-        <v>151.3136247634888</v>
+        <v>151.3138998031616</v>
       </c>
       <c r="AJ44" s="72" t="n">
-        <v>188.8043780061433</v>
+        <v>188.8021441763133</v>
       </c>
       <c r="AK44" s="72" t="n">
-        <v>175.4707481384277</v>
+        <v>175.4734985351562</v>
       </c>
       <c r="AL44" s="72" t="n">
-        <v>162.1371182707121</v>
+        <v>162.1448528939991</v>
       </c>
       <c r="AM44" s="76" t="n">
-        <v>0.2725394577729469</v>
+        <v>0.2744147461344391</v>
       </c>
       <c r="AN44" s="29" t="n">
-        <v>15.19755287895257</v>
+        <v>15.19163378222233</v>
       </c>
       <c r="AO44" s="77" t="n">
-        <v>4.660043992432883</v>
+        <v>4.65853130870295</v>
       </c>
       <c r="AP44" s="72" t="n">
         <v>207.5200042724609</v>
@@ -10322,36 +10322,36 @@
         <v>106.370002746582</v>
       </c>
       <c r="AR44" s="29" t="n">
-        <v>-18.36690666366864</v>
+        <v>-18.3403993711485</v>
       </c>
       <c r="AS44" s="78" t="n">
-        <v>62.31833423807467</v>
+        <v>62.37271677266736</v>
       </c>
       <c r="AT44" s="26" t="n">
-        <v>-0.0456056406800176</v>
+        <v>-0.04529573682328347</v>
       </c>
       <c r="AU44" s="26" t="n">
-        <v>0.04146683244394089</v>
+        <v>0.04180500982825097</v>
       </c>
       <c r="AV44" s="26" t="n">
-        <v>0.1913150662088743</v>
+        <v>0.1917019012000898</v>
       </c>
       <c r="AW44" s="26" t="n">
-        <v>-0.04694796748637486</v>
+        <v>-0.04663849950004395</v>
       </c>
       <c r="AX44" s="79" t="inlineStr">
         <is>
-          <t>Jim Cramer Explains Why Palantir’s Rule of 40 Dominance Proves Bears Wrong</t>
+          <t>Palantir Shares Sink Despite $192 Million Army Contract</t>
         </is>
       </c>
       <c r="AY44" s="79" t="inlineStr">
         <is>
-          <t>Palantir stock tumbles as Google encroaches on defense AI market</t>
+          <t>Palantir Stock Gets New Problem From Google</t>
         </is>
       </c>
       <c r="AZ44" s="79" t="inlineStr">
         <is>
-          <t>Palantir Falls 7% Despite Army TITAN Production Award, Salesforce Slips</t>
+          <t>Palantir Technologies (PLTR) Could Be 5% Overvalued On Peter Zaffino Hire</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="C45" s="33" t="n">
-        <v>0.0201668603207652</v>
+        <v>0.02010687288424085</v>
       </c>
       <c r="D45" s="34" t="n">
         <v>8</v>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="K45" s="30" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L45" s="30" t="inlineStr">
@@ -10432,10 +10432,10 @@
         </is>
       </c>
       <c r="R45" s="81" t="n">
-        <v>169.9700012207031</v>
+        <v>169.9600067138672</v>
       </c>
       <c r="S45" s="82" t="n">
-        <v>3.360000610351562</v>
+        <v>3.350006103515625</v>
       </c>
       <c r="T45" s="83" t="n">
         <v>166.0399932861328</v>
@@ -10447,61 +10447,61 @@
         <v>165.0800018310547</v>
       </c>
       <c r="W45" s="84" t="n">
-        <v>4380176</v>
+        <v>7511325</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>0.4808493099892057</v>
+        <v>0.8106499097150882</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>54.40531156514164</v>
+        <v>54.39558251894007</v>
       </c>
       <c r="Z45" s="35" t="n">
-        <v>90.69305075885991</v>
+        <v>90.62708045657493</v>
       </c>
       <c r="AA45" s="35" t="n">
         <v>12.4119975912398</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-1.029769478667731</v>
+        <v>-1.030566761264339</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-2.898268583409876</v>
+        <v>-2.898428039929198</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.868499104742145</v>
+        <v>1.867861278664859</v>
       </c>
       <c r="AE45" s="83" t="n">
-        <v>165.8227186941047</v>
+        <v>165.8204976925856</v>
       </c>
       <c r="AF45" s="83" t="n">
-        <v>164.9988762111758</v>
+        <v>164.9979676196453</v>
       </c>
       <c r="AG45" s="83" t="n">
-        <v>171.4103997802735</v>
+        <v>171.4101998901367</v>
       </c>
       <c r="AH45" s="83" t="n">
-        <v>182.3604002380371</v>
+        <v>182.3603002929688</v>
       </c>
       <c r="AI45" s="83" t="n">
-        <v>167.896849822998</v>
+        <v>167.8967998504639</v>
       </c>
       <c r="AJ45" s="83" t="n">
-        <v>170.1363586832424</v>
+        <v>170.1339093397529</v>
       </c>
       <c r="AK45" s="83" t="n">
-        <v>163.2349990844727</v>
+        <v>163.2344993591309</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>156.3336394857029</v>
+        <v>156.3350893785088</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>0.9879474862772718</v>
+        <v>0.9873972827840245</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>8.455735151746936</v>
+        <v>8.453372305131044</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>3.779513542536959</v>
+        <v>3.779735797022986</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -10510,22 +10510,22 @@
         <v>121.9899978637695</v>
       </c>
       <c r="AR45" s="36" t="n">
-        <v>-34.60680500158564</v>
+        <v>-34.61065022562367</v>
       </c>
       <c r="AS45" s="89" t="n">
-        <v>34.78575940179093</v>
+        <v>34.77851333080698</v>
       </c>
       <c r="AT45" s="33" t="n">
-        <v>0.05860739788984715</v>
+        <v>0.05854515008847749</v>
       </c>
       <c r="AU45" s="33" t="n">
-        <v>0.1213960084934582</v>
+        <v>0.121330068621762</v>
       </c>
       <c r="AV45" s="33" t="n">
-        <v>-0.294261734740102</v>
+        <v>-0.2943032332743484</v>
       </c>
       <c r="AW45" s="33" t="n">
-        <v>-0.006313953883578027</v>
+        <v>-0.006372384206043025</v>
       </c>
       <c r="AX45" s="90" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         </is>
       </c>
       <c r="C46" s="26" t="n">
-        <v>0.009274032744911898</v>
+        <v>0.008954230099071037</v>
       </c>
       <c r="D46" s="27" t="n">
         <v>11</v>
@@ -10620,10 +10620,10 @@
         </is>
       </c>
       <c r="R46" s="70" t="n">
-        <v>63.11999893188477</v>
+        <v>63.09999847412109</v>
       </c>
       <c r="S46" s="71" t="n">
-        <v>0.5799980163574219</v>
+        <v>0.55999755859375</v>
       </c>
       <c r="T46" s="72" t="n">
         <v>62.29000091552734</v>
@@ -10635,61 +10635,61 @@
         <v>61.45000076293945</v>
       </c>
       <c r="W46" s="73" t="n">
-        <v>15023775</v>
+        <v>16363403</v>
       </c>
       <c r="X46" s="74" t="n">
-        <v>0.856821874093518</v>
+        <v>0.9296709223530761</v>
       </c>
       <c r="Y46" s="28" t="n">
-        <v>34.58088188897442</v>
+        <v>34.53788326518939</v>
       </c>
       <c r="Z46" s="28" t="n">
-        <v>6.929452325073592</v>
+        <v>6.846462881653697</v>
       </c>
       <c r="AA46" s="28" t="n">
         <v>21.44414543586801</v>
       </c>
       <c r="AB46" s="75" t="n">
-        <v>-3.86717623537109</v>
+        <v>-3.868771713483298</v>
       </c>
       <c r="AC46" s="75" t="n">
-        <v>-2.885779833853273</v>
+        <v>-2.886098929475715</v>
       </c>
       <c r="AD46" s="75" t="n">
-        <v>-0.9813964015178169</v>
+        <v>-0.9826727840075828</v>
       </c>
       <c r="AE46" s="72" t="n">
-        <v>65.94910556211107</v>
+        <v>65.94466101594138</v>
       </c>
       <c r="AF46" s="72" t="n">
-        <v>70.33524207203271</v>
+        <v>70.33342384859965</v>
       </c>
       <c r="AG46" s="72" t="n">
-        <v>75.67640014648437</v>
+        <v>75.6760001373291</v>
       </c>
       <c r="AH46" s="72" t="n">
-        <v>90.39729988098145</v>
+        <v>90.39709987640381</v>
       </c>
       <c r="AI46" s="72" t="n">
-        <v>79.27757513046265</v>
+        <v>79.27747512817383</v>
       </c>
       <c r="AJ46" s="72" t="n">
-        <v>87.40990981048152</v>
+        <v>87.41178695842407</v>
       </c>
       <c r="AK46" s="72" t="n">
-        <v>73.27699985504151</v>
+        <v>73.27599983215332</v>
       </c>
       <c r="AL46" s="72" t="n">
-        <v>59.1440898996015</v>
+        <v>59.14021270588256</v>
       </c>
       <c r="AM46" s="76" t="n">
-        <v>0.1406613728106597</v>
+        <v>0.1400624433880813</v>
       </c>
       <c r="AN46" s="29" t="n">
-        <v>38.57393174774651</v>
+        <v>38.58231114867166</v>
       </c>
       <c r="AO46" s="77" t="n">
-        <v>6.900389747641153</v>
+        <v>6.902576926041119</v>
       </c>
       <c r="AP46" s="72" t="n">
         <v>151</v>
@@ -10698,36 +10698,36 @@
         <v>37.56999969482422</v>
       </c>
       <c r="AR46" s="29" t="n">
-        <v>-58.19867620404982</v>
+        <v>-58.21192154031716</v>
       </c>
       <c r="AS46" s="78" t="n">
-        <v>22.52490449468394</v>
+        <v>22.50727207141861</v>
       </c>
       <c r="AT46" s="26" t="n">
-        <v>-0.04623755453581802</v>
+        <v>-0.04653976755593647</v>
       </c>
       <c r="AU46" s="26" t="n">
-        <v>-0.1525242200998275</v>
+        <v>-0.1527927546978701</v>
       </c>
       <c r="AV46" s="26" t="n">
-        <v>-0.4496948508170636</v>
+        <v>-0.4498692227289713</v>
       </c>
       <c r="AW46" s="26" t="n">
-        <v>-0.09518352925762252</v>
+        <v>-0.09547023305852864</v>
       </c>
       <c r="AX46" s="79" t="inlineStr">
         <is>
+          <t>Rocket Lab Gets Bullish Call From Top Bank as Space Market Could Double</t>
+        </is>
+      </c>
+      <c r="AY46" s="79" t="inlineStr">
+        <is>
+          <t>Rocket Lab Stock Flashes Major Warning Signal</t>
+        </is>
+      </c>
+      <c r="AZ46" s="79" t="inlineStr">
+        <is>
           <t>Rocket Lab (RKLB) Marks 94th Electron Mission With Perfect Customer Launch Record</t>
-        </is>
-      </c>
-      <c r="AY46" s="79" t="inlineStr">
-        <is>
-          <t>Rocket Lab Stock Has Collapsed 57% From Highs. Here's Why I'm Not Buying (Yet).</t>
-        </is>
-      </c>
-      <c r="AZ46" s="79" t="inlineStr">
-        <is>
-          <t>Rocket Lab Surges 43.7% in a Year: Is There More Room to Run?</t>
         </is>
       </c>
     </row>
@@ -10739,10 +10739,10 @@
         </is>
       </c>
       <c r="C47" s="33" t="n">
-        <v>0.012089478038948</v>
+        <v>0.01075564579267785</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
@@ -10808,10 +10808,10 @@
         </is>
       </c>
       <c r="R47" s="81" t="n">
-        <v>1555.449951171875</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="S47" s="82" t="n">
-        <v>18.5799560546875</v>
+        <v>16.530029296875</v>
       </c>
       <c r="T47" s="83" t="n">
         <v>1531.619995117188</v>
@@ -10823,61 +10823,61 @@
         <v>1509.239990234375</v>
       </c>
       <c r="W47" s="84" t="n">
-        <v>7625250</v>
+        <v>8866446</v>
       </c>
       <c r="X47" s="85" t="n">
-        <v>0.5600296273501424</v>
+        <v>0.648233550440682</v>
       </c>
       <c r="Y47" s="35" t="n">
-        <v>52.59881195474022</v>
+        <v>52.49743744689197</v>
       </c>
       <c r="Z47" s="35" t="n">
-        <v>33.75784839578523</v>
+        <v>33.25960395604839</v>
       </c>
       <c r="AA47" s="35" t="n">
         <v>10.91061990816512</v>
       </c>
       <c r="AB47" s="86" t="n">
-        <v>13.74372736321743</v>
+        <v>13.5802004423665</v>
       </c>
       <c r="AC47" s="86" t="n">
-        <v>4.667301582231953</v>
+        <v>4.634596198061767</v>
       </c>
       <c r="AD47" s="86" t="n">
-        <v>9.076425780985478</v>
+        <v>8.945604244304736</v>
       </c>
       <c r="AE47" s="83" t="n">
-        <v>1531.49977028893</v>
+        <v>1531.044231009416</v>
       </c>
       <c r="AF47" s="83" t="n">
-        <v>1508.540643934597</v>
+        <v>1508.354286956614</v>
       </c>
       <c r="AG47" s="83" t="n">
-        <v>1569.380988769531</v>
+        <v>1569.339990234375</v>
       </c>
       <c r="AH47" s="83" t="n">
-        <v>1509.958294067383</v>
+        <v>1509.937794799805</v>
       </c>
       <c r="AI47" s="83" t="n">
-        <v>990.1031479644776</v>
+        <v>990.0928983306885</v>
       </c>
       <c r="AJ47" s="83" t="n">
-        <v>1784.167467143735</v>
+        <v>1783.973669508179</v>
       </c>
       <c r="AK47" s="83" t="n">
-        <v>1488.683990478516</v>
+        <v>1488.581494140625</v>
       </c>
       <c r="AL47" s="83" t="n">
-        <v>1193.200513813297</v>
+        <v>1193.189318773071</v>
       </c>
       <c r="AM47" s="87" t="n">
-        <v>0.6129774859949356</v>
+        <v>0.6097160583092365</v>
       </c>
       <c r="AN47" s="36" t="n">
-        <v>39.69727337099128</v>
+        <v>39.68773984229696</v>
       </c>
       <c r="AO47" s="88" t="n">
-        <v>8.374845829132486</v>
+        <v>8.385897599628093</v>
       </c>
       <c r="AP47" s="83" t="n">
         <v>2354.389892578125</v>
@@ -10886,22 +10886,22 @@
         <v>50.65000152587891</v>
       </c>
       <c r="AR47" s="36" t="n">
-        <v>-33.93405416514882</v>
+        <v>-34.02112244403816</v>
       </c>
       <c r="AS47" s="89" t="n">
-        <v>65.31987206935372</v>
+        <v>65.23088950818115</v>
       </c>
       <c r="AT47" s="33" t="n">
-        <v>0.03740234647706453</v>
+        <v>0.03603515441340566</v>
       </c>
       <c r="AU47" s="33" t="n">
-        <v>0.08954060358631666</v>
+        <v>0.08810469853817793</v>
       </c>
       <c r="AV47" s="33" t="n">
-        <v>-0.1507234773836337</v>
+        <v>-0.1518427385126604</v>
       </c>
       <c r="AW47" s="33" t="n">
-        <v>5.552573591612127</v>
+        <v>5.543937957962931</v>
       </c>
       <c r="AX47" s="90" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="AZ47" s="90" t="inlineStr">
         <is>
-          <t>3 Stocks Drive Half of August's $665 Billion CEX Perpetual Futures Volume</t>
+          <t>Is Sandisk Stock Outperforming the Nasdaq?</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="C48" s="26" t="n">
-        <v>0.002358943937008418</v>
+        <v>0.002583654236838928</v>
       </c>
       <c r="D48" s="27" t="n">
         <v>14</v>
@@ -10996,10 +10996,10 @@
         </is>
       </c>
       <c r="R48" s="70" t="n">
-        <v>356.9299926757812</v>
+        <v>357.010009765625</v>
       </c>
       <c r="S48" s="71" t="n">
-        <v>0.839996337890625</v>
+        <v>0.920013427734375</v>
       </c>
       <c r="T48" s="72" t="n">
         <v>360.6099853515625</v>
@@ -11011,61 +11011,61 @@
         <v>349.9200134277344</v>
       </c>
       <c r="W48" s="73" t="n">
-        <v>29795216</v>
+        <v>33758963</v>
       </c>
       <c r="X48" s="74" t="n">
-        <v>0.8612742810234443</v>
+        <v>0.9702934737727589</v>
       </c>
       <c r="Y48" s="28" t="n">
-        <v>53.42156784563646</v>
+        <v>53.45367344446802</v>
       </c>
       <c r="Z48" s="28" t="n">
-        <v>68.28038374624889</v>
+        <v>68.4920690665743</v>
       </c>
       <c r="AA48" s="28" t="n">
         <v>21.27183912026909</v>
       </c>
       <c r="AB48" s="75" t="n">
-        <v>2.25686103986834</v>
+        <v>2.263244169542418</v>
       </c>
       <c r="AC48" s="75" t="n">
-        <v>-1.016187277608191</v>
+        <v>-1.014910651673376</v>
       </c>
       <c r="AD48" s="75" t="n">
-        <v>3.273048317476531</v>
+        <v>3.278154821215793</v>
       </c>
       <c r="AE48" s="72" t="n">
-        <v>354.300396699056</v>
+        <v>354.3181782745768</v>
       </c>
       <c r="AF48" s="72" t="n">
-        <v>348.9265145334309</v>
+        <v>348.9337888143257</v>
       </c>
       <c r="AG48" s="72" t="n">
-        <v>358.3501983642578</v>
+        <v>358.3517987060547</v>
       </c>
       <c r="AH48" s="72" t="n">
-        <v>381.3396994018555</v>
+        <v>381.3404995727539</v>
       </c>
       <c r="AI48" s="72" t="n">
-        <v>399.972149810791</v>
+        <v>399.9725498962403</v>
       </c>
       <c r="AJ48" s="72" t="n">
-        <v>368.800994171907</v>
+        <v>368.8132622024257</v>
       </c>
       <c r="AK48" s="72" t="n">
-        <v>344.3184982299805</v>
+        <v>344.3224990844727</v>
       </c>
       <c r="AL48" s="72" t="n">
-        <v>319.836002288054</v>
+        <v>319.8317359665197</v>
       </c>
       <c r="AM48" s="76" t="n">
-        <v>0.7575614527970461</v>
+        <v>0.7590264464207676</v>
       </c>
       <c r="AN48" s="29" t="n">
-        <v>14.22084266037541</v>
+        <v>14.22547941715809</v>
       </c>
       <c r="AO48" s="77" t="n">
-        <v>3.797135278079099</v>
+        <v>3.79628422150818</v>
       </c>
       <c r="AP48" s="72" t="n">
         <v>498.8299865722656</v>
@@ -11074,36 +11074,36 @@
         <v>297.3800048828125</v>
       </c>
       <c r="AR48" s="29" t="n">
-        <v>-28.44656450418248</v>
+        <v>-28.43052354995005</v>
       </c>
       <c r="AS48" s="78" t="n">
-        <v>29.56068166080478</v>
+        <v>29.60040223519882</v>
       </c>
       <c r="AT48" s="26" t="n">
-        <v>0.0321264967794257</v>
+        <v>0.03235788041296073</v>
       </c>
       <c r="AU48" s="26" t="n">
-        <v>0.09036195515729339</v>
+        <v>0.09060639410139548</v>
       </c>
       <c r="AV48" s="26" t="n">
-        <v>-0.1575879575349749</v>
+        <v>-0.1573991043663688</v>
       </c>
       <c r="AW48" s="26" t="n">
-        <v>-0.2063284005449083</v>
+        <v>-0.2061504740803825</v>
       </c>
       <c r="AX48" s="79" t="inlineStr">
         <is>
-          <t>Lemonade Brings Car Insurance and Autonomous Car to Missouri</t>
+          <t>Tesla's Cybercab to take center stage at Austin event</t>
         </is>
       </c>
       <c r="AY48" s="79" t="inlineStr">
         <is>
-          <t>Elon Musk Says AI Could Add $20-$30 Trillion a Year to the Global Economy</t>
+          <t>Dow Jones Futures: Snowflake, Broadcom, HPE Are Big Earnings Movers; Tesla Cybercab Event Due</t>
         </is>
       </c>
       <c r="AZ48" s="79" t="inlineStr">
         <is>
-          <t>Tesla's Cybercab Event Has 'More At Stake' Than Past Product Demos, Morgan Stanley</t>
+          <t>Morgan Stanley Warns Tesla Stock Could Sink If Cybercab Launch Falls Short</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11640,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 2 Sep 2026, 07:58 PM · Yahoo Finance data</t>
+          <t>Built 2 Sep 2026, 10:41 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -13224,58 +13224,58 @@
         <v>5152000</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>1.265665745832601</v>
+        <v>1.239516319175452</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>48.61344868347395</v>
+        <v>48.88880247143053</v>
       </c>
       <c r="Z13" s="28" t="n">
-        <v>16.7999267578125</v>
+        <v>23.9951231388846</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>12.43975931717117</v>
+        <v>11.83810281460942</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.3863393428060533</v>
+        <v>0.3565484873495421</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.4441268313019384</v>
+        <v>0.410945273242301</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>-0.05778748849588505</v>
+        <v>-0.05439678589275887</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>111.7249349790308</v>
+        <v>111.5730122285287</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.3947258727882</v>
+        <v>111.2670251154313</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.2189996337891</v>
+        <v>110.0963996887207</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.6122998809814</v>
+        <v>112.6250998687744</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0061999893188</v>
+        <v>114.0089500045776</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.3095009115325</v>
+        <v>113.1535579924061</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.5860000610352</v>
+        <v>111.5385002136231</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.8624992105378</v>
+        <v>109.92344243484</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.2951835047213828</v>
+        <v>0.2961364079800141</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>3.089098721263724</v>
+        <v>2.895964668145748</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.502083376291115</v>
+        <v>1.452338817113611</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -13290,13 +13290,13 @@
         <v>38.04877056338923</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>-0.02032163850111446</v>
+        <v>-0.01282053459151322</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>-0.004131481045469676</v>
+        <v>0.02439023874493351</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>-0.02368585408677115</v>
+        <v>-0.04091344461518909</v>
       </c>
       <c r="AW13" s="26" t="n">
         <v>-0.05810400863368514</v>
@@ -15562,58 +15562,58 @@
         <v>2955000</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>0.7887214171895894</v>
+        <v>0.7300920212430836</v>
       </c>
       <c r="Y28" s="28" t="n">
-        <v>38.9337628788725</v>
+        <v>38.52933689785394</v>
       </c>
       <c r="Z28" s="28" t="n">
         <v>9.06256004501231</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>9.940110389550453</v>
+        <v>10.16349900617751</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-10.79506874406277</v>
+        <v>-10.69840329886961</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-10.19515648070744</v>
+        <v>-10.08656173250177</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-0.599912263355332</v>
+        <v>-0.6118415663678398</v>
       </c>
       <c r="AE28" s="72" t="n">
-        <v>244.5626711704651</v>
+        <v>246.2650557636435</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>255.1344693060406</v>
+        <v>256.7577340694023</v>
       </c>
       <c r="AG28" s="72" t="n">
-        <v>280.4515994262695</v>
+        <v>283.8249993896484</v>
       </c>
       <c r="AH28" s="72" t="n">
-        <v>275.0708995056152</v>
+        <v>274.1783494567871</v>
       </c>
       <c r="AI28" s="72" t="n">
-        <v>200.2264749526977</v>
+        <v>199.774974937439</v>
       </c>
       <c r="AJ28" s="72" t="n">
-        <v>291.8280848830508</v>
+        <v>293.8307394437642</v>
       </c>
       <c r="AK28" s="72" t="n">
-        <v>259.0544998168945</v>
+        <v>261.1299995422363</v>
       </c>
       <c r="AL28" s="72" t="n">
-        <v>226.2809147507382</v>
+        <v>228.4292596407084</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.1302740081111605</v>
+        <v>0.09771564348016051</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>25.30246345021713</v>
+        <v>25.0455634809119</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>7.434546618854288</v>
+        <v>7.822392621976077</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -15628,13 +15628,13 @@
         <v>38.22161867198396</v>
       </c>
       <c r="AT28" s="26" t="n">
-        <v>-0.02790193037959487</v>
+        <v>-0.01658426784204114</v>
       </c>
       <c r="AU28" s="26" t="n">
-        <v>-0.01773609251935082</v>
+        <v>-0.02031789005625295</v>
       </c>
       <c r="AV28" s="26" t="n">
-        <v>-0.4169004685586186</v>
+        <v>-0.4256573221995616</v>
       </c>
       <c r="AW28" s="26" t="n">
         <v>1.148202475243378</v>
@@ -19576,7 +19576,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 2 Sep 2026, 07:58 PM · Yahoo Finance data</t>
+          <t>Built 2 Sep 2026, 10:41 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -20186,7 +20186,7 @@
         <v>-0.003622402212613562</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>-0.006712554214991062</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>-0.001175346403020305</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
@@ -21073,14 +21073,14 @@
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>-0.0135410107816939</v>
+        <v>0.0004487516445552675</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -21100,31 +21100,31 @@
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
+        <is>
           <t>Same</t>
         </is>
       </c>
-      <c r="J13" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L13" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M13" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N13" s="69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13" s="23" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>111.4599990844727</v>
       </c>
       <c r="S13" s="71" t="n">
-        <v>-1.529998779296875</v>
+        <v>0.04999542236328125</v>
       </c>
       <c r="T13" s="72" t="n">
         <v>112.4800033569336</v>
@@ -21160,58 +21160,58 @@
         <v>3317200</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>0.8118383714285364</v>
+        <v>0.773537607704595</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>50.60670939628083</v>
+        <v>51.19732185915565</v>
       </c>
       <c r="Z13" s="28" t="n">
         <v>38.12426703044879</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>12.94289846133665</v>
+        <v>12.37838648315917</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.4970496905289821</v>
+        <v>0.4500206222888323</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.4585737034259096</v>
+        <v>0.4245444697154907</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>0.03847598710307248</v>
+        <v>0.02547615257334163</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>111.9663457577774</v>
+        <v>111.7710165071318</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.4461987347252</v>
+        <v>111.3057279016326</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.1385997009277</v>
+        <v>110.0677996826172</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.6461998748779</v>
+        <v>112.6543998718262</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0195000076294</v>
+        <v>114.0255500030518</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.3465085287042</v>
+        <v>113.1512961186677</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.6440002441406</v>
+        <v>111.5615001678467</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.9414919595771</v>
+        <v>109.9717042170256</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.4459617432301825</v>
+        <v>0.4680773235956488</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>3.049887644370549</v>
+        <v>2.850079908264389</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.518112090927286</v>
+        <v>1.464819793708611</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -21226,13 +21226,13 @@
         <v>41.82114019626525</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>-0.007656700611540224</v>
+        <v>0.0005385777178810169</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>0.02974871844284221</v>
+        <v>0.04578717554493483</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>-0.03589656175044875</v>
+        <v>-0.03656325756476642</v>
       </c>
       <c r="AW13" s="26" t="n">
         <v>-0.05317704783653654</v>
@@ -21254,7 +21254,7 @@
         <v>-0.01014467255628793</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>-0.01118710886762897</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>-0.008318321395966555</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>-0.008914626195478559</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>0.01104002490802869</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>-0.02499719943397638</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>-0.02071409493576004</v>
       </c>
       <c r="D27" s="34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
@@ -23411,14 +23411,14 @@
         </is>
       </c>
       <c r="C28" s="26" t="n">
-        <v>0.0119640266632095</v>
+        <v>-0.05211395596517232</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
@@ -23462,11 +23462,11 @@
         </is>
       </c>
       <c r="N28" s="69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Very Weak</t>
         </is>
       </c>
       <c r="P28" s="25" t="inlineStr">
@@ -23483,7 +23483,7 @@
         <v>241.9100036621094</v>
       </c>
       <c r="S28" s="71" t="n">
-        <v>2.860000610351562</v>
+        <v>-13.30000305175781</v>
       </c>
       <c r="T28" s="72" t="n">
         <v>238.8049926757812</v>
@@ -23498,58 +23498,58 @@
         <v>2149400</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>0.5250853196463602</v>
+        <v>0.5115006740605096</v>
       </c>
       <c r="Y28" s="28" t="n">
-        <v>41.36836395483869</v>
+        <v>40.87239625133375</v>
       </c>
       <c r="Z28" s="28" t="n">
         <v>15.14408055740155</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>10.67322913700918</v>
+        <v>10.93726953363565</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-10.30896815323408</v>
+        <v>-10.03232074718645</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-10.04517841486861</v>
+        <v>-9.933601340909807</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-0.2637897383654675</v>
+        <v>-0.09871940627663989</v>
       </c>
       <c r="AE28" s="72" t="n">
-        <v>247.3462894122498</v>
+        <v>249.5350696034791</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>257.1659155042228</v>
+        <v>258.9515067439207</v>
       </c>
       <c r="AG28" s="72" t="n">
-        <v>283.9095993041992</v>
+        <v>287.9177990722656</v>
       </c>
       <c r="AH28" s="72" t="n">
-        <v>274.2206494140625</v>
+        <v>273.319249420166</v>
       </c>
       <c r="AI28" s="72" t="n">
-        <v>199.7961249160766</v>
+        <v>199.3495749282837</v>
       </c>
       <c r="AJ28" s="72" t="n">
-        <v>293.4073935523879</v>
+        <v>293.4065039518117</v>
       </c>
       <c r="AK28" s="72" t="n">
-        <v>261.3414993286133</v>
+        <v>261.3419990539551</v>
       </c>
       <c r="AL28" s="72" t="n">
-        <v>229.2756051048386</v>
+        <v>229.2774941560985</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.1970068021353231</v>
+        <v>0.1969858812143288</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>24.53945837622573</v>
+        <v>24.53834822870299</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>7.370803403981273</v>
+        <v>7.776242171358298</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -23564,13 +23564,13 @@
         <v>40.23193851575314</v>
       </c>
       <c r="AT28" s="26" t="n">
-        <v>0.01310832104369664</v>
+        <v>-0.005794852949476459</v>
       </c>
       <c r="AU28" s="26" t="n">
-        <v>0.009261968367853868</v>
+        <v>0.001531880377003469</v>
       </c>
       <c r="AV28" s="26" t="n">
-        <v>-0.4083160081918629</v>
+        <v>-0.3152650858753346</v>
       </c>
       <c r="AW28" s="26" t="n">
         <v>1.213063846538261</v>
@@ -23766,7 +23766,7 @@
         <v>0.004202900721427705</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>0.007835640584247017</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>-0.0005040778398927026</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>-0.02178605084672747</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>0.0004470874592776841</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>-0.01215122854742678</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>-0.01367236567406971</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>-0.008198704832808712</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E41" s="30" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>-0.00685599359086031</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>0.0004831799877809129</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>-0.007299289100143769</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 2 Sep 2026, 07:58 PM · Yahoo Finance data</t>
+          <t>Built 2 Sep 2026, 10:41 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27547,7 +27547,7 @@
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.4 / 9</t>
+          <t>4.5 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
@@ -27944,7 +27944,7 @@
         <v>-0.008539388474021248</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>-0.002447827045478523</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>0.003800922632101411</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>0.006261027194032653</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
@@ -29009,19 +29009,19 @@
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>0.0141817983100696</v>
+        <v>-0.01065622006694034</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -29056,11 +29056,11 @@
       </c>
       <c r="M13" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="N13" s="69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O13" s="23" t="inlineStr">
         <is>
@@ -29078,76 +29078,76 @@
         </is>
       </c>
       <c r="R13" s="70" t="n">
-        <v>112.9899978637695</v>
+        <v>111.4100036621094</v>
       </c>
       <c r="S13" s="71" t="n">
-        <v>1.579994201660156</v>
+        <v>-1.199996948242188</v>
       </c>
       <c r="T13" s="72" t="n">
-        <v>111.870002746582</v>
+        <v>112.0299987792969</v>
       </c>
       <c r="U13" s="72" t="n">
-        <v>113.5299987792969</v>
+        <v>112.370002746582</v>
       </c>
       <c r="V13" s="72" t="n">
-        <v>111.8300018310547</v>
+        <v>111.370002746582</v>
       </c>
       <c r="W13" s="73" t="n">
-        <v>3743500</v>
+        <v>4425600</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>0.8686290001659062</v>
+        <v>1.011861756125221</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>56.25686254478231</v>
+        <v>51.01216980941457</v>
       </c>
       <c r="Z13" s="28" t="n">
-        <v>75.39582678965377</v>
+        <v>36.90635274351316</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>12.82782318000766</v>
+        <v>12.27746093969639</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.5720718069620858</v>
+        <v>0.5037245699433868</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.4489547066501414</v>
+        <v>0.4181754315721553</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>0.1231171003119444</v>
+        <v>0.08554913837123146</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>112.1110162358644</v>
+        <v>111.8598786278915</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.4448186997505</v>
+        <v>111.2903007833486</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.0983996582031</v>
+        <v>110.0225996398926</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.6696998596191</v>
+        <v>112.6579998779297</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0331999969482</v>
+        <v>114.0346500015259</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.343902461012</v>
+        <v>113.5518211204788</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.6380001068115</v>
+        <v>111.4005001068115</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.932097752611</v>
+        <v>109.2491790931443</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.8962705584024059</v>
+        <v>0.502208772014376</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>3.056132056411507</v>
+        <v>3.86231841258263</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.494293618107402</v>
+        <v>1.485686049174404</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -29156,22 +29156,22 @@
         <v>105.0299987792969</v>
       </c>
       <c r="AR13" s="29" t="n">
-        <v>-6.15838294979687</v>
+        <v>-7.470616011279885</v>
       </c>
       <c r="AS13" s="78" t="n">
-        <v>51.77235176892785</v>
+        <v>41.49596671747967</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>0.01427285741572693</v>
+        <v>0.006595621204560587</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>0.06014257761860109</v>
+        <v>0.01735002729262392</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>-0.02333827055630144</v>
+        <v>-0.04508437978390245</v>
       </c>
       <c r="AW13" s="26" t="n">
-        <v>-0.04018011644483177</v>
+        <v>-0.05360174560959852</v>
       </c>
       <c r="AX13" s="25" t="n"/>
       <c r="AY13" s="25" t="n"/>
@@ -29190,7 +29190,7 @@
         <v>-0.008198223248004122</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>-0.004030459153398613</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>-0.007584418043843133</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>0.01627575132974779</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>-0.02326562725379</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -31347,29 +31347,29 @@
         </is>
       </c>
       <c r="C28" s="26" t="n">
-        <v>-0.06332041548914424</v>
+        <v>0.01652994979538658</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -31398,11 +31398,11 @@
         </is>
       </c>
       <c r="N28" s="69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="P28" s="25" t="inlineStr">
@@ -31416,76 +31416,76 @@
         </is>
       </c>
       <c r="R28" s="70" t="n">
-        <v>239.0500030517578</v>
+        <v>255.2100067138672</v>
       </c>
       <c r="S28" s="71" t="n">
-        <v>-16.16000366210938</v>
+        <v>4.150009155273438</v>
       </c>
       <c r="T28" s="72" t="n">
-        <v>251.1000061035156</v>
+        <v>255.4600067138672</v>
       </c>
       <c r="U28" s="72" t="n">
-        <v>251.6900024414062</v>
+        <v>267.6900024414062</v>
       </c>
       <c r="V28" s="72" t="n">
-        <v>238.6600036621094</v>
+        <v>249.4649963378906</v>
       </c>
       <c r="W28" s="73" t="n">
-        <v>3874900</v>
+        <v>4880000</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>0.9035728776565728</v>
+        <v>1.095119425241829</v>
       </c>
       <c r="Y28" s="28" t="n">
-        <v>39.96211488858304</v>
+        <v>45.7149076110599</v>
       </c>
       <c r="Z28" s="28" t="n">
-        <v>10.1194833993645</v>
+        <v>38.51021456935605</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>10.96817945327786</v>
+        <v>11.24998118180373</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-10.26046894402361</v>
+        <v>-9.758123070209763</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-9.97923098027724</v>
+        <v>-9.908921489340647</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-0.2812379637463742</v>
+        <v>0.1507984191308847</v>
       </c>
       <c r="AE28" s="72" t="n">
-        <v>248.8995139122899</v>
+        <v>251.7136598724419</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>258.6915066884342</v>
+        <v>260.6556570521018</v>
       </c>
       <c r="AG28" s="72" t="n">
-        <v>287.8605990600586</v>
+        <v>291.4571990966797</v>
       </c>
       <c r="AH28" s="72" t="n">
-        <v>273.2906494140625</v>
+        <v>272.3387493896485</v>
       </c>
       <c r="AI28" s="72" t="n">
-        <v>199.3352749252319</v>
+        <v>198.9142248916626</v>
       </c>
       <c r="AJ28" s="72" t="n">
-        <v>293.6322659954897</v>
+        <v>293.5779384582031</v>
       </c>
       <c r="AK28" s="72" t="n">
-        <v>261.1989990234375</v>
+        <v>261.2309989929199</v>
       </c>
       <c r="AL28" s="72" t="n">
-        <v>228.7657320513854</v>
+        <v>228.8840595276368</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.1585450982972891</v>
+        <v>0.4069310361569932</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>24.8341433874652</v>
+        <v>24.76500843313761</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>7.852394965332765</v>
+        <v>7.422125855023981</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -31494,22 +31494,22 @@
         <v>100.0199966430664</v>
       </c>
       <c r="AR28" s="29" t="n">
-        <v>-47.19461086684615</v>
+        <v>-43.62491720076359</v>
       </c>
       <c r="AS28" s="78" t="n">
-        <v>39.42100495441195</v>
+        <v>44.00306317970384</v>
       </c>
       <c r="AT28" s="26" t="n">
-        <v>-0.01754892382019058</v>
+        <v>0.01790844556199422</v>
       </c>
       <c r="AU28" s="26" t="n">
-        <v>-0.01030881139184814</v>
+        <v>0.1348215012072891</v>
       </c>
       <c r="AV28" s="26" t="n">
-        <v>-0.3233604198535892</v>
+        <v>-0.2387925699384323</v>
       </c>
       <c r="AW28" s="26" t="n">
-        <v>1.18689971997867</v>
+        <v>1.33473618528869</v>
       </c>
       <c r="AX28" s="25" t="n"/>
       <c r="AY28" s="25" t="n"/>
@@ -31526,7 +31526,7 @@
         <v>-0.05517577254916717</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E29" s="30" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>-0.007401625495918829</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>-0.00959387829211289</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>-0.02960829037404245</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>-0.03392203277851213</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>0.01530903307141895</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>-0.02845037703741871</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>-0.002704785444845648</v>
       </c>
       <c r="D39" s="34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E39" s="30" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>-0.04256684013924827</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>-0.03588291869363736</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>-0.04574959589106331</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>0.00193621591207882</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>0.006474453644578437</v>
       </c>
       <c r="D45" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>-0.04649784460844808</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>2.022243029231596e-05</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>-0.01707955694679375</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 2 Sep 2026, 07:58 PM · Yahoo Finance data</t>
+          <t>Built 2 Sep 2026, 10:41 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -43352,22 +43352,22 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>0.004863400613437818</v>
+        <v>0.005094979900543306</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>0.04252761118562365</v>
+        <v>0.04276787050926778</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>0.1121838444182381</v>
+        <v>0.1124401566111826</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>0.1085845699099326</v>
+        <v>0.1088400526195619</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>0.158302201017239</v>
+        <v>0.1585691415763248</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0.4557146145654034</v>
+        <v>0.4560500963358258</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>8</v>
@@ -43390,22 +43390,22 @@
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.007805652427233634</v>
+        <v>0.007456158868465623</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>-0.003054044023287572</v>
+        <v>-0.003399771584166378</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.06730405917661275</v>
+        <v>0.06693393236393752</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.1725516159165867</v>
+        <v>0.1721449906549615</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>0.1016236303403211</v>
+        <v>0.1012416019580995</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>0.1176356013958835</v>
+        <v>0.1172480202756576</v>
       </c>
       <c r="J7" s="34" t="n">
         <v>7</v>
@@ -43428,22 +43428,22 @@
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>0.0181486402988813</v>
+        <v>0.01690034709569455</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>-0.01054502467520968</v>
+        <v>-0.01175813823414407</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>0.03930604066044152</v>
+        <v>0.03803180759147962</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>0.02901783615297848</v>
+        <v>0.02775621685694873</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>0.02069697326458253</v>
+        <v>0.0194455556976294</v>
       </c>
       <c r="I8" s="26" t="n">
-        <v>0.1690187689841129</v>
+        <v>0.1675855026358002</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>7</v>
@@ -43466,22 +43466,22 @@
         </is>
       </c>
       <c r="D9" s="33" t="n">
-        <v>-0.0005717475925072213</v>
+        <v>-0.0002177809097458905</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>0.009876736627549176</v>
+        <v>0.01023440384137952</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.03086391026282165</v>
+        <v>0.03122901048668969</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>-0.07403764973855442</v>
+        <v>-0.07370970241397712</v>
       </c>
       <c r="H9" s="33" t="n">
-        <v>0.3348000266335227</v>
+        <v>0.3352727716619319</v>
       </c>
       <c r="I9" s="33" t="n">
-        <v>0.2748142120298651</v>
+        <v>0.2752657119316162</v>
       </c>
       <c r="J9" s="34" t="n">
         <v>2</v>
@@ -43495,76 +43495,76 @@
     <row r="10">
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>0.003636334998167179</v>
+        <v>0.0138888974898479</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>-0.01109569026491164</v>
+        <v>-0.006714986165234249</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>0.008248844487479312</v>
+        <v>0.00970003472765657</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>0.04558225154681006</v>
+        <v>-0.01012592699629389</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>-0.02484614039494948</v>
+        <v>-0.04696508103191899</v>
       </c>
       <c r="I10" s="26" t="n">
-        <v>0.1014417768081926</v>
+        <v>-0.04502211176349968</v>
       </c>
       <c r="J10" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10" s="101" t="inlineStr">
         <is>
-          <t>Long-term up, short-term mixed</t>
+          <t>Long-term down, short-term mixed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>State Street Communication Services Select Sector SPDR ETF</t>
+          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D11" s="33" t="n">
-        <v>0.01424965611645512</v>
+        <v>0.003284443158907635</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>-0.001332044446016312</v>
+        <v>-0.0114424168074545</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.003748644818933666</v>
+        <v>0.007895335424539018</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>0.003390410842344149</v>
+        <v>0.04521565276121042</v>
       </c>
       <c r="H11" s="33" t="n">
-        <v>-0.05328732875047293</v>
+        <v>-0.02518804579758527</v>
       </c>
       <c r="I11" s="33" t="n">
-        <v>-0.04468231465924755</v>
+        <v>0.1010555927301928</v>
       </c>
       <c r="J11" s="34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K11" s="102" t="inlineStr">
         <is>
-          <t>Long-term down, short-term mixed</t>
+          <t>Long-term up, short-term mixed</t>
         </is>
       </c>
     </row>
@@ -43580,22 +43580,22 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.008216737757639647</v>
+        <v>0.008041941928971008</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>-0.01012701973199037</v>
+        <v>-0.0102986352799006</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>-0.003628246290506842</v>
+        <v>-0.003800988539102157</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>0.1336740589707066</v>
+        <v>0.1334775124453844</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>0.1198057896882585</v>
+        <v>0.1196116475225653</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0.05294865230863022</v>
+        <v>0.05276610125057579</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>5</v>
@@ -43618,22 +43618,22 @@
         </is>
       </c>
       <c r="D13" s="33" t="n">
-        <v>0.002399873764442839</v>
+        <v>0.002356263906883926</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>-0.0261551434022198</v>
+        <v>-0.02619751096090783</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.0282971089299543</v>
+        <v>-0.02833938330146835</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>-0.0231737270089788</v>
+        <v>-0.02321622427552861</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>0.004415855637659449</v>
+        <v>0.00437215807390201</v>
       </c>
       <c r="I13" s="33" t="n">
-        <v>-0.03806218624028102</v>
+        <v>-0.0381040357777126</v>
       </c>
       <c r="J13" s="34" t="n">
         <v>1</v>
@@ -43656,25 +43656,25 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>-0.006244357860173189</v>
+        <v>-0.007039086440657094</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.0293856899191739</v>
+        <v>-0.03016191185959682</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.0311046897553966</v>
+        <v>-0.03187953697326018</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>0.005860746447995835</v>
+        <v>0.00505633714525433</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.0001142840106731491</v>
+        <v>-0.0006855297177219555</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0.08463447446516237</v>
+        <v>0.08376706805287815</v>
       </c>
       <c r="J14" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="101" t="inlineStr">
         <is>
@@ -43694,22 +43694,22 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>0.001409717026733981</v>
+        <v>0.002584511092692976</v>
       </c>
       <c r="E15" s="33" t="n">
-        <v>-0.01593171137213978</v>
+        <v>-0.01477726123417744</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>-0.03922456389824214</v>
+        <v>-0.03809743954358469</v>
       </c>
       <c r="G15" s="33" t="n">
-        <v>-0.0291572334738891</v>
+        <v>-0.02801829872849804</v>
       </c>
       <c r="H15" s="33" t="n">
-        <v>-0.09454006356045874</v>
+        <v>-0.09347783204601823</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>-0.001639721177700504</v>
+        <v>-0.0004685045305005131</v>
       </c>
       <c r="J15" s="34" t="n">
         <v>1</v>
@@ -43732,22 +43732,22 @@
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>0.0002316247664648774</v>
+        <v>0.0002894867885985253</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>-0.03155823888250919</v>
+        <v>-0.03150221586021174</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>-0.0567263550006023</v>
+        <v>-0.05667178791916472</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>-0.008152007285395002</v>
+        <v>-0.008094630244830925</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>-0.01521886760026148</v>
+        <v>-0.0151618993678353</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>0.1137829403742534</v>
+        <v>0.1138473711836303</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>3</v>
@@ -43861,7 +43861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G38"/>
+  <dimension ref="B2:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -43937,11 +43937,11 @@
       </c>
       <c r="D6" s="104" t="inlineStr">
         <is>
-          <t>Volume 4.8x its 20-day average</t>
+          <t>Volume 5.0x its 20-day average</t>
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>0.1560941090303309</v>
+        <v>0.1581176757812499</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>8</v>
@@ -43969,7 +43969,7 @@
         </is>
       </c>
       <c r="E7" s="33" t="n">
-        <v>0.1560941090303309</v>
+        <v>0.1581176757812499</v>
       </c>
       <c r="F7" s="34" t="n">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>0.1560941090303309</v>
+        <v>0.1581176757812499</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>8</v>
@@ -44025,7 +44025,7 @@
         </is>
       </c>
       <c r="E9" s="33" t="n">
-        <v>0.1560941090303309</v>
+        <v>0.1581176757812499</v>
       </c>
       <c r="F9" s="34" t="n">
         <v>8</v>
@@ -44053,7 +44053,7 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>0.03136493740275537</v>
+        <v>0.03205482497444945</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>8</v>
@@ -44081,7 +44081,7 @@
         </is>
       </c>
       <c r="E11" s="33" t="n">
-        <v>0.02398656002515054</v>
+        <v>0.02425438655856049</v>
       </c>
       <c r="F11" s="34" t="n">
         <v>8</v>
@@ -44109,7 +44109,7 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.02398656002515054</v>
+        <v>0.02425438655856049</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>8</v>
@@ -44137,7 +44137,7 @@
         </is>
       </c>
       <c r="E13" s="33" t="n">
-        <v>0.004863400613437818</v>
+        <v>0.005094979900543306</v>
       </c>
       <c r="F13" s="34" t="n">
         <v>8</v>
@@ -44165,7 +44165,7 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>0.0201668603207652</v>
+        <v>0.02010687288424085</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>7</v>
@@ -44193,7 +44193,7 @@
         </is>
       </c>
       <c r="E15" s="33" t="n">
-        <v>0.0201668603207652</v>
+        <v>0.02010687288424085</v>
       </c>
       <c r="F15" s="34" t="n">
         <v>7</v>
@@ -44221,7 +44221,7 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>0.0181486402988813</v>
+        <v>0.01690034709569455</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>7</v>
@@ -44249,7 +44249,7 @@
         </is>
       </c>
       <c r="E17" s="33" t="n">
-        <v>0.0181486402988813</v>
+        <v>0.01690034709569455</v>
       </c>
       <c r="F17" s="34" t="n">
         <v>7</v>
@@ -44277,7 +44277,7 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>-0.0006766561603024357</v>
+        <v>-0.000522909067699362</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>7</v>
@@ -44305,7 +44305,7 @@
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>0.01424965611645512</v>
+        <v>0.0138888974898479</v>
       </c>
       <c r="F19" s="34" t="n">
         <v>6</v>
@@ -44333,7 +44333,7 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0.008216737757639647</v>
+        <v>0.008041941928971008</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>5</v>
@@ -44361,7 +44361,7 @@
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>0.008216737757639647</v>
+        <v>0.008041941928971008</v>
       </c>
       <c r="F21" s="34" t="n">
         <v>5</v>
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>0.004200623603678011</v>
+        <v>0.004436902672253051</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>5</v>
@@ -44417,7 +44417,7 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>0.004200623603678011</v>
+        <v>0.004436902672253051</v>
       </c>
       <c r="F23" s="34" t="n">
         <v>5</v>
@@ -44445,10 +44445,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>0.003636334998167179</v>
+        <v>0.003284443158907635</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
@@ -44473,10 +44473,10 @@
         </is>
       </c>
       <c r="E25" s="33" t="n">
-        <v>0.003636334998167179</v>
+        <v>0.003284443158907635</v>
       </c>
       <c r="F25" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" s="30" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>-0.05844263837627894</v>
+        <v>-0.0581369028542128</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>4</v>
@@ -44525,11 +44525,11 @@
       </c>
       <c r="D27" s="105" t="inlineStr">
         <is>
-          <t>Gapped up 4.5% at the open</t>
+          <t>Volume 1.9x its 20-day average</t>
         </is>
       </c>
       <c r="E27" s="33" t="n">
-        <v>0.1177867782454238</v>
+        <v>0.1182796125279308</v>
       </c>
       <c r="F27" s="34" t="n">
         <v>3</v>
@@ -44543,21 +44543,21 @@
     <row r="28">
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="C28" s="101" t="inlineStr">
         <is>
-          <t>IREN Limited</t>
+          <t>AST SpaceMobile, Inc.</t>
         </is>
       </c>
       <c r="D28" s="104" t="inlineStr">
         <is>
-          <t>Gapped down 2.8% at the open</t>
+          <t>Gapped up 4.5% at the open</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>0.07509504108000065</v>
+        <v>0.1182796125279308</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>3</v>
@@ -44571,21 +44571,21 @@
     <row r="29">
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C29" s="102" t="inlineStr">
         <is>
-          <t>State Street Industrial Select Sector SPDR ETF</t>
+          <t>IREN Limited</t>
         </is>
       </c>
       <c r="D29" s="105" t="inlineStr">
         <is>
-          <t>Closed below lower band</t>
+          <t>Gapped down 2.8% at the open</t>
         </is>
       </c>
       <c r="E29" s="33" t="n">
-        <v>0.0002316247664648774</v>
+        <v>0.07550241179626238</v>
       </c>
       <c r="F29" s="34" t="n">
         <v>3</v>
@@ -44599,24 +44599,24 @@
     <row r="30">
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C30" s="101" t="inlineStr">
         <is>
-          <t>Nebius Group N.V.</t>
+          <t>Cameco Corporation</t>
         </is>
       </c>
       <c r="D30" s="104" t="inlineStr">
         <is>
-          <t>Gapped down 2.0% at the open</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>0.02272729184472988</v>
+        <v>0.001246572974491267</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
@@ -44627,24 +44627,24 @@
     <row r="31">
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C31" s="102" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
+          <t>State Street Industrial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D31" s="105" t="inlineStr">
         <is>
-          <t>8 EMA crossed below 21</t>
+          <t>Closed below lower band</t>
         </is>
       </c>
       <c r="E31" s="33" t="n">
-        <v>0.002077286010819135</v>
+        <v>0.0002894867885985253</v>
       </c>
       <c r="F31" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="30" t="inlineStr">
         <is>
@@ -44655,24 +44655,24 @@
     <row r="32">
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C32" s="101" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
+          <t>State Street Industrial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D32" s="104" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Volume 1.8x its 20-day average</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>0.002077286010819135</v>
+        <v>0.0002894867885985253</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
@@ -44683,21 +44683,21 @@
     <row r="33">
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C33" s="102" t="inlineStr">
         <is>
-          <t>Cameco Corporation</t>
+          <t>Nebius Group N.V.</t>
         </is>
       </c>
       <c r="D33" s="105" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Gapped down 2.0% at the open</t>
         </is>
       </c>
       <c r="E33" s="33" t="n">
-        <v>0.001651740894481168</v>
+        <v>0.02280246168613065</v>
       </c>
       <c r="F33" s="34" t="n">
         <v>2</v>
@@ -44711,105 +44711,105 @@
     <row r="34">
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C34" s="101" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Invesco QQQ Trust</t>
         </is>
       </c>
       <c r="D34" s="104" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>8 EMA crossed below 21</t>
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>0.005270608096960672</v>
+        <v>0.002261002137834645</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C35" s="102" t="inlineStr">
         <is>
-          <t>State Street Real Estate Select Sector SPDR ETF</t>
+          <t>Invesco QQQ Trust</t>
         </is>
       </c>
       <c r="D35" s="105" t="inlineStr">
         <is>
-          <t>Closed below lower band</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E35" s="33" t="n">
-        <v>-0.006244357860173189</v>
+        <v>0.002261002137834645</v>
       </c>
       <c r="F35" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="C36" s="101" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>State Street Real Estate Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D36" s="104" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Closed below lower band</t>
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>-0.006331396699976732</v>
+        <v>-0.007039086440657094</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C37" s="102" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D37" s="105" t="inlineStr">
         <is>
-          <t>Lost the 200 DMA</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E37" s="33" t="n">
-        <v>-0.007425327774216117</v>
+        <v>0.005270608096960672</v>
       </c>
       <c r="F37" s="34" t="n">
         <v>1</v>
@@ -44823,37 +44823,93 @@
     <row r="38">
       <c r="B38" s="24" t="inlineStr">
         <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C38" s="101" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="D38" s="104" t="inlineStr">
+        <is>
+          <t>Bands squeezing — a big move often follows</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="n">
+        <v>-0.005548155771720742</v>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C39" s="102" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="D39" s="105" t="inlineStr">
+        <is>
+          <t>Lost the 200 DMA</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="n">
+        <v>-0.006600309699600682</v>
+      </c>
+      <c r="F39" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="30" t="inlineStr">
+        <is>
+          <t>Very Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="24" t="inlineStr">
+        <is>
           <t>CRWV</t>
         </is>
       </c>
-      <c r="C38" s="101" t="inlineStr">
+      <c r="C40" s="101" t="inlineStr">
         <is>
           <t>CoreWeave, Inc.</t>
         </is>
       </c>
-      <c r="D38" s="104" t="inlineStr">
+      <c r="D40" s="104" t="inlineStr">
         <is>
           <t>Gapped down 2.1% at the open</t>
         </is>
       </c>
-      <c r="E38" s="26" t="n">
-        <v>-0.01246177962225503</v>
-      </c>
-      <c r="F38" s="27" t="n">
+      <c r="E40" s="26" t="n">
+        <v>-0.01124005114350968</v>
+      </c>
+      <c r="F40" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="23" t="inlineStr">
+      <c r="G40" s="23" t="inlineStr">
         <is>
           <t>Very Weak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:G38"/>
+  <autoFilter ref="B5:G40"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E38">
+  <conditionalFormatting sqref="E6:E40">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'08-28'!$5:$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'08-27'!$A$6:$AZ$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'08-27'!$5:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -348,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -640,6 +640,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1299,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 2 Sep 2026, 10:41 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 2 Sep 2026, 11:18 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1401,7 +1404,7 @@
       <c r="P8" s="10" t="n"/>
       <c r="Q8" s="16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R8" s="12" t="n"/>
@@ -1526,16 +1529,16 @@
         <v>7</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>54.05040407002677</v>
+        <v>53.89714101141512</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>2.347717249193892</v>
+        <v>2.256401659127816</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>-0.01175813823414407</v>
+        <v>-0.01341526794428827</v>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.03803180759147962</v>
+        <v>0.01826924544114328</v>
       </c>
     </row>
     <row r="15">
@@ -1559,16 +1562,16 @@
         <v>6</v>
       </c>
       <c r="G15" s="35" t="n">
-        <v>54.72608401943974</v>
+        <v>53.81500394124588</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>2.007482729214516</v>
+        <v>1.901704565746232</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>-0.006714986165234249</v>
+        <v>-0.001687260814993596</v>
       </c>
       <c r="J15" s="33" t="n">
-        <v>0.00970003472765657</v>
+        <v>0.003391621298757919</v>
       </c>
     </row>
     <row r="16">
@@ -1688,19 +1691,19 @@
         <v>0.003284443158907635</v>
       </c>
       <c r="F19" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="35" t="n">
-        <v>50.46824785757966</v>
+        <v>50.4832288975912</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>0.6609502075595408</v>
+        <v>0.6199768268461137</v>
       </c>
       <c r="I19" s="33" t="n">
-        <v>-0.0114424168074545</v>
+        <v>-0.008577696679776148</v>
       </c>
       <c r="J19" s="33" t="n">
-        <v>0.007895335424539018</v>
+        <v>0.001874148150021515</v>
       </c>
     </row>
     <row r="20">
@@ -1724,16 +1727,16 @@
         <v>1</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>38.17497212155799</v>
+        <v>38.32389938220743</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>-4.311052907273593</v>
+        <v>-4.210521249756949</v>
       </c>
       <c r="I20" s="26" t="n">
-        <v>-0.01477726123417744</v>
+        <v>-0.01930591093983502</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>-0.03809743954358469</v>
+        <v>-0.03264571347723622</v>
       </c>
     </row>
     <row r="21">
@@ -1757,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>43.53170083284979</v>
+        <v>43.5366795914509</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>-1.085594686590152</v>
+        <v>-1.14433564061972</v>
       </c>
       <c r="I21" s="33" t="n">
-        <v>-0.02619751096090783</v>
+        <v>-0.01963129890633197</v>
       </c>
       <c r="J21" s="33" t="n">
-        <v>-0.02833938330146835</v>
+        <v>-0.02899653629747789</v>
       </c>
     </row>
     <row r="22">
@@ -1790,16 +1793,16 @@
         <v>3</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>30.59156978165758</v>
+        <v>30.15246259938382</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>-4.803883697477406</v>
+        <v>-4.793287687951942</v>
       </c>
       <c r="I22" s="26" t="n">
-        <v>-0.03150221586021174</v>
+        <v>-0.04192080354947503</v>
       </c>
       <c r="J22" s="26" t="n">
-        <v>-0.05667178791916472</v>
+        <v>-0.07306864572512406</v>
       </c>
     </row>
     <row r="23">
@@ -1823,16 +1826,16 @@
         <v>2</v>
       </c>
       <c r="G23" s="35" t="n">
-        <v>49.7084196689224</v>
+        <v>49.49536274589462</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>0.622260574529121</v>
+        <v>0.6057194395941323</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>0.01023440384137952</v>
+        <v>0.004156693178994031</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>0.03122901048668969</v>
+        <v>-0.01765643606599832</v>
       </c>
     </row>
     <row r="24">
@@ -2089,7 +2092,7 @@
         </is>
       </c>
       <c r="L32" s="35" t="n">
-        <v>43.53170083284979</v>
+        <v>43.5366795914509</v>
       </c>
     </row>
     <row r="33">
@@ -2129,7 +2132,7 @@
         </is>
       </c>
       <c r="L33" s="28" t="n">
-        <v>38.17497212155799</v>
+        <v>38.32389938220743</v>
       </c>
     </row>
     <row r="34">
@@ -2150,7 +2153,7 @@
         </is>
       </c>
       <c r="F34" s="35" t="n">
-        <v>54.39558251894007</v>
+        <v>54.62647043454713</v>
       </c>
       <c r="H34" s="31" t="inlineStr">
         <is>
@@ -2190,7 +2193,7 @@
         </is>
       </c>
       <c r="F35" s="28" t="n">
-        <v>54.05040407002677</v>
+        <v>53.89714101141512</v>
       </c>
       <c r="H35" s="24" t="inlineStr">
         <is>
@@ -2295,11 +2298,11 @@
     <row r="38">
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C38" s="33" t="n">
-        <v>0.003731313815136028</v>
+        <v>-0.000522909067699362</v>
       </c>
       <c r="D38" s="34" t="n">
         <v>7</v>
@@ -2310,7 +2313,7 @@
         </is>
       </c>
       <c r="F38" s="35" t="n">
-        <v>54.26467799669614</v>
+        <v>60.85736584032756</v>
       </c>
       <c r="H38" s="31" t="inlineStr">
         <is>
@@ -2329,7 +2332,7 @@
         </is>
       </c>
       <c r="L38" s="35" t="n">
-        <v>49.7084196689224</v>
+        <v>49.49536274589462</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -2694,7 +2697,7 @@
         </is>
       </c>
       <c r="F50" s="35" t="n">
-        <v>54.39558251894007</v>
+        <v>54.62647043454713</v>
       </c>
       <c r="H50" s="31" t="inlineStr">
         <is>
@@ -2734,7 +2737,7 @@
         </is>
       </c>
       <c r="F51" s="28" t="n">
-        <v>54.05040407002677</v>
+        <v>53.89714101141512</v>
       </c>
       <c r="H51" s="24" t="inlineStr">
         <is>
@@ -2774,7 +2777,7 @@
         </is>
       </c>
       <c r="F52" s="35" t="n">
-        <v>54.72608401943974</v>
+        <v>53.81500394124588</v>
       </c>
       <c r="H52" s="31" t="inlineStr">
         <is>
@@ -2793,7 +2796,7 @@
         </is>
       </c>
       <c r="L52" s="35" t="n">
-        <v>49.7084196689224</v>
+        <v>49.49536274589462</v>
       </c>
     </row>
   </sheetData>
@@ -3104,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 2 Sep 2026, 10:41 PM · Yahoo Finance data</t>
+          <t>Built 2 Sep 2026, 11:18 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -3575,7 +3578,7 @@
       </c>
       <c r="L7" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M7" s="23" t="inlineStr">
@@ -3620,58 +3623,58 @@
         <v>10797498</v>
       </c>
       <c r="X7" s="74" t="n">
-        <v>1.781015938524481</v>
+        <v>1.743721459021068</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>30.59156978165758</v>
+        <v>30.15246259938382</v>
       </c>
       <c r="Z7" s="28" t="n">
         <v>7.385063308280859</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>23.06108551951775</v>
+        <v>24.14483404359851</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>-1.948609984988963</v>
+        <v>-2.051161070952446</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>-0.6722768913025545</v>
+        <v>-0.8532696092721895</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-1.276333093686408</v>
+        <v>-1.197891461680257</v>
       </c>
       <c r="AE7" s="72" t="n">
-        <v>176.6950869484179</v>
+        <v>176.3492192903427</v>
       </c>
       <c r="AF7" s="72" t="n">
-        <v>179.687799414156</v>
+        <v>179.3732866240469</v>
       </c>
       <c r="AG7" s="72" t="n">
-        <v>181.4989996337891</v>
+        <v>181.4787997436523</v>
       </c>
       <c r="AH7" s="72" t="n">
-        <v>177.5791996765137</v>
+        <v>177.6353996276856</v>
       </c>
       <c r="AI7" s="72" t="n">
-        <v>170.3844497680664</v>
+        <v>170.5101497650147</v>
       </c>
       <c r="AJ7" s="72" t="n">
-        <v>190.4905493667063</v>
+        <v>189.9702421048737</v>
       </c>
       <c r="AK7" s="72" t="n">
-        <v>181.6904998779297</v>
+        <v>181.2299995422363</v>
       </c>
       <c r="AL7" s="72" t="n">
-        <v>172.890450389153</v>
+        <v>172.489756979599</v>
       </c>
       <c r="AM7" s="76" t="n">
-        <v>-0.006275624358533936</v>
+        <v>0.01660376114380646</v>
       </c>
       <c r="AN7" s="29" t="n">
-        <v>9.686857039513958</v>
+        <v>9.645469938436356</v>
       </c>
       <c r="AO7" s="77" t="n">
-        <v>1.500053845450322</v>
+        <v>1.453209141759633</v>
       </c>
       <c r="AP7" s="72" t="n">
         <v>188.1900024414062</v>
@@ -3686,13 +3689,13 @@
         <v>62.46040799880161</v>
       </c>
       <c r="AT7" s="26" t="n">
-        <v>-0.03150221586021174</v>
+        <v>-0.04192080354947503</v>
       </c>
       <c r="AU7" s="26" t="n">
-        <v>-0.05667178791916472</v>
+        <v>-0.07306864572512406</v>
       </c>
       <c r="AV7" s="26" t="n">
-        <v>-0.008094630244830925</v>
+        <v>-0.007296778225756584</v>
       </c>
       <c r="AW7" s="26" t="n">
         <v>0.1138473711836303</v>
@@ -4344,7 +4347,7 @@
         </is>
       </c>
       <c r="N11" s="69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" s="23" t="inlineStr">
         <is>
@@ -4380,58 +4383,58 @@
         <v>8426913</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>0.9822125668524383</v>
+        <v>0.9875760490190137</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>50.46824785757966</v>
+        <v>50.4832288975912</v>
       </c>
       <c r="Z11" s="28" t="n">
         <v>32.63891832323147</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>15.51690569335987</v>
+        <v>14.6888745773202</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.1634873561398535</v>
+        <v>0.1298466110755214</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.2731332480310088</v>
+        <v>0.2465365852614052</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.1096458918911553</v>
+        <v>-0.1166899741858838</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>85.59799228285212</v>
+        <v>85.54733314865717</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.54174738684888</v>
+        <v>85.52935488390062</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>84.9683999633789</v>
+        <v>85.00299987792968</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.28780014038085</v>
+        <v>84.31860008239747</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.20605022430419</v>
+        <v>83.24670021057129</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>86.98623859549889</v>
+        <v>86.98897957710869</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.57799987792968</v>
+        <v>85.58399963378906</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>84.16976116036048</v>
+        <v>84.17901969046943</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.4829570448412093</v>
+        <v>0.4807823397234425</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.291123231620153</v>
+        <v>3.283277129677256</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.377527375715853</v>
+        <v>1.336766590373574</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -4446,13 +4449,13 @@
         <v>69.22562132727056</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-0.0114424168074545</v>
+        <v>-0.008577696679776148</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>0.007895335424539018</v>
+        <v>0.001874148150021515</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.04521565276121042</v>
+        <v>0.04101746551822116</v>
       </c>
       <c r="AW11" s="26" t="n">
         <v>0.1010555927301928</v>
@@ -4525,7 +4528,7 @@
       </c>
       <c r="L12" s="30" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M12" s="30" t="inlineStr">
@@ -4570,58 +4573,58 @@
         <v>4221465</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>0.8369374496828449</v>
+        <v>0.8505268086650895</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>43.53170083284979</v>
+        <v>43.5366795914509</v>
       </c>
       <c r="Z12" s="35" t="n">
         <v>12.37323676656066</v>
       </c>
       <c r="AA12" s="35" t="n">
-        <v>13.59380012353222</v>
+        <v>13.04795181979406</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>-0.1282971680671068</v>
+        <v>-0.1522668871156867</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.2920133219803698</v>
+        <v>0.2544211520515133</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.4203104900474766</v>
+        <v>-0.4066880391672</v>
       </c>
       <c r="AE12" s="83" t="n">
-        <v>116.1798761746035</v>
+        <v>116.1735903136837</v>
       </c>
       <c r="AF12" s="83" t="n">
-        <v>116.6585378060762</v>
+        <v>116.6653300039721</v>
       </c>
       <c r="AG12" s="83" t="n">
-        <v>116.1205996704102</v>
+        <v>116.189599609375</v>
       </c>
       <c r="AH12" s="83" t="n">
-        <v>116.9368998718262</v>
+        <v>116.9800998687744</v>
       </c>
       <c r="AI12" s="83" t="n">
-        <v>116.9547999191284</v>
+        <v>116.9608499145508</v>
       </c>
       <c r="AJ12" s="83" t="n">
-        <v>120.4242475651574</v>
+        <v>120.3149966413769</v>
       </c>
       <c r="AK12" s="83" t="n">
-        <v>117.5889987945557</v>
+        <v>117.5174987792969</v>
       </c>
       <c r="AL12" s="83" t="n">
-        <v>114.7537500239539</v>
+        <v>114.7200009172169</v>
       </c>
       <c r="AM12" s="87" t="n">
-        <v>0.01873743628766048</v>
+        <v>0.0250223056525599</v>
       </c>
       <c r="AN12" s="36" t="n">
-        <v>4.822302765848549</v>
+        <v>4.760989454572775</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.400010040492322</v>
+        <v>1.383911384496584</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -4636,13 +4639,13 @@
         <v>48.78909343005958</v>
       </c>
       <c r="AT12" s="33" t="n">
-        <v>-0.02619751096090783</v>
+        <v>-0.01963129890633197</v>
       </c>
       <c r="AU12" s="33" t="n">
-        <v>-0.02833938330146835</v>
+        <v>-0.02899653629747789</v>
       </c>
       <c r="AV12" s="33" t="n">
-        <v>-0.02321622427552861</v>
+        <v>-0.01601989799369741</v>
       </c>
       <c r="AW12" s="33" t="n">
         <v>-0.0381040357777126</v>
@@ -4760,58 +4763,58 @@
         <v>5098194</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>1.231947836219613</v>
+        <v>1.262978136272434</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>54.72608401943974</v>
+        <v>53.81500394124588</v>
       </c>
       <c r="Z13" s="28" t="n">
         <v>57.86661783854166</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>12.10741423181737</v>
+        <v>12.70478720520246</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.4021011784522983</v>
+        <v>0.4180468147141312</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.4091764542843005</v>
+        <v>0.4389108279843769</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>-0.007075275832002181</v>
+        <v>-0.02086401327024573</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>111.7612313263991</v>
+        <v>111.8793934656785</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.3718408475689</v>
+        <v>111.4879324451661</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.2075996398926</v>
+        <v>110.3219996643066</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.6065998840332</v>
+        <v>112.5969998931885</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0033499908447</v>
+        <v>114.0086499786377</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.2043378909943</v>
+        <v>113.3906392189749</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.5575000762939</v>
+        <v>111.6634998321533</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.9106622615936</v>
+        <v>109.9363604453317</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.7618649161903897</v>
+        <v>0.7190032670681386</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>2.952446610177032</v>
+        <v>3.093471706363788</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.468637558676278</v>
+        <v>1.514196176088373</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -4826,13 +4829,13 @@
         <v>48.06503668064025</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>-0.006714986165234249</v>
+        <v>-0.001687260814993596</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>0.00970003472765657</v>
+        <v>0.003391621298757919</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>-0.01012592699629389</v>
+        <v>0.003033514742470489</v>
       </c>
       <c r="AW13" s="26" t="n">
         <v>-0.04502211176349968</v>
@@ -4950,58 +4953,58 @@
         <v>12839941</v>
       </c>
       <c r="X14" s="85" t="n">
-        <v>1.2128647893584</v>
+        <v>1.204196563652695</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>54.05040407002677</v>
+        <v>53.89714101141512</v>
       </c>
       <c r="Z14" s="35" t="n">
         <v>49.18038681677405</v>
       </c>
       <c r="AA14" s="35" t="n">
-        <v>12.83321990595936</v>
+        <v>14.36448273711229</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.345158460396064</v>
+        <v>0.3216008678605959</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.4176142015451955</v>
+        <v>0.4111425658014495</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>-0.07245574114913145</v>
+        <v>-0.08954169794085354</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>52.86410226254483</v>
+        <v>52.86567199454959</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.59885884048205</v>
+        <v>52.63810268379272</v>
       </c>
       <c r="AG14" s="83" t="n">
-        <v>51.73539985656738</v>
+        <v>51.78159988403321</v>
       </c>
       <c r="AH14" s="83" t="n">
-        <v>51.55159999847412</v>
+        <v>51.56380001068115</v>
       </c>
       <c r="AI14" s="83" t="n">
-        <v>49.92902498245239</v>
+        <v>49.97599998474121</v>
       </c>
       <c r="AJ14" s="83" t="n">
-        <v>53.88206629554979</v>
+        <v>53.91959254658747</v>
       </c>
       <c r="AK14" s="83" t="n">
-        <v>52.78950023651123</v>
+        <v>52.8165002822876</v>
       </c>
       <c r="AL14" s="83" t="n">
-        <v>51.69693417747267</v>
+        <v>51.71340801798772</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.5734511772082048</v>
+        <v>0.5605119285903912</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>4.139330943250339</v>
+        <v>4.177074430922886</v>
       </c>
       <c r="AO14" s="88" t="n">
-        <v>1.551153729109351</v>
+        <v>1.566562867166497</v>
       </c>
       <c r="AP14" s="83" t="n">
         <v>54.18999862670898</v>
@@ -5016,13 +5019,13 @@
         <v>89.79845340765011</v>
       </c>
       <c r="AT14" s="33" t="n">
-        <v>-0.01175813823414407</v>
+        <v>-0.01341526794428827</v>
       </c>
       <c r="AU14" s="33" t="n">
-        <v>0.03803180759147962</v>
+        <v>0.01826924544114328</v>
       </c>
       <c r="AV14" s="33" t="n">
-        <v>0.02775621685694873</v>
+        <v>0.02556652464683751</v>
       </c>
       <c r="AW14" s="33" t="n">
         <v>0.1675855026358002</v>
@@ -5140,58 +5143,58 @@
         <v>5668731</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>0.9231406141208736</v>
+        <v>0.9327956167155593</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>49.7084196689224</v>
+        <v>49.49536274589462</v>
       </c>
       <c r="Z15" s="28" t="n">
         <v>36.96830229649036</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>12.54910890277319</v>
+        <v>12.02263429786104</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.6278516932520404</v>
+        <v>0.6210963931255549</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>0.9061379503182541</v>
+        <v>0.8879795754756272</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.2782862570662137</v>
+        <v>-0.2668831823500724</v>
       </c>
       <c r="AE15" s="72" t="n">
-        <v>184.4457683113689</v>
+        <v>184.5645144324723</v>
       </c>
       <c r="AF15" s="72" t="n">
-        <v>184.0866488157398</v>
+        <v>184.2052659552141</v>
       </c>
       <c r="AG15" s="72" t="n">
-        <v>182.4646008300781</v>
+        <v>182.4946008300781</v>
       </c>
       <c r="AH15" s="72" t="n">
-        <v>177.7903009033203</v>
+        <v>178.2210009765625</v>
       </c>
       <c r="AI15" s="72" t="n">
-        <v>159.7063751220703</v>
+        <v>159.9183501434326</v>
       </c>
       <c r="AJ15" s="72" t="n">
-        <v>191.5723244706226</v>
+        <v>191.560618646972</v>
       </c>
       <c r="AK15" s="72" t="n">
-        <v>185.7115013122558</v>
+        <v>185.7005012512207</v>
       </c>
       <c r="AL15" s="72" t="n">
-        <v>179.8506781538891</v>
+        <v>179.8403838554694</v>
       </c>
       <c r="AM15" s="76" t="n">
-        <v>0.3198635966582695</v>
+        <v>0.320780454907953</v>
       </c>
       <c r="AN15" s="29" t="n">
-        <v>6.311750340666694</v>
+        <v>6.31136411185407</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.138032601666799</v>
+        <v>2.040131868445747</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -5206,13 +5209,13 @@
         <v>79.00070702943125</v>
       </c>
       <c r="AT15" s="26" t="n">
-        <v>0.01023440384137952</v>
+        <v>0.004156693178994031</v>
       </c>
       <c r="AU15" s="26" t="n">
-        <v>0.03122901048668969</v>
+        <v>-0.01765643606599832</v>
       </c>
       <c r="AV15" s="26" t="n">
-        <v>-0.07370970241397712</v>
+        <v>-0.06436319573466176</v>
       </c>
       <c r="AW15" s="26" t="n">
         <v>0.2752657119316162</v>
@@ -5520,58 +5523,58 @@
         <v>29748425</v>
       </c>
       <c r="X17" s="74" t="n">
-        <v>1.442524741063707</v>
+        <v>1.462746094706761</v>
       </c>
       <c r="Y17" s="28" t="n">
-        <v>38.17497212155799</v>
+        <v>38.32389938220743</v>
       </c>
       <c r="Z17" s="28" t="n">
         <v>29.03216103212822</v>
       </c>
       <c r="AA17" s="28" t="n">
-        <v>16.2096219818047</v>
+        <v>16.92836864768358</v>
       </c>
       <c r="AB17" s="75" t="n">
-        <v>-0.521771646114324</v>
+        <v>-0.5270817200397104</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.4442308396091301</v>
+        <v>-0.4570689396802105</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.0775408065051939</v>
+        <v>-0.07001278035949993</v>
       </c>
       <c r="AE17" s="72" t="n">
-        <v>42.95833137406509</v>
+        <v>42.88316176663835</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>43.52162683400584</v>
+        <v>43.44447254877277</v>
       </c>
       <c r="AG17" s="72" t="n">
-        <v>44.59240013122559</v>
+        <v>44.54560012817383</v>
       </c>
       <c r="AH17" s="72" t="n">
-        <v>44.84869987487793</v>
+        <v>44.80639987945557</v>
       </c>
       <c r="AI17" s="72" t="n">
-        <v>44.68632495880127</v>
+        <v>44.67827495574952</v>
       </c>
       <c r="AJ17" s="72" t="n">
-        <v>44.56864939502348</v>
+        <v>44.56042907445746</v>
       </c>
       <c r="AK17" s="72" t="n">
-        <v>43.45200042724609</v>
+        <v>43.4055004119873</v>
       </c>
       <c r="AL17" s="72" t="n">
-        <v>42.3353514594687</v>
+        <v>42.25057174951715</v>
       </c>
       <c r="AM17" s="76" t="n">
-        <v>0.1498441852065223</v>
+        <v>0.1815810937322726</v>
       </c>
       <c r="AN17" s="29" t="n">
-        <v>5.139689573772587</v>
+        <v>5.321577456810973</v>
       </c>
       <c r="AO17" s="77" t="n">
-        <v>1.588143623399645</v>
+        <v>1.547288343491567</v>
       </c>
       <c r="AP17" s="72" t="n">
         <v>47.79999923706055</v>
@@ -5586,13 +5589,13 @@
         <v>22.85710024396862</v>
       </c>
       <c r="AT17" s="26" t="n">
-        <v>-0.01477726123417744</v>
+        <v>-0.01930591093983502</v>
       </c>
       <c r="AU17" s="26" t="n">
-        <v>-0.03809743954358469</v>
+        <v>-0.03264571347723622</v>
       </c>
       <c r="AV17" s="26" t="n">
-        <v>-0.02801829872849804</v>
+        <v>-0.02379320378198746</v>
       </c>
       <c r="AW17" s="26" t="n">
         <v>-0.0004685045305005131</v>
@@ -6105,58 +6108,58 @@
         <v>22223877</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>1.31869132441236</v>
+        <v>1.313773146531027</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>44.60613909456504</v>
+        <v>44.56480346603605</v>
       </c>
       <c r="Z21" s="28" t="n">
         <v>26.56154381712717</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>18.89249594097669</v>
+        <v>19.66960321265908</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>-0.4505355177273032</v>
+        <v>-0.6488048666528243</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>0.7321312816139827</v>
+        <v>0.5222544148770829</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-1.182666799341286</v>
+        <v>-1.171059281529907</v>
       </c>
       <c r="AE21" s="72" t="n">
-        <v>296.07249410974</v>
+        <v>295.6615761341597</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>297.5595216869958</v>
+        <v>297.3292906842972</v>
       </c>
       <c r="AG21" s="72" t="n">
-        <v>297.0934008789063</v>
+        <v>297.1020007324219</v>
       </c>
       <c r="AH21" s="72" t="n">
-        <v>289.5873010253906</v>
+        <v>289.9318011474609</v>
       </c>
       <c r="AI21" s="72" t="n">
-        <v>271.7811502838135</v>
+        <v>272.0759503173828</v>
       </c>
       <c r="AJ21" s="72" t="n">
-        <v>306.4171341175905</v>
+        <v>306.4037252577242</v>
       </c>
       <c r="AK21" s="72" t="n">
-        <v>299.4970001220703</v>
+        <v>299.2960006713867</v>
       </c>
       <c r="AL21" s="72" t="n">
-        <v>292.57686612655</v>
+        <v>292.1882760850492</v>
       </c>
       <c r="AM21" s="76" t="n">
-        <v>0.1035488359042399</v>
+        <v>0.1281516790955529</v>
       </c>
       <c r="AN21" s="29" t="n">
-        <v>4.621170824882858</v>
+        <v>4.749628842612871</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.211035682485545</v>
+        <v>1.154851869199024</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -6171,13 +6174,13 @@
         <v>85.3566031870626</v>
       </c>
       <c r="AT21" s="26" t="n">
-        <v>-0.01744477836129088</v>
+        <v>-0.01645864593952751</v>
       </c>
       <c r="AU21" s="26" t="n">
-        <v>-0.007460642245530003</v>
+        <v>-0.0255211358838926</v>
       </c>
       <c r="AV21" s="26" t="n">
-        <v>0.008057347850266572</v>
+        <v>0.0220391283135366</v>
       </c>
       <c r="AW21" s="26" t="n">
         <v>0.1943857872589114</v>
@@ -6996,7 +6999,7 @@
       </c>
       <c r="G27" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" s="30" t="inlineStr">
@@ -7030,7 +7033,7 @@
         </is>
       </c>
       <c r="N27" s="80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O27" s="30" t="inlineStr">
         <is>
@@ -7066,58 +7069,58 @@
         <v>3715137</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>0.8008569866919399</v>
+        <v>0.8014616741192124</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>54.26467799669614</v>
+        <v>53.74926983196325</v>
       </c>
       <c r="Z27" s="35" t="n">
         <v>49.40169037792232</v>
       </c>
       <c r="AA27" s="35" t="n">
-        <v>24.16780966287277</v>
+        <v>24.22981831228937</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.035316944040559</v>
+        <v>1.921484580026075</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>2.006934221910854</v>
+        <v>2.012805174852286</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.02838272212970505</v>
+        <v>-0.09132059482621102</v>
       </c>
       <c r="AE27" s="83" t="n">
-        <v>84.28082384347923</v>
+        <v>84.26154881343163</v>
       </c>
       <c r="AF27" s="83" t="n">
-        <v>82.29754161346727</v>
+        <v>82.49137800083233</v>
       </c>
       <c r="AG27" s="83" t="n">
-        <v>79.19199966430664</v>
+        <v>79.35019958496093</v>
       </c>
       <c r="AH27" s="83" t="n">
-        <v>78.17699996948242</v>
+        <v>78.32999992370605</v>
       </c>
       <c r="AI27" s="83" t="n">
-        <v>76.78135007858276</v>
+        <v>76.81885007858277</v>
       </c>
       <c r="AJ27" s="83" t="n">
-        <v>88.57031181052821</v>
+        <v>88.37958882881064</v>
       </c>
       <c r="AK27" s="83" t="n">
-        <v>82.33099975585938</v>
+        <v>82.75149955749512</v>
       </c>
       <c r="AL27" s="83" t="n">
-        <v>76.09168770119055</v>
+        <v>77.12341028617961</v>
       </c>
       <c r="AM27" s="87" t="n">
-        <v>0.584865096064286</v>
+        <v>0.5567243873873442</v>
       </c>
       <c r="AN27" s="36" t="n">
-        <v>15.15665320030269</v>
+        <v>13.60238618372145</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.886046382997098</v>
+        <v>2.822208403527926</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -7132,13 +7135,13 @@
         <v>68.82679156562203</v>
       </c>
       <c r="AT27" s="33" t="n">
-        <v>-0.03450275862184715</v>
+        <v>-0.0278619657689394</v>
       </c>
       <c r="AU27" s="33" t="n">
-        <v>0.133940690120951</v>
+        <v>0.08637307281012485</v>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>0.0435489371550255</v>
+        <v>0.06691396471971345</v>
       </c>
       <c r="AW27" s="33" t="n">
         <v>0.08411338240664756</v>
@@ -7254,58 +7257,58 @@
         <v>2423600</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>0.6596615954523741</v>
+        <v>0.664767670062826</v>
       </c>
       <c r="Y28" s="28" t="n">
-        <v>38.55073600426524</v>
+        <v>38.95558671795506</v>
       </c>
       <c r="Z28" s="28" t="n">
-        <v>9.128219696542685</v>
+        <v>9.611060395008831</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>9.470357924200014</v>
+        <v>9.232053722506933</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-11.09515337438438</v>
+        <v>-11.04970571127058</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-10.28828006087829</v>
+        <v>-10.36606632682007</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-0.8068733135060899</v>
+        <v>-0.6836393844505064</v>
       </c>
       <c r="AE28" s="72" t="n">
-        <v>243.7305990629119</v>
+        <v>242.4065221571065</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>254.7670310276704</v>
+        <v>253.2913357882507</v>
       </c>
       <c r="AG28" s="72" t="n">
-        <v>280.3677993774414</v>
+        <v>277.8209991455078</v>
       </c>
       <c r="AH28" s="72" t="n">
-        <v>275.0289994812012</v>
+        <v>275.9301995849609</v>
       </c>
       <c r="AI28" s="72" t="n">
-        <v>200.2055249404907</v>
+        <v>200.6992249679566</v>
       </c>
       <c r="AJ28" s="72" t="n">
-        <v>292.1762327516705</v>
+        <v>290.6422658097709</v>
       </c>
       <c r="AK28" s="72" t="n">
-        <v>258.8449996948242</v>
+        <v>257.0685005187988</v>
       </c>
       <c r="AL28" s="72" t="n">
-        <v>225.5137666379779</v>
+        <v>223.4947352278268</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.1402023434961691</v>
+        <v>0.169258128839974</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>25.75381645088256</v>
+        <v>26.12048167956454</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>7.476826938691822</v>
+        <v>7.11674554864134</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -7320,13 +7323,13 @@
         <v>38.23295849402318</v>
       </c>
       <c r="AT28" s="26" t="n">
-        <v>-0.02773636784218381</v>
+        <v>-0.06452639650194114</v>
       </c>
       <c r="AU28" s="26" t="n">
-        <v>-0.01756879859087579</v>
+        <v>-0.1628884992369518</v>
       </c>
       <c r="AV28" s="26" t="n">
-        <v>-0.4168011581690544</v>
+        <v>-0.4297161249351141</v>
       </c>
       <c r="AW28" s="26" t="n">
         <v>1.148568345584848</v>
@@ -7818,79 +7821,79 @@
         <v>2386914</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>0.8980853837940804</v>
+        <v>0.8871024958433458</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>47.10679167818135</v>
+        <v>46.73504086446756</v>
       </c>
       <c r="Z31" s="35" t="n">
         <v>14.01017570113195</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>17.23665722789432</v>
+        <v>16.69767659568942</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>1.543488015895591</v>
+        <v>1.318616936985251</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.831109008986867</v>
+        <v>1.806636278957881</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>-0.2876209930912765</v>
+        <v>-0.4880193419726302</v>
       </c>
       <c r="AE31" s="83" t="n">
-        <v>99.84874585114538</v>
+        <v>99.52394629035021</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>98.54187877950032</v>
+        <v>98.60863252562338</v>
       </c>
       <c r="AG31" s="83" t="n">
-        <v>95.74919998168946</v>
+        <v>95.57160003662109</v>
       </c>
       <c r="AH31" s="83" t="n">
-        <v>104.3438997650147</v>
+        <v>104.1835997772217</v>
       </c>
       <c r="AI31" s="83" t="n">
-        <v>105.130899772644</v>
+        <v>105.2010497665405</v>
       </c>
       <c r="AJ31" s="83" t="n">
-        <v>106.8660775204759</v>
+        <v>106.8468630588073</v>
       </c>
       <c r="AK31" s="83" t="n">
-        <v>99.04249992370606</v>
+        <v>99.32950019836426</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>91.21892232693625</v>
+        <v>91.81213733792126</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.3298411029125995</v>
+        <v>0.3038206349950976</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>15.79842512617599</v>
+        <v>15.13621400576985</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>4.445765512302909</v>
+        <v>4.213478048344434</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
       </c>
       <c r="AQ31" s="83" t="n">
-        <v>73.19999694824219</v>
+        <v>74.62999725341797</v>
       </c>
       <c r="AR31" s="36" t="n">
         <v>-28.73410726215205</v>
       </c>
       <c r="AS31" s="89" t="n">
-        <v>37.36298696411627</v>
+        <v>35.88516258563557</v>
       </c>
       <c r="AT31" s="33" t="n">
-        <v>-0.09891550038906627</v>
+        <v>-0.1022727579593076</v>
       </c>
       <c r="AU31" s="33" t="n">
-        <v>0.07423089547593587</v>
+        <v>0.03534215323830892</v>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>-0.2002323828318811</v>
+        <v>-0.1586941401240629</v>
       </c>
       <c r="AW31" s="33" t="n">
         <v>0.05344845888978766</v>
@@ -8461,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
+          <t>The Builders Stage brings practical strategies for scaling startups to TechCrunch Disrupt 2026</t>
+        </is>
+      </c>
+      <c r="AY34" s="79" t="inlineStr">
+        <is>
           <t>Google Dodges Major Breakup Threat</t>
         </is>
       </c>
-      <c r="AY34" s="79" t="inlineStr">
+      <c r="AZ34" s="79" t="inlineStr">
         <is>
           <t>Stock Market Today, Sept. 2: Eos Energy Surges 19% on Google Partnership for $350M West Virginia Project</t>
-        </is>
-      </c>
-      <c r="AZ34" s="79" t="inlineStr">
-        <is>
-          <t>Google spared from ad-business breakup, but judge orders changes to how it operates</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10156,7 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
-          <t>Broadcom's Q3 earnings beat just isn't 'enough' to keep investors happy</t>
+          <t>Why Hycroft Mining Stock Zoomed More Than 7% Higher Today</t>
         </is>
       </c>
       <c r="AY43" s="90" t="inlineStr">
@@ -10400,7 +10403,7 @@
       </c>
       <c r="K45" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="L45" s="30" t="inlineStr">
@@ -10450,58 +10453,58 @@
         <v>7511325</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>0.8106499097150882</v>
+        <v>0.8193761921845464</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>54.39558251894007</v>
+        <v>54.62647043454713</v>
       </c>
       <c r="Z45" s="35" t="n">
         <v>90.62708045657493</v>
       </c>
       <c r="AA45" s="35" t="n">
-        <v>12.4119975912398</v>
+        <v>12.58109748040995</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-1.030566761264339</v>
+        <v>-0.7915374673961537</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-2.898428039929198</v>
+        <v>-2.590065791856142</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.867861278664859</v>
+        <v>1.798528324459988</v>
       </c>
       <c r="AE45" s="83" t="n">
-        <v>165.8204976925856</v>
+        <v>166.0239571546667</v>
       </c>
       <c r="AF45" s="83" t="n">
-        <v>164.9979676196453</v>
+        <v>165.0333455304389</v>
       </c>
       <c r="AG45" s="83" t="n">
-        <v>171.4101998901367</v>
+        <v>170.6113998413086</v>
       </c>
       <c r="AH45" s="83" t="n">
-        <v>182.3603002929688</v>
+        <v>182.7216003417969</v>
       </c>
       <c r="AI45" s="83" t="n">
-        <v>167.8967998504639</v>
+        <v>167.8452498626709</v>
       </c>
       <c r="AJ45" s="83" t="n">
-        <v>170.1339093397529</v>
+        <v>169.9575412829369</v>
       </c>
       <c r="AK45" s="83" t="n">
-        <v>163.2344993591309</v>
+        <v>163.5674995422363</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>156.3350893785088</v>
+        <v>157.1774578015357</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>0.9873972827840245</v>
+        <v>1.000192911958191</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>8.453372305131044</v>
+        <v>7.813339151828968</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>3.779735797022986</v>
+        <v>3.688788149914612</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -10516,13 +10519,13 @@
         <v>34.77851333080698</v>
       </c>
       <c r="AT45" s="33" t="n">
-        <v>0.05854515008847749</v>
+        <v>0.03811388618762712</v>
       </c>
       <c r="AU45" s="33" t="n">
-        <v>0.121330068621762</v>
+        <v>0.04481470847101532</v>
       </c>
       <c r="AV45" s="33" t="n">
-        <v>-0.2943032332743484</v>
+        <v>-0.3201871507212084</v>
       </c>
       <c r="AW45" s="33" t="n">
         <v>-0.006372384206043025</v>
@@ -10905,17 +10908,17 @@
       </c>
       <c r="AX47" s="90" t="inlineStr">
         <is>
+          <t>Data Centers Now Deliver a Third of Sandisk's Revenue -- $2.98 Billion in a Single Quarter</t>
+        </is>
+      </c>
+      <c r="AY47" s="90" t="inlineStr">
+        <is>
           <t>Sandisk Stock: Buy, Sell, or Hold?</t>
         </is>
       </c>
-      <c r="AY47" s="90" t="inlineStr">
+      <c r="AZ47" s="90" t="inlineStr">
         <is>
           <t>The Memory Crunch Is Bigger Than Expected. 1 Top Stock to Buy on the Dip (Hint: Not Micron or Sandisk)</t>
-        </is>
-      </c>
-      <c r="AZ47" s="90" t="inlineStr">
-        <is>
-          <t>Is Sandisk Stock Outperforming the Nasdaq?</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 2 Sep 2026, 10:41 PM · Yahoo Finance data</t>
+          <t>Built 2 Sep 2026, 11:18 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -12156,58 +12159,58 @@
         <v>9138900</v>
       </c>
       <c r="X7" s="74" t="n">
-        <v>1.511167699449779</v>
+        <v>1.539988490823412</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>30.42030144051444</v>
+        <v>29.96960284763098</v>
       </c>
       <c r="Z7" s="28" t="n">
-        <v>3.800795936325094</v>
+        <v>3.805784921238044</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>20.95965578633558</v>
+        <v>22.05304419537534</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>-1.562165395773604</v>
+        <v>-1.7110278554199</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>-0.3531936178809524</v>
+        <v>-0.5537967438521253</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-1.208971777892652</v>
+        <v>-1.157231111567774</v>
       </c>
       <c r="AE7" s="72" t="n">
-        <v>177.8136835681667</v>
+        <v>177.368996579213</v>
       </c>
       <c r="AF7" s="72" t="n">
-        <v>180.3785794776419</v>
+        <v>180.0326154085219</v>
       </c>
       <c r="AG7" s="72" t="n">
-        <v>181.6793997192383</v>
+        <v>181.5861996459961</v>
       </c>
       <c r="AH7" s="72" t="n">
-        <v>177.5732997131348</v>
+        <v>177.6227996826172</v>
       </c>
       <c r="AI7" s="72" t="n">
-        <v>170.2924997711182</v>
+        <v>170.4062497711182</v>
       </c>
       <c r="AJ7" s="72" t="n">
-        <v>190.3803877683187</v>
+        <v>190.0024964444434</v>
       </c>
       <c r="AK7" s="72" t="n">
-        <v>182.3714996337891</v>
+        <v>181.9084999084473</v>
       </c>
       <c r="AL7" s="72" t="n">
-        <v>174.3626114992594</v>
+        <v>173.8145033724511</v>
       </c>
       <c r="AM7" s="76" t="n">
-        <v>-0.1019252450712531</v>
+        <v>-0.06699457061100429</v>
       </c>
       <c r="AN7" s="29" t="n">
-        <v>8.783047954984051</v>
+        <v>8.898975627933584</v>
       </c>
       <c r="AO7" s="77" t="n">
-        <v>1.539090008511495</v>
+        <v>1.488627262004623</v>
       </c>
       <c r="AP7" s="72" t="n">
         <v>188.1900024414062</v>
@@ -12222,13 +12225,13 @@
         <v>62.33859789395273</v>
       </c>
       <c r="AT7" s="26" t="n">
-        <v>-0.03502795682939075</v>
+        <v>-0.03178250203436273</v>
       </c>
       <c r="AU7" s="26" t="n">
-        <v>-0.03953514654767343</v>
+        <v>-0.05694478994339525</v>
       </c>
       <c r="AV7" s="26" t="n">
-        <v>0.001914163820984971</v>
+        <v>-0.008381690644721718</v>
       </c>
       <c r="AW7" s="26" t="n">
         <v>0.1135250204014502</v>
@@ -12868,58 +12871,58 @@
         <v>9353100</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>1.060288302831335</v>
+        <v>1.100554389668337</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>48.9318172316673</v>
+        <v>48.94633859203591</v>
       </c>
       <c r="Z11" s="28" t="n">
-        <v>35.83809803113058</v>
+        <v>22.9167549696944</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>15.76101063524304</v>
+        <v>14.9702235353203</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.1865988883489678</v>
+        <v>0.1464442725417143</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.3005447210037976</v>
+        <v>0.2757090788078762</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.1139458326548298</v>
+        <v>-0.1292648062661618</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>85.61741899815361</v>
+        <v>85.55228582561726</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.5429222476041</v>
+        <v>85.52929049436101</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>84.90139999389649</v>
+        <v>84.96679992675782</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.26700012207031</v>
+        <v>84.28700012207031</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.16500022888184</v>
+        <v>83.20565021514892</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>86.98105359710452</v>
+        <v>86.98321531696089</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.57000007629395</v>
+        <v>85.57399978637696</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>84.15894655548338</v>
+        <v>84.16478425579302</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.3866095185000036</v>
+        <v>0.3850425008292723</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.298009862223858</v>
+        <v>3.293560039502272</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.395424253334772</v>
+        <v>1.351383848292627</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -12934,13 +12937,13 @@
         <v>67.35647006454938</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-0.02515719868514421</v>
+        <v>-0.01467864877879865</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>0.002351521940810342</v>
+        <v>0.004595797629547427</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.03925394695380402</v>
+        <v>0.04179393978269985</v>
       </c>
       <c r="AW11" s="26" t="n">
         <v>0.09745107704794687</v>
@@ -13046,58 +13049,58 @@
         <v>5883300</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>1.098058757985857</v>
+        <v>1.163132765932208</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>42.47758893926807</v>
+        <v>42.4920862965588</v>
       </c>
       <c r="Z12" s="35" t="n">
-        <v>5.399932861328125</v>
+        <v>5.555485785152509</v>
       </c>
       <c r="AA12" s="35" t="n">
-        <v>13.66989746612066</v>
+        <v>13.20986958843927</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.02922968977189555</v>
+        <v>0.002264023856156427</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.397090944492239</v>
+        <v>0.3560931618433134</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.3678612547203434</v>
+        <v>-0.3538291379871569</v>
       </c>
       <c r="AE12" s="83" t="n">
-        <v>116.5569834786755</v>
+        <v>116.5489016574929</v>
       </c>
       <c r="AF12" s="83" t="n">
-        <v>116.8383915256486</v>
+        <v>116.8458629433342</v>
       </c>
       <c r="AG12" s="83" t="n">
-        <v>116.1221997070313</v>
+        <v>116.1675996398926</v>
       </c>
       <c r="AH12" s="83" t="n">
-        <v>116.9156998443603</v>
+        <v>116.9603998565674</v>
       </c>
       <c r="AI12" s="83" t="n">
-        <v>116.9753499221802</v>
+        <v>116.966549911499</v>
       </c>
       <c r="AJ12" s="83" t="n">
-        <v>120.3158424554142</v>
+        <v>120.260447151783</v>
       </c>
       <c r="AK12" s="83" t="n">
-        <v>117.7604988098145</v>
+        <v>117.7064987182617</v>
       </c>
       <c r="AL12" s="83" t="n">
-        <v>115.2051551642147</v>
+        <v>115.1525502847405</v>
       </c>
       <c r="AM12" s="87" t="n">
-        <v>-0.1203671426704948</v>
+        <v>-0.1101341631385697</v>
       </c>
       <c r="AN12" s="36" t="n">
-        <v>4.339899493338025</v>
+        <v>4.339519841864104</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.453860177755761</v>
+        <v>1.436482313025812</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -13112,13 +13115,13 @@
         <v>47.42681150968475</v>
       </c>
       <c r="AT12" s="33" t="n">
-        <v>-0.03136100268944209</v>
+        <v>-0.02848665279598073</v>
       </c>
       <c r="AU12" s="33" t="n">
-        <v>-0.01292100996914591</v>
+        <v>-0.03062349018372956</v>
       </c>
       <c r="AV12" s="33" t="n">
-        <v>-0.03045948074415483</v>
+        <v>-0.02551237429568076</v>
       </c>
       <c r="AW12" s="33" t="n">
         <v>-0.04036518864749195</v>
@@ -13224,58 +13227,58 @@
         <v>5152000</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>1.239516319175452</v>
+        <v>1.265665745832601</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>48.88880247143053</v>
+        <v>48.61344868347395</v>
       </c>
       <c r="Z13" s="28" t="n">
-        <v>23.9951231388846</v>
+        <v>16.7999267578125</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>11.83810281460942</v>
+        <v>12.43975931717117</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.3565484873495421</v>
+        <v>0.3863393428060533</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.410945273242301</v>
+        <v>0.4441268313019384</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>-0.05439678589275887</v>
+        <v>-0.05778748849588505</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>111.5730122285287</v>
+        <v>111.7249349790308</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.2670251154313</v>
+        <v>111.3947258727882</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.0963996887207</v>
+        <v>110.2189996337891</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.6250998687744</v>
+        <v>112.6122998809814</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0089500045776</v>
+        <v>114.0061999893188</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.1535579924061</v>
+        <v>113.3095009115325</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.5385002136231</v>
+        <v>111.5860000610352</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.92344243484</v>
+        <v>109.8624992105378</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.2961364079800141</v>
+        <v>0.2951835047213828</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>2.895964668145748</v>
+        <v>3.089098721263724</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.452338817113611</v>
+        <v>1.502083376291115</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -13290,13 +13293,13 @@
         <v>38.04877056338923</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>-0.01282053459151322</v>
+        <v>-0.02032163850111446</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>0.02439023874493351</v>
+        <v>-0.004131481045469676</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>-0.04091344461518909</v>
+        <v>-0.02368585408677115</v>
       </c>
       <c r="AW13" s="26" t="n">
         <v>-0.05810400863368514</v>
@@ -13402,58 +13405,58 @@
         <v>15500500</v>
       </c>
       <c r="X14" s="85" t="n">
-        <v>1.436788667718115</v>
+        <v>1.458983187408346</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>47.03073809436141</v>
+        <v>46.41206241272101</v>
       </c>
       <c r="Z14" s="35" t="n">
         <v>13.11474897245443</v>
       </c>
       <c r="AA14" s="35" t="n">
-        <v>13.16409788156925</v>
+        <v>14.25051466025261</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.3594542334584645</v>
+        <v>0.336000387695762</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.4357281368324782</v>
+        <v>0.4335279902866629</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>-0.07627390337401374</v>
+        <v>-0.09752760259090087</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>52.83955983386065</v>
+        <v>52.84157806072392</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.56374464823632</v>
+        <v>52.60691287587805</v>
       </c>
       <c r="AG14" s="83" t="n">
-        <v>51.70879981994629</v>
+        <v>51.73999984741211</v>
       </c>
       <c r="AH14" s="83" t="n">
-        <v>51.53879997253418</v>
+        <v>51.55389999389649</v>
       </c>
       <c r="AI14" s="83" t="n">
-        <v>49.88464998245239</v>
+        <v>49.93017498016357</v>
       </c>
       <c r="AJ14" s="83" t="n">
-        <v>53.88400966406964</v>
+        <v>53.90486504791999</v>
       </c>
       <c r="AK14" s="83" t="n">
-        <v>52.74200019836426</v>
+        <v>52.80100021362305</v>
       </c>
       <c r="AL14" s="83" t="n">
-        <v>51.59999073265887</v>
+        <v>51.69713537932611</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.2057815527277763</v>
+        <v>0.1688903858123138</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>4.330550458497035</v>
+        <v>4.181226983696938</v>
       </c>
       <c r="AO14" s="88" t="n">
-        <v>1.533247239442797</v>
+        <v>1.550122147884535</v>
       </c>
       <c r="AP14" s="83" t="n">
         <v>54.18999862670898</v>
@@ -13471,10 +13474,10 @@
         <v>-0.02818219642828157</v>
       </c>
       <c r="AU14" s="33" t="n">
-        <v>0.03252031290351032</v>
+        <v>0.02078026677455402</v>
       </c>
       <c r="AV14" s="33" t="n">
-        <v>0.02258447696842736</v>
+        <v>0.01067545093504885</v>
       </c>
       <c r="AW14" s="33" t="n">
         <v>0.1481808477796946</v>
@@ -13580,58 +13583,58 @@
         <v>7648700</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>1.170948499361993</v>
+        <v>1.239202725089209</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>49.77037300465658</v>
+        <v>49.55853776648325</v>
       </c>
       <c r="Z15" s="28" t="n">
         <v>37.27760862895041</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>12.89589537992149</v>
+        <v>12.2697100887299</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.7651872183634794</v>
+        <v>0.7694094258643247</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>0.9757095145848074</v>
+        <v>0.9547003710631453</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.210522296221328</v>
+        <v>-0.1852909451988206</v>
       </c>
       <c r="AE15" s="72" t="n">
-        <v>184.6874146564698</v>
+        <v>184.8400882407456</v>
       </c>
       <c r="AF15" s="72" t="n">
-        <v>184.1353130869622</v>
+        <v>184.265791940384</v>
       </c>
       <c r="AG15" s="72" t="n">
-        <v>182.6356005859375</v>
+        <v>182.5064007568359</v>
       </c>
       <c r="AH15" s="72" t="n">
-        <v>177.3750009155274</v>
+        <v>177.8112008666992</v>
       </c>
       <c r="AI15" s="72" t="n">
-        <v>159.5231751251221</v>
+        <v>159.7168251037598</v>
       </c>
       <c r="AJ15" s="72" t="n">
-        <v>191.6757393950913</v>
+        <v>191.5964835730046</v>
       </c>
       <c r="AK15" s="72" t="n">
-        <v>185.8765007019043</v>
+        <v>185.8160011291504</v>
       </c>
       <c r="AL15" s="72" t="n">
-        <v>180.0772620087173</v>
+        <v>180.0355186852961</v>
       </c>
       <c r="AM15" s="76" t="n">
-        <v>0.307172852284619</v>
+        <v>0.311780265692577</v>
       </c>
       <c r="AN15" s="29" t="n">
-        <v>6.239883655317391</v>
+        <v>6.221727309519014</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.239163245725061</v>
+        <v>2.133754647852423</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -13646,13 +13649,13 @@
         <v>79.05621471669531</v>
       </c>
       <c r="AT15" s="26" t="n">
-        <v>0.01993888518212716</v>
+        <v>0.0104544615332689</v>
       </c>
       <c r="AU15" s="26" t="n">
-        <v>0.04727683488781254</v>
+        <v>0.03145364139907425</v>
       </c>
       <c r="AV15" s="26" t="n">
-        <v>-0.06191252276912107</v>
+        <v>-0.07350793012812806</v>
       </c>
       <c r="AW15" s="26" t="n">
         <v>0.2755435009556748</v>
@@ -13936,58 +13939,58 @@
         <v>30615800</v>
       </c>
       <c r="X17" s="74" t="n">
-        <v>1.495374667896539</v>
+        <v>1.519162708420427</v>
       </c>
       <c r="Y17" s="28" t="n">
-        <v>36.70361122725726</v>
+        <v>36.76234205862237</v>
       </c>
       <c r="Z17" s="28" t="n">
         <v>25.08962484720707</v>
       </c>
       <c r="AA17" s="28" t="n">
-        <v>15.44436840277224</v>
+        <v>16.2087376392035</v>
       </c>
       <c r="AB17" s="75" t="n">
-        <v>-0.5137436051498128</v>
+        <v>-0.5275494543014574</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.4248456379828316</v>
+        <v>-0.4395657445903355</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.08889796716698117</v>
+        <v>-0.0879837097111219</v>
       </c>
       <c r="AE17" s="72" t="n">
-        <v>43.0407122898136</v>
+        <v>42.94406565169351</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>43.6067897005119</v>
+        <v>43.52191998675551</v>
       </c>
       <c r="AG17" s="72" t="n">
-        <v>44.63340019226074</v>
+        <v>44.59360015869141</v>
       </c>
       <c r="AH17" s="72" t="n">
-        <v>44.89349990844727</v>
+        <v>44.84929988861084</v>
       </c>
       <c r="AI17" s="72" t="n">
-        <v>44.6977749633789</v>
+        <v>44.68662496566773</v>
       </c>
       <c r="AJ17" s="72" t="n">
-        <v>44.61508083450245</v>
+        <v>44.56352224345727</v>
       </c>
       <c r="AK17" s="72" t="n">
-        <v>43.5240005493164</v>
+        <v>43.45500049591065</v>
       </c>
       <c r="AL17" s="72" t="n">
-        <v>42.43292026413036</v>
+        <v>42.34647874836402</v>
       </c>
       <c r="AM17" s="76" t="n">
-        <v>0.05823636944323803</v>
+        <v>0.09630962378481163</v>
       </c>
       <c r="AN17" s="29" t="n">
-        <v>5.0136948415381</v>
+        <v>5.101929512811503</v>
       </c>
       <c r="AO17" s="77" t="n">
-        <v>1.59001826557555</v>
+        <v>1.545906558525494</v>
       </c>
       <c r="AP17" s="72" t="n">
         <v>47.79999923706055</v>
@@ -14002,13 +14005,13 @@
         <v>21.2030125219632</v>
       </c>
       <c r="AT17" s="26" t="n">
-        <v>-0.01527070404375552</v>
+        <v>-0.0173170163061348</v>
       </c>
       <c r="AU17" s="26" t="n">
-        <v>-0.04036070264747738</v>
+        <v>-0.04057707872620075</v>
       </c>
       <c r="AV17" s="26" t="n">
-        <v>-0.01252893549762679</v>
+        <v>-0.03052392041029806</v>
       </c>
       <c r="AW17" s="26" t="n">
         <v>-0.00304514541109957</v>
@@ -14485,58 +14488,58 @@
         <v>22801600</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>1.358906395500428</v>
+        <v>1.365821224750179</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>38.37419555412637</v>
+        <v>37.92677930233195</v>
       </c>
       <c r="Z21" s="28" t="n">
         <v>3.944815520033066</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>17.69365844532797</v>
+        <v>18.49256040451482</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>-0.1813943103584279</v>
+        <v>-0.4331170541788651</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>1.027797981449304</v>
+        <v>0.8150192352595598</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-1.209192291807732</v>
+        <v>-1.248136289438425</v>
       </c>
       <c r="AE21" s="72" t="n">
-        <v>296.6617753509157</v>
+        <v>296.1334522394553</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>297.9144728791328</v>
+        <v>297.6612187761644</v>
       </c>
       <c r="AG21" s="72" t="n">
-        <v>297.1768005371094</v>
+        <v>297.1282006835938</v>
       </c>
       <c r="AH21" s="72" t="n">
-        <v>289.2668008422851</v>
+        <v>289.6047009277344</v>
       </c>
       <c r="AI21" s="72" t="n">
-        <v>271.5293002319336</v>
+        <v>271.7898502349854</v>
       </c>
       <c r="AJ21" s="72" t="n">
-        <v>306.3822615727421</v>
+        <v>306.2656587244949</v>
       </c>
       <c r="AK21" s="72" t="n">
-        <v>299.881999206543</v>
+        <v>299.5839996337891</v>
       </c>
       <c r="AL21" s="72" t="n">
-        <v>293.3817368403438</v>
+        <v>292.9023405430832</v>
       </c>
       <c r="AM21" s="76" t="n">
-        <v>-0.2162781559976599</v>
+        <v>-0.1745324916463267</v>
       </c>
       <c r="AN21" s="29" t="n">
-        <v>4.335213439551667</v>
+        <v>4.460624798970247</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.219696319408194</v>
+        <v>1.158474359633289</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -14551,13 +14554,13 @@
         <v>80.84689881310302</v>
       </c>
       <c r="AT21" s="26" t="n">
-        <v>-0.02483469431878571</v>
+        <v>-0.02894095961018117</v>
       </c>
       <c r="AU21" s="26" t="n">
-        <v>-0.00216347821566909</v>
+        <v>-0.01907364078455576</v>
       </c>
       <c r="AV21" s="26" t="n">
-        <v>0.005502097991012533</v>
+        <v>-0.003737215676488104</v>
       </c>
       <c r="AW21" s="26" t="n">
         <v>0.1804111269151125</v>
@@ -15386,58 +15389,58 @@
         <v>4145000</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>0.8664098442552534</v>
+        <v>0.8807399490466973</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>53.6361945639654</v>
+        <v>53.11883078599014</v>
       </c>
       <c r="Z27" s="35" t="n">
         <v>45.86895528175718</v>
       </c>
       <c r="AA27" s="35" t="n">
-        <v>24.74561915002105</v>
+        <v>24.87642762391344</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.231843511365867</v>
+        <v>2.118236871714331</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>1.999838541378428</v>
+        <v>2.035635323558838</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.2320049699874389</v>
+        <v>0.08260154815549203</v>
       </c>
       <c r="AE27" s="83" t="n">
-        <v>84.5353451160023</v>
+        <v>84.51056293451254</v>
       </c>
       <c r="AF27" s="83" t="n">
-        <v>82.18829583584916</v>
+        <v>82.40151586195071</v>
       </c>
       <c r="AG27" s="83" t="n">
-        <v>79.09279968261718</v>
+        <v>79.21599960327148</v>
       </c>
       <c r="AH27" s="83" t="n">
-        <v>78.03229995727538</v>
+        <v>78.18899993896484</v>
       </c>
       <c r="AI27" s="83" t="n">
-        <v>76.77120008468628</v>
+        <v>76.78735006332397</v>
       </c>
       <c r="AJ27" s="83" t="n">
-        <v>88.66825938281181</v>
+        <v>88.69266065853544</v>
       </c>
       <c r="AK27" s="83" t="n">
-        <v>81.99949989318847</v>
+        <v>82.39099960327148</v>
       </c>
       <c r="AL27" s="83" t="n">
-        <v>75.33074040356513</v>
+        <v>76.08933854800752</v>
       </c>
       <c r="AM27" s="87" t="n">
-        <v>0.5810122137068737</v>
+        <v>0.5546683026697907</v>
       </c>
       <c r="AN27" s="36" t="n">
-        <v>16.26536624811123</v>
+        <v>15.29696468208342</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.986319148685328</v>
+        <v>2.917314032834978</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -15452,13 +15455,13 @@
         <v>67.78320449447206</v>
       </c>
       <c r="AT27" s="33" t="n">
-        <v>-0.01000948946876246</v>
+        <v>-0.03809193945704192</v>
       </c>
       <c r="AU27" s="33" t="n">
-        <v>0.1661988254116249</v>
+        <v>0.1297253303883636</v>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>0.02239723907185032</v>
+        <v>0.03966960359993599</v>
       </c>
       <c r="AW27" s="33" t="n">
         <v>0.08008325284381423</v>
@@ -15562,58 +15565,58 @@
         <v>2955000</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>0.7300920212430836</v>
+        <v>0.7887214171895894</v>
       </c>
       <c r="Y28" s="28" t="n">
-        <v>38.52933689785394</v>
+        <v>38.9337628788725</v>
       </c>
       <c r="Z28" s="28" t="n">
         <v>9.06256004501231</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>10.16349900617751</v>
+        <v>9.940110389550453</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-10.69840329886961</v>
+        <v>-10.79506874406277</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-10.08656173250177</v>
+        <v>-10.19515648070744</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-0.6118415663678398</v>
+        <v>-0.599912263355332</v>
       </c>
       <c r="AE28" s="72" t="n">
-        <v>246.2650557636435</v>
+        <v>244.5626711704651</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>256.7577340694023</v>
+        <v>255.1344693060406</v>
       </c>
       <c r="AG28" s="72" t="n">
-        <v>283.8249993896484</v>
+        <v>280.4515994262695</v>
       </c>
       <c r="AH28" s="72" t="n">
-        <v>274.1783494567871</v>
+        <v>275.0708995056152</v>
       </c>
       <c r="AI28" s="72" t="n">
-        <v>199.774974937439</v>
+        <v>200.2264749526977</v>
       </c>
       <c r="AJ28" s="72" t="n">
-        <v>293.8307394437642</v>
+        <v>291.8280848830508</v>
       </c>
       <c r="AK28" s="72" t="n">
-        <v>261.1299995422363</v>
+        <v>259.0544998168945</v>
       </c>
       <c r="AL28" s="72" t="n">
-        <v>228.4292596407084</v>
+        <v>226.2809147507382</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.09771564348016051</v>
+        <v>0.1302740081111605</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>25.0455634809119</v>
+        <v>25.30246345021713</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>7.822392621976077</v>
+        <v>7.434546618854288</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -15628,13 +15631,13 @@
         <v>38.22161867198396</v>
       </c>
       <c r="AT28" s="26" t="n">
-        <v>-0.01658426784204114</v>
+        <v>-0.02790193037959487</v>
       </c>
       <c r="AU28" s="26" t="n">
-        <v>-0.02031789005625295</v>
+        <v>-0.01773609251935082</v>
       </c>
       <c r="AV28" s="26" t="n">
-        <v>-0.4256573221995616</v>
+        <v>-0.4169004685586186</v>
       </c>
       <c r="AW28" s="26" t="n">
         <v>1.148202475243378</v>
@@ -16020,7 +16023,7 @@
       </c>
       <c r="G31" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" s="30" t="inlineStr">
@@ -16054,11 +16057,11 @@
         </is>
       </c>
       <c r="N31" s="80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" s="30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Very Weak</t>
         </is>
       </c>
       <c r="P31" s="32" t="inlineStr">
@@ -16090,58 +16093,58 @@
         <v>2210500</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>0.8072600451013868</v>
+        <v>0.8044090568344747</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>46.90485088138379</v>
+        <v>46.51784464542615</v>
       </c>
       <c r="Z31" s="35" t="n">
         <v>13.32954532176966</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>18.41821041137974</v>
+        <v>17.7806217290446</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>2.002343329639928</v>
+        <v>1.746196310685875</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.903014257259686</v>
+        <v>1.928641114451038</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>0.09932907238024158</v>
+        <v>-0.1824448037651636</v>
       </c>
       <c r="AE31" s="83" t="n">
-        <v>100.8398168790675</v>
+        <v>100.4222174437594</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>98.75806693210856</v>
+        <v>98.83149605284392</v>
       </c>
       <c r="AG31" s="83" t="n">
-        <v>95.96300003051758</v>
+        <v>95.82180007934571</v>
       </c>
       <c r="AH31" s="83" t="n">
-        <v>104.5354998016357</v>
+        <v>104.3801998138428</v>
       </c>
       <c r="AI31" s="83" t="n">
-        <v>105.1118497848511</v>
+        <v>105.1490497970581</v>
       </c>
       <c r="AJ31" s="83" t="n">
-        <v>107.0492177214587</v>
+        <v>106.9600214365982</v>
       </c>
       <c r="AK31" s="83" t="n">
-        <v>98.87799987792968</v>
+        <v>99.22400016784668</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>90.70678203440062</v>
+        <v>91.48797889909517</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.3398036992874659</v>
+        <v>0.3084287821448453</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>16.52787850404919</v>
+        <v>15.59304453693725</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>4.534801159407194</v>
+        <v>4.284333591617422</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -16156,13 +16159,13 @@
         <v>37.16957126350331</v>
       </c>
       <c r="AT31" s="33" t="n">
-        <v>-0.05876595975466281</v>
+        <v>-0.1000373694823218</v>
       </c>
       <c r="AU31" s="33" t="n">
-        <v>0.1143783884806915</v>
+        <v>0.07289345548981352</v>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>-0.1450394771543706</v>
+        <v>-0.2012281102823864</v>
       </c>
       <c r="AW31" s="33" t="n">
         <v>0.05213689347291894</v>
@@ -18554,58 +18557,58 @@
         <v>8900900</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>0.9168798540145233</v>
+        <v>0.9593714919790102</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>50.88260328192964</v>
+        <v>51.00490620595838</v>
       </c>
       <c r="Z45" s="35" t="n">
         <v>68.51484231083393</v>
       </c>
       <c r="AA45" s="35" t="n">
-        <v>12.17585872366302</v>
+        <v>12.10331854086442</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-1.629804958922534</v>
+        <v>-1.352837224149567</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-3.365393359595412</v>
+        <v>-3.039697872971139</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.735588400672877</v>
+        <v>1.686860648821571</v>
       </c>
       <c r="AE45" s="83" t="n">
-        <v>164.6377808293622</v>
+        <v>164.8993715663237</v>
       </c>
       <c r="AF45" s="83" t="n">
-        <v>164.5017637102231</v>
+        <v>164.540679412096</v>
       </c>
       <c r="AG45" s="83" t="n">
-        <v>172.4489996337891</v>
+        <v>171.2947998046875</v>
       </c>
       <c r="AH45" s="83" t="n">
-        <v>181.9382002258301</v>
+        <v>182.3026002502442</v>
       </c>
       <c r="AI45" s="83" t="n">
-        <v>167.9303498077392</v>
+        <v>167.8679498291016</v>
       </c>
       <c r="AJ45" s="83" t="n">
-        <v>169.0415188676768</v>
+        <v>169.1431788250064</v>
       </c>
       <c r="AK45" s="83" t="n">
-        <v>162.8699989318848</v>
+        <v>162.9459991455078</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>156.6984789960927</v>
+        <v>156.7488194660093</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>0.8030049094370144</v>
+        <v>0.7956184631022526</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>7.578461320397125</v>
+        <v>7.606421405860468</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>3.897473344923669</v>
+        <v>3.797560385044389</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -18620,13 +18623,13 @@
         <v>32.34974096402502</v>
       </c>
       <c r="AT45" s="33" t="n">
-        <v>0.05096828293239031</v>
+        <v>0.03768063741748606</v>
       </c>
       <c r="AU45" s="33" t="n">
-        <v>0.1287175660282978</v>
+        <v>0.0992280303448243</v>
       </c>
       <c r="AV45" s="33" t="n">
-        <v>-0.2724136573055574</v>
+        <v>-0.3082129083883427</v>
       </c>
       <c r="AW45" s="33" t="n">
         <v>-0.02595733623028795</v>
@@ -19576,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 2 Sep 2026, 10:41 PM · Yahoo Finance data</t>
+          <t>Built 2 Sep 2026, 11:18 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19601,22 +19604,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>18 of 40</t>
+          <t>19 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>22 of 40</t>
+          <t>21 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.4 / 9</t>
+          <t>4.3 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>16 of 40</t>
+          <t>15 of 40</t>
         </is>
       </c>
     </row>
@@ -20005,10 +20008,10 @@
         </is>
       </c>
       <c r="C7" s="26" t="n">
-        <v>-0.02052571647822032</v>
+        <v>-0.01134692623778677</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
@@ -20017,7 +20020,7 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -20056,11 +20059,11 @@
         </is>
       </c>
       <c r="N7" s="69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Very Weak</t>
         </is>
       </c>
       <c r="P7" s="25" t="inlineStr">
@@ -20077,7 +20080,7 @@
         <v>175.1300048828125</v>
       </c>
       <c r="S7" s="71" t="n">
-        <v>-3.669998168945312</v>
+        <v>-2.009994506835938</v>
       </c>
       <c r="T7" s="72" t="n">
         <v>176.0899963378906</v>
@@ -20092,58 +20095,58 @@
         <v>7362100</v>
       </c>
       <c r="X7" s="74" t="n">
-        <v>1.22064287644682</v>
+        <v>1.22653627329296</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>34.17917919934816</v>
+        <v>33.92838825265433</v>
       </c>
       <c r="Z7" s="28" t="n">
         <v>3.154644360930304</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>18.81409179122884</v>
+        <v>19.92227020763802</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>-1.04110794905759</v>
+        <v>-1.246915289882395</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>-0.0509506734077893</v>
+        <v>-0.2644889659601817</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-0.9901572756498007</v>
+        <v>-0.9824263239222133</v>
       </c>
       <c r="AE7" s="72" t="n">
-        <v>179.2661658083461</v>
+        <v>178.6944253939769</v>
       </c>
       <c r="AF7" s="72" t="n">
-        <v>181.1434378526523</v>
+        <v>180.7628773766202</v>
       </c>
       <c r="AG7" s="72" t="n">
-        <v>181.8429998779297</v>
+        <v>181.7675997924805</v>
       </c>
       <c r="AH7" s="72" t="n">
-        <v>177.5503997802734</v>
+        <v>177.6173997497559</v>
       </c>
       <c r="AI7" s="72" t="n">
-        <v>170.2000498199463</v>
+        <v>170.3145497894287</v>
       </c>
       <c r="AJ7" s="72" t="n">
-        <v>189.5703547988331</v>
+        <v>189.7215024134614</v>
       </c>
       <c r="AK7" s="72" t="n">
-        <v>182.8930000305176</v>
+        <v>182.5919998168945</v>
       </c>
       <c r="AL7" s="72" t="n">
-        <v>176.215645262202</v>
+        <v>175.4624972203277</v>
       </c>
       <c r="AM7" s="76" t="n">
-        <v>-0.08129269876006585</v>
+        <v>-0.02331805992155048</v>
       </c>
       <c r="AN7" s="29" t="n">
-        <v>7.301924914787736</v>
+        <v>7.809216837228797</v>
       </c>
       <c r="AO7" s="77" t="n">
-        <v>1.490258752502163</v>
+        <v>1.436659001795164</v>
       </c>
       <c r="AP7" s="72" t="n">
         <v>188.1900024414062</v>
@@ -20158,13 +20161,13 @@
         <v>68.18514838567228</v>
       </c>
       <c r="AT7" s="26" t="n">
-        <v>-0.02840496597607489</v>
+        <v>-0.02162008445356145</v>
       </c>
       <c r="AU7" s="26" t="n">
-        <v>-0.01827453622955222</v>
+        <v>-0.02618989963850316</v>
       </c>
       <c r="AV7" s="26" t="n">
-        <v>0.01155201261245131</v>
+        <v>0.01583533110776858</v>
       </c>
       <c r="AW7" s="26" t="n">
         <v>0.1289969726372682</v>
@@ -20186,7 +20189,7 @@
         <v>-0.003622402212613562</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
@@ -20717,10 +20720,10 @@
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>-0.001175346403020305</v>
+        <v>-0.005500217765873949</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
@@ -20729,7 +20732,7 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -20749,7 +20752,7 @@
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
@@ -20768,7 +20771,7 @@
         </is>
       </c>
       <c r="N11" s="69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" s="23" t="inlineStr">
         <is>
@@ -20789,7 +20792,7 @@
         <v>84.98000335693359</v>
       </c>
       <c r="S11" s="71" t="n">
-        <v>-0.09999847412109375</v>
+        <v>-0.4699935913085938</v>
       </c>
       <c r="T11" s="72" t="n">
         <v>85.34999847412109</v>
@@ -20804,58 +20807,58 @@
         <v>7012600</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>0.7806306180947875</v>
+        <v>0.8066036460840454</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>47.47290145839173</v>
+        <v>47.48693481569663</v>
       </c>
       <c r="Z11" s="28" t="n">
         <v>28.03472477944208</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>15.92319707054252</v>
+        <v>15.16847015679679</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.2418924086119318</v>
+        <v>0.1940077921954639</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.329031179167505</v>
+        <v>0.3080252803744166</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.08713877055557318</v>
+        <v>-0.1140174881789527</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>85.72239585476893</v>
+        <v>85.63865320436504</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.57221447236451</v>
+        <v>85.55721954379712</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>84.86240005493164</v>
+        <v>84.90539993286133</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.24230010986328</v>
+        <v>84.26900009155274</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.12590023040771</v>
+        <v>83.16600021362305</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>86.98921164214956</v>
+        <v>86.98466080490893</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.55050010681153</v>
+        <v>85.57999992370605</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>84.1117885714735</v>
+        <v>84.17533904250318</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.3017334483441489</v>
+        <v>0.286426540810812</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.363420514296864</v>
+        <v>3.282684932122265</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.400726645825778</v>
+        <v>1.353147829686729</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -20870,13 +20873,13 @@
         <v>65.55408875565456</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-0.01174548821871158</v>
+        <v>-0.02824463896517315</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>-0.005732980657204401</v>
+        <v>-0.0008230416497647663</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.02496682672045547</v>
+        <v>0.03596250910077115</v>
       </c>
       <c r="AW11" s="26" t="n">
         <v>0.09397532213026283</v>
@@ -20895,19 +20898,19 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>0.006127020204530709</v>
+        <v>-0.005289674527982902</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G12" s="30" t="inlineStr">
@@ -20967,7 +20970,7 @@
         <v>116.5899963378906</v>
       </c>
       <c r="S12" s="82" t="n">
-        <v>0.7099990844726562</v>
+        <v>-0.6200027465820312</v>
       </c>
       <c r="T12" s="83" t="n">
         <v>116.5599975585938</v>
@@ -20982,58 +20985,58 @@
         <v>4912700</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>0.8826552062409492</v>
+        <v>0.9288479445644519</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>48.73504905390154</v>
+        <v>48.6875434606039</v>
       </c>
       <c r="Z12" s="35" t="n">
-        <v>18.79514439772846</v>
+        <v>22.22217391965883</v>
       </c>
       <c r="AA12" s="35" t="n">
-        <v>13.78987054065863</v>
+        <v>13.42405384927395</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.2573574278493851</v>
+        <v>0.2269600721638056</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.4890562581723248</v>
+        <v>0.4445504463401025</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.2316988303229398</v>
+        <v>-0.2175903741762969</v>
       </c>
       <c r="AE12" s="83" t="n">
-        <v>117.1189798046141</v>
+        <v>117.108588891665</v>
       </c>
       <c r="AF12" s="83" t="n">
-        <v>117.0632310444245</v>
+        <v>117.0714496038786</v>
       </c>
       <c r="AG12" s="83" t="n">
-        <v>116.1735998535156</v>
+        <v>116.1745997619629</v>
       </c>
       <c r="AH12" s="83" t="n">
-        <v>116.8779998779297</v>
+        <v>116.9418998718262</v>
       </c>
       <c r="AI12" s="83" t="n">
-        <v>117.0012749481201</v>
+        <v>116.9884499359131</v>
       </c>
       <c r="AJ12" s="83" t="n">
-        <v>120.0459537132867</v>
+        <v>120.0154880732483</v>
       </c>
       <c r="AK12" s="83" t="n">
-        <v>117.9414989471436</v>
+        <v>117.8914989471436</v>
       </c>
       <c r="AL12" s="83" t="n">
-        <v>115.8370441810004</v>
+        <v>115.7675098210388</v>
       </c>
       <c r="AM12" s="87" t="n">
-        <v>0.1788948303864417</v>
+        <v>0.1936183445440202</v>
       </c>
       <c r="AN12" s="36" t="n">
-        <v>3.568641716324644</v>
+        <v>3.603294800852466</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.389068897616946</v>
+        <v>1.370675307154388</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -21048,13 +21051,13 @@
         <v>57.51762902126261</v>
       </c>
       <c r="AT12" s="33" t="n">
-        <v>-0.01211659333884407</v>
+        <v>-0.01445483237324208</v>
       </c>
       <c r="AU12" s="33" t="n">
-        <v>0.0373698458141376</v>
+        <v>0.004307003323048564</v>
       </c>
       <c r="AV12" s="33" t="n">
-        <v>-0.03540999678526469</v>
+        <v>-0.01353757568715541</v>
       </c>
       <c r="AW12" s="33" t="n">
         <v>-0.02361617316584663</v>
@@ -21073,36 +21076,36 @@
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>0.0004487516445552675</v>
+        <v>-0.0135410107816939</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
           <t>Same</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -21120,11 +21123,11 @@
       </c>
       <c r="M13" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N13" s="69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13" s="23" t="inlineStr">
         <is>
@@ -21145,7 +21148,7 @@
         <v>111.4599990844727</v>
       </c>
       <c r="S13" s="71" t="n">
-        <v>0.04999542236328125</v>
+        <v>-1.529998779296875</v>
       </c>
       <c r="T13" s="72" t="n">
         <v>112.4800033569336</v>
@@ -21160,58 +21163,58 @@
         <v>3317200</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>0.773537607704595</v>
+        <v>0.8118383714285364</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>51.19732185915565</v>
+        <v>50.60670939628083</v>
       </c>
       <c r="Z13" s="28" t="n">
         <v>38.12426703044879</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>12.37838648315917</v>
+        <v>12.94289846133665</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.4500206222888323</v>
+        <v>0.4970496905289821</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.4245444697154907</v>
+        <v>0.4585737034259096</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>0.02547615257334163</v>
+        <v>0.03847598710307248</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>111.7710165071318</v>
+        <v>111.9663457577774</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.3057279016326</v>
+        <v>111.4461987347252</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.0677996826172</v>
+        <v>110.1385997009277</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.6543998718262</v>
+        <v>112.6461998748779</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0255500030518</v>
+        <v>114.0195000076294</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.1512961186677</v>
+        <v>113.3465085287042</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.5615001678467</v>
+        <v>111.6440002441406</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.9717042170256</v>
+        <v>109.9414919595771</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.4680773235956488</v>
+        <v>0.4459617432301825</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>2.850079908264389</v>
+        <v>3.049887644370549</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.464819793708611</v>
+        <v>1.518112090927286</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -21226,13 +21229,13 @@
         <v>41.82114019626525</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>0.0005385777178810169</v>
+        <v>-0.007656700611540224</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>0.04578717554493483</v>
+        <v>0.02974871844284221</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>-0.03656325756476642</v>
+        <v>-0.03589656175044875</v>
       </c>
       <c r="AW13" s="26" t="n">
         <v>-0.05317704783653654</v>
@@ -21251,7 +21254,7 @@
         </is>
       </c>
       <c r="C14" s="33" t="n">
-        <v>-0.01014467255628793</v>
+        <v>-0.00921402173100605</v>
       </c>
       <c r="D14" s="34" t="n">
         <v>8</v>
@@ -21263,12 +21266,12 @@
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" s="30" t="inlineStr">
@@ -21278,7 +21281,7 @@
       </c>
       <c r="I14" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="J14" s="30" t="inlineStr">
@@ -21298,15 +21301,15 @@
       </c>
       <c r="M14" s="30" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N14" s="80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O14" s="30" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="P14" s="32" t="inlineStr">
@@ -21323,7 +21326,7 @@
         <v>52.68999862670898</v>
       </c>
       <c r="S14" s="82" t="n">
-        <v>-0.5400009155273438</v>
+        <v>-0.4900016784667969</v>
       </c>
       <c r="T14" s="83" t="n">
         <v>53.15999984741211</v>
@@ -21338,58 +21341,58 @@
         <v>12112700</v>
       </c>
       <c r="X14" s="85" t="n">
-        <v>1.14147292574588</v>
+        <v>1.132770160637951</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>52.25313881276035</v>
+        <v>51.92762795972261</v>
       </c>
       <c r="Z14" s="35" t="n">
         <v>38.52455556406741</v>
       </c>
       <c r="AA14" s="35" t="n">
-        <v>13.92171663730387</v>
+        <v>15.01491119983173</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.4620725218886221</v>
+        <v>0.4390922415815268</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.4547966126759816</v>
+        <v>0.4579098909343881</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>0.007275909212640486</v>
+        <v>-0.01881764935286123</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>53.05943415929963</v>
+        <v>53.06202902240955</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.61311914357753</v>
+        <v>52.66060419398343</v>
       </c>
       <c r="AG14" s="83" t="n">
-        <v>51.70359985351563</v>
+        <v>51.73099983215332</v>
       </c>
       <c r="AH14" s="83" t="n">
-        <v>51.53559997558594</v>
+        <v>51.5498999786377</v>
       </c>
       <c r="AI14" s="83" t="n">
-        <v>49.84312498092651</v>
+        <v>49.89019998550415</v>
       </c>
       <c r="AJ14" s="83" t="n">
-        <v>54.03160906589987</v>
+        <v>53.91101560352768</v>
       </c>
       <c r="AK14" s="83" t="n">
-        <v>52.68900012969971</v>
+        <v>52.79750022888184</v>
       </c>
       <c r="AL14" s="83" t="n">
-        <v>51.34639119349954</v>
+        <v>51.68398485423599</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.5003718495320399</v>
+        <v>0.4517287301906163</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>5.096353822980838</v>
+        <v>4.218060968108926</v>
       </c>
       <c r="AO14" s="88" t="n">
-        <v>1.533945686013897</v>
+        <v>1.551904824376719</v>
       </c>
       <c r="AP14" s="83" t="n">
         <v>54.18999862670898</v>
@@ -21404,13 +21407,13 @@
         <v>87.65939818476255</v>
       </c>
       <c r="AT14" s="33" t="n">
-        <v>-0.01587602305348201</v>
+        <v>-0.01661073486245879</v>
       </c>
       <c r="AU14" s="33" t="n">
-        <v>0.02033306060168205</v>
+        <v>0.04481456093311298</v>
       </c>
       <c r="AV14" s="33" t="n">
-        <v>0.03010746930380703</v>
+        <v>0.0347604187237216</v>
       </c>
       <c r="AW14" s="33" t="n">
         <v>0.1618522690089272</v>
@@ -21429,14 +21432,14 @@
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>-0.01118710886762897</v>
+        <v>0.004362095686057943</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -21480,7 +21483,7 @@
         </is>
       </c>
       <c r="N15" s="69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O15" s="23" t="inlineStr">
         <is>
@@ -21501,7 +21504,7 @@
         <v>186.5</v>
       </c>
       <c r="S15" s="71" t="n">
-        <v>-2.110000610351562</v>
+        <v>0.80999755859375</v>
       </c>
       <c r="T15" s="72" t="n">
         <v>185.7799987792969</v>
@@ -21516,58 +21519,58 @@
         <v>4874800</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>0.736731859406147</v>
+        <v>0.7540725455285144</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>54.26111161887398</v>
+        <v>54.14795211299604</v>
       </c>
       <c r="Z15" s="28" t="n">
         <v>59.39672874035261</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>13.36314976897932</v>
+        <v>12.63520409915696</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.9252752490141916</v>
+        <v>0.9434473341411547</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>1.028340088640139</v>
+        <v>1.00102310736285</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.1030648396259477</v>
+        <v>-0.05757577322169571</v>
       </c>
       <c r="AE15" s="72" t="n">
-        <v>184.9866761612759</v>
+        <v>185.1829707696305</v>
       </c>
       <c r="AF15" s="72" t="n">
-        <v>184.1848444566936</v>
+        <v>184.3283711954575</v>
       </c>
       <c r="AG15" s="72" t="n">
-        <v>182.7916006469727</v>
+        <v>182.6766006469726</v>
       </c>
       <c r="AH15" s="72" t="n">
-        <v>176.9555009460449</v>
+        <v>177.3955009460449</v>
       </c>
       <c r="AI15" s="72" t="n">
-        <v>159.3375001525879</v>
+        <v>159.5334251403809</v>
       </c>
       <c r="AJ15" s="72" t="n">
-        <v>192.2747749349986</v>
+        <v>191.6882663932217</v>
       </c>
       <c r="AK15" s="72" t="n">
-        <v>185.5965003967285</v>
+        <v>185.9790008544922</v>
       </c>
       <c r="AL15" s="72" t="n">
-        <v>178.9182258584584</v>
+        <v>180.2697353157627</v>
       </c>
       <c r="AM15" s="76" t="n">
-        <v>0.5676446886163441</v>
+        <v>0.5456275104016038</v>
       </c>
       <c r="AN15" s="29" t="n">
-        <v>7.196552223770107</v>
+        <v>6.139688365350884</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.214807014797722</v>
+        <v>2.103030859761249</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -21582,13 +21585,13 @@
         <v>83.02568146486927</v>
       </c>
       <c r="AT15" s="26" t="n">
-        <v>0.017402228377569</v>
+        <v>0.03582336483708937</v>
       </c>
       <c r="AU15" s="26" t="n">
-        <v>0.0612872277602472</v>
+        <v>0.06358707447037171</v>
       </c>
       <c r="AV15" s="26" t="n">
-        <v>-0.02366246556048568</v>
+        <v>-0.04730279304596419</v>
       </c>
       <c r="AW15" s="26" t="n">
         <v>0.2954087547314752</v>
@@ -21785,10 +21788,10 @@
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>-0.02200094386811713</v>
+        <v>-0.01170138088828609</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
@@ -21857,7 +21860,7 @@
         <v>42.22999954223633</v>
       </c>
       <c r="S17" s="71" t="n">
-        <v>-0.9500007629394531</v>
+        <v>-0.5</v>
       </c>
       <c r="T17" s="72" t="n">
         <v>42</v>
@@ -21872,58 +21875,58 @@
         <v>31622300</v>
       </c>
       <c r="X17" s="74" t="n">
-        <v>1.562636433514582</v>
+        <v>1.584212134723384</v>
       </c>
       <c r="Y17" s="28" t="n">
-        <v>32.20915042159244</v>
+        <v>31.96352183535305</v>
       </c>
       <c r="Z17" s="28" t="n">
         <v>13.26160611007654</v>
       </c>
       <c r="AA17" s="28" t="n">
-        <v>14.39624069073164</v>
+        <v>15.19564649696477</v>
       </c>
       <c r="AB17" s="75" t="n">
-        <v>-0.4848245975953986</v>
+        <v>-0.5092733329572638</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.4026211461910862</v>
+        <v>-0.417569817162555</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.0822034514043124</v>
+        <v>-0.09170351579470887</v>
       </c>
       <c r="AE17" s="72" t="n">
-        <v>43.1780582659629</v>
+        <v>43.05379830266564</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>43.71146853323398</v>
+        <v>43.61811184810197</v>
       </c>
       <c r="AG17" s="72" t="n">
-        <v>44.67740013122559</v>
+        <v>44.63680015563965</v>
       </c>
       <c r="AH17" s="72" t="n">
-        <v>44.93569988250732</v>
+        <v>44.89519989013672</v>
       </c>
       <c r="AI17" s="72" t="n">
-        <v>44.70924995422363</v>
+        <v>44.69862495422363</v>
       </c>
       <c r="AJ17" s="72" t="n">
-        <v>44.66850350041232</v>
+        <v>44.59570120669143</v>
       </c>
       <c r="AK17" s="72" t="n">
-        <v>43.61400051116944</v>
+        <v>43.53250045776367</v>
       </c>
       <c r="AL17" s="72" t="n">
-        <v>42.55949752192655</v>
+        <v>42.46929970883592</v>
       </c>
       <c r="AM17" s="76" t="n">
-        <v>-0.156233781720618</v>
+        <v>-0.1125376213480506</v>
       </c>
       <c r="AN17" s="29" t="n">
-        <v>4.835616897710765</v>
+        <v>4.884629817941653</v>
       </c>
       <c r="AO17" s="77" t="n">
-        <v>1.630988684420252</v>
+        <v>1.583112547037588</v>
       </c>
       <c r="AP17" s="72" t="n">
         <v>47.79999923706055</v>
@@ -21938,13 +21941,13 @@
         <v>16.24057726428174</v>
       </c>
       <c r="AT17" s="26" t="n">
-        <v>-0.01262569347083842</v>
+        <v>-0.02290610019678962</v>
       </c>
       <c r="AU17" s="26" t="n">
-        <v>-0.05441111315446168</v>
+        <v>-0.04780155591486246</v>
       </c>
       <c r="AV17" s="26" t="n">
-        <v>-0.04930208728013963</v>
+        <v>-0.0201855907815669</v>
       </c>
       <c r="AW17" s="26" t="n">
         <v>-0.01077533612720372</v>
@@ -22334,7 +22337,7 @@
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>-0.01961243764615728</v>
+        <v>-0.006153870918744753</v>
       </c>
       <c r="D21" s="27" t="n">
         <v>4</v>
@@ -22406,7 +22409,7 @@
         <v>293.9299926757812</v>
       </c>
       <c r="S21" s="71" t="n">
-        <v>-5.8800048828125</v>
+        <v>-1.82000732421875</v>
       </c>
       <c r="T21" s="72" t="n">
         <v>295.0899963378906</v>
@@ -22421,58 +22424,58 @@
         <v>20883400</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>1.243201603992837</v>
+        <v>1.258647650198726</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>42.73469720129305</v>
+        <v>42.54763745691413</v>
       </c>
       <c r="Z21" s="28" t="n">
         <v>9.78348918424833</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>15.69992067893879</v>
+        <v>16.47959107866174</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>0.5150209965044041</v>
+        <v>0.1987337049282019</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>1.330096054401237</v>
+        <v>1.127053307619166</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.8150750578968331</v>
+        <v>-0.9283196026909641</v>
       </c>
       <c r="AE21" s="72" t="n">
-        <v>298.4022805014006</v>
+        <v>297.723007929523</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>298.6489194346242</v>
+        <v>298.370339921359</v>
       </c>
       <c r="AG21" s="72" t="n">
-        <v>297.2772003173828</v>
+        <v>297.280400390625</v>
       </c>
       <c r="AH21" s="72" t="n">
-        <v>288.96580078125</v>
+        <v>289.318600769043</v>
       </c>
       <c r="AI21" s="72" t="n">
-        <v>271.2976502227783</v>
+        <v>271.5552001953125</v>
       </c>
       <c r="AJ21" s="72" t="n">
-        <v>305.3869115435745</v>
+        <v>305.4378972265099</v>
       </c>
       <c r="AK21" s="72" t="n">
-        <v>300.1644989013672</v>
+        <v>300.140998840332</v>
       </c>
       <c r="AL21" s="72" t="n">
-        <v>294.9420862591599</v>
+        <v>294.8441004541542</v>
       </c>
       <c r="AM21" s="76" t="n">
-        <v>-0.09689904386326761</v>
+        <v>-0.08628707894022007</v>
       </c>
       <c r="AN21" s="29" t="n">
-        <v>3.479700405159083</v>
+        <v>3.529606689285191</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.194868827155104</v>
+        <v>1.129691163083167</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -22487,13 +22490,13 @@
         <v>85.2517040114933</v>
       </c>
       <c r="AT21" s="26" t="n">
-        <v>-0.02010267686049028</v>
+        <v>-0.01355844054223931</v>
       </c>
       <c r="AU21" s="26" t="n">
-        <v>0.004579774956978255</v>
+        <v>0.00937493253540489</v>
       </c>
       <c r="AV21" s="26" t="n">
-        <v>0.01205109695370621</v>
+        <v>0.01712914908044394</v>
       </c>
       <c r="AW21" s="26" t="n">
         <v>0.1940607259627896</v>
@@ -22710,7 +22713,7 @@
         <v>-0.008914626195478559</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
@@ -22886,7 +22889,7 @@
         <v>0.01104002490802869</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -23062,7 +23065,7 @@
         <v>-0.02499719943397638</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
@@ -23235,19 +23238,19 @@
         </is>
       </c>
       <c r="C27" s="33" t="n">
-        <v>-0.02071409493576004</v>
+        <v>0.01158533395626371</v>
       </c>
       <c r="D27" s="34" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G27" s="30" t="inlineStr">
@@ -23307,7 +23310,7 @@
         <v>85.56999969482422</v>
       </c>
       <c r="S27" s="82" t="n">
-        <v>-1.80999755859375</v>
+        <v>0.9800033569335938</v>
       </c>
       <c r="T27" s="83" t="n">
         <v>83.83999633789062</v>
@@ -23322,58 +23325,58 @@
         <v>3100100</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>0.6417024852749554</v>
+        <v>0.6418512878537703</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>59.76137193386293</v>
+        <v>59.13045381552157</v>
       </c>
       <c r="Z27" s="35" t="n">
         <v>74.24499437902826</v>
       </c>
       <c r="AA27" s="35" t="n">
-        <v>25.25744420442534</v>
+        <v>25.45544121663947</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.481783084916216</v>
+        <v>2.370117011846517</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>1.941837298881568</v>
+        <v>2.014984936519965</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.5399457860346484</v>
+        <v>0.3551320753265519</v>
       </c>
       <c r="AE27" s="83" t="n">
-        <v>84.9511574831302</v>
+        <v>84.91929467835763</v>
       </c>
       <c r="AF27" s="83" t="n">
-        <v>82.0991252363286</v>
+        <v>82.3336672650403</v>
       </c>
       <c r="AG27" s="83" t="n">
-        <v>79.03499969482422</v>
+        <v>79.12299957275391</v>
       </c>
       <c r="AH27" s="83" t="n">
-        <v>77.90509994506836</v>
+        <v>78.04739990234376</v>
       </c>
       <c r="AI27" s="83" t="n">
-        <v>76.76605009078979</v>
+        <v>76.77875005722046</v>
       </c>
       <c r="AJ27" s="83" t="n">
-        <v>89.11469087891429</v>
+        <v>88.82468033503761</v>
       </c>
       <c r="AK27" s="83" t="n">
-        <v>81.52249984741211</v>
+        <v>82.07499961853027</v>
       </c>
       <c r="AL27" s="83" t="n">
-        <v>73.93030881590992</v>
+        <v>75.32531890202293</v>
       </c>
       <c r="AM27" s="87" t="n">
-        <v>0.7665567706751498</v>
+        <v>0.7589011408899986</v>
       </c>
       <c r="AN27" s="36" t="n">
-        <v>18.62600152280093</v>
+        <v>16.44759244076426</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.870746677021745</v>
+        <v>2.798595912103206</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -23388,13 +23391,13 @@
         <v>76.16562398709232</v>
       </c>
       <c r="AT27" s="33" t="n">
-        <v>-0.007423725744635901</v>
+        <v>0.01966160107102444</v>
       </c>
       <c r="AU27" s="33" t="n">
-        <v>0.1737996968964064</v>
+        <v>0.2011510704766948</v>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>0.04417331154836224</v>
+        <v>0.05303959445346984</v>
       </c>
       <c r="AW27" s="33" t="n">
         <v>0.1124545206940883</v>
@@ -23411,14 +23414,14 @@
         </is>
       </c>
       <c r="C28" s="26" t="n">
-        <v>-0.05211395596517232</v>
+        <v>0.0119640266632095</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
@@ -23462,11 +23465,11 @@
         </is>
       </c>
       <c r="N28" s="69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="P28" s="25" t="inlineStr">
@@ -23483,7 +23486,7 @@
         <v>241.9100036621094</v>
       </c>
       <c r="S28" s="71" t="n">
-        <v>-13.30000305175781</v>
+        <v>2.860000610351562</v>
       </c>
       <c r="T28" s="72" t="n">
         <v>238.8049926757812</v>
@@ -23498,58 +23501,58 @@
         <v>2149400</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>0.5115006740605096</v>
+        <v>0.5250853196463602</v>
       </c>
       <c r="Y28" s="28" t="n">
-        <v>40.87239625133375</v>
+        <v>41.36836395483869</v>
       </c>
       <c r="Z28" s="28" t="n">
         <v>15.14408055740155</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>10.93726953363565</v>
+        <v>10.67322913700918</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-10.03232074718645</v>
+        <v>-10.30896815323408</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-9.933601340909807</v>
+        <v>-10.04517841486861</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>-0.09871940627663989</v>
+        <v>-0.2637897383654675</v>
       </c>
       <c r="AE28" s="72" t="n">
-        <v>249.5350696034791</v>
+        <v>247.3462894122498</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>258.9515067439207</v>
+        <v>257.1659155042228</v>
       </c>
       <c r="AG28" s="72" t="n">
-        <v>287.9177990722656</v>
+        <v>283.9095993041992</v>
       </c>
       <c r="AH28" s="72" t="n">
-        <v>273.319249420166</v>
+        <v>274.2206494140625</v>
       </c>
       <c r="AI28" s="72" t="n">
-        <v>199.3495749282837</v>
+        <v>199.7961249160766</v>
       </c>
       <c r="AJ28" s="72" t="n">
-        <v>293.4065039518117</v>
+        <v>293.4073935523879</v>
       </c>
       <c r="AK28" s="72" t="n">
-        <v>261.3419990539551</v>
+        <v>261.3414993286133</v>
       </c>
       <c r="AL28" s="72" t="n">
-        <v>229.2774941560985</v>
+        <v>229.2756051048386</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.1969858812143288</v>
+        <v>0.1970068021353231</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>24.53834822870299</v>
+        <v>24.53945837622573</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>7.776242171358298</v>
+        <v>7.370803403981273</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -23564,13 +23567,13 @@
         <v>40.23193851575314</v>
       </c>
       <c r="AT28" s="26" t="n">
-        <v>-0.005794852949476459</v>
+        <v>0.01310832104369664</v>
       </c>
       <c r="AU28" s="26" t="n">
-        <v>0.001531880377003469</v>
+        <v>0.009261968367853868</v>
       </c>
       <c r="AV28" s="26" t="n">
-        <v>-0.3152650858753346</v>
+        <v>-0.4083160081918629</v>
       </c>
       <c r="AW28" s="26" t="n">
         <v>1.213063846538261</v>
@@ -23766,7 +23769,7 @@
         <v>0.004202900721427705</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
@@ -23939,10 +23942,10 @@
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>-0.07119345024419377</v>
+        <v>-0.01249874985801214</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -23951,7 +23954,7 @@
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -23986,15 +23989,15 @@
       </c>
       <c r="M31" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N31" s="80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O31" s="30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="P31" s="32" t="inlineStr">
@@ -24011,7 +24014,7 @@
         <v>98.76000213623047</v>
       </c>
       <c r="S31" s="82" t="n">
-        <v>-7.569999694824219</v>
+        <v>-1.25</v>
       </c>
       <c r="T31" s="83" t="n">
         <v>99.59999847412109</v>
@@ -24026,58 +24029,58 @@
         <v>3128400</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>1.128085114822434</v>
+        <v>1.10259948295824</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>50.64559111168269</v>
+        <v>50.50174829706862</v>
       </c>
       <c r="Z31" s="35" t="n">
         <v>27.50992189281716</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>19.4645964776505</v>
+        <v>18.7041232745334</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>2.57110225722883</v>
+        <v>2.278761540531065</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.878181989164625</v>
+        <v>1.974252315392329</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>0.6929202680642046</v>
+        <v>0.3045092251387356</v>
       </c>
       <c r="AE31" s="83" t="n">
-        <v>102.148335377021</v>
+        <v>101.6114218173391</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>99.00787341169638</v>
+        <v>99.08864544450526</v>
       </c>
       <c r="AG31" s="83" t="n">
-        <v>96.16759994506836</v>
+        <v>96.03800003051758</v>
       </c>
       <c r="AH31" s="83" t="n">
-        <v>104.7318997955322</v>
+        <v>104.5729998016357</v>
       </c>
       <c r="AI31" s="83" t="n">
-        <v>105.0931497573852</v>
+        <v>105.1305997848511</v>
       </c>
       <c r="AJ31" s="83" t="n">
-        <v>107.5922436831232</v>
+        <v>107.1595519801748</v>
       </c>
       <c r="AK31" s="83" t="n">
-        <v>98.55099983215332</v>
+        <v>99.06549987792968</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>89.50975598118343</v>
+        <v>90.97144777568455</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.5115582716008</v>
+        <v>0.4811282570312048</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>18.3483554025194</v>
+        <v>16.34080908534004</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>4.443000496321981</v>
+        <v>4.180094217506338</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -24092,13 +24095,13 @@
         <v>41.19922899346607</v>
       </c>
       <c r="AT31" s="33" t="n">
-        <v>-0.03658179613552681</v>
+        <v>-0.03432086263859191</v>
       </c>
       <c r="AU31" s="33" t="n">
-        <v>0.1193471424533201</v>
+        <v>0.1433202740964736</v>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>-0.1236911729324509</v>
+        <v>-0.122835017776849</v>
       </c>
       <c r="AW31" s="33" t="n">
         <v>0.0794622848640365</v>
@@ -24118,7 +24121,7 @@
         <v>0.007835640584247017</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -24294,7 +24297,7 @@
         <v>-0.0005040778398927026</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -24470,7 +24473,7 @@
         <v>-0.02178605084672747</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
@@ -24822,7 +24825,7 @@
         <v>0.0004470874592776841</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -24998,7 +25001,7 @@
         <v>-0.01215122854742678</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -25526,7 +25529,7 @@
         <v>-0.01367236567406971</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
@@ -25702,7 +25705,7 @@
         <v>-0.008198704832808712</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E41" s="30" t="inlineStr">
         <is>
@@ -25878,7 +25881,7 @@
         <v>-0.00685599359086031</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -26230,7 +26233,7 @@
         <v>0.0004831799877809129</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
@@ -26403,7 +26406,7 @@
         </is>
       </c>
       <c r="C45" s="33" t="n">
-        <v>0.03459155838371286</v>
+        <v>0.03830923437849076</v>
       </c>
       <c r="D45" s="34" t="n">
         <v>5</v>
@@ -26415,7 +26418,7 @@
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
@@ -26454,11 +26457,11 @@
         </is>
       </c>
       <c r="N45" s="80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O45" s="30" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Very Strong</t>
         </is>
       </c>
       <c r="P45" s="32" t="inlineStr">
@@ -26475,7 +26478,7 @@
         <v>170.4799957275391</v>
       </c>
       <c r="S45" s="82" t="n">
-        <v>5.699996948242188</v>
+        <v>6.289993286132812</v>
       </c>
       <c r="T45" s="83" t="n">
         <v>164.7899932861328</v>
@@ -26490,58 +26493,58 @@
         <v>12734600</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>1.280141699601068</v>
+        <v>1.31959638874137</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>55.46586429173728</v>
+        <v>55.780846199514</v>
       </c>
       <c r="Z45" s="35" t="n">
         <v>94.05934909973199</v>
       </c>
       <c r="AA45" s="35" t="n">
-        <v>12.49227043299314</v>
+        <v>12.1523068230342</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-2.029853019445795</v>
+        <v>-1.70849065987835</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-3.799290459763631</v>
+        <v>-3.461413035176531</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.769437440317836</v>
+        <v>1.752922375298181</v>
       </c>
       <c r="AE45" s="83" t="n">
-        <v>164.0742894633653</v>
+        <v>164.4106204108871</v>
       </c>
       <c r="AF45" s="83" t="n">
-        <v>164.2909400202102</v>
+        <v>164.3337472922705</v>
       </c>
       <c r="AG45" s="83" t="n">
-        <v>173.6389996337891</v>
+        <v>172.4005996704101</v>
       </c>
       <c r="AH45" s="83" t="n">
-        <v>181.5472002410889</v>
+        <v>181.9140002441406</v>
       </c>
       <c r="AI45" s="83" t="n">
-        <v>167.9671997833252</v>
+        <v>167.9182498168945</v>
       </c>
       <c r="AJ45" s="83" t="n">
-        <v>169.7708473578702</v>
+        <v>168.7139008456425</v>
       </c>
       <c r="AK45" s="83" t="n">
-        <v>162.1179992675781</v>
+        <v>162.7489990234375</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>154.465151177286</v>
+        <v>156.7840972012325</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>1.046332317151862</v>
+        <v>1.148040565841508</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>9.44108380915921</v>
+        <v>7.330185571643363</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>3.728844265518225</v>
+        <v>3.623688243548068</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -26556,13 +26559,13 @@
         <v>35.15550815064062</v>
       </c>
       <c r="AT45" s="33" t="n">
-        <v>0.06052874480584181</v>
+        <v>0.07538003557849504</v>
       </c>
       <c r="AU45" s="33" t="n">
-        <v>0.1245381851180916</v>
+        <v>0.1549352687664962</v>
       </c>
       <c r="AV45" s="33" t="n">
-        <v>-0.3208509567926806</v>
+        <v>-0.2555133777110271</v>
       </c>
       <c r="AW45" s="33" t="n">
         <v>-0.003332401719082556</v>
@@ -26582,7 +26585,7 @@
         <v>-0.007299289100143769</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -27512,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 2 Sep 2026, 10:41 PM · Yahoo Finance data</t>
+          <t>Built 2 Sep 2026, 11:18 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27537,22 +27540,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>14 of 40</t>
+          <t>12 of 40</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>26 of 40</t>
+          <t>28 of 40</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.5 / 9</t>
+          <t>4.2 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>18 of 40</t>
+          <t>16 of 40</t>
         </is>
       </c>
     </row>
@@ -27941,10 +27944,10 @@
         </is>
       </c>
       <c r="C7" s="26" t="n">
-        <v>-0.008539388474021248</v>
+        <v>-0.009284136654230668</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
@@ -27953,7 +27956,7 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -27992,11 +27995,11 @@
         </is>
       </c>
       <c r="N7" s="69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="P7" s="25" t="inlineStr">
@@ -28010,76 +28013,76 @@
         </is>
       </c>
       <c r="R7" s="70" t="n">
-        <v>178.8000030517578</v>
+        <v>177.1399993896484</v>
       </c>
       <c r="S7" s="71" t="n">
-        <v>-1.539993286132812</v>
+        <v>-1.660003662109375</v>
       </c>
       <c r="T7" s="72" t="n">
-        <v>180.4700012207031</v>
+        <v>179.4400024414062</v>
       </c>
       <c r="U7" s="72" t="n">
-        <v>180.4900054931641</v>
+        <v>179.5200042724609</v>
       </c>
       <c r="V7" s="72" t="n">
-        <v>178.1799926757812</v>
+        <v>176.6499938964844</v>
       </c>
       <c r="W7" s="73" t="n">
-        <v>5464700</v>
+        <v>8234400</v>
       </c>
       <c r="X7" s="74" t="n">
-        <v>0.9072247442739189</v>
+        <v>1.355469061859819</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>41.45211287326175</v>
+        <v>37.81271866245149</v>
       </c>
       <c r="Z7" s="28" t="n">
-        <v>6.918912320523648</v>
+        <v>4.553950264334173</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>17.13266720317049</v>
+        <v>18.2876238537092</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>-0.60527035179976</v>
+        <v>-0.8807665069167854</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>0.1965886455046609</v>
+        <v>-0.01888238497962835</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-0.8018589973044209</v>
+        <v>-0.861884121937157</v>
       </c>
       <c r="AE7" s="72" t="n">
-        <v>180.4479260727842</v>
+        <v>179.7128312543096</v>
       </c>
       <c r="AF7" s="72" t="n">
-        <v>181.7447811496363</v>
+        <v>181.326164626001</v>
       </c>
       <c r="AG7" s="72" t="n">
-        <v>181.9323999023437</v>
+        <v>181.8831997680664</v>
       </c>
       <c r="AH7" s="72" t="n">
-        <v>177.4418997192383</v>
+        <v>177.5704997253418</v>
       </c>
       <c r="AI7" s="72" t="n">
-        <v>170.0953997802734</v>
+        <v>170.2100997924805</v>
       </c>
       <c r="AJ7" s="72" t="n">
-        <v>188.974572993476</v>
+        <v>189.2475584751936</v>
       </c>
       <c r="AK7" s="72" t="n">
-        <v>183.1284996032715</v>
+        <v>182.9934997558594</v>
       </c>
       <c r="AL7" s="72" t="n">
-        <v>177.2824262130669</v>
+        <v>176.7394410365251</v>
       </c>
       <c r="AM7" s="76" t="n">
-        <v>0.1297945421993561</v>
+        <v>0.03202387210444745</v>
       </c>
       <c r="AN7" s="29" t="n">
-        <v>6.384668036782299</v>
+        <v>6.835279644007153</v>
       </c>
       <c r="AO7" s="77" t="n">
-        <v>1.396853178710199</v>
+        <v>1.42496114202849</v>
       </c>
       <c r="AP7" s="72" t="n">
         <v>188.1900024414062</v>
@@ -28088,22 +28091,22 @@
         <v>147.1399993896484</v>
       </c>
       <c r="AR7" s="29" t="n">
-        <v>-4.989637742617092</v>
+        <v>-5.871726929382593</v>
       </c>
       <c r="AS7" s="78" t="n">
-        <v>77.12545994744731</v>
+        <v>73.0816023623057</v>
       </c>
       <c r="AT7" s="26" t="n">
-        <v>-0.005395790163263192</v>
+        <v>-0.01725381753315702</v>
       </c>
       <c r="AU7" s="26" t="n">
-        <v>0.01211366096052813</v>
+        <v>-0.007007119257115391</v>
       </c>
       <c r="AV7" s="26" t="n">
-        <v>0.02876869914962543</v>
+        <v>0.02316175355941463</v>
       </c>
       <c r="AW7" s="26" t="n">
-        <v>0.152656064208105</v>
+        <v>0.1419546477926694</v>
       </c>
       <c r="AX7" s="25" t="n"/>
       <c r="AY7" s="25" t="n"/>
@@ -28122,7 +28125,7 @@
         <v>-0.002447827045478523</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
@@ -28300,7 +28303,7 @@
         <v>0.003800922632101411</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
@@ -28478,7 +28481,7 @@
         <v>0.006261027194032653</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
@@ -28653,19 +28656,19 @@
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>-0.01379384326320543</v>
+        <v>0.004348790658493584</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -28722,76 +28725,76 @@
         </is>
       </c>
       <c r="R11" s="70" t="n">
-        <v>85.08000183105469</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="S11" s="71" t="n">
-        <v>-1.189994812011719</v>
+        <v>0.3699951171875</v>
       </c>
       <c r="T11" s="72" t="n">
-        <v>85.30999755859375</v>
+        <v>85.5</v>
       </c>
       <c r="U11" s="72" t="n">
-        <v>85.86000061035156</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="V11" s="72" t="n">
-        <v>85.06999969482422</v>
+        <v>85.20999908447266</v>
       </c>
       <c r="W11" s="73" t="n">
-        <v>8492100</v>
+        <v>6807200</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>0.9228772958231383</v>
+        <v>0.758633140829468</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>47.94394812605087</v>
+        <v>49.78740689917412</v>
       </c>
       <c r="Z11" s="28" t="n">
-        <v>30.92485485403817</v>
+        <v>41.61835818032277</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>16.73591344057998</v>
+        <v>16.06676903557024</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.3364391794618058</v>
+        <v>0.2793847748701808</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.3508158718063983</v>
+        <v>0.3365296524191548</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.01437669234459249</v>
+        <v>-0.05714487754897402</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>85.9345079970076</v>
+        <v>85.82683887505974</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.6314355839076</v>
+        <v>85.61494116248348</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>84.83639999389648</v>
+        <v>84.87179992675782</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.20510009765626</v>
+        <v>84.24700004577636</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.08315021514892</v>
+        <v>83.12825019836426</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>86.9874742051806</v>
+        <v>86.98984187178345</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.55400009155274</v>
+        <v>85.57399978637696</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>84.12052597792487</v>
+        <v>84.15815770097046</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.3346680083052058</v>
+        <v>0.4562088034347526</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.351039371844408</v>
+        <v>3.309047348355667</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.466016456168893</v>
+        <v>1.399709783339811</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -28800,22 +28803,22 @@
         <v>75.16000366210938</v>
       </c>
       <c r="AR11" s="29" t="n">
-        <v>-5.613487456019262</v>
+        <v>-5.203020271980218</v>
       </c>
       <c r="AS11" s="78" t="n">
-        <v>66.22163550226182</v>
+        <v>68.6915635577639</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-0.002812914493998675</v>
+        <v>-0.006279810779654227</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>-0.02609888694330786</v>
+        <v>-0.0002340502185004256</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.007698703346315838</v>
+        <v>0.03063554666435997</v>
       </c>
       <c r="AW11" s="26" t="n">
-        <v>0.09526263512882416</v>
+        <v>0.1000257030450693</v>
       </c>
       <c r="AX11" s="25" t="n"/>
       <c r="AY11" s="25" t="n"/>
@@ -28831,19 +28834,19 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>-0.01092528481292099</v>
+        <v>0.01147740647720341</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" s="30" t="inlineStr">
@@ -28853,17 +28856,17 @@
       </c>
       <c r="H12" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="I12" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="J12" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K12" s="30" t="inlineStr">
@@ -28882,16 +28885,16 @@
         </is>
       </c>
       <c r="N12" s="80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O12" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="P12" s="32" t="inlineStr">
         <is>
-          <t>Below every average</t>
+          <t>Long-term up, short-term mixed</t>
         </is>
       </c>
       <c r="Q12" s="32" t="inlineStr">
@@ -28900,76 +28903,76 @@
         </is>
       </c>
       <c r="R12" s="81" t="n">
-        <v>115.879997253418</v>
+        <v>117.2099990844727</v>
       </c>
       <c r="S12" s="82" t="n">
-        <v>-1.280006408691406</v>
+        <v>1.330001831054688</v>
       </c>
       <c r="T12" s="83" t="n">
-        <v>116.5400009155273</v>
+        <v>116.7099990844727</v>
       </c>
       <c r="U12" s="83" t="n">
-        <v>116.620002746582</v>
+        <v>117.5699996948242</v>
       </c>
       <c r="V12" s="83" t="n">
-        <v>115.8099975585938</v>
+        <v>116.379997253418</v>
       </c>
       <c r="W12" s="84" t="n">
-        <v>5231500</v>
+        <v>4505600</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>0.8751130169611171</v>
+        <v>0.8124837141700471</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>46.11854978280344</v>
+        <v>50.82050597356402</v>
       </c>
       <c r="Z12" s="35" t="n">
-        <v>1.686739014135516</v>
+        <v>33.73496412347481</v>
       </c>
       <c r="AA12" s="35" t="n">
-        <v>14.60964167370293</v>
+        <v>14.02483206422039</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>0.341151632772295</v>
+        <v>0.3068163364086445</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>0.5469809657530598</v>
+        <v>0.4989480398841767</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.2058293329807648</v>
+        <v>-0.1921317034755323</v>
       </c>
       <c r="AE12" s="83" t="n">
-        <v>117.2701179379637</v>
+        <v>117.2567581927434</v>
       </c>
       <c r="AF12" s="83" t="n">
-        <v>117.1105545150778</v>
+        <v>117.1195949304774</v>
       </c>
       <c r="AG12" s="83" t="n">
-        <v>116.1515998840332</v>
+        <v>116.1859999084473</v>
       </c>
       <c r="AH12" s="83" t="n">
-        <v>116.7897998809814</v>
+        <v>116.8841999053955</v>
       </c>
       <c r="AI12" s="83" t="n">
-        <v>117.0157249832153</v>
+        <v>117.004374961853</v>
       </c>
       <c r="AJ12" s="83" t="n">
-        <v>120.0951522891402</v>
+        <v>120.0137223397632</v>
       </c>
       <c r="AK12" s="83" t="n">
-        <v>117.9164989471436</v>
+        <v>117.9724990844727</v>
       </c>
       <c r="AL12" s="83" t="n">
-        <v>115.7378456051469</v>
+        <v>115.9312758291821</v>
       </c>
       <c r="AM12" s="87" t="n">
-        <v>0.03262374181585737</v>
+        <v>0.3132247420698089</v>
       </c>
       <c r="AN12" s="36" t="n">
-        <v>3.695247673479995</v>
+        <v>3.46050693361846</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.421444839978871</v>
+        <v>1.407925686600866</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -28978,22 +28981,22 @@
         <v>105.1900024414062</v>
       </c>
       <c r="AR12" s="36" t="n">
-        <v>-7.303419507875075</v>
+        <v>-6.239503174520156</v>
       </c>
       <c r="AS12" s="89" t="n">
-        <v>53.93539342386214</v>
+        <v>60.64579630748077</v>
       </c>
       <c r="AT12" s="33" t="n">
-        <v>-0.006856385410228039</v>
+        <v>-0.006863223026886356</v>
       </c>
       <c r="AU12" s="33" t="n">
-        <v>0.03825819030297883</v>
+        <v>0.04288637530919104</v>
       </c>
       <c r="AV12" s="33" t="n">
-        <v>-0.05063084080604807</v>
+        <v>-0.03028049622686779</v>
       </c>
       <c r="AW12" s="33" t="n">
-        <v>-0.02956206599473987</v>
+        <v>-0.01842395536526409</v>
       </c>
       <c r="AX12" s="32" t="n"/>
       <c r="AY12" s="32" t="n"/>
@@ -29009,19 +29012,19 @@
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>-0.01065622006694034</v>
+        <v>0.0141817983100696</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -29031,7 +29034,7 @@
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -29056,11 +29059,11 @@
       </c>
       <c r="M13" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N13" s="69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O13" s="23" t="inlineStr">
         <is>
@@ -29078,76 +29081,76 @@
         </is>
       </c>
       <c r="R13" s="70" t="n">
-        <v>111.4100036621094</v>
+        <v>112.9899978637695</v>
       </c>
       <c r="S13" s="71" t="n">
-        <v>-1.199996948242188</v>
+        <v>1.579994201660156</v>
       </c>
       <c r="T13" s="72" t="n">
-        <v>112.0299987792969</v>
+        <v>111.870002746582</v>
       </c>
       <c r="U13" s="72" t="n">
-        <v>112.370002746582</v>
+        <v>113.5299987792969</v>
       </c>
       <c r="V13" s="72" t="n">
-        <v>111.370002746582</v>
+        <v>111.8300018310547</v>
       </c>
       <c r="W13" s="73" t="n">
-        <v>4425600</v>
+        <v>3743500</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>1.011861756125221</v>
+        <v>0.8686290001659062</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>51.01216980941457</v>
+        <v>56.25686254478231</v>
       </c>
       <c r="Z13" s="28" t="n">
-        <v>36.90635274351316</v>
+        <v>75.39582678965377</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>12.27746093969639</v>
+        <v>12.82782318000766</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.5037245699433868</v>
+        <v>0.5720718069620858</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.4181754315721553</v>
+        <v>0.4489547066501414</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>0.08554913837123146</v>
+        <v>0.1231171003119444</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>111.8598786278915</v>
+        <v>112.1110162358644</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.2903007833486</v>
+        <v>111.4448186997505</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.0225996398926</v>
+        <v>110.0983996582031</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.6579998779297</v>
+        <v>112.6696998596191</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0346500015259</v>
+        <v>114.0331999969482</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.5518211204788</v>
+        <v>113.343902461012</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.4005001068115</v>
+        <v>111.6380001068115</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.2491790931443</v>
+        <v>109.932097752611</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.502208772014376</v>
+        <v>0.8962705584024059</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>3.86231841258263</v>
+        <v>3.056132056411507</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.485686049174404</v>
+        <v>1.494293618107402</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -29156,22 +29159,22 @@
         <v>105.0299987792969</v>
       </c>
       <c r="AR13" s="29" t="n">
-        <v>-7.470616011279885</v>
+        <v>-6.15838294979687</v>
       </c>
       <c r="AS13" s="78" t="n">
-        <v>41.49596671747967</v>
+        <v>51.77235176892785</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>0.006595621204560587</v>
+        <v>0.01427285741572693</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>0.01735002729262392</v>
+        <v>0.06014257761860109</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>-0.04508437978390245</v>
+        <v>-0.02333827055630144</v>
       </c>
       <c r="AW13" s="26" t="n">
-        <v>-0.05360174560959852</v>
+        <v>-0.04018011644483177</v>
       </c>
       <c r="AX13" s="25" t="n"/>
       <c r="AY13" s="25" t="n"/>
@@ -29187,14 +29190,14 @@
         </is>
       </c>
       <c r="C14" s="33" t="n">
-        <v>-0.008198223248004122</v>
+        <v>-0.0009393056075620576</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
@@ -29209,7 +29212,7 @@
       </c>
       <c r="H14" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="I14" s="30" t="inlineStr">
@@ -29256,76 +29259,76 @@
         </is>
       </c>
       <c r="R14" s="81" t="n">
-        <v>53.22999954223633</v>
+        <v>53.18000030517578</v>
       </c>
       <c r="S14" s="82" t="n">
-        <v>-0.4399986267089844</v>
+        <v>-0.04999923706054688</v>
       </c>
       <c r="T14" s="83" t="n">
-        <v>53.22000122070312</v>
+        <v>53.65999984741211</v>
       </c>
       <c r="U14" s="83" t="n">
-        <v>53.4900016784668</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="V14" s="83" t="n">
-        <v>53.09999847412109</v>
+        <v>52.84000015258789</v>
       </c>
       <c r="W14" s="84" t="n">
-        <v>7784600</v>
+        <v>13594400</v>
       </c>
       <c r="X14" s="85" t="n">
-        <v>0.7127269730893976</v>
+        <v>1.272222768130793</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>57.40881785747306</v>
+        <v>56.88909549935826</v>
       </c>
       <c r="Z14" s="35" t="n">
-        <v>60.65575308263671</v>
+        <v>58.60660286946693</v>
       </c>
       <c r="AA14" s="35" t="n">
-        <v>14.50656016427661</v>
+        <v>14.98720365065416</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.5232025548291901</v>
+        <v>0.5011609748717305</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.4529776353728215</v>
+        <v>0.4626143032726033</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>0.07022491945636855</v>
+        <v>0.03854667159912717</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>53.16498716861125</v>
+        <v>53.16832342118115</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.60543119526439</v>
+        <v>52.65766475071088</v>
       </c>
       <c r="AG14" s="83" t="n">
-        <v>51.69019989013672</v>
+        <v>51.71339988708496</v>
       </c>
       <c r="AH14" s="83" t="n">
-        <v>51.50950000762939</v>
+        <v>51.54049999237061</v>
       </c>
       <c r="AI14" s="83" t="n">
-        <v>49.79624998092651</v>
+        <v>49.84557498931885</v>
       </c>
       <c r="AJ14" s="83" t="n">
-        <v>54.24097428953887</v>
+        <v>54.07306403124243</v>
       </c>
       <c r="AK14" s="83" t="n">
-        <v>52.57600021362305</v>
+        <v>52.71350021362305</v>
       </c>
       <c r="AL14" s="83" t="n">
-        <v>50.91102613770722</v>
+        <v>51.35393639600367</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.6963992527191595</v>
+        <v>0.6715624104977951</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>6.333589733531719</v>
+        <v>5.158313570943717</v>
       </c>
       <c r="AO14" s="88" t="n">
-        <v>1.535470876341906</v>
+        <v>1.556076914497055</v>
       </c>
       <c r="AP14" s="83" t="n">
         <v>54.18999862670898</v>
@@ -29334,22 +29337,22 @@
         <v>42.03499984741211</v>
       </c>
       <c r="AR14" s="36" t="n">
-        <v>-1.771542920836122</v>
+        <v>-1.863809461392751</v>
       </c>
       <c r="AS14" s="89" t="n">
-        <v>92.10202237035364</v>
+        <v>91.69067525326705</v>
       </c>
       <c r="AT14" s="33" t="n">
-        <v>0.01545214424999508</v>
+        <v>-0.006723955999170639</v>
       </c>
       <c r="AU14" s="33" t="n">
-        <v>0.0287977931084924</v>
+        <v>0.02982186161365541</v>
       </c>
       <c r="AV14" s="33" t="n">
-        <v>0.03640963609155157</v>
+        <v>0.03968716947681439</v>
       </c>
       <c r="AW14" s="33" t="n">
-        <v>0.1737596765876839</v>
+        <v>0.1726571575415348</v>
       </c>
       <c r="AX14" s="32" t="n"/>
       <c r="AY14" s="32" t="n"/>
@@ -29365,19 +29368,19 @@
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>0.03155767002859644</v>
+        <v>-0.01548167201896</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -29412,15 +29415,15 @@
       </c>
       <c r="M15" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="N15" s="69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O15" s="23" t="inlineStr">
         <is>
-          <t>Very Strong</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="P15" s="25" t="inlineStr">
@@ -29434,76 +29437,76 @@
         </is>
       </c>
       <c r="R15" s="70" t="n">
-        <v>188.6100006103516</v>
+        <v>185.6900024414062</v>
       </c>
       <c r="S15" s="71" t="n">
-        <v>5.770004272460938</v>
+        <v>-2.919998168945312</v>
       </c>
       <c r="T15" s="72" t="n">
-        <v>186.4700012207031</v>
+        <v>188.0700073242188</v>
       </c>
       <c r="U15" s="72" t="n">
-        <v>188.7400054931641</v>
+        <v>188.6699981689453</v>
       </c>
       <c r="V15" s="72" t="n">
-        <v>185.6699981689453</v>
+        <v>185.5099945068359</v>
       </c>
       <c r="W15" s="73" t="n">
-        <v>8136000</v>
+        <v>6300200</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>1.191152442916625</v>
+        <v>0.9420070992186075</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>57.83612648825964</v>
+        <v>53.00339310126717</v>
       </c>
       <c r="Z15" s="28" t="n">
-        <v>75.71538152894806</v>
+        <v>53.13224291345087</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>14.2014856168803</v>
+        <v>13.42241089458476</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.8249471787323728</v>
+        <v>0.860660059154867</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>1.054106298546626</v>
+        <v>1.015417050668274</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.2291591198142533</v>
+        <v>-0.1547569915134073</v>
       </c>
       <c r="AE15" s="72" t="n">
-        <v>184.5542979216405</v>
+        <v>184.8066767038106</v>
       </c>
       <c r="AF15" s="72" t="n">
-        <v>183.953328902363</v>
+        <v>184.1112083150033</v>
       </c>
       <c r="AG15" s="72" t="n">
-        <v>182.7776007080078</v>
+        <v>182.7754006958008</v>
       </c>
       <c r="AH15" s="72" t="n">
-        <v>176.4648008728027</v>
+        <v>176.947400970459</v>
       </c>
       <c r="AI15" s="72" t="n">
-        <v>159.1438251495361</v>
+        <v>159.3334501647949</v>
       </c>
       <c r="AJ15" s="72" t="n">
-        <v>193.0509289294371</v>
+        <v>192.2216794840587</v>
       </c>
       <c r="AK15" s="72" t="n">
-        <v>185.0390007019043</v>
+        <v>185.5560005187988</v>
       </c>
       <c r="AL15" s="72" t="n">
-        <v>177.0270724743714</v>
+        <v>178.890321553539</v>
       </c>
       <c r="AM15" s="76" t="n">
-        <v>0.7228552108202617</v>
+        <v>0.5100516333974229</v>
       </c>
       <c r="AN15" s="29" t="n">
-        <v>8.659718434645001</v>
+        <v>7.184546925589225</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.222682097325518</v>
+        <v>2.217928968762917</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -29512,22 +29515,22 @@
         <v>126.6800003051758</v>
       </c>
       <c r="AR15" s="29" t="n">
-        <v>-5.092333988202824</v>
+        <v>-6.561663345482471</v>
       </c>
       <c r="AS15" s="78" t="n">
-        <v>85.95420435787231</v>
+        <v>81.90146548977381</v>
       </c>
       <c r="AT15" s="26" t="n">
-        <v>0.03009281443563072</v>
+        <v>0.01298349743336691</v>
       </c>
       <c r="AU15" s="26" t="n">
-        <v>0.1323166975866985</v>
+        <v>0.05667789766130582</v>
       </c>
       <c r="AV15" s="26" t="n">
-        <v>0.009419290603934538</v>
+        <v>-0.02790284636080442</v>
       </c>
       <c r="AW15" s="26" t="n">
-        <v>0.3100645899225647</v>
+        <v>0.2897825996177301</v>
       </c>
       <c r="AX15" s="25" t="n"/>
       <c r="AY15" s="25" t="n"/>
@@ -29546,7 +29549,7 @@
         <v>-0.004030459153398613</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
@@ -29721,10 +29724,10 @@
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>-0.007584418043843133</v>
+        <v>-0.01042150902637939</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
@@ -29763,7 +29766,7 @@
       </c>
       <c r="L17" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="M17" s="23" t="inlineStr">
@@ -29790,76 +29793,76 @@
         </is>
       </c>
       <c r="R17" s="70" t="n">
-        <v>43.18000030517578</v>
+        <v>42.72999954223633</v>
       </c>
       <c r="S17" s="71" t="n">
-        <v>-0.3299980163574219</v>
+        <v>-0.4500007629394531</v>
       </c>
       <c r="T17" s="72" t="n">
-        <v>43.22000122070312</v>
+        <v>43.34000015258789</v>
       </c>
       <c r="U17" s="72" t="n">
-        <v>43.33000183105469</v>
+        <v>43.38000106811523</v>
       </c>
       <c r="V17" s="72" t="n">
-        <v>42.91999816894531</v>
+        <v>42.56000137329102</v>
       </c>
       <c r="W17" s="73" t="n">
-        <v>16033500</v>
+        <v>20360500</v>
       </c>
       <c r="X17" s="74" t="n">
-        <v>0.8141181858825758</v>
+        <v>1.034924541570439</v>
       </c>
       <c r="Y17" s="28" t="n">
-        <v>39.75511151129263</v>
+        <v>35.78398855531299</v>
       </c>
       <c r="Z17" s="28" t="n">
-        <v>24.61535150954359</v>
+        <v>8.133883087750807</v>
       </c>
       <c r="AA17" s="28" t="n">
-        <v>12.79951889238299</v>
+        <v>13.605059038268</v>
       </c>
       <c r="AB17" s="75" t="n">
-        <v>-0.4072612473717143</v>
+        <v>-0.4449385577093565</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.3820702833400081</v>
+        <v>-0.3946439382138778</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.02519096403170623</v>
+        <v>-0.05029461949547875</v>
       </c>
       <c r="AE17" s="72" t="n">
-        <v>43.44893218702764</v>
+        <v>43.28916937707401</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>43.85961543233375</v>
+        <v>43.75692307868853</v>
       </c>
       <c r="AG17" s="72" t="n">
-        <v>44.72200012207031</v>
+        <v>44.68740013122559</v>
       </c>
       <c r="AH17" s="72" t="n">
-        <v>44.9760998916626</v>
+        <v>44.94069988250732</v>
       </c>
       <c r="AI17" s="72" t="n">
-        <v>44.72224996566772</v>
+        <v>44.71174995422363</v>
       </c>
       <c r="AJ17" s="72" t="n">
-        <v>44.61010127424603</v>
+        <v>44.57850908512476</v>
       </c>
       <c r="AK17" s="72" t="n">
-        <v>43.72000045776367</v>
+        <v>43.63900051116944</v>
       </c>
       <c r="AL17" s="72" t="n">
-        <v>42.82989964128132</v>
+        <v>42.69949193721411</v>
       </c>
       <c r="AM17" s="76" t="n">
-        <v>0.1966634887933531</v>
+        <v>0.01623593752518172</v>
       </c>
       <c r="AN17" s="29" t="n">
-        <v>4.071824369454222</v>
+        <v>4.305820770184054</v>
       </c>
       <c r="AO17" s="77" t="n">
-        <v>1.482654263344682</v>
+        <v>1.528322572540179</v>
       </c>
       <c r="AP17" s="72" t="n">
         <v>47.79999923706055</v>
@@ -29868,22 +29871,22 @@
         <v>41.15000152587891</v>
       </c>
       <c r="AR17" s="29" t="n">
-        <v>-9.665269886244609</v>
+        <v>-10.60669409152065</v>
       </c>
       <c r="AS17" s="78" t="n">
-        <v>30.52630793967843</v>
+        <v>23.75937684460753</v>
       </c>
       <c r="AT17" s="26" t="n">
-        <v>-0.01347955554986158</v>
+        <v>-0.0009352563736080288</v>
       </c>
       <c r="AU17" s="26" t="n">
-        <v>-0.0385214773572532</v>
+        <v>-0.04321541226533654</v>
       </c>
       <c r="AV17" s="26" t="n">
-        <v>-0.03248937325200674</v>
+        <v>-0.03804589591114593</v>
       </c>
       <c r="AW17" s="26" t="n">
-        <v>0.01147813760200567</v>
+        <v>0.0009370090610010262</v>
       </c>
       <c r="AX17" s="25" t="n"/>
       <c r="AY17" s="25" t="n"/>
@@ -29921,7 +29924,7 @@
         <v>-0.002269485222937795</v>
       </c>
       <c r="D19" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
@@ -30097,7 +30100,7 @@
         <v>-0.006489984566639517</v>
       </c>
       <c r="D20" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
@@ -30270,14 +30273,14 @@
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>0.002943849410811605</v>
+        <v>-0.01354190184335091</v>
       </c>
       <c r="D21" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -30292,17 +30295,17 @@
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K21" s="23" t="inlineStr">
@@ -30317,20 +30320,20 @@
       </c>
       <c r="M21" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N21" s="69" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O21" s="23" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="P21" s="25" t="inlineStr">
         <is>
-          <t>Above every average</t>
+          <t>Long-term up, short-term mixed</t>
         </is>
       </c>
       <c r="Q21" s="25" t="inlineStr">
@@ -30339,76 +30342,76 @@
         </is>
       </c>
       <c r="R21" s="70" t="n">
-        <v>299.8099975585938</v>
+        <v>295.75</v>
       </c>
       <c r="S21" s="71" t="n">
-        <v>0.8800048828125</v>
+        <v>-4.05999755859375</v>
       </c>
       <c r="T21" s="72" t="n">
-        <v>298.7699890136719</v>
+        <v>299.7000122070312</v>
       </c>
       <c r="U21" s="72" t="n">
-        <v>300.3200073242188</v>
+        <v>300.3900146484375</v>
       </c>
       <c r="V21" s="72" t="n">
-        <v>298.1400146484375</v>
+        <v>295.6700134277344</v>
       </c>
       <c r="W21" s="73" t="n">
-        <v>13658700</v>
+        <v>19052800</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>0.7954310193463625</v>
+        <v>1.140438929641368</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>52.41279782132757</v>
+        <v>45.32522468665713</v>
       </c>
       <c r="Z21" s="28" t="n">
-        <v>34.0294154035339</v>
+        <v>0.8410804080571717</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>14.16121708747648</v>
+        <v>14.94790355833013</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>1.054301356064684</v>
+        <v>0.6602067659577529</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>1.533864818875446</v>
+        <v>1.359133208291907</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.4795634628107615</v>
+        <v>-0.6989264423341541</v>
       </c>
       <c r="AE21" s="72" t="n">
-        <v>299.680077023006</v>
+        <v>298.8067265734492</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>299.1208121105085</v>
+        <v>298.8143746459168</v>
       </c>
       <c r="AG21" s="72" t="n">
-        <v>297.1962005615234</v>
+        <v>297.3136004638672</v>
       </c>
       <c r="AH21" s="72" t="n">
-        <v>288.5556008911133</v>
+        <v>288.9840008544922</v>
       </c>
       <c r="AI21" s="72" t="n">
-        <v>271.0481502532959</v>
+        <v>271.3067502593994</v>
       </c>
       <c r="AJ21" s="72" t="n">
-        <v>305.9859908677769</v>
+        <v>305.0891537932497</v>
       </c>
       <c r="AK21" s="72" t="n">
-        <v>300.0279998779297</v>
+        <v>300.2554992675781</v>
       </c>
       <c r="AL21" s="72" t="n">
-        <v>294.0700088880825</v>
+        <v>295.4218447419065</v>
       </c>
       <c r="AM21" s="76" t="n">
-        <v>0.4817050479173745</v>
+        <v>0.03394483990846393</v>
       </c>
       <c r="AN21" s="29" t="n">
-        <v>3.97162331000525</v>
+        <v>3.21969425203699</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.07937807342217</v>
+        <v>1.130034660141968</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -30417,22 +30420,22 @@
         <v>228.8999938964844</v>
       </c>
       <c r="AR21" s="29" t="n">
-        <v>-1.759615717303098</v>
+        <v>-3.089977358312457</v>
       </c>
       <c r="AS21" s="78" t="n">
-        <v>92.96015311598961</v>
+        <v>87.63766016427803</v>
       </c>
       <c r="AT21" s="26" t="n">
-        <v>0.007189115578747796</v>
+        <v>-0.01403517660690634</v>
       </c>
       <c r="AU21" s="26" t="n">
-        <v>0.0389506530446404</v>
+        <v>0.0108001083484075</v>
       </c>
       <c r="AV21" s="26" t="n">
-        <v>0.02664109444857621</v>
+        <v>0.01831769258816762</v>
       </c>
       <c r="AW21" s="26" t="n">
-        <v>0.2179476482707843</v>
+        <v>0.2014543207675612</v>
       </c>
       <c r="AX21" s="25" t="n"/>
       <c r="AY21" s="25" t="n"/>
@@ -30646,7 +30649,7 @@
         <v>0.01627575132974779</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
@@ -30822,7 +30825,7 @@
         <v>-0.02326562725379</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -31171,19 +31174,19 @@
         </is>
       </c>
       <c r="C27" s="33" t="n">
-        <v>0.01865234899615387</v>
+        <v>-0.03192951480000428</v>
       </c>
       <c r="D27" s="34" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G27" s="30" t="inlineStr">
@@ -31193,7 +31196,7 @@
       </c>
       <c r="H27" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I27" s="30" t="inlineStr">
@@ -31222,16 +31225,16 @@
         </is>
       </c>
       <c r="N27" s="80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O27" s="30" t="inlineStr">
         <is>
-          <t>Very Strong</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="P27" s="32" t="inlineStr">
         <is>
-          <t>Above every average</t>
+          <t>Long-term up, short-term mixed</t>
         </is>
       </c>
       <c r="Q27" s="32" t="inlineStr">
@@ -31240,76 +31243,76 @@
         </is>
       </c>
       <c r="R27" s="81" t="n">
-        <v>87.37999725341797</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="S27" s="82" t="n">
-        <v>1.599998474121094</v>
+        <v>-2.790000915527344</v>
       </c>
       <c r="T27" s="83" t="n">
-        <v>86.5</v>
+        <v>86.70999908447266</v>
       </c>
       <c r="U27" s="83" t="n">
-        <v>87.83000183105469</v>
+        <v>87.19000244140625</v>
       </c>
       <c r="V27" s="83" t="n">
-        <v>86.02799987792969</v>
+        <v>84.18000030517578</v>
       </c>
       <c r="W27" s="84" t="n">
-        <v>2907800</v>
+        <v>5061500</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>0.5832274472717499</v>
+        <v>1.026855679253417</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>64.75266026536364</v>
+        <v>57.36713154759599</v>
       </c>
       <c r="Z27" s="35" t="n">
-        <v>94.87174359674376</v>
+        <v>63.07686689730184</v>
       </c>
       <c r="AA27" s="35" t="n">
-        <v>25.33738466636874</v>
+        <v>25.57602069893318</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.511171149610618</v>
+        <v>2.403606178950014</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>1.806850852372906</v>
+        <v>1.926201917688327</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>0.7043202972377125</v>
+        <v>0.4774042612616864</v>
       </c>
       <c r="AE27" s="83" t="n">
-        <v>84.77434542264621</v>
+        <v>84.73337895936719</v>
       </c>
       <c r="AF27" s="83" t="n">
-        <v>81.75203779047905</v>
+        <v>82.01003402206192</v>
       </c>
       <c r="AG27" s="83" t="n">
-        <v>78.89339965820312</v>
+        <v>79.01539962768555</v>
       </c>
       <c r="AH27" s="83" t="n">
-        <v>77.73699996948243</v>
+        <v>77.89529991149902</v>
       </c>
       <c r="AI27" s="83" t="n">
-        <v>76.75240007400512</v>
+        <v>76.76115007400513</v>
       </c>
       <c r="AJ27" s="83" t="n">
-        <v>89.37672863617078</v>
+        <v>88.97264740006578</v>
       </c>
       <c r="AK27" s="83" t="n">
-        <v>80.80599975585938</v>
+        <v>81.47349967956544</v>
       </c>
       <c r="AL27" s="83" t="n">
-        <v>72.23527087554797</v>
+        <v>73.97435195906509</v>
       </c>
       <c r="AM27" s="87" t="n">
-        <v>0.8835144938874636</v>
+        <v>0.7077900565824069</v>
       </c>
       <c r="AN27" s="36" t="n">
-        <v>21.21310028019282</v>
+        <v>18.40880224857022</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.693889727016816</v>
+        <v>2.854184757973381</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -31318,22 +31321,22 @@
         <v>62.94499969482422</v>
       </c>
       <c r="AR27" s="36" t="n">
-        <v>-5.688077912215606</v>
+        <v>-8.699411824334369</v>
       </c>
       <c r="AS27" s="89" t="n">
-        <v>82.25886568722078</v>
+        <v>72.86650499525619</v>
       </c>
       <c r="AT27" s="33" t="n">
-        <v>0.04935752102847935</v>
+        <v>-0.01879135557111744</v>
       </c>
       <c r="AU27" s="33" t="n">
-        <v>0.2380276988739238</v>
+        <v>0.160356578426982</v>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>0.07863220527355863</v>
+        <v>0.03221475885247194</v>
       </c>
       <c r="AW27" s="33" t="n">
-        <v>0.1359854307523325</v>
+        <v>0.09971396712853675</v>
       </c>
       <c r="AX27" s="32" t="n"/>
       <c r="AY27" s="32" t="n"/>
@@ -31347,29 +31350,29 @@
         </is>
       </c>
       <c r="C28" s="26" t="n">
-        <v>0.01652994979538658</v>
+        <v>-0.06332041548914424</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -31398,11 +31401,11 @@
         </is>
       </c>
       <c r="N28" s="69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Very Weak</t>
         </is>
       </c>
       <c r="P28" s="25" t="inlineStr">
@@ -31416,76 +31419,76 @@
         </is>
       </c>
       <c r="R28" s="70" t="n">
-        <v>255.2100067138672</v>
+        <v>239.0500030517578</v>
       </c>
       <c r="S28" s="71" t="n">
-        <v>4.150009155273438</v>
+        <v>-16.16000366210938</v>
       </c>
       <c r="T28" s="72" t="n">
-        <v>255.4600067138672</v>
+        <v>251.1000061035156</v>
       </c>
       <c r="U28" s="72" t="n">
-        <v>267.6900024414062</v>
+        <v>251.6900024414062</v>
       </c>
       <c r="V28" s="72" t="n">
-        <v>249.4649963378906</v>
+        <v>238.6600036621094</v>
       </c>
       <c r="W28" s="73" t="n">
-        <v>4880000</v>
+        <v>3874900</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>1.095119425241829</v>
+        <v>0.9035728776565728</v>
       </c>
       <c r="Y28" s="28" t="n">
-        <v>45.7149076110599</v>
+        <v>39.96211488858304</v>
       </c>
       <c r="Z28" s="28" t="n">
-        <v>38.51021456935605</v>
+        <v>10.1194833993645</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>11.24998118180373</v>
+        <v>10.96817945327786</v>
       </c>
       <c r="AB28" s="75" t="n">
-        <v>-9.758123070209763</v>
+        <v>-10.26046894402361</v>
       </c>
       <c r="AC28" s="75" t="n">
-        <v>-9.908921489340647</v>
+        <v>-9.97923098027724</v>
       </c>
       <c r="AD28" s="75" t="n">
-        <v>0.1507984191308847</v>
+        <v>-0.2812379637463742</v>
       </c>
       <c r="AE28" s="72" t="n">
-        <v>251.7136598724419</v>
+        <v>248.8995139122899</v>
       </c>
       <c r="AF28" s="72" t="n">
-        <v>260.6556570521018</v>
+        <v>258.6915066884342</v>
       </c>
       <c r="AG28" s="72" t="n">
-        <v>291.4571990966797</v>
+        <v>287.8605990600586</v>
       </c>
       <c r="AH28" s="72" t="n">
-        <v>272.3387493896485</v>
+        <v>273.2906494140625</v>
       </c>
       <c r="AI28" s="72" t="n">
-        <v>198.9142248916626</v>
+        <v>199.3352749252319</v>
       </c>
       <c r="AJ28" s="72" t="n">
-        <v>293.5779384582031</v>
+        <v>293.6322659954897</v>
       </c>
       <c r="AK28" s="72" t="n">
-        <v>261.2309989929199</v>
+        <v>261.1989990234375</v>
       </c>
       <c r="AL28" s="72" t="n">
-        <v>228.8840595276368</v>
+        <v>228.7657320513854</v>
       </c>
       <c r="AM28" s="76" t="n">
-        <v>0.4069310361569932</v>
+        <v>0.1585450982972891</v>
       </c>
       <c r="AN28" s="29" t="n">
-        <v>24.76500843313761</v>
+        <v>24.8341433874652</v>
       </c>
       <c r="AO28" s="77" t="n">
-        <v>7.422125855023981</v>
+        <v>7.852394965332765</v>
       </c>
       <c r="AP28" s="72" t="n">
         <v>452.7000122070312</v>
@@ -31494,22 +31497,22 @@
         <v>100.0199966430664</v>
       </c>
       <c r="AR28" s="29" t="n">
-        <v>-43.62491720076359</v>
+        <v>-47.19461086684615</v>
       </c>
       <c r="AS28" s="78" t="n">
-        <v>44.00306317970384</v>
+        <v>39.42100495441195</v>
       </c>
       <c r="AT28" s="26" t="n">
-        <v>0.01790844556199422</v>
+        <v>-0.01754892382019058</v>
       </c>
       <c r="AU28" s="26" t="n">
-        <v>0.1348215012072891</v>
+        <v>-0.01030881139184814</v>
       </c>
       <c r="AV28" s="26" t="n">
-        <v>-0.2387925699384323</v>
+        <v>-0.3233604198535892</v>
       </c>
       <c r="AW28" s="26" t="n">
-        <v>1.33473618528869</v>
+        <v>1.18689971997867</v>
       </c>
       <c r="AX28" s="25" t="n"/>
       <c r="AY28" s="25" t="n"/>
@@ -31526,7 +31529,7 @@
         <v>-0.05517577254916717</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E29" s="30" t="inlineStr">
         <is>
@@ -31702,7 +31705,7 @@
         <v>-0.007401625495918829</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
@@ -31875,10 +31878,10 @@
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>-0.00959387829211289</v>
+        <v>-0.05943759603113641</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -31887,7 +31890,7 @@
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -31897,7 +31900,7 @@
       </c>
       <c r="H31" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I31" s="30" t="inlineStr">
@@ -31926,7 +31929,7 @@
         </is>
       </c>
       <c r="N31" s="80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O31" s="30" t="inlineStr">
         <is>
@@ -31935,7 +31938,7 @@
       </c>
       <c r="P31" s="32" t="inlineStr">
         <is>
-          <t>Above every average</t>
+          <t>Long-term down, short-term mixed</t>
         </is>
       </c>
       <c r="Q31" s="32" t="inlineStr">
@@ -31944,76 +31947,76 @@
         </is>
       </c>
       <c r="R31" s="81" t="n">
-        <v>106.3300018310547</v>
+        <v>100.0100021362305</v>
       </c>
       <c r="S31" s="82" t="n">
-        <v>-1.029998779296875</v>
+        <v>-6.319999694824219</v>
       </c>
       <c r="T31" s="83" t="n">
-        <v>108.129997253418</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="U31" s="83" t="n">
-        <v>108.9700012207031</v>
+        <v>106.4700012207031</v>
       </c>
       <c r="V31" s="83" t="n">
-        <v>105.1399993896484</v>
+        <v>99.52999877929688</v>
       </c>
       <c r="W31" s="84" t="n">
-        <v>2313900</v>
+        <v>4190900</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>0.7987945069284782</v>
+        <v>1.482811571230434</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>65.28503598146889</v>
+        <v>52.59298094718957</v>
       </c>
       <c r="Z31" s="35" t="n">
-        <v>70.448100418946</v>
+        <v>34.60011017834091</v>
       </c>
       <c r="AA31" s="35" t="n">
-        <v>20.69494291305342</v>
+        <v>19.91066925997254</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>3.005102164700801</v>
+        <v>2.670817356943928</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.704951922148574</v>
+        <v>1.898125009107645</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>1.300150242552227</v>
+        <v>0.772692347836283</v>
       </c>
       <c r="AE31" s="83" t="n">
-        <v>103.1164305886754</v>
+        <v>102.4261131547987</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>99.03266053924297</v>
+        <v>99.12150977533274</v>
       </c>
       <c r="AG31" s="83" t="n">
-        <v>96.30579986572266</v>
+        <v>96.19259994506837</v>
       </c>
       <c r="AH31" s="83" t="n">
-        <v>104.8465998077393</v>
+        <v>104.7443997955322</v>
       </c>
       <c r="AI31" s="83" t="n">
-        <v>105.070549736023</v>
+        <v>105.0993997573853</v>
       </c>
       <c r="AJ31" s="83" t="n">
-        <v>108.4119504240334</v>
+        <v>107.6769134564309</v>
       </c>
       <c r="AK31" s="83" t="n">
-        <v>97.9319995880127</v>
+        <v>98.61349983215332</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>87.45204875199201</v>
+        <v>89.55008620787579</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.9006699255771874</v>
+        <v>0.5770406362309468</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>21.40250557551872</v>
+        <v>18.38168940298044</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>3.807500555819707</v>
+        <v>4.254624645273521</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -32022,22 +32025,22 @@
         <v>73.19999694824219</v>
       </c>
       <c r="AR31" s="36" t="n">
-        <v>-21.37681343378138</v>
+        <v>-26.04998663558495</v>
       </c>
       <c r="AS31" s="89" t="n">
-        <v>53.40103210789172</v>
+        <v>43.21405785844745</v>
       </c>
       <c r="AT31" s="33" t="n">
-        <v>0.1123549106038293</v>
+        <v>-0.02438786409035121</v>
       </c>
       <c r="AU31" s="33" t="n">
-        <v>0.2573016697972415</v>
+        <v>0.1335146586319509</v>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>-0.03886825932494031</v>
+        <v>-0.1125997795531408</v>
       </c>
       <c r="AW31" s="33" t="n">
-        <v>0.1622035666607209</v>
+        <v>0.09312498055959506</v>
       </c>
       <c r="AX31" s="32" t="n"/>
       <c r="AY31" s="32" t="n"/>
@@ -32054,7 +32057,7 @@
         <v>-0.02960829037404245</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -32230,7 +32233,7 @@
         <v>-0.03392203277851213</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -32406,7 +32409,7 @@
         <v>0.01530903307141895</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
@@ -32758,7 +32761,7 @@
         <v>-0.02845037703741871</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -32934,7 +32937,7 @@
         <v>0.01677034764032892</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -33286,7 +33289,7 @@
         <v>-0.002704785444845648</v>
       </c>
       <c r="D39" s="34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E39" s="30" t="inlineStr">
         <is>
@@ -33462,7 +33465,7 @@
         <v>-0.04256684013924827</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
@@ -33814,7 +33817,7 @@
         <v>-0.03588291869363736</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -33990,7 +33993,7 @@
         <v>-0.04574959589106331</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
@@ -34166,7 +34169,7 @@
         <v>0.00193621591207882</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
@@ -34339,19 +34342,19 @@
         </is>
       </c>
       <c r="C45" s="33" t="n">
-        <v>0.006474453644578437</v>
+        <v>-0.003580509420204936</v>
       </c>
       <c r="D45" s="34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
@@ -34390,11 +34393,11 @@
         </is>
       </c>
       <c r="N45" s="80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O45" s="30" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="P45" s="32" t="inlineStr">
@@ -34408,76 +34411,76 @@
         </is>
       </c>
       <c r="R45" s="81" t="n">
-        <v>164.7799987792969</v>
+        <v>164.1900024414062</v>
       </c>
       <c r="S45" s="82" t="n">
-        <v>1.05999755859375</v>
+        <v>-0.589996337890625</v>
       </c>
       <c r="T45" s="83" t="n">
-        <v>165.1600036621094</v>
+        <v>164.5899963378906</v>
       </c>
       <c r="U45" s="83" t="n">
-        <v>166.9499969482422</v>
+        <v>165.4900054931641</v>
       </c>
       <c r="V45" s="83" t="n">
-        <v>161.9199981689453</v>
+        <v>161.8999938964844</v>
       </c>
       <c r="W45" s="84" t="n">
-        <v>15065100</v>
+        <v>7752100</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>1.506263725880818</v>
+        <v>0.7992943369613185</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>49.20875651303804</v>
+        <v>48.50336989918072</v>
       </c>
       <c r="Z45" s="35" t="n">
-        <v>67.64243247321564</v>
+        <v>74.11548084340996</v>
       </c>
       <c r="AA45" s="35" t="n">
-        <v>12.40692899222806</v>
+        <v>11.75275876428061</v>
       </c>
       <c r="AB45" s="86" t="n">
-        <v>-2.904970548344465</v>
+        <v>-2.531618865633021</v>
       </c>
       <c r="AC45" s="86" t="n">
-        <v>-4.24164981984309</v>
+        <v>-3.899643629001076</v>
       </c>
       <c r="AD45" s="86" t="n">
-        <v>1.336679271498625</v>
+        <v>1.368024763368055</v>
       </c>
       <c r="AE45" s="83" t="n">
-        <v>162.2440876736013</v>
+        <v>162.676513177558</v>
       </c>
       <c r="AF45" s="83" t="n">
-        <v>163.6720344494773</v>
+        <v>163.7191224487436</v>
       </c>
       <c r="AG45" s="83" t="n">
-        <v>174.4887997436524</v>
+        <v>173.5131997680664</v>
       </c>
       <c r="AH45" s="83" t="n">
-        <v>181.0831002807617</v>
+        <v>181.4843003082275</v>
       </c>
       <c r="AI45" s="83" t="n">
-        <v>167.9726498413086</v>
+        <v>167.9357498168945</v>
       </c>
       <c r="AJ45" s="83" t="n">
-        <v>169.9993277746179</v>
+        <v>168.5150185229261</v>
       </c>
       <c r="AK45" s="83" t="n">
-        <v>160.9744995117188</v>
+        <v>161.8034996032715</v>
       </c>
       <c r="AL45" s="83" t="n">
-        <v>151.9496712488196</v>
+        <v>155.0919806836168</v>
       </c>
       <c r="AM45" s="87" t="n">
-        <v>0.7108349963412831</v>
+        <v>0.6777915600554963</v>
       </c>
       <c r="AN45" s="36" t="n">
-        <v>11.21274275152156</v>
+        <v>8.295888452488022</v>
       </c>
       <c r="AO45" s="88" t="n">
-        <v>3.81894123578364</v>
+        <v>3.715080851846692</v>
       </c>
       <c r="AP45" s="83" t="n">
         <v>259.9200134277344</v>
@@ -34486,22 +34489,22 @@
         <v>121.9899978637695</v>
       </c>
       <c r="AR45" s="36" t="n">
-        <v>-36.60357407410234</v>
+        <v>-36.83056557433734</v>
       </c>
       <c r="AS45" s="89" t="n">
-        <v>31.02297983551198</v>
+        <v>30.59522933067932</v>
       </c>
       <c r="AT45" s="33" t="n">
-        <v>0.0251337137493417</v>
+        <v>0.02139970414560644</v>
       </c>
       <c r="AU45" s="33" t="n">
-        <v>0.05845327936562317</v>
+        <v>0.08304746590375411</v>
       </c>
       <c r="AV45" s="33" t="n">
-        <v>-0.3227012892984074</v>
+        <v>-0.3459086939414122</v>
       </c>
       <c r="AW45" s="33" t="n">
-        <v>-0.03665597287691191</v>
+        <v>-0.04010523524092424</v>
       </c>
       <c r="AX45" s="32" t="n"/>
       <c r="AY45" s="32" t="n"/>
@@ -34518,7 +34521,7 @@
         <v>-0.04649784460844808</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -34694,7 +34697,7 @@
         <v>2.022243029231596e-05</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
@@ -34870,7 +34873,7 @@
         <v>-0.01707955694679375</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
@@ -35448,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 2 Sep 2026, 10:41 PM · Yahoo Finance data</t>
+          <t>Built 2 Sep 2026, 11:18 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -43431,16 +43434,16 @@
         <v>0.01690034709569455</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>-0.01175813823414407</v>
+        <v>-0.01341526794428827</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>0.03803180759147962</v>
+        <v>0.01826924544114328</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>0.02775621685694873</v>
+        <v>0.02556652464683751</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>0.0194455556976294</v>
+        <v>0.01983826329582206</v>
       </c>
       <c r="I8" s="26" t="n">
         <v>0.1675855026358002</v>
@@ -43457,110 +43460,110 @@
     <row r="9">
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>State Street Technology Select Sector SPDR ETF</t>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D9" s="33" t="n">
-        <v>-0.0002177809097458905</v>
+        <v>0.0138888974898479</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>0.01023440384137952</v>
+        <v>-0.001687260814993596</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.03122901048668969</v>
+        <v>0.003391621298757919</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>-0.07370970241397712</v>
+        <v>0.003033514742470489</v>
       </c>
       <c r="H9" s="33" t="n">
-        <v>0.3352727716619319</v>
+        <v>-0.05362406513585094</v>
       </c>
       <c r="I9" s="33" t="n">
-        <v>0.2752657119316162</v>
+        <v>-0.04502211176349968</v>
       </c>
       <c r="J9" s="34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K9" s="102" t="inlineStr">
         <is>
-          <t>Long-term up, short-term mixed</t>
+          <t>Long-term down, short-term mixed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>State Street Communication Services Select Sector SPDR ETF</t>
+          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>0.0138888974898479</v>
+        <v>0.003284443158907635</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>-0.006714986165234249</v>
+        <v>-0.008577696679776148</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>0.00970003472765657</v>
+        <v>0.001874148150021515</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>-0.01012592699629389</v>
+        <v>0.04101746551822116</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>-0.04696508103191899</v>
+        <v>-0.01870129433600631</v>
       </c>
       <c r="I10" s="26" t="n">
-        <v>-0.04502211176349968</v>
+        <v>0.1010555927301928</v>
       </c>
       <c r="J10" s="27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K10" s="101" t="inlineStr">
         <is>
-          <t>Long-term down, short-term mixed</t>
+          <t>Long-term up, short-term mixed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
+          <t>State Street Financial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D11" s="33" t="n">
-        <v>0.003284443158907635</v>
+        <v>0.008041941928971008</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>-0.0114424168074545</v>
+        <v>-0.0102986352799006</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.007895335424539018</v>
+        <v>-0.003800988539102157</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>0.04521565276121042</v>
+        <v>0.1334775124453844</v>
       </c>
       <c r="H11" s="33" t="n">
-        <v>-0.02518804579758527</v>
+        <v>0.1196116475225653</v>
       </c>
       <c r="I11" s="33" t="n">
-        <v>0.1010555927301928</v>
+        <v>0.05276610125057579</v>
       </c>
       <c r="J11" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K11" s="102" t="inlineStr">
         <is>
@@ -43571,34 +43574,34 @@
     <row r="12">
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>State Street Financial Select Sector SPDR ETF</t>
+          <t>State Street Technology Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.008041941928971008</v>
+        <v>-0.0002177809097458905</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>-0.0102986352799006</v>
+        <v>0.004156693178994031</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>-0.003800988539102157</v>
+        <v>-0.01765643606599832</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>0.1334775124453844</v>
+        <v>-0.06436319573466176</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>0.1196116475225653</v>
+        <v>0.3129291398141143</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0.05276610125057579</v>
+        <v>0.2752657119316162</v>
       </c>
       <c r="J12" s="27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K12" s="101" t="inlineStr">
         <is>
@@ -43621,16 +43624,16 @@
         <v>0.002356263906883926</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>-0.02619751096090783</v>
+        <v>-0.01963129890633197</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.02833938330146835</v>
+        <v>-0.02899653629747789</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>-0.02321622427552861</v>
+        <v>-0.01601989799369741</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>0.00437215807390201</v>
+        <v>-0.01314544881278645</v>
       </c>
       <c r="I13" s="33" t="n">
         <v>-0.0381040357777126</v>
@@ -43697,16 +43700,16 @@
         <v>0.002584511092692976</v>
       </c>
       <c r="E15" s="33" t="n">
-        <v>-0.01477726123417744</v>
+        <v>-0.01930591093983502</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>-0.03809743954358469</v>
+        <v>-0.03264571347723622</v>
       </c>
       <c r="G15" s="33" t="n">
-        <v>-0.02801829872849804</v>
+        <v>-0.02379320378198746</v>
       </c>
       <c r="H15" s="33" t="n">
-        <v>-0.09347783204601823</v>
+        <v>-0.09731335401463592</v>
       </c>
       <c r="I15" s="33" t="n">
         <v>-0.0004685045305005131</v>
@@ -43735,16 +43738,16 @@
         <v>0.0002894867885985253</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>-0.03150221586021174</v>
+        <v>-0.04192080354947503</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>-0.05667178791916472</v>
+        <v>-0.07306864572512406</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>-0.008094630244830925</v>
+        <v>-0.007296778225756584</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>-0.0151618993678353</v>
+        <v>-0.01812810376358021</v>
       </c>
       <c r="I16" s="26" t="n">
         <v>0.1138473711836303</v>
@@ -43861,7 +43864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G40"/>
+  <dimension ref="B2:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -44159,9 +44162,9 @@
           <t>QUALCOMM Incorporated</t>
         </is>
       </c>
-      <c r="D14" s="104" t="inlineStr">
-        <is>
-          <t>Reclaimed the 200 DMA</t>
+      <c r="D14" s="106" t="inlineStr">
+        <is>
+          <t>Closed above upper band</t>
         </is>
       </c>
       <c r="E14" s="26" t="n">
@@ -44189,7 +44192,7 @@
       </c>
       <c r="D15" s="105" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Reclaimed the 200 DMA</t>
         </is>
       </c>
       <c r="E15" s="33" t="n">
@@ -44207,21 +44210,21 @@
     <row r="16">
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="C16" s="101" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>QUALCOMM Incorporated</t>
         </is>
       </c>
       <c r="D16" s="104" t="inlineStr">
         <is>
-          <t>RSI crossed back above 50</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>0.01690034709569455</v>
+        <v>0.02010687288424085</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>7</v>
@@ -44245,7 +44248,7 @@
       </c>
       <c r="D17" s="105" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>RSI crossed back above 50</t>
         </is>
       </c>
       <c r="E17" s="33" t="n">
@@ -44263,21 +44266,21 @@
     <row r="18">
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C18" s="101" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="D18" s="106" t="inlineStr">
-        <is>
-          <t>Closed above upper band</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
+        </is>
+      </c>
+      <c r="D18" s="104" t="inlineStr">
+        <is>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>-0.000522909067699362</v>
+        <v>0.01690034709569455</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>7</v>
@@ -44291,24 +44294,24 @@
     <row r="19">
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C19" s="102" t="inlineStr">
         <is>
-          <t>State Street Communication Services Select Sector SPDR ETF</t>
-        </is>
-      </c>
-      <c r="D19" s="105" t="inlineStr">
-        <is>
-          <t>RSI crossed back above 50</t>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D19" s="107" t="inlineStr">
+        <is>
+          <t>Closed above upper band</t>
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>0.0138888974898479</v>
+        <v>-0.000522909067699362</v>
       </c>
       <c r="F19" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" s="30" t="inlineStr">
         <is>
@@ -44319,12 +44322,12 @@
     <row r="20">
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C20" s="101" t="inlineStr">
         <is>
-          <t>State Street Financial Select Sector SPDR ETF</t>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D20" s="104" t="inlineStr">
@@ -44333,54 +44336,54 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0.008041941928971008</v>
+        <v>0.0138888974898479</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>ARKK</t>
         </is>
       </c>
       <c r="C21" s="102" t="inlineStr">
         <is>
-          <t>State Street Financial Select Sector SPDR ETF</t>
+          <t>ARK Innovation ETF</t>
         </is>
       </c>
       <c r="D21" s="105" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>0.008041941928971008</v>
+        <v>0.003731313815136028</v>
       </c>
       <c r="F21" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" s="30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C22" s="101" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
+          <t>State Street Financial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D22" s="104" t="inlineStr">
@@ -44389,7 +44392,7 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>0.004436902672253051</v>
+        <v>0.008041941928971008</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>5</v>
@@ -44403,12 +44406,12 @@
     <row r="23">
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C23" s="102" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
+          <t>State Street Financial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D23" s="105" t="inlineStr">
@@ -44417,7 +44420,7 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>0.004436902672253051</v>
+        <v>0.008041941928971008</v>
       </c>
       <c r="F23" s="34" t="n">
         <v>5</v>
@@ -44431,12 +44434,12 @@
     <row r="24">
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C24" s="101" t="inlineStr">
         <is>
-          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
+          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
         </is>
       </c>
       <c r="D24" s="104" t="inlineStr">
@@ -44445,10 +44448,10 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>0.003284443158907635</v>
+        <v>0.004436902672253051</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
@@ -44459,12 +44462,12 @@
     <row r="25">
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C25" s="102" t="inlineStr">
         <is>
-          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
+          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
         </is>
       </c>
       <c r="D25" s="105" t="inlineStr">
@@ -44473,10 +44476,10 @@
         </is>
       </c>
       <c r="E25" s="33" t="n">
-        <v>0.003284443158907635</v>
+        <v>0.004436902672253051</v>
       </c>
       <c r="F25" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" s="30" t="inlineStr">
         <is>
@@ -44487,24 +44490,24 @@
     <row r="26">
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C26" s="101" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D26" s="104" t="inlineStr">
         <is>
-          <t>Gapped down 1.6% at the open</t>
+          <t>RSI crossed back above 50</t>
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>-0.0581369028542128</v>
+        <v>0.003284443158907635</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
@@ -44515,77 +44518,77 @@
     <row r="27">
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C27" s="102" t="inlineStr">
         <is>
-          <t>AST SpaceMobile, Inc.</t>
+          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D27" s="105" t="inlineStr">
         <is>
-          <t>Volume 1.9x its 20-day average</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E27" s="33" t="n">
-        <v>0.1182796125279308</v>
+        <v>0.003284443158907635</v>
       </c>
       <c r="F27" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C28" s="101" t="inlineStr">
         <is>
-          <t>AST SpaceMobile, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="D28" s="104" t="inlineStr">
         <is>
-          <t>Gapped up 4.5% at the open</t>
+          <t>Gapped down 1.6% at the open</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>0.1182796125279308</v>
+        <v>-0.0581369028542128</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="C29" s="102" t="inlineStr">
         <is>
-          <t>IREN Limited</t>
+          <t>AST SpaceMobile, Inc.</t>
         </is>
       </c>
       <c r="D29" s="105" t="inlineStr">
         <is>
-          <t>Gapped down 2.8% at the open</t>
+          <t>Volume 1.9x its 20-day average</t>
         </is>
       </c>
       <c r="E29" s="33" t="n">
-        <v>0.07550241179626238</v>
+        <v>0.1182796125279308</v>
       </c>
       <c r="F29" s="34" t="n">
         <v>3</v>
@@ -44599,21 +44602,21 @@
     <row r="30">
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="C30" s="101" t="inlineStr">
         <is>
-          <t>Cameco Corporation</t>
+          <t>AST SpaceMobile, Inc.</t>
         </is>
       </c>
       <c r="D30" s="104" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Gapped up 4.5% at the open</t>
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>0.001246572974491267</v>
+        <v>0.1182796125279308</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>3</v>
@@ -44627,21 +44630,21 @@
     <row r="31">
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C31" s="102" t="inlineStr">
         <is>
-          <t>State Street Industrial Select Sector SPDR ETF</t>
+          <t>IREN Limited</t>
         </is>
       </c>
       <c r="D31" s="105" t="inlineStr">
         <is>
-          <t>Closed below lower band</t>
+          <t>Gapped down 2.8% at the open</t>
         </is>
       </c>
       <c r="E31" s="33" t="n">
-        <v>0.0002894867885985253</v>
+        <v>0.07550241179626238</v>
       </c>
       <c r="F31" s="34" t="n">
         <v>3</v>
@@ -44655,24 +44658,24 @@
     <row r="32">
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C32" s="101" t="inlineStr">
         <is>
-          <t>State Street Industrial Select Sector SPDR ETF</t>
+          <t>Nebius Group N.V.</t>
         </is>
       </c>
       <c r="D32" s="104" t="inlineStr">
         <is>
-          <t>Volume 1.8x its 20-day average</t>
+          <t>Gapped down 2.0% at the open</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>0.0002894867885985253</v>
+        <v>0.02280246168613065</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
@@ -44683,21 +44686,21 @@
     <row r="33">
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C33" s="102" t="inlineStr">
         <is>
-          <t>Nebius Group N.V.</t>
+          <t>Invesco QQQ Trust</t>
         </is>
       </c>
       <c r="D33" s="105" t="inlineStr">
         <is>
-          <t>Gapped down 2.0% at the open</t>
+          <t>8 EMA crossed below 21</t>
         </is>
       </c>
       <c r="E33" s="33" t="n">
-        <v>0.02280246168613065</v>
+        <v>0.002261002137834645</v>
       </c>
       <c r="F33" s="34" t="n">
         <v>2</v>
@@ -44721,7 +44724,7 @@
       </c>
       <c r="D34" s="104" t="inlineStr">
         <is>
-          <t>8 EMA crossed below 21</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E34" s="26" t="n">
@@ -44739,21 +44742,21 @@
     <row r="35">
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="C35" s="102" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
+          <t>State Street Real Estate Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D35" s="105" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Closed below lower band</t>
         </is>
       </c>
       <c r="E35" s="33" t="n">
-        <v>0.002261002137834645</v>
+        <v>-0.007039086440657094</v>
       </c>
       <c r="F35" s="34" t="n">
         <v>2</v>
@@ -44767,40 +44770,40 @@
     <row r="36">
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C36" s="101" t="inlineStr">
         <is>
-          <t>State Street Real Estate Select Sector SPDR ETF</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D36" s="104" t="inlineStr">
         <is>
-          <t>Closed below lower band</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>-0.007039086440657094</v>
+        <v>0.005270608096960672</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Very Weak</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C37" s="102" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="D37" s="105" t="inlineStr">
@@ -44809,7 +44812,7 @@
         </is>
       </c>
       <c r="E37" s="33" t="n">
-        <v>0.005270608096960672</v>
+        <v>-0.005548155771720742</v>
       </c>
       <c r="F37" s="34" t="n">
         <v>1</v>
@@ -44823,21 +44826,21 @@
     <row r="38">
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C38" s="101" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="D38" s="104" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Lost the 200 DMA</t>
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>-0.005548155771720742</v>
+        <v>-0.006600309699600682</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>1</v>
@@ -44851,65 +44854,37 @@
     <row r="39">
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="C39" s="102" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>CoreWeave, Inc.</t>
         </is>
       </c>
       <c r="D39" s="105" t="inlineStr">
         <is>
-          <t>Lost the 200 DMA</t>
+          <t>Gapped down 2.1% at the open</t>
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>-0.006600309699600682</v>
+        <v>-0.01124005114350968</v>
       </c>
       <c r="F39" s="34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="30" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
-      </c>
-      <c r="C40" s="101" t="inlineStr">
-        <is>
-          <t>CoreWeave, Inc.</t>
-        </is>
-      </c>
-      <c r="D40" s="104" t="inlineStr">
-        <is>
-          <t>Gapped down 2.1% at the open</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="n">
-        <v>-0.01124005114350968</v>
-      </c>
-      <c r="F40" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="23" t="inlineStr">
         <is>
           <t>Very Weak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:G40"/>
+  <autoFilter ref="B5:G39"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E40">
+  <conditionalFormatting sqref="E6:E39">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -44951,14 +44926,14 @@
       <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="107" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
         <is>
           <t>Every column, in plain English. Nothing here needs to be typed in by hand any more.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="108" t="inlineStr">
+      <c r="B5" s="109" t="inlineStr">
         <is>
           <t>THE DAILY CHECKLIST</t>
         </is>
@@ -44967,194 +44942,194 @@
       <c r="D5" s="4" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="109" t="inlineStr">
+      <c r="B6" s="110" t="inlineStr">
         <is>
           <t>%change</t>
         </is>
       </c>
-      <c r="C6" s="110" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
         <is>
           <t>The day's move, close against yesterday's close.</t>
         </is>
       </c>
-      <c r="D6" s="111" t="inlineStr">
+      <c r="D6" s="112" t="inlineStr">
         <is>
           <t>Green is up, red is down. This is the same number the watchlist shows.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="109" t="inlineStr">
+      <c r="B7" s="110" t="inlineStr">
         <is>
           <t>Prev Strength</t>
         </is>
       </c>
-      <c r="C7" s="110" t="inlineStr">
+      <c r="C7" s="111" t="inlineStr">
         <is>
           <t>Rank of that move inside its own group. 1 is the strongest.</t>
         </is>
       </c>
-      <c r="D7" s="111" t="inlineStr">
+      <c r="D7" s="112" t="inlineStr">
         <is>
           <t>Sectors are ranked against the other ten sectors, not against the stocks.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="109" t="inlineStr">
+      <c r="B8" s="110" t="inlineStr">
         <is>
           <t>Price &gt; Pre-Day</t>
         </is>
       </c>
-      <c r="C8" s="110" t="inlineStr">
+      <c r="C8" s="111" t="inlineStr">
         <is>
           <t>Did it close higher than yesterday?</t>
         </is>
       </c>
-      <c r="D8" s="111" t="inlineStr">
+      <c r="D8" s="112" t="inlineStr">
         <is>
           <t>Yes, No, or Same when the two closes are within a tenth of a percent.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="109" t="inlineStr">
+      <c r="B9" s="110" t="inlineStr">
         <is>
           <t>Yest Volum &gt; 2Pre-Day</t>
         </is>
       </c>
-      <c r="C9" s="110" t="inlineStr">
+      <c r="C9" s="111" t="inlineStr">
         <is>
           <t>Did more shares trade than the day before?</t>
         </is>
       </c>
-      <c r="D9" s="111" t="inlineStr">
+      <c r="D9" s="112" t="inlineStr">
         <is>
           <t>Rising volume behind a rising price is the healthy combination.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="109" t="inlineStr">
+      <c r="B10" s="110" t="inlineStr">
         <is>
           <t>MACD (Green &gt; Red)</t>
         </is>
       </c>
-      <c r="C10" s="110" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
         <is>
           <t>Is the MACD line above its signal line?</t>
         </is>
       </c>
-      <c r="D10" s="111" t="inlineStr">
+      <c r="D10" s="112" t="inlineStr">
         <is>
           <t>Above means momentum is with the buyers. The Histogram column is the gap.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="109" t="inlineStr">
+      <c r="B11" s="110" t="inlineStr">
         <is>
           <t>Price &gt; 8 EMA</t>
         </is>
       </c>
-      <c r="C11" s="110" t="inlineStr">
+      <c r="C11" s="111" t="inlineStr">
         <is>
           <t>Above the 8-day exponential average.</t>
         </is>
       </c>
-      <c r="D11" s="111" t="inlineStr">
+      <c r="D11" s="112" t="inlineStr">
         <is>
           <t>The fastest line. Losing it first is usually the first crack.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="109" t="inlineStr">
+      <c r="B12" s="110" t="inlineStr">
         <is>
           <t>&gt; 21 EMA</t>
         </is>
       </c>
-      <c r="C12" s="110" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
         <is>
           <t>Above the 21-day exponential average.</t>
         </is>
       </c>
-      <c r="D12" s="111" t="inlineStr">
+      <c r="D12" s="112" t="inlineStr">
         <is>
           <t>The line that separates a dip from a change of trend.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="109" t="inlineStr">
+      <c r="B13" s="110" t="inlineStr">
         <is>
           <t>Price &gt; 50 DMA</t>
         </is>
       </c>
-      <c r="C13" s="110" t="inlineStr">
+      <c r="C13" s="111" t="inlineStr">
         <is>
           <t>Above the 50-day simple average.</t>
         </is>
       </c>
-      <c r="D13" s="111" t="inlineStr">
+      <c r="D13" s="112" t="inlineStr">
         <is>
           <t>The line most desks watch for the medium-term trend.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="109" t="inlineStr">
+      <c r="B14" s="110" t="inlineStr">
         <is>
           <t>Price &gt; Upper BB</t>
         </is>
       </c>
-      <c r="C14" s="110" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
         <is>
           <t>Above the top Bollinger Band.</t>
         </is>
       </c>
-      <c r="D14" s="111" t="inlineStr">
+      <c r="D14" s="112" t="inlineStr">
         <is>
           <t>Rare. Either a genuine breakout or a stretched move about to snap back.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="109" t="inlineStr">
+      <c r="B15" s="110" t="inlineStr">
         <is>
           <t>Price &gt; Lower BB</t>
         </is>
       </c>
-      <c r="C15" s="110" t="inlineStr">
+      <c r="C15" s="111" t="inlineStr">
         <is>
           <t>Above the bottom Bollinger Band.</t>
         </is>
       </c>
-      <c r="D15" s="111" t="inlineStr">
+      <c r="D15" s="112" t="inlineStr">
         <is>
           <t>Almost always Yes. A No here means something is badly wrong.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="109" t="inlineStr">
+      <c r="B16" s="110" t="inlineStr">
         <is>
           <t>Price &gt; Mid BB</t>
         </is>
       </c>
-      <c r="C16" s="110" t="inlineStr">
+      <c r="C16" s="111" t="inlineStr">
         <is>
           <t>Above the middle band, which is the 20-day average.</t>
         </is>
       </c>
-      <c r="D16" s="111" t="inlineStr">
+      <c r="D16" s="112" t="inlineStr">
         <is>
           <t>The simplest read on whether the last month has been up or down.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="108" t="inlineStr">
+      <c r="B18" s="109" t="inlineStr">
         <is>
           <t>THE NEW COLUMNS</t>
         </is>
@@ -45163,262 +45138,262 @@
       <c r="D18" s="4" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="109" t="inlineStr">
+      <c r="B19" s="110" t="inlineStr">
         <is>
           <t>Bull Score</t>
         </is>
       </c>
-      <c r="C19" s="110" t="inlineStr">
+      <c r="C19" s="111" t="inlineStr">
         <is>
           <t>Nine checks, one point each, added up.</t>
         </is>
       </c>
-      <c r="D19" s="111" t="inlineStr">
+      <c r="D19" s="112" t="inlineStr">
         <is>
           <t>8 or 9 is a strong tape. 0 or 1 is a broken one. The bar length shows it.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="109" t="inlineStr">
+      <c r="B20" s="110" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C20" s="110" t="inlineStr">
+      <c r="C20" s="111" t="inlineStr">
         <is>
           <t>The score turned into words.</t>
         </is>
       </c>
-      <c r="D20" s="111" t="inlineStr">
+      <c r="D20" s="112" t="inlineStr">
         <is>
           <t>Very Strong, Strong, Neutral, Weak, Very Weak.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="109" t="inlineStr">
+      <c r="B21" s="110" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="C21" s="110" t="inlineStr">
+      <c r="C21" s="111" t="inlineStr">
         <is>
           <t>Where the price sits against all four averages at once.</t>
         </is>
       </c>
-      <c r="D21" s="111" t="inlineStr">
+      <c r="D21" s="112" t="inlineStr">
         <is>
           <t>'Above every average' is the cleanest possible setup.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="109" t="inlineStr">
+      <c r="B22" s="110" t="inlineStr">
         <is>
           <t>Vol vs 20d Avg</t>
         </is>
       </c>
-      <c r="C22" s="110" t="inlineStr">
+      <c r="C22" s="111" t="inlineStr">
         <is>
           <t>Today's volume divided by its 20-day average.</t>
         </is>
       </c>
-      <c r="D22" s="111" t="inlineStr">
+      <c r="D22" s="112" t="inlineStr">
         <is>
           <t>2.00x means twice the usual interest. Big moves on 0.5x rarely hold.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="109" t="inlineStr">
+      <c r="B23" s="110" t="inlineStr">
         <is>
           <t>RSI (14)</t>
         </is>
       </c>
-      <c r="C23" s="110" t="inlineStr">
+      <c r="C23" s="111" t="inlineStr">
         <is>
           <t>Momentum on a 0 to 100 scale.</t>
         </is>
       </c>
-      <c r="D23" s="111" t="inlineStr">
+      <c r="D23" s="112" t="inlineStr">
         <is>
           <t>Over 70 is stretched, under 30 is beaten down, 50 is the dividing line.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="109" t="inlineStr">
+      <c r="B24" s="110" t="inlineStr">
         <is>
           <t>Stoch %K</t>
         </is>
       </c>
-      <c r="C24" s="110" t="inlineStr">
+      <c r="C24" s="111" t="inlineStr">
         <is>
           <t>Where the close sits inside the last 14 days' range.</t>
         </is>
       </c>
-      <c r="D24" s="111" t="inlineStr">
+      <c r="D24" s="112" t="inlineStr">
         <is>
           <t>100 means it closed at the top of the range, 0 at the very bottom.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="109" t="inlineStr">
+      <c r="B25" s="110" t="inlineStr">
         <is>
           <t>ADX (14)</t>
         </is>
       </c>
-      <c r="C25" s="110" t="inlineStr">
+      <c r="C25" s="111" t="inlineStr">
         <is>
           <t>How strong the trend is, whichever way it points.</t>
         </is>
       </c>
-      <c r="D25" s="111" t="inlineStr">
+      <c r="D25" s="112" t="inlineStr">
         <is>
           <t>Over 25 means a real trend. Under 20 means it is drifting sideways.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="109" t="inlineStr">
+      <c r="B26" s="110" t="inlineStr">
         <is>
           <t>MACD / Signal / Histogram</t>
         </is>
       </c>
-      <c r="C26" s="110" t="inlineStr">
+      <c r="C26" s="111" t="inlineStr">
         <is>
           <t>The three raw MACD numbers off the chart.</t>
         </is>
       </c>
-      <c r="D26" s="111" t="inlineStr">
+      <c r="D26" s="112" t="inlineStr">
         <is>
           <t>Histogram is MACD minus Signal. It crossing zero is the actual event.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="109" t="inlineStr">
+      <c r="B27" s="110" t="inlineStr">
         <is>
           <t>%B</t>
         </is>
       </c>
-      <c r="C27" s="110" t="inlineStr">
+      <c r="C27" s="111" t="inlineStr">
         <is>
           <t>Where the price sits inside the Bollinger Bands.</t>
         </is>
       </c>
-      <c r="D27" s="111" t="inlineStr">
+      <c r="D27" s="112" t="inlineStr">
         <is>
           <t>1.00 is the upper band, 0.00 is the lower, 0.50 is the middle.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="109" t="inlineStr">
+      <c r="B28" s="110" t="inlineStr">
         <is>
           <t>Band Width</t>
         </is>
       </c>
-      <c r="C28" s="110" t="inlineStr">
+      <c r="C28" s="111" t="inlineStr">
         <is>
           <t>How far apart the bands are, as a percent of the middle.</t>
         </is>
       </c>
-      <c r="D28" s="111" t="inlineStr">
+      <c r="D28" s="112" t="inlineStr">
         <is>
           <t>Narrow bands come before big moves. Wide bands come after them.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="109" t="inlineStr">
+      <c r="B29" s="110" t="inlineStr">
         <is>
           <t>ATR (14)</t>
         </is>
       </c>
-      <c r="C29" s="110" t="inlineStr">
+      <c r="C29" s="111" t="inlineStr">
         <is>
           <t>The average daily range, as a percent of price.</t>
         </is>
       </c>
-      <c r="D29" s="111" t="inlineStr">
+      <c r="D29" s="112" t="inlineStr">
         <is>
           <t>A 4% ATR means 4% swings are normal for that name. It sizes the risk.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="109" t="inlineStr">
+      <c r="B30" s="110" t="inlineStr">
         <is>
           <t>% Off 52W High</t>
         </is>
       </c>
-      <c r="C30" s="110" t="inlineStr">
+      <c r="C30" s="111" t="inlineStr">
         <is>
           <t>How far below the year's high it is trading.</t>
         </is>
       </c>
-      <c r="D30" s="111" t="inlineStr">
+      <c r="D30" s="112" t="inlineStr">
         <is>
           <t>Zero means it is at a new high right now.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="109" t="inlineStr">
+      <c r="B31" s="110" t="inlineStr">
         <is>
           <t>52W Range Position</t>
         </is>
       </c>
-      <c r="C31" s="110" t="inlineStr">
+      <c r="C31" s="111" t="inlineStr">
         <is>
           <t>Where it sits between the year's low and high.</t>
         </is>
       </c>
-      <c r="D31" s="111" t="inlineStr">
+      <c r="D31" s="112" t="inlineStr">
         <is>
           <t>100% is at the high, 0% is at the low.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="109" t="inlineStr">
+      <c r="B32" s="110" t="inlineStr">
         <is>
           <t>5-Day / 1-Month / 3-Month / YTD</t>
         </is>
       </c>
-      <c r="C32" s="110" t="inlineStr">
+      <c r="C32" s="111" t="inlineStr">
         <is>
           <t>Returns over longer windows.</t>
         </is>
       </c>
-      <c r="D32" s="111" t="inlineStr">
+      <c r="D32" s="112" t="inlineStr">
         <is>
           <t>One green day inside four red columns is noise, not a turn.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="109" t="inlineStr">
+      <c r="B33" s="110" t="inlineStr">
         <is>
           <t>Top News 1-3</t>
         </is>
       </c>
-      <c r="C33" s="110" t="inlineStr">
+      <c r="C33" s="111" t="inlineStr">
         <is>
           <t>The three most recent headlines. Click to open.</t>
         </is>
       </c>
-      <c r="D33" s="111" t="inlineStr">
+      <c r="D33" s="112" t="inlineStr">
         <is>
           <t>Straight from Yahoo Finance. Useful for explaining an odd move.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="108" t="inlineStr">
+      <c r="B35" s="109" t="inlineStr">
         <is>
           <t>THE OTHER TABS</t>
         </is>
@@ -45427,51 +45402,51 @@
       <c r="D35" s="4" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="109" t="inlineStr">
+      <c r="B36" s="110" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="C36" s="110" t="inlineStr">
+      <c r="C36" s="111" t="inlineStr">
         <is>
           <t>The whole watchlist in one screen.</t>
         </is>
       </c>
-      <c r="D36" s="111" t="inlineStr">
+      <c r="D36" s="112" t="inlineStr">
         <is>
           <t>Advancers, decliners, breadth, sector ranking, leaders and laggards.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="109" t="inlineStr">
+      <c r="B37" s="110" t="inlineStr">
         <is>
           <t>Sector Rotation</t>
         </is>
       </c>
-      <c r="C37" s="110" t="inlineStr">
+      <c r="C37" s="111" t="inlineStr">
         <is>
           <t>The eleven sectors across six time windows.</t>
         </is>
       </c>
-      <c r="D37" s="111" t="inlineStr">
+      <c r="D37" s="112" t="inlineStr">
         <is>
           <t>Green all the way across is a real trend. Green in one column is a bounce.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="109" t="inlineStr">
+      <c r="B38" s="110" t="inlineStr">
         <is>
           <t>Signals</t>
         </is>
       </c>
-      <c r="C38" s="110" t="inlineStr">
+      <c r="C38" s="111" t="inlineStr">
         <is>
           <t>Only the tickers where something actually happened.</t>
         </is>
       </c>
-      <c r="D38" s="111" t="inlineStr">
+      <c r="D38" s="112" t="inlineStr">
         <is>
           <t>Crossovers, band breaks, volume spikes, new highs and lows.</t>
         </is>
@@ -45485,7 +45460,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="112" t="inlineStr">
+      <c r="B41" s="113" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45497,7 +45472,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="113" t="inlineStr">
+      <c r="B42" s="114" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -45509,7 +45484,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="114" t="inlineStr">
+      <c r="B43" s="115" t="inlineStr">
         <is>
           <t>Same</t>
         </is>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 3 Sep 2026, 08:01 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 3 Sep 2026, 10:37 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>0.01543529989600545</v>
+        <v>0.01560876739959438</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>8</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>60.4423848474622</v>
+        <v>60.51478853366662</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>3.144178463200342</v>
+        <v>3.161435108605559</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0.01157564195890104</v>
+        <v>0.01174845011449688</v>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.009482745466561138</v>
+        <v>0.009655196091224338</v>
       </c>
     </row>
     <row r="15">
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>0.01296290601799632</v>
+        <v>0.01290846970806347</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>8</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>53.30975797119432</v>
+        <v>53.29494491643694</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>1.877148705754395</v>
+        <v>1.871785406098092</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>-0.01394414333440253</v>
+        <v>-0.013997133667914</v>
       </c>
       <c r="J16" s="26" t="n">
-        <v>0.000376483589107357</v>
+        <v>0.0003227236695815261</v>
       </c>
     </row>
     <row r="17">
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>0.01018633244166245</v>
+        <v>0.0103021113084425</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>2</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>36.44308780900172</v>
+        <v>36.50808171075061</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>-3.763345273529972</v>
+        <v>-3.75252777449977</v>
       </c>
       <c r="I18" s="26" t="n">
-        <v>-0.02382555756663962</v>
+        <v>-0.02371367685008763</v>
       </c>
       <c r="J18" s="26" t="n">
-        <v>-0.06337543563493342</v>
+        <v>-0.06326808778515758</v>
       </c>
     </row>
     <row r="19">
@@ -1688,22 +1688,22 @@
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>0.008717340089801739</v>
+        <v>0.008539397794954384</v>
       </c>
       <c r="F19" s="34" t="n">
         <v>7</v>
       </c>
       <c r="G19" s="35" t="n">
-        <v>56.81104466027816</v>
+        <v>56.75377954276501</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>2.662342166136944</v>
+        <v>2.64460384611116</v>
       </c>
       <c r="I19" s="33" t="n">
-        <v>0.01786193158923965</v>
+        <v>0.01768237614714829</v>
       </c>
       <c r="J19" s="33" t="n">
-        <v>0.02281950677930222</v>
+        <v>0.02263907679855559</v>
       </c>
     </row>
     <row r="20">
@@ -1721,22 +1721,22 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0.007968131407967594</v>
+        <v>0.008436855537846455</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>2</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>43.00853421006479</v>
+        <v>43.26204319173591</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>-3.337457584480208</v>
+        <v>-3.293377075693615</v>
       </c>
       <c r="I20" s="26" t="n">
-        <v>-0.003937053785110778</v>
+        <v>-0.003473865790152075</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>-0.01488780412621638</v>
+        <v>-0.0144297084360292</v>
       </c>
     </row>
     <row r="21">
@@ -1754,22 +1754,22 @@
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>0.001965864954553087</v>
+        <v>0.00179241147189213</v>
       </c>
       <c r="F21" s="34" t="n">
         <v>7</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>61.30211948766858</v>
+        <v>61.24050752750126</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>4.762522905060274</v>
+        <v>4.744767058530708</v>
       </c>
       <c r="I21" s="33" t="n">
-        <v>0.009966146618659355</v>
+        <v>0.009791308181914093</v>
       </c>
       <c r="J21" s="33" t="n">
-        <v>0.05561640728770745</v>
+        <v>0.05543366618982959</v>
       </c>
     </row>
     <row r="22">
@@ -1787,22 +1787,22 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>-0.003273690907203086</v>
+        <v>-0.003156747888692357</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>48.89800079075733</v>
+        <v>48.95291184688658</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>0.2714682934706225</v>
+        <v>0.2829968980809339</v>
       </c>
       <c r="I22" s="26" t="n">
-        <v>0.001998097852452752</v>
+        <v>0.00211565939470959</v>
       </c>
       <c r="J22" s="26" t="n">
-        <v>-0.0009375580609161105</v>
+        <v>-0.0008203409506870596</v>
       </c>
     </row>
     <row r="23">
@@ -1820,22 +1820,22 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>-0.005854605643518473</v>
+        <v>-0.006232329108589174</v>
       </c>
       <c r="F23" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="35" t="n">
-        <v>51.18485252513628</v>
+        <v>51.01920682289664</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>1.599653196166129</v>
+        <v>1.561834729939116</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>-0.01108397816384998</v>
+        <v>-0.0114597147397596</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>0</v>
+        <v>-0.0003799479102503112</v>
       </c>
     </row>
     <row r="24">
@@ -1853,22 +1853,22 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>-0.006913919215374764</v>
+        <v>-0.007373206433021195</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>7</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>67.85891849823807</v>
+        <v>67.62030622942083</v>
       </c>
       <c r="H24" s="29" t="n">
-        <v>9.568309040509382</v>
+        <v>9.518745306511555</v>
       </c>
       <c r="I24" s="26" t="n">
-        <v>0.037885718310118</v>
+        <v>0.03740571194106179</v>
       </c>
       <c r="J24" s="26" t="n">
-        <v>0.1280736484832767</v>
+        <v>0.1275519315673546</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -2077,11 +2077,11 @@
       </c>
       <c r="H32" s="31" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SOXL</t>
         </is>
       </c>
       <c r="I32" s="33" t="n">
-        <v>0.003979398222152097</v>
+        <v>0.003667131125943079</v>
       </c>
       <c r="J32" s="34" t="n">
         <v>2</v>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="L32" s="35" t="n">
-        <v>46.65428964450938</v>
+        <v>39.31394302464612</v>
       </c>
     </row>
     <row r="33">
@@ -2117,11 +2117,11 @@
       </c>
       <c r="H33" s="24" t="inlineStr">
         <is>
-          <t>SOXL</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>0.004043256336109913</v>
+        <v>0.004013443884859136</v>
       </c>
       <c r="J33" s="27" t="n">
         <v>2</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="L33" s="28" t="n">
-        <v>39.33796822889906</v>
+        <v>46.67148684589938</v>
       </c>
     </row>
     <row r="34">
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="C34" s="33" t="n">
-        <v>0.04823240480617752</v>
+        <v>0.04914669207938038</v>
       </c>
       <c r="D34" s="34" t="n">
         <v>8</v>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="F34" s="35" t="n">
-        <v>62.47909653795556</v>
+        <v>62.5415624260926</v>
       </c>
       <c r="H34" s="31" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="I34" s="33" t="n">
-        <v>0.007968131407967594</v>
+        <v>0.008436855537846455</v>
       </c>
       <c r="J34" s="34" t="n">
         <v>2</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="L34" s="35" t="n">
-        <v>43.00853421006479</v>
+        <v>43.26204319173591</v>
       </c>
     </row>
     <row r="35">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>0.01018633244166245</v>
+        <v>0.0103021113084425</v>
       </c>
       <c r="J35" s="27" t="n">
         <v>2</v>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="L35" s="28" t="n">
-        <v>36.44308780900172</v>
+        <v>36.50808171075061</v>
       </c>
     </row>
     <row r="36">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C37" s="26" t="n">
-        <v>0.01543529989600545</v>
+        <v>0.01560876739959438</v>
       </c>
       <c r="D37" s="27" t="n">
         <v>8</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="F37" s="28" t="n">
-        <v>60.4423848474622</v>
+        <v>60.51478853366662</v>
       </c>
       <c r="H37" s="24" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C38" s="33" t="n">
-        <v>0.01296290601799632</v>
+        <v>0.01290846970806347</v>
       </c>
       <c r="D38" s="34" t="n">
         <v>8</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F38" s="35" t="n">
-        <v>53.30975797119432</v>
+        <v>53.29494491643694</v>
       </c>
       <c r="H38" s="31" t="inlineStr">
         <is>
@@ -2501,22 +2501,22 @@
       </c>
       <c r="H45" s="24" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="I45" s="26" t="n">
-        <v>-0.007621931717695318</v>
+        <v>-0.007373206433021195</v>
       </c>
       <c r="J45" s="27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K45" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L45" s="28" t="n">
-        <v>42.78947923002418</v>
+        <v>67.62030622942083</v>
       </c>
     </row>
     <row r="46">
@@ -2541,22 +2541,22 @@
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="I46" s="33" t="n">
-        <v>-0.006913919215374764</v>
+        <v>-0.007113790014099619</v>
       </c>
       <c r="J46" s="34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K46" s="30" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="L46" s="35" t="n">
-        <v>67.85891849823807</v>
+        <v>42.85202081378689</v>
       </c>
     </row>
     <row r="47">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="C47" s="26" t="n">
-        <v>0.04823240480617752</v>
+        <v>0.04914669207938038</v>
       </c>
       <c r="D47" s="27" t="n">
         <v>8</v>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="F47" s="28" t="n">
-        <v>62.47909653795556</v>
+        <v>62.5415624260926</v>
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="I47" s="26" t="n">
-        <v>-0.005854605643518473</v>
+        <v>-0.006232329108589174</v>
       </c>
       <c r="J47" s="27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47" s="23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="L47" s="28" t="n">
-        <v>51.18485252513628</v>
+        <v>51.01920682289664</v>
       </c>
     </row>
     <row r="48">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="I49" s="26" t="n">
-        <v>-0.003273690907203086</v>
+        <v>-0.003156747888692357</v>
       </c>
       <c r="J49" s="27" t="n">
         <v>3</v>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L49" s="28" t="n">
-        <v>48.89800079075733</v>
+        <v>48.95291184688658</v>
       </c>
     </row>
     <row r="50">
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="C50" s="33" t="n">
-        <v>0.04394065917242362</v>
+        <v>0.04399258781898019</v>
       </c>
       <c r="D50" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F50" s="35" t="n">
-        <v>53.85734515399562</v>
+        <v>53.86463558689864</v>
       </c>
       <c r="H50" s="31" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 3 Sep 2026, 08:01 PM · Yahoo Finance data</t>
+          <t>Built 3 Sep 2026, 10:37 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="C7" s="26" t="n">
-        <v>0.01018633244166245</v>
+        <v>0.0103021113084425</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>5</v>
@@ -3605,76 +3605,76 @@
         </is>
       </c>
       <c r="R7" s="70" t="n">
-        <v>174.5399932861328</v>
+        <v>174.5599975585938</v>
       </c>
       <c r="S7" s="71" t="n">
-        <v>1.759994506835938</v>
+        <v>1.779998779296875</v>
       </c>
       <c r="T7" s="72" t="n">
         <v>173.7599945068359</v>
       </c>
       <c r="U7" s="72" t="n">
-        <v>174.5500030517578</v>
+        <v>174.5599975585938</v>
       </c>
       <c r="V7" s="72" t="n">
         <v>172.0200042724609</v>
       </c>
       <c r="W7" s="73" t="n">
-        <v>7835876</v>
+        <v>8340536</v>
       </c>
       <c r="X7" s="74" t="n">
-        <v>1.241891757562664</v>
+        <v>1.31660899058603</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>36.44308780900172</v>
+        <v>36.50808171075061</v>
       </c>
       <c r="Z7" s="28" t="n">
-        <v>18.51615331547175</v>
+        <v>18.64300345523912</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>25.31380752301438</v>
+        <v>25.30789385702951</v>
       </c>
       <c r="AB7" s="75" t="n">
-        <v>-2.153873731340553</v>
+        <v>-2.152277948922034</v>
       </c>
       <c r="AC7" s="75" t="n">
-        <v>-1.113390433685862</v>
+        <v>-1.113071277202158</v>
       </c>
       <c r="AD7" s="75" t="n">
-        <v>-1.040483297654691</v>
+        <v>-1.039206671719876</v>
       </c>
       <c r="AE7" s="72" t="n">
-        <v>175.9471690671849</v>
+        <v>175.9516144610652</v>
       </c>
       <c r="AF7" s="72" t="n">
-        <v>178.9338963206002</v>
+        <v>178.9357148908239</v>
       </c>
       <c r="AG7" s="72" t="n">
-        <v>181.3653994750977</v>
+        <v>181.3657995605469</v>
       </c>
       <c r="AH7" s="72" t="n">
-        <v>177.6534996032715</v>
+        <v>177.6536996459961</v>
       </c>
       <c r="AI7" s="72" t="n">
-        <v>170.6227997589111</v>
+        <v>170.6228997802734</v>
       </c>
       <c r="AJ7" s="72" t="n">
-        <v>189.763689617162</v>
+        <v>189.7619603825642</v>
       </c>
       <c r="AK7" s="72" t="n">
-        <v>180.7189994812012</v>
+        <v>180.7199996948242</v>
       </c>
       <c r="AL7" s="72" t="n">
-        <v>171.6743093452403</v>
+        <v>171.6780390070842</v>
       </c>
       <c r="AM7" s="76" t="n">
-        <v>0.1584180274733118</v>
+        <v>0.1593657974767113</v>
       </c>
       <c r="AN7" s="29" t="n">
-        <v>10.0096726541491</v>
+        <v>10.00659661687565</v>
       </c>
       <c r="AO7" s="77" t="n">
-        <v>1.439149376148468</v>
+        <v>1.43939341945109</v>
       </c>
       <c r="AP7" s="72" t="n">
         <v>188.1900024414062</v>
@@ -3683,22 +3683,22 @@
         <v>147.1399993896484</v>
       </c>
       <c r="AR7" s="29" t="n">
-        <v>-7.253312598007655</v>
+        <v>-7.24268277059843</v>
       </c>
       <c r="AS7" s="78" t="n">
-        <v>66.7478486224158</v>
+        <v>66.79658009860039</v>
       </c>
       <c r="AT7" s="26" t="n">
-        <v>-0.02382555756663962</v>
+        <v>-0.02371367685008763</v>
       </c>
       <c r="AU7" s="26" t="n">
-        <v>-0.06337543563493342</v>
+        <v>-0.06326808778515758</v>
       </c>
       <c r="AV7" s="26" t="n">
-        <v>-0.009196243995793107</v>
+        <v>-0.009082686593175682</v>
       </c>
       <c r="AW7" s="26" t="n">
-        <v>0.1251933907957785</v>
+        <v>0.1253223507821801</v>
       </c>
       <c r="AX7" s="79" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>0.001965864954553087</v>
+        <v>0.00179241147189213</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>8</v>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="R8" s="81" t="n">
-        <v>173.2899932861328</v>
+        <v>173.2599945068359</v>
       </c>
       <c r="S8" s="82" t="n">
-        <v>0.339996337890625</v>
+        <v>0.30999755859375</v>
       </c>
       <c r="T8" s="83" t="n">
         <v>174.0700073242188</v>
@@ -3810,61 +3810,61 @@
         <v>171.3899993896484</v>
       </c>
       <c r="W8" s="84" t="n">
-        <v>5571056</v>
+        <v>5933824</v>
       </c>
       <c r="X8" s="85" t="n">
-        <v>0.746844129311832</v>
+        <v>0.7935464651417891</v>
       </c>
       <c r="Y8" s="35" t="n">
-        <v>61.30211948766858</v>
+        <v>61.24050752750126</v>
       </c>
       <c r="Z8" s="35" t="n">
-        <v>69.18052956779573</v>
+        <v>68.90121146767028</v>
       </c>
       <c r="AA8" s="35" t="n">
         <v>27.67604920258904</v>
       </c>
       <c r="AB8" s="86" t="n">
-        <v>2.385782238825414</v>
+        <v>2.383389173810258</v>
       </c>
       <c r="AC8" s="86" t="n">
-        <v>2.721020654964855</v>
+        <v>2.720542041961823</v>
       </c>
       <c r="AD8" s="86" t="n">
-        <v>-0.3352384161394411</v>
+        <v>-0.3371528681515654</v>
       </c>
       <c r="AE8" s="83" t="n">
-        <v>172.3412267109</v>
+        <v>172.3345603155007</v>
       </c>
       <c r="AF8" s="83" t="n">
-        <v>170.4057594910344</v>
+        <v>170.4030323292801</v>
       </c>
       <c r="AG8" s="83" t="n">
-        <v>165.4121994018555</v>
+        <v>165.4115994262695</v>
       </c>
       <c r="AH8" s="83" t="n">
-        <v>156.7725999450684</v>
+        <v>156.7722999572754</v>
       </c>
       <c r="AI8" s="83" t="n">
-        <v>155.2762998962402</v>
+        <v>155.2761499023437</v>
       </c>
       <c r="AJ8" s="83" t="n">
-        <v>176.9101711652937</v>
+        <v>176.9063765261217</v>
       </c>
       <c r="AK8" s="83" t="n">
-        <v>171.0254974365234</v>
+        <v>171.0239974975586</v>
       </c>
       <c r="AL8" s="83" t="n">
-        <v>165.1408237077531</v>
+        <v>165.1416184689955</v>
       </c>
       <c r="AM8" s="87" t="n">
-        <v>0.6924062364356923</v>
+        <v>0.6900589029047605</v>
       </c>
       <c r="AN8" s="36" t="n">
-        <v>6.881633226594673</v>
+        <v>6.879010097570775</v>
       </c>
       <c r="AO8" s="88" t="n">
-        <v>1.532508124251243</v>
+        <v>1.532773467518285</v>
       </c>
       <c r="AP8" s="83" t="n">
         <v>176.6000061035156</v>
@@ -3873,22 +3873,22 @@
         <v>133.7299957275391</v>
       </c>
       <c r="AR8" s="36" t="n">
-        <v>-1.874299378813504</v>
+        <v>-1.891286229470401</v>
       </c>
       <c r="AS8" s="89" t="n">
-        <v>92.27895494226969</v>
+        <v>92.20897880036119</v>
       </c>
       <c r="AT8" s="33" t="n">
-        <v>0.009966146618659355</v>
+        <v>0.009791308181914093</v>
       </c>
       <c r="AU8" s="33" t="n">
-        <v>0.05561640728770745</v>
+        <v>0.05543366618982959</v>
       </c>
       <c r="AV8" s="33" t="n">
-        <v>0.1394660126230156</v>
+        <v>0.1392687560545276</v>
       </c>
       <c r="AW8" s="33" t="n">
-        <v>0.1194443790042614</v>
+        <v>0.1192505884441486</v>
       </c>
       <c r="AX8" s="90" t="inlineStr">
         <is>
@@ -3897,12 +3897,12 @@
       </c>
       <c r="AY8" s="90" t="inlineStr">
         <is>
+          <t>Bristol-Myers Squibb Stock: Is BMY Outperforming the Healthcare Sector?</t>
+        </is>
+      </c>
+      <c r="AZ8" s="90" t="inlineStr">
+        <is>
           <t>Abbott Laboratories Stock: Is ABT Underperforming the Healthcare Sector?</t>
-        </is>
-      </c>
-      <c r="AZ8" s="90" t="inlineStr">
-        <is>
-          <t>How Is AbbVie’s Stock Performance Compared to Other Healthcare Stocks</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="C9" s="26" t="n">
-        <v>0.01543529989600545</v>
+        <v>0.01560876739959438</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>1</v>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="R9" s="70" t="n">
-        <v>58.54999923706055</v>
+        <v>58.56000137329102</v>
       </c>
       <c r="S9" s="71" t="n">
-        <v>0.8899993896484375</v>
+        <v>0.9000015258789062</v>
       </c>
       <c r="T9" s="72" t="n">
         <v>58</v>
@@ -4000,61 +4000,61 @@
         <v>57.99900054931641</v>
       </c>
       <c r="W9" s="73" t="n">
-        <v>31745401</v>
+        <v>32643053</v>
       </c>
       <c r="X9" s="74" t="n">
-        <v>1.15796305916888</v>
+        <v>1.188760123219851</v>
       </c>
       <c r="Y9" s="28" t="n">
-        <v>60.4423848474622</v>
+        <v>60.51478853366662</v>
       </c>
       <c r="Z9" s="28" t="n">
-        <v>97.04146285858748</v>
+        <v>97.63330572001905</v>
       </c>
       <c r="AA9" s="28" t="n">
         <v>20.01864967579689</v>
       </c>
       <c r="AB9" s="75" t="n">
-        <v>0.3353941092978303</v>
+        <v>0.3361920005070971</v>
       </c>
       <c r="AC9" s="75" t="n">
-        <v>0.4113443820370709</v>
+        <v>0.4115039602789242</v>
       </c>
       <c r="AD9" s="75" t="n">
-        <v>-0.0759502727392406</v>
+        <v>-0.07531195977182714</v>
       </c>
       <c r="AE9" s="72" t="n">
-        <v>57.91020396099223</v>
+        <v>57.91242665793233</v>
       </c>
       <c r="AF9" s="72" t="n">
-        <v>57.67634644961277</v>
+        <v>57.67725573472463</v>
       </c>
       <c r="AG9" s="72" t="n">
-        <v>56.76520004272461</v>
+        <v>56.76540008544922</v>
       </c>
       <c r="AH9" s="72" t="n">
-        <v>54.42589992523193</v>
+        <v>54.42599994659424</v>
       </c>
       <c r="AI9" s="72" t="n">
-        <v>53.45440002441406</v>
+        <v>53.45445003509521</v>
       </c>
       <c r="AJ9" s="72" t="n">
-        <v>58.61799333221823</v>
+        <v>58.62032940234909</v>
       </c>
       <c r="AK9" s="72" t="n">
-        <v>57.83849983215332</v>
+        <v>57.83899993896485</v>
       </c>
       <c r="AL9" s="72" t="n">
-        <v>57.0590063320884</v>
+        <v>57.0576704755806</v>
       </c>
       <c r="AM9" s="76" t="n">
-        <v>0.9563857202452463</v>
+        <v>0.9613939881412046</v>
       </c>
       <c r="AN9" s="29" t="n">
-        <v>2.695413962419487</v>
+        <v>2.701739187083979</v>
       </c>
       <c r="AO9" s="77" t="n">
-        <v>1.130793263502062</v>
+        <v>1.130600122313456</v>
       </c>
       <c r="AP9" s="72" t="n">
         <v>58.59999847412109</v>
@@ -4063,36 +4063,36 @@
         <v>47.66999816894531</v>
       </c>
       <c r="AR9" s="29" t="n">
-        <v>-0.08532293235916644</v>
+        <v>-0.06825444005384984</v>
       </c>
       <c r="AS9" s="78" t="n">
-        <v>99.54255045137674</v>
+        <v>99.63406130179943</v>
       </c>
       <c r="AT9" s="26" t="n">
-        <v>0.01157564195890104</v>
+        <v>0.01174845011449688</v>
       </c>
       <c r="AU9" s="26" t="n">
-        <v>0.009482745466561138</v>
+        <v>0.009655196091224338</v>
       </c>
       <c r="AV9" s="26" t="n">
-        <v>0.1218624406534616</v>
+        <v>0.1220540891779616</v>
       </c>
       <c r="AW9" s="26" t="n">
-        <v>0.06901586174372687</v>
+        <v>0.06919848245117377</v>
       </c>
       <c r="AX9" s="79" t="inlineStr">
         <is>
+          <t>Sector Update: Financial Stocks Gain Late Afternoon</t>
+        </is>
+      </c>
+      <c r="AY9" s="79" t="inlineStr">
+        <is>
           <t>Sector Update: Financial Stocks Higher Thursday Afternoon</t>
         </is>
       </c>
-      <c r="AY9" s="79" t="inlineStr">
+      <c r="AZ9" s="79" t="inlineStr">
         <is>
           <t>Exchange-Traded Funds Rise as US Equities Advance After Midday</t>
-        </is>
-      </c>
-      <c r="AZ9" s="79" t="inlineStr">
-        <is>
-          <t>Sector Update: Financial Stocks Higher Late Afternoon</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>-0.006913919215374764</v>
+        <v>-0.007373206433021195</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>11</v>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="R10" s="81" t="n">
-        <v>64.64990234375</v>
+        <v>64.62000274658203</v>
       </c>
       <c r="S10" s="82" t="n">
-        <v>-0.4500961303710938</v>
+        <v>-0.4799957275390625</v>
       </c>
       <c r="T10" s="83" t="n">
         <v>65.12000274658203</v>
@@ -4190,61 +4190,61 @@
         <v>64.58249664306641</v>
       </c>
       <c r="W10" s="84" t="n">
-        <v>23356482</v>
+        <v>24069781</v>
       </c>
       <c r="X10" s="85" t="n">
-        <v>0.919676734864996</v>
+        <v>0.9464342422426696</v>
       </c>
       <c r="Y10" s="35" t="n">
-        <v>67.85891849823807</v>
+        <v>67.62030622942083</v>
       </c>
       <c r="Z10" s="35" t="n">
-        <v>79.33265375467209</v>
+        <v>78.62244874844264</v>
       </c>
       <c r="AA10" s="35" t="n">
         <v>28.38186567925541</v>
       </c>
       <c r="AB10" s="86" t="n">
-        <v>1.493461536769338</v>
+        <v>1.491076383718905</v>
       </c>
       <c r="AC10" s="86" t="n">
-        <v>1.423253159474421</v>
+        <v>1.422776128864334</v>
       </c>
       <c r="AD10" s="86" t="n">
-        <v>0.07020837729491736</v>
+        <v>0.06830025485457081</v>
       </c>
       <c r="AE10" s="83" t="n">
-        <v>63.89730620972787</v>
+        <v>63.89066185480165</v>
       </c>
       <c r="AF10" s="83" t="n">
-        <v>62.42400394485963</v>
+        <v>62.42128579966254</v>
       </c>
       <c r="AG10" s="83" t="n">
-        <v>59.00419830322266</v>
+        <v>59.0036003112793</v>
       </c>
       <c r="AH10" s="83" t="n">
-        <v>58.13069911956787</v>
+        <v>58.13040012359619</v>
       </c>
       <c r="AI10" s="83" t="n">
-        <v>54.73654941558838</v>
+        <v>54.73639991760254</v>
       </c>
       <c r="AJ10" s="83" t="n">
-        <v>66.06958407987308</v>
+        <v>66.06453981783808</v>
       </c>
       <c r="AK10" s="83" t="n">
-        <v>62.54449520111084</v>
+        <v>62.54300022125244</v>
       </c>
       <c r="AL10" s="83" t="n">
-        <v>59.01940632234859</v>
+        <v>59.0214606246668</v>
       </c>
       <c r="AM10" s="87" t="n">
-        <v>0.7986317813607056</v>
+        <v>0.7948997829448485</v>
       </c>
       <c r="AN10" s="36" t="n">
-        <v>11.27225942883503</v>
+        <v>11.26117897807212</v>
       </c>
       <c r="AO10" s="88" t="n">
-        <v>1.805156816068809</v>
+        <v>1.805992059945803</v>
       </c>
       <c r="AP10" s="83" t="n">
         <v>65.51999664306641</v>
@@ -4253,22 +4253,22 @@
         <v>42.34999847412109</v>
       </c>
       <c r="AR10" s="36" t="n">
-        <v>-1.327982820353946</v>
+        <v>-1.373617128503957</v>
       </c>
       <c r="AS10" s="89" t="n">
-        <v>96.24473729789676</v>
+        <v>96.11569284588622</v>
       </c>
       <c r="AT10" s="33" t="n">
-        <v>0.037885718310118</v>
+        <v>0.03740571194106179</v>
       </c>
       <c r="AU10" s="33" t="n">
-        <v>0.1280736484832767</v>
+        <v>0.1275519315673546</v>
       </c>
       <c r="AV10" s="33" t="n">
-        <v>0.100423869680851</v>
+        <v>0.09991494036735382</v>
       </c>
       <c r="AW10" s="33" t="n">
-        <v>0.4459830835962213</v>
+        <v>0.4453143383987213</v>
       </c>
       <c r="AX10" s="90" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>-0.003273690907203086</v>
+        <v>-0.003156747888692357</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>9</v>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="R11" s="70" t="n">
-        <v>85.25</v>
+        <v>85.26000213623047</v>
       </c>
       <c r="S11" s="71" t="n">
-        <v>-0.279998779296875</v>
+        <v>-0.2699966430664062</v>
       </c>
       <c r="T11" s="72" t="n">
         <v>85.37000274658203</v>
@@ -4380,61 +4380,61 @@
         <v>84.78500366210938</v>
       </c>
       <c r="W11" s="73" t="n">
-        <v>9952632</v>
+        <v>10264950</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>1.15490762915421</v>
+        <v>1.188994593899611</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>48.89800079075733</v>
+        <v>48.95291184688658</v>
       </c>
       <c r="Z11" s="28" t="n">
-        <v>22.9167549696944</v>
+        <v>23.26405077777307</v>
       </c>
       <c r="AA11" s="28" t="n">
         <v>14.15434989105051</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>0.0930269268367141</v>
+        <v>0.09382481804597376</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.215834653576467</v>
+        <v>0.2159942318183189</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.1228077267397529</v>
+        <v>-0.1221694137723452</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>85.48125911562225</v>
+        <v>85.48348181256236</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.50395898536421</v>
+        <v>85.50486827047607</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>85.01919982910157</v>
+        <v>85.01939987182617</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.35560005187989</v>
+        <v>84.35570007324219</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.28665019989013</v>
+        <v>83.28670021057128</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>86.98783487597555</v>
+        <v>86.9878533534679</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.59099960327148</v>
+        <v>85.59149971008301</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>84.19416433056742</v>
+        <v>84.19514606669813</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.3779385050137803</v>
+        <v>0.3812988473861946</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.263977005009009</v>
+        <v>3.262832519852175</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.318194764009776</v>
+        <v>1.318040122169786</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -4443,22 +4443,22 @@
         <v>75.16000366210938</v>
       </c>
       <c r="AR11" s="29" t="n">
-        <v>-5.424893968004618</v>
+        <v>-5.413797744021709</v>
       </c>
       <c r="AS11" s="78" t="n">
-        <v>67.35647006454938</v>
+        <v>67.42324001837574</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>0.001998097852452752</v>
+        <v>0.00211565939470959</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>-0.0009375580609161105</v>
+        <v>-0.0008203409506870596</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.03912724340139673</v>
+        <v>0.03924916119904243</v>
       </c>
       <c r="AW11" s="26" t="n">
-        <v>0.09745107704794687</v>
+        <v>0.09757983781250879</v>
       </c>
       <c r="AX11" s="79" t="inlineStr">
         <is>
@@ -4570,10 +4570,10 @@
         <v>115.8300018310547</v>
       </c>
       <c r="W12" s="84" t="n">
-        <v>5319546</v>
+        <v>5658526</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>1.066299352650941</v>
+        <v>1.130407198630101</v>
       </c>
       <c r="Y12" s="35" t="n">
         <v>49.40193762534471</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>0.008717340089801739</v>
+        <v>0.008539397794954384</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>6</v>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="R13" s="70" t="n">
-        <v>113.4000015258789</v>
+        <v>113.379997253418</v>
       </c>
       <c r="S13" s="71" t="n">
-        <v>0.9800033569335938</v>
+        <v>0.9599990844726562</v>
       </c>
       <c r="T13" s="72" t="n">
         <v>113.4150009155273</v>
@@ -4760,61 +4760,61 @@
         <v>112.8450012207031</v>
       </c>
       <c r="W13" s="73" t="n">
-        <v>3244198</v>
+        <v>3366972</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>0.8100592228515445</v>
+        <v>0.8394285695195491</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>56.81104466027816</v>
+        <v>56.75377954276501</v>
       </c>
       <c r="Z13" s="28" t="n">
-        <v>77.97031712968646</v>
+        <v>77.47516198296228</v>
       </c>
       <c r="AA13" s="28" t="n">
         <v>13.49986566465467</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.5163016908110194</v>
+        <v>0.5147059083924859</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.4543890005497054</v>
+        <v>0.4540698440659988</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>0.06191269026131396</v>
+        <v>0.0606360643264871</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>112.2173063679453</v>
+        <v>112.2128609740651</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.6617569070491</v>
+        <v>111.6599383368254</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.4591996765137</v>
+        <v>110.4587995910644</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.582799911499</v>
+        <v>112.5825998687744</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0189999771118</v>
+        <v>114.0188999557495</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.642670034062</v>
+        <v>113.6382058003006</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.7744998931885</v>
+        <v>111.7734996795654</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.906329752315</v>
+        <v>109.9087935588303</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.9350518181203786</v>
+        <v>0.9307642786143717</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>3.342748377597231</v>
+        <v>3.336580005244354</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.511676335240576</v>
+        <v>1.511943048823355</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -4823,22 +4823,22 @@
         <v>105.0299987792969</v>
       </c>
       <c r="AR13" s="29" t="n">
-        <v>-5.817862484478886</v>
+        <v>-5.834476638927411</v>
       </c>
       <c r="AS13" s="78" t="n">
-        <v>54.43904225419207</v>
+        <v>54.30893316501524</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>0.01786193158923965</v>
+        <v>0.01768237614714829</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>0.02281950677930222</v>
+        <v>0.02263907679855559</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>0.002563883953341728</v>
+        <v>0.00238702715594985</v>
       </c>
       <c r="AW13" s="26" t="n">
-        <v>-0.03669724473350133</v>
+        <v>-0.03686717569046283</v>
       </c>
       <c r="AX13" s="79" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C14" s="33" t="n">
-        <v>-0.005854605643518473</v>
+        <v>-0.006232329108589174</v>
       </c>
       <c r="D14" s="34" t="n">
         <v>10</v>
@@ -4878,24 +4878,24 @@
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="30" t="inlineStr">
+        <is>
           <t>Same</t>
         </is>
       </c>
-      <c r="G14" s="30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" s="30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I14" s="30" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
       <c r="J14" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="N14" s="80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O14" s="30" t="inlineStr">
         <is>
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="R14" s="81" t="n">
-        <v>52.63999938964844</v>
+        <v>52.61999893188477</v>
       </c>
       <c r="S14" s="82" t="n">
-        <v>-0.3100013732910156</v>
+        <v>-0.3300018310546875</v>
       </c>
       <c r="T14" s="83" t="n">
         <v>53.45000076293945</v>
@@ -4950,61 +4950,61 @@
         <v>52.33499908447266</v>
       </c>
       <c r="W14" s="84" t="n">
-        <v>13039854</v>
+        <v>14287443</v>
       </c>
       <c r="X14" s="85" t="n">
-        <v>1.200175312233383</v>
+        <v>1.307495394703732</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>51.18485252513628</v>
+        <v>51.01920682289664</v>
       </c>
       <c r="Z14" s="35" t="n">
-        <v>36.47540535089762</v>
+        <v>35.65571399760174</v>
       </c>
       <c r="AA14" s="35" t="n">
         <v>14.79868881918597</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.2819247713413375</v>
+        <v>0.2803292932291299</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.3852990069094271</v>
+        <v>0.3849799112869856</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>-0.1033742355680896</v>
+        <v>-0.1046506180578556</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>52.81552252679378</v>
+        <v>52.81107798062408</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.63827511159779</v>
+        <v>52.63645688816472</v>
       </c>
       <c r="AG14" s="83" t="n">
-        <v>51.81119987487793</v>
+        <v>51.81079986572266</v>
       </c>
       <c r="AH14" s="83" t="n">
-        <v>51.56830001831054</v>
+        <v>51.56810001373291</v>
       </c>
       <c r="AI14" s="83" t="n">
-        <v>50.02227499008179</v>
+        <v>50.02217498779297</v>
       </c>
       <c r="AJ14" s="83" t="n">
-        <v>53.90641538850587</v>
+        <v>53.90620090904133</v>
       </c>
       <c r="AK14" s="83" t="n">
-        <v>52.84000034332276</v>
+        <v>52.83900032043457</v>
       </c>
       <c r="AL14" s="83" t="n">
-        <v>51.77358529813964</v>
+        <v>51.77179973182781</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.4062274324721398</v>
+        <v>0.3973944585076951</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>4.036393028971179</v>
+        <v>4.03944276816319</v>
       </c>
       <c r="AO14" s="88" t="n">
-        <v>1.623349448464686</v>
+        <v>1.623966471131708</v>
       </c>
       <c r="AP14" s="83" t="n">
         <v>54.18999862670898</v>
@@ -5013,22 +5013,22 @@
         <v>42.03499984741211</v>
       </c>
       <c r="AR14" s="36" t="n">
-        <v>-2.860304994170249</v>
+        <v>-2.897213018290068</v>
       </c>
       <c r="AS14" s="89" t="n">
-        <v>87.24805106767597</v>
+        <v>87.08350594408667</v>
       </c>
       <c r="AT14" s="33" t="n">
-        <v>-0.01108397816384998</v>
+        <v>-0.0114597147397596</v>
       </c>
       <c r="AU14" s="33" t="n">
-        <v>0</v>
+        <v>-0.0003799479102503112</v>
       </c>
       <c r="AV14" s="33" t="n">
-        <v>0.01975979230665259</v>
+        <v>0.01937233670460836</v>
       </c>
       <c r="AW14" s="33" t="n">
-        <v>0.1607497499627784</v>
+        <v>0.1603087255209565</v>
       </c>
       <c r="AX14" s="90" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>0.01296290601799632</v>
+        <v>0.01290846970806347</v>
       </c>
       <c r="D15" s="27" t="n">
         <v>3</v>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="R15" s="70" t="n">
-        <v>185.9799957275391</v>
+        <v>185.9700012207031</v>
       </c>
       <c r="S15" s="71" t="n">
-        <v>2.379989624023438</v>
+        <v>2.3699951171875</v>
       </c>
       <c r="T15" s="72" t="n">
         <v>183.5200042724609</v>
@@ -5140,61 +5140,61 @@
         <v>182.5</v>
       </c>
       <c r="W15" s="73" t="n">
-        <v>5835122</v>
+        <v>6090009</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>0.9668648026996621</v>
+        <v>1.006972497100184</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>53.30975797119432</v>
+        <v>53.29494491643694</v>
       </c>
       <c r="Z15" s="28" t="n">
-        <v>55.37503835351318</v>
+        <v>55.29774127310062</v>
       </c>
       <c r="AA15" s="28" t="n">
         <v>11.28058245136133</v>
       </c>
       <c r="AB15" s="75" t="n">
-        <v>0.6876754241711183</v>
+        <v>0.6868781415745104</v>
       </c>
       <c r="AC15" s="75" t="n">
-        <v>0.8479187452147254</v>
+        <v>0.847759288695404</v>
       </c>
       <c r="AD15" s="75" t="n">
-        <v>-0.1602433210436072</v>
+        <v>-0.1608811471208935</v>
       </c>
       <c r="AE15" s="72" t="n">
-        <v>184.879065831376</v>
+        <v>184.8768448298569</v>
       </c>
       <c r="AF15" s="72" t="n">
-        <v>184.3666050254255</v>
+        <v>184.3656964338949</v>
       </c>
       <c r="AG15" s="72" t="n">
-        <v>182.5532006835938</v>
+        <v>182.553000793457</v>
       </c>
       <c r="AH15" s="72" t="n">
-        <v>178.6247009277344</v>
+        <v>178.624600982666</v>
       </c>
       <c r="AI15" s="72" t="n">
-        <v>160.1278751373291</v>
+        <v>160.1278251647949</v>
       </c>
       <c r="AJ15" s="72" t="n">
-        <v>191.5917482899507</v>
+        <v>191.5911659134844</v>
       </c>
       <c r="AK15" s="72" t="n">
-        <v>185.7330009460449</v>
+        <v>185.7325012207031</v>
       </c>
       <c r="AL15" s="72" t="n">
-        <v>179.8742536021391</v>
+        <v>179.8738365279218</v>
       </c>
       <c r="AM15" s="76" t="n">
-        <v>0.5210791460183953</v>
+        <v>0.5202691238067136</v>
       </c>
       <c r="AN15" s="29" t="n">
-        <v>6.308784453019991</v>
+        <v>6.30871242703991</v>
       </c>
       <c r="AO15" s="77" t="n">
-        <v>2.017235271040187</v>
+        <v>2.017343682459092</v>
       </c>
       <c r="AP15" s="72" t="n">
         <v>198.7299957275391</v>
@@ -5203,22 +5203,22 @@
         <v>126.6800003051758</v>
       </c>
       <c r="AR15" s="29" t="n">
-        <v>-6.415740086604938</v>
+        <v>-6.420769275479699</v>
       </c>
       <c r="AS15" s="78" t="n">
-        <v>82.30395446209484</v>
+        <v>82.29008283479304</v>
       </c>
       <c r="AT15" s="26" t="n">
-        <v>-0.01394414333440253</v>
+        <v>-0.013997133667914</v>
       </c>
       <c r="AU15" s="26" t="n">
-        <v>0.000376483589107357</v>
+        <v>0.0003227236695815261</v>
       </c>
       <c r="AV15" s="26" t="n">
-        <v>-0.03722111357643598</v>
+        <v>-0.03727285301284267</v>
       </c>
       <c r="AW15" s="26" t="n">
-        <v>0.291796861503359</v>
+        <v>0.2917274407438175</v>
       </c>
       <c r="AX15" s="79" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         <v>43.84000015258789</v>
       </c>
       <c r="W16" s="84" t="n">
-        <v>4143450</v>
+        <v>4414470</v>
       </c>
       <c r="X16" s="85" t="n">
-        <v>0.8075550724221049</v>
+        <v>0.8581103153064147</v>
       </c>
       <c r="Y16" s="35" t="n">
         <v>43.70604864099334</v>
@@ -5412,17 +5412,17 @@
       </c>
       <c r="AX16" s="90" t="inlineStr">
         <is>
+          <t>Sector Update: Financial Stocks Gain Late Afternoon</t>
+        </is>
+      </c>
+      <c r="AY16" s="90" t="inlineStr">
+        <is>
           <t>Sector Update: Financial Stocks Higher Thursday Afternoon</t>
         </is>
       </c>
-      <c r="AY16" s="90" t="inlineStr">
+      <c r="AZ16" s="90" t="inlineStr">
         <is>
           <t>Sector Update: Financial Stocks Higher Late Afternoon</t>
-        </is>
-      </c>
-      <c r="AZ16" s="90" t="inlineStr">
-        <is>
-          <t>Sector Update: Financial Stocks Rise Wednesday Afternoon</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>0.007968131407967594</v>
+        <v>0.008436855537846455</v>
       </c>
       <c r="D17" s="27" t="n">
         <v>7</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="R17" s="70" t="n">
-        <v>43.0099983215332</v>
+        <v>43.02999877929688</v>
       </c>
       <c r="S17" s="71" t="n">
-        <v>0.3400001525878906</v>
+        <v>0.3600006103515625</v>
       </c>
       <c r="T17" s="72" t="n">
         <v>42.81999969482422</v>
@@ -5520,61 +5520,61 @@
         <v>42.79000091552734</v>
       </c>
       <c r="W17" s="73" t="n">
-        <v>20601238</v>
+        <v>22875638</v>
       </c>
       <c r="X17" s="74" t="n">
-        <v>1.029162828498838</v>
+        <v>1.136328048216559</v>
       </c>
       <c r="Y17" s="28" t="n">
-        <v>43.00853421006479</v>
+        <v>43.26204319173591</v>
       </c>
       <c r="Z17" s="28" t="n">
-        <v>41.21854243063133</v>
+        <v>41.93540448083218</v>
       </c>
       <c r="AA17" s="28" t="n">
         <v>16.71578460388293</v>
       </c>
       <c r="AB17" s="75" t="n">
-        <v>-0.4935861129895756</v>
+        <v>-0.491990634877375</v>
       </c>
       <c r="AC17" s="75" t="n">
-        <v>-0.4643723743420835</v>
+        <v>-0.4640532787196434</v>
       </c>
       <c r="AD17" s="75" t="n">
-        <v>-0.02921373864749205</v>
+        <v>-0.02793735615773163</v>
       </c>
       <c r="AE17" s="72" t="n">
-        <v>42.9113476677261</v>
+        <v>42.9157922138958</v>
       </c>
       <c r="AF17" s="72" t="n">
-        <v>43.40497489175099</v>
+        <v>43.40679311518405</v>
       </c>
       <c r="AG17" s="72" t="n">
-        <v>44.49500007629395</v>
+        <v>44.49540008544922</v>
       </c>
       <c r="AH17" s="72" t="n">
-        <v>44.77259986877441</v>
+        <v>44.77279987335205</v>
       </c>
       <c r="AI17" s="72" t="n">
-        <v>44.6714249420166</v>
+        <v>44.67152494430542</v>
       </c>
       <c r="AJ17" s="72" t="n">
-        <v>44.55475261675537</v>
+        <v>44.5544930970511</v>
       </c>
       <c r="AK17" s="72" t="n">
-        <v>43.38700027465821</v>
+        <v>43.38800029754638</v>
       </c>
       <c r="AL17" s="72" t="n">
-        <v>42.21924793256104</v>
+        <v>42.22150749804167</v>
       </c>
       <c r="AM17" s="76" t="n">
-        <v>0.3385779503349379</v>
+        <v>0.3465479090820306</v>
       </c>
       <c r="AN17" s="29" t="n">
-        <v>5.382959571783238</v>
+        <v>5.377029554278317</v>
       </c>
       <c r="AO17" s="77" t="n">
-        <v>1.501804572681108</v>
+        <v>1.501106529925419</v>
       </c>
       <c r="AP17" s="72" t="n">
         <v>47.79999923706055</v>
@@ -5583,22 +5583,22 @@
         <v>41.15000152587891</v>
       </c>
       <c r="AR17" s="29" t="n">
-        <v>-10.02092257736593</v>
+        <v>-9.979080614849401</v>
       </c>
       <c r="AS17" s="78" t="n">
-        <v>27.96988625314569</v>
+        <v>28.27064512002534</v>
       </c>
       <c r="AT17" s="26" t="n">
-        <v>-0.003937053785110778</v>
+        <v>-0.003473865790152075</v>
       </c>
       <c r="AU17" s="26" t="n">
-        <v>-0.01488780412621638</v>
+        <v>-0.0144297084360292</v>
       </c>
       <c r="AV17" s="26" t="n">
-        <v>-0.02116523291401473</v>
+        <v>-0.02071005634622314</v>
       </c>
       <c r="AW17" s="26" t="n">
-        <v>0.00749589377180282</v>
+        <v>0.007964398302303222</v>
       </c>
       <c r="AX17" s="79" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="C19" s="26" t="n">
-        <v>0.01044232781374466</v>
+        <v>0.01046841189654324</v>
       </c>
       <c r="D19" s="27" t="n">
         <v>2</v>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="R19" s="70" t="n">
-        <v>773.1500244140625</v>
+        <v>773.1699829101562</v>
       </c>
       <c r="S19" s="71" t="n">
-        <v>7.99005126953125</v>
+        <v>8.010009765625</v>
       </c>
       <c r="T19" s="72" t="n">
         <v>767.9000244140625</v>
@@ -5729,61 +5729,61 @@
         <v>767.4500122070312</v>
       </c>
       <c r="W19" s="73" t="n">
-        <v>37276512</v>
+        <v>42648446</v>
       </c>
       <c r="X19" s="74" t="n">
-        <v>1.021643195735175</v>
+        <v>1.160330888149106</v>
       </c>
       <c r="Y19" s="28" t="n">
-        <v>58.77649139395812</v>
+        <v>58.79115045203841</v>
       </c>
       <c r="Z19" s="28" t="n">
-        <v>79.01737203821565</v>
+        <v>79.13273874204428</v>
       </c>
       <c r="AA19" s="28" t="n">
         <v>13.44376294928172</v>
       </c>
       <c r="AB19" s="75" t="n">
-        <v>3.069369028978258</v>
+        <v>3.07096115972081</v>
       </c>
       <c r="AC19" s="75" t="n">
-        <v>3.90001341073205</v>
+        <v>3.90033183688056</v>
       </c>
       <c r="AD19" s="75" t="n">
-        <v>-0.8306443817537916</v>
+        <v>-0.8293706771597504</v>
       </c>
       <c r="AE19" s="72" t="n">
-        <v>767.7018123284879</v>
+        <v>767.7062475498421</v>
       </c>
       <c r="AF19" s="72" t="n">
-        <v>765.5851549077978</v>
+        <v>765.5869693165336</v>
       </c>
       <c r="AG19" s="72" t="n">
-        <v>756.1390014648438</v>
+        <v>756.1394006347656</v>
       </c>
       <c r="AH19" s="72" t="n">
-        <v>744.5563012695312</v>
+        <v>744.5565008544922</v>
       </c>
       <c r="AI19" s="72" t="n">
-        <v>711.6302005004883</v>
+        <v>711.6303002929687</v>
       </c>
       <c r="AJ19" s="72" t="n">
-        <v>778.0323789695482</v>
+        <v>778.0351647978197</v>
       </c>
       <c r="AK19" s="72" t="n">
-        <v>769.2054962158203</v>
+        <v>769.206494140625</v>
       </c>
       <c r="AL19" s="72" t="n">
-        <v>760.3786134620924</v>
+        <v>760.3778234834302</v>
       </c>
       <c r="AM19" s="76" t="n">
-        <v>0.7234383478457502</v>
+        <v>0.7244669058020271</v>
       </c>
       <c r="AN19" s="29" t="n">
-        <v>2.295064920142297</v>
+        <v>2.295526812227012</v>
       </c>
       <c r="AO19" s="77" t="n">
-        <v>0.8247771104614723</v>
+        <v>0.8247558197865869</v>
       </c>
       <c r="AP19" s="72" t="n">
         <v>779.3699951171875</v>
@@ -5792,22 +5792,22 @@
         <v>629.280029296875</v>
       </c>
       <c r="AR19" s="29" t="n">
-        <v>-0.7980767468716565</v>
+        <v>-0.7955158969263354</v>
       </c>
       <c r="AS19" s="78" t="n">
-        <v>95.85583841722534</v>
+        <v>95.86913610570484</v>
       </c>
       <c r="AT19" s="26" t="n">
-        <v>0.002658603155274664</v>
+        <v>0.002684486304964206</v>
       </c>
       <c r="AU19" s="26" t="n">
-        <v>0.004364887154453712</v>
+        <v>0.00439081435104427</v>
       </c>
       <c r="AV19" s="26" t="n">
-        <v>0.02121279767123352</v>
+        <v>0.02123915978853219</v>
       </c>
       <c r="AW19" s="26" t="n">
-        <v>0.1337840858022281</v>
+        <v>0.1338133538931976</v>
       </c>
       <c r="AX19" s="79" t="inlineStr">
         <is>
@@ -5917,10 +5917,10 @@
         <v>709.6937866210938</v>
       </c>
       <c r="W20" s="84" t="n">
-        <v>27984653</v>
+        <v>29342845</v>
       </c>
       <c r="X20" s="85" t="n">
-        <v>0.9136779999442776</v>
+        <v>0.9559025285381031</v>
       </c>
       <c r="Y20" s="35" t="n">
         <v>52.85437750437693</v>
@@ -6021,10 +6021,10 @@
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>0.003979398222152097</v>
+        <v>0.004013443884859136</v>
       </c>
       <c r="D21" s="27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="R21" s="70" t="n">
-        <v>295.1799926757812</v>
+        <v>295.1900024414062</v>
       </c>
       <c r="S21" s="71" t="n">
-        <v>1.16998291015625</v>
+        <v>1.17999267578125</v>
       </c>
       <c r="T21" s="72" t="n">
         <v>295.7900085449219</v>
@@ -6105,61 +6105,61 @@
         <v>293.4299926757812</v>
       </c>
       <c r="W21" s="73" t="n">
-        <v>16038850</v>
+        <v>16613075</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>0.9484342100030616</v>
+        <v>0.9807251019376435</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>46.65428964450938</v>
+        <v>46.67148684589938</v>
       </c>
       <c r="Z21" s="28" t="n">
-        <v>36.28131455239423</v>
+        <v>36.3510205122538</v>
       </c>
       <c r="AA21" s="28" t="n">
         <v>19.93049326643414</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>-0.7170652868219349</v>
+        <v>-0.7162667869999382</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>0.2743904745372794</v>
+        <v>0.2745501745016787</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.9914557613592143</v>
+        <v>-0.9908169615016169</v>
       </c>
       <c r="AE21" s="72" t="n">
-        <v>295.5545575878534</v>
+        <v>295.5567819802145</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>297.1338999562503</v>
+        <v>297.1348099349435</v>
       </c>
       <c r="AG21" s="72" t="n">
-        <v>297.0718005371094</v>
+        <v>297.0720007324219</v>
       </c>
       <c r="AH21" s="72" t="n">
-        <v>290.2329010009765</v>
+        <v>290.2330010986328</v>
       </c>
       <c r="AI21" s="72" t="n">
-        <v>272.364450302124</v>
+        <v>272.3645003509521</v>
       </c>
       <c r="AJ21" s="72" t="n">
-        <v>306.4633595599753</v>
+        <v>306.462777686003</v>
       </c>
       <c r="AK21" s="72" t="n">
-        <v>299.1425003051758</v>
+        <v>299.143000793457</v>
       </c>
       <c r="AL21" s="72" t="n">
-        <v>291.8216410503762</v>
+        <v>291.823223900911</v>
       </c>
       <c r="AM21" s="76" t="n">
-        <v>0.2293686784924412</v>
+        <v>0.2299782213255524</v>
       </c>
       <c r="AN21" s="29" t="n">
-        <v>4.89456312448487</v>
+        <v>4.893831293482214</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.134769820088047</v>
+        <v>1.134731340533037</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -6168,22 +6168,22 @@
         <v>228.8999938964844</v>
       </c>
       <c r="AR21" s="29" t="n">
-        <v>-3.27675478078403</v>
+        <v>-3.273474826047396</v>
       </c>
       <c r="AS21" s="78" t="n">
-        <v>86.89040356577182</v>
+        <v>86.90352596454632</v>
       </c>
       <c r="AT21" s="26" t="n">
-        <v>-0.0154431303842949</v>
+        <v>-0.01540974335348699</v>
       </c>
       <c r="AU21" s="26" t="n">
-        <v>-0.01531172734466524</v>
+        <v>-0.01527833585788585</v>
       </c>
       <c r="AV21" s="26" t="n">
-        <v>0.01085573372193838</v>
+        <v>0.01089001256612265</v>
       </c>
       <c r="AW21" s="26" t="n">
-        <v>0.1991387239372933</v>
+        <v>0.1991793875929484</v>
       </c>
       <c r="AX21" s="79" t="inlineStr">
         <is>
@@ -6209,10 +6209,10 @@
         </is>
       </c>
       <c r="C22" s="33" t="n">
-        <v>0.004043256336109913</v>
+        <v>0.003667131125943079</v>
       </c>
       <c r="D22" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="R22" s="81" t="n">
-        <v>106.7799987792969</v>
+        <v>106.7399978637695</v>
       </c>
       <c r="S22" s="82" t="n">
-        <v>0.4300003051757812</v>
+        <v>0.3899993896484375</v>
       </c>
       <c r="T22" s="83" t="n">
         <v>103</v>
@@ -6293,61 +6293,61 @@
         <v>98.62000274658203</v>
       </c>
       <c r="W22" s="84" t="n">
-        <v>53290604</v>
+        <v>54538100</v>
       </c>
       <c r="X22" s="85" t="n">
-        <v>0.9836683881425153</v>
+        <v>1.005537655968398</v>
       </c>
       <c r="Y22" s="35" t="n">
-        <v>39.33796822889906</v>
+        <v>39.31394302464612</v>
       </c>
       <c r="Z22" s="35" t="n">
-        <v>13.99656376230992</v>
+        <v>13.92795155190141</v>
       </c>
       <c r="AA22" s="35" t="n">
         <v>20.05925473325475</v>
       </c>
       <c r="AB22" s="86" t="n">
-        <v>-10.77548603426438</v>
+        <v>-10.77867699048879</v>
       </c>
       <c r="AC22" s="86" t="n">
-        <v>-10.45858757131133</v>
+        <v>-10.45922576255621</v>
       </c>
       <c r="AD22" s="86" t="n">
-        <v>-0.3168984629530485</v>
+        <v>-0.3194512279325821</v>
       </c>
       <c r="AE22" s="83" t="n">
-        <v>111.9179347600227</v>
+        <v>111.9090456676833</v>
       </c>
       <c r="AF22" s="83" t="n">
-        <v>122.1318498512239</v>
+        <v>122.1282134043578</v>
       </c>
       <c r="AG22" s="83" t="n">
-        <v>147.915599822998</v>
+        <v>147.9147998046875</v>
       </c>
       <c r="AH22" s="83" t="n">
-        <v>163.4701000976563</v>
+        <v>163.469700088501</v>
       </c>
       <c r="AI22" s="83" t="n">
-        <v>108.4174999713898</v>
+        <v>108.4172999668121</v>
       </c>
       <c r="AJ22" s="83" t="n">
-        <v>152.484279384695</v>
+        <v>152.4873396300005</v>
       </c>
       <c r="AK22" s="83" t="n">
-        <v>124.4775001525879</v>
+        <v>124.4755001068115</v>
       </c>
       <c r="AL22" s="83" t="n">
-        <v>96.4707209204808</v>
+        <v>96.46366058362254</v>
       </c>
       <c r="AM22" s="87" t="n">
-        <v>0.1840496862094995</v>
+        <v>0.1834284619480264</v>
       </c>
       <c r="AN22" s="36" t="n">
-        <v>44.99894229523508</v>
+        <v>45.00779591028312</v>
       </c>
       <c r="AO22" s="88" t="n">
-        <v>12.95409405606911</v>
+        <v>12.9589486151139</v>
       </c>
       <c r="AP22" s="83" t="n">
         <v>302</v>
@@ -6356,22 +6356,22 @@
         <v>23.97999954223633</v>
       </c>
       <c r="AR22" s="36" t="n">
-        <v>-64.64238451016659</v>
+        <v>-64.65562984643394</v>
       </c>
       <c r="AS22" s="89" t="n">
-        <v>29.78202974632373</v>
+        <v>29.76764196290474</v>
       </c>
       <c r="AT22" s="33" t="n">
-        <v>-0.1322227051519648</v>
+        <v>-0.1325477836934948</v>
       </c>
       <c r="AU22" s="33" t="n">
-        <v>-0.1914894157826267</v>
+        <v>-0.1917922923882829</v>
       </c>
       <c r="AV22" s="33" t="n">
-        <v>-0.593528763542102</v>
+        <v>-0.5936810319610918</v>
       </c>
       <c r="AW22" s="33" t="n">
-        <v>1.540566306937285</v>
+        <v>1.539614583961099</v>
       </c>
       <c r="AX22" s="90" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -6502,10 +6502,10 @@
         <v>324.1099853515625</v>
       </c>
       <c r="W24" s="73" t="n">
-        <v>34667051</v>
+        <v>37197362</v>
       </c>
       <c r="X24" s="74" t="n">
-        <v>0.8828002339443918</v>
+        <v>0.9441929425958945</v>
       </c>
       <c r="Y24" s="28" t="n">
         <v>63.3841943924303</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="AX24" s="79" t="inlineStr">
         <is>
-          <t>How Apple's John Ternus inherited a 'reckoning' with China</t>
+          <t>What Happens To Qualcomm Stock If The New Revenue Earns Less?</t>
         </is>
       </c>
       <c r="AY24" s="79" t="inlineStr">
@@ -6690,10 +6690,10 @@
         <v>440.5</v>
       </c>
       <c r="W25" s="84" t="n">
-        <v>13795477</v>
+        <v>14826068</v>
       </c>
       <c r="X25" s="85" t="n">
-        <v>0.7750721329410792</v>
+        <v>0.8305693193246186</v>
       </c>
       <c r="Y25" s="35" t="n">
         <v>42.75037085775087</v>
@@ -6772,17 +6772,17 @@
       </c>
       <c r="AX25" s="90" t="inlineStr">
         <is>
-          <t>Could a $10,000 Investment in AMD Double by the End of 2028?</t>
+          <t>AMD (AMD) Stock May Be 24% Undervalued On Saudi AI Expansion</t>
         </is>
       </c>
       <c r="AY25" s="90" t="inlineStr">
         <is>
-          <t>ASUS Expands AI Infrastructure Ecosystem from Cloud to Edge</t>
+          <t>Why Is AMD (AMD) Becoming More Important In Secure AI Infrastructure?</t>
         </is>
       </c>
       <c r="AZ25" s="90" t="inlineStr">
         <is>
-          <t>Why Is Advanced Micro (AMD) Down 5.2% Since Last Earnings Report?</t>
+          <t>Cathie Wood Sold About $72.8 Million of AMD and Bought About $53 Million of Nvidia. What Changed?</t>
         </is>
       </c>
     </row>
@@ -6878,10 +6878,10 @@
         <v>256</v>
       </c>
       <c r="W26" s="73" t="n">
-        <v>25054524</v>
+        <v>26809147</v>
       </c>
       <c r="X26" s="74" t="n">
-        <v>0.7647190022275767</v>
+        <v>0.8160886640327858</v>
       </c>
       <c r="Y26" s="28" t="n">
         <v>49.89729833030852</v>
@@ -6960,17 +6960,17 @@
       </c>
       <c r="AX26" s="79" t="inlineStr">
         <is>
-          <t>Amazon Signed a Multibillion-Dollar Deal With a 175-Year-Old Glassmaker. Is Fiber the Next AI Bottleneck?</t>
+          <t>Amazon vs. Microsoft: 1 Key Metric Identifies the Superior Artificial Intelligence (AI) Cloud Stock</t>
         </is>
       </c>
       <c r="AY26" s="79" t="inlineStr">
         <is>
+          <t>Top Analyst Reports for Amazon, AbbVie &amp; Alibaba</t>
+        </is>
+      </c>
+      <c r="AZ26" s="79" t="inlineStr">
+        <is>
           <t>Microsoft, Amazon and 8 More Stocks Set to Win in a $26 Trillion AI Market</t>
-        </is>
-      </c>
-      <c r="AZ26" s="79" t="inlineStr">
-        <is>
-          <t>This Is The Biggest Reason I Keep Accumulating Amazon Stock After Jumping 10% This Year</t>
         </is>
       </c>
     </row>
@@ -7066,10 +7066,10 @@
         <v>84.38999938964844</v>
       </c>
       <c r="W27" s="84" t="n">
-        <v>7962256</v>
+        <v>8200546</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>1.640607019091461</v>
+        <v>1.685568198964707</v>
       </c>
       <c r="Y27" s="35" t="n">
         <v>60.64394628659645</v>
@@ -7254,10 +7254,10 @@
         <v>225.4600067138672</v>
       </c>
       <c r="W28" s="73" t="n">
-        <v>3454439</v>
+        <v>3988455</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>0.9595712000722669</v>
+        <v>1.099752935378756</v>
       </c>
       <c r="Y28" s="28" t="n">
         <v>43.1821885698378</v>
@@ -7442,10 +7442,10 @@
         <v>61.06999969482422</v>
       </c>
       <c r="W29" s="84" t="n">
-        <v>7443437</v>
+        <v>7712346</v>
       </c>
       <c r="X29" s="85" t="n">
-        <v>0.721810448780269</v>
+        <v>0.7469134330044204</v>
       </c>
       <c r="Y29" s="35" t="n">
         <v>46.90028524397902</v>
@@ -7630,10 +7630,10 @@
         <v>342.3305053710938</v>
       </c>
       <c r="W30" s="73" t="n">
-        <v>59051560</v>
+        <v>60115767</v>
       </c>
       <c r="X30" s="74" t="n">
-        <v>2.625767961256873</v>
+        <v>2.666778961403967</v>
       </c>
       <c r="Y30" s="28" t="n">
         <v>37.51016967676528</v>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
-          <t>Broadcom's 2028 AI revenue outlook is what's really 'important'</t>
+          <t>Broadcom Shares Fall 5.6% Even as Revenue Surges 86%</t>
         </is>
       </c>
       <c r="AY30" s="79" t="inlineStr">
         <is>
-          <t>Broadcom Delivered Bullish AI Commentary on Fiscal 2027, 2028 Revenue Outlook, Demand Visibility, UBS Says</t>
+          <t>Why Broadcom (AVGO) Stock Is Nosediving</t>
         </is>
       </c>
       <c r="AZ30" s="79" t="inlineStr">
         <is>
-          <t>Kyndryl Holdings (KD) Expands Broadcom Alliance, Is The Stock Still Undervalued?</t>
+          <t>Broadcom Forecasts Steep Ramp In AI Revenue</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>0.04394065917242362</v>
+        <v>0.04399258781898019</v>
       </c>
       <c r="D31" s="34" t="n">
         <v>8</v>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="N31" s="80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O31" s="30" t="inlineStr">
         <is>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="R31" s="81" t="n">
-        <v>100.6149978637695</v>
+        <v>100.620002746582</v>
       </c>
       <c r="S31" s="82" t="n">
-        <v>4.235000610351562</v>
+        <v>4.240005493164062</v>
       </c>
       <c r="T31" s="83" t="n">
         <v>98.98999786376953</v>
@@ -7818,61 +7818,61 @@
         <v>98.72000122070312</v>
       </c>
       <c r="W31" s="84" t="n">
-        <v>2396396</v>
+        <v>3216302</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>0.8890672005926532</v>
+        <v>1.175377094891935</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>53.85734515399562</v>
+        <v>53.86463558689864</v>
       </c>
       <c r="Z31" s="35" t="n">
-        <v>38.03173707449242</v>
+        <v>38.0601255236825</v>
       </c>
       <c r="AA31" s="35" t="n">
         <v>16.02560998343604</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>1.306426685059975</v>
+        <v>1.306825934970945</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.7065943601783</v>
+        <v>1.706674210160494</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>-0.4001676751183247</v>
+        <v>-0.3998482751895489</v>
       </c>
       <c r="AE31" s="83" t="n">
-        <v>99.76640219555451</v>
+        <v>99.76751439173506</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>98.79102937454574</v>
+        <v>98.79148436389234</v>
       </c>
       <c r="AG31" s="83" t="n">
-        <v>95.45110000610352</v>
+        <v>95.45120010375976</v>
       </c>
       <c r="AH31" s="83" t="n">
-        <v>104.0227497863769</v>
+        <v>104.0227998352051</v>
       </c>
       <c r="AI31" s="83" t="n">
-        <v>105.2803247451782</v>
+        <v>105.2803497695923</v>
       </c>
       <c r="AJ31" s="83" t="n">
-        <v>106.7384477434802</v>
+        <v>106.7388310101748</v>
       </c>
       <c r="AK31" s="83" t="n">
-        <v>99.67924995422364</v>
+        <v>99.67950019836425</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>92.62005216496712</v>
+        <v>92.62016938655371</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.5662786294903099</v>
+        <v>0.5666141432729205</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>14.16382605707478</v>
+        <v>14.16405739949002</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>4.113441840578714</v>
+        <v>4.113237236187875</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -7881,22 +7881,22 @@
         <v>74.62999725341797</v>
       </c>
       <c r="AR31" s="36" t="n">
-        <v>-25.60263695873978</v>
+        <v>-25.59893621738426</v>
       </c>
       <c r="AS31" s="89" t="n">
-        <v>42.87245846851978</v>
+        <v>42.88071598729903</v>
       </c>
       <c r="AT31" s="33" t="n">
-        <v>-0.05374780277315894</v>
+        <v>-0.05370073343500115</v>
       </c>
       <c r="AU31" s="33" t="n">
-        <v>0.06730668766996084</v>
+        <v>0.06735977861077669</v>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>-0.1175670862476914</v>
+        <v>-0.1175231914664263</v>
       </c>
       <c r="AW31" s="33" t="n">
-        <v>0.09973767857757854</v>
+        <v>0.09979238273026581</v>
       </c>
       <c r="AX31" s="90" t="inlineStr">
         <is>
@@ -8006,10 +8006,10 @@
         <v>79.04000091552734</v>
       </c>
       <c r="W32" s="73" t="n">
-        <v>16987141</v>
+        <v>18737553</v>
       </c>
       <c r="X32" s="74" t="n">
-        <v>0.6280517896294787</v>
+        <v>0.6905339040657145</v>
       </c>
       <c r="Y32" s="28" t="n">
         <v>46.47792492475057</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>0.04823240480617752</v>
+        <v>0.04914669207938038</v>
       </c>
       <c r="D33" s="34" t="n">
         <v>5</v>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="R33" s="81" t="n">
-        <v>515.9400024414062</v>
+        <v>516.3900146484375</v>
       </c>
       <c r="S33" s="82" t="n">
-        <v>23.739990234375</v>
+        <v>24.19000244140625</v>
       </c>
       <c r="T33" s="83" t="n">
         <v>486.3099975585938</v>
@@ -8194,61 +8194,61 @@
         <v>478.306396484375</v>
       </c>
       <c r="W33" s="84" t="n">
-        <v>18803945</v>
+        <v>20266015</v>
       </c>
       <c r="X33" s="85" t="n">
-        <v>2.365965876403778</v>
+        <v>2.52668698948853</v>
       </c>
       <c r="Y33" s="35" t="n">
-        <v>62.47909653795556</v>
+        <v>62.5415624260926</v>
       </c>
       <c r="Z33" s="35" t="n">
-        <v>86.37154480750023</v>
+        <v>86.7848170515018</v>
       </c>
       <c r="AA33" s="35" t="n">
         <v>9.244106021666912</v>
       </c>
       <c r="AB33" s="86" t="n">
-        <v>12.02442571002194</v>
+        <v>12.06032411969966</v>
       </c>
       <c r="AC33" s="86" t="n">
-        <v>9.400957805664699</v>
+        <v>9.408137487600243</v>
       </c>
       <c r="AD33" s="86" t="n">
-        <v>2.623467904357245</v>
+        <v>2.652186632099415</v>
       </c>
       <c r="AE33" s="83" t="n">
-        <v>471.7156197715044</v>
+        <v>471.815622484178</v>
       </c>
       <c r="AF33" s="83" t="n">
-        <v>458.3412919665577</v>
+        <v>458.382202167197</v>
       </c>
       <c r="AG33" s="83" t="n">
-        <v>437.1495989990235</v>
+        <v>437.1585992431641</v>
       </c>
       <c r="AH33" s="83" t="n">
-        <v>367.0556986999512</v>
+        <v>367.0601988220215</v>
       </c>
       <c r="AI33" s="83" t="n">
-        <v>251.4406495666504</v>
+        <v>251.4428996276855</v>
       </c>
       <c r="AJ33" s="83" t="n">
-        <v>510.1528702752637</v>
+        <v>510.2766170482452</v>
       </c>
       <c r="AK33" s="83" t="n">
-        <v>462.5735000610351</v>
+        <v>462.5960006713867</v>
       </c>
       <c r="AL33" s="83" t="n">
-        <v>414.9941298468066</v>
+        <v>414.9153842945283</v>
       </c>
       <c r="AM33" s="87" t="n">
-        <v>1.060815560820642</v>
+        <v>1.064107787028939</v>
       </c>
       <c r="AN33" s="36" t="n">
-        <v>20.57159357721556</v>
+        <v>20.6143660159869</v>
       </c>
       <c r="AO33" s="88" t="n">
-        <v>6.329534985633925</v>
+        <v>6.324019061763271</v>
       </c>
       <c r="AP33" s="83" t="n">
         <v>530.780029296875</v>
@@ -8257,36 +8257,36 @@
         <v>110.2200012207031</v>
       </c>
       <c r="AR33" s="36" t="n">
-        <v>-2.795890206179641</v>
+        <v>-2.711107022526826</v>
       </c>
       <c r="AS33" s="89" t="n">
-        <v>96.4713653545836</v>
+        <v>96.57836844022866</v>
       </c>
       <c r="AT33" s="33" t="n">
-        <v>0.09249140679402212</v>
+        <v>0.09344429756970851</v>
       </c>
       <c r="AU33" s="33" t="n">
-        <v>0.1150637320721599</v>
+        <v>0.1160363108384426</v>
       </c>
       <c r="AV33" s="33" t="n">
-        <v>0.2224618347684779</v>
+        <v>0.2235280881035022</v>
       </c>
       <c r="AW33" s="33" t="n">
-        <v>3.09866550443857</v>
+        <v>3.10224043466458</v>
       </c>
       <c r="AX33" s="90" t="inlineStr">
         <is>
-          <t>Dell Is Now Up 20% in a Month: Take Profits, or Buy More?</t>
+          <t>AI Infrastructure Demand Remains Red-Hot: HPE, AVGO, DELL Deliver</t>
         </is>
       </c>
       <c r="AY33" s="90" t="inlineStr">
         <is>
-          <t>Could Dell Be the Next Magnificent Seven Stock?</t>
+          <t>Bank of America sees 41% upside in surging AI stock</t>
         </is>
       </c>
       <c r="AZ33" s="90" t="inlineStr">
         <is>
-          <t>Dell Earnings Surge: Is It the Next Big AI Stock to Buy in 2026?</t>
+          <t>CLS Stock Jumps 12% As Broadcom AI Call Sparks Switch Rally</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -8382,10 +8382,10 @@
         <v>336.3800048828125</v>
       </c>
       <c r="W34" s="73" t="n">
-        <v>11640568</v>
+        <v>12835737</v>
       </c>
       <c r="X34" s="74" t="n">
-        <v>0.766810155053832</v>
+        <v>0.8422252133990685</v>
       </c>
       <c r="Y34" s="28" t="n">
         <v>46.87941335471027</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="AZ34" s="79" t="inlineStr">
         <is>
-          <t>AI wants electricity now. The electric grid needs years to catch up</t>
+          <t>Tesla's 45 Cybercabs Face a $1.3 Trillion Reality Check</t>
         </is>
       </c>
     </row>
@@ -8570,10 +8570,10 @@
         <v>39.02999877929688</v>
       </c>
       <c r="W35" s="84" t="n">
-        <v>43775049</v>
+        <v>44874993</v>
       </c>
       <c r="X35" s="85" t="n">
-        <v>0.9599586729865889</v>
+        <v>0.9828943146758904</v>
       </c>
       <c r="Y35" s="35" t="n">
         <v>52.29302829294181</v>
@@ -8758,10 +8758,10 @@
         <v>87.72499847412109</v>
       </c>
       <c r="W36" s="73" t="n">
-        <v>74985819</v>
+        <v>79677381</v>
       </c>
       <c r="X36" s="74" t="n">
-        <v>0.7763475089877393</v>
+        <v>0.8229218722870226</v>
       </c>
       <c r="Y36" s="28" t="n">
         <v>45.47576951193744</v>
@@ -8840,17 +8840,17 @@
       </c>
       <c r="AX36" s="79" t="inlineStr">
         <is>
+          <t>Intel (INTC) Outperforms Broader Market: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="AY36" s="79" t="inlineStr">
+        <is>
+          <t>Nvidia’s $5 Billion Intel Bet Was Worth $30 Billion by June. Is the Partnership Still Mispriced?</t>
+        </is>
+      </c>
+      <c r="AZ36" s="79" t="inlineStr">
+        <is>
           <t>ASUS Expands AI Infrastructure Ecosystem from Cloud to Edge</t>
-        </is>
-      </c>
-      <c r="AY36" s="79" t="inlineStr">
-        <is>
-          <t>AMD is Quietly Eating Intel’s Lunch</t>
-        </is>
-      </c>
-      <c r="AZ36" s="79" t="inlineStr">
-        <is>
-          <t>Intel (INTC) Could Be 82% Below Fair Value After Kasm AI Partnership</t>
         </is>
       </c>
     </row>
@@ -8946,10 +8946,10 @@
         <v>500.7999877929688</v>
       </c>
       <c r="W37" s="84" t="n">
-        <v>22168345</v>
+        <v>24108434</v>
       </c>
       <c r="X37" s="85" t="n">
-        <v>0.9458652368457289</v>
+        <v>1.024403823153436</v>
       </c>
       <c r="Y37" s="35" t="n">
         <v>66.11056614319938</v>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="AX37" s="90" t="inlineStr">
         <is>
-          <t>Canva’s productivity push is starting to gain traction—and in Southeast Asia, it’s happening on phones</t>
+          <t>S&amp;P 500, Dow End Best Day In A Month On Calmer Yields As Rate Hike Bets Wane — SPCX, VSXY, NVDA, TSLA In Focus</t>
         </is>
       </c>
       <c r="AY37" s="90" t="inlineStr">
         <is>
-          <t>Microsoft's AI Shake-Up Changes What Investors See</t>
+          <t>Microsoft Finally Reveals Azure's $29.4 Billion Core</t>
         </is>
       </c>
       <c r="AZ37" s="90" t="inlineStr">
         <is>
-          <t>Microsoft, Amazon and 8 More Stocks Set to Win in a $26 Trillion AI Market</t>
+          <t>Amazon vs. Microsoft: 1 Key Metric Identifies the Superior Artificial Intelligence (AI) Cloud Stock</t>
         </is>
       </c>
     </row>
@@ -9134,10 +9134,10 @@
         <v>127.5875015258789</v>
       </c>
       <c r="W38" s="73" t="n">
-        <v>42445799</v>
+        <v>44800410</v>
       </c>
       <c r="X38" s="74" t="n">
-        <v>1.53015511708225</v>
+        <v>1.608212477241803</v>
       </c>
       <c r="Y38" s="28" t="n">
         <v>67.78995829466069</v>
@@ -9216,17 +9216,17 @@
       </c>
       <c r="AX38" s="79" t="inlineStr">
         <is>
+          <t>Coinbase, Circle, MicroStrategy stocks surge on crypto rebound</t>
+        </is>
+      </c>
+      <c r="AY38" s="79" t="inlineStr">
+        <is>
           <t>Saylor says Strategy’s Bitcoin-heavy reserve capital surpasses nearly all S&amp;P 500 financial firms</t>
         </is>
       </c>
-      <c r="AY38" s="79" t="inlineStr">
+      <c r="AZ38" s="79" t="inlineStr">
         <is>
           <t>Strategy (MSTR) Looks Cheap As Bitcoin Buying Resumes With 4,603 More Coins</t>
-        </is>
-      </c>
-      <c r="AZ38" s="79" t="inlineStr">
-        <is>
-          <t>MicroStrategy Reserve Capital Beats All S&amp;P 500 Financials But Berkshire, MSTR Still Slips</t>
         </is>
       </c>
     </row>
@@ -9322,10 +9322,10 @@
         <v>918.880126953125</v>
       </c>
       <c r="W39" s="84" t="n">
-        <v>23723224</v>
+        <v>24105584</v>
       </c>
       <c r="X39" s="85" t="n">
-        <v>0.8579647504841599</v>
+        <v>0.8711906777793956</v>
       </c>
       <c r="Y39" s="35" t="n">
         <v>53.48729626756077</v>
@@ -9404,17 +9404,17 @@
       </c>
       <c r="AX39" s="90" t="inlineStr">
         <is>
+          <t>China Is Grabbing Memory Market Share. This Stock Could Be a Big Loser.</t>
+        </is>
+      </c>
+      <c r="AY39" s="90" t="inlineStr">
+        <is>
           <t>Micron, SanDisk Lag Tech Rally as China Grabs Memory Market Share</t>
         </is>
       </c>
-      <c r="AY39" s="90" t="inlineStr">
+      <c r="AZ39" s="90" t="inlineStr">
         <is>
           <t>Micron's 11% Drop Hasn't Shaken Wall Street's Bull Case</t>
-        </is>
-      </c>
-      <c r="AZ39" s="90" t="inlineStr">
-        <is>
-          <t>The Fed's September Decision Could Hit Micron Harder Than Its Own Earnings</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr">
@@ -9510,10 +9510,10 @@
         <v>196.6300048828125</v>
       </c>
       <c r="W40" s="73" t="n">
-        <v>10438843</v>
+        <v>10639270</v>
       </c>
       <c r="X40" s="74" t="n">
-        <v>0.4692948440856147</v>
+        <v>0.4780899678316393</v>
       </c>
       <c r="Y40" s="28" t="n">
         <v>48.37077454734214</v>
@@ -9698,10 +9698,10 @@
         <v>81.62999725341797</v>
       </c>
       <c r="W41" s="84" t="n">
-        <v>23071599</v>
+        <v>23970646</v>
       </c>
       <c r="X41" s="85" t="n">
-        <v>0.8472874465772849</v>
+        <v>0.878853436103154</v>
       </c>
       <c r="Y41" s="35" t="n">
         <v>63.65191183967269</v>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="C42" s="26" t="n">
-        <v>-0.007621931717695318</v>
+        <v>-0.007113790014099619</v>
       </c>
       <c r="D42" s="27" t="n">
         <v>23</v>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="R42" s="70" t="n">
-        <v>9.765000343322754</v>
+        <v>9.770000457763672</v>
       </c>
       <c r="S42" s="71" t="n">
-        <v>-0.07499980926513672</v>
+        <v>-0.06999969482421875</v>
       </c>
       <c r="T42" s="72" t="n">
         <v>9.760000228881836</v>
@@ -9886,61 +9886,61 @@
         <v>9.539999961853027</v>
       </c>
       <c r="W42" s="73" t="n">
-        <v>71481044</v>
+        <v>81929446</v>
       </c>
       <c r="X42" s="74" t="n">
-        <v>1.054112456011614</v>
+        <v>1.198955589499316</v>
       </c>
       <c r="Y42" s="28" t="n">
-        <v>42.78947923002418</v>
+        <v>42.85202081378689</v>
       </c>
       <c r="Z42" s="28" t="n">
-        <v>14.15096603000415</v>
+        <v>14.46543860617213</v>
       </c>
       <c r="AA42" s="28" t="n">
         <v>13.09263785060373</v>
       </c>
       <c r="AB42" s="75" t="n">
-        <v>-0.1340415964857264</v>
+        <v>-0.1336427269576745</v>
       </c>
       <c r="AC42" s="75" t="n">
-        <v>-0.1435260559518347</v>
+        <v>-0.1434462820462243</v>
       </c>
       <c r="AD42" s="75" t="n">
-        <v>0.009484459466108264</v>
+        <v>0.009803555088549798</v>
       </c>
       <c r="AE42" s="72" t="n">
-        <v>10.03305777497242</v>
+        <v>10.03416891151484</v>
       </c>
       <c r="AF42" s="72" t="n">
-        <v>10.13315978604743</v>
+        <v>10.1336143419057</v>
       </c>
       <c r="AG42" s="72" t="n">
-        <v>10.60909997940063</v>
+        <v>10.60919998168945</v>
       </c>
       <c r="AH42" s="72" t="n">
-        <v>12.01465000152588</v>
+        <v>12.01470000267029</v>
       </c>
       <c r="AI42" s="72" t="n">
-        <v>9.589174997806548</v>
+        <v>9.589199998378753</v>
       </c>
       <c r="AJ42" s="72" t="n">
-        <v>10.99456497934714</v>
+        <v>10.99440967320634</v>
       </c>
       <c r="AK42" s="72" t="n">
-        <v>10.12125005722046</v>
+        <v>10.12150006294251</v>
       </c>
       <c r="AL42" s="72" t="n">
-        <v>9.247935135093774</v>
+        <v>9.248590452678668</v>
       </c>
       <c r="AM42" s="76" t="n">
-        <v>0.2960359402595739</v>
+        <v>0.2986620830806338</v>
       </c>
       <c r="AN42" s="29" t="n">
-        <v>17.25705653332151</v>
+        <v>17.24862134733943</v>
       </c>
       <c r="AO42" s="77" t="n">
-        <v>4.707074405059595</v>
+        <v>4.704665407147163</v>
       </c>
       <c r="AP42" s="72" t="n">
         <v>17.45000076293945</v>
@@ -9949,22 +9949,22 @@
         <v>4.480000019073486</v>
       </c>
       <c r="AR42" s="29" t="n">
-        <v>-44.04011509236268</v>
+        <v>-44.01146114266464</v>
       </c>
       <c r="AS42" s="78" t="n">
-        <v>40.74787988542526</v>
+        <v>40.7864312667217</v>
       </c>
       <c r="AT42" s="26" t="n">
-        <v>-0.07790366358621159</v>
+        <v>-0.0774315092548733</v>
       </c>
       <c r="AU42" s="26" t="n">
-        <v>0.01931110867327979</v>
+        <v>0.0198330412913108</v>
       </c>
       <c r="AV42" s="26" t="n">
-        <v>-0.4124548826573244</v>
+        <v>-0.4121540334281767</v>
       </c>
       <c r="AW42" s="26" t="n">
-        <v>0.5092736723309077</v>
+        <v>0.5100464875709481</v>
       </c>
       <c r="AX42" s="79" t="inlineStr">
         <is>
@@ -10074,10 +10074,10 @@
         <v>224.75</v>
       </c>
       <c r="W43" s="84" t="n">
-        <v>127001728</v>
+        <v>133890362</v>
       </c>
       <c r="X43" s="85" t="n">
-        <v>0.9996046625221428</v>
+        <v>1.050974552707904</v>
       </c>
       <c r="Y43" s="35" t="n">
         <v>59.20979550440254</v>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
-          <t>Stock Market Today: Dow Pops On Fed Official's Dovish Rates View; Nvidia Hovers In Buy Zone (Live Coverage)</t>
+          <t>Nvidia’s $12.93 Billion Hugging Face Deal Expands Jensen Huang's AI Platform Beyond Chips</t>
         </is>
       </c>
       <c r="AY43" s="90" t="inlineStr">
         <is>
-          <t>Sector Update: Tech Stocks Rise Late Afternoon</t>
+          <t>Nvidia’s $5 Billion Intel Bet Was Worth $30 Billion by June. Is the Partnership Still Mispriced?</t>
         </is>
       </c>
       <c r="AZ43" s="90" t="inlineStr">
         <is>
-          <t>Better Small Modular Reactor Stock to Buy After the Sell-Off: Oklo vs. NuScale Power</t>
+          <t>Rosenblatt Doubles Down on Nvidia After Massive Deal</t>
         </is>
       </c>
     </row>
@@ -10262,10 +10262,10 @@
         <v>171.9375</v>
       </c>
       <c r="W44" s="73" t="n">
-        <v>36980824</v>
+        <v>38010148</v>
       </c>
       <c r="X44" s="74" t="n">
-        <v>1.03936596019443</v>
+        <v>1.066752623224575</v>
       </c>
       <c r="Y44" s="28" t="n">
         <v>60.53699266646308</v>
@@ -10344,17 +10344,17 @@
       </c>
       <c r="AX44" s="79" t="inlineStr">
         <is>
-          <t>Sector Update: Tech Stocks Rise Late Afternoon</t>
+          <t>Palantir Technologies, Workiva, Elastic, RingCentral, and 8x8 Shares Skyrocket, What You Need To Know</t>
         </is>
       </c>
       <c r="AY44" s="79" t="inlineStr">
         <is>
-          <t>Michael Burry doubles down on his surprising AI bet</t>
+          <t>Palantir Stock Jumps on Expanded PwC AI Deal</t>
         </is>
       </c>
       <c r="AZ44" s="79" t="inlineStr">
         <is>
-          <t>The $1 Trillion Question Hanging Over Palantir Stock</t>
+          <t>Palantir Stock Defies Red Flag and Skyrockets 8% – Here’s Why</t>
         </is>
       </c>
     </row>
@@ -10450,10 +10450,10 @@
         <v>164.9049987792969</v>
       </c>
       <c r="W45" s="84" t="n">
-        <v>6516183</v>
+        <v>6987656</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>0.7135553191303785</v>
+        <v>0.7632138336630525</v>
       </c>
       <c r="Y45" s="35" t="n">
         <v>52.87989293804576</v>
@@ -10638,10 +10638,10 @@
         <v>62.36000061035156</v>
       </c>
       <c r="W46" s="73" t="n">
-        <v>18270422</v>
+        <v>18818827</v>
       </c>
       <c r="X46" s="74" t="n">
-        <v>1.040859834961954</v>
+        <v>1.070430141537631</v>
       </c>
       <c r="Y46" s="28" t="n">
         <v>36.14248318653912</v>
@@ -10826,10 +10826,10 @@
         <v>1511</v>
       </c>
       <c r="W47" s="84" t="n">
-        <v>8375587</v>
+        <v>8670816</v>
       </c>
       <c r="X47" s="85" t="n">
-        <v>0.6373043357432135</v>
+        <v>0.6590282924394725</v>
       </c>
       <c r="Y47" s="35" t="n">
         <v>52.58214372024118</v>
@@ -11014,10 +11014,10 @@
         <v>365.9100036621094</v>
       </c>
       <c r="W48" s="73" t="n">
-        <v>61561072</v>
+        <v>62838720</v>
       </c>
       <c r="X48" s="74" t="n">
-        <v>1.682983365551952</v>
+        <v>1.71491725396638</v>
       </c>
       <c r="Y48" s="28" t="n">
         <v>60.53898330136157</v>
@@ -11096,17 +11096,17 @@
       </c>
       <c r="AX48" s="79" t="inlineStr">
         <is>
-          <t>Tesla Cybercab: Here's What To Expect From Thursday's Event</t>
+          <t>Dow Jones Futures: Stocks Jump On Fed's Waller; Tesla Cybercab Event Private, Jobs Report Looms</t>
         </is>
       </c>
       <c r="AY48" s="79" t="inlineStr">
         <is>
-          <t>Tesla Is Now Up 18% in a Month: Take Profits, or Buy More?</t>
+          <t>Tesla Launching Cybercab Robotaxis. Here's What To Look For.</t>
         </is>
       </c>
       <c r="AZ48" s="79" t="inlineStr">
         <is>
-          <t>Market Indexes Rally as Tesla and Goldman Sachs Take the Wheel</t>
+          <t>Tesla's 45 Cybercabs Face a $1.3 Trillion Reality Check</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 3 Sep 2026, 08:01 PM · Yahoo Finance data</t>
+          <t>Built 3 Sep 2026, 10:37 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 3 Sep 2026, 08:01 PM · Yahoo Finance data</t>
+          <t>Built 3 Sep 2026, 10:37 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 3 Sep 2026, 08:01 PM · Yahoo Finance data</t>
+          <t>Built 3 Sep 2026, 10:37 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 3 Sep 2026, 08:01 PM · Yahoo Finance data</t>
+          <t>Built 3 Sep 2026, 10:37 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -43355,22 +43355,22 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>-0.006913919215374764</v>
+        <v>-0.007373206433021195</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>0.037885718310118</v>
+        <v>0.03740571194106179</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>0.1280736484832767</v>
+        <v>0.1275519315673546</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>0.100423869680851</v>
+        <v>0.09991494036735382</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>0.1446512547402579</v>
+        <v>0.1441218709334182</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0.4459830835962213</v>
+        <v>0.4453143383987213</v>
       </c>
       <c r="J6" s="27" t="n">
         <v>7</v>
@@ -43393,22 +43393,22 @@
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.001965864954553087</v>
+        <v>0.00179241147189213</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>0.009966146618659355</v>
+        <v>0.009791308181914093</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.05561640728770745</v>
+        <v>0.05543366618982959</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.1394660126230156</v>
+        <v>0.1392687560545276</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>0.1259176737242489</v>
+        <v>0.1257227625515955</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>0.1194443790042614</v>
+        <v>0.1192505884441486</v>
       </c>
       <c r="J7" s="34" t="n">
         <v>7</v>
@@ -43431,22 +43431,22 @@
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>0.008717340089801739</v>
+        <v>0.008539397794954384</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>0.01786193158923965</v>
+        <v>0.01768237614714829</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>0.02281950677930222</v>
+        <v>0.02263907679855559</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>0.002563883953341728</v>
+        <v>0.00238702715594985</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>-0.0425531983420947</v>
+        <v>-0.0427220962823901</v>
       </c>
       <c r="I8" s="26" t="n">
-        <v>-0.03669724473350133</v>
+        <v>-0.03686717569046283</v>
       </c>
       <c r="J8" s="27" t="n">
         <v>7</v>
@@ -43469,22 +43469,22 @@
         </is>
       </c>
       <c r="D9" s="33" t="n">
-        <v>0.01543529989600545</v>
+        <v>0.01560876739959438</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>0.01157564195890104</v>
+        <v>0.01174845011449688</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.009482745466561138</v>
+        <v>0.009655196091224338</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>0.1218624406534616</v>
+        <v>0.1220540891779616</v>
       </c>
       <c r="H9" s="33" t="n">
-        <v>0.1428850236234978</v>
+        <v>0.1430802634501587</v>
       </c>
       <c r="I9" s="33" t="n">
-        <v>0.06901586174372687</v>
+        <v>0.06919848245117377</v>
       </c>
       <c r="J9" s="34" t="n">
         <v>8</v>
@@ -43507,22 +43507,22 @@
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>0.01296290601799632</v>
+        <v>0.01290846970806347</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>-0.01394414333440253</v>
+        <v>-0.013997133667914</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>0.000376483589107357</v>
+        <v>0.0003227236695815261</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>-0.03722111357643598</v>
+        <v>-0.03727285301284267</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>0.3267228238318394</v>
+        <v>0.3266515261619996</v>
       </c>
       <c r="I10" s="26" t="n">
-        <v>0.291796861503359</v>
+        <v>0.2917274407438175</v>
       </c>
       <c r="J10" s="27" t="n">
         <v>8</v>
@@ -43536,34 +43536,34 @@
     <row r="11">
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D11" s="33" t="n">
-        <v>-0.003273690907203086</v>
+        <v>-0.006232329108589174</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>0.001998097852452752</v>
+        <v>-0.0114597147397596</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>-0.0009375580609161105</v>
+        <v>-0.0003799479102503112</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>0.03912724340139673</v>
+        <v>0.01937233670460836</v>
       </c>
       <c r="H11" s="33" t="n">
-        <v>-0.001873359738308489</v>
+        <v>0.03521536565706906</v>
       </c>
       <c r="I11" s="33" t="n">
-        <v>0.09745107704794687</v>
+        <v>0.1603087255209565</v>
       </c>
       <c r="J11" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" s="102" t="inlineStr">
         <is>
@@ -43574,72 +43574,72 @@
     <row r="12">
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>State Street Utilities Select Sector SPDR ETF</t>
+          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.007968131407967594</v>
+        <v>-0.003156747888692357</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>-0.003937053785110778</v>
+        <v>0.00211565939470959</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>-0.01488780412621638</v>
+        <v>-0.0008203409506870596</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>-0.02116523291401473</v>
+        <v>0.03924916119904243</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>-0.08294249632804895</v>
+        <v>-0.001756252422986937</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0.00749589377180282</v>
+        <v>0.09757983781250879</v>
       </c>
       <c r="J12" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="101" t="inlineStr">
         <is>
-          <t>Long-term down, short-term mixed</t>
+          <t>Long-term up, short-term mixed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
+          <t>State Street Utilities Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D13" s="33" t="n">
-        <v>0.01392998838254322</v>
+        <v>0.008436855537846455</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>0.005005193690040155</v>
+        <v>-0.003473865790152075</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.01837491837821092</v>
+        <v>-0.0144297084360292</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>-0.00682247174811057</v>
+        <v>-0.02071005634622314</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>-0.000772234791321158</v>
+        <v>-0.08251604734909457</v>
       </c>
       <c r="I13" s="33" t="n">
-        <v>-0.02470483617088104</v>
+        <v>0.007964398302303222</v>
       </c>
       <c r="J13" s="34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K13" s="102" t="inlineStr">
         <is>
@@ -43650,69 +43650,69 @@
     <row r="14">
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>State Street Real Estate Select Sector SPDR ETF</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>0.01189116083254094</v>
+        <v>0.01392998838254322</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.009180471312425831</v>
+        <v>0.005005193690040155</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.02101771563947363</v>
+        <v>-0.01837491837821092</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-0.003378412628915695</v>
+        <v>-0.00682247174811057</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.0209967661330932</v>
+        <v>-0.000772234791321158</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0.09665431656410628</v>
+        <v>-0.02470483617088104</v>
       </c>
       <c r="J14" s="27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" s="101" t="inlineStr">
         <is>
-          <t>Long-term up, short-term mixed</t>
+          <t>Long-term down, short-term mixed</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>State Street Industrial Select Sector SPDR ETF</t>
+          <t>State Street Real Estate Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>0.01018633244166245</v>
+        <v>0.01189116083254094</v>
       </c>
       <c r="E15" s="33" t="n">
-        <v>-0.02382555756663962</v>
+        <v>-0.009180471312425831</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>-0.06337543563493342</v>
+        <v>-0.02101771563947363</v>
       </c>
       <c r="G15" s="33" t="n">
-        <v>-0.009196243995793107</v>
+        <v>-0.003378412628915695</v>
       </c>
       <c r="H15" s="33" t="n">
-        <v>0.01441355203259564</v>
+        <v>0.0209967661330932</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>0.1251933907957785</v>
+        <v>0.09665431656410628</v>
       </c>
       <c r="J15" s="34" t="n">
         <v>2</v>
@@ -43726,34 +43726,34 @@
     <row r="16">
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>State Street Industrial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>-0.005854605643518473</v>
+        <v>0.0103021113084425</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>-0.01108397816384998</v>
+        <v>-0.02371367685008763</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>0</v>
+        <v>-0.06326808778515758</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>0.01975979230665259</v>
+        <v>-0.009082686593175682</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>0.03560884307283119</v>
+        <v>0.01452981538691844</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>0.1607497499627784</v>
+        <v>0.1253223507821801</v>
       </c>
       <c r="J16" s="27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K16" s="101" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>0.04823240480617752</v>
+        <v>0.04914669207938038</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>8</v>
@@ -44196,7 +44196,7 @@
         </is>
       </c>
       <c r="E15" s="33" t="n">
-        <v>0.04823240480617752</v>
+        <v>0.04914669207938038</v>
       </c>
       <c r="F15" s="34" t="n">
         <v>8</v>
@@ -44220,11 +44220,11 @@
       </c>
       <c r="D16" s="104" t="inlineStr">
         <is>
-          <t>Volume 2.4x its 20-day average</t>
+          <t>Volume 2.5x its 20-day average</t>
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>0.04823240480617752</v>
+        <v>0.04914669207938038</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>8</v>
@@ -44308,7 +44308,7 @@
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>0.01543529989600545</v>
+        <v>0.01560876739959438</v>
       </c>
       <c r="F19" s="34" t="n">
         <v>8</v>
@@ -44336,7 +44336,7 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0.01296290601799632</v>
+        <v>0.01290846970806347</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>8</v>
@@ -44364,7 +44364,7 @@
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>0.01296290601799632</v>
+        <v>0.01290846970806347</v>
       </c>
       <c r="F21" s="34" t="n">
         <v>8</v>
@@ -44392,7 +44392,7 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>0.01044232781374466</v>
+        <v>0.01046841189654324</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>8</v>
@@ -44518,21 +44518,21 @@
     <row r="27">
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C27" s="102" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
-        </is>
-      </c>
-      <c r="D27" s="107" t="inlineStr">
-        <is>
-          <t>8 EMA crossed above 21</t>
+          <t>Cameco Corporation</t>
+        </is>
+      </c>
+      <c r="D27" s="105" t="inlineStr">
+        <is>
+          <t>RSI crossed back above 50</t>
         </is>
       </c>
       <c r="E27" s="33" t="n">
-        <v>0.01188595227547085</v>
+        <v>0.04399258781898019</v>
       </c>
       <c r="F27" s="34" t="n">
         <v>7</v>
@@ -44546,21 +44546,21 @@
     <row r="28">
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C28" s="101" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
+          <t>Cameco Corporation</t>
         </is>
       </c>
       <c r="D28" s="104" t="inlineStr">
         <is>
-          <t>RSI crossed back above 50</t>
+          <t>Gapped up 2.7% at the open</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>0.01188595227547085</v>
+        <v>0.04399258781898019</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>7</v>
@@ -44574,21 +44574,21 @@
     <row r="29">
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C29" s="102" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
+          <t>Cameco Corporation</t>
         </is>
       </c>
       <c r="D29" s="105" t="inlineStr">
         <is>
-          <t>Reclaimed the 50 DMA</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E29" s="33" t="n">
-        <v>0.01188595227547085</v>
+        <v>0.04399258781898019</v>
       </c>
       <c r="F29" s="34" t="n">
         <v>7</v>
@@ -44610,9 +44610,9 @@
           <t>Invesco QQQ Trust</t>
         </is>
       </c>
-      <c r="D30" s="104" t="inlineStr">
-        <is>
-          <t>Bands squeezing — a big move often follows</t>
+      <c r="D30" s="106" t="inlineStr">
+        <is>
+          <t>8 EMA crossed above 21</t>
         </is>
       </c>
       <c r="E30" s="26" t="n">
@@ -44630,21 +44630,21 @@
     <row r="31">
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C31" s="102" t="inlineStr">
         <is>
-          <t>State Street Communication Services Select Sector SPDR ETF</t>
-        </is>
-      </c>
-      <c r="D31" s="107" t="inlineStr">
-        <is>
-          <t>MACD crossed up</t>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D31" s="105" t="inlineStr">
+        <is>
+          <t>RSI crossed back above 50</t>
         </is>
       </c>
       <c r="E31" s="33" t="n">
-        <v>0.008717340089801739</v>
+        <v>0.01188595227547085</v>
       </c>
       <c r="F31" s="34" t="n">
         <v>7</v>
@@ -44658,24 +44658,24 @@
     <row r="32">
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C32" s="101" t="inlineStr">
         <is>
-          <t>Cameco Corporation</t>
+          <t>Invesco QQQ Trust</t>
         </is>
       </c>
       <c r="D32" s="104" t="inlineStr">
         <is>
-          <t>RSI crossed back above 50</t>
+          <t>Reclaimed the 50 DMA</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>0.04394065917242362</v>
+        <v>0.01188595227547085</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
@@ -44686,24 +44686,24 @@
     <row r="33">
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C33" s="102" t="inlineStr">
         <is>
-          <t>Cameco Corporation</t>
+          <t>Invesco QQQ Trust</t>
         </is>
       </c>
       <c r="D33" s="105" t="inlineStr">
         <is>
-          <t>Gapped up 2.7% at the open</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E33" s="33" t="n">
-        <v>0.04394065917242362</v>
+        <v>0.01188595227547085</v>
       </c>
       <c r="F33" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G33" s="30" t="inlineStr">
         <is>
@@ -44714,24 +44714,24 @@
     <row r="34">
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C34" s="101" t="inlineStr">
         <is>
-          <t>Cameco Corporation</t>
-        </is>
-      </c>
-      <c r="D34" s="104" t="inlineStr">
-        <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
+        </is>
+      </c>
+      <c r="D34" s="106" t="inlineStr">
+        <is>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>0.04394065917242362</v>
+        <v>0.008539397794954384</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
@@ -44798,24 +44798,24 @@
     <row r="37">
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C37" s="102" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="D37" s="105" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped down 1.6% at the open</t>
         </is>
       </c>
       <c r="E37" s="33" t="n">
-        <v>-0.005854605643518473</v>
+        <v>0.03291320662288366</v>
       </c>
       <c r="F37" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37" s="30" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
       </c>
       <c r="D38" s="104" t="inlineStr">
         <is>
-          <t>Gapped down 1.6% at the open</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E38" s="26" t="n">
@@ -44854,21 +44854,21 @@
     <row r="39">
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C39" s="102" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D39" s="105" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Reclaimed the 50 DMA</t>
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>0.03291320662288366</v>
+        <v>0.01392998838254322</v>
       </c>
       <c r="F39" s="34" t="n">
         <v>4</v>
@@ -44882,21 +44882,21 @@
     <row r="40">
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C40" s="101" t="inlineStr">
         <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D40" s="104" t="inlineStr">
         <is>
-          <t>Reclaimed the 50 DMA</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>0.01392998838254322</v>
+        <v>-0.006232329108589174</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>4</v>
@@ -44980,7 +44980,7 @@
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>-0.003273690907203086</v>
+        <v>-0.003156747888692357</v>
       </c>
       <c r="F43" s="34" t="n">
         <v>3</v>
@@ -45008,7 +45008,7 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>-0.003273690907203086</v>
+        <v>-0.003156747888692357</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>3</v>
@@ -45036,7 +45036,7 @@
         </is>
       </c>
       <c r="E45" s="33" t="n">
-        <v>-0.003273690907203086</v>
+        <v>-0.003156747888692357</v>
       </c>
       <c r="F45" s="34" t="n">
         <v>3</v>
@@ -45092,7 +45092,7 @@
         </is>
       </c>
       <c r="E47" s="33" t="n">
-        <v>0.004043256336109913</v>
+        <v>0.003667131125943079</v>
       </c>
       <c r="F47" s="34" t="n">
         <v>2</v>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="D48" s="104" t="inlineStr">
         <is>
-          <t>Volume 2.6x its 20-day average</t>
+          <t>Volume 2.7x its 20-day average</t>
         </is>
       </c>
       <c r="E48" s="26" t="n">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'08-31'!$5:$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'08-28'!$A$6:$AZ$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'08-28'!$5:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 3 Sep 2026, 10:37 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 3 Sep 2026, 11:15 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1376,21 +1376,21 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="L8" s="10" t="n"/>
@@ -1404,7 +1404,7 @@
       <c r="P8" s="10" t="n"/>
       <c r="Q8" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R8" s="12" t="n"/>
@@ -1413,14 +1413,14 @@
     <row r="9" ht="15" customHeight="1">
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>of 40 names</t>
+          <t>of 39 names</t>
         </is>
       </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>of 40 names</t>
+          <t>of 39 names</t>
         </is>
       </c>
       <c r="F9" s="8" t="n"/>
@@ -1441,7 +1441,7 @@
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>of 40 names</t>
+          <t>of 39 names</t>
         </is>
       </c>
       <c r="O9" s="10" t="n"/>
@@ -1957,11 +1957,11 @@
       </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>-0.02744795458096083</v>
+        <v>-0.004326930307072097</v>
       </c>
       <c r="J29" s="27" t="n">
         <v>1</v>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="L29" s="28" t="n">
-        <v>37.51016967676528</v>
+        <v>46.90028524397902</v>
       </c>
     </row>
     <row r="30">
@@ -1997,22 +1997,22 @@
       </c>
       <c r="H30" s="31" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I30" s="33" t="n">
-        <v>-0.004326930307072097</v>
+        <v>-0.001969093557282919</v>
       </c>
       <c r="J30" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="L30" s="35" t="n">
-        <v>46.90028524397902</v>
+        <v>42.75037085775087</v>
       </c>
     </row>
     <row r="31">
@@ -2037,11 +2037,11 @@
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SOXL</t>
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>-0.001969093557282919</v>
+        <v>0.003667131125943079</v>
       </c>
       <c r="J31" s="27" t="n">
         <v>2</v>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="L31" s="28" t="n">
-        <v>42.75037085775087</v>
+        <v>39.31394302464612</v>
       </c>
     </row>
     <row r="32">
@@ -2077,11 +2077,11 @@
       </c>
       <c r="H32" s="31" t="inlineStr">
         <is>
-          <t>SOXL</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="I32" s="33" t="n">
-        <v>0.003667131125943079</v>
+        <v>0.004013443884859136</v>
       </c>
       <c r="J32" s="34" t="n">
         <v>2</v>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="L32" s="35" t="n">
-        <v>39.31394302464612</v>
+        <v>46.67148684589938</v>
       </c>
     </row>
     <row r="33">
@@ -2117,11 +2117,11 @@
       </c>
       <c r="H33" s="24" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>0.004013443884859136</v>
+        <v>0.008436855537846455</v>
       </c>
       <c r="J33" s="27" t="n">
         <v>2</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="L33" s="28" t="n">
-        <v>46.67148684589938</v>
+        <v>43.26204319173591</v>
       </c>
     </row>
     <row r="34">
@@ -2157,11 +2157,11 @@
       </c>
       <c r="H34" s="31" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="I34" s="33" t="n">
-        <v>0.008436855537846455</v>
+        <v>0.0103021113084425</v>
       </c>
       <c r="J34" s="34" t="n">
         <v>2</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="L34" s="35" t="n">
-        <v>43.26204319173591</v>
+        <v>36.50808171075061</v>
       </c>
     </row>
     <row r="35">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="H35" s="24" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>0.0103021113084425</v>
+        <v>0.0112520272003036</v>
       </c>
       <c r="J35" s="27" t="n">
         <v>2</v>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="L35" s="28" t="n">
-        <v>36.50808171075061</v>
+        <v>36.14248318653912</v>
       </c>
     </row>
     <row r="36">
@@ -2237,11 +2237,11 @@
       </c>
       <c r="H36" s="31" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="I36" s="33" t="n">
-        <v>0.0112520272003036</v>
+        <v>0.01189116083254094</v>
       </c>
       <c r="J36" s="34" t="n">
         <v>2</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="L36" s="35" t="n">
-        <v>36.14248318653912</v>
+        <v>43.70604864099334</v>
       </c>
     </row>
     <row r="37">
@@ -2277,11 +2277,11 @@
       </c>
       <c r="H37" s="24" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>0.01189116083254094</v>
+        <v>0.0320447286112655</v>
       </c>
       <c r="J37" s="27" t="n">
         <v>2</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="L37" s="28" t="n">
-        <v>43.70604864099334</v>
+        <v>48.37077454734214</v>
       </c>
     </row>
     <row r="38">
@@ -2317,11 +2317,11 @@
       </c>
       <c r="H38" s="31" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="I38" s="33" t="n">
-        <v>0.0320447286112655</v>
+        <v>0.04485354305856615</v>
       </c>
       <c r="J38" s="34" t="n">
         <v>2</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="L38" s="35" t="n">
-        <v>48.37077454734214</v>
+        <v>46.47792492475057</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -2421,22 +2421,22 @@
       </c>
       <c r="H43" s="24" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I43" s="26" t="n">
-        <v>-0.02744795458096083</v>
+        <v>-0.008178391002234719</v>
       </c>
       <c r="J43" s="27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K43" s="23" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L43" s="28" t="n">
-        <v>37.51016967676528</v>
+        <v>52.87989293804576</v>
       </c>
     </row>
     <row r="44">
@@ -2461,14 +2461,14 @@
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="I44" s="33" t="n">
-        <v>-0.008178391002234719</v>
+        <v>-0.007373206433021195</v>
       </c>
       <c r="J44" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K44" s="30" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="L44" s="35" t="n">
-        <v>52.87989293804576</v>
+        <v>67.62030622942083</v>
       </c>
     </row>
     <row r="45">
@@ -2501,22 +2501,22 @@
       </c>
       <c r="H45" s="24" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="I45" s="26" t="n">
-        <v>-0.007373206433021195</v>
+        <v>-0.007113790014099619</v>
       </c>
       <c r="J45" s="27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K45" s="23" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="L45" s="28" t="n">
-        <v>67.62030622942083</v>
+        <v>42.85202081378689</v>
       </c>
     </row>
     <row r="46">
@@ -2541,22 +2541,22 @@
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="I46" s="33" t="n">
-        <v>-0.007113790014099619</v>
+        <v>-0.006232329108589174</v>
       </c>
       <c r="J46" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K46" s="30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="L46" s="35" t="n">
-        <v>42.85202081378689</v>
+        <v>51.01920682289664</v>
       </c>
     </row>
     <row r="47">
@@ -2581,22 +2581,22 @@
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="I47" s="26" t="n">
-        <v>-0.006232329108589174</v>
+        <v>-0.004326930307072097</v>
       </c>
       <c r="J47" s="27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K47" s="23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Very Weak</t>
         </is>
       </c>
       <c r="L47" s="28" t="n">
-        <v>51.01920682289664</v>
+        <v>46.90028524397902</v>
       </c>
     </row>
     <row r="48">
@@ -2621,22 +2621,22 @@
       </c>
       <c r="H48" s="31" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="I48" s="33" t="n">
-        <v>-0.004326930307072097</v>
+        <v>-0.003156747888692357</v>
       </c>
       <c r="J48" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K48" s="30" t="inlineStr">
         <is>
-          <t>Very Weak</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="L48" s="35" t="n">
-        <v>46.90028524397902</v>
+        <v>48.95291184688658</v>
       </c>
     </row>
     <row r="49">
@@ -2661,14 +2661,14 @@
       </c>
       <c r="H49" s="24" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I49" s="26" t="n">
-        <v>-0.003156747888692357</v>
+        <v>-0.001969093557282919</v>
       </c>
       <c r="J49" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L49" s="28" t="n">
-        <v>48.95291184688658</v>
+        <v>42.75037085775087</v>
       </c>
     </row>
     <row r="50">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="H50" s="31" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="I50" s="33" t="n">
-        <v>-0.001969093557282919</v>
+        <v>-0.0007253134963550734</v>
       </c>
       <c r="J50" s="34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K50" s="30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="L50" s="35" t="n">
-        <v>42.75037085775087</v>
+        <v>63.65191183967269</v>
       </c>
     </row>
     <row r="51">
@@ -2741,11 +2741,11 @@
       </c>
       <c r="H51" s="24" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="I51" s="26" t="n">
-        <v>-0.0007253134963550734</v>
+        <v>0.001023539201315593</v>
       </c>
       <c r="J51" s="27" t="n">
         <v>7</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="L51" s="28" t="n">
-        <v>63.65191183967269</v>
+        <v>52.58214372024118</v>
       </c>
     </row>
     <row r="52">
@@ -2781,11 +2781,11 @@
       </c>
       <c r="H52" s="31" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="I52" s="33" t="n">
-        <v>0.001023539201315593</v>
+        <v>0.00179241147189213</v>
       </c>
       <c r="J52" s="34" t="n">
         <v>7</v>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L52" s="35" t="n">
-        <v>52.58214372024118</v>
+        <v>61.24050752750126</v>
       </c>
     </row>
   </sheetData>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 3 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 3 Sep 2026, 11:15 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -3132,22 +3132,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>31 of 40</t>
+          <t>31 of 39</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>9 of 40</t>
+          <t>8 of 39</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>5.3 / 9</t>
+          <t>5.4 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>21 of 40</t>
+          <t>21 of 39</t>
         </is>
       </c>
     </row>
@@ -6584,17 +6584,17 @@
       </c>
       <c r="AX24" s="79" t="inlineStr">
         <is>
+          <t>Dan Ives Says M&amp;A Is the ‘Missing Piece’ for Apple in AI Arms Race — New CEO John Ternus Could Finally Shak...</t>
+        </is>
+      </c>
+      <c r="AY24" s="79" t="inlineStr">
+        <is>
           <t>What Happens To Qualcomm Stock If The New Revenue Earns Less?</t>
         </is>
       </c>
-      <c r="AY24" s="79" t="inlineStr">
+      <c r="AZ24" s="79" t="inlineStr">
         <is>
           <t>Apple (AAPL) Faces Mixed Outlook Ahead of Foldable iPhone Launch</t>
-        </is>
-      </c>
-      <c r="AZ24" s="79" t="inlineStr">
-        <is>
-          <t>Apple faces £2 bn lawsuit in UK over app privacy feature</t>
         </is>
       </c>
     </row>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="AY26" s="79" t="inlineStr">
         <is>
+          <t>Amazon Signed a Multibillion-Dollar Deal With a 175-Year-Old Glassmaker. Is Fiber the Next AI Bottleneck?</t>
+        </is>
+      </c>
+      <c r="AZ26" s="79" t="inlineStr">
+        <is>
           <t>Top Analyst Reports for Amazon, AbbVie &amp; Alibaba</t>
-        </is>
-      </c>
-      <c r="AZ26" s="79" t="inlineStr">
-        <is>
-          <t>Microsoft, Amazon and 8 More Stocks Set to Win in a $26 Trillion AI Market</t>
         </is>
       </c>
     </row>
@@ -7545,171 +7545,57 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n">
-        <v>-0.02744795458096083</v>
-      </c>
-      <c r="D30" s="27" t="n">
-        <v>25</v>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N30" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="23" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-      <c r="P30" s="25" t="inlineStr">
-        <is>
-          <t>Below every average</t>
-        </is>
-      </c>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="23" t="n"/>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="23" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="69" t="n"/>
+      <c r="O30" s="23" t="n"/>
+      <c r="P30" s="25" t="n"/>
       <c r="Q30" s="25" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
       </c>
-      <c r="R30" s="70" t="n">
-        <v>357.1600036621094</v>
-      </c>
-      <c r="S30" s="71" t="n">
-        <v>-10.07998657226562</v>
-      </c>
-      <c r="T30" s="72" t="n">
-        <v>351.614990234375</v>
-      </c>
-      <c r="U30" s="72" t="n">
-        <v>359.3999938964844</v>
-      </c>
-      <c r="V30" s="72" t="n">
-        <v>342.3305053710938</v>
-      </c>
-      <c r="W30" s="73" t="n">
-        <v>60115767</v>
-      </c>
-      <c r="X30" s="74" t="n">
-        <v>2.666778961403967</v>
-      </c>
-      <c r="Y30" s="28" t="n">
-        <v>37.51016967676528</v>
-      </c>
-      <c r="Z30" s="28" t="n">
-        <v>26.00321499704079</v>
-      </c>
-      <c r="AA30" s="28" t="n">
-        <v>22.72566419470456</v>
-      </c>
-      <c r="AB30" s="75" t="n">
-        <v>-8.502136860224084</v>
-      </c>
-      <c r="AC30" s="75" t="n">
-        <v>-7.068182913720201</v>
-      </c>
-      <c r="AD30" s="75" t="n">
-        <v>-1.433953946503883</v>
-      </c>
-      <c r="AE30" s="72" t="n">
-        <v>366.3384274771434</v>
-      </c>
-      <c r="AF30" s="72" t="n">
-        <v>375.7477269644173</v>
-      </c>
-      <c r="AG30" s="72" t="n">
-        <v>384.0817999267578</v>
-      </c>
-      <c r="AH30" s="72" t="n">
-        <v>398.3593008422852</v>
-      </c>
-      <c r="AI30" s="72" t="n">
-        <v>369.7574003601074</v>
-      </c>
-      <c r="AJ30" s="72" t="n">
-        <v>430.2575826074662</v>
-      </c>
-      <c r="AK30" s="72" t="n">
-        <v>381.8164993286133</v>
-      </c>
-      <c r="AL30" s="72" t="n">
-        <v>333.3754160497604</v>
-      </c>
-      <c r="AM30" s="76" t="n">
-        <v>0.2455001622840689</v>
-      </c>
-      <c r="AN30" s="29" t="n">
-        <v>25.37401257621489</v>
-      </c>
-      <c r="AO30" s="77" t="n">
-        <v>3.788657765020125</v>
-      </c>
-      <c r="AP30" s="72" t="n">
-        <v>495</v>
-      </c>
-      <c r="AQ30" s="72" t="n">
-        <v>289.9599914550781</v>
-      </c>
-      <c r="AR30" s="29" t="n">
-        <v>-27.84646390664457</v>
-      </c>
-      <c r="AS30" s="78" t="n">
-        <v>32.7740974475762</v>
-      </c>
-      <c r="AT30" s="26" t="n">
-        <v>-0.03870378573529543</v>
-      </c>
-      <c r="AU30" s="26" t="n">
-        <v>-0.1461222035372461</v>
-      </c>
-      <c r="AV30" s="26" t="n">
-        <v>-0.1474063628468687</v>
-      </c>
-      <c r="AW30" s="26" t="n">
-        <v>0.03195607443961102</v>
-      </c>
+      <c r="R30" s="70" t="n"/>
+      <c r="S30" s="71" t="n"/>
+      <c r="T30" s="72" t="n"/>
+      <c r="U30" s="72" t="n"/>
+      <c r="V30" s="72" t="n"/>
+      <c r="W30" s="73" t="n"/>
+      <c r="X30" s="74" t="n"/>
+      <c r="Y30" s="28" t="n"/>
+      <c r="Z30" s="28" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="75" t="n"/>
+      <c r="AC30" s="75" t="n"/>
+      <c r="AD30" s="75" t="n"/>
+      <c r="AE30" s="72" t="n"/>
+      <c r="AF30" s="72" t="n"/>
+      <c r="AG30" s="72" t="n"/>
+      <c r="AH30" s="72" t="n"/>
+      <c r="AI30" s="72" t="n"/>
+      <c r="AJ30" s="72" t="n"/>
+      <c r="AK30" s="72" t="n"/>
+      <c r="AL30" s="72" t="n"/>
+      <c r="AM30" s="76" t="n"/>
+      <c r="AN30" s="29" t="n"/>
+      <c r="AO30" s="77" t="n"/>
+      <c r="AP30" s="72" t="n"/>
+      <c r="AQ30" s="72" t="n"/>
+      <c r="AR30" s="29" t="n"/>
+      <c r="AS30" s="78" t="n"/>
+      <c r="AT30" s="26" t="n"/>
+      <c r="AU30" s="26" t="n"/>
+      <c r="AV30" s="26" t="n"/>
+      <c r="AW30" s="26" t="n"/>
       <c r="AX30" s="79" t="inlineStr">
         <is>
           <t>Broadcom Shares Fall 5.6% Even as Revenue Surges 86%</t>
@@ -11096,17 +10982,17 @@
       </c>
       <c r="AX48" s="79" t="inlineStr">
         <is>
+          <t>Musk Said Robots Will Outproduce All Humans, Then Promised Austin 30,000 Jobs</t>
+        </is>
+      </c>
+      <c r="AY48" s="79" t="inlineStr">
+        <is>
           <t>Dow Jones Futures: Stocks Jump On Fed's Waller; Tesla Cybercab Event Private, Jobs Report Looms</t>
         </is>
       </c>
-      <c r="AY48" s="79" t="inlineStr">
-        <is>
-          <t>Tesla Launching Cybercab Robotaxis. Here's What To Look For.</t>
-        </is>
-      </c>
       <c r="AZ48" s="79" t="inlineStr">
         <is>
-          <t>Tesla's 45 Cybercabs Face a $1.3 Trillion Reality Check</t>
+          <t>Tesla is asking people if they want to buy and run Cybercab fleets</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11529,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 3 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 3 Sep 2026, 11:15 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -11668,22 +11554,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>30 of 40</t>
+          <t>30 of 39</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>10 of 40</t>
+          <t>9 of 39</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.0 / 9</t>
+          <t>4.1 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>13 of 40</t>
+          <t>13 of 39</t>
         </is>
       </c>
     </row>
@@ -15829,171 +15715,57 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n">
-        <v>-0.006600309699600682</v>
-      </c>
-      <c r="D30" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N30" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="23" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-      <c r="P30" s="25" t="inlineStr">
-        <is>
-          <t>Below every average</t>
-        </is>
-      </c>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="23" t="n"/>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="23" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="69" t="n"/>
+      <c r="O30" s="23" t="n"/>
+      <c r="P30" s="25" t="n"/>
       <c r="Q30" s="25" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
       </c>
-      <c r="R30" s="70" t="n">
-        <v>367.239990234375</v>
-      </c>
-      <c r="S30" s="71" t="n">
-        <v>-2.44000244140625</v>
-      </c>
-      <c r="T30" s="72" t="n">
-        <v>369.6799926757812</v>
-      </c>
-      <c r="U30" s="72" t="n">
-        <v>371.0899963378906</v>
-      </c>
-      <c r="V30" s="72" t="n">
-        <v>364.6499938964844</v>
-      </c>
-      <c r="W30" s="73" t="n">
-        <v>38874600</v>
-      </c>
-      <c r="X30" s="74" t="n">
-        <v>1.921436532630159</v>
-      </c>
-      <c r="Y30" s="28" t="n">
-        <v>42.128064745238</v>
-      </c>
-      <c r="Z30" s="28" t="n">
-        <v>27.51440103145891</v>
-      </c>
-      <c r="AA30" s="28" t="n">
-        <v>21.57471555558841</v>
-      </c>
-      <c r="AB30" s="75" t="n">
-        <v>-7.916960229685571</v>
-      </c>
-      <c r="AC30" s="75" t="n">
-        <v>-6.70969442709423</v>
-      </c>
-      <c r="AD30" s="75" t="n">
-        <v>-1.207265802591341</v>
-      </c>
-      <c r="AE30" s="72" t="n">
-        <v>368.9608342814388</v>
-      </c>
-      <c r="AF30" s="72" t="n">
-        <v>377.6064992946481</v>
-      </c>
-      <c r="AG30" s="72" t="n">
-        <v>384.58</v>
-      </c>
-      <c r="AH30" s="72" t="n">
-        <v>398.585200805664</v>
-      </c>
-      <c r="AI30" s="72" t="n">
-        <v>369.6839002990723</v>
-      </c>
-      <c r="AJ30" s="72" t="n">
-        <v>434.8378629372112</v>
-      </c>
-      <c r="AK30" s="72" t="n">
-        <v>384.9869995117188</v>
-      </c>
-      <c r="AL30" s="72" t="n">
-        <v>335.1361360862263</v>
-      </c>
-      <c r="AM30" s="76" t="n">
-        <v>0.3219989779728831</v>
-      </c>
-      <c r="AN30" s="29" t="n">
-        <v>25.89742692024332</v>
-      </c>
-      <c r="AO30" s="77" t="n">
-        <v>3.446341995677256</v>
-      </c>
-      <c r="AP30" s="72" t="n">
-        <v>495</v>
-      </c>
-      <c r="AQ30" s="72" t="n">
-        <v>289.9599914550781</v>
-      </c>
-      <c r="AR30" s="29" t="n">
-        <v>-25.81010298295454</v>
-      </c>
-      <c r="AS30" s="78" t="n">
-        <v>37.69020462285327</v>
-      </c>
-      <c r="AT30" s="26" t="n">
-        <v>0.03276243431048109</v>
-      </c>
-      <c r="AU30" s="26" t="n">
-        <v>-0.1217716017356836</v>
-      </c>
-      <c r="AV30" s="26" t="n">
-        <v>-0.2336874114404076</v>
-      </c>
-      <c r="AW30" s="26" t="n">
-        <v>0.06108056561124875</v>
-      </c>
+      <c r="R30" s="70" t="n"/>
+      <c r="S30" s="71" t="n"/>
+      <c r="T30" s="72" t="n"/>
+      <c r="U30" s="72" t="n"/>
+      <c r="V30" s="72" t="n"/>
+      <c r="W30" s="73" t="n"/>
+      <c r="X30" s="74" t="n"/>
+      <c r="Y30" s="28" t="n"/>
+      <c r="Z30" s="28" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="75" t="n"/>
+      <c r="AC30" s="75" t="n"/>
+      <c r="AD30" s="75" t="n"/>
+      <c r="AE30" s="72" t="n"/>
+      <c r="AF30" s="72" t="n"/>
+      <c r="AG30" s="72" t="n"/>
+      <c r="AH30" s="72" t="n"/>
+      <c r="AI30" s="72" t="n"/>
+      <c r="AJ30" s="72" t="n"/>
+      <c r="AK30" s="72" t="n"/>
+      <c r="AL30" s="72" t="n"/>
+      <c r="AM30" s="76" t="n"/>
+      <c r="AN30" s="29" t="n"/>
+      <c r="AO30" s="77" t="n"/>
+      <c r="AP30" s="72" t="n"/>
+      <c r="AQ30" s="72" t="n"/>
+      <c r="AR30" s="29" t="n"/>
+      <c r="AS30" s="78" t="n"/>
+      <c r="AT30" s="26" t="n"/>
+      <c r="AU30" s="26" t="n"/>
+      <c r="AV30" s="26" t="n"/>
+      <c r="AW30" s="26" t="n"/>
       <c r="AX30" s="25" t="n"/>
       <c r="AY30" s="25" t="n"/>
       <c r="AZ30" s="25" t="n"/>
@@ -16185,7 +15957,7 @@
         <v>-0.01124005114350968</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -17065,7 +16837,7 @@
         <v>-0.008382862523551915</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -17241,7 +17013,7 @@
         <v>-0.01353295042585745</v>
       </c>
       <c r="D38" s="27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
@@ -17945,7 +17717,7 @@
         <v>-0.009063459196570256</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -18297,7 +18069,7 @@
         <v>-0.0581369028542128</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
@@ -19579,7 +19351,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 3 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 3 Sep 2026, 11:15 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19604,22 +19376,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>5 of 40</t>
+          <t>5 of 39</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>35 of 40</t>
+          <t>34 of 39</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>3.2 / 9</t>
+          <t>3.3 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>9 of 40</t>
+          <t>9 of 39</t>
         </is>
       </c>
     </row>
@@ -22889,7 +22661,7 @@
         <v>-0.02360217505168549</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -23065,7 +22837,7 @@
         <v>-0.01867032778937106</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
@@ -23241,7 +23013,7 @@
         <v>-0.02909895842760113</v>
       </c>
       <c r="D27" s="34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
@@ -23417,7 +23189,7 @@
         <v>-0.02930840490496478</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
@@ -23593,7 +23365,7 @@
         <v>-0.05583755198412677</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E29" s="30" t="inlineStr">
         <is>
@@ -23765,171 +23537,57 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n">
-        <v>-0.001782156042112182</v>
-      </c>
-      <c r="D30" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N30" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="O30" s="23" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="P30" s="25" t="inlineStr">
-        <is>
-          <t>Long-term up, short-term mixed</t>
-        </is>
-      </c>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="23" t="n"/>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="23" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="69" t="n"/>
+      <c r="O30" s="23" t="n"/>
+      <c r="P30" s="25" t="n"/>
       <c r="Q30" s="25" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
       </c>
-      <c r="R30" s="70" t="n">
-        <v>369.6799926757812</v>
-      </c>
-      <c r="S30" s="71" t="n">
-        <v>-0.660003662109375</v>
-      </c>
-      <c r="T30" s="72" t="n">
-        <v>364.25</v>
-      </c>
-      <c r="U30" s="72" t="n">
-        <v>371.3999938964844</v>
-      </c>
-      <c r="V30" s="72" t="n">
-        <v>362</v>
-      </c>
-      <c r="W30" s="73" t="n">
-        <v>19288900</v>
-      </c>
-      <c r="X30" s="74" t="n">
-        <v>1.008183003229087</v>
-      </c>
-      <c r="Y30" s="28" t="n">
-        <v>43.32701006182213</v>
-      </c>
-      <c r="Z30" s="28" t="n">
-        <v>26.20891124506882</v>
-      </c>
-      <c r="AA30" s="28" t="n">
-        <v>21.64620451808354</v>
-      </c>
-      <c r="AB30" s="75" t="n">
-        <v>-8.081232177997094</v>
-      </c>
-      <c r="AC30" s="75" t="n">
-        <v>-6.407877976446394</v>
-      </c>
-      <c r="AD30" s="75" t="n">
-        <v>-1.6733542015507</v>
-      </c>
-      <c r="AE30" s="72" t="n">
-        <v>369.4525040091713</v>
-      </c>
-      <c r="AF30" s="72" t="n">
-        <v>378.6431502006754</v>
-      </c>
-      <c r="AG30" s="72" t="n">
-        <v>384.8382000732422</v>
-      </c>
-      <c r="AH30" s="72" t="n">
-        <v>398.62830078125</v>
-      </c>
-      <c r="AI30" s="72" t="n">
-        <v>369.547600402832</v>
-      </c>
-      <c r="AJ30" s="72" t="n">
-        <v>438.7029643273173</v>
-      </c>
-      <c r="AK30" s="72" t="n">
-        <v>387.5389999389648</v>
-      </c>
-      <c r="AL30" s="72" t="n">
-        <v>336.3750355506123</v>
-      </c>
-      <c r="AM30" s="76" t="n">
-        <v>0.3254727963647674</v>
-      </c>
-      <c r="AN30" s="29" t="n">
-        <v>26.4045499402179</v>
-      </c>
-      <c r="AO30" s="77" t="n">
-        <v>3.552944855814614</v>
-      </c>
-      <c r="AP30" s="72" t="n">
-        <v>495</v>
-      </c>
-      <c r="AQ30" s="72" t="n">
-        <v>287.1700134277344</v>
-      </c>
-      <c r="AR30" s="29" t="n">
-        <v>-25.31717319681187</v>
-      </c>
-      <c r="AS30" s="78" t="n">
-        <v>39.70070951207848</v>
-      </c>
-      <c r="AT30" s="26" t="n">
-        <v>0.03627292368569268</v>
-      </c>
-      <c r="AU30" s="26" t="n">
-        <v>-0.05749182285629051</v>
-      </c>
-      <c r="AV30" s="26" t="n">
-        <v>-0.2323442343723602</v>
-      </c>
-      <c r="AW30" s="26" t="n">
-        <v>0.06813055809427815</v>
-      </c>
+      <c r="R30" s="70" t="n"/>
+      <c r="S30" s="71" t="n"/>
+      <c r="T30" s="72" t="n"/>
+      <c r="U30" s="72" t="n"/>
+      <c r="V30" s="72" t="n"/>
+      <c r="W30" s="73" t="n"/>
+      <c r="X30" s="74" t="n"/>
+      <c r="Y30" s="28" t="n"/>
+      <c r="Z30" s="28" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="75" t="n"/>
+      <c r="AC30" s="75" t="n"/>
+      <c r="AD30" s="75" t="n"/>
+      <c r="AE30" s="72" t="n"/>
+      <c r="AF30" s="72" t="n"/>
+      <c r="AG30" s="72" t="n"/>
+      <c r="AH30" s="72" t="n"/>
+      <c r="AI30" s="72" t="n"/>
+      <c r="AJ30" s="72" t="n"/>
+      <c r="AK30" s="72" t="n"/>
+      <c r="AL30" s="72" t="n"/>
+      <c r="AM30" s="76" t="n"/>
+      <c r="AN30" s="29" t="n"/>
+      <c r="AO30" s="77" t="n"/>
+      <c r="AP30" s="72" t="n"/>
+      <c r="AQ30" s="72" t="n"/>
+      <c r="AR30" s="29" t="n"/>
+      <c r="AS30" s="78" t="n"/>
+      <c r="AT30" s="26" t="n"/>
+      <c r="AU30" s="26" t="n"/>
+      <c r="AV30" s="26" t="n"/>
+      <c r="AW30" s="26" t="n"/>
       <c r="AX30" s="25" t="n"/>
       <c r="AY30" s="25" t="n"/>
       <c r="AZ30" s="25" t="n"/>
@@ -23945,7 +23603,7 @@
         <v>-0.02531389171652176</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -24121,7 +23779,7 @@
         <v>-0.03581106063593686</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -24297,7 +23955,7 @@
         <v>-0.06800291463242925</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -24473,7 +24131,7 @@
         <v>-0.01007723337380684</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
@@ -24649,7 +24307,7 @@
         <v>-0.007948321980374096</v>
       </c>
       <c r="D35" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" s="30" t="inlineStr">
         <is>
@@ -24825,7 +24483,7 @@
         <v>-0.006032855576357687</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -25001,7 +24659,7 @@
         <v>-0.01235983249351691</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -25177,7 +24835,7 @@
         <v>-0.06062889303421481</v>
       </c>
       <c r="D38" s="27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
@@ -25353,7 +25011,7 @@
         <v>-0.02637862437031413</v>
       </c>
       <c r="D39" s="34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E39" s="30" t="inlineStr">
         <is>
@@ -25529,7 +25187,7 @@
         <v>-0.03286164112737533</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
@@ -25705,7 +25363,7 @@
         <v>-0.002961202765295323</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="30" t="inlineStr">
         <is>
@@ -25881,7 +25539,7 @@
         <v>-0.02071006223241978</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -26057,7 +25715,7 @@
         <v>-0.0151281653970361</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
@@ -26233,7 +25891,7 @@
         <v>-0.03466040639889967</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
@@ -26409,7 +26067,7 @@
         <v>-0.02270058196958502</v>
       </c>
       <c r="D45" s="34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
@@ -26585,7 +26243,7 @@
         <v>-0.02158944450796974</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -26761,7 +26419,7 @@
         <v>-0.01903999296889936</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E47" s="30" t="inlineStr">
         <is>
@@ -26937,7 +26595,7 @@
         <v>-0.03223268236356913</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
@@ -27515,7 +27173,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 3 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 3 Sep 2026, 11:15 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27540,12 +27198,12 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>19 of 40</t>
+          <t>18 of 39</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>21 of 40</t>
+          <t>21 of 39</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
@@ -27555,7 +27213,7 @@
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>15 of 40</t>
+          <t>15 of 39</t>
         </is>
       </c>
     </row>
@@ -30649,7 +30307,7 @@
         <v>-0.008914626195478559</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
@@ -31001,7 +30659,7 @@
         <v>-0.02499719943397638</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
@@ -31701,171 +31359,57 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n">
-        <v>0.004202900721427705</v>
-      </c>
-      <c r="D30" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N30" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="O30" s="23" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="P30" s="25" t="inlineStr">
-        <is>
-          <t>Long-term up, short-term mixed</t>
-        </is>
-      </c>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="23" t="n"/>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="23" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="69" t="n"/>
+      <c r="O30" s="23" t="n"/>
+      <c r="P30" s="25" t="n"/>
       <c r="Q30" s="25" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
       </c>
-      <c r="R30" s="70" t="n">
-        <v>370.3399963378906</v>
-      </c>
-      <c r="S30" s="71" t="n">
-        <v>1.54998779296875</v>
-      </c>
-      <c r="T30" s="72" t="n">
-        <v>369.5199890136719</v>
-      </c>
-      <c r="U30" s="72" t="n">
-        <v>372.75</v>
-      </c>
-      <c r="V30" s="72" t="n">
-        <v>366.2999877929688</v>
-      </c>
-      <c r="W30" s="73" t="n">
-        <v>21948000</v>
-      </c>
-      <c r="X30" s="74" t="n">
-        <v>1.117168008620538</v>
-      </c>
-      <c r="Y30" s="28" t="n">
-        <v>43.63895186508395</v>
-      </c>
-      <c r="Z30" s="28" t="n">
-        <v>26.53060980059774</v>
-      </c>
-      <c r="AA30" s="28" t="n">
-        <v>21.72319263153983</v>
-      </c>
-      <c r="AB30" s="75" t="n">
-        <v>-8.421794336196172</v>
-      </c>
-      <c r="AC30" s="75" t="n">
-        <v>-5.989539426058719</v>
-      </c>
-      <c r="AD30" s="75" t="n">
-        <v>-2.432254910137453</v>
-      </c>
-      <c r="AE30" s="72" t="n">
-        <v>369.3875072472828</v>
-      </c>
-      <c r="AF30" s="72" t="n">
-        <v>379.5394659531648</v>
-      </c>
-      <c r="AG30" s="72" t="n">
-        <v>385.2872003173828</v>
-      </c>
-      <c r="AH30" s="72" t="n">
-        <v>398.4806008911133</v>
-      </c>
-      <c r="AI30" s="72" t="n">
-        <v>369.4753004455566</v>
-      </c>
-      <c r="AJ30" s="72" t="n">
-        <v>442.0973316242758</v>
-      </c>
-      <c r="AK30" s="72" t="n">
-        <v>389.9630004882812</v>
-      </c>
-      <c r="AL30" s="72" t="n">
-        <v>337.8286693522867</v>
-      </c>
-      <c r="AM30" s="76" t="n">
-        <v>0.3118034342935829</v>
-      </c>
-      <c r="AN30" s="29" t="n">
-        <v>26.73809108593175</v>
-      </c>
-      <c r="AO30" s="77" t="n">
-        <v>3.624182680102603</v>
-      </c>
-      <c r="AP30" s="72" t="n">
-        <v>495</v>
-      </c>
-      <c r="AQ30" s="72" t="n">
-        <v>287.1700134277344</v>
-      </c>
-      <c r="AR30" s="29" t="n">
-        <v>-25.18383912365846</v>
-      </c>
-      <c r="AS30" s="78" t="n">
-        <v>40.01827853712381</v>
-      </c>
-      <c r="AT30" s="26" t="n">
-        <v>0.03227780760690346</v>
-      </c>
-      <c r="AU30" s="26" t="n">
-        <v>-0.04865393161939546</v>
-      </c>
-      <c r="AV30" s="26" t="n">
-        <v>-0.1948605444810436</v>
-      </c>
-      <c r="AW30" s="26" t="n">
-        <v>0.0700375319471247</v>
-      </c>
+      <c r="R30" s="70" t="n"/>
+      <c r="S30" s="71" t="n"/>
+      <c r="T30" s="72" t="n"/>
+      <c r="U30" s="72" t="n"/>
+      <c r="V30" s="72" t="n"/>
+      <c r="W30" s="73" t="n"/>
+      <c r="X30" s="74" t="n"/>
+      <c r="Y30" s="28" t="n"/>
+      <c r="Z30" s="28" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="75" t="n"/>
+      <c r="AC30" s="75" t="n"/>
+      <c r="AD30" s="75" t="n"/>
+      <c r="AE30" s="72" t="n"/>
+      <c r="AF30" s="72" t="n"/>
+      <c r="AG30" s="72" t="n"/>
+      <c r="AH30" s="72" t="n"/>
+      <c r="AI30" s="72" t="n"/>
+      <c r="AJ30" s="72" t="n"/>
+      <c r="AK30" s="72" t="n"/>
+      <c r="AL30" s="72" t="n"/>
+      <c r="AM30" s="76" t="n"/>
+      <c r="AN30" s="29" t="n"/>
+      <c r="AO30" s="77" t="n"/>
+      <c r="AP30" s="72" t="n"/>
+      <c r="AQ30" s="72" t="n"/>
+      <c r="AR30" s="29" t="n"/>
+      <c r="AS30" s="78" t="n"/>
+      <c r="AT30" s="26" t="n"/>
+      <c r="AU30" s="26" t="n"/>
+      <c r="AV30" s="26" t="n"/>
+      <c r="AW30" s="26" t="n"/>
       <c r="AX30" s="25" t="n"/>
       <c r="AY30" s="25" t="n"/>
       <c r="AZ30" s="25" t="n"/>
@@ -31881,7 +31425,7 @@
         <v>-0.01249874985801214</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -32233,7 +31777,7 @@
         <v>-0.0005040778398927026</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -32409,7 +31953,7 @@
         <v>-0.02178605084672747</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
@@ -32761,7 +32305,7 @@
         <v>0.0004470874592776841</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -32937,7 +32481,7 @@
         <v>-0.01215122854742678</v>
       </c>
       <c r="D37" s="34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E37" s="30" t="inlineStr">
         <is>
@@ -33465,7 +33009,7 @@
         <v>-0.01367236567406971</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
@@ -33641,7 +33185,7 @@
         <v>-0.008198704832808712</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E41" s="30" t="inlineStr">
         <is>
@@ -33817,7 +33361,7 @@
         <v>-0.00685599359086031</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -34169,7 +33713,7 @@
         <v>0.0004831799877809129</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
@@ -34521,7 +34065,7 @@
         <v>-0.007299289100143769</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -35451,7 +34995,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 3 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 3 Sep 2026, 11:15 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35476,22 +35020,22 @@
       </c>
       <c r="Y3" s="44" t="inlineStr">
         <is>
-          <t>12 of 40</t>
+          <t>12 of 39</t>
         </is>
       </c>
       <c r="AA3" s="45" t="inlineStr">
         <is>
-          <t>28 of 40</t>
+          <t>27 of 39</t>
         </is>
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>4.2 / 9</t>
+          <t>4.4 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>16 of 40</t>
+          <t>16 of 39</t>
         </is>
       </c>
     </row>
@@ -38761,7 +38305,7 @@
         <v>-0.02326562725379</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -39113,7 +38657,7 @@
         <v>-0.03192951480000428</v>
       </c>
       <c r="D27" s="34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
@@ -39289,7 +38833,7 @@
         <v>-0.06332041548914424</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
@@ -39465,7 +39009,7 @@
         <v>-0.05517577254916717</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29" s="30" t="inlineStr">
         <is>
@@ -39637,171 +39181,57 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n">
-        <v>-0.007401625495918829</v>
-      </c>
-      <c r="D30" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M30" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N30" s="69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="23" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-      <c r="P30" s="25" t="inlineStr">
-        <is>
-          <t>Below every average</t>
-        </is>
-      </c>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="23" t="n"/>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="23" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="69" t="n"/>
+      <c r="O30" s="23" t="n"/>
+      <c r="P30" s="25" t="n"/>
       <c r="Q30" s="25" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
       </c>
-      <c r="R30" s="70" t="n">
-        <v>368.7900085449219</v>
-      </c>
-      <c r="S30" s="71" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="T30" s="72" t="n">
-        <v>373.6000061035156</v>
-      </c>
-      <c r="U30" s="72" t="n">
-        <v>376.5899963378906</v>
-      </c>
-      <c r="V30" s="72" t="n">
-        <v>365.3500061035156</v>
-      </c>
-      <c r="W30" s="73" t="n">
-        <v>16596100</v>
-      </c>
-      <c r="X30" s="74" t="n">
-        <v>0.8548319139445547</v>
-      </c>
-      <c r="Y30" s="28" t="n">
-        <v>42.73994319076292</v>
-      </c>
-      <c r="Z30" s="28" t="n">
-        <v>24.41982790794276</v>
-      </c>
-      <c r="AA30" s="28" t="n">
-        <v>22.09664002115975</v>
-      </c>
-      <c r="AB30" s="75" t="n">
-        <v>-8.801177037003981</v>
-      </c>
-      <c r="AC30" s="75" t="n">
-        <v>-5.381475698524355</v>
-      </c>
-      <c r="AD30" s="75" t="n">
-        <v>-3.419701338479626</v>
-      </c>
-      <c r="AE30" s="72" t="n">
-        <v>369.1153675071091</v>
-      </c>
-      <c r="AF30" s="72" t="n">
-        <v>380.4594129146923</v>
-      </c>
-      <c r="AG30" s="72" t="n">
-        <v>386.1074005126953</v>
-      </c>
-      <c r="AH30" s="72" t="n">
-        <v>398.2835009765625</v>
-      </c>
-      <c r="AI30" s="72" t="n">
-        <v>369.3834004211426</v>
-      </c>
-      <c r="AJ30" s="72" t="n">
-        <v>442.4112952823579</v>
-      </c>
-      <c r="AK30" s="72" t="n">
-        <v>391.0575012207031</v>
-      </c>
-      <c r="AL30" s="72" t="n">
-        <v>339.7037071590483</v>
-      </c>
-      <c r="AM30" s="76" t="n">
-        <v>0.2831952528274042</v>
-      </c>
-      <c r="AN30" s="29" t="n">
-        <v>26.26406290704136</v>
-      </c>
-      <c r="AO30" s="77" t="n">
-        <v>3.784833888275186</v>
-      </c>
-      <c r="AP30" s="72" t="n">
-        <v>495</v>
-      </c>
-      <c r="AQ30" s="72" t="n">
-        <v>287.1700134277344</v>
-      </c>
-      <c r="AR30" s="29" t="n">
-        <v>-25.49696797072285</v>
-      </c>
-      <c r="AS30" s="78" t="n">
-        <v>39.27248250521683</v>
-      </c>
-      <c r="AT30" s="26" t="n">
-        <v>0.0009227746685473992</v>
-      </c>
-      <c r="AU30" s="26" t="n">
-        <v>-0.04911816205869646</v>
-      </c>
-      <c r="AV30" s="26" t="n">
-        <v>-0.174541671075323</v>
-      </c>
-      <c r="AW30" s="26" t="n">
-        <v>0.06555909286699024</v>
-      </c>
+      <c r="R30" s="70" t="n"/>
+      <c r="S30" s="71" t="n"/>
+      <c r="T30" s="72" t="n"/>
+      <c r="U30" s="72" t="n"/>
+      <c r="V30" s="72" t="n"/>
+      <c r="W30" s="73" t="n"/>
+      <c r="X30" s="74" t="n"/>
+      <c r="Y30" s="28" t="n"/>
+      <c r="Z30" s="28" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="75" t="n"/>
+      <c r="AC30" s="75" t="n"/>
+      <c r="AD30" s="75" t="n"/>
+      <c r="AE30" s="72" t="n"/>
+      <c r="AF30" s="72" t="n"/>
+      <c r="AG30" s="72" t="n"/>
+      <c r="AH30" s="72" t="n"/>
+      <c r="AI30" s="72" t="n"/>
+      <c r="AJ30" s="72" t="n"/>
+      <c r="AK30" s="72" t="n"/>
+      <c r="AL30" s="72" t="n"/>
+      <c r="AM30" s="76" t="n"/>
+      <c r="AN30" s="29" t="n"/>
+      <c r="AO30" s="77" t="n"/>
+      <c r="AP30" s="72" t="n"/>
+      <c r="AQ30" s="72" t="n"/>
+      <c r="AR30" s="29" t="n"/>
+      <c r="AS30" s="78" t="n"/>
+      <c r="AT30" s="26" t="n"/>
+      <c r="AU30" s="26" t="n"/>
+      <c r="AV30" s="26" t="n"/>
+      <c r="AW30" s="26" t="n"/>
       <c r="AX30" s="25" t="n"/>
       <c r="AY30" s="25" t="n"/>
       <c r="AZ30" s="25" t="n"/>
@@ -39817,7 +39247,7 @@
         <v>-0.05943759603113641</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E31" s="30" t="inlineStr">
         <is>
@@ -39993,7 +39423,7 @@
         <v>-0.02960829037404245</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
@@ -40169,7 +39599,7 @@
         <v>-0.03392203277851213</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E33" s="30" t="inlineStr">
         <is>
@@ -40521,7 +39951,7 @@
         <v>-0.1253392097053883</v>
       </c>
       <c r="D35" s="34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" s="30" t="inlineStr">
         <is>
@@ -40697,7 +40127,7 @@
         <v>-0.02845037703741871</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
@@ -41049,7 +40479,7 @@
         <v>-0.07343520222782773</v>
       </c>
       <c r="D38" s="27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
@@ -41401,7 +40831,7 @@
         <v>-0.04256684013924827</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
@@ -41753,7 +41183,7 @@
         <v>-0.03588291869363736</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
@@ -41929,7 +41359,7 @@
         <v>-0.04574959589106331</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
@@ -42457,7 +41887,7 @@
         <v>-0.04649784460844808</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
@@ -42809,7 +42239,7 @@
         <v>-0.01707955694679375</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
@@ -43864,7 +43294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G49"/>
+  <dimension ref="B2:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -45103,68 +44533,12 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="C48" s="101" t="inlineStr">
-        <is>
-          <t>Broadcom Inc.</t>
-        </is>
-      </c>
-      <c r="D48" s="104" t="inlineStr">
-        <is>
-          <t>Volume 2.7x its 20-day average</t>
-        </is>
-      </c>
-      <c r="E48" s="26" t="n">
-        <v>-0.02744795458096083</v>
-      </c>
-      <c r="F48" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="23" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="31" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="C49" s="102" t="inlineStr">
-        <is>
-          <t>Broadcom Inc.</t>
-        </is>
-      </c>
-      <c r="D49" s="105" t="inlineStr">
-        <is>
-          <t>Gapped down 4.3% at the open</t>
-        </is>
-      </c>
-      <c r="E49" s="33" t="n">
-        <v>-0.02744795458096083</v>
-      </c>
-      <c r="F49" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="30" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="B5:G49"/>
+  <autoFilter ref="B5:G47"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E49">
+  <conditionalFormatting sqref="E6:E47">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 4 Sep 2026, 10:23 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 4 Sep 2026, 11:02 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 4 Sep 2026, 10:23 PM · Yahoo Finance data</t>
+          <t>Built 4 Sep 2026, 11:02 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -5811,17 +5811,17 @@
       </c>
       <c r="AX19" s="79" t="inlineStr">
         <is>
+          <t>S&amp;P 500, Dow End Lower As Blowout Jobs Report Fans Rate Hike Fears, While Chipmaker Strength Aids Nasdaq —T...</t>
+        </is>
+      </c>
+      <c r="AY19" s="79" t="inlineStr">
+        <is>
           <t>This Is the Most Expensive Market in Decades. Is It Really Safe to Invest Right Now?</t>
         </is>
       </c>
-      <c r="AY19" s="79" t="inlineStr">
+      <c r="AZ19" s="79" t="inlineStr">
         <is>
           <t>GoPro Zooms 34% Higher on Starman Optical Merger and Markiplier Stake; Coherent Climbs 7%, Lumentum Gains 3%</t>
-        </is>
-      </c>
-      <c r="AZ19" s="79" t="inlineStr">
-        <is>
-          <t>SanDisk Rises 8%, Micron Gains 5%: Is the NAND Pricing Cycle Still Accelerating?</t>
         </is>
       </c>
     </row>
@@ -6589,12 +6589,12 @@
       </c>
       <c r="AY24" s="79" t="inlineStr">
         <is>
+          <t>Dow Jones Futures: Nvidia, Micron, Sandisk Flash Buy Signals; Apple, Inflation Reports Ahead</t>
+        </is>
+      </c>
+      <c r="AZ24" s="79" t="inlineStr">
+        <is>
           <t>Why Apple (AAPL) Dipped More Than Broader Market Today</t>
-        </is>
-      </c>
-      <c r="AZ24" s="79" t="inlineStr">
-        <is>
-          <t>Top Research Reports for Apple, Broadcom &amp; Shell</t>
         </is>
       </c>
     </row>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
+          <t>Jim Cramer Says “Someone Must Know Something” About Broadcom Inc. (NASDAQ:AVGO)’s Post-Earnings Share Dip</t>
+        </is>
+      </c>
+      <c r="AY30" s="79" t="inlineStr">
+        <is>
           <t>Top Research Reports for Apple, Broadcom &amp; Shell</t>
         </is>
       </c>
-      <c r="AY30" s="79" t="inlineStr">
+      <c r="AZ30" s="79" t="inlineStr">
         <is>
           <t>5-star analyst resets Broadcom stock price target</t>
-        </is>
-      </c>
-      <c r="AZ30" s="79" t="inlineStr">
-        <is>
-          <t>Is AVGO Stock Poised for a Rebound After Broadcom's Strong Q3 Results?</t>
         </is>
       </c>
     </row>
@@ -8276,17 +8276,17 @@
       </c>
       <c r="AX33" s="90" t="inlineStr">
         <is>
+          <t>Jim Cramer Couldn’t Stop Gushing About This Computer Hardware AI Stock</t>
+        </is>
+      </c>
+      <c r="AY33" s="90" t="inlineStr">
+        <is>
           <t>DELL Stock Hits 52-Week High: Does it Have More Room to Run?</t>
         </is>
       </c>
-      <c r="AY33" s="90" t="inlineStr">
+      <c r="AZ33" s="90" t="inlineStr">
         <is>
           <t>Super Micro Surges 7% as Semiconductors Lead a Flat Tape; Hewlett Packard Enterprise Falls 3%, Dell Edges H...</t>
-        </is>
-      </c>
-      <c r="AZ33" s="90" t="inlineStr">
-        <is>
-          <t>Dell Afterglow Continues. These Other Stocks Top Buy Points.</t>
         </is>
       </c>
     </row>
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
+          <t>Jim Cramer Flagged Another Risk For Adobe Inc. (NASDAQ:ADBE)</t>
+        </is>
+      </c>
+      <c r="AY34" s="79" t="inlineStr">
+        <is>
           <t>Jim Cramer flagged one stock quietly concentrating portfolios</t>
         </is>
       </c>
-      <c r="AY34" s="79" t="inlineStr">
+      <c r="AZ34" s="79" t="inlineStr">
         <is>
           <t>Why IBM, Microsoft Back Move for Quantum Policy Czar</t>
-        </is>
-      </c>
-      <c r="AZ34" s="79" t="inlineStr">
-        <is>
-          <t>Google Turns Three Everyday Apps Into Paid Gemini Microphones</t>
         </is>
       </c>
     </row>
@@ -8840,17 +8840,17 @@
       </c>
       <c r="AX36" s="79" t="inlineStr">
         <is>
+          <t>Coatue Opened Positions in Intel and Cerebras. Is the AI Chip Trade Broadening Beyond NVIDIA?</t>
+        </is>
+      </c>
+      <c r="AY36" s="79" t="inlineStr">
+        <is>
           <t>Mizuho Resets Intel Target For the Rest of 2026</t>
         </is>
       </c>
-      <c r="AY36" s="79" t="inlineStr">
+      <c r="AZ36" s="79" t="inlineStr">
         <is>
           <t>Lone Star JV Spends $1.2B On 2M SF R&amp;D Portfolio In Silicon Valley</t>
-        </is>
-      </c>
-      <c r="AZ36" s="79" t="inlineStr">
-        <is>
-          <t>Why Intel Stock Popped Today</t>
         </is>
       </c>
     </row>
@@ -9404,12 +9404,12 @@
       </c>
       <c r="AX39" s="90" t="inlineStr">
         <is>
+          <t>Dow Jones Futures: Nvidia, Micron, Sandisk Flash Buy Signals; Apple, Inflation Reports Ahead</t>
+        </is>
+      </c>
+      <c r="AY39" s="90" t="inlineStr">
+        <is>
           <t>David Tepper Sold 41% of His Micron Shares and It Is Still His Second-Biggest Holding</t>
-        </is>
-      </c>
-      <c r="AY39" s="90" t="inlineStr">
-        <is>
-          <t>Dow Jones Futures: Nvidia, Micron, Sandisk Flash Buy Signals; Apple, Inflation Reports Ahead</t>
         </is>
       </c>
       <c r="AZ39" s="90" t="inlineStr">
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
+          <t>Jim Cramer Believes Nvidia Corp. (NASDAQ:NVDA) Buying Back Half A Trillion Worth In Stock Would Be Great</t>
+        </is>
+      </c>
+      <c r="AY43" s="90" t="inlineStr">
+        <is>
+          <t>Dow Jones Futures: Nvidia, Micron, Sandisk Flash Buy Signals; Apple, Inflation Reports Ahead</t>
+        </is>
+      </c>
+      <c r="AZ43" s="90" t="inlineStr">
+        <is>
           <t>Elon Musk Committed SpaceX to Building "Exclusively on Nvidia." Here's What That Locks In for SpaceX's Comp...</t>
-        </is>
-      </c>
-      <c r="AY43" s="90" t="inlineStr">
-        <is>
-          <t>AI compute provider Nscale is looking for $3.5B in pre-IPO financing</t>
-        </is>
-      </c>
-      <c r="AZ43" s="90" t="inlineStr">
-        <is>
-          <t>Dow Jones Futures: Nvidia, Micron, Sandisk Flash Buy Signals; Apple, Inflation Reports Ahead</t>
         </is>
       </c>
     </row>
@@ -10908,17 +10908,17 @@
       </c>
       <c r="AX47" s="90" t="inlineStr">
         <is>
+          <t>Dow Jones Futures: Nvidia, Micron, Sandisk Flash Buy Signals; Apple, Inflation Reports Ahead</t>
+        </is>
+      </c>
+      <c r="AY47" s="90" t="inlineStr">
+        <is>
           <t>Stock Market Today: Dow Sinks Amid Rate Fears; Sandisk, KLA Lead Nasdaq-100 As Utilities Gain</t>
         </is>
       </c>
-      <c r="AY47" s="90" t="inlineStr">
+      <c r="AZ47" s="90" t="inlineStr">
         <is>
           <t>Analyst Has Strong Take on Micron, SanDisk Stocks</t>
-        </is>
-      </c>
-      <c r="AZ47" s="90" t="inlineStr">
-        <is>
-          <t>Micron, SanDisk Lead Memory Chip Stocks Rally on Strong AI Demand</t>
         </is>
       </c>
     </row>
@@ -11101,12 +11101,12 @@
       </c>
       <c r="AY48" s="79" t="inlineStr">
         <is>
+          <t>Tesla Launched the Cybercab Thursday, 6 Weeks After Removing Volume Production of It From This Year's Plan</t>
+        </is>
+      </c>
+      <c r="AZ48" s="79" t="inlineStr">
+        <is>
           <t>From Launch Party to Federal Probe: What Went Wrong With Tesla's Cybercab in 24 Hours</t>
-        </is>
-      </c>
-      <c r="AZ48" s="79" t="inlineStr">
-        <is>
-          <t>Tesla (TSLA) Falls More Steeply Than Broader Market: What Investors Need to Know</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 4 Sep 2026, 10:23 PM · Yahoo Finance data</t>
+          <t>Built 4 Sep 2026, 11:02 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 4 Sep 2026, 10:23 PM · Yahoo Finance data</t>
+          <t>Built 4 Sep 2026, 11:02 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 4 Sep 2026, 10:23 PM · Yahoo Finance data</t>
+          <t>Built 4 Sep 2026, 11:02 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 4 Sep 2026, 10:23 PM · Yahoo Finance data</t>
+          <t>Built 4 Sep 2026, 11:02 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'09-01'!$5:$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'08-31'!$A$6:$AZ$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'08-31'!$5:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 4 Sep 2026, 11:02 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 7 Sep 2026, 08:41 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       <c r="P8" s="10" t="n"/>
       <c r="Q8" s="16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R8" s="12" t="n"/>
@@ -2018,14 +2018,14 @@
     <row r="31">
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
-        <v>0.07482312178459227</v>
+        <v>0.00836070775935327</v>
       </c>
       <c r="D31" s="27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="F31" s="28" t="n">
-        <v>53.52927511621272</v>
+        <v>60.39157103041679</v>
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
@@ -2058,11 +2058,11 @@
     <row r="32">
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C32" s="33" t="n">
-        <v>0.04505296133202719</v>
+        <v>0.07482312178459227</v>
       </c>
       <c r="D32" s="34" t="n">
         <v>8</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="F32" s="35" t="n">
-        <v>51.7442898847969</v>
+        <v>53.52927511621272</v>
       </c>
       <c r="H32" s="31" t="inlineStr">
         <is>
@@ -2098,11 +2098,11 @@
     <row r="33">
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
-        <v>0.0150080361357805</v>
+        <v>0.04505296133202719</v>
       </c>
       <c r="D33" s="27" t="n">
         <v>8</v>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="F33" s="28" t="n">
-        <v>63.66351534495513</v>
+        <v>51.7442898847969</v>
       </c>
       <c r="H33" s="24" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>0.002057860185984861</v>
+        <v>0.002071873185092388</v>
       </c>
       <c r="J33" s="27" t="n">
         <v>1</v>
@@ -2132,17 +2132,17 @@
         </is>
       </c>
       <c r="L33" s="28" t="n">
-        <v>38.04345929080058</v>
+        <v>38.04705952649971</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C34" s="33" t="n">
-        <v>0.00836070775935327</v>
+        <v>0.0150080361357805</v>
       </c>
       <c r="D34" s="34" t="n">
         <v>8</v>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="F34" s="35" t="n">
-        <v>60.39157103041679</v>
+        <v>63.66351534495513</v>
       </c>
       <c r="H34" s="31" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 4 Sep 2026, 11:02 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 08:41 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -3614,16 +3614,16 @@
         <v>174.3399963378906</v>
       </c>
       <c r="U7" s="72" t="n">
-        <v>175.7749938964844</v>
+        <v>175.7799987792969</v>
       </c>
       <c r="V7" s="72" t="n">
         <v>174.1000061035156</v>
       </c>
       <c r="W7" s="73" t="n">
-        <v>5807775</v>
+        <v>5841600</v>
       </c>
       <c r="X7" s="74" t="n">
-        <v>0.9194254555600739</v>
+        <v>0.9245327363500614</v>
       </c>
       <c r="Y7" s="28" t="n">
         <v>38.89644652840126</v>
@@ -3632,7 +3632,7 @@
         <v>26.14618481270283</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>25.67048740529762</v>
+        <v>25.66774107790977</v>
       </c>
       <c r="AB7" s="75" t="n">
         <v>-2.150334477861264</v>
@@ -3674,7 +3674,7 @@
         <v>10.09407349005902</v>
       </c>
       <c r="AO7" s="77" t="n">
-        <v>1.399426741109238</v>
+        <v>1.399630707344618</v>
       </c>
       <c r="AP7" s="72" t="n">
         <v>188.1900024414062</v>
@@ -3804,16 +3804,16 @@
         <v>171.3899993896484</v>
       </c>
       <c r="U8" s="83" t="n">
-        <v>172.5325012207031</v>
+        <v>172.5299987792969</v>
       </c>
       <c r="V8" s="83" t="n">
-        <v>171.2350006103516</v>
+        <v>171.2400054931641</v>
       </c>
       <c r="W8" s="84" t="n">
-        <v>6068699</v>
+        <v>6083000</v>
       </c>
       <c r="X8" s="85" t="n">
-        <v>0.8220440424387842</v>
+        <v>0.823901402718211</v>
       </c>
       <c r="Y8" s="35" t="n">
         <v>55.49904605891764</v>
@@ -3822,7 +3822,7 @@
         <v>36.80977460079121</v>
       </c>
       <c r="AA8" s="35" t="n">
-        <v>27.21330025120935</v>
+        <v>27.21565887309683</v>
       </c>
       <c r="AB8" s="86" t="n">
         <v>2.171795734698321</v>
@@ -3864,7 +3864,7 @@
         <v>6.242793151423582</v>
       </c>
       <c r="AO8" s="88" t="n">
-        <v>1.523066162305396</v>
+        <v>1.52285765158167</v>
       </c>
       <c r="AP8" s="83" t="n">
         <v>176.6000061035156</v>
@@ -4000,10 +4000,10 @@
         <v>57.91999816894531</v>
       </c>
       <c r="W9" s="73" t="n">
-        <v>26249596</v>
+        <v>26345200</v>
       </c>
       <c r="X9" s="74" t="n">
-        <v>0.9465192594140487</v>
+        <v>0.9498028754888005</v>
       </c>
       <c r="Y9" s="28" t="n">
         <v>55.48490520235243</v>
@@ -4187,13 +4187,13 @@
         <v>64.33000183105469</v>
       </c>
       <c r="V10" s="83" t="n">
-        <v>63.375</v>
+        <v>63.38000106811523</v>
       </c>
       <c r="W10" s="84" t="n">
-        <v>26088239</v>
+        <v>26281800</v>
       </c>
       <c r="X10" s="85" t="n">
-        <v>1.015822317560993</v>
+        <v>1.022973683585705</v>
       </c>
       <c r="Y10" s="35" t="n">
         <v>63.1419828676078</v>
@@ -4202,7 +4202,7 @@
         <v>65.32064786499038</v>
       </c>
       <c r="AA10" s="35" t="n">
-        <v>27.79215071422096</v>
+        <v>27.79717980666603</v>
       </c>
       <c r="AB10" s="86" t="n">
         <v>1.431671632215661</v>
@@ -4244,7 +4244,7 @@
         <v>8.62123254027785</v>
       </c>
       <c r="AO10" s="88" t="n">
-        <v>1.830732073401575</v>
+        <v>1.830174441236882</v>
       </c>
       <c r="AP10" s="83" t="n">
         <v>65.51999664306641</v>
@@ -4374,16 +4374,16 @@
         <v>84.81999969482422</v>
       </c>
       <c r="U11" s="72" t="n">
-        <v>85.29000091552734</v>
+        <v>85.30000305175781</v>
       </c>
       <c r="V11" s="72" t="n">
         <v>84.54000091552734</v>
       </c>
       <c r="W11" s="73" t="n">
-        <v>9823945</v>
+        <v>9903700</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>1.11131011260251</v>
+        <v>1.11982704570523</v>
       </c>
       <c r="Y11" s="28" t="n">
         <v>45.23385101242543</v>
@@ -4434,7 +4434,7 @@
         <v>3.392922385647933</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.29785730515503</v>
+        <v>1.298701994545795</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -4570,10 +4570,10 @@
         <v>114.4599990844727</v>
       </c>
       <c r="W12" s="84" t="n">
-        <v>5071369</v>
+        <v>5120000</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>1.013169759045266</v>
+        <v>1.022388715384554</v>
       </c>
       <c r="Y12" s="35" t="n">
         <v>44.57163034145746</v>
@@ -4757,13 +4757,13 @@
         <v>113.2900009155273</v>
       </c>
       <c r="V13" s="72" t="n">
-        <v>111.879997253418</v>
+        <v>111.875</v>
       </c>
       <c r="W13" s="73" t="n">
-        <v>2683037</v>
+        <v>2689600</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>0.6729645801653736</v>
+        <v>0.674555203876385</v>
       </c>
       <c r="Y13" s="28" t="n">
         <v>51.76547604388368</v>
@@ -4772,7 +4772,7 @@
         <v>44.05936574062708</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>13.60542362334407</v>
+        <v>13.60236670559791</v>
       </c>
       <c r="AB13" s="75" t="n">
         <v>0.4768781871747763</v>
@@ -4814,7 +4814,7 @@
         <v>3.312441843346797</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.516502792182393</v>
+        <v>1.516821409228364</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -4947,13 +4947,13 @@
         <v>52.66999816894531</v>
       </c>
       <c r="V14" s="83" t="n">
-        <v>51.97499847412109</v>
+        <v>51.97999954223633</v>
       </c>
       <c r="W14" s="84" t="n">
-        <v>10873762</v>
+        <v>10873800</v>
       </c>
       <c r="X14" s="85" t="n">
-        <v>1.00518864889215</v>
+        <v>1.00519198512429</v>
       </c>
       <c r="Y14" s="35" t="n">
         <v>49.4676143244987</v>
@@ -4962,7 +4962,7 @@
         <v>28.27864815807864</v>
       </c>
       <c r="AA14" s="35" t="n">
-        <v>14.67800803150836</v>
+        <v>14.68486547704828</v>
       </c>
       <c r="AB14" s="86" t="n">
         <v>0.2304403794357057</v>
@@ -5004,7 +5004,7 @@
         <v>4.093904564425986</v>
       </c>
       <c r="AO14" s="88" t="n">
-        <v>1.607810943237288</v>
+        <v>1.607129747279159</v>
       </c>
       <c r="AP14" s="83" t="n">
         <v>54.18999862670898</v>
@@ -5140,10 +5140,10 @@
         <v>186.4199981689453</v>
       </c>
       <c r="W15" s="73" t="n">
-        <v>5081462</v>
+        <v>5103800</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>0.8491878409696834</v>
+        <v>0.8527616843705749</v>
       </c>
       <c r="Y15" s="28" t="n">
         <v>55.29688065294555</v>
@@ -5222,12 +5222,12 @@
       </c>
       <c r="AX15" s="79" t="inlineStr">
         <is>
+          <t>Sector Update: Tech Stocks Rise Late Afternoon</t>
+        </is>
+      </c>
+      <c r="AY15" s="79" t="inlineStr">
+        <is>
           <t>Blowout jobs report raises worries of Fed rate hike: AlphaCheck</t>
-        </is>
-      </c>
-      <c r="AY15" s="79" t="inlineStr">
-        <is>
-          <t>Sector Update: Tech Stocks Rise Late Afternoon</t>
         </is>
       </c>
       <c r="AZ15" s="79" t="inlineStr">
@@ -5324,16 +5324,16 @@
         <v>44.04000091552734</v>
       </c>
       <c r="U16" s="83" t="n">
-        <v>44.27500152587891</v>
+        <v>44.27999877929688</v>
       </c>
       <c r="V16" s="83" t="n">
         <v>43.875</v>
       </c>
       <c r="W16" s="84" t="n">
-        <v>3761109</v>
+        <v>3829200</v>
       </c>
       <c r="X16" s="85" t="n">
-        <v>0.7318342943625612</v>
+        <v>0.7445901419391973</v>
       </c>
       <c r="Y16" s="35" t="n">
         <v>40.1911612158916</v>
@@ -5342,7 +5342,7 @@
         <v>19.21059922822713</v>
       </c>
       <c r="AA16" s="35" t="n">
-        <v>15.03752197299594</v>
+        <v>15.02292579591458</v>
       </c>
       <c r="AB16" s="86" t="n">
         <v>-0.2422262788982081</v>
@@ -5384,7 +5384,7 @@
         <v>4.440833217234127</v>
       </c>
       <c r="AO16" s="88" t="n">
-        <v>1.173863809120602</v>
+        <v>1.174676344222428</v>
       </c>
       <c r="AP16" s="83" t="n">
         <v>46.45500183105469</v>
@@ -5517,13 +5517,13 @@
         <v>43.22999954223633</v>
       </c>
       <c r="V17" s="72" t="n">
-        <v>42.7599983215332</v>
+        <v>42.75</v>
       </c>
       <c r="W17" s="73" t="n">
-        <v>18838974</v>
+        <v>18858100</v>
       </c>
       <c r="X17" s="74" t="n">
-        <v>0.935472252533345</v>
+        <v>0.9363775123613292</v>
       </c>
       <c r="Y17" s="28" t="n">
         <v>43.93351550138382</v>
@@ -5574,7 +5574,7 @@
         <v>5.392769992681686</v>
       </c>
       <c r="AO17" s="77" t="n">
-        <v>1.470195056267271</v>
+        <v>1.471852822733022</v>
       </c>
       <c r="AP17" s="72" t="n">
         <v>47.79999923706055</v>
@@ -5729,10 +5729,10 @@
         <v>769</v>
       </c>
       <c r="W19" s="73" t="n">
-        <v>32960393</v>
+        <v>34015600</v>
       </c>
       <c r="X19" s="74" t="n">
-        <v>0.908793946613346</v>
+        <v>0.9365260466110001</v>
       </c>
       <c r="Y19" s="28" t="n">
         <v>55.61138482356586</v>
@@ -5811,17 +5811,17 @@
       </c>
       <c r="AX19" s="79" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Dow End Lower As Blowout Jobs Report Fans Rate Hike Fears, While Chipmaker Strength Aids Nasdaq —T...</t>
+          <t>IBB Just Beat the S&amp;P 500 by 22 Points in Three Months. Are You Late to the Party?</t>
         </is>
       </c>
       <c r="AY19" s="79" t="inlineStr">
         <is>
-          <t>This Is the Most Expensive Market in Decades. Is It Really Safe to Invest Right Now?</t>
+          <t>Microsoft Is Close to a New All-Time High. This Number Will Determine If It Keeps Climbing</t>
         </is>
       </c>
       <c r="AZ19" s="79" t="inlineStr">
         <is>
-          <t>GoPro Zooms 34% Higher on Starman Optical Merger and Markiplier Stake; Coherent Climbs 7%, Lumentum Gains 3%</t>
+          <t>Roblox Has Collapsed 47% This Year: Is It Time to Switch to Take-Two or GameStop?</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
         <v>1.2900390625</v>
       </c>
       <c r="T20" s="83" t="n">
-        <v>719.3599853515625</v>
+        <v>719.3499755859375</v>
       </c>
       <c r="U20" s="83" t="n">
         <v>721.8599853515625</v>
@@ -5917,10 +5917,10 @@
         <v>716.5599975585938</v>
       </c>
       <c r="W20" s="84" t="n">
-        <v>32489892</v>
+        <v>32784600</v>
       </c>
       <c r="X20" s="85" t="n">
-        <v>1.05579885949037</v>
+        <v>1.06486585157502</v>
       </c>
       <c r="Y20" s="35" t="n">
         <v>53.61942940327157</v>
@@ -5999,17 +5999,17 @@
       </c>
       <c r="AX20" s="90" t="inlineStr">
         <is>
+          <t>This ETF Would Have Increased Your Investment by 6x Over the Past 10 Years -- and It's Still Soaring</t>
+        </is>
+      </c>
+      <c r="AY20" s="90" t="inlineStr">
+        <is>
+          <t>The VIX Is Playing Tricks: Why Stocks Are Volatile, But the Fear Gauge Is Sleeping</t>
+        </is>
+      </c>
+      <c r="AZ20" s="90" t="inlineStr">
+        <is>
           <t>Exchange-Traded Funds Mixed, US Equities Lower After Midday</t>
-        </is>
-      </c>
-      <c r="AY20" s="90" t="inlineStr">
-        <is>
-          <t>GoPro Zooms 34% Higher on Starman Optical Merger and Markiplier Stake; Coherent Climbs 7%, Lumentum Gains 3%</t>
-        </is>
-      </c>
-      <c r="AZ20" s="90" t="inlineStr">
-        <is>
-          <t>SCHG Owns More Apple Than Tesla, Meta and Palantir Combined. Is That Why Growth Investors Are Falling Behind?</t>
         </is>
       </c>
     </row>
@@ -6102,13 +6102,13 @@
         <v>296.1799926757812</v>
       </c>
       <c r="V21" s="72" t="n">
-        <v>293.5700073242188</v>
+        <v>293.5599975585938</v>
       </c>
       <c r="W21" s="73" t="n">
-        <v>13897211</v>
+        <v>13951100</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>0.8313961430271718</v>
+        <v>0.8344855204251892</v>
       </c>
       <c r="Y21" s="28" t="n">
         <v>48.14623240653629</v>
@@ -6159,7 +6159,7 @@
         <v>4.920574083904603</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.113740340880568</v>
+        <v>1.113981881110743</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -6187,17 +6187,17 @@
       </c>
       <c r="AX21" s="79" t="inlineStr">
         <is>
+          <t>3 ETFs That Could Move as Rate Expectations Shift</t>
+        </is>
+      </c>
+      <c r="AY21" s="79" t="inlineStr">
+        <is>
           <t>Forget IWM: The Small-Cap Fund That Screens Out Money-Losers Charges 84% Less, and It’s Winning by 2.5 Points</t>
         </is>
       </c>
-      <c r="AY21" s="79" t="inlineStr">
+      <c r="AZ21" s="79" t="inlineStr">
         <is>
           <t>Small Caps Pay Too: The 42% Friday Payer Riding the Russell’s Big Year</t>
-        </is>
-      </c>
-      <c r="AZ21" s="79" t="inlineStr">
-        <is>
-          <t>Small Caps Are Beating the S&amp;P for Once. This Fund Pays 14% While They Run</t>
         </is>
       </c>
     </row>
@@ -6287,16 +6287,16 @@
         <v>111.2200012207031</v>
       </c>
       <c r="U22" s="83" t="n">
-        <v>118.1750030517578</v>
+        <v>118.1800003051758</v>
       </c>
       <c r="V22" s="83" t="n">
-        <v>109.75</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="W22" s="84" t="n">
-        <v>62998272</v>
+        <v>63251400</v>
       </c>
       <c r="X22" s="85" t="n">
-        <v>1.159165591762556</v>
+        <v>1.163552171650776</v>
       </c>
       <c r="Y22" s="35" t="n">
         <v>45.44506021968484</v>
@@ -6305,7 +6305,7 @@
         <v>47.87068862423708</v>
       </c>
       <c r="AA22" s="35" t="n">
-        <v>19.58635703872865</v>
+        <v>19.58597074313625</v>
       </c>
       <c r="AB22" s="86" t="n">
         <v>-9.817400463372863</v>
@@ -6347,7 +6347,7 @@
         <v>44.11439815483754</v>
       </c>
       <c r="AO22" s="88" t="n">
-        <v>11.64831211952354</v>
+        <v>11.6486164737838</v>
       </c>
       <c r="AP22" s="83" t="n">
         <v>302</v>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -6493,7 +6493,7 @@
         <v>-8.239990234375</v>
       </c>
       <c r="T24" s="72" t="n">
-        <v>328.3049926757812</v>
+        <v>328.3099975585938</v>
       </c>
       <c r="U24" s="72" t="n">
         <v>328.9299926757812</v>
@@ -6502,10 +6502,10 @@
         <v>317.8599853515625</v>
       </c>
       <c r="W24" s="73" t="n">
-        <v>38272821</v>
+        <v>39551800</v>
       </c>
       <c r="X24" s="74" t="n">
-        <v>0.9667505992467851</v>
+        <v>0.9974457220667698</v>
       </c>
       <c r="Y24" s="28" t="n">
         <v>53.88621122935447</v>
@@ -6584,17 +6584,17 @@
       </c>
       <c r="AX24" s="79" t="inlineStr">
         <is>
-          <t>Apple's John Ternus needs to be his own type of CEO and 'not Tim Cook 2'</t>
+          <t>KeyBanc Delivers Stark Warning on Apple Stock Ahead of iPhone 18 Launch</t>
         </is>
       </c>
       <c r="AY24" s="79" t="inlineStr">
         <is>
-          <t>Dow Jones Futures: Nvidia, Micron, Sandisk Flash Buy Signals; Apple, Inflation Reports Ahead</t>
+          <t>Apple’s new CEO faces a staggering $14 billion iPhone test</t>
         </is>
       </c>
       <c r="AZ24" s="79" t="inlineStr">
         <is>
-          <t>Why Apple (AAPL) Dipped More Than Broader Market Today</t>
+          <t>Apple Faces Its Biggest iPhone Test in Years -- Morgan Stanley Sees $14B Foldable Opportunity</t>
         </is>
       </c>
     </row>
@@ -6690,10 +6690,10 @@
         <v>458</v>
       </c>
       <c r="W25" s="84" t="n">
-        <v>19364684</v>
+        <v>19651900</v>
       </c>
       <c r="X25" s="85" t="n">
-        <v>1.10719337981666</v>
+        <v>1.12269338094845</v>
       </c>
       <c r="Y25" s="35" t="n">
         <v>49.6732371841989</v>
@@ -6772,17 +6772,17 @@
       </c>
       <c r="AX25" s="90" t="inlineStr">
         <is>
-          <t>Intel Climbs 4%, AMD Rises 3%, NVIDIA Ticks Up as Chip Stocks Shrug Off Rising Rate Hike Odds</t>
+          <t>Wall Street Is Worried About AMD. Here’s Why Long-Term Investors Shouldn’t Be</t>
         </is>
       </c>
       <c r="AY25" s="90" t="inlineStr">
         <is>
-          <t>Cathie Wood Cuts AMD and Puts $53 Million Into Nvidia</t>
+          <t>AMD Is Behind The AI Chip Shift Nobody Is Talking About</t>
         </is>
       </c>
       <c r="AZ25" s="90" t="inlineStr">
         <is>
-          <t>ORCL Eyes Breakout as AMD and Intel Test Key Support</t>
+          <t>AMD’s Whole AI Story Has One Threat It Cannot Ignore: Broadcom</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
         <v>-0.389984130859375</v>
       </c>
       <c r="T26" s="72" t="n">
-        <v>259.2149963378906</v>
+        <v>259.0700073242188</v>
       </c>
       <c r="U26" s="72" t="n">
         <v>261.1199951171875</v>
@@ -6878,10 +6878,10 @@
         <v>255.2899932861328</v>
       </c>
       <c r="W26" s="73" t="n">
-        <v>29968655</v>
+        <v>30698000</v>
       </c>
       <c r="X26" s="74" t="n">
-        <v>0.9175878288958084</v>
+        <v>0.9388707890469152</v>
       </c>
       <c r="Y26" s="28" t="n">
         <v>49.54908461556442</v>
@@ -6960,17 +6960,17 @@
       </c>
       <c r="AX26" s="79" t="inlineStr">
         <is>
-          <t>Amazon's $100 Billion Anthropic Contract Gets a 45% Cheaper Engine</t>
+          <t>Fatal Amazon Plane Crash Delays Hundreds of Miami Flights</t>
         </is>
       </c>
       <c r="AY26" s="79" t="inlineStr">
         <is>
-          <t>Cramer Says the Magnificent Seven Are Finally Cheap and Most Investors Will Miss It</t>
+          <t>Are Retail-Wholesale Stocks Lagging Amazon.com (AMZN) This Year?</t>
         </is>
       </c>
       <c r="AZ26" s="79" t="inlineStr">
         <is>
-          <t>DOJ expands beef price probe to eight retailers, including Walmart and Amazon, with inflation a key issue a...</t>
+          <t>Amazon.com, Inc. (AMZN) is Attracting Investor Attention: Here is What You Should Know</t>
         </is>
       </c>
     </row>
@@ -7066,10 +7066,10 @@
         <v>85.80000305175781</v>
       </c>
       <c r="W27" s="84" t="n">
-        <v>3440341</v>
+        <v>3450700</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>0.7343095758532827</v>
+        <v>0.7364391958008005</v>
       </c>
       <c r="Y27" s="35" t="n">
         <v>58.3459649207801</v>
@@ -7148,17 +7148,17 @@
       </c>
       <c r="AX27" s="90" t="inlineStr">
         <is>
-          <t>Cathie Wood buys $44.5 million of tumbling tech stock</t>
+          <t>Cathie Wood buys $3.5 million of surging tech stock</t>
         </is>
       </c>
       <c r="AY27" s="90" t="inlineStr">
         <is>
-          <t>Nvidia Blew Wall Street Away with Its Q2 Results. Cathie Wood Is Celebrating by Buying More Than 243,000 Sh...</t>
+          <t>Cathie Wood's 2 Biggest Positions Are Both Elon Musk Companies. Together They Are 16% of the Fund.</t>
         </is>
       </c>
       <c r="AZ27" s="90" t="inlineStr">
         <is>
-          <t>Cathie Wood's Ark Has Delivered Just a 13.8% Annualized Return Since 2014, Roughly Matching the S&amp;P 500. Sh...</t>
+          <t>Cathie Wood’s Ark Invest Buys HOOD Stock As Robinhood Sees Its Third-Best Week In Six Months</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7245,7 @@
         <v>9.5</v>
       </c>
       <c r="T28" s="72" t="n">
-        <v>248.8390045166016</v>
+        <v>248.5899963378906</v>
       </c>
       <c r="U28" s="72" t="n">
         <v>255.6900024414062</v>
@@ -7254,10 +7254,10 @@
         <v>247.5099945068359</v>
       </c>
       <c r="W28" s="73" t="n">
-        <v>4120464</v>
+        <v>4126100</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>1.131635532891704</v>
+        <v>1.133095698405027</v>
       </c>
       <c r="Y28" s="28" t="n">
         <v>47.95177147980165</v>
@@ -7336,17 +7336,17 @@
       </c>
       <c r="AX28" s="79" t="inlineStr">
         <is>
+          <t>Arm Expands Into AI Accelerators With Samsung — But It’s Not the Data Center Goldmine Investors Hope For</t>
+        </is>
+      </c>
+      <c r="AY28" s="79" t="inlineStr">
+        <is>
+          <t>Rising CPU Demand Positions Arm Holdings (ARM) for Gains</t>
+        </is>
+      </c>
+      <c r="AZ28" s="79" t="inlineStr">
+        <is>
           <t>Can ARM's AGI CPU Push Unlock $15B in Revenues by FY'31?</t>
-        </is>
-      </c>
-      <c r="AY28" s="79" t="inlineStr">
-        <is>
-          <t>ARM vs. Sandisk: Comparing Steady Historical Revenue Generation Against Rapid Sequential Revenue Expansion</t>
-        </is>
-      </c>
-      <c r="AZ28" s="79" t="inlineStr">
-        <is>
-          <t>Why Arm Holdings Stock Fell on Tuesday</t>
         </is>
       </c>
     </row>
@@ -7433,19 +7433,19 @@
         <v>0.1800003051757812</v>
       </c>
       <c r="T29" s="83" t="n">
-        <v>63.43999862670898</v>
+        <v>63.40000152587891</v>
       </c>
       <c r="U29" s="83" t="n">
-        <v>65.75</v>
+        <v>65.76000213623047</v>
       </c>
       <c r="V29" s="83" t="n">
         <v>61.66999816894531</v>
       </c>
       <c r="W29" s="84" t="n">
-        <v>10104414</v>
+        <v>10216600</v>
       </c>
       <c r="X29" s="85" t="n">
-        <v>0.9991953859870389</v>
+        <v>1.009729041643935</v>
       </c>
       <c r="Y29" s="35" t="n">
         <v>47.16085559699919</v>
@@ -7454,7 +7454,7 @@
         <v>45.90278931238216</v>
       </c>
       <c r="AA29" s="35" t="n">
-        <v>13.53102658052938</v>
+        <v>13.53342673358475</v>
       </c>
       <c r="AB29" s="86" t="n">
         <v>-2.047894896957622</v>
@@ -7496,7 +7496,7 @@
         <v>31.50978950370434</v>
       </c>
       <c r="AO29" s="88" t="n">
-        <v>7.301854407621104</v>
+        <v>7.303000994503515</v>
       </c>
       <c r="AP29" s="83" t="n">
         <v>133.8600006103516</v>
@@ -7524,17 +7524,17 @@
       </c>
       <c r="AX29" s="90" t="inlineStr">
         <is>
-          <t>AST SpaceMobile vs. Space Exploration Technologies: Which Telecom Stock Is a Better Buy in 2026?</t>
+          <t>AST SpaceMobile Director Adriana Cisneros Buys $619,235 Shares. What Does This Mean for Investors?</t>
         </is>
       </c>
       <c r="AY29" s="90" t="inlineStr">
         <is>
-          <t>SPCX Stock Blasts Past ASTS, RKLB, LUNR, PL — Here’s Everything Shaking Up Space Stocks This Week</t>
+          <t>The Real Satellite Race Isn’t About Rockets — It’s About Who Controls the Spectrum in Your Phone</t>
         </is>
       </c>
       <c r="AZ29" s="90" t="inlineStr">
         <is>
-          <t>ASTS Stock Is Surging on a New Analyst Target. Here’s How High It Can Soar.</t>
+          <t>Forget Starlink? Japan’s $1 Billion BlueBird Play Makes ASTS the National Satellite OS</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="C30" s="26" t="n">
-        <v>0.002057860185984861</v>
+        <v>0.002071873185092388</v>
       </c>
       <c r="D30" s="27" t="n">
         <v>14</v>
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="R30" s="70" t="n">
-        <v>357.8949890136719</v>
+        <v>357.8999938964844</v>
       </c>
       <c r="S30" s="71" t="n">
-        <v>0.7349853515625</v>
+        <v>0.739990234375</v>
       </c>
       <c r="T30" s="72" t="n">
-        <v>360.0050048828125</v>
+        <v>359.7000122070312</v>
       </c>
       <c r="U30" s="72" t="n">
-        <v>360.0450134277344</v>
+        <v>360.1600036621094</v>
       </c>
       <c r="V30" s="72" t="n">
         <v>353.7000122070312</v>
       </c>
       <c r="W30" s="73" t="n">
-        <v>32481307</v>
+        <v>32773600</v>
       </c>
       <c r="X30" s="74" t="n">
-        <v>1.385842174155349</v>
+        <v>1.397441730266662</v>
       </c>
       <c r="Y30" s="28" t="n">
-        <v>38.04345929080058</v>
+        <v>38.04705952649971</v>
       </c>
       <c r="Z30" s="28" t="n">
-        <v>35.82278036480611</v>
+        <v>35.83429907920521</v>
       </c>
       <c r="AA30" s="28" t="n">
-        <v>23.72914532271137</v>
+        <v>23.71759503882551</v>
       </c>
       <c r="AB30" s="75" t="n">
-        <v>-8.805086820661245</v>
+        <v>-8.804687570750275</v>
       </c>
       <c r="AC30" s="75" t="n">
-        <v>-7.415563695108411</v>
+        <v>-7.415483845126216</v>
       </c>
       <c r="AD30" s="75" t="n">
-        <v>-1.389523125552834</v>
+        <v>-1.389203725624059</v>
       </c>
       <c r="AE30" s="72" t="n">
-        <v>364.4621078185942</v>
+        <v>364.4632200147747</v>
       </c>
       <c r="AF30" s="72" t="n">
-        <v>374.1247507870768</v>
+        <v>374.1252057764234</v>
       </c>
       <c r="AG30" s="72" t="n">
-        <v>383.661499633789</v>
+        <v>383.6615997314453</v>
       </c>
       <c r="AH30" s="72" t="n">
-        <v>398.1304507446289</v>
+        <v>398.130500793457</v>
       </c>
       <c r="AI30" s="72" t="n">
-        <v>369.8336253356933</v>
+        <v>369.8336503601074</v>
       </c>
       <c r="AJ30" s="72" t="n">
-        <v>422.932819448747</v>
+        <v>422.9326113622287</v>
       </c>
       <c r="AK30" s="72" t="n">
-        <v>378.3232482910156</v>
+        <v>378.3234985351563</v>
       </c>
       <c r="AL30" s="72" t="n">
-        <v>333.7136771332842</v>
+        <v>333.7143857080838</v>
       </c>
       <c r="AM30" s="76" t="n">
-        <v>0.2710327767429874</v>
+        <v>0.2710837164836281</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>23.58278078825152</v>
+        <v>23.58252289365901</v>
       </c>
       <c r="AO30" s="77" t="n">
-        <v>3.637457540758624</v>
+        <v>3.639701613912953</v>
       </c>
       <c r="AP30" s="72" t="n">
         <v>495</v>
@@ -7693,36 +7693,36 @@
         <v>289.9599914550781</v>
       </c>
       <c r="AR30" s="29" t="n">
-        <v>-27.69798201744003</v>
+        <v>-27.69697093000316</v>
       </c>
       <c r="AS30" s="78" t="n">
-        <v>33.13255692910781</v>
+        <v>33.13499785897706</v>
       </c>
       <c r="AT30" s="26" t="n">
-        <v>-0.02954261037124295</v>
+        <v>-0.02952903928011652</v>
       </c>
       <c r="AU30" s="26" t="n">
-        <v>-0.1490239846376646</v>
+        <v>-0.1490120844005451</v>
       </c>
       <c r="AV30" s="26" t="n">
-        <v>-0.07216192979509406</v>
+        <v>-0.07214895470197202</v>
       </c>
       <c r="AW30" s="26" t="n">
-        <v>0.03407969575888559</v>
+        <v>0.03409415655843562</v>
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
-          <t>Jim Cramer Says “Someone Must Know Something” About Broadcom Inc. (NASDAQ:AVGO)’s Post-Earnings Share Dip</t>
+          <t>Broadcom Inc. (AVGO)’s AI Opportunity Expands Across AI Infrastructure</t>
         </is>
       </c>
       <c r="AY30" s="79" t="inlineStr">
         <is>
-          <t>Top Research Reports for Apple, Broadcom &amp; Shell</t>
+          <t>Broadcom vs Marvell: One of These AI Chip Stocks Is a Clear Winner</t>
         </is>
       </c>
       <c r="AZ30" s="79" t="inlineStr">
         <is>
-          <t>5-star analyst resets Broadcom stock price target</t>
+          <t>Broadcom Inc. (AVGO) Is a Trending Stock: Facts to Know Before Betting on It</t>
         </is>
       </c>
     </row>
@@ -7815,13 +7815,13 @@
         <v>101.5400009155273</v>
       </c>
       <c r="V31" s="83" t="n">
-        <v>99.61000061035156</v>
+        <v>99.51999664306641</v>
       </c>
       <c r="W31" s="84" t="n">
-        <v>1550370</v>
+        <v>1554900</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>0.5842640228057313</v>
+        <v>0.5859211612159305</v>
       </c>
       <c r="Y31" s="35" t="n">
         <v>54.05207932909197</v>
@@ -7872,7 +7872,7 @@
         <v>14.00692232542185</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>3.951729625582283</v>
+        <v>3.958111256456225</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -7997,7 +7997,7 @@
         <v>4.800003051757812</v>
       </c>
       <c r="T32" s="72" t="n">
-        <v>85.98000335693359</v>
+        <v>85.72499847412109</v>
       </c>
       <c r="U32" s="72" t="n">
         <v>89.62999725341797</v>
@@ -8006,10 +8006,10 @@
         <v>84.90000152587891</v>
       </c>
       <c r="W32" s="73" t="n">
-        <v>20537770</v>
+        <v>20732400</v>
       </c>
       <c r="X32" s="74" t="n">
-        <v>0.7541887865692521</v>
+        <v>0.7610640227433788</v>
       </c>
       <c r="Y32" s="28" t="n">
         <v>52.00788852164074</v>
@@ -8088,17 +8088,17 @@
       </c>
       <c r="AX32" s="79" t="inlineStr">
         <is>
-          <t>BigBear.ai vs. CoreWeave: Evaluating the Better Artificial Intelligence Stock to Buy for 2026</t>
+          <t>CRWV Stock Takes a 13% Hit in 3 Months: Time to Buy, Hold or Bail Out?</t>
         </is>
       </c>
       <c r="AY32" s="79" t="inlineStr">
         <is>
-          <t>CoreWeave to Participate in the Goldman Sachs Communacopia + Technology Conference</t>
+          <t>Nebius Stock Up 254% in a Year: Should You Buy, Hold or Sell?</t>
         </is>
       </c>
       <c r="AZ32" s="79" t="inlineStr">
         <is>
-          <t>CoreWeave (CRWV) Could Be 21% Overvalued After The Rescale Cloud Deal</t>
+          <t>Nvidia’s $99 Billion Portfolio Is Turning Intel and CoreWeave Into an AI Stress Test</t>
         </is>
       </c>
     </row>
@@ -8188,25 +8188,25 @@
         <v>513.780029296875</v>
       </c>
       <c r="U33" s="83" t="n">
-        <v>534.9600219726562</v>
+        <v>534.989990234375</v>
       </c>
       <c r="V33" s="83" t="n">
-        <v>510.2699890136719</v>
+        <v>510.1499938964844</v>
       </c>
       <c r="W33" s="84" t="n">
-        <v>10960031</v>
+        <v>11108300</v>
       </c>
       <c r="X33" s="85" t="n">
-        <v>1.318663912567873</v>
+        <v>1.335311965072221</v>
       </c>
       <c r="Y33" s="35" t="n">
         <v>63.66351534495513</v>
       </c>
       <c r="Z33" s="35" t="n">
-        <v>90.43070078416703</v>
+        <v>90.40673923250029</v>
       </c>
       <c r="AA33" s="35" t="n">
-        <v>9.865862732315552</v>
+        <v>9.866654611304808</v>
       </c>
       <c r="AB33" s="86" t="n">
         <v>15.7781744109642</v>
@@ -8248,19 +8248,19 @@
         <v>23.36758426314429</v>
       </c>
       <c r="AO33" s="88" t="n">
-        <v>6.121899206618705</v>
+        <v>6.123942872361161</v>
       </c>
       <c r="AP33" s="83" t="n">
-        <v>534.9600219726562</v>
+        <v>534.989990234375</v>
       </c>
       <c r="AQ33" s="83" t="n">
         <v>110.2200012207031</v>
       </c>
       <c r="AR33" s="36" t="n">
-        <v>-2.022582413601703</v>
+        <v>-2.028070764685563</v>
       </c>
       <c r="AS33" s="89" t="n">
-        <v>97.45255761275729</v>
+        <v>97.44568216527456</v>
       </c>
       <c r="AT33" s="33" t="n">
         <v>0.1488252364269551</v>
@@ -8276,17 +8276,17 @@
       </c>
       <c r="AX33" s="90" t="inlineStr">
         <is>
-          <t>Jim Cramer Couldn’t Stop Gushing About This Computer Hardware AI Stock</t>
+          <t>Dell &amp; 2 Momentum Stocks to Buy Now for Explosive Upside</t>
         </is>
       </c>
       <c r="AY33" s="90" t="inlineStr">
         <is>
-          <t>DELL Stock Hits 52-Week High: Does it Have More Room to Run?</t>
+          <t>Jim Cramer Explains Why “Buyers Flocked in” for Dell (DELL)</t>
         </is>
       </c>
       <c r="AZ33" s="90" t="inlineStr">
         <is>
-          <t>Super Micro Surges 7% as Semiconductors Lead a Flat Tape; Hewlett Packard Enterprise Falls 3%, Dell Edges H...</t>
+          <t>DELL Expands Consumer PC Reach: Can It Challenge HPQ &amp; AAPL?</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -8373,7 +8373,7 @@
         <v>-3.769989013671875</v>
       </c>
       <c r="T34" s="72" t="n">
-        <v>339.2049865722656</v>
+        <v>339.1799926757812</v>
       </c>
       <c r="U34" s="72" t="n">
         <v>340.1799926757812</v>
@@ -8382,10 +8382,10 @@
         <v>333.75</v>
       </c>
       <c r="W34" s="73" t="n">
-        <v>12195409</v>
+        <v>12676800</v>
       </c>
       <c r="X34" s="74" t="n">
-        <v>0.806290417278123</v>
+        <v>0.836785615271892</v>
       </c>
       <c r="Y34" s="28" t="n">
         <v>43.96862904014093</v>
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
-          <t>Jim Cramer Flagged Another Risk For Adobe Inc. (NASDAQ:ADBE)</t>
+          <t>Google-Backed Pixxel Raises $100 Million in India's Biggest Space-Tech Round</t>
         </is>
       </c>
       <c r="AY34" s="79" t="inlineStr">
         <is>
-          <t>Jim Cramer flagged one stock quietly concentrating portfolios</t>
+          <t>Alphabet May Be the Mag 7 Stock Investors Are Underestimating</t>
         </is>
       </c>
       <c r="AZ34" s="79" t="inlineStr">
         <is>
-          <t>Why IBM, Microsoft Back Move for Quantum Policy Czar</t>
+          <t>Agentic Commerce Optimisation: Azoma on Which Platforms Help Brands Get Recommended by AI Shopping Agents</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
         <v>3.029998779296875</v>
       </c>
       <c r="T35" s="83" t="n">
-        <v>41.02000045776367</v>
+        <v>41.04999923706055</v>
       </c>
       <c r="U35" s="83" t="n">
         <v>44.74499893188477</v>
@@ -8570,10 +8570,10 @@
         <v>41</v>
       </c>
       <c r="W35" s="84" t="n">
-        <v>35805723</v>
+        <v>36132300</v>
       </c>
       <c r="X35" s="85" t="n">
-        <v>0.7812574030649195</v>
+        <v>0.7881023102382216</v>
       </c>
       <c r="Y35" s="35" t="n">
         <v>57.15950356150678</v>
@@ -8652,17 +8652,17 @@
       </c>
       <c r="AX35" s="90" t="inlineStr">
         <is>
-          <t>IREN Climbs 4% on $2.4B Blue Owl-Led GPU Financing; Cipher Digital Gains 2%</t>
+          <t>IREN Jumps 23% as Its AI Business Starts to Take Over the Story</t>
         </is>
       </c>
       <c r="AY35" s="90" t="inlineStr">
         <is>
-          <t>Blue Owl leads $2.4 billion IREN GPU financing at 9%</t>
+          <t>IREN’s AI Pricing Is Exploding — Why the Neocloud’s $2.6 Billion Contract Base Could Scale Dramatically</t>
         </is>
       </c>
       <c r="AZ35" s="90" t="inlineStr">
         <is>
-          <t>IREN obtains $2.4B private credit financing to buy Nvidia chips</t>
+          <t>APLD Slides 36% in 3 Months: Should Investors Exit or Hold the Stock?</t>
         </is>
       </c>
     </row>
@@ -8749,19 +8749,19 @@
         <v>4.1300048828125</v>
       </c>
       <c r="T36" s="72" t="n">
-        <v>92.36000061035156</v>
+        <v>92.44999694824219</v>
       </c>
       <c r="U36" s="72" t="n">
         <v>95.94000244140625</v>
       </c>
       <c r="V36" s="72" t="n">
-        <v>91.87010192871094</v>
+        <v>91.87000274658203</v>
       </c>
       <c r="W36" s="73" t="n">
-        <v>97018400</v>
+        <v>97428100</v>
       </c>
       <c r="X36" s="74" t="n">
-        <v>0.9915221009495907</v>
+        <v>0.995500796324208</v>
       </c>
       <c r="Y36" s="28" t="n">
         <v>51.7442898847969</v>
@@ -8840,17 +8840,17 @@
       </c>
       <c r="AX36" s="79" t="inlineStr">
         <is>
-          <t>Coatue Opened Positions in Intel and Cerebras. Is the AI Chip Trade Broadening Beyond NVIDIA?</t>
+          <t>Prediction: Intel Stock Is Up Big in 2026. But the Best May Still Be Ahead</t>
         </is>
       </c>
       <c r="AY36" s="79" t="inlineStr">
         <is>
-          <t>Mizuho Resets Intel Target For the Rest of 2026</t>
+          <t>Nvidia just sent a strong signal to AMD and Intel investors</t>
         </is>
       </c>
       <c r="AZ36" s="79" t="inlineStr">
         <is>
-          <t>Lone Star JV Spends $1.2B On 2M SF R&amp;D Portfolio In Silicon Valley</t>
+          <t>AMD and Intel Soared as Nvidia Lagged: Has the AI Trade Changed?</t>
         </is>
       </c>
     </row>
@@ -8946,10 +8946,10 @@
         <v>499.3599853515625</v>
       </c>
       <c r="W37" s="84" t="n">
-        <v>17437000</v>
+        <v>18074400</v>
       </c>
       <c r="X37" s="85" t="n">
-        <v>0.7593015749291571</v>
+        <v>0.785966669993275</v>
       </c>
       <c r="Y37" s="35" t="n">
         <v>59.36327597001683</v>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="AX37" s="90" t="inlineStr">
         <is>
-          <t>Why IBM, Microsoft Back Move for Quantum Policy Czar</t>
+          <t>Nvidia, Microsoft at Center of $7 Trillion AI Boom</t>
         </is>
       </c>
       <c r="AY37" s="90" t="inlineStr">
         <is>
-          <t>Stifel Revamps Microsoft Target With a Catch</t>
+          <t>Microsoft Has a $1,000 Problem With Its Next Xbox</t>
         </is>
       </c>
       <c r="AZ37" s="90" t="inlineStr">
         <is>
-          <t>Microsoft Drops 1.6%, Opens Azure's $101.9 Billion Door</t>
+          <t>Microsoft Is Close to a New All-Time High. This Number Will Determine If It Keeps Climbing</t>
         </is>
       </c>
     </row>
@@ -9125,19 +9125,19 @@
         <v>-2.020004272460938</v>
       </c>
       <c r="T38" s="72" t="n">
-        <v>137.2200012207031</v>
+        <v>137.3500061035156</v>
       </c>
       <c r="U38" s="72" t="n">
         <v>144.3999938964844</v>
       </c>
       <c r="V38" s="72" t="n">
-        <v>137.0675048828125</v>
+        <v>137.0700073242188</v>
       </c>
       <c r="W38" s="73" t="n">
-        <v>26374686</v>
+        <v>27054700</v>
       </c>
       <c r="X38" s="74" t="n">
-        <v>0.9505035535867831</v>
+        <v>0.9738169729307915</v>
       </c>
       <c r="Y38" s="28" t="n">
         <v>66.19651579663915</v>
@@ -9188,7 +9188,7 @@
         <v>59.4034632349296</v>
       </c>
       <c r="AO38" s="77" t="n">
-        <v>6.064735586583529</v>
+        <v>6.064610414447036</v>
       </c>
       <c r="AP38" s="72" t="n">
         <v>365.2099914550781</v>
@@ -9216,17 +9216,17 @@
       </c>
       <c r="AX38" s="79" t="inlineStr">
         <is>
-          <t>Bitmine Sinks 6%, Strategy Slips: Is the Crypto Treasury Trade Unwinding?</t>
+          <t>Strategy Is Down More Than 50% in 12 Months. One Analyst Thinks the Stock Is About to Triple</t>
         </is>
       </c>
       <c r="AY38" s="79" t="inlineStr">
         <is>
-          <t>Michael Saylor Says Strategy Now Has More Reserve Capital Than Every S&amp;P 500 Finance Giant Except Berkshire...</t>
+          <t>MicroStrategy Drops $250 Bitcoin Jordans. But You Can’t Buy With Crypto</t>
         </is>
       </c>
       <c r="AZ38" s="79" t="inlineStr">
         <is>
-          <t>Michael Saylor Says ‘We’re Back’ as Strategy Resumes Bitcoin Buying. What Comes Next for MSTR Stock.</t>
+          <t>Michael Saylor's Strategy Continues to Sell Bitcoin. That's Why I'm Doubling Down on Bitcoin Right Now.</t>
         </is>
       </c>
     </row>
@@ -9313,7 +9313,7 @@
         <v>58.4300537109375</v>
       </c>
       <c r="T39" s="83" t="n">
-        <v>971.0599975585938</v>
+        <v>971.3400268554688</v>
       </c>
       <c r="U39" s="83" t="n">
         <v>1017.77001953125</v>
@@ -9322,10 +9322,10 @@
         <v>969</v>
       </c>
       <c r="W39" s="84" t="n">
-        <v>34925945</v>
+        <v>35116600</v>
       </c>
       <c r="X39" s="85" t="n">
-        <v>1.261270266663148</v>
+        <v>1.267718917482713</v>
       </c>
       <c r="Y39" s="35" t="n">
         <v>60.14679067938084</v>
@@ -9404,17 +9404,17 @@
       </c>
       <c r="AX39" s="90" t="inlineStr">
         <is>
-          <t>Dow Jones Futures: Nvidia, Micron, Sandisk Flash Buy Signals; Apple, Inflation Reports Ahead</t>
+          <t>Is Micron Technology Stock Running Out of Steam?</t>
         </is>
       </c>
       <c r="AY39" s="90" t="inlineStr">
         <is>
-          <t>David Tepper Sold 41% of His Micron Shares and It Is Still His Second-Biggest Holding</t>
+          <t>Why Micron and SK Hynix Sit in the Most Valuable Spot in the Entire Compute Stack</t>
         </is>
       </c>
       <c r="AZ39" s="90" t="inlineStr">
         <is>
-          <t>Analyst Has Strong Take on Micron, SanDisk Stocks</t>
+          <t>Everyone Is Watching Nvidia. But This Memory Stock Could Be the Next AI Winner</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
         <v>15.75999450683594</v>
       </c>
       <c r="T40" s="72" t="n">
-        <v>209.8919982910156</v>
+        <v>210.1900024414062</v>
       </c>
       <c r="U40" s="72" t="n">
         <v>226.5800018310547</v>
@@ -9510,10 +9510,10 @@
         <v>209.4049987792969</v>
       </c>
       <c r="W40" s="73" t="n">
-        <v>14803876</v>
+        <v>14890300</v>
       </c>
       <c r="X40" s="74" t="n">
-        <v>0.677375245757632</v>
+        <v>0.6811950271477512</v>
       </c>
       <c r="Y40" s="28" t="n">
         <v>53.52927511621272</v>
@@ -9592,17 +9592,17 @@
       </c>
       <c r="AX40" s="79" t="inlineStr">
         <is>
+          <t>Nebius Stock Up 254% in a Year: Should You Buy, Hold or Sell?</t>
+        </is>
+      </c>
+      <c r="AY40" s="79" t="inlineStr">
+        <is>
           <t>Billionaire Stephen Mandel’s Top 2 AI Stock Picks</t>
         </is>
       </c>
-      <c r="AY40" s="79" t="inlineStr">
+      <c r="AZ40" s="79" t="inlineStr">
         <is>
           <t>CoreWeave vs. Nebius: Which AI Infrastructure Stock Is the Better Buy?</t>
-        </is>
-      </c>
-      <c r="AZ40" s="79" t="inlineStr">
-        <is>
-          <t>3 Founder Backed Growth Stocks To Watch In September 2026</t>
         </is>
       </c>
     </row>
@@ -9698,10 +9698,10 @@
         <v>78.23000335693359</v>
       </c>
       <c r="W41" s="84" t="n">
-        <v>39850506</v>
+        <v>40066200</v>
       </c>
       <c r="X41" s="85" t="n">
-        <v>1.421796834890664</v>
+        <v>1.428942594534659</v>
       </c>
       <c r="Y41" s="35" t="n">
         <v>49.16100735547449</v>
@@ -9780,17 +9780,17 @@
       </c>
       <c r="AX41" s="90" t="inlineStr">
         <is>
-          <t>Walt Disney vs. Netflix: Which Media Stock Is a Better Buy in 2026?</t>
+          <t>Is Netflix Stock More Likely to Hit $100 or $60 by the End of 2026?</t>
         </is>
       </c>
       <c r="AY41" s="90" t="inlineStr">
         <is>
-          <t>NFLX Stock Falls 4% As Netflix Hikes UK Subscription Prices — Region Accounts For About 20% Of EMEA Revenue</t>
+          <t>Investors Heavily Search Netflix, Inc. (NFLX): Here is What You Need to Know</t>
         </is>
       </c>
       <c r="AZ41" s="90" t="inlineStr">
         <is>
-          <t>Netflix subscription rises above £20 a month for first time</t>
+          <t>Netflix Has Momentum Despite Being Down in 2026. One Analyst’s Price Target Implies 70% Upside</t>
         </is>
       </c>
     </row>
@@ -9880,16 +9880,16 @@
         <v>10</v>
       </c>
       <c r="U42" s="72" t="n">
-        <v>10.10499954223633</v>
+        <v>10.10999965667725</v>
       </c>
       <c r="V42" s="72" t="n">
-        <v>9.932000160217285</v>
+        <v>9.930000305175781</v>
       </c>
       <c r="W42" s="73" t="n">
-        <v>45518995</v>
+        <v>45824000</v>
       </c>
       <c r="X42" s="74" t="n">
-        <v>0.6683527848122022</v>
+        <v>0.6726805300353824</v>
       </c>
       <c r="Y42" s="28" t="n">
         <v>47.17559913079245</v>
@@ -9898,7 +9898,7 @@
         <v>40.83332075012855</v>
       </c>
       <c r="AA42" s="28" t="n">
-        <v>12.55979865142888</v>
+        <v>12.54951106034842</v>
       </c>
       <c r="AB42" s="75" t="n">
         <v>-0.1271678064059536</v>
@@ -9940,7 +9940,7 @@
         <v>15.7948809207682</v>
       </c>
       <c r="AO42" s="77" t="n">
-        <v>4.493943217535415</v>
+        <v>4.497504045461661</v>
       </c>
       <c r="AP42" s="72" t="n">
         <v>17.45000076293945</v>
@@ -10041,7 +10041,7 @@
         </is>
       </c>
       <c r="N43" s="80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O43" s="30" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>1.910003662109375</v>
       </c>
       <c r="T43" s="83" t="n">
-        <v>231.1419982910156</v>
+        <v>231.0899963378906</v>
       </c>
       <c r="U43" s="83" t="n">
         <v>234.7599945068359</v>
@@ -10074,10 +10074,10 @@
         <v>229.6300048828125</v>
       </c>
       <c r="W43" s="84" t="n">
-        <v>132204717</v>
+        <v>134946800</v>
       </c>
       <c r="X43" s="85" t="n">
-        <v>1.026731349422683</v>
+        <v>1.046912245494214</v>
       </c>
       <c r="Y43" s="35" t="n">
         <v>60.39157103041679</v>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
-          <t>Jim Cramer Believes Nvidia Corp. (NASDAQ:NVDA) Buying Back Half A Trillion Worth In Stock Would Be Great</t>
+          <t>Jim Cramer Discusses NVIDIA (NVDA) Acquiring Hugging Face</t>
         </is>
       </c>
       <c r="AY43" s="90" t="inlineStr">
         <is>
-          <t>Dow Jones Futures: Nvidia, Micron, Sandisk Flash Buy Signals; Apple, Inflation Reports Ahead</t>
+          <t>Could This Vanguard Growth ETF Be a No-Brainer Buy for Long-Term Investors?</t>
         </is>
       </c>
       <c r="AZ43" s="90" t="inlineStr">
         <is>
-          <t>Elon Musk Committed SpaceX to Building "Exclusively on Nvidia." Here's What That Locks In for SpaceX's Comp...</t>
+          <t>Nvidia, Microsoft at Center of $7 Trillion AI Boom</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10253,7 @@
         <v>-8.199996948242188</v>
       </c>
       <c r="T44" s="72" t="n">
-        <v>180.0200042724609</v>
+        <v>180.0099945068359</v>
       </c>
       <c r="U44" s="72" t="n">
         <v>182.1900024414062</v>
@@ -10262,10 +10262,10 @@
         <v>173.6699981689453</v>
       </c>
       <c r="W44" s="73" t="n">
-        <v>27620762</v>
+        <v>27895300</v>
       </c>
       <c r="X44" s="74" t="n">
-        <v>0.8334926717933018</v>
+        <v>0.8414286729082638</v>
       </c>
       <c r="Y44" s="28" t="n">
         <v>54.156136979617</v>
@@ -10344,17 +10344,17 @@
       </c>
       <c r="AX44" s="79" t="inlineStr">
         <is>
-          <t>Palantir (PLTR) Stock Fair Value Edges Higher After Strong Q2 And Raised Guidance</t>
+          <t>Cathie Wood Is Moving Money From Palantir Into Rocket Lab and Fintech</t>
         </is>
       </c>
       <c r="AY44" s="79" t="inlineStr">
         <is>
-          <t>Palantir just won the Army and lost Michael Burry</t>
+          <t>Cathie Wood Dumps $25 Million of Palantir Shares. Should PLTR Investors Worry?</t>
         </is>
       </c>
       <c r="AZ44" s="79" t="inlineStr">
         <is>
-          <t>SCHG Owns More Apple Than Tesla, Meta and Palantir Combined. Is That Why Growth Investors Are Falling Behind?</t>
+          <t>Palantir Surged 51% in August. The Rest of Tech Wasn't Even Close</t>
         </is>
       </c>
     </row>
@@ -10441,7 +10441,7 @@
         <v>0.1699981689453125</v>
       </c>
       <c r="T45" s="83" t="n">
-        <v>169.8200073242188</v>
+        <v>169.9799957275391</v>
       </c>
       <c r="U45" s="83" t="n">
         <v>170.6300048828125</v>
@@ -10450,10 +10450,10 @@
         <v>167.0399932861328</v>
       </c>
       <c r="W45" s="84" t="n">
-        <v>8495424</v>
+        <v>8531400</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>0.9341388349337777</v>
+        <v>0.9379091685639812</v>
       </c>
       <c r="Y45" s="35" t="n">
         <v>53.07748990482058</v>
@@ -10638,10 +10638,10 @@
         <v>63.20000076293945</v>
       </c>
       <c r="W46" s="73" t="n">
-        <v>14797841</v>
+        <v>14867600</v>
       </c>
       <c r="X46" s="74" t="n">
-        <v>0.864714088590396</v>
+        <v>0.8686134265378823</v>
       </c>
       <c r="Y46" s="28" t="n">
         <v>37.19328452182177</v>
@@ -10720,17 +10720,17 @@
       </c>
       <c r="AX46" s="79" t="inlineStr">
         <is>
-          <t>Cathie Wood Just Bought 705,102 Shares of a Rocket Company 50 Times Smaller Than SpaceX</t>
+          <t>Cathie Wood Is Moving Money From Palantir Into Rocket Lab and Fintech</t>
         </is>
       </c>
       <c r="AY46" s="79" t="inlineStr">
         <is>
-          <t>SPCX Stock Blasts Past ASTS, RKLB, LUNR, PL — Here’s Everything Shaking Up Space Stocks This Week</t>
+          <t>The Real Satellite Race Isn’t About Rockets — It’s About Who Controls the Spectrum in Your Phone</t>
         </is>
       </c>
       <c r="AZ46" s="79" t="inlineStr">
         <is>
-          <t>Is Rocket Lab Stock a Millionaire Maker?</t>
+          <t>Cathie Wood Buys $45 Million of Rocket Lab Stock</t>
         </is>
       </c>
     </row>
@@ -10817,7 +10817,7 @@
         <v>185.010009765625</v>
       </c>
       <c r="T47" s="83" t="n">
-        <v>1585.589965820312</v>
+        <v>1586</v>
       </c>
       <c r="U47" s="83" t="n">
         <v>1740</v>
@@ -10826,10 +10826,10 @@
         <v>1581</v>
       </c>
       <c r="W47" s="84" t="n">
-        <v>16217211</v>
+        <v>16487100</v>
       </c>
       <c r="X47" s="85" t="n">
-        <v>1.221999037596914</v>
+        <v>1.24107374396338</v>
       </c>
       <c r="Y47" s="35" t="n">
         <v>61.24267366525383</v>
@@ -10908,17 +10908,17 @@
       </c>
       <c r="AX47" s="90" t="inlineStr">
         <is>
-          <t>Dow Jones Futures: Nvidia, Micron, Sandisk Flash Buy Signals; Apple, Inflation Reports Ahead</t>
+          <t>Innovation Engine Drives SharkNinja’s (SN) Sustainable Advantage</t>
         </is>
       </c>
       <c r="AY47" s="90" t="inlineStr">
         <is>
-          <t>Stock Market Today: Dow Sinks Amid Rate Fears; Sandisk, KLA Lead Nasdaq-100 As Utilities Gain</t>
+          <t>Nike Exits S&amp;P 100 After Nearly 18 Years. Dell, SanDisk and 2 Tech Giants Take Its Place</t>
         </is>
       </c>
       <c r="AZ47" s="90" t="inlineStr">
         <is>
-          <t>Analyst Has Strong Take on Micron, SanDisk Stocks</t>
+          <t>Sandisk Jumps 12% as AI Storage Trade Keeps Running</t>
         </is>
       </c>
     </row>
@@ -11005,19 +11005,19 @@
         <v>-22.29000854492188</v>
       </c>
       <c r="T48" s="72" t="n">
-        <v>362.1799926757812</v>
+        <v>362.0700073242188</v>
       </c>
       <c r="U48" s="72" t="n">
         <v>364.6900024414062</v>
       </c>
       <c r="V48" s="72" t="n">
-        <v>351.3200988769531</v>
+        <v>351.3200073242188</v>
       </c>
       <c r="W48" s="73" t="n">
-        <v>64559388</v>
+        <v>64829000</v>
       </c>
       <c r="X48" s="74" t="n">
-        <v>1.701892134477516</v>
+        <v>1.708392439317929</v>
       </c>
       <c r="Y48" s="28" t="n">
         <v>50.92656358273328</v>
@@ -11026,7 +11026,7 @@
         <v>43.38621623071099</v>
       </c>
       <c r="AA48" s="28" t="n">
-        <v>22.80348946706436</v>
+        <v>22.80348165299782</v>
       </c>
       <c r="AB48" s="75" t="n">
         <v>3.659291261924011</v>
@@ -11068,7 +11068,7 @@
         <v>13.87044531288085</v>
       </c>
       <c r="AO48" s="77" t="n">
-        <v>4.312073231750098</v>
+        <v>4.312075078643816</v>
       </c>
       <c r="AP48" s="72" t="n">
         <v>498.8299865722656</v>
@@ -11096,17 +11096,17 @@
       </c>
       <c r="AX48" s="79" t="inlineStr">
         <is>
-          <t>No steering wheel, no problem: Can Tesla speed by Cybercab probe?</t>
+          <t>Goldman Sachs Delivers Stark Message on Tesla Stock</t>
         </is>
       </c>
       <c r="AY48" s="79" t="inlineStr">
         <is>
-          <t>Tesla Launched the Cybercab Thursday, 6 Weeks After Removing Volume Production of It From This Year's Plan</t>
+          <t>Cybercab Could Transform Tesla, But Regulatory Risks Loom</t>
         </is>
       </c>
       <c r="AZ48" s="79" t="inlineStr">
         <is>
-          <t>From Launch Party to Federal Probe: What Went Wrong With Tesla's Cybercab in 24 Hours</t>
+          <t>Is Tesla Stock Under $360 a Share an Obvious Buy in September?</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 4 Sep 2026, 11:02 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 08:41 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 4 Sep 2026, 11:02 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 08:41 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 4 Sep 2026, 11:02 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 08:41 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 4 Sep 2026, 11:02 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 08:41 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -43864,7 +43864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G45"/>
+  <dimension ref="B2:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -44238,21 +44238,21 @@
     <row r="17">
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C17" s="102" t="inlineStr">
         <is>
-          <t>IREN Limited</t>
-        </is>
-      </c>
-      <c r="D17" s="105" t="inlineStr">
-        <is>
-          <t>Gapped down 1.5% at the open</t>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="D17" s="106" t="inlineStr">
+        <is>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E17" s="33" t="n">
-        <v>0.07274906766604095</v>
+        <v>0.04693529351593129</v>
       </c>
       <c r="F17" s="34" t="n">
         <v>7</v>
@@ -44266,21 +44266,21 @@
     <row r="18">
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C18" s="101" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
-        </is>
-      </c>
-      <c r="D18" s="107" t="inlineStr">
-        <is>
-          <t>MACD crossed up</t>
+          <t>State Street Technology Select Sector SPDR ETF</t>
+        </is>
+      </c>
+      <c r="D18" s="104" t="inlineStr">
+        <is>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>0.04693529351593129</v>
+        <v>0.007044133731219926</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>7</v>
@@ -44294,21 +44294,21 @@
     <row r="19">
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C19" s="102" t="inlineStr">
         <is>
-          <t>State Street Technology Select Sector SPDR ETF</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="D19" s="105" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped down 5.2% at the open</t>
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>0.007044133731219926</v>
+        <v>-0.01394837847189589</v>
       </c>
       <c r="F19" s="34" t="n">
         <v>7</v>
@@ -44322,24 +44322,24 @@
     <row r="20">
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="C20" s="101" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>CoreWeave, Inc.</t>
         </is>
       </c>
       <c r="D20" s="104" t="inlineStr">
         <is>
-          <t>Gapped down 5.2% at the open</t>
+          <t>RSI crossed back above 50</t>
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.01394837847189589</v>
+        <v>0.05676446535410284</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
       </c>
       <c r="D21" s="105" t="inlineStr">
         <is>
-          <t>RSI crossed back above 50</t>
+          <t>Reclaimed the 50 DMA</t>
         </is>
       </c>
       <c r="E21" s="33" t="n">
@@ -44378,21 +44378,21 @@
     <row r="22">
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C22" s="101" t="inlineStr">
         <is>
-          <t>CoreWeave, Inc.</t>
+          <t>Cameco Corporation</t>
         </is>
       </c>
       <c r="D22" s="104" t="inlineStr">
         <is>
-          <t>Reclaimed the 50 DMA</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>0.05676446535410284</v>
+        <v>0.00119255728395995</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>6</v>
@@ -44406,21 +44406,21 @@
     <row r="23">
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C23" s="102" t="inlineStr">
         <is>
-          <t>CoreWeave, Inc.</t>
+          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
         </is>
       </c>
       <c r="D23" s="105" t="inlineStr">
         <is>
-          <t>Gapped up 1.7% at the open</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>0.05676446535410284</v>
+        <v>-0.003854237146576178</v>
       </c>
       <c r="F23" s="34" t="n">
         <v>6</v>
@@ -44434,56 +44434,56 @@
     <row r="24">
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>SOXL</t>
         </is>
       </c>
       <c r="C24" s="101" t="inlineStr">
         <is>
-          <t>Cameco Corporation</t>
-        </is>
-      </c>
-      <c r="D24" s="104" t="inlineStr">
-        <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Direxion Daily Semiconductor Bull 3X Shares</t>
+        </is>
+      </c>
+      <c r="D24" s="107" t="inlineStr">
+        <is>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>0.00119255728395995</v>
+        <v>0.09874462363189629</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SOXL</t>
         </is>
       </c>
       <c r="C25" s="102" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
+          <t>Direxion Daily Semiconductor Bull 3X Shares</t>
         </is>
       </c>
       <c r="D25" s="105" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Reclaimed the 200 DMA</t>
         </is>
       </c>
       <c r="E25" s="33" t="n">
-        <v>-0.003854237146576178</v>
+        <v>0.09874462363189629</v>
       </c>
       <c r="F25" s="34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" s="30" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -44498,9 +44498,9 @@
           <t>Direxion Daily Semiconductor Bull 3X Shares</t>
         </is>
       </c>
-      <c r="D26" s="107" t="inlineStr">
-        <is>
-          <t>MACD crossed up</t>
+      <c r="D26" s="104" t="inlineStr">
+        <is>
+          <t>Gapped up 4.2% at the open</t>
         </is>
       </c>
       <c r="E26" s="26" t="n">
@@ -44518,21 +44518,21 @@
     <row r="27">
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>SOXL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C27" s="102" t="inlineStr">
         <is>
-          <t>Direxion Daily Semiconductor Bull 3X Shares</t>
-        </is>
-      </c>
-      <c r="D27" s="105" t="inlineStr">
-        <is>
-          <t>Reclaimed the 200 DMA</t>
+          <t>Arm Holdings plc</t>
+        </is>
+      </c>
+      <c r="D27" s="106" t="inlineStr">
+        <is>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E27" s="33" t="n">
-        <v>0.09874462363189629</v>
+        <v>0.03916072444622976</v>
       </c>
       <c r="F27" s="34" t="n">
         <v>5</v>
@@ -44546,21 +44546,21 @@
     <row r="28">
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>SOXL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C28" s="101" t="inlineStr">
         <is>
-          <t>Direxion Daily Semiconductor Bull 3X Shares</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="D28" s="104" t="inlineStr">
         <is>
-          <t>Gapped up 4.2% at the open</t>
+          <t>Gapped up 2.5% at the open</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>0.09874462363189629</v>
+        <v>0.03916072444622976</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>5</v>
@@ -44582,9 +44582,9 @@
           <t>Arm Holdings plc</t>
         </is>
       </c>
-      <c r="D29" s="106" t="inlineStr">
-        <is>
-          <t>MACD crossed up</t>
+      <c r="D29" s="105" t="inlineStr">
+        <is>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E29" s="33" t="n">
@@ -44602,21 +44602,21 @@
     <row r="30">
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C30" s="101" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="D30" s="104" t="inlineStr">
         <is>
-          <t>Gapped up 2.6% at the open</t>
+          <t>Lost the 50 DMA</t>
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>0.03916072444622976</v>
+        <v>-0.05922365978717725</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>5</v>
@@ -44630,21 +44630,21 @@
     <row r="31">
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C31" s="102" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="D31" s="105" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped down 3.8% at the open</t>
         </is>
       </c>
       <c r="E31" s="33" t="n">
-        <v>0.03916072444622976</v>
+        <v>-0.05922365978717725</v>
       </c>
       <c r="F31" s="34" t="n">
         <v>5</v>
@@ -44658,24 +44658,24 @@
     <row r="32">
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C32" s="101" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="D32" s="104" t="inlineStr">
         <is>
-          <t>Lost the 50 DMA</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>-0.05922365978717725</v>
+        <v>-0.04492410564335281</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
@@ -44686,40 +44686,40 @@
     <row r="33">
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C33" s="102" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Nokia Oyj</t>
         </is>
       </c>
       <c r="D33" s="105" t="inlineStr">
         <is>
-          <t>Gapped down 3.8% at the open</t>
+          <t>Gapped up 2.4% at the open</t>
         </is>
       </c>
       <c r="E33" s="33" t="n">
-        <v>-0.05922365978717725</v>
+        <v>0.02661200235675665</v>
       </c>
       <c r="F33" s="34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33" s="30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C34" s="101" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Nokia Oyj</t>
         </is>
       </c>
       <c r="D34" s="104" t="inlineStr">
@@ -44728,35 +44728,35 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>-0.04492410564335281</v>
+        <v>0.02661200235675665</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="C35" s="102" t="inlineStr">
         <is>
-          <t>Nokia Oyj</t>
+          <t>AST SpaceMobile, Inc.</t>
         </is>
       </c>
       <c r="D35" s="105" t="inlineStr">
         <is>
-          <t>Gapped up 2.4% at the open</t>
+          <t>Gapped up 2.0% at the open</t>
         </is>
       </c>
       <c r="E35" s="33" t="n">
-        <v>0.02661200235675665</v>
+        <v>0.002897155996801626</v>
       </c>
       <c r="F35" s="34" t="n">
         <v>3</v>
@@ -44770,21 +44770,21 @@
     <row r="36">
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C36" s="101" t="inlineStr">
         <is>
-          <t>Nokia Oyj</t>
-        </is>
-      </c>
-      <c r="D36" s="104" t="inlineStr">
-        <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>State Street Utilities Select Sector SPDR ETF</t>
+        </is>
+      </c>
+      <c r="D36" s="107" t="inlineStr">
+        <is>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>0.02661200235675665</v>
+        <v>0.001162050968541273</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>3</v>
@@ -44798,24 +44798,24 @@
     <row r="37">
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C37" s="102" t="inlineStr">
         <is>
-          <t>AST SpaceMobile, Inc.</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D37" s="105" t="inlineStr">
         <is>
-          <t>Gapped up 2.1% at the open</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E37" s="33" t="n">
-        <v>0.002897155996801626</v>
+        <v>-0.003420758434616977</v>
       </c>
       <c r="F37" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" s="30" t="inlineStr">
         <is>
@@ -44826,24 +44826,24 @@
     <row r="38">
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C38" s="101" t="inlineStr">
         <is>
-          <t>State Street Utilities Select Sector SPDR ETF</t>
-        </is>
-      </c>
-      <c r="D38" s="107" t="inlineStr">
-        <is>
-          <t>MACD crossed up</t>
+          <t>State Street Materials Select Sector SPDR ETF</t>
+        </is>
+      </c>
+      <c r="D38" s="104" t="inlineStr">
+        <is>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>0.001162050968541273</v>
+        <v>-0.003420758434616977</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
@@ -44854,21 +44854,21 @@
     <row r="39">
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C39" s="102" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="D39" s="105" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>-0.003420758434616977</v>
+        <v>-0.05346556510032285</v>
       </c>
       <c r="F39" s="34" t="n">
         <v>2</v>
@@ -44882,21 +44882,21 @@
     <row r="40">
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C40" s="101" t="inlineStr">
         <is>
-          <t>State Street Materials Select Sector SPDR ETF</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="D40" s="104" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>RSI dropped below 50</t>
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>-0.003420758434616977</v>
+        <v>-0.05346556510032285</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>2</v>
@@ -44910,68 +44910,68 @@
     <row r="41">
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C41" s="102" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D41" s="105" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Lost the 50 DMA</t>
         </is>
       </c>
       <c r="E41" s="33" t="n">
-        <v>-0.05346556510032285</v>
+        <v>-0.007975607414239305</v>
       </c>
       <c r="F41" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Very Weak</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C42" s="101" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D42" s="104" t="inlineStr">
         <is>
-          <t>RSI dropped below 50</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>-0.05346556510032285</v>
+        <v>-0.01111828820032235</v>
       </c>
       <c r="F42" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Very Weak</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C43" s="102" t="inlineStr">
         <is>
-          <t>State Street Consumer Staples Select Sector SPDR ETF</t>
+          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D43" s="105" t="inlineStr">
@@ -44980,79 +44980,23 @@
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>-0.007975607414239305</v>
+        <v>-0.01330925154171614</v>
       </c>
       <c r="F43" s="34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="30" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="C44" s="101" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="D44" s="104" t="inlineStr">
-        <is>
-          <t>Bands squeezing — a big move often follows</t>
-        </is>
-      </c>
-      <c r="E44" s="26" t="n">
-        <v>-0.01111828820032235</v>
-      </c>
-      <c r="F44" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="23" t="inlineStr">
-        <is>
-          <t>Very Weak</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="31" t="inlineStr">
-        <is>
-          <t>XLY</t>
-        </is>
-      </c>
-      <c r="C45" s="102" t="inlineStr">
-        <is>
-          <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
-        </is>
-      </c>
-      <c r="D45" s="105" t="inlineStr">
-        <is>
-          <t>Lost the 50 DMA</t>
-        </is>
-      </c>
-      <c r="E45" s="33" t="n">
-        <v>-0.01330925154171614</v>
-      </c>
-      <c r="F45" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="30" t="inlineStr">
         <is>
           <t>Very Weak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:G45"/>
+  <autoFilter ref="B5:G43"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E45">
+  <conditionalFormatting sqref="E6:E43">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 7 Sep 2026, 08:41 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 7 Sep 2026, 10:51 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 7 Sep 2026, 08:41 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 10:51 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -5999,17 +5999,17 @@
       </c>
       <c r="AX20" s="90" t="inlineStr">
         <is>
+          <t>QQQ Charged 0.20% for Years. The Fee Only Fell After Shareholders Approved a Structural Change</t>
+        </is>
+      </c>
+      <c r="AY20" s="90" t="inlineStr">
+        <is>
           <t>This ETF Would Have Increased Your Investment by 6x Over the Past 10 Years -- and It's Still Soaring</t>
         </is>
       </c>
-      <c r="AY20" s="90" t="inlineStr">
+      <c r="AZ20" s="90" t="inlineStr">
         <is>
           <t>The VIX Is Playing Tricks: Why Stocks Are Volatile, But the Fear Gauge Is Sleeping</t>
-        </is>
-      </c>
-      <c r="AZ20" s="90" t="inlineStr">
-        <is>
-          <t>Exchange-Traded Funds Mixed, US Equities Lower After Midday</t>
         </is>
       </c>
     </row>
@@ -6584,17 +6584,17 @@
       </c>
       <c r="AX24" s="79" t="inlineStr">
         <is>
-          <t>KeyBanc Delivers Stark Warning on Apple Stock Ahead of iPhone 18 Launch</t>
+          <t>Apple's $54 Billion iPhone Engine Hits an AI Memory Squeeze</t>
         </is>
       </c>
       <c r="AY24" s="79" t="inlineStr">
         <is>
-          <t>Apple’s new CEO faces a staggering $14 billion iPhone test</t>
+          <t>Tim Cook Delivered a 2,720% Total Return Over 15 Years. Here's Whether John Ternus Can Do the Same for Appl...</t>
         </is>
       </c>
       <c r="AZ24" s="79" t="inlineStr">
         <is>
-          <t>Apple Faces Its Biggest iPhone Test in Years -- Morgan Stanley Sees $14B Foldable Opportunity</t>
+          <t>Apple's $320 Stock Faces Huawei's 68% Foldable Fortress</t>
         </is>
       </c>
     </row>
@@ -6772,17 +6772,17 @@
       </c>
       <c r="AX25" s="90" t="inlineStr">
         <is>
+          <t>AMD Stock Jumps After Unveiling $100,000-Plus AI Workstation for 2027</t>
+        </is>
+      </c>
+      <c r="AY25" s="90" t="inlineStr">
+        <is>
           <t>Wall Street Is Worried About AMD. Here’s Why Long-Term Investors Shouldn’t Be</t>
         </is>
       </c>
-      <c r="AY25" s="90" t="inlineStr">
+      <c r="AZ25" s="90" t="inlineStr">
         <is>
           <t>AMD Is Behind The AI Chip Shift Nobody Is Talking About</t>
-        </is>
-      </c>
-      <c r="AZ25" s="90" t="inlineStr">
-        <is>
-          <t>AMD’s Whole AI Story Has One Threat It Cannot Ignore: Broadcom</t>
         </is>
       </c>
     </row>
@@ -6960,17 +6960,17 @@
       </c>
       <c r="AX26" s="79" t="inlineStr">
         <is>
-          <t>Fatal Amazon Plane Crash Delays Hundreds of Miami Flights</t>
+          <t>Scene of Fatal Amazon Plane Crash in Miami Is ‘Devastating’</t>
         </is>
       </c>
       <c r="AY26" s="79" t="inlineStr">
         <is>
-          <t>Are Retail-Wholesale Stocks Lagging Amazon.com (AMZN) This Year?</t>
+          <t>Amazon's 250-Flight Air Network Faces a Fatal Miami Investigation</t>
         </is>
       </c>
       <c r="AZ26" s="79" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc. (AMZN) is Attracting Investor Attention: Here is What You Should Know</t>
+          <t>Is Amazon Stock at $255 a Share an Obvious Buy Right Now?</t>
         </is>
       </c>
     </row>
@@ -7524,17 +7524,17 @@
       </c>
       <c r="AX29" s="90" t="inlineStr">
         <is>
+          <t>Is AST SpaceMobile a Millionaire-Maker Over The Next Decade?</t>
+        </is>
+      </c>
+      <c r="AY29" s="90" t="inlineStr">
+        <is>
           <t>AST SpaceMobile Director Adriana Cisneros Buys $619,235 Shares. What Does This Mean for Investors?</t>
         </is>
       </c>
-      <c r="AY29" s="90" t="inlineStr">
+      <c r="AZ29" s="90" t="inlineStr">
         <is>
           <t>The Real Satellite Race Isn’t About Rockets — It’s About Who Controls the Spectrum in Your Phone</t>
-        </is>
-      </c>
-      <c r="AZ29" s="90" t="inlineStr">
-        <is>
-          <t>Forget Starlink? Japan’s $1 Billion BlueBird Play Makes ASTS the National Satellite OS</t>
         </is>
       </c>
     </row>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
+          <t>Broadcom’s AI Forecast Suggests Hyperscalers Want More Than Just Nvidia GPUs</t>
+        </is>
+      </c>
+      <c r="AY30" s="79" t="inlineStr">
+        <is>
           <t>Broadcom Inc. (AVGO)’s AI Opportunity Expands Across AI Infrastructure</t>
         </is>
       </c>
-      <c r="AY30" s="79" t="inlineStr">
+      <c r="AZ30" s="79" t="inlineStr">
         <is>
           <t>Broadcom vs Marvell: One of These AI Chip Stocks Is a Clear Winner</t>
-        </is>
-      </c>
-      <c r="AZ30" s="79" t="inlineStr">
-        <is>
-          <t>Broadcom Inc. (AVGO) Is a Trending Stock: Facts to Know Before Betting on It</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AZ31" s="90" t="inlineStr">
         <is>
-          <t>Cameco (TSX:CCO) Tests Nuclear Growth Hopes On A Fair Value Gap</t>
+          <t>Jefferies Sees Cameco (CCJ) and BWXT as Winners in the Nuclear Boom</t>
         </is>
       </c>
     </row>
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
+          <t>Google's AI Slashes Contrail Warming 40% in a Real-World Test</t>
+        </is>
+      </c>
+      <c r="AY34" s="79" t="inlineStr">
+        <is>
           <t>Google-Backed Pixxel Raises $100 Million in India's Biggest Space-Tech Round</t>
         </is>
       </c>
-      <c r="AY34" s="79" t="inlineStr">
+      <c r="AZ34" s="79" t="inlineStr">
         <is>
           <t>Alphabet May Be the Mag 7 Stock Investors Are Underestimating</t>
-        </is>
-      </c>
-      <c r="AZ34" s="79" t="inlineStr">
-        <is>
-          <t>Agentic Commerce Optimisation: Azoma on Which Platforms Help Brands Get Recommended by AI Shopping Agents</t>
         </is>
       </c>
     </row>
@@ -8840,17 +8840,17 @@
       </c>
       <c r="AX36" s="79" t="inlineStr">
         <is>
+          <t>5-star analyst resets Intel stock price target</t>
+        </is>
+      </c>
+      <c r="AY36" s="79" t="inlineStr">
+        <is>
           <t>Prediction: Intel Stock Is Up Big in 2026. But the Best May Still Be Ahead</t>
         </is>
       </c>
-      <c r="AY36" s="79" t="inlineStr">
+      <c r="AZ36" s="79" t="inlineStr">
         <is>
           <t>Nvidia just sent a strong signal to AMD and Intel investors</t>
-        </is>
-      </c>
-      <c r="AZ36" s="79" t="inlineStr">
-        <is>
-          <t>AMD and Intel Soared as Nvidia Lagged: Has the AI Trade Changed?</t>
         </is>
       </c>
     </row>
@@ -9404,17 +9404,17 @@
       </c>
       <c r="AX39" s="90" t="inlineStr">
         <is>
+          <t>Micron's $50 Billion Guide Gets an 8.3% Signal From Seoul</t>
+        </is>
+      </c>
+      <c r="AY39" s="90" t="inlineStr">
+        <is>
+          <t>Micron, SanDisk get new aggressive price targets from top analyst</t>
+        </is>
+      </c>
+      <c r="AZ39" s="90" t="inlineStr">
+        <is>
           <t>Is Micron Technology Stock Running Out of Steam?</t>
-        </is>
-      </c>
-      <c r="AY39" s="90" t="inlineStr">
-        <is>
-          <t>Why Micron and SK Hynix Sit in the Most Valuable Spot in the Entire Compute Stack</t>
-        </is>
-      </c>
-      <c r="AZ39" s="90" t="inlineStr">
-        <is>
-          <t>Everyone Is Watching Nvidia. But This Memory Stock Could Be the Next AI Winner</t>
         </is>
       </c>
     </row>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
-          <t>Jim Cramer Discusses NVIDIA (NVDA) Acquiring Hugging Face</t>
+          <t>Palantir Stock Leads August Rally -- Nvidia, Salesforce and Super Micro Jump</t>
         </is>
       </c>
       <c r="AY43" s="90" t="inlineStr">
         <is>
-          <t>Could This Vanguard Growth ETF Be a No-Brainer Buy for Long-Term Investors?</t>
+          <t>Nvidia Insider Makes Stunning $410 Million Stock Move</t>
         </is>
       </c>
       <c r="AZ43" s="90" t="inlineStr">
         <is>
-          <t>Nvidia, Microsoft at Center of $7 Trillion AI Boom</t>
+          <t>Tencent Slips 1% While Its AI-Chip Bet Attacks Nvidia's China Moat</t>
         </is>
       </c>
     </row>
@@ -10344,17 +10344,17 @@
       </c>
       <c r="AX44" s="79" t="inlineStr">
         <is>
+          <t>Palantir Stock Leads August Rally -- Nvidia, Salesforce and Super Micro Jump</t>
+        </is>
+      </c>
+      <c r="AY44" s="79" t="inlineStr">
+        <is>
+          <t>Burry’s Palantir Warning Is Back. Accenture Shows What Investors Should Check</t>
+        </is>
+      </c>
+      <c r="AZ44" s="79" t="inlineStr">
+        <is>
           <t>Cathie Wood Is Moving Money From Palantir Into Rocket Lab and Fintech</t>
-        </is>
-      </c>
-      <c r="AY44" s="79" t="inlineStr">
-        <is>
-          <t>Cathie Wood Dumps $25 Million of Palantir Shares. Should PLTR Investors Worry?</t>
-        </is>
-      </c>
-      <c r="AZ44" s="79" t="inlineStr">
-        <is>
-          <t>Palantir Surged 51% in August. The Rest of Tech Wasn't Even Close</t>
         </is>
       </c>
     </row>
@@ -10908,17 +10908,17 @@
       </c>
       <c r="AX47" s="90" t="inlineStr">
         <is>
+          <t>Sandisk Soars Nearly 12% Before Joining the S&amp;P 100</t>
+        </is>
+      </c>
+      <c r="AY47" s="90" t="inlineStr">
+        <is>
+          <t>Micron, SanDisk get new aggressive price targets from top analyst</t>
+        </is>
+      </c>
+      <c r="AZ47" s="90" t="inlineStr">
+        <is>
           <t>Innovation Engine Drives SharkNinja’s (SN) Sustainable Advantage</t>
-        </is>
-      </c>
-      <c r="AY47" s="90" t="inlineStr">
-        <is>
-          <t>Nike Exits S&amp;P 100 After Nearly 18 Years. Dell, SanDisk and 2 Tech Giants Take Its Place</t>
-        </is>
-      </c>
-      <c r="AZ47" s="90" t="inlineStr">
-        <is>
-          <t>Sandisk Jumps 12% as AI Storage Trade Keeps Running</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 7 Sep 2026, 08:41 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 10:51 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 7 Sep 2026, 08:41 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 10:51 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 7 Sep 2026, 08:41 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 10:51 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 7 Sep 2026, 08:41 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 10:51 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 7 Sep 2026, 10:51 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 7 Sep 2026, 11:29 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 7 Sep 2026, 10:51 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 11:29 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 7 Sep 2026, 10:51 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 11:29 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 7 Sep 2026, 10:51 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 11:29 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 7 Sep 2026, 10:51 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 11:29 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 7 Sep 2026, 10:51 PM · Yahoo Finance data</t>
+          <t>Built 7 Sep 2026, 11:29 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'09-02'!$5:$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'09-01'!$A$6:$AZ$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'09-01'!$5:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Signals'!$B$5:$G$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 8 Sep 2026, 08:02 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 8 Sep 2026, 10:43 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1390,7 +1390,7 @@
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="L8" s="10" t="n"/>
@@ -1404,7 +1404,7 @@
       <c r="P8" s="10" t="n"/>
       <c r="Q8" s="16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R8" s="12" t="n"/>
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>0.01100533652705571</v>
+        <v>0.01108334548129264</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>66.17874588140691</v>
+        <v>66.19848629337565</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>8.992534896549875</v>
+        <v>9.000761401287027</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0.01258599619603817</v>
+        <v>0.01266412711363518</v>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.1263478154721467</v>
+        <v>0.1264347242272419</v>
       </c>
     </row>
     <row r="15">
@@ -1559,7 +1559,7 @@
         <v>0.008588647078887623</v>
       </c>
       <c r="F15" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" s="35" t="n">
         <v>48.76529694830028</v>
@@ -1622,22 +1622,22 @@
         </is>
       </c>
       <c r="E17" s="33" t="n">
-        <v>-0.0007967185788519959</v>
+        <v>-0.0006828768287838738</v>
       </c>
       <c r="F17" s="34" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="35" t="n">
-        <v>39.81401726539807</v>
+        <v>39.86747270631402</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>-2.066650765349909</v>
+        <v>-2.055711540290439</v>
       </c>
       <c r="I17" s="33" t="n">
-        <v>-0.004874181582700698</v>
+        <v>-0.004760804388276862</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>-0.0241218118166906</v>
+        <v>-0.02401062755332628</v>
       </c>
     </row>
     <row r="18">
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>-0.004373809418090291</v>
+        <v>-0.004552371166540725</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="28" t="n">
-        <v>50.0460883623922</v>
+        <v>49.97831737646933</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>0.7633600223907022</v>
+        <v>0.7456526247258566</v>
       </c>
       <c r="I18" s="26" t="n">
-        <v>0.0007177627104955064</v>
+        <v>0.0005382878080617548</v>
       </c>
       <c r="J18" s="26" t="n">
-        <v>0.002606749802492869</v>
+        <v>0.002426936117450929</v>
       </c>
     </row>
     <row r="19">
@@ -1721,22 +1721,22 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.006739178085651609</v>
+        <v>-0.006621011774235575</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>2</v>
       </c>
       <c r="G20" s="28" t="n">
-        <v>42.33075771069067</v>
+        <v>42.37844791946197</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>-1.185861127811172</v>
+        <v>-1.174337755058386</v>
       </c>
       <c r="I20" s="26" t="n">
-        <v>-0.01141446437262328</v>
+        <v>-0.01129685427093907</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>-0.01304042028354058</v>
+        <v>-0.01292300361867404</v>
       </c>
     </row>
     <row r="21">
@@ -1754,22 +1754,22 @@
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>-0.007745252725428697</v>
+        <v>-0.008006315977894363</v>
       </c>
       <c r="F21" s="34" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>42.03041121598466</v>
+        <v>41.94979478135864</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>-1.911194394984128</v>
+        <v>-1.936495511209113</v>
       </c>
       <c r="I21" s="33" t="n">
-        <v>-0.02204305494080361</v>
+        <v>-0.02230035642668704</v>
       </c>
       <c r="J21" s="33" t="n">
-        <v>-0.04872354361377162</v>
+        <v>-0.04897382543543116</v>
       </c>
     </row>
     <row r="22">
@@ -1787,22 +1787,22 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>-0.009343971712462262</v>
+        <v>-0.009534706580738517</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G22" s="28" t="n">
-        <v>45.41830871370646</v>
+        <v>45.3425445112604</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>0.2319146171392283</v>
+        <v>0.2130033586920765</v>
       </c>
       <c r="I22" s="26" t="n">
-        <v>-0.01404437052678953</v>
+        <v>-0.0142342004089524</v>
       </c>
       <c r="J22" s="26" t="n">
-        <v>-0.0172152825748153</v>
+        <v>-0.0174045019489163</v>
       </c>
     </row>
     <row r="23">
@@ -1820,22 +1820,22 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>-0.01368327349095233</v>
+        <v>-0.0137693503970896</v>
       </c>
       <c r="F23" s="34" t="n">
         <v>3</v>
       </c>
       <c r="G23" s="35" t="n">
-        <v>48.05141437193593</v>
+        <v>48.01095166648066</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>0.6532232619636202</v>
+        <v>0.6446159632309101</v>
       </c>
       <c r="I23" s="33" t="n">
-        <v>-0.007017826818954909</v>
+        <v>-0.00710448542568809</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>-0.005121496124307234</v>
+        <v>-0.005208320225830065</v>
       </c>
     </row>
     <row r="24">
@@ -1853,22 +1853,22 @@
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>-0.02502183355201748</v>
+        <v>-0.02519680456298767</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G24" s="28" t="n">
-        <v>44.78249044535038</v>
+        <v>44.72210407835785</v>
       </c>
       <c r="H24" s="29" t="n">
-        <v>0.7811225631442209</v>
+        <v>0.7634007231370532</v>
       </c>
       <c r="I24" s="26" t="n">
-        <v>-0.0198193371472255</v>
+        <v>-0.01999524180582679</v>
       </c>
       <c r="J24" s="26" t="n">
-        <v>0.008932949370805243</v>
+        <v>0.008751884784717445</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="I30" s="33" t="n">
-        <v>-0.007745252725428697</v>
+        <v>-0.008006315977894363</v>
       </c>
       <c r="J30" s="34" t="n">
         <v>1</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="L30" s="35" t="n">
-        <v>42.03041121598466</v>
+        <v>41.94979478135864</v>
       </c>
     </row>
     <row r="31">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>-0.006739178085651609</v>
+        <v>-0.006621011774235575</v>
       </c>
       <c r="J31" s="27" t="n">
         <v>2</v>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="L31" s="28" t="n">
-        <v>42.33075771069067</v>
+        <v>42.37844791946197</v>
       </c>
     </row>
     <row r="32">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="C32" s="33" t="n">
-        <v>0.06281157838618334</v>
+        <v>0.06181454656683427</v>
       </c>
       <c r="D32" s="34" t="n">
         <v>9</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="F32" s="35" t="n">
-        <v>55.88489331573219</v>
+        <v>55.76913742500214</v>
       </c>
       <c r="H32" s="31" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="H34" s="31" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I34" s="33" t="n">
-        <v>-0.004459333403163956</v>
+        <v>-0.004552371166540725</v>
       </c>
       <c r="J34" s="34" t="n">
         <v>2</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="L34" s="35" t="n">
-        <v>45.94367785704903</v>
+        <v>49.97831737646933</v>
       </c>
     </row>
     <row r="35">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="H35" s="24" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>-0.0007967185788519959</v>
+        <v>-0.004526861571173213</v>
       </c>
       <c r="J35" s="27" t="n">
         <v>2</v>
@@ -2212,17 +2212,17 @@
         </is>
       </c>
       <c r="L35" s="28" t="n">
-        <v>39.81401726539807</v>
+        <v>45.91187219850499</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C36" s="33" t="n">
-        <v>0.003150343559036095</v>
+        <v>0.01108334548129264</v>
       </c>
       <c r="D36" s="34" t="n">
         <v>9</v>
@@ -2233,15 +2233,15 @@
         </is>
       </c>
       <c r="F36" s="35" t="n">
-        <v>56.207320537553</v>
+        <v>66.19848629337565</v>
       </c>
       <c r="H36" s="31" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="I36" s="33" t="n">
-        <v>0.0297848668452132</v>
+        <v>-0.0006828768287838738</v>
       </c>
       <c r="J36" s="34" t="n">
         <v>2</v>
@@ -2252,20 +2252,20 @@
         </is>
       </c>
       <c r="L36" s="35" t="n">
-        <v>45.33346661314823</v>
+        <v>39.86747270631402</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C37" s="26" t="n">
-        <v>0.03744695378055884</v>
+        <v>0.003150343559036095</v>
       </c>
       <c r="D37" s="27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
@@ -2273,18 +2273,18 @@
         </is>
       </c>
       <c r="F37" s="28" t="n">
-        <v>52.24195279097528</v>
+        <v>56.207320537553</v>
       </c>
       <c r="H37" s="24" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>-0.02502183355201748</v>
+        <v>0.0297848668452132</v>
       </c>
       <c r="J37" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="23" t="inlineStr">
         <is>
@@ -2292,17 +2292,17 @@
         </is>
       </c>
       <c r="L37" s="28" t="n">
-        <v>44.78249044535038</v>
+        <v>45.33346661314823</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C38" s="33" t="n">
-        <v>0.01783869829554785</v>
+        <v>0.03744695378055884</v>
       </c>
       <c r="D38" s="34" t="n">
         <v>8</v>
@@ -2313,15 +2313,15 @@
         </is>
       </c>
       <c r="F38" s="35" t="n">
-        <v>65.0245878859218</v>
+        <v>52.24195279097528</v>
       </c>
       <c r="H38" s="31" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="I38" s="33" t="n">
-        <v>-0.02311706956328952</v>
+        <v>-0.02519680456298767</v>
       </c>
       <c r="J38" s="34" t="n">
         <v>3</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="L38" s="35" t="n">
-        <v>51.29456085708777</v>
+        <v>44.72210407835785</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I44" s="33" t="n">
-        <v>-0.02502183355201748</v>
+        <v>-0.02519680456298767</v>
       </c>
       <c r="J44" s="34" t="n">
         <v>3</v>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="L44" s="35" t="n">
-        <v>44.78249044535038</v>
+        <v>44.72210407835785</v>
       </c>
     </row>
     <row r="45">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="C46" s="33" t="n">
-        <v>0.06281157838618334</v>
+        <v>0.06181454656683427</v>
       </c>
       <c r="D46" s="34" t="n">
         <v>9</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="F46" s="35" t="n">
-        <v>55.88489331573219</v>
+        <v>55.76913742500214</v>
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="C49" s="26" t="n">
-        <v>0.05192704664625403</v>
+        <v>0.05107433429498753</v>
       </c>
       <c r="D49" s="27" t="n">
         <v>6</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F49" s="28" t="n">
-        <v>48.67183074907373</v>
+        <v>48.62192842970096</v>
       </c>
       <c r="H49" s="24" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="I49" s="26" t="n">
-        <v>-0.01368327349095233</v>
+        <v>-0.0137693503970896</v>
       </c>
       <c r="J49" s="27" t="n">
         <v>3</v>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L49" s="28" t="n">
-        <v>48.05141437193593</v>
+        <v>48.01095166648066</v>
       </c>
     </row>
     <row r="50">
@@ -2748,7 +2748,7 @@
         <v>-0.01150690386138653</v>
       </c>
       <c r="J51" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K51" s="23" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="I52" s="33" t="n">
-        <v>-0.009343971712462262</v>
+        <v>-0.009534706580738517</v>
       </c>
       <c r="J52" s="34" t="n">
         <v>3</v>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L52" s="35" t="n">
-        <v>45.41830871370646</v>
+        <v>45.3425445112604</v>
       </c>
     </row>
   </sheetData>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 8 Sep 2026, 08:02 PM · Yahoo Finance data</t>
+          <t>Built 8 Sep 2026, 10:43 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="AC3" s="46" t="inlineStr">
         <is>
-          <t>5.4 / 9</t>
+          <t>5.5 / 9</t>
         </is>
       </c>
       <c r="AE3" s="47" t="inlineStr">
         <is>
-          <t>21 of 40</t>
+          <t>22 of 40</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -3620,10 +3620,10 @@
         <v>174.2700042724609</v>
       </c>
       <c r="W7" s="73" t="n">
-        <v>5949174</v>
+        <v>6185829</v>
       </c>
       <c r="X7" s="74" t="n">
-        <v>0.923215127336724</v>
+        <v>0.9581806777989758</v>
       </c>
       <c r="Y7" s="28" t="n">
         <v>37.09729108830635</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>-0.02502183355201748</v>
+        <v>-0.02519680456298767</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>11</v>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="R8" s="81" t="n">
-        <v>167.1600036621094</v>
+        <v>167.1300048828125</v>
       </c>
       <c r="S8" s="82" t="n">
-        <v>-4.289993286132812</v>
+        <v>-4.319992065429688</v>
       </c>
       <c r="T8" s="83" t="n">
         <v>168.2899932861328</v>
@@ -3810,61 +3810,61 @@
         <v>166.9349975585938</v>
       </c>
       <c r="W8" s="84" t="n">
-        <v>10415966</v>
+        <v>10776391</v>
       </c>
       <c r="X8" s="85" t="n">
-        <v>1.378836899887444</v>
+        <v>1.423153888164355</v>
       </c>
       <c r="Y8" s="35" t="n">
-        <v>44.78249044535038</v>
+        <v>44.72210407835785</v>
       </c>
       <c r="Z8" s="35" t="n">
-        <v>2.328048676520273</v>
+        <v>2.017663236533914</v>
       </c>
       <c r="AA8" s="35" t="n">
         <v>25.49629080616576</v>
       </c>
       <c r="AB8" s="86" t="n">
-        <v>1.639045903626254</v>
+        <v>1.636652838611127</v>
       </c>
       <c r="AC8" s="86" t="n">
-        <v>2.416443405132549</v>
+        <v>2.415964792129524</v>
       </c>
       <c r="AD8" s="86" t="n">
-        <v>-0.7773975015062953</v>
+        <v>-0.779311953518397</v>
       </c>
       <c r="AE8" s="83" t="n">
-        <v>171.0317713413937</v>
+        <v>171.0251049459944</v>
       </c>
       <c r="AF8" s="83" t="n">
-        <v>170.1947375429226</v>
+        <v>170.1920103811683</v>
       </c>
       <c r="AG8" s="83" t="n">
-        <v>165.8643994140625</v>
+        <v>165.8637994384766</v>
       </c>
       <c r="AH8" s="83" t="n">
-        <v>157.1923999023437</v>
+        <v>157.1920999145508</v>
       </c>
       <c r="AI8" s="83" t="n">
-        <v>155.4477499389648</v>
+        <v>155.4475999450684</v>
       </c>
       <c r="AJ8" s="83" t="n">
-        <v>176.7599479193007</v>
+        <v>176.7629124122553</v>
       </c>
       <c r="AK8" s="83" t="n">
-        <v>171.2484977722168</v>
+        <v>171.246997833252</v>
       </c>
       <c r="AL8" s="83" t="n">
-        <v>165.7370476251329</v>
+        <v>165.7310832542486</v>
       </c>
       <c r="AM8" s="87" t="n">
-        <v>0.1290908925057894</v>
+        <v>0.1268077676446398</v>
       </c>
       <c r="AN8" s="36" t="n">
-        <v>6.436786563132175</v>
+        <v>6.442056968933639</v>
       </c>
       <c r="AO8" s="88" t="n">
-        <v>1.643301999378363</v>
+        <v>1.643596961698456</v>
       </c>
       <c r="AP8" s="83" t="n">
         <v>176.6000061035156</v>
@@ -3873,22 +3873,22 @@
         <v>133.7299957275391</v>
       </c>
       <c r="AR8" s="36" t="n">
-        <v>-5.345414561238981</v>
+        <v>-5.362401411895878</v>
       </c>
       <c r="AS8" s="89" t="n">
-        <v>77.97993898621442</v>
+        <v>77.90996284430594</v>
       </c>
       <c r="AT8" s="33" t="n">
-        <v>-0.0198193371472255</v>
+        <v>-0.01999524180582679</v>
       </c>
       <c r="AU8" s="33" t="n">
-        <v>0.008932949370805243</v>
+        <v>0.008751884784717445</v>
       </c>
       <c r="AV8" s="33" t="n">
-        <v>0.09505411297601873</v>
+        <v>0.09485759295966534</v>
       </c>
       <c r="AW8" s="33" t="n">
-        <v>0.07984496360907012</v>
+        <v>0.0796511730489573</v>
       </c>
       <c r="AX8" s="90" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="C9" s="26" t="n">
-        <v>-0.01368327349095233</v>
+        <v>-0.0137693503970896</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>10</v>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="R9" s="70" t="n">
-        <v>57.30500030517578</v>
+        <v>57.29999923706055</v>
       </c>
       <c r="S9" s="71" t="n">
-        <v>-0.7949981689453125</v>
+        <v>-0.7999992370605469</v>
       </c>
       <c r="T9" s="72" t="n">
         <v>57.70500183105469</v>
@@ -4000,61 +4000,61 @@
         <v>57.2599983215332</v>
       </c>
       <c r="W9" s="73" t="n">
-        <v>35700282</v>
+        <v>38063059</v>
       </c>
       <c r="X9" s="74" t="n">
-        <v>1.265114208027167</v>
+        <v>1.343220765722555</v>
       </c>
       <c r="Y9" s="28" t="n">
-        <v>48.05141437193593</v>
+        <v>48.01095166648066</v>
       </c>
       <c r="Z9" s="28" t="n">
-        <v>23.37282714441463</v>
+        <v>23.07690571369884</v>
       </c>
       <c r="AA9" s="28" t="n">
         <v>18.46505946477791</v>
       </c>
       <c r="AB9" s="75" t="n">
-        <v>0.2584065141210914</v>
+        <v>0.2580075685164616</v>
       </c>
       <c r="AC9" s="75" t="n">
-        <v>0.3678833062969867</v>
+        <v>0.3678035171760607</v>
       </c>
       <c r="AD9" s="75" t="n">
-        <v>-0.1094767921758953</v>
+        <v>-0.1097959486595992</v>
       </c>
       <c r="AE9" s="72" t="n">
-        <v>57.80986284406844</v>
+        <v>57.80875149559839</v>
       </c>
       <c r="AF9" s="72" t="n">
-        <v>57.67835174851741</v>
+        <v>57.67789710596148</v>
       </c>
       <c r="AG9" s="72" t="n">
-        <v>56.93310005187988</v>
+        <v>56.93300003051758</v>
       </c>
       <c r="AH9" s="72" t="n">
-        <v>54.54054996490478</v>
+        <v>54.54049995422363</v>
       </c>
       <c r="AI9" s="72" t="n">
-        <v>53.51737503051758</v>
+        <v>53.517350025177</v>
       </c>
       <c r="AJ9" s="72" t="n">
-        <v>58.65700297946822</v>
+        <v>58.6574080107208</v>
       </c>
       <c r="AK9" s="72" t="n">
-        <v>57.83874988555908</v>
+        <v>57.83849983215332</v>
       </c>
       <c r="AL9" s="72" t="n">
-        <v>57.02049679164994</v>
+        <v>57.01959165358583</v>
       </c>
       <c r="AM9" s="76" t="n">
-        <v>0.1738481135260042</v>
+        <v>0.1712081957498762</v>
       </c>
       <c r="AN9" s="29" t="n">
-        <v>2.82942869798588</v>
+        <v>2.831706150553508</v>
       </c>
       <c r="AO9" s="77" t="n">
-        <v>1.174982680027602</v>
+        <v>1.175085230961202</v>
       </c>
       <c r="AP9" s="72" t="n">
         <v>58.59999847412109</v>
@@ -4063,22 +4063,22 @@
         <v>47.66999816894531</v>
       </c>
       <c r="AR9" s="29" t="n">
-        <v>-2.209894543797997</v>
+        <v>-2.218428789950655</v>
       </c>
       <c r="AS9" s="78" t="n">
-        <v>88.15189265518977</v>
+        <v>88.10613722997842</v>
       </c>
       <c r="AT9" s="26" t="n">
-        <v>-0.007017826818954909</v>
+        <v>-0.00710448542568809</v>
       </c>
       <c r="AU9" s="26" t="n">
-        <v>-0.005121496124307234</v>
+        <v>-0.005208320225830065</v>
       </c>
       <c r="AV9" s="26" t="n">
-        <v>0.1026553580750613</v>
+        <v>0.1025591281732379</v>
       </c>
       <c r="AW9" s="26" t="n">
-        <v>0.0462844591240601</v>
+        <v>0.04619314877033642</v>
       </c>
       <c r="AX9" s="79" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>0.01100533652705571</v>
+        <v>0.01108334548129264</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>1</v>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
           <t>Same</t>
         </is>
       </c>
-      <c r="G10" s="30" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
       <c r="H10" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="N10" s="80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O10" s="30" t="inlineStr">
         <is>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="R10" s="81" t="n">
-        <v>64.76499938964844</v>
+        <v>64.76999664306641</v>
       </c>
       <c r="S10" s="82" t="n">
-        <v>0.7050018310546875</v>
+        <v>0.7099990844726562</v>
       </c>
       <c r="T10" s="83" t="n">
         <v>64.83000183105469</v>
@@ -4190,61 +4190,61 @@
         <v>64.31199645996094</v>
       </c>
       <c r="W10" s="84" t="n">
-        <v>26177295</v>
+        <v>27876575</v>
       </c>
       <c r="X10" s="85" t="n">
-        <v>1.033999515277455</v>
+        <v>1.097437765384704</v>
       </c>
       <c r="Y10" s="35" t="n">
-        <v>66.17874588140691</v>
+        <v>66.19848629337565</v>
       </c>
       <c r="Z10" s="35" t="n">
-        <v>82.06655340355647</v>
+        <v>82.18525314305131</v>
       </c>
       <c r="AA10" s="35" t="n">
         <v>27.84150329734461</v>
       </c>
       <c r="AB10" s="86" t="n">
-        <v>1.425053564059759</v>
+        <v>1.425452205358056</v>
       </c>
       <c r="AC10" s="86" t="n">
-        <v>1.424654896439632</v>
+        <v>1.424734624699291</v>
       </c>
       <c r="AD10" s="86" t="n">
-        <v>0.0003986676201273021</v>
+        <v>0.0007175806587649269</v>
       </c>
       <c r="AE10" s="83" t="n">
-        <v>64.11422698418846</v>
+        <v>64.11533748494801</v>
       </c>
       <c r="AF10" s="83" t="n">
-        <v>62.76978139535805</v>
+        <v>62.77023569112333</v>
       </c>
       <c r="AG10" s="83" t="n">
-        <v>59.42150024414062</v>
+        <v>59.42160018920899</v>
       </c>
       <c r="AH10" s="83" t="n">
-        <v>58.30155010223389</v>
+        <v>58.30160007476807</v>
       </c>
       <c r="AI10" s="83" t="n">
-        <v>54.92702491760254</v>
+        <v>54.92704990386963</v>
       </c>
       <c r="AJ10" s="83" t="n">
-        <v>65.63080728586772</v>
+        <v>65.63171549782244</v>
       </c>
       <c r="AK10" s="83" t="n">
-        <v>63.10025005340576</v>
+        <v>63.10049991607666</v>
       </c>
       <c r="AL10" s="83" t="n">
-        <v>60.56969282094381</v>
+        <v>60.56928433433087</v>
       </c>
       <c r="AM10" s="87" t="n">
-        <v>0.828929398412194</v>
+        <v>0.8297816154083356</v>
       </c>
       <c r="AN10" s="36" t="n">
-        <v>8.020751836387918</v>
+        <v>8.0228067451519</v>
       </c>
       <c r="AO10" s="88" t="n">
-        <v>1.811089167517567</v>
+        <v>1.810949435048805</v>
       </c>
       <c r="AP10" s="83" t="n">
         <v>65.51999664306641</v>
@@ -4253,36 +4253,36 @@
         <v>42.34999847412109</v>
       </c>
       <c r="AR10" s="36" t="n">
-        <v>-1.152315769384071</v>
+        <v>-1.14468870333706</v>
       </c>
       <c r="AS10" s="89" t="n">
-        <v>96.74148764314583</v>
+        <v>96.76305541963649</v>
       </c>
       <c r="AT10" s="33" t="n">
-        <v>0.01258599619603817</v>
+        <v>0.01266412711363518</v>
       </c>
       <c r="AU10" s="33" t="n">
-        <v>0.1263478154721467</v>
+        <v>0.1264347242272419</v>
       </c>
       <c r="AV10" s="33" t="n">
-        <v>0.1103205444298097</v>
+        <v>0.1104062165241195</v>
       </c>
       <c r="AW10" s="33" t="n">
-        <v>0.4485573857267353</v>
+        <v>0.4486691561029441</v>
       </c>
       <c r="AX10" s="90" t="inlineStr">
         <is>
+          <t>Sector Update: Energy Stocks Gain Late Afternoon</t>
+        </is>
+      </c>
+      <c r="AY10" s="90" t="inlineStr">
+        <is>
           <t>Sector Update: Energy</t>
         </is>
       </c>
-      <c r="AY10" s="90" t="inlineStr">
+      <c r="AZ10" s="90" t="inlineStr">
         <is>
           <t>Blowout jobs report raises worries of Fed rate hike: AlphaCheck</t>
-        </is>
-      </c>
-      <c r="AZ10" s="90" t="inlineStr">
-        <is>
-          <t>Bond yields still high as investors weigh rate hike risk: AlphaCheck</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>-0.006739178085651609</v>
+        <v>-0.006621011774235575</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>7</v>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="R11" s="70" t="n">
-        <v>84.01000213623047</v>
+        <v>84.01999664306641</v>
       </c>
       <c r="S11" s="71" t="n">
-        <v>-0.5699996948242188</v>
+        <v>-0.5600051879882812</v>
       </c>
       <c r="T11" s="72" t="n">
         <v>84.27999877929688</v>
@@ -4380,61 +4380,61 @@
         <v>83.80999755859375</v>
       </c>
       <c r="W11" s="73" t="n">
-        <v>12346694</v>
+        <v>13529156</v>
       </c>
       <c r="X11" s="74" t="n">
-        <v>1.354485166758239</v>
+        <v>1.474641698026466</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>42.33075771069067</v>
+        <v>42.37844791946197</v>
       </c>
       <c r="Z11" s="28" t="n">
-        <v>5.464600478608533</v>
+        <v>5.73767416264352</v>
       </c>
       <c r="AA11" s="28" t="n">
         <v>12.87555988659817</v>
       </c>
       <c r="AB11" s="75" t="n">
-        <v>-0.1007477601409761</v>
+        <v>-0.09995047754436825</v>
       </c>
       <c r="AC11" s="75" t="n">
-        <v>0.11973289205469</v>
+        <v>0.1198923485740115</v>
       </c>
       <c r="AD11" s="75" t="n">
-        <v>-0.220480652195666</v>
+        <v>-0.2198428261183798</v>
       </c>
       <c r="AE11" s="72" t="n">
-        <v>84.99988485064777</v>
+        <v>85.00210585216688</v>
       </c>
       <c r="AF11" s="72" t="n">
-        <v>85.29253610625362</v>
+        <v>85.29344469778415</v>
       </c>
       <c r="AG11" s="72" t="n">
-        <v>85.0181999206543</v>
+        <v>85.01839981079101</v>
       </c>
       <c r="AH11" s="72" t="n">
-        <v>84.41630012512206</v>
+        <v>84.41640007019043</v>
       </c>
       <c r="AI11" s="72" t="n">
-        <v>83.36030025482178</v>
+        <v>83.36035022735595</v>
       </c>
       <c r="AJ11" s="72" t="n">
-        <v>87.1005302755715</v>
+        <v>87.09913133087643</v>
       </c>
       <c r="AK11" s="72" t="n">
-        <v>85.51749992370605</v>
+        <v>85.51799964904785</v>
       </c>
       <c r="AL11" s="72" t="n">
-        <v>83.93446957184061</v>
+        <v>83.93686796721927</v>
       </c>
       <c r="AM11" s="76" t="n">
-        <v>0.02385695394306634</v>
+        <v>0.02628771430061936</v>
       </c>
       <c r="AN11" s="29" t="n">
-        <v>3.702237210577338</v>
+        <v>3.697775177897732</v>
       </c>
       <c r="AO11" s="77" t="n">
-        <v>1.279588493694595</v>
+        <v>1.279436281644388</v>
       </c>
       <c r="AP11" s="72" t="n">
         <v>90.13999938964844</v>
@@ -4443,22 +4443,22 @@
         <v>75.16000366210938</v>
       </c>
       <c r="AR11" s="29" t="n">
-        <v>-6.800529504021635</v>
+        <v>-6.789441743977697</v>
       </c>
       <c r="AS11" s="78" t="n">
-        <v>59.07877835940468</v>
+        <v>59.14549738267893</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>-0.01141446437262328</v>
+        <v>-0.01129685427093907</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>-0.01304042028354058</v>
+        <v>-0.01292300361867404</v>
       </c>
       <c r="AV11" s="26" t="n">
-        <v>0.01131578722594861</v>
+        <v>0.0114361015015314</v>
       </c>
       <c r="AW11" s="26" t="n">
-        <v>0.08148817979127787</v>
+        <v>0.08161684234015376</v>
       </c>
       <c r="AX11" s="79" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>-0.007745252725428697</v>
+        <v>-0.008006315977894363</v>
       </c>
       <c r="D12" s="34" t="n">
         <v>8</v>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="R12" s="81" t="n">
-        <v>114.0199966430664</v>
+        <v>113.9899978637695</v>
       </c>
       <c r="S12" s="82" t="n">
-        <v>-0.8900070190429688</v>
+        <v>-0.9200057983398438</v>
       </c>
       <c r="T12" s="83" t="n">
         <v>114.4700012207031</v>
@@ -4570,61 +4570,61 @@
         <v>113.75</v>
       </c>
       <c r="W12" s="84" t="n">
-        <v>6525252</v>
+        <v>7811077</v>
       </c>
       <c r="X12" s="85" t="n">
-        <v>1.276748061804977</v>
+        <v>1.50934927929379</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>42.03041121598466</v>
+        <v>41.94979478135864</v>
       </c>
       <c r="Z12" s="35" t="n">
-        <v>5.084684881435419</v>
+        <v>4.519735859032862</v>
       </c>
       <c r="AA12" s="35" t="n">
         <v>11.84696289897842</v>
       </c>
       <c r="AB12" s="86" t="n">
-        <v>-0.4180060848270131</v>
+        <v>-0.4203991498421402</v>
       </c>
       <c r="AC12" s="86" t="n">
-        <v>-0.01328083163369766</v>
+        <v>-0.01375944463672309</v>
       </c>
       <c r="AD12" s="86" t="n">
-        <v>-0.4047252531933154</v>
+        <v>-0.4066397052054171</v>
       </c>
       <c r="AE12" s="83" t="n">
-        <v>115.5151183888538</v>
+        <v>115.5084519934544</v>
       </c>
       <c r="AF12" s="83" t="n">
-        <v>116.2643500443745</v>
+        <v>116.2616228826202</v>
       </c>
       <c r="AG12" s="83" t="n">
-        <v>116.2415995788574</v>
+        <v>116.2409996032715</v>
       </c>
       <c r="AH12" s="83" t="n">
-        <v>116.9485998535156</v>
+        <v>116.9482998657227</v>
       </c>
       <c r="AI12" s="83" t="n">
-        <v>116.9775249099731</v>
+        <v>116.9773749160767</v>
       </c>
       <c r="AJ12" s="83" t="n">
-        <v>119.7805320092117</v>
+        <v>119.785077054902</v>
       </c>
       <c r="AK12" s="83" t="n">
-        <v>116.9054988861084</v>
+        <v>116.9039989471435</v>
       </c>
       <c r="AL12" s="83" t="n">
-        <v>114.0304657630052</v>
+        <v>114.0229208393851</v>
       </c>
       <c r="AM12" s="87" t="n">
-        <v>-0.001820695534708708</v>
+        <v>-0.005713655510921202</v>
       </c>
       <c r="AN12" s="36" t="n">
-        <v>4.918559264528974</v>
+        <v>4.928964164965954</v>
       </c>
       <c r="AO12" s="88" t="n">
-        <v>1.424836852364758</v>
+        <v>1.425211827073672</v>
       </c>
       <c r="AP12" s="83" t="n">
         <v>125.0100021362305</v>
@@ -4633,22 +4633,22 @@
         <v>105.1900024414062</v>
       </c>
       <c r="AR12" s="36" t="n">
-        <v>-8.791300940214075</v>
+        <v>-8.815298043473208</v>
       </c>
       <c r="AS12" s="89" t="n">
-        <v>44.55093005862162</v>
+        <v>44.39957395489419</v>
       </c>
       <c r="AT12" s="33" t="n">
-        <v>-0.02204305494080361</v>
+        <v>-0.02230035642668704</v>
       </c>
       <c r="AU12" s="33" t="n">
-        <v>-0.04872354361377162</v>
+        <v>-0.04897382543543116</v>
       </c>
       <c r="AV12" s="33" t="n">
-        <v>-0.01187280313570171</v>
+        <v>-0.01213278042537624</v>
       </c>
       <c r="AW12" s="33" t="n">
-        <v>-0.04513865550406393</v>
+        <v>-0.0453898805135009</v>
       </c>
       <c r="AX12" s="90" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>-0.004373809418090291</v>
+        <v>-0.004552371166540725</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>5</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="N13" s="69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O13" s="23" t="inlineStr">
         <is>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="R13" s="70" t="n">
-        <v>111.5400009155273</v>
+        <v>111.5199966430664</v>
       </c>
       <c r="S13" s="71" t="n">
-        <v>-0.4899978637695312</v>
+        <v>-0.5100021362304688</v>
       </c>
       <c r="T13" s="72" t="n">
         <v>111.5899963378906</v>
@@ -4760,61 +4760,61 @@
         <v>110.9649963378906</v>
       </c>
       <c r="W13" s="73" t="n">
-        <v>4982154</v>
+        <v>5655285</v>
       </c>
       <c r="X13" s="74" t="n">
-        <v>1.238270563796091</v>
+        <v>1.393911231801117</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>50.0460883623922</v>
+        <v>49.97831737646933</v>
       </c>
       <c r="Z13" s="28" t="n">
-        <v>31.93070849487565</v>
+        <v>31.43555334815148</v>
       </c>
       <c r="AA13" s="28" t="n">
         <v>13.13904941230394</v>
       </c>
       <c r="AB13" s="75" t="n">
-        <v>0.4027184257243022</v>
+        <v>0.4011226433057686</v>
       </c>
       <c r="AC13" s="75" t="n">
-        <v>0.4474488952950639</v>
+        <v>0.4471297388113572</v>
       </c>
       <c r="AD13" s="75" t="n">
-        <v>-0.04473046957076171</v>
+        <v>-0.04600709550558857</v>
       </c>
       <c r="AE13" s="72" t="n">
-        <v>112.0317307051708</v>
+        <v>112.0272853112906</v>
       </c>
       <c r="AF13" s="72" t="n">
-        <v>111.6796184425315</v>
+        <v>111.6777998723077</v>
       </c>
       <c r="AG13" s="72" t="n">
-        <v>110.6949995422363</v>
+        <v>110.6945994567871</v>
       </c>
       <c r="AH13" s="72" t="n">
-        <v>112.4790998840332</v>
+        <v>112.4788998413086</v>
       </c>
       <c r="AI13" s="72" t="n">
-        <v>114.0217999649048</v>
+        <v>114.0216999435425</v>
       </c>
       <c r="AJ13" s="72" t="n">
-        <v>113.6536239281415</v>
+        <v>113.6532003749035</v>
       </c>
       <c r="AK13" s="72" t="n">
-        <v>111.7979995727539</v>
+        <v>111.7969993591309</v>
       </c>
       <c r="AL13" s="72" t="n">
-        <v>109.9423752173663</v>
+        <v>109.9407983433583</v>
       </c>
       <c r="AM13" s="76" t="n">
-        <v>0.4304819813133256</v>
+        <v>0.4253845047732718</v>
       </c>
       <c r="AN13" s="29" t="n">
-        <v>3.319602072450357</v>
+        <v>3.320663392422275</v>
       </c>
       <c r="AO13" s="77" t="n">
-        <v>1.482865681273606</v>
+        <v>1.483131675265752</v>
       </c>
       <c r="AP13" s="72" t="n">
         <v>120.4049987792969</v>
@@ -4823,22 +4823,22 @@
         <v>105.0299987792969</v>
       </c>
       <c r="AR13" s="29" t="n">
-        <v>-7.36264935313784</v>
+        <v>-7.379263507586376</v>
       </c>
       <c r="AS13" s="78" t="n">
-        <v>42.34147730881605</v>
+        <v>42.21136821963923</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>0.0007177627104955064</v>
+        <v>0.0005382878080617548</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>0.002606749802492869</v>
+        <v>0.002426936117450929</v>
       </c>
       <c r="AV13" s="26" t="n">
-        <v>0.004050810986328424</v>
+        <v>0.003870738314437405</v>
       </c>
       <c r="AW13" s="26" t="n">
-        <v>-0.05249745362803238</v>
+        <v>-0.05266738458499387</v>
       </c>
       <c r="AX13" s="79" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C14" s="33" t="n">
-        <v>-0.009343971712462262</v>
+        <v>-0.009534706580738517</v>
       </c>
       <c r="D14" s="34" t="n">
         <v>9</v>
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="R14" s="81" t="n">
-        <v>51.95000076293945</v>
+        <v>51.93999862670898</v>
       </c>
       <c r="S14" s="82" t="n">
-        <v>-0.4899978637695312</v>
+        <v>-0.5</v>
       </c>
       <c r="T14" s="83" t="n">
         <v>52.36000061035156</v>
@@ -4950,61 +4950,61 @@
         <v>51.93500137329102</v>
       </c>
       <c r="W14" s="84" t="n">
-        <v>11452863</v>
+        <v>11931041</v>
       </c>
       <c r="X14" s="85" t="n">
-        <v>1.061074331944015</v>
+        <v>1.102933032370742</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>45.41830871370646</v>
+        <v>45.3425445112604</v>
       </c>
       <c r="Z14" s="35" t="n">
-        <v>0.6651622136436071</v>
+        <v>0.2216079602932668</v>
       </c>
       <c r="AA14" s="35" t="n">
         <v>14.50877910679219</v>
       </c>
       <c r="AB14" s="86" t="n">
-        <v>0.1496393737477248</v>
+        <v>0.1488414825384581</v>
       </c>
       <c r="AC14" s="86" t="n">
-        <v>0.3131854786829287</v>
+        <v>0.3130259004410754</v>
       </c>
       <c r="AD14" s="86" t="n">
-        <v>-0.1635461049352038</v>
+        <v>-0.1641844179026173</v>
       </c>
       <c r="AE14" s="83" t="n">
-        <v>52.55559031552365</v>
+        <v>52.55336761858355</v>
       </c>
       <c r="AF14" s="83" t="n">
-        <v>52.5578155659165</v>
+        <v>52.55690628080464</v>
       </c>
       <c r="AG14" s="83" t="n">
-        <v>51.82979988098145</v>
+        <v>51.82959983825683</v>
       </c>
       <c r="AH14" s="83" t="n">
-        <v>51.57810001373291</v>
+        <v>51.57799999237061</v>
       </c>
       <c r="AI14" s="83" t="n">
-        <v>50.11670000076294</v>
+        <v>50.11664999008179</v>
       </c>
       <c r="AJ14" s="83" t="n">
-        <v>53.88709838608983</v>
+        <v>53.88803275778218</v>
       </c>
       <c r="AK14" s="83" t="n">
-        <v>52.75650024414062</v>
+        <v>52.7560001373291</v>
       </c>
       <c r="AL14" s="83" t="n">
-        <v>51.62590210219142</v>
+        <v>51.62396751687603</v>
       </c>
       <c r="AM14" s="87" t="n">
-        <v>0.1433306179812365</v>
+        <v>0.1395856904311072</v>
       </c>
       <c r="AN14" s="36" t="n">
-        <v>4.286099861503896</v>
+        <v>4.291578654584431</v>
       </c>
       <c r="AO14" s="88" t="n">
-        <v>1.595094859565964</v>
+        <v>1.595402028539928</v>
       </c>
       <c r="AP14" s="83" t="n">
         <v>54.18999862670898</v>
@@ -5013,22 +5013,22 @@
         <v>42.03499984741211</v>
       </c>
       <c r="AR14" s="36" t="n">
-        <v>-4.133600148617623</v>
+        <v>-4.15205768042044</v>
       </c>
       <c r="AS14" s="89" t="n">
-        <v>81.57138553082515</v>
+        <v>81.48909727714383</v>
       </c>
       <c r="AT14" s="33" t="n">
-        <v>-0.01404437052678953</v>
+        <v>-0.0142342004089524</v>
       </c>
       <c r="AU14" s="33" t="n">
-        <v>-0.0172152825748153</v>
+        <v>-0.0174045019489163</v>
       </c>
       <c r="AV14" s="33" t="n">
-        <v>0.03983189981853474</v>
+        <v>0.03963169692794688</v>
       </c>
       <c r="AW14" s="33" t="n">
-        <v>0.1455347852455748</v>
+        <v>0.1453142309662583</v>
       </c>
       <c r="AX14" s="90" t="inlineStr">
         <is>
@@ -5140,10 +5140,10 @@
         <v>187.0200042724609</v>
       </c>
       <c r="W15" s="73" t="n">
-        <v>7886687</v>
+        <v>8376789</v>
       </c>
       <c r="X15" s="74" t="n">
-        <v>1.302504012642008</v>
+        <v>1.377869119351926</v>
       </c>
       <c r="Y15" s="28" t="n">
         <v>56.207320537553</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="C16" s="33" t="n">
-        <v>-0.0007967185788519959</v>
+        <v>-0.0006828768287838738</v>
       </c>
       <c r="D16" s="34" t="n">
         <v>4</v>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="R16" s="81" t="n">
-        <v>43.89500045776367</v>
+        <v>43.90000152587891</v>
       </c>
       <c r="S16" s="82" t="n">
-        <v>-0.03499984741210938</v>
+        <v>-0.029998779296875</v>
       </c>
       <c r="T16" s="83" t="n">
         <v>43.66500091552734</v>
@@ -5330,61 +5330,61 @@
         <v>43.66120147705078</v>
       </c>
       <c r="W16" s="84" t="n">
-        <v>4716707</v>
+        <v>4811042</v>
       </c>
       <c r="X16" s="85" t="n">
-        <v>0.9223504831401624</v>
+        <v>0.9399307075299359</v>
       </c>
       <c r="Y16" s="35" t="n">
-        <v>39.81401726539807</v>
+        <v>39.86747270631402</v>
       </c>
       <c r="Z16" s="35" t="n">
-        <v>17.36850347538719</v>
+        <v>17.63171737532977</v>
       </c>
       <c r="AA16" s="35" t="n">
         <v>16.09873250539317</v>
       </c>
       <c r="AB16" s="86" t="n">
-        <v>-0.264953969438757</v>
+        <v>-0.2645550238341272</v>
       </c>
       <c r="AC16" s="86" t="n">
-        <v>-0.152846591403284</v>
+        <v>-0.1527668022823581</v>
       </c>
       <c r="AD16" s="86" t="n">
-        <v>-0.112107378035473</v>
+        <v>-0.1117882215517692</v>
       </c>
       <c r="AE16" s="83" t="n">
-        <v>44.17683746697216</v>
+        <v>44.17794881544221</v>
       </c>
       <c r="AF16" s="83" t="n">
-        <v>44.52978563175613</v>
+        <v>44.53024027431206</v>
       </c>
       <c r="AG16" s="83" t="n">
-        <v>44.82130020141602</v>
+        <v>44.82140022277832</v>
       </c>
       <c r="AH16" s="83" t="n">
-        <v>44.54565021514892</v>
+        <v>44.54570022583007</v>
       </c>
       <c r="AI16" s="83" t="n">
-        <v>43.0836750793457</v>
+        <v>43.08370008468628</v>
       </c>
       <c r="AJ16" s="83" t="n">
-        <v>45.662080349638</v>
+        <v>45.66163291099435</v>
       </c>
       <c r="AK16" s="83" t="n">
-        <v>44.62225074768067</v>
+        <v>44.62250080108642</v>
       </c>
       <c r="AL16" s="83" t="n">
-        <v>43.58242114572334</v>
+        <v>43.5833686911785</v>
       </c>
       <c r="AM16" s="87" t="n">
-        <v>0.1503031417128099</v>
+        <v>0.1523544656552202</v>
       </c>
       <c r="AN16" s="36" t="n">
-        <v>4.660587866072071</v>
+        <v>4.657435559428015</v>
       </c>
       <c r="AO16" s="88" t="n">
-        <v>1.189080427172075</v>
+        <v>1.188944967673121</v>
       </c>
       <c r="AP16" s="83" t="n">
         <v>46.45500183105469</v>
@@ -5393,22 +5393,22 @@
         <v>39.72499847412109</v>
       </c>
       <c r="AR16" s="36" t="n">
-        <v>-5.510712027525266</v>
+        <v>-5.499946624623298</v>
       </c>
       <c r="AS16" s="89" t="n">
-        <v>61.96136558158517</v>
+        <v>62.03567562052567</v>
       </c>
       <c r="AT16" s="33" t="n">
-        <v>-0.004874181582700698</v>
+        <v>-0.004760804388276862</v>
       </c>
       <c r="AU16" s="33" t="n">
-        <v>-0.0241218118166906</v>
+        <v>-0.02401062755332628</v>
       </c>
       <c r="AV16" s="33" t="n">
-        <v>-0.003066053265408653</v>
+        <v>-0.00295247006636512</v>
       </c>
       <c r="AW16" s="33" t="n">
-        <v>0.08785631022802143</v>
+        <v>0.08798025244126451</v>
       </c>
       <c r="AX16" s="90" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -5487,11 +5487,11 @@
         </is>
       </c>
       <c r="N17" s="69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O17" s="23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="P17" s="25" t="inlineStr">
@@ -5520,10 +5520,10 @@
         <v>43.03499984741211</v>
       </c>
       <c r="W17" s="73" t="n">
-        <v>16898692</v>
+        <v>19693441</v>
       </c>
       <c r="X17" s="74" t="n">
-        <v>0.8572600883809205</v>
+        <v>0.9920038487658337</v>
       </c>
       <c r="Y17" s="28" t="n">
         <v>48.76529694830028</v>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="C19" s="26" t="n">
-        <v>-0.005440219203215357</v>
+        <v>-0.005492125910932955</v>
       </c>
       <c r="D19" s="27" t="n">
         <v>4</v>
@@ -5657,24 +5657,24 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
           <t>Same</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5696,11 +5696,11 @@
         </is>
       </c>
       <c r="N19" s="69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O19" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="P19" s="25" t="inlineStr">
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="R19" s="70" t="n">
-        <v>766</v>
+        <v>765.9600219726562</v>
       </c>
       <c r="S19" s="71" t="n">
-        <v>-4.19000244140625</v>
+        <v>-4.22998046875</v>
       </c>
       <c r="T19" s="72" t="n">
         <v>769.0700073242188</v>
@@ -5729,61 +5729,61 @@
         <v>765.1500244140625</v>
       </c>
       <c r="W19" s="73" t="n">
-        <v>33180231</v>
+        <v>43496831</v>
       </c>
       <c r="X19" s="74" t="n">
-        <v>0.9212233075687043</v>
+        <v>1.190604301859171</v>
       </c>
       <c r="Y19" s="28" t="n">
-        <v>51.40173051184327</v>
+        <v>51.36463221333177</v>
       </c>
       <c r="Z19" s="28" t="n">
-        <v>41.21375798144255</v>
+        <v>40.96105248943845</v>
       </c>
       <c r="AA19" s="28" t="n">
         <v>13.08669418896927</v>
       </c>
       <c r="AB19" s="75" t="n">
-        <v>2.700022622934398</v>
+        <v>2.69683349254808</v>
       </c>
       <c r="AC19" s="75" t="n">
-        <v>3.527417499015546</v>
+        <v>3.526779672938283</v>
       </c>
       <c r="AD19" s="75" t="n">
-        <v>-0.827394876081148</v>
+        <v>-0.8299461803902024</v>
       </c>
       <c r="AE19" s="72" t="n">
-        <v>767.7563723965673</v>
+        <v>767.7474883904908</v>
       </c>
       <c r="AF19" s="72" t="n">
-        <v>766.0049335212183</v>
+        <v>766.0012991550961</v>
       </c>
       <c r="AG19" s="72" t="n">
-        <v>757.5974011230469</v>
+        <v>757.5966015625</v>
       </c>
       <c r="AH19" s="72" t="n">
-        <v>745.9744006347656</v>
+        <v>745.9740008544921</v>
       </c>
       <c r="AI19" s="72" t="n">
-        <v>712.6825003051758</v>
+        <v>712.6823004150391</v>
       </c>
       <c r="AJ19" s="72" t="n">
-        <v>777.2434484569314</v>
+        <v>777.2439956536774</v>
       </c>
       <c r="AK19" s="72" t="n">
-        <v>768.7014923095703</v>
+        <v>768.6994934082031</v>
       </c>
       <c r="AL19" s="72" t="n">
-        <v>760.1595361622092</v>
+        <v>760.1549911627288</v>
       </c>
       <c r="AM19" s="76" t="n">
-        <v>0.3418692239244939</v>
+        <v>0.3396939132997553</v>
       </c>
       <c r="AN19" s="29" t="n">
-        <v>2.222437768839697</v>
+        <v>2.22310599102656</v>
       </c>
       <c r="AO19" s="77" t="n">
-        <v>0.8009022879495987</v>
+        <v>0.8009440897312178</v>
       </c>
       <c r="AP19" s="72" t="n">
         <v>779.3699951171875</v>
@@ -5792,22 +5792,22 @@
         <v>629.280029296875</v>
       </c>
       <c r="AR19" s="29" t="n">
-        <v>-1.715487534925841</v>
+        <v>-1.720617066161867</v>
       </c>
       <c r="AS19" s="78" t="n">
-        <v>91.09201268444951</v>
+        <v>91.06537664177654</v>
       </c>
       <c r="AT19" s="26" t="n">
-        <v>-0.001368864884529697</v>
+        <v>-0.00142098407881952</v>
       </c>
       <c r="AU19" s="26" t="n">
-        <v>-0.009388833864336976</v>
+        <v>-0.009440534491343189</v>
       </c>
       <c r="AV19" s="26" t="n">
-        <v>0.03622741586838174</v>
+        <v>0.03617333450027993</v>
       </c>
       <c r="AW19" s="26" t="n">
-        <v>0.1232989488459109</v>
+        <v>0.1232403231591064</v>
       </c>
       <c r="AX19" s="79" t="inlineStr">
         <is>
@@ -5816,12 +5816,12 @@
       </c>
       <c r="AY19" s="79" t="inlineStr">
         <is>
-          <t>5 Leveraged ETF Areas of Last Week</t>
+          <t>QQQ vs QQQM: Same Index, Same Stocks, Different Fee – and the Math Says One Leaves You Thousands Richer</t>
         </is>
       </c>
       <c r="AZ19" s="79" t="inlineStr">
         <is>
-          <t>Amgen Falls 10% as Novartis Trial Failure Clouds a Cholesterol Drug Class; NVS Stock Drops 14%</t>
+          <t>XYLD vs GPIX vs ISPY: We Compared 3 Ways to Sell Covered Calls on the S&amp;P 500, and the Highest Yield Is Not...</t>
         </is>
       </c>
     </row>
@@ -5917,10 +5917,10 @@
         <v>715.5700073242188</v>
       </c>
       <c r="W20" s="84" t="n">
-        <v>26307263</v>
+        <v>27628455</v>
       </c>
       <c r="X20" s="85" t="n">
-        <v>0.8543886996114936</v>
+        <v>0.8953764660533405</v>
       </c>
       <c r="Y20" s="35" t="n">
         <v>53.18709936797907</v>
@@ -5999,17 +5999,17 @@
       </c>
       <c r="AX20" s="90" t="inlineStr">
         <is>
+          <t>QQQ vs QQQM: Same Index, Same Stocks, Different Fee – and the Math Says One Leaves You Thousands Richer</t>
+        </is>
+      </c>
+      <c r="AY20" s="90" t="inlineStr">
+        <is>
           <t>Exchange-Traded Funds Mixed, US Equities Fall After Midday</t>
         </is>
       </c>
-      <c r="AY20" s="90" t="inlineStr">
+      <c r="AZ20" s="90" t="inlineStr">
         <is>
           <t>QQQ Charged 0.20% for Years. The Fee Only Fell After Shareholders Approved a Structural Change</t>
-        </is>
-      </c>
-      <c r="AZ20" s="90" t="inlineStr">
-        <is>
-          <t>This ETF Would Have Increased Your Investment by 6x Over the Past 10 Years -- and It's Still Soaring</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>-0.004459333403163956</v>
+        <v>-0.004526861571173213</v>
       </c>
       <c r="D21" s="27" t="n">
         <v>3</v>
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="R21" s="70" t="n">
-        <v>294.6900024414062</v>
+        <v>294.6700134277344</v>
       </c>
       <c r="S21" s="71" t="n">
-        <v>-1.32000732421875</v>
+        <v>-1.339996337890625</v>
       </c>
       <c r="T21" s="72" t="n">
         <v>295.3399963378906</v>
@@ -6105,61 +6105,61 @@
         <v>294.260009765625</v>
       </c>
       <c r="W21" s="73" t="n">
-        <v>16255655</v>
+        <v>17205591</v>
       </c>
       <c r="X21" s="74" t="n">
-        <v>0.972248943536787</v>
+        <v>1.026149448371472</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>45.94367785704903</v>
+        <v>45.91187219850499</v>
       </c>
       <c r="Z21" s="28" t="n">
-        <v>35.11905032220562</v>
+        <v>34.97032256892567</v>
       </c>
       <c r="AA21" s="28" t="n">
         <v>20.40181804023351</v>
       </c>
       <c r="AB21" s="75" t="n">
-        <v>-0.7766837930649331</v>
+        <v>-0.7782783582580919</v>
       </c>
       <c r="AC21" s="75" t="n">
-        <v>-0.09091189393194882</v>
+        <v>-0.09123080697058059</v>
       </c>
       <c r="AD21" s="75" t="n">
-        <v>-0.6857718991329842</v>
+        <v>-0.6870475512875113</v>
       </c>
       <c r="AE21" s="72" t="n">
-        <v>295.4424999715379</v>
+        <v>295.4380579684997</v>
       </c>
       <c r="AF21" s="72" t="n">
-        <v>296.819596016579</v>
+        <v>296.8177788335179</v>
       </c>
       <c r="AG21" s="72" t="n">
-        <v>296.911201171875</v>
+        <v>296.9108013916016</v>
       </c>
       <c r="AH21" s="72" t="n">
-        <v>290.7589010620117</v>
+        <v>290.758701171875</v>
       </c>
       <c r="AI21" s="72" t="n">
-        <v>272.9868504333496</v>
+        <v>272.9867504882812</v>
       </c>
       <c r="AJ21" s="72" t="n">
-        <v>306.1524612384081</v>
+        <v>306.1535370427105</v>
       </c>
       <c r="AK21" s="72" t="n">
-        <v>298.6010009765625</v>
+        <v>298.6000015258789</v>
       </c>
       <c r="AL21" s="72" t="n">
-        <v>291.0495407147169</v>
+        <v>291.0464660090473</v>
       </c>
       <c r="AM21" s="76" t="n">
-        <v>0.241043559818695</v>
+        <v>0.2398577070705955</v>
       </c>
       <c r="AN21" s="29" t="n">
-        <v>5.057893467971538</v>
+        <v>5.059300387295496</v>
       </c>
       <c r="AO21" s="77" t="n">
-        <v>1.083401409175358</v>
+        <v>1.083474901979489</v>
       </c>
       <c r="AP21" s="72" t="n">
         <v>305.1799926757812</v>
@@ -6168,22 +6168,22 @@
         <v>228.8999938964844</v>
       </c>
       <c r="AR21" s="29" t="n">
-        <v>-3.437312565086603</v>
+        <v>-3.443862474697845</v>
       </c>
       <c r="AS21" s="78" t="n">
-        <v>86.24804614283491</v>
+        <v>86.22184135259926</v>
       </c>
       <c r="AT21" s="26" t="n">
-        <v>0.00258568293322603</v>
+        <v>0.002517676897197063</v>
       </c>
       <c r="AU21" s="26" t="n">
-        <v>-0.02278152000532707</v>
+        <v>-0.02284780536755593</v>
       </c>
       <c r="AV21" s="26" t="n">
-        <v>0.03723915960486868</v>
+        <v>0.03716880300107972</v>
       </c>
       <c r="AW21" s="26" t="n">
-        <v>0.197148188403147</v>
+        <v>0.1970669850663964</v>
       </c>
       <c r="AX21" s="79" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="C22" s="33" t="n">
-        <v>0.05192704664625403</v>
+        <v>0.05107433429498753</v>
       </c>
       <c r="D22" s="34" t="n">
         <v>1</v>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="R22" s="81" t="n">
-        <v>123.370002746582</v>
+        <v>123.2699966430664</v>
       </c>
       <c r="S22" s="82" t="n">
-        <v>6.090003967285156</v>
+        <v>5.989997863769531</v>
       </c>
       <c r="T22" s="83" t="n">
         <v>125.120002746582</v>
@@ -6293,61 +6293,61 @@
         <v>121.5999984741211</v>
       </c>
       <c r="W22" s="84" t="n">
-        <v>50614561</v>
+        <v>51964601</v>
       </c>
       <c r="X22" s="85" t="n">
-        <v>0.930653151956731</v>
+        <v>0.9542919908418375</v>
       </c>
       <c r="Y22" s="35" t="n">
-        <v>48.67183074907373</v>
+        <v>48.62192842970096</v>
       </c>
       <c r="Z22" s="35" t="n">
-        <v>70.47265963670442</v>
+        <v>70.1879042389408</v>
       </c>
       <c r="AA22" s="35" t="n">
         <v>18.43662711393569</v>
       </c>
       <c r="AB22" s="86" t="n">
-        <v>-8.466572093303455</v>
+        <v>-8.474549788170805</v>
       </c>
       <c r="AC22" s="86" t="n">
-        <v>-9.958002980836323</v>
+        <v>-9.959598519809793</v>
       </c>
       <c r="AD22" s="86" t="n">
-        <v>1.491430887532868</v>
+        <v>1.485048731638988</v>
       </c>
       <c r="AE22" s="83" t="n">
-        <v>115.3842379020385</v>
+        <v>115.3620143234794</v>
       </c>
       <c r="AF22" s="83" t="n">
-        <v>121.8404244499269</v>
+        <v>121.8313329859709</v>
       </c>
       <c r="AG22" s="83" t="n">
-        <v>143.3635997009277</v>
+        <v>143.3615995788574</v>
       </c>
       <c r="AH22" s="83" t="n">
-        <v>164.1635001373291</v>
+        <v>164.162500076294</v>
       </c>
       <c r="AI22" s="83" t="n">
-        <v>109.264599981308</v>
+        <v>109.2640999507904</v>
       </c>
       <c r="AJ22" s="83" t="n">
-        <v>150.0256692158687</v>
+        <v>150.0204269432186</v>
       </c>
       <c r="AK22" s="83" t="n">
-        <v>122.9955001831055</v>
+        <v>122.9904998779297</v>
       </c>
       <c r="AL22" s="83" t="n">
-        <v>95.96533115034225</v>
+        <v>95.96057281264075</v>
       </c>
       <c r="AM22" s="87" t="n">
-        <v>0.5069274920741826</v>
+        <v>0.5051701353921823</v>
       </c>
       <c r="AN22" s="36" t="n">
-        <v>43.95310233711469</v>
+        <v>43.9544958222247</v>
       </c>
       <c r="AO22" s="88" t="n">
-        <v>10.875870442058</v>
+        <v>10.88469378475996</v>
       </c>
       <c r="AP22" s="83" t="n">
         <v>302</v>
@@ -6356,22 +6356,22 @@
         <v>26.56999969482422</v>
       </c>
       <c r="AR22" s="36" t="n">
-        <v>-59.1490057130523</v>
+        <v>-59.18212031686543</v>
       </c>
       <c r="AS22" s="89" t="n">
-        <v>35.14504699724201</v>
+        <v>35.10873791565872</v>
       </c>
       <c r="AT22" s="33" t="n">
-        <v>0.09380265755098671</v>
+        <v>0.09291600002191625</v>
       </c>
       <c r="AU22" s="33" t="n">
-        <v>-0.1203564866553866</v>
+        <v>-0.1210695426519329</v>
       </c>
       <c r="AV22" s="33" t="n">
-        <v>-0.4165247761914398</v>
+        <v>-0.4169977524606457</v>
       </c>
       <c r="AW22" s="33" t="n">
-        <v>1.935284471322697</v>
+        <v>1.932905073120933</v>
       </c>
       <c r="AX22" s="90" t="inlineStr">
         <is>
@@ -6502,10 +6502,10 @@
         <v>314.9200134277344</v>
       </c>
       <c r="W24" s="73" t="n">
-        <v>31822388</v>
+        <v>35028027</v>
       </c>
       <c r="X24" s="74" t="n">
-        <v>0.8158837852712565</v>
+        <v>0.894396665511635</v>
       </c>
       <c r="Y24" s="28" t="n">
         <v>50.1995004401049</v>
@@ -6589,12 +6589,12 @@
       </c>
       <c r="AY24" s="79" t="inlineStr">
         <is>
-          <t>How Apple's stock is performing ahead of a pivotal product launch</t>
+          <t>Apple Is Set to Reveal New iPhones Wednesday—Here’s What You Need to Know</t>
         </is>
       </c>
       <c r="AZ24" s="79" t="inlineStr">
         <is>
-          <t>Apple to Unveil First Foldable Phone</t>
+          <t>Apple event expected to debut foldable iPhone and new CEO John Ternus</t>
         </is>
       </c>
     </row>
@@ -6690,10 +6690,10 @@
         <v>486.5705871582031</v>
       </c>
       <c r="W25" s="84" t="n">
-        <v>26808296</v>
+        <v>27979240</v>
       </c>
       <c r="X25" s="85" t="n">
-        <v>1.50087064428304</v>
+        <v>1.561308671128961</v>
       </c>
       <c r="Y25" s="35" t="n">
         <v>57.03501141183438</v>
@@ -6772,17 +6772,17 @@
       </c>
       <c r="AX25" s="90" t="inlineStr">
         <is>
-          <t>F-Secure and AMD Silo AI Demonstrate Unique Approach to Helping Secure Digital Journeys in Agentic AI Era</t>
+          <t>Dow Jones Futures: Dow Skids But AMD, HPE Are New Buys; Apple iPhone Event Due</t>
         </is>
       </c>
       <c r="AY25" s="90" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Sees AI Boom Fueling MI450, Helios and Server CPU Growth</t>
+          <t>AMD Just Put a $70 Billion Number on Its AI Ambitions</t>
         </is>
       </c>
       <c r="AZ25" s="90" t="inlineStr">
         <is>
-          <t>AI-Optimized Processors Fuel Advanced Micro Devices (AMD) Stock Growth</t>
+          <t>Why AMD Stock Popped Today?</t>
         </is>
       </c>
     </row>
@@ -6878,10 +6878,10 @@
         <v>254.75</v>
       </c>
       <c r="W26" s="73" t="n">
-        <v>26723936</v>
+        <v>28792611</v>
       </c>
       <c r="X26" s="74" t="n">
-        <v>0.8287435702599156</v>
+        <v>0.8900409310757634</v>
       </c>
       <c r="Y26" s="28" t="n">
         <v>48.12096671477681</v>
@@ -6960,17 +6960,17 @@
       </c>
       <c r="AX26" s="79" t="inlineStr">
         <is>
-          <t>Qualcomm and Amazon ink deal for custom data center chips</t>
+          <t>AMD Jumps 6.7% While Amazon Opens a $60 Billion AI-Chip Door</t>
         </is>
       </c>
       <c r="AY26" s="79" t="inlineStr">
         <is>
-          <t>Qualcomm Stock Rises 6% on Multi-Generation Amazon Silicon Deal</t>
+          <t>Spotting Winners: Amazon (NASDAQ:AMZN) And Online Retail Stocks In Q2</t>
         </is>
       </c>
       <c r="AZ26" s="79" t="inlineStr">
         <is>
-          <t>The Market Marked AMZN Stock Down. The Numbers Push Back</t>
+          <t>DAL Stock Drops: Jefferies Sees Possible Snag To In-Cabin Experience Owing To SPCX-VSAT Spectrum Fight</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="C27" s="33" t="n">
-        <v>-0.001159805992870688</v>
+        <v>-0.001623746087524025</v>
       </c>
       <c r="D27" s="34" t="n">
         <v>17</v>
@@ -6994,12 +6994,12 @@
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G27" s="30" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" s="30" t="inlineStr">
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="R27" s="81" t="n">
-        <v>86.12000274658203</v>
+        <v>86.08000183105469</v>
       </c>
       <c r="S27" s="82" t="n">
-        <v>-0.09999847412109375</v>
+        <v>-0.1399993896484375</v>
       </c>
       <c r="T27" s="83" t="n">
         <v>86.15000152587891</v>
@@ -7066,61 +7066,61 @@
         <v>85.20999908447266</v>
       </c>
       <c r="W27" s="84" t="n">
-        <v>3495437</v>
+        <v>3752324</v>
       </c>
       <c r="X27" s="85" t="n">
-        <v>0.7502544777912034</v>
+        <v>0.8031779813299504</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>58.08830973887118</v>
+        <v>57.98587981166301</v>
       </c>
       <c r="Z27" s="35" t="n">
-        <v>76.57536479986958</v>
+        <v>76.02740728199275</v>
       </c>
       <c r="AA27" s="35" t="n">
         <v>25.45153673228566</v>
       </c>
       <c r="AB27" s="86" t="n">
-        <v>2.012868107416338</v>
+        <v>2.009677151191951</v>
       </c>
       <c r="AC27" s="86" t="n">
-        <v>2.021930047903917</v>
+        <v>2.021291856659039</v>
       </c>
       <c r="AD27" s="86" t="n">
-        <v>-0.009061940487578468</v>
+        <v>-0.01161470546708765</v>
       </c>
       <c r="AE27" s="83" t="n">
-        <v>85.39998872695128</v>
+        <v>85.39109963461188</v>
       </c>
       <c r="AF27" s="83" t="n">
-        <v>83.47866146236734</v>
+        <v>83.47502501550122</v>
       </c>
       <c r="AG27" s="83" t="n">
-        <v>79.91199966430663</v>
+        <v>79.91119964599609</v>
       </c>
       <c r="AH27" s="83" t="n">
-        <v>78.68219993591309</v>
+        <v>78.68179992675782</v>
       </c>
       <c r="AI27" s="83" t="n">
-        <v>76.97935010910034</v>
+        <v>76.9791501045227</v>
       </c>
       <c r="AJ27" s="83" t="n">
-        <v>88.5677000647153</v>
+        <v>88.56196773119783</v>
       </c>
       <c r="AK27" s="83" t="n">
-        <v>83.94549942016602</v>
+        <v>83.94349937438965</v>
       </c>
       <c r="AL27" s="83" t="n">
-        <v>79.32329877561673</v>
+        <v>79.32503101758147</v>
       </c>
       <c r="AM27" s="87" t="n">
-        <v>0.7352238136806429</v>
+        <v>0.7312998911766473</v>
       </c>
       <c r="AN27" s="36" t="n">
-        <v>11.0123846459335</v>
+        <v>11.00375464741998</v>
       </c>
       <c r="AO27" s="88" t="n">
-        <v>2.701031624354151</v>
+        <v>2.702286779274508</v>
       </c>
       <c r="AP27" s="83" t="n">
         <v>92.65000152587891</v>
@@ -7129,22 +7129,22 @@
         <v>62.94499969482422</v>
       </c>
       <c r="AR27" s="36" t="n">
-        <v>-7.048028787644345</v>
+        <v>-7.091203007685964</v>
       </c>
       <c r="AS27" s="89" t="n">
-        <v>78.0171742912664</v>
+        <v>77.88251375242905</v>
       </c>
       <c r="AT27" s="33" t="n">
-        <v>0.006427521955350457</v>
+        <v>0.005960057707716793</v>
       </c>
       <c r="AU27" s="33" t="n">
-        <v>0.08422513427801559</v>
+        <v>0.08372153468877142</v>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>0.1349499982052622</v>
+        <v>0.1344228379920938</v>
       </c>
       <c r="AW27" s="33" t="n">
-        <v>0.1196048465501784</v>
+        <v>0.1190848138346356</v>
       </c>
       <c r="AX27" s="90" t="inlineStr">
         <is>
@@ -7254,10 +7254,10 @@
         <v>254.6399993896484</v>
       </c>
       <c r="W28" s="73" t="n">
-        <v>4946625</v>
+        <v>5095872</v>
       </c>
       <c r="X28" s="74" t="n">
-        <v>1.326304041451819</v>
+        <v>1.363592284656718</v>
       </c>
       <c r="Y28" s="28" t="n">
         <v>52.24195279097528</v>
@@ -7442,10 +7442,10 @@
         <v>63.15000152587891</v>
       </c>
       <c r="W29" s="84" t="n">
-        <v>11761743</v>
+        <v>12009781</v>
       </c>
       <c r="X29" s="85" t="n">
-        <v>1.181540009923967</v>
+        <v>1.204955773479053</v>
       </c>
       <c r="Y29" s="35" t="n">
         <v>52.47674092186459</v>
@@ -7630,10 +7630,10 @@
         <v>362.739990234375</v>
       </c>
       <c r="W30" s="73" t="n">
-        <v>26562775</v>
+        <v>29871614</v>
       </c>
       <c r="X30" s="74" t="n">
-        <v>1.102738743969184</v>
+        <v>1.231644128817539</v>
       </c>
       <c r="Y30" s="28" t="n">
         <v>45.33346661314823</v>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
+          <t>Broadcom CEO Sees AI Value Flowing to Frontier Models and Custom Chips</t>
+        </is>
+      </c>
+      <c r="AY30" s="79" t="inlineStr">
+        <is>
+          <t>Intel Leads Chip Stocks Rally as Qualcomm, AMD and Broadcom Stocks Jump</t>
+        </is>
+      </c>
+      <c r="AZ30" s="79" t="inlineStr">
+        <is>
           <t>Why Broadcom Stock Rallied Tuesday Morning</t>
-        </is>
-      </c>
-      <c r="AY30" s="79" t="inlineStr">
-        <is>
-          <t>Jim Cramer picks Nvidia and Broadcom as OpenAI GPT-6 Astra winners</t>
-        </is>
-      </c>
-      <c r="AZ30" s="79" t="inlineStr">
-        <is>
-          <t>Amazon Just Handed Qualcomm a Slice of AWS’s AI Buildout</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>0.01211039553875048</v>
+        <v>0.0122096821820159</v>
       </c>
       <c r="D31" s="34" t="n">
         <v>14</v>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="R31" s="81" t="n">
-        <v>101.9599990844727</v>
+        <v>101.9700012207031</v>
       </c>
       <c r="S31" s="82" t="n">
-        <v>1.220001220703125</v>
+        <v>1.230003356933594</v>
       </c>
       <c r="T31" s="83" t="n">
         <v>102.495002746582</v>
@@ -7818,61 +7818,61 @@
         <v>101.5500030517578</v>
       </c>
       <c r="W31" s="84" t="n">
-        <v>1929177</v>
+        <v>2186442</v>
       </c>
       <c r="X31" s="85" t="n">
-        <v>0.7278364563826674</v>
+        <v>0.820913025928136</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>56.00903873570904</v>
+        <v>56.02439410574521</v>
       </c>
       <c r="Z31" s="35" t="n">
-        <v>45.06880453003986</v>
+        <v>45.12615622058046</v>
       </c>
       <c r="AA31" s="35" t="n">
         <v>15.37669590983723</v>
       </c>
       <c r="AB31" s="86" t="n">
-        <v>1.363456883782675</v>
+        <v>1.364254774991949</v>
       </c>
       <c r="AC31" s="86" t="n">
-        <v>1.571725691618105</v>
+        <v>1.57188526985996</v>
       </c>
       <c r="AD31" s="86" t="n">
-        <v>-0.2082688078354304</v>
+        <v>-0.2076304948680112</v>
       </c>
       <c r="AE31" s="83" t="n">
-        <v>100.4228167754111</v>
+        <v>100.4250394723512</v>
       </c>
       <c r="AF31" s="83" t="n">
-        <v>99.24056533021594</v>
+        <v>99.2414746153278</v>
       </c>
       <c r="AG31" s="83" t="n">
-        <v>95.34380004882813</v>
+        <v>95.34400009155273</v>
       </c>
       <c r="AH31" s="83" t="n">
-        <v>103.698099822998</v>
+        <v>103.6981998443603</v>
       </c>
       <c r="AI31" s="83" t="n">
-        <v>105.4621997451782</v>
+        <v>105.4622497558594</v>
       </c>
       <c r="AJ31" s="83" t="n">
-        <v>107.0284530879407</v>
+        <v>107.0294958891796</v>
       </c>
       <c r="AK31" s="83" t="n">
-        <v>100.0795001983643</v>
+        <v>100.0800003051758</v>
       </c>
       <c r="AL31" s="83" t="n">
-        <v>93.13054730878778</v>
+        <v>93.13050472117202</v>
       </c>
       <c r="AM31" s="87" t="n">
-        <v>0.6353080756187865</v>
+        <v>0.6359811581057558</v>
       </c>
       <c r="AN31" s="36" t="n">
-        <v>13.88686569338013</v>
+        <v>13.88788082096832</v>
       </c>
       <c r="AO31" s="88" t="n">
-        <v>3.866797668803516</v>
+        <v>3.866418378457375</v>
       </c>
       <c r="AP31" s="83" t="n">
         <v>135.2400054931641</v>
@@ -7881,22 +7881,22 @@
         <v>74.98999786376953</v>
       </c>
       <c r="AR31" s="36" t="n">
-        <v>-24.60810785043454</v>
+        <v>-24.6007120090975</v>
       </c>
       <c r="AS31" s="89" t="n">
-        <v>44.76348183488878</v>
+        <v>44.78008288877079</v>
       </c>
       <c r="AT31" s="33" t="n">
-        <v>0.03240175049640115</v>
+        <v>0.03250302769378988</v>
       </c>
       <c r="AU31" s="33" t="n">
-        <v>0.04692473275967557</v>
+        <v>0.04702743464172876</v>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>-0.03300458342522761</v>
+        <v>-0.03290972249959334</v>
       </c>
       <c r="AW31" s="33" t="n">
-        <v>0.114438752488476</v>
+        <v>0.114548077403374</v>
       </c>
       <c r="AX31" s="90" t="inlineStr">
         <is>
@@ -8006,10 +8006,10 @@
         <v>92.87999725341797</v>
       </c>
       <c r="W32" s="73" t="n">
-        <v>50102585</v>
+        <v>50881908</v>
       </c>
       <c r="X32" s="74" t="n">
-        <v>1.745629794349376</v>
+        <v>1.770378765848993</v>
       </c>
       <c r="Y32" s="28" t="n">
         <v>61.38093875257105</v>
@@ -8088,17 +8088,17 @@
       </c>
       <c r="AX32" s="79" t="inlineStr">
         <is>
+          <t>Why CoreWeave Stock Soared 12% Today</t>
+        </is>
+      </c>
+      <c r="AY32" s="79" t="inlineStr">
+        <is>
           <t>Billionaire David Tepper Just Bought These 2 Artificial Intelligence (AI) Stocks That Wall Street Thinks Co...</t>
         </is>
       </c>
-      <c r="AY32" s="79" t="inlineStr">
+      <c r="AZ32" s="79" t="inlineStr">
         <is>
           <t>CRWV Stock Takes a 13% Hit in 3 Months: Time to Buy, Hold or Bail Out?</t>
-        </is>
-      </c>
-      <c r="AZ32" s="79" t="inlineStr">
-        <is>
-          <t>Nebius Stock Up 254% in a Year: Should You Buy, Hold or Sell?</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>0.01783869829554785</v>
+        <v>0.01858280223254472</v>
       </c>
       <c r="D33" s="34" t="n">
         <v>13</v>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="R33" s="81" t="n">
-        <v>533.489990234375</v>
+        <v>533.8800048828125</v>
       </c>
       <c r="S33" s="82" t="n">
-        <v>9.3499755859375</v>
+        <v>9.739990234375</v>
       </c>
       <c r="T33" s="83" t="n">
         <v>521.1500244140625</v>
@@ -8194,61 +8194,61 @@
         <v>515.5601196289062</v>
       </c>
       <c r="W33" s="84" t="n">
-        <v>6260404</v>
+        <v>6589879</v>
       </c>
       <c r="X33" s="85" t="n">
-        <v>0.7468358570978624</v>
+        <v>0.784598704237046</v>
       </c>
       <c r="Y33" s="35" t="n">
-        <v>65.0245878859218</v>
+        <v>65.07915030378641</v>
       </c>
       <c r="Z33" s="35" t="n">
-        <v>95.76572344090685</v>
+        <v>96.10040124674029</v>
       </c>
       <c r="AA33" s="35" t="n">
         <v>10.54085024096999</v>
       </c>
       <c r="AB33" s="86" t="n">
-        <v>19.25707882367112</v>
+        <v>19.28819110331858</v>
       </c>
       <c r="AC33" s="86" t="n">
-        <v>12.39713166255265</v>
+        <v>12.40335411848215</v>
       </c>
       <c r="AD33" s="86" t="n">
-        <v>6.85994716111847</v>
+        <v>6.884836984836436</v>
       </c>
       <c r="AE33" s="83" t="n">
-        <v>494.564759642242</v>
+        <v>494.651429564117</v>
       </c>
       <c r="AF33" s="83" t="n">
-        <v>470.6447128577041</v>
+        <v>470.6801687348348</v>
       </c>
       <c r="AG33" s="83" t="n">
-        <v>442.1323992919922</v>
+        <v>442.140199584961</v>
       </c>
       <c r="AH33" s="83" t="n">
-        <v>374.0185989379883</v>
+        <v>374.0224990844727</v>
       </c>
       <c r="AI33" s="83" t="n">
-        <v>255.5051996231079</v>
+        <v>255.5071496963501</v>
       </c>
       <c r="AJ33" s="83" t="n">
-        <v>531.5637648284028</v>
+        <v>531.6638865410406</v>
       </c>
       <c r="AK33" s="83" t="n">
-        <v>469.8950012207031</v>
+        <v>469.914501953125</v>
       </c>
       <c r="AL33" s="83" t="n">
-        <v>408.2262376130034</v>
+        <v>408.1651173652094</v>
       </c>
       <c r="AM33" s="87" t="n">
-        <v>1.015617512767288</v>
+        <v>1.017944456908852</v>
       </c>
       <c r="AN33" s="36" t="n">
-        <v>26.24789088945201</v>
+        <v>26.28111468416662</v>
       </c>
       <c r="AO33" s="88" t="n">
-        <v>5.892983959488309</v>
+        <v>5.88867896577027</v>
       </c>
       <c r="AP33" s="83" t="n">
         <v>538.4243774414062</v>
@@ -8257,36 +8257,36 @@
         <v>110.2200012207031</v>
       </c>
       <c r="AR33" s="36" t="n">
-        <v>-0.9164494428130165</v>
+        <v>-0.8440131518911986</v>
       </c>
       <c r="AS33" s="89" t="n">
-        <v>98.84765605373262</v>
+        <v>98.93873747888753</v>
       </c>
       <c r="AT33" s="33" t="n">
-        <v>0.169908508167556</v>
+        <v>0.1707637846748369</v>
       </c>
       <c r="AU33" s="33" t="n">
-        <v>0.1756837233638675</v>
+        <v>0.1765432219157335</v>
       </c>
       <c r="AV33" s="33" t="n">
-        <v>0.3311625242881535</v>
+        <v>0.3321356875966073</v>
       </c>
       <c r="AW33" s="33" t="n">
-        <v>3.238083904310614</v>
+        <v>3.241182209497675</v>
       </c>
       <c r="AX33" s="90" t="inlineStr">
         <is>
+          <t>Is Dell Making Money Where You Think It Is?</t>
+        </is>
+      </c>
+      <c r="AY33" s="90" t="inlineStr">
+        <is>
           <t>Snowflake Expands in Cloud Analytics: Can It Challenge DELL &amp; ORCL?</t>
         </is>
       </c>
-      <c r="AY33" s="90" t="inlineStr">
+      <c r="AZ33" s="90" t="inlineStr">
         <is>
           <t>The Enterprise AI Fight Has a New Challenger and It Is Not Who You Would Expect</t>
-        </is>
-      </c>
-      <c r="AZ33" s="90" t="inlineStr">
-        <is>
-          <t>Why Did DELL, VOD, ZETA Stocks Surge To 52-Week Highs Last Week?</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -8382,10 +8382,10 @@
         <v>330.3900146484375</v>
       </c>
       <c r="W34" s="73" t="n">
-        <v>12912913</v>
+        <v>13853543</v>
       </c>
       <c r="X34" s="74" t="n">
-        <v>0.8520242027310269</v>
+        <v>0.9112613000926292</v>
       </c>
       <c r="Y34" s="28" t="n">
         <v>44.03811679114303</v>
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
-          <t>Google Cloud Boss Makes Bold Claim About AI Chip Business</t>
+          <t>Google Warns EU Regulations Will Result In Lower Search Quality</t>
         </is>
       </c>
       <c r="AY34" s="79" t="inlineStr">
         <is>
-          <t>Will Direct TPU Sales Re-Rate Google Stock?</t>
+          <t>Bank of America Spots Reassuring Signal for Google Stock</t>
         </is>
       </c>
       <c r="AZ34" s="79" t="inlineStr">
         <is>
-          <t>Google degrades E.U. search results to comply with DMA rules</t>
+          <t>Google, Blackstone Venture Faces Delays at Data-Center Sites</t>
         </is>
       </c>
     </row>
@@ -8570,10 +8570,10 @@
         <v>46.0099983215332</v>
       </c>
       <c r="W35" s="84" t="n">
-        <v>49654576</v>
+        <v>50573887</v>
       </c>
       <c r="X35" s="85" t="n">
-        <v>1.064175032340439</v>
+        <v>1.082810610039409</v>
       </c>
       <c r="Y35" s="35" t="n">
         <v>60.3906396358092</v>
@@ -8758,10 +8758,10 @@
         <v>100.3499984741211</v>
       </c>
       <c r="W36" s="73" t="n">
-        <v>135748800</v>
+        <v>139493818</v>
       </c>
       <c r="X36" s="74" t="n">
-        <v>1.362964390922728</v>
+        <v>1.397937442200805</v>
       </c>
       <c r="Y36" s="28" t="n">
         <v>61.6991840431096</v>
@@ -8840,17 +8840,17 @@
       </c>
       <c r="AX36" s="79" t="inlineStr">
         <is>
-          <t>Why Broadcom Stock Rallied Tuesday Morning</t>
+          <t>Stock Market Today, Sept. 8: Stocks Slide Amid Surging Oil Prices, Persistent Geopolotical Tenisons</t>
         </is>
       </c>
       <c r="AY36" s="79" t="inlineStr">
         <is>
-          <t>Update: Market Chatter: Intel May Raise PC CPU Prices Another 10% in October; Shares Rise in Afternoon Trading</t>
+          <t>Intel Leads Chip Stocks Rally as Qualcomm, AMD and Broadcom Stocks Jump</t>
         </is>
       </c>
       <c r="AZ36" s="79" t="inlineStr">
         <is>
-          <t>Intel Stock Jumps on Major Analyst Upgrade</t>
+          <t>AMD, Amgen, Novartis, Qualcomn, Corning, and More Stocks That Explain Today’s Market</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="F37" s="30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G37" s="30" t="inlineStr">
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="N37" s="80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O37" s="30" t="inlineStr">
         <is>
@@ -8946,10 +8946,10 @@
         <v>490.1499938964844</v>
       </c>
       <c r="W37" s="84" t="n">
-        <v>15678467</v>
+        <v>18684730</v>
       </c>
       <c r="X37" s="85" t="n">
-        <v>0.7056011512252309</v>
+        <v>0.835246190975353</v>
       </c>
       <c r="Y37" s="35" t="n">
         <v>55.96867258696406</v>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="AX37" s="90" t="inlineStr">
         <is>
-          <t>Alphabet Stock Is Pulling Back From Its High. Here’s Why I’d Buy the Dip.</t>
+          <t>Microsoft's OpenAI Partnership Draws Fresh Legal Fire</t>
         </is>
       </c>
       <c r="AY37" s="90" t="inlineStr">
         <is>
-          <t>Network to Code Appoints Chris Millerick as Chief Revenue Officer to Scale Commercial Software Growth</t>
+          <t>Goldman's New AI Office Adds Just 1% to Its Engineering Army</t>
         </is>
       </c>
       <c r="AZ37" s="90" t="inlineStr">
         <is>
-          <t>AI Could Nearly Triple America's Data Center Footprint by 2030</t>
+          <t>Prop Industry Leader The5ers Brings Single Stock Futures via CME Feed</t>
         </is>
       </c>
     </row>
@@ -9134,10 +9134,10 @@
         <v>135.3800048828125</v>
       </c>
       <c r="W38" s="73" t="n">
-        <v>17715754</v>
+        <v>19289134</v>
       </c>
       <c r="X38" s="74" t="n">
-        <v>0.6329339733410267</v>
+        <v>0.6872149063484077</v>
       </c>
       <c r="Y38" s="28" t="n">
         <v>61.36705890882406</v>
@@ -9221,12 +9221,12 @@
       </c>
       <c r="AY38" s="79" t="inlineStr">
         <is>
+          <t>Strategy doubles STRC buyback to $2 billion as Bitcoin treasury grows</t>
+        </is>
+      </c>
+      <c r="AZ38" s="79" t="inlineStr">
+        <is>
           <t>Strategy CEO says 'never sell' was just a marketing slogan</t>
-        </is>
-      </c>
-      <c r="AZ38" s="79" t="inlineStr">
-        <is>
-          <t>Strategy's Return to Bitcoin Buying Lasted Exactly One Week</t>
         </is>
       </c>
     </row>
@@ -9322,10 +9322,10 @@
         <v>997.6400146484375</v>
       </c>
       <c r="W39" s="84" t="n">
-        <v>25252605</v>
+        <v>26367138</v>
       </c>
       <c r="X39" s="85" t="n">
-        <v>0.9158679708864907</v>
+        <v>0.9543612726384941</v>
       </c>
       <c r="Y39" s="35" t="n">
         <v>57.66197475179354</v>
@@ -9404,17 +9404,17 @@
       </c>
       <c r="AX39" s="90" t="inlineStr">
         <is>
-          <t>Thinking of Buying Micron Stock Now? Here's 1 Green Flag and 1 Red Flag.</t>
+          <t>Micron (MU) Falls More Steeply Than Broader Market: What Investors Need to Know</t>
         </is>
       </c>
       <c r="AY39" s="90" t="inlineStr">
         <is>
-          <t>SK Hynix Jumps 7% as AI Diverts Memory From Phones; Micron Holds Steady, Apple Slips</t>
+          <t>Micron and Sandisk Soar as Goldman Sees New Memory Stock Rally</t>
         </is>
       </c>
       <c r="AZ39" s="90" t="inlineStr">
         <is>
-          <t>Micron Technology (MU) Rose on Elevated Demand for High-Bandwidth Memory</t>
+          <t>Goldman Says the Worst May Be Over for Micron and SanDisk</t>
         </is>
       </c>
     </row>
@@ -9510,10 +9510,10 @@
         <v>234.3249969482422</v>
       </c>
       <c r="W40" s="73" t="n">
-        <v>25750274</v>
+        <v>26604516</v>
       </c>
       <c r="X40" s="74" t="n">
-        <v>1.152738990388753</v>
+        <v>1.188707189744639</v>
       </c>
       <c r="Y40" s="28" t="n">
         <v>58.48647113982799</v>
@@ -9698,10 +9698,10 @@
         <v>75.91999816894531</v>
       </c>
       <c r="W41" s="84" t="n">
-        <v>32107555</v>
+        <v>33754561</v>
       </c>
       <c r="X41" s="85" t="n">
-        <v>1.134685407529787</v>
+        <v>1.189429264580592</v>
       </c>
       <c r="Y41" s="35" t="n">
         <v>45.43138140489266</v>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="C42" s="26" t="n">
-        <v>0.06281157838618334</v>
+        <v>0.06181454656683427</v>
       </c>
       <c r="D42" s="27" t="n">
         <v>4</v>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="R42" s="70" t="n">
-        <v>10.65999984741211</v>
+        <v>10.64999961853027</v>
       </c>
       <c r="S42" s="71" t="n">
-        <v>0.630000114440918</v>
+        <v>0.619999885559082</v>
       </c>
       <c r="T42" s="72" t="n">
         <v>10.46000003814697</v>
@@ -9886,61 +9886,61 @@
         <v>10.32999992370605</v>
       </c>
       <c r="W42" s="73" t="n">
-        <v>108781432</v>
+        <v>112224091</v>
       </c>
       <c r="X42" s="74" t="n">
-        <v>1.52289036766127</v>
+        <v>1.5673091469557</v>
       </c>
       <c r="Y42" s="28" t="n">
-        <v>55.88489331573219</v>
+        <v>55.76913742500214</v>
       </c>
       <c r="Z42" s="28" t="n">
-        <v>84.84849579516226</v>
+        <v>84.09090252290264</v>
       </c>
       <c r="AA42" s="28" t="n">
         <v>12.62105813084566</v>
       </c>
       <c r="AB42" s="75" t="n">
-        <v>-0.0703892377971389</v>
+        <v>-0.07118697685324094</v>
       </c>
       <c r="AC42" s="75" t="n">
-        <v>-0.126230317093964</v>
+        <v>-0.1263898649051844</v>
       </c>
       <c r="AD42" s="75" t="n">
-        <v>0.05584107929682505</v>
+        <v>0.05520288805194343</v>
       </c>
       <c r="AE42" s="72" t="n">
-        <v>10.17252185406472</v>
+        <v>10.17029958097986</v>
       </c>
       <c r="AF42" s="72" t="n">
-        <v>10.17290437885797</v>
+        <v>10.17199526714144</v>
       </c>
       <c r="AG42" s="72" t="n">
-        <v>10.48319997787476</v>
+        <v>10.48299997329712</v>
       </c>
       <c r="AH42" s="72" t="n">
-        <v>12.01819999694824</v>
+        <v>12.01809999465942</v>
       </c>
       <c r="AI42" s="72" t="n">
-        <v>9.626149997711181</v>
+        <v>9.626099996566772</v>
       </c>
       <c r="AJ42" s="72" t="n">
-        <v>10.9102128486372</v>
+        <v>10.90846297148201</v>
       </c>
       <c r="AK42" s="72" t="n">
-        <v>10.23150005340576</v>
+        <v>10.23100004196167</v>
       </c>
       <c r="AL42" s="72" t="n">
-        <v>9.552787258174327</v>
+        <v>9.553537112441333</v>
       </c>
       <c r="AM42" s="76" t="n">
-        <v>0.8156709266547955</v>
+        <v>0.8092417004021665</v>
       </c>
       <c r="AN42" s="29" t="n">
-        <v>13.26712196039157</v>
+        <v>13.24333743997212</v>
       </c>
       <c r="AO42" s="77" t="n">
-        <v>4.485590584481948</v>
+        <v>4.489802503178826</v>
       </c>
       <c r="AP42" s="72" t="n">
         <v>17.45000076293945</v>
@@ -9949,22 +9949,22 @@
         <v>4.480000019073486</v>
       </c>
       <c r="AR42" s="29" t="n">
-        <v>-38.91117833042185</v>
+        <v>-38.9684862298179</v>
       </c>
       <c r="AS42" s="78" t="n">
-        <v>47.64841537315557</v>
+        <v>47.57131261056271</v>
       </c>
       <c r="AT42" s="26" t="n">
-        <v>0.05128200063935684</v>
+        <v>0.05029578480668961</v>
       </c>
       <c r="AU42" s="26" t="n">
-        <v>0.1388889143609602</v>
+        <v>0.1378205138002078</v>
       </c>
       <c r="AV42" s="26" t="n">
-        <v>-0.2693625952072866</v>
+        <v>-0.2700480118472626</v>
       </c>
       <c r="AW42" s="26" t="n">
-        <v>0.6476043575105503</v>
+        <v>0.6460587270304696</v>
       </c>
       <c r="AX42" s="79" t="inlineStr">
         <is>
@@ -10074,10 +10074,10 @@
         <v>224.8500061035156</v>
       </c>
       <c r="W43" s="84" t="n">
-        <v>112572117</v>
+        <v>118984635</v>
       </c>
       <c r="X43" s="85" t="n">
-        <v>0.874440973657972</v>
+        <v>0.9219561243039245</v>
       </c>
       <c r="Y43" s="35" t="n">
         <v>56.14514785469748</v>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
-          <t>6 Massive Reasons Standard Lithium Stock Popped 33% in August</t>
+          <t>Dow Jones Futures: Dow Skids But AMD, HPE Are New Buys; Apple iPhone Event Due</t>
         </is>
       </c>
       <c r="AY43" s="90" t="inlineStr">
         <is>
-          <t>James Altucher: Elon Musk's Next Move Could Eclipse Everything He's Ever Built, and It May Be His Last</t>
+          <t>Prop Industry Leader The5ers Brings Single Stock Futures via CME Feed</t>
         </is>
       </c>
       <c r="AZ43" s="90" t="inlineStr">
         <is>
-          <t>1 No-Brainer ETF I'm Loading Up on in 2026 and Beyond</t>
+          <t>Nvidia Falls as Its Firmus Bet Lands OpenAI</t>
         </is>
       </c>
     </row>
@@ -10262,10 +10262,10 @@
         <v>170.0200042724609</v>
       </c>
       <c r="W44" s="73" t="n">
-        <v>21993292</v>
+        <v>24436325</v>
       </c>
       <c r="X44" s="74" t="n">
-        <v>0.7008287526950384</v>
+        <v>0.7756581915090189</v>
       </c>
       <c r="Y44" s="28" t="n">
         <v>51.29456085708777</v>
@@ -10344,17 +10344,17 @@
       </c>
       <c r="AX44" s="79" t="inlineStr">
         <is>
+          <t>Palantir Technologies Inc. (PLTR) Falls More Steeply Than Broader Market: What Investors Need to Know</t>
+        </is>
+      </c>
+      <c r="AY44" s="79" t="inlineStr">
+        <is>
           <t>Sector Update: Tech Stocks Rise Late Afternoon</t>
         </is>
       </c>
-      <c r="AY44" s="79" t="inlineStr">
+      <c r="AZ44" s="79" t="inlineStr">
         <is>
           <t>Palantir Wants to Kill the 'Pay-Per-Token' AI Economy</t>
-        </is>
-      </c>
-      <c r="AZ44" s="79" t="inlineStr">
-        <is>
-          <t>Sector Update: Tech Stocks Gain Tuesday Afternoon</t>
         </is>
       </c>
     </row>
@@ -10450,10 +10450,10 @@
         <v>172.0352020263672</v>
       </c>
       <c r="W45" s="84" t="n">
-        <v>25046873</v>
+        <v>25627305</v>
       </c>
       <c r="X45" s="85" t="n">
-        <v>2.533689519128793</v>
+        <v>2.584816399101715</v>
       </c>
       <c r="Y45" s="35" t="n">
         <v>58.91644929504607</v>
@@ -10532,17 +10532,17 @@
       </c>
       <c r="AX45" s="90" t="inlineStr">
         <is>
-          <t>How They Run: Qualcomm CEO Cristiano Amon</t>
+          <t>Qualcomm and Amazon ink deal for custom data center chips</t>
         </is>
       </c>
       <c r="AY45" s="90" t="inlineStr">
         <is>
-          <t>Qualcomm and Amazon ink deal for custom data center chips</t>
+          <t>AMD Jumps 6.7% While Amazon Opens a $60 Billion AI-Chip Door</t>
         </is>
       </c>
       <c r="AZ45" s="90" t="inlineStr">
         <is>
-          <t>Qualcomm Stock Rises 6% on Multi-Generation Amazon Silicon Deal</t>
+          <t>Stock Market Today: Dow Dives, Qualcomm Clears Key Level On Amazon Deal; Fertilizer Leader Rises (Live Cove...</t>
         </is>
       </c>
     </row>
@@ -10638,10 +10638,10 @@
         <v>64.15000152587891</v>
       </c>
       <c r="W46" s="73" t="n">
-        <v>22391532</v>
+        <v>23996422</v>
       </c>
       <c r="X46" s="74" t="n">
-        <v>1.35416532106073</v>
+        <v>1.444215065552374</v>
       </c>
       <c r="Y46" s="28" t="n">
         <v>40.93796259622257</v>
@@ -10720,17 +10720,17 @@
       </c>
       <c r="AX46" s="79" t="inlineStr">
         <is>
+          <t>Rocket Lab Introduces New Solar Cell — Can RKLB Tackle Supply Chain Constraints In The Space Power Industry?</t>
+        </is>
+      </c>
+      <c r="AY46" s="79" t="inlineStr">
+        <is>
+          <t>Rocket Lab Introduces High-Efficiency Solar Cell to Reduce Reliance on Supply-Constrained Critical Minerals</t>
+        </is>
+      </c>
+      <c r="AZ46" s="79" t="inlineStr">
+        <is>
           <t>SpaceX Rises 4% as Pivotal Research Launches Coverage at $220, Intuitive Machines Climbs 5%, Rocket Lab Gai...</t>
-        </is>
-      </c>
-      <c r="AY46" s="79" t="inlineStr">
-        <is>
-          <t>How Far Could RKLB Stock Fall In The Next Shock?</t>
-        </is>
-      </c>
-      <c r="AZ46" s="79" t="inlineStr">
-        <is>
-          <t>Grounded and Falling: Why One Wall Street Pro Says Rocket Lab Will More Than Double Soon</t>
         </is>
       </c>
     </row>
@@ -10826,10 +10826,10 @@
         <v>1733.780029296875</v>
       </c>
       <c r="W47" s="84" t="n">
-        <v>10879063</v>
+        <v>11080819</v>
       </c>
       <c r="X47" s="85" t="n">
-        <v>0.8189011189700732</v>
+        <v>0.8334550485156649</v>
       </c>
       <c r="Y47" s="35" t="n">
         <v>61.1120814610072</v>
@@ -10908,17 +10908,17 @@
       </c>
       <c r="AX47" s="90" t="inlineStr">
         <is>
-          <t>SanDisk Stock Has Soared More Than 500% in 2026. Can the Rally Possibly Continue?</t>
+          <t>Micron and Sandisk Soar as Goldman Sees New Memory Stock Rally</t>
         </is>
       </c>
       <c r="AY47" s="90" t="inlineStr">
         <is>
-          <t>SanDisk Up Over 40% Past Month: Can the Rally Last?</t>
+          <t>Goldman Says the Worst May Be Over for Micron and SanDisk</t>
         </is>
       </c>
       <c r="AZ47" s="90" t="inlineStr">
         <is>
-          <t>Goldman Spots Breakout Signal for Micron, SanDisk Stocks</t>
+          <t>Sandisk Jumps Nearly 3.5% as S&amp;P 100 Promotion Extends Its AI Run</t>
         </is>
       </c>
     </row>
@@ -11014,10 +11014,10 @@
         <v>355.7999877929688</v>
       </c>
       <c r="W48" s="73" t="n">
-        <v>49716440</v>
+        <v>50850639</v>
       </c>
       <c r="X48" s="74" t="n">
-        <v>1.268826722362927</v>
+        <v>1.295897356861204</v>
       </c>
       <c r="Y48" s="28" t="n">
         <v>55.7109935010271</v>
@@ -11096,17 +11096,17 @@
       </c>
       <c r="AX48" s="79" t="inlineStr">
         <is>
+          <t>Tesla Cybercab Could Beat Waymo on Cost by Up to 30 Cents A Mile, Goldman Says</t>
+        </is>
+      </c>
+      <c r="AY48" s="79" t="inlineStr">
+        <is>
+          <t>Uber Stock Falls As Wall Street Sizes Up Tesla's Cybercab Rollout</t>
+        </is>
+      </c>
+      <c r="AZ48" s="79" t="inlineStr">
+        <is>
           <t>Uber Falls 4% on Tesla Cybercab Threat as Slovenia Clears Full Self-Driving; TSLA Stock Rises 4%</t>
-        </is>
-      </c>
-      <c r="AY48" s="79" t="inlineStr">
-        <is>
-          <t>Tesla Stock Rises. Musk's Robotaxi Bet Gets a New Vehicle</t>
-        </is>
-      </c>
-      <c r="AZ48" s="79" t="inlineStr">
-        <is>
-          <t>Tesla Jumps as Slovenia Opens Europe's Sixth FSD Door</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 8 Sep 2026, 08:02 PM · Yahoo Finance data</t>
+          <t>Built 8 Sep 2026, 10:43 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 8 Sep 2026, 08:02 PM · Yahoo Finance data</t>
+          <t>Built 8 Sep 2026, 10:43 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 8 Sep 2026, 08:02 PM · Yahoo Finance data</t>
+          <t>Built 8 Sep 2026, 10:43 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 8 Sep 2026, 08:02 PM · Yahoo Finance data</t>
+          <t>Built 8 Sep 2026, 10:43 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -43355,25 +43355,25 @@
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>0.01100533652705571</v>
+        <v>0.01108334548129264</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>0.01258599619603817</v>
+        <v>0.01266412711363518</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>0.1263478154721467</v>
+        <v>0.1264347242272419</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>0.1103205444298097</v>
+        <v>0.1104062165241195</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>0.1499467283484432</v>
+        <v>0.1500354579905785</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0.4485573857267353</v>
+        <v>0.4486691561029441</v>
       </c>
       <c r="J6" s="27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" s="101" t="inlineStr">
         <is>
@@ -43393,22 +43393,22 @@
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>-0.02502183355201748</v>
+        <v>-0.02519680456298767</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>-0.0198193371472255</v>
+        <v>-0.01999524180582679</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.008932949370805243</v>
+        <v>0.008751884784717445</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.09505411297601873</v>
+        <v>0.09485759295966534</v>
       </c>
       <c r="H7" s="33" t="n">
-        <v>0.08362511094671254</v>
+        <v>0.08343064199581729</v>
       </c>
       <c r="I7" s="33" t="n">
-        <v>0.07984496360907012</v>
+        <v>0.0796511730489573</v>
       </c>
       <c r="J7" s="34" t="n">
         <v>3</v>
@@ -43431,25 +43431,25 @@
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>-0.004373809418090291</v>
+        <v>-0.004552371166540725</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>0.0007177627104955064</v>
+        <v>0.0005382878080617548</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>0.002606749802492869</v>
+        <v>0.002426936117450929</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>0.004050810986328424</v>
+        <v>0.003870738314437405</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>-0.05120786634982655</v>
+        <v>-0.05137802858933294</v>
       </c>
       <c r="I8" s="26" t="n">
-        <v>-0.05249745362803238</v>
+        <v>-0.05266738458499387</v>
       </c>
       <c r="J8" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" s="101" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>0.0178028147266085</v>
       </c>
       <c r="J10" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10" s="101" t="inlineStr">
         <is>
@@ -43545,22 +43545,22 @@
         </is>
       </c>
       <c r="D11" s="33" t="n">
-        <v>-0.01368327349095233</v>
+        <v>-0.0137693503970896</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>-0.007017826818954909</v>
+        <v>-0.00710448542568809</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>-0.005121496124307234</v>
+        <v>-0.005208320225830065</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>0.1026553580750613</v>
+        <v>0.1025591281732379</v>
       </c>
       <c r="H11" s="33" t="n">
-        <v>0.1385853014179184</v>
+        <v>0.1384859358718564</v>
       </c>
       <c r="I11" s="33" t="n">
-        <v>0.0462844591240601</v>
+        <v>0.04619314877033642</v>
       </c>
       <c r="J11" s="34" t="n">
         <v>3</v>
@@ -43583,22 +43583,22 @@
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>-0.006739178085651609</v>
+        <v>-0.006621011774235575</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>-0.01141446437262328</v>
+        <v>-0.01129685427093907</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>-0.01304042028354058</v>
+        <v>-0.01292300361867404</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>0.01131578722594861</v>
+        <v>0.0114361015015314</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>-0.02279863971899831</v>
+        <v>-0.02268238397055089</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0.08148817979127787</v>
+        <v>0.08161684234015376</v>
       </c>
       <c r="J12" s="27" t="n">
         <v>2</v>
@@ -43621,22 +43621,22 @@
         </is>
       </c>
       <c r="D13" s="33" t="n">
-        <v>-0.009343971712462262</v>
+        <v>-0.009534706580738517</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>-0.01404437052678953</v>
+        <v>-0.0142342004089524</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.0172152825748153</v>
+        <v>-0.0174045019489163</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>0.03983189981853474</v>
+        <v>0.03963169692794688</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>0.03920782193766015</v>
+        <v>0.03900773920322043</v>
       </c>
       <c r="I13" s="33" t="n">
-        <v>0.1455347852455748</v>
+        <v>0.1453142309662583</v>
       </c>
       <c r="J13" s="34" t="n">
         <v>3</v>
@@ -43659,22 +43659,22 @@
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>-0.0007967185788519959</v>
+        <v>-0.0006828768287838738</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.004874181582700698</v>
+        <v>-0.004760804388276862</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.0241218118166906</v>
+        <v>-0.02401062755332628</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-0.003066053265408653</v>
+        <v>-0.00295247006636512</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.02128899314268673</v>
+        <v>0.02140535117359632</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0.08785631022802143</v>
+        <v>0.08798025244126451</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>2</v>
@@ -43697,22 +43697,22 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-0.007745252725428697</v>
+        <v>-0.008006315977894363</v>
       </c>
       <c r="E15" s="33" t="n">
-        <v>-0.02204305494080361</v>
+        <v>-0.02230035642668704</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>-0.04872354361377162</v>
+        <v>-0.04897382543543116</v>
       </c>
       <c r="G15" s="33" t="n">
-        <v>-0.01187280313570171</v>
+        <v>-0.01213278042537624</v>
       </c>
       <c r="H15" s="33" t="n">
-        <v>-0.00497425353905645</v>
+        <v>-0.005236045844280168</v>
       </c>
       <c r="I15" s="33" t="n">
-        <v>-0.04513865550406393</v>
+        <v>-0.0453898805135009</v>
       </c>
       <c r="J15" s="34" t="n">
         <v>1</v>
@@ -43864,7 +43864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G61"/>
+  <dimension ref="B2:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -43996,7 +43996,7 @@
       </c>
       <c r="D8" s="106" t="inlineStr">
         <is>
-          <t>Reclaimed the 200 DMA</t>
+          <t>Volume 1.8x its 20-day average</t>
         </is>
       </c>
       <c r="E8" s="26" t="n">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="D9" s="107" t="inlineStr">
         <is>
-          <t>Gapped up 4.0% at the open</t>
+          <t>Reclaimed the 200 DMA</t>
         </is>
       </c>
       <c r="E9" s="33" t="n">
@@ -44042,21 +44042,21 @@
     <row r="10">
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="C10" s="101" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
-        </is>
-      </c>
-      <c r="D10" s="104" t="inlineStr">
-        <is>
-          <t>8 EMA crossed above 21</t>
+          <t>CoreWeave, Inc.</t>
+        </is>
+      </c>
+      <c r="D10" s="106" t="inlineStr">
+        <is>
+          <t>Gapped up 4.0% at the open</t>
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>0.09050102184507414</v>
+        <v>0.1171665303177076</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>9</v>
@@ -44078,9 +44078,9 @@
           <t>Intel Corporation</t>
         </is>
       </c>
-      <c r="D11" s="107" t="inlineStr">
-        <is>
-          <t>Reclaimed the 50 DMA</t>
+      <c r="D11" s="105" t="inlineStr">
+        <is>
+          <t>8 EMA crossed above 21</t>
         </is>
       </c>
       <c r="E11" s="33" t="n">
@@ -44108,7 +44108,7 @@
       </c>
       <c r="D12" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 5.3% at the open</t>
+          <t>Reclaimed the 50 DMA</t>
         </is>
       </c>
       <c r="E12" s="26" t="n">
@@ -44126,21 +44126,21 @@
     <row r="13">
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C13" s="102" t="inlineStr">
         <is>
-          <t>Nebius Group N.V.</t>
-        </is>
-      </c>
-      <c r="D13" s="105" t="inlineStr">
-        <is>
-          <t>MACD crossed up</t>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="D13" s="107" t="inlineStr">
+        <is>
+          <t>Gapped up 5.3% at the open</t>
         </is>
       </c>
       <c r="E13" s="33" t="n">
-        <v>0.07725608701937992</v>
+        <v>0.09050102184507414</v>
       </c>
       <c r="F13" s="34" t="n">
         <v>9</v>
@@ -44164,7 +44164,7 @@
       </c>
       <c r="D14" s="104" t="inlineStr">
         <is>
-          <t>8 EMA crossed above 21</t>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E14" s="26" t="n">
@@ -44190,9 +44190,9 @@
           <t>Nebius Group N.V.</t>
         </is>
       </c>
-      <c r="D15" s="107" t="inlineStr">
-        <is>
-          <t>Gapped up 3.7% at the open</t>
+      <c r="D15" s="105" t="inlineStr">
+        <is>
+          <t>8 EMA crossed above 21</t>
         </is>
       </c>
       <c r="E15" s="33" t="n">
@@ -44210,21 +44210,21 @@
     <row r="16">
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C16" s="101" t="inlineStr">
         <is>
-          <t>Nokia Oyj</t>
+          <t>Nebius Group N.V.</t>
         </is>
       </c>
       <c r="D16" s="106" t="inlineStr">
         <is>
-          <t>RSI crossed back above 50</t>
+          <t>Gapped up 3.7% at the open</t>
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>0.06281157838618334</v>
+        <v>0.07725608701937992</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>9</v>
@@ -44248,11 +44248,11 @@
       </c>
       <c r="D17" s="107" t="inlineStr">
         <is>
-          <t>Reclaimed the 50 DMA</t>
+          <t>RSI crossed back above 50</t>
         </is>
       </c>
       <c r="E17" s="33" t="n">
-        <v>0.06281157838618334</v>
+        <v>0.06181454656683427</v>
       </c>
       <c r="F17" s="34" t="n">
         <v>9</v>
@@ -44276,11 +44276,11 @@
       </c>
       <c r="D18" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 4.3% at the open</t>
+          <t>Reclaimed the 50 DMA</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>0.06281157838618334</v>
+        <v>0.06181454656683427</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>9</v>
@@ -44304,11 +44304,11 @@
       </c>
       <c r="D19" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped up 4.3% at the open</t>
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>0.06281157838618334</v>
+        <v>0.06181454656683427</v>
       </c>
       <c r="F19" s="34" t="n">
         <v>9</v>
@@ -44322,21 +44322,21 @@
     <row r="20">
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C20" s="101" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Nokia Oyj</t>
         </is>
       </c>
       <c r="D20" s="106" t="inlineStr">
         <is>
-          <t>RSI crossed back above 50</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0.05898608052877963</v>
+        <v>0.06181454656683427</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>9</v>
@@ -44360,7 +44360,7 @@
       </c>
       <c r="D21" s="107" t="inlineStr">
         <is>
-          <t>Reclaimed the 50 DMA</t>
+          <t>RSI crossed back above 50</t>
         </is>
       </c>
       <c r="E21" s="33" t="n">
@@ -44388,7 +44388,7 @@
       </c>
       <c r="D22" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 2.4% at the open</t>
+          <t>Reclaimed the 50 DMA</t>
         </is>
       </c>
       <c r="E22" s="26" t="n">
@@ -44406,21 +44406,21 @@
     <row r="23">
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C23" s="102" t="inlineStr">
         <is>
-          <t>IREN Limited</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="D23" s="107" t="inlineStr">
         <is>
-          <t>Reclaimed the 200 DMA</t>
+          <t>Gapped up 2.4% at the open</t>
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>0.05035810171512822</v>
+        <v>0.05898608052877963</v>
       </c>
       <c r="F23" s="34" t="n">
         <v>9</v>
@@ -44444,7 +44444,7 @@
       </c>
       <c r="D24" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 3.5% at the open</t>
+          <t>Reclaimed the 200 DMA</t>
         </is>
       </c>
       <c r="E24" s="26" t="n">
@@ -44462,21 +44462,21 @@
     <row r="25">
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C25" s="102" t="inlineStr">
         <is>
-          <t>QUALCOMM Incorporated</t>
-        </is>
-      </c>
-      <c r="D25" s="105" t="inlineStr">
-        <is>
-          <t>Closed above upper band</t>
+          <t>IREN Limited</t>
+        </is>
+      </c>
+      <c r="D25" s="107" t="inlineStr">
+        <is>
+          <t>Gapped up 3.5% at the open</t>
         </is>
       </c>
       <c r="E25" s="33" t="n">
-        <v>0.03170552726421061</v>
+        <v>0.05035810171512822</v>
       </c>
       <c r="F25" s="34" t="n">
         <v>9</v>
@@ -44498,9 +44498,9 @@
           <t>QUALCOMM Incorporated</t>
         </is>
       </c>
-      <c r="D26" s="106" t="inlineStr">
-        <is>
-          <t>Volume 2.5x its 20-day average</t>
+      <c r="D26" s="104" t="inlineStr">
+        <is>
+          <t>Closed above upper band</t>
         </is>
       </c>
       <c r="E26" s="26" t="n">
@@ -44528,7 +44528,7 @@
       </c>
       <c r="D27" s="107" t="inlineStr">
         <is>
-          <t>Reclaimed the 50 DMA</t>
+          <t>Volume 2.6x its 20-day average</t>
         </is>
       </c>
       <c r="E27" s="33" t="n">
@@ -44556,7 +44556,7 @@
       </c>
       <c r="D28" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 6.9% at the open</t>
+          <t>Reclaimed the 50 DMA</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
@@ -44574,21 +44574,21 @@
     <row r="29">
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="C29" s="102" t="inlineStr">
         <is>
-          <t>State Street Technology Select Sector SPDR ETF</t>
-        </is>
-      </c>
-      <c r="D29" s="105" t="inlineStr">
-        <is>
-          <t>MACD crossed up</t>
+          <t>QUALCOMM Incorporated</t>
+        </is>
+      </c>
+      <c r="D29" s="107" t="inlineStr">
+        <is>
+          <t>Gapped up 6.9% at the open</t>
         </is>
       </c>
       <c r="E29" s="33" t="n">
-        <v>0.003150343559036095</v>
+        <v>0.03170552726421061</v>
       </c>
       <c r="F29" s="34" t="n">
         <v>9</v>
@@ -44602,24 +44602,24 @@
     <row r="30">
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C30" s="101" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>State Street Energy Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D30" s="106" t="inlineStr">
         <is>
-          <t>RSI crossed back above 50</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>0.03744695378055884</v>
+        <v>0.01108334548129264</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
@@ -44630,24 +44630,24 @@
     <row r="31">
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C31" s="102" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
-        </is>
-      </c>
-      <c r="D31" s="107" t="inlineStr">
-        <is>
-          <t>Gapped up 3.7% at the open</t>
+          <t>State Street Technology Select Sector SPDR ETF</t>
+        </is>
+      </c>
+      <c r="D31" s="105" t="inlineStr">
+        <is>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E31" s="33" t="n">
-        <v>0.03744695378055884</v>
+        <v>0.003150343559036095</v>
       </c>
       <c r="F31" s="34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" s="30" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
       </c>
       <c r="D32" s="106" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>RSI crossed back above 50</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
@@ -44686,21 +44686,21 @@
     <row r="33">
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C33" s="102" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="D33" s="105" t="inlineStr">
-        <is>
-          <t>Closed above upper band</t>
+          <t>Arm Holdings plc</t>
+        </is>
+      </c>
+      <c r="D33" s="107" t="inlineStr">
+        <is>
+          <t>Gapped up 3.7% at the open</t>
         </is>
       </c>
       <c r="E33" s="33" t="n">
-        <v>0.01783869829554785</v>
+        <v>0.03744695378055884</v>
       </c>
       <c r="F33" s="34" t="n">
         <v>8</v>
@@ -44714,12 +44714,12 @@
     <row r="34">
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C34" s="101" t="inlineStr">
         <is>
-          <t>State Street Energy Select Sector SPDR ETF</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="D34" s="106" t="inlineStr">
@@ -44728,7 +44728,7 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>0.01100533652705571</v>
+        <v>0.03744695378055884</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>8</v>
@@ -44742,28 +44742,28 @@
     <row r="35">
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C35" s="102" t="inlineStr">
         <is>
-          <t>AST SpaceMobile, Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D35" s="105" t="inlineStr">
         <is>
-          <t>MACD crossed up</t>
+          <t>Closed above upper band</t>
         </is>
       </c>
       <c r="E35" s="33" t="n">
-        <v>0.06114590417781884</v>
+        <v>0.01858280223254472</v>
       </c>
       <c r="F35" s="34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G35" s="30" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Very Strong</t>
         </is>
       </c>
     </row>
@@ -44778,9 +44778,9 @@
           <t>AST SpaceMobile, Inc.</t>
         </is>
       </c>
-      <c r="D36" s="106" t="inlineStr">
-        <is>
-          <t>RSI crossed back above 50</t>
+      <c r="D36" s="104" t="inlineStr">
+        <is>
+          <t>MACD crossed up</t>
         </is>
       </c>
       <c r="E36" s="26" t="n">
@@ -44808,7 +44808,7 @@
       </c>
       <c r="D37" s="107" t="inlineStr">
         <is>
-          <t>Gapped up 1.6% at the open</t>
+          <t>RSI crossed back above 50</t>
         </is>
       </c>
       <c r="E37" s="33" t="n">
@@ -44826,21 +44826,21 @@
     <row r="38">
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="C38" s="101" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>AST SpaceMobile, Inc.</t>
         </is>
       </c>
       <c r="D38" s="106" t="inlineStr">
         <is>
-          <t>Reclaimed the 50 DMA</t>
+          <t>Gapped up 1.6% at the open</t>
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>0.03976507462663403</v>
+        <v>0.06114590417781884</v>
       </c>
       <c r="F38" s="27" t="n">
         <v>7</v>
@@ -44854,21 +44854,21 @@
     <row r="39">
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C39" s="102" t="inlineStr">
         <is>
-          <t>Cameco Corporation</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="D39" s="107" t="inlineStr">
         <is>
-          <t>Gapped up 1.7% at the open</t>
+          <t>Reclaimed the 50 DMA</t>
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>0.01211039553875048</v>
+        <v>0.03976507462663403</v>
       </c>
       <c r="F39" s="34" t="n">
         <v>7</v>
@@ -44892,11 +44892,11 @@
       </c>
       <c r="D40" s="106" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped up 1.7% at the open</t>
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>0.01211039553875048</v>
+        <v>0.0122096821820159</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>7</v>
@@ -44910,21 +44910,21 @@
     <row r="41">
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C41" s="102" t="inlineStr">
         <is>
-          <t>Sandisk Corporation</t>
+          <t>Cameco Corporation</t>
         </is>
       </c>
       <c r="D41" s="107" t="inlineStr">
         <is>
-          <t>Gapped up 1.7% at the open</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E41" s="33" t="n">
-        <v>-0.001155178026221226</v>
+        <v>0.0122096821820159</v>
       </c>
       <c r="F41" s="34" t="n">
         <v>7</v>
@@ -44948,7 +44948,7 @@
       </c>
       <c r="D42" s="106" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped up 1.7% at the open</t>
         </is>
       </c>
       <c r="E42" s="26" t="n">
@@ -44966,21 +44966,21 @@
     <row r="43">
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C43" s="102" t="inlineStr">
         <is>
-          <t>ARK Innovation ETF</t>
+          <t>Sandisk Corporation</t>
         </is>
       </c>
       <c r="D43" s="107" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>-0.001159805992870688</v>
+        <v>-0.001155178026221226</v>
       </c>
       <c r="F43" s="34" t="n">
         <v>7</v>
@@ -44994,21 +44994,21 @@
     <row r="44">
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>ARKK</t>
         </is>
       </c>
       <c r="C44" s="101" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>ARK Innovation ETF</t>
         </is>
       </c>
       <c r="D44" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 2.0% at the open</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>-0.01606352281495027</v>
+        <v>-0.001623746087524025</v>
       </c>
       <c r="F44" s="27" t="n">
         <v>7</v>
@@ -45032,7 +45032,7 @@
       </c>
       <c r="D45" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped up 2.0% at the open</t>
         </is>
       </c>
       <c r="E45" s="33" t="n">
@@ -45050,24 +45050,24 @@
     <row r="46">
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>SOXL</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C46" s="101" t="inlineStr">
         <is>
-          <t>Direxion Daily Semiconductor Bull 3X Shares</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D46" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 6.7% at the open</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E46" s="26" t="n">
-        <v>0.05192704664625403</v>
+        <v>-0.01606352281495027</v>
       </c>
       <c r="F46" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
@@ -45078,21 +45078,21 @@
     <row r="47">
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SOXL</t>
         </is>
       </c>
       <c r="C47" s="102" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
+          <t>Direxion Daily Semiconductor Bull 3X Shares</t>
         </is>
       </c>
       <c r="D47" s="107" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>Gapped up 6.7% at the open</t>
         </is>
       </c>
       <c r="E47" s="33" t="n">
-        <v>-0.0008345896889334625</v>
+        <v>0.05107433429498753</v>
       </c>
       <c r="F47" s="34" t="n">
         <v>6</v>
@@ -45106,21 +45106,21 @@
     <row r="48">
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C48" s="101" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Invesco QQQ Trust</t>
         </is>
       </c>
       <c r="D48" s="106" t="inlineStr">
         <is>
-          <t>Lost the 200 DMA</t>
+          <t>Bands squeezing — a big move often follows</t>
         </is>
       </c>
       <c r="E48" s="26" t="n">
-        <v>-0.04397758154823495</v>
+        <v>-0.0008345896889334625</v>
       </c>
       <c r="F48" s="27" t="n">
         <v>6</v>
@@ -45144,7 +45144,7 @@
       </c>
       <c r="D49" s="107" t="inlineStr">
         <is>
-          <t>Gapped down 3.6% at the open</t>
+          <t>Lost the 200 DMA</t>
         </is>
       </c>
       <c r="E49" s="33" t="n">
@@ -45162,40 +45162,40 @@
     <row r="50">
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C50" s="101" t="inlineStr">
         <is>
-          <t>Rocket Lab Corporation</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="D50" s="106" t="inlineStr">
         <is>
-          <t>Gapped up 1.6% at the open</t>
+          <t>Gapped down 3.6% at the open</t>
         </is>
       </c>
       <c r="E50" s="26" t="n">
-        <v>0.02505447489619406</v>
+        <v>-0.04397758154823495</v>
       </c>
       <c r="F50" s="27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C51" s="102" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
         </is>
       </c>
       <c r="D51" s="107" t="inlineStr">
@@ -45204,35 +45204,35 @@
         </is>
       </c>
       <c r="E51" s="33" t="n">
-        <v>0.0002087838857429691</v>
+        <v>-0.005492125910932955</v>
       </c>
       <c r="F51" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G51" s="30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="C52" s="101" t="inlineStr">
         <is>
-          <t>State Street Communication Services Select Sector SPDR ETF</t>
+          <t>Rocket Lab Corporation</t>
         </is>
       </c>
       <c r="D52" s="106" t="inlineStr">
         <is>
-          <t>MACD crossed down</t>
+          <t>Gapped up 1.6% at the open</t>
         </is>
       </c>
       <c r="E52" s="26" t="n">
-        <v>-0.004373809418090291</v>
+        <v>0.02505447489619406</v>
       </c>
       <c r="F52" s="27" t="n">
         <v>3</v>
@@ -45246,12 +45246,12 @@
     <row r="53">
       <c r="B53" s="31" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C53" s="102" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P 500 ETF Trust</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D53" s="107" t="inlineStr">
@@ -45260,7 +45260,7 @@
         </is>
       </c>
       <c r="E53" s="33" t="n">
-        <v>-0.005440219203215357</v>
+        <v>0.0002087838857429691</v>
       </c>
       <c r="F53" s="34" t="n">
         <v>3</v>
@@ -45288,7 +45288,7 @@
         </is>
       </c>
       <c r="E54" s="26" t="n">
-        <v>-0.009343971712462262</v>
+        <v>-0.009534706580738517</v>
       </c>
       <c r="F54" s="27" t="n">
         <v>3</v>
@@ -45316,7 +45316,7 @@
         </is>
       </c>
       <c r="E55" s="33" t="n">
-        <v>-0.01368327349095233</v>
+        <v>-0.0137693503970896</v>
       </c>
       <c r="F55" s="34" t="n">
         <v>3</v>
@@ -45372,7 +45372,7 @@
         </is>
       </c>
       <c r="E57" s="33" t="n">
-        <v>-0.02502183355201748</v>
+        <v>-0.02519680456298767</v>
       </c>
       <c r="F57" s="34" t="n">
         <v>3</v>
@@ -45400,7 +45400,7 @@
         </is>
       </c>
       <c r="E58" s="26" t="n">
-        <v>-0.02502183355201748</v>
+        <v>-0.02519680456298767</v>
       </c>
       <c r="F58" s="27" t="n">
         <v>3</v>
@@ -45442,21 +45442,21 @@
     <row r="60">
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C60" s="101" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="D60" s="106" t="inlineStr">
         <is>
-          <t>Bands squeezing — a big move often follows</t>
+          <t>MACD crossed down</t>
         </is>
       </c>
       <c r="E60" s="26" t="n">
-        <v>-0.005957249184734059</v>
+        <v>-0.004552371166540725</v>
       </c>
       <c r="F60" s="27" t="n">
         <v>2</v>
@@ -45470,37 +45470,93 @@
     <row r="61">
       <c r="B61" s="31" t="inlineStr">
         <is>
+          <t>XLC</t>
+        </is>
+      </c>
+      <c r="C61" s="102" t="inlineStr">
+        <is>
+          <t>State Street Communication Services Select Sector SPDR ETF</t>
+        </is>
+      </c>
+      <c r="D61" s="107" t="inlineStr">
+        <is>
+          <t>RSI dropped below 50</t>
+        </is>
+      </c>
+      <c r="E61" s="33" t="n">
+        <v>-0.004552371166540725</v>
+      </c>
+      <c r="F61" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="30" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C62" s="101" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="D62" s="106" t="inlineStr">
+        <is>
+          <t>Bands squeezing — a big move often follows</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="n">
+        <v>-0.005957249184734059</v>
+      </c>
+      <c r="F62" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="23" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="31" t="inlineStr">
+        <is>
           <t>XLY</t>
         </is>
       </c>
-      <c r="C61" s="102" t="inlineStr">
+      <c r="C63" s="102" t="inlineStr">
         <is>
           <t>State Street Consumer Discretionary Select Sector SPDR ETF</t>
         </is>
       </c>
-      <c r="D61" s="107" t="inlineStr">
+      <c r="D63" s="107" t="inlineStr">
         <is>
           <t>Closed below lower band</t>
         </is>
       </c>
-      <c r="E61" s="33" t="n">
-        <v>-0.007745252725428697</v>
-      </c>
-      <c r="F61" s="34" t="n">
+      <c r="E63" s="33" t="n">
+        <v>-0.008006315977894363</v>
+      </c>
+      <c r="F63" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="30" t="inlineStr">
+      <c r="G63" s="30" t="inlineStr">
         <is>
           <t>Very Weak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:G61"/>
+  <autoFilter ref="B5:G63"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E61">
+  <conditionalFormatting sqref="E6:E63">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 8 Sep 2026, 10:43 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 8 Sep 2026, 11:22 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 8 Sep 2026, 10:43 PM · Yahoo Finance data</t>
+          <t>Built 8 Sep 2026, 11:22 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -5811,17 +5811,17 @@
       </c>
       <c r="AX19" s="79" t="inlineStr">
         <is>
+          <t>S&amp;P 500, Dow End Lower As Middle East Tensions Spur Oil Rally Ahead Of Key Inflation Data — META, QCOM, BE,...</t>
+        </is>
+      </c>
+      <c r="AY19" s="79" t="inlineStr">
+        <is>
           <t>Wall Street Keeps Asking How Much Meta Will Spend. The Better Question Is at What Price to Buy</t>
         </is>
       </c>
-      <c r="AY19" s="79" t="inlineStr">
+      <c r="AZ19" s="79" t="inlineStr">
         <is>
           <t>QQQ vs QQQM: Same Index, Same Stocks, Different Fee – and the Math Says One Leaves You Thousands Richer</t>
-        </is>
-      </c>
-      <c r="AZ19" s="79" t="inlineStr">
-        <is>
-          <t>XYLD vs GPIX vs ISPY: We Compared 3 Ways to Sell Covered Calls on the S&amp;P 500, and the Highest Yield Is Not...</t>
         </is>
       </c>
     </row>
@@ -6960,17 +6960,17 @@
       </c>
       <c r="AX26" s="79" t="inlineStr">
         <is>
+          <t>Jim Cramer Says Amazon and Alphabet Are Cheap. Their Cash Flows Complicate the Case</t>
+        </is>
+      </c>
+      <c r="AY26" s="79" t="inlineStr">
+        <is>
           <t>AMD Jumps 6.7% While Amazon Opens a $60 Billion AI-Chip Door</t>
         </is>
       </c>
-      <c r="AY26" s="79" t="inlineStr">
+      <c r="AZ26" s="79" t="inlineStr">
         <is>
           <t>Spotting Winners: Amazon (NASDAQ:AMZN) And Online Retail Stocks In Q2</t>
-        </is>
-      </c>
-      <c r="AZ26" s="79" t="inlineStr">
-        <is>
-          <t>DAL Stock Drops: Jefferies Sees Possible Snag To In-Cabin Experience Owing To SPCX-VSAT Spectrum Fight</t>
         </is>
       </c>
     </row>
@@ -8276,17 +8276,17 @@
       </c>
       <c r="AX33" s="90" t="inlineStr">
         <is>
+          <t>Dell (DELL) Q2 2027 Earnings Call Transcript</t>
+        </is>
+      </c>
+      <c r="AY33" s="90" t="inlineStr">
+        <is>
           <t>Is Dell Making Money Where You Think It Is?</t>
         </is>
       </c>
-      <c r="AY33" s="90" t="inlineStr">
+      <c r="AZ33" s="90" t="inlineStr">
         <is>
           <t>Snowflake Expands in Cloud Analytics: Can It Challenge DELL &amp; ORCL?</t>
-        </is>
-      </c>
-      <c r="AZ33" s="90" t="inlineStr">
-        <is>
-          <t>The Enterprise AI Fight Has a New Challenger and It Is Not Who You Would Expect</t>
         </is>
       </c>
     </row>
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
+          <t>Jim Cramer Says Amazon and Alphabet Are Cheap. Their Cash Flows Complicate the Case</t>
+        </is>
+      </c>
+      <c r="AY34" s="79" t="inlineStr">
+        <is>
+          <t>Druckenmiller Exited Micron and Bought Alphabet. The AI Risks Moved With Him</t>
+        </is>
+      </c>
+      <c r="AZ34" s="79" t="inlineStr">
+        <is>
           <t>Google Warns EU Regulations Will Result In Lower Search Quality</t>
-        </is>
-      </c>
-      <c r="AY34" s="79" t="inlineStr">
-        <is>
-          <t>Bank of America Spots Reassuring Signal for Google Stock</t>
-        </is>
-      </c>
-      <c r="AZ34" s="79" t="inlineStr">
-        <is>
-          <t>Google, Blackstone Venture Faces Delays at Data-Center Sites</t>
         </is>
       </c>
     </row>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="AX37" s="90" t="inlineStr">
         <is>
+          <t>Microsoft’s ‘Useful Yield’ Test Raises the Stakes for NVIDIA’s AI Economics</t>
+        </is>
+      </c>
+      <c r="AY37" s="90" t="inlineStr">
+        <is>
           <t>Microsoft's OpenAI Partnership Draws Fresh Legal Fire</t>
         </is>
       </c>
-      <c r="AY37" s="90" t="inlineStr">
+      <c r="AZ37" s="90" t="inlineStr">
         <is>
           <t>Goldman's New AI Office Adds Just 1% to Its Engineering Army</t>
-        </is>
-      </c>
-      <c r="AZ37" s="90" t="inlineStr">
-        <is>
-          <t>Prop Industry Leader The5ers Brings Single Stock Futures via CME Feed</t>
         </is>
       </c>
     </row>
@@ -9221,12 +9221,12 @@
       </c>
       <c r="AY38" s="79" t="inlineStr">
         <is>
+          <t>Strategy just dropped $250 'Bitcoin' Jordans with one big catch</t>
+        </is>
+      </c>
+      <c r="AZ38" s="79" t="inlineStr">
+        <is>
           <t>Strategy doubles STRC buyback to $2 billion as Bitcoin treasury grows</t>
-        </is>
-      </c>
-      <c r="AZ38" s="79" t="inlineStr">
-        <is>
-          <t>Strategy CEO says 'never sell' was just a marketing slogan</t>
         </is>
       </c>
     </row>
@@ -9404,17 +9404,17 @@
       </c>
       <c r="AX39" s="90" t="inlineStr">
         <is>
+          <t>Druckenmiller Exited Micron and Bought Alphabet. The AI Risks Moved With Him</t>
+        </is>
+      </c>
+      <c r="AY39" s="90" t="inlineStr">
+        <is>
           <t>Micron (MU) Falls More Steeply Than Broader Market: What Investors Need to Know</t>
         </is>
       </c>
-      <c r="AY39" s="90" t="inlineStr">
+      <c r="AZ39" s="90" t="inlineStr">
         <is>
           <t>Micron and Sandisk Soar as Goldman Sees New Memory Stock Rally</t>
-        </is>
-      </c>
-      <c r="AZ39" s="90" t="inlineStr">
-        <is>
-          <t>Goldman Says the Worst May Be Over for Micron and SanDisk</t>
         </is>
       </c>
     </row>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
+          <t>Why Okta Stock Soared 22% in August and Why There's More Upside Ahead</t>
+        </is>
+      </c>
+      <c r="AY43" s="90" t="inlineStr">
+        <is>
           <t>Dow Jones Futures: Dow Skids But AMD, HPE Are New Buys; Apple iPhone Event Due</t>
         </is>
       </c>
-      <c r="AY43" s="90" t="inlineStr">
+      <c r="AZ43" s="90" t="inlineStr">
         <is>
           <t>Prop Industry Leader The5ers Brings Single Stock Futures via CME Feed</t>
-        </is>
-      </c>
-      <c r="AZ43" s="90" t="inlineStr">
-        <is>
-          <t>Nvidia Falls as Its Firmus Bet Lands OpenAI</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 8 Sep 2026, 10:43 PM · Yahoo Finance data</t>
+          <t>Built 8 Sep 2026, 11:22 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 8 Sep 2026, 10:43 PM · Yahoo Finance data</t>
+          <t>Built 8 Sep 2026, 11:22 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 8 Sep 2026, 10:43 PM · Yahoo Finance data</t>
+          <t>Built 8 Sep 2026, 11:22 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 8 Sep 2026, 10:43 PM · Yahoo Finance data</t>
+          <t>Built 8 Sep 2026, 11:22 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 9 Sep 2026, 10:35 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 9 Sep 2026, 11:12 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 9 Sep 2026, 10:35 PM · Yahoo Finance data</t>
+          <t>Built 9 Sep 2026, 11:12 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="AY24" s="79" t="inlineStr">
         <is>
-          <t>Dow Jones Futures: Oil Prices, Yields Hit Stocks, Apple Unfolds iPhone. Inflation Data Due.</t>
+          <t>S&amp;P 500, Dow, Nasdaq End Lower As Oil Crosses $101, Yields Pop Following Bessent’s Expanded Buyback Plan — ...</t>
         </is>
       </c>
       <c r="AZ24" s="79" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Dow, Nasdaq End Lower As Oil Crosses $101, Yields Pop Following Bessent’s Expanded Buyback Plan — ...</t>
+          <t>Apple Finds Advantages Across Fintech In Search Results</t>
         </is>
       </c>
     </row>
@@ -6772,17 +6772,17 @@
       </c>
       <c r="AX25" s="90" t="inlineStr">
         <is>
-          <t>Dow Jones Futures: Oil Prices, Yields Hit Stocks, Apple Unfolds iPhone. Inflation Data Due.</t>
+          <t>Could Advanced Micro Devices (AMD)’s Partnership With Cisco Systems (CSCO) Unlock a Massive Middle East AI ...</t>
         </is>
       </c>
       <c r="AY25" s="90" t="inlineStr">
         <is>
-          <t>Could Advanced Micro Devices (AMD)’s Partnership With Cisco Systems (CSCO) Unlock a Massive Middle East AI ...</t>
+          <t>AMD, IBD Stock Of The Day, Runs Past Early Buy Point As Chipmaker Returns To Favor</t>
         </is>
       </c>
       <c r="AZ25" s="90" t="inlineStr">
         <is>
-          <t>AMD, IBD Stock Of The Day, Runs Past Early Buy Point As Chipmaker Returns To Favor</t>
+          <t>HostColor Stocks AMD Ryzen 9 9950X Dedicated Servers in Tokyo</t>
         </is>
       </c>
     </row>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="AX30" s="79" t="inlineStr">
         <is>
+          <t>Broadcom Forecasts $230 Billion in AI Semiconductor Revenue in 2028. The Stock Could Reach $900 Per Share a...</t>
+        </is>
+      </c>
+      <c r="AY30" s="79" t="inlineStr">
+        <is>
           <t>Broadcom (AVGO) Q3 2026 Earnings Call Transcript</t>
         </is>
       </c>
-      <c r="AY30" s="79" t="inlineStr">
+      <c r="AZ30" s="79" t="inlineStr">
         <is>
           <t>What Investors Need To Understand About Broadcom, Credo and Snowflake Earnings</t>
-        </is>
-      </c>
-      <c r="AZ30" s="79" t="inlineStr">
-        <is>
-          <t>Broadcom Stock Jumps -- AI Revenue Set to Double Again</t>
         </is>
       </c>
     </row>
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AX34" s="79" t="inlineStr">
         <is>
+          <t>HIVE joins Google, Microsoft, and Amazon in new Canada data center pledge</t>
+        </is>
+      </c>
+      <c r="AY34" s="79" t="inlineStr">
+        <is>
           <t>Do Amazon and Alphabet's Combined $420 Billion in Capital Expenditures Make Sense?</t>
         </is>
       </c>
-      <c r="AY34" s="79" t="inlineStr">
+      <c r="AZ34" s="79" t="inlineStr">
         <is>
           <t>Google Commits €13B to Finland AI Infrastructure, Securing Its First Non-US Nuclear Deal</t>
-        </is>
-      </c>
-      <c r="AZ34" s="79" t="inlineStr">
-        <is>
-          <t>Should You Buy Alphabet Stock For The Chips It Now Sells?</t>
         </is>
       </c>
     </row>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="AX37" s="90" t="inlineStr">
         <is>
+          <t>HIVE joins Google, Microsoft, and Amazon in new Canada data center pledge</t>
+        </is>
+      </c>
+      <c r="AY37" s="90" t="inlineStr">
+        <is>
           <t>Can Microsoft Stock Keep Earning Like This?</t>
         </is>
       </c>
-      <c r="AY37" s="90" t="inlineStr">
+      <c r="AZ37" s="90" t="inlineStr">
         <is>
           <t>Microsoft CFO Touts AI Stack, Azure Efficiency and Agent Growth at Goldman Conference</t>
-        </is>
-      </c>
-      <c r="AZ37" s="90" t="inlineStr">
-        <is>
-          <t>ARPA-H Selects UpDoc to Lead Development of Autonomous Clinical AI System, in an Initiative Joined by Micro...</t>
         </is>
       </c>
     </row>
@@ -9216,17 +9216,17 @@
       </c>
       <c r="AX38" s="79" t="inlineStr">
         <is>
+          <t>Strive Added 1,375 Bitcoin While Strategy Added None. Their Preferred Shares Explain Why.</t>
+        </is>
+      </c>
+      <c r="AY38" s="79" t="inlineStr">
+        <is>
           <t>Strategy Put $176.3 Million Into Its Own Preferred Stock Instead of Bitcoin, With Its Last BTC Purchase Alr...</t>
         </is>
       </c>
-      <c r="AY38" s="79" t="inlineStr">
-        <is>
-          <t>Investors Heavily Search Strategy Inc (MSTR): Here is What You Need to Know</t>
-        </is>
-      </c>
       <c r="AZ38" s="79" t="inlineStr">
         <is>
-          <t>Strategy Launches $250 Bitcoin Air Jordans but Won’t Let You Pay in BTC</t>
+          <t>MicroStrategy Says It Has the One Thing JPMorgan Lacks</t>
         </is>
       </c>
     </row>
@@ -10344,17 +10344,17 @@
       </c>
       <c r="AX44" s="79" t="inlineStr">
         <is>
+          <t>Jim Cramer Compares Palantir (PLTR) to an NFL Wide Receiver</t>
+        </is>
+      </c>
+      <c r="AY44" s="79" t="inlineStr">
+        <is>
           <t>Meet the AI Software Stock That’s Crushing Palantir (Hint: It’s Significantly Cheaper)</t>
         </is>
       </c>
-      <c r="AY44" s="79" t="inlineStr">
+      <c r="AZ44" s="79" t="inlineStr">
         <is>
           <t>Palantir's CEO says a new partner will power data sovereignty</t>
-        </is>
-      </c>
-      <c r="AZ44" s="79" t="inlineStr">
-        <is>
-          <t>Palantir Changed The Number It Wants You To Judge It By</t>
         </is>
       </c>
     </row>
@@ -11096,17 +11096,17 @@
       </c>
       <c r="AX48" s="79" t="inlineStr">
         <is>
+          <t>Goldman Sachs sends stark message to Tesla investors</t>
+        </is>
+      </c>
+      <c r="AY48" s="79" t="inlineStr">
+        <is>
           <t>Could Tesla’s (TSLA) Cybercab Unlock a New Growth Driver?</t>
         </is>
       </c>
-      <c r="AY48" s="79" t="inlineStr">
+      <c r="AZ48" s="79" t="inlineStr">
         <is>
           <t>45 Tesla Cybercabs Are Now Roaming Austin. Here's What That Means for the Robotaxi Business Wall Street Has...</t>
-        </is>
-      </c>
-      <c r="AZ48" s="79" t="inlineStr">
-        <is>
-          <t>Entrepreneurs could hold the key to Tesla's Cybercab plans</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 9 Sep 2026, 10:35 PM · Yahoo Finance data</t>
+          <t>Built 9 Sep 2026, 11:12 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 9 Sep 2026, 10:35 PM · Yahoo Finance data</t>
+          <t>Built 9 Sep 2026, 11:12 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 9 Sep 2026, 10:35 PM · Yahoo Finance data</t>
+          <t>Built 9 Sep 2026, 11:12 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 9 Sep 2026, 10:35 PM · Yahoo Finance data</t>
+          <t>Built 9 Sep 2026, 11:12 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1299,7 +1299,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 10 Sep 2026, 10:37 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 10 Sep 2026, 11:08 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3104,7 +3104,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 10 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 10 Sep 2026, 11:08 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="AY19" s="79" t="inlineStr">
         <is>
+          <t>S&amp;P 500, Dow, Nasdaq End Lower As Surging Oil Raises Odds For A September Rate Hike — ORCL, ADBE, M, NVDA, ...</t>
+        </is>
+      </c>
+      <c r="AZ19" s="79" t="inlineStr">
+        <is>
           <t>Oracle Jumped 36% in a Day After Last September’s Earnings, but Traders Are Betting Against It Tonight</t>
-        </is>
-      </c>
-      <c r="AZ19" s="79" t="inlineStr">
-        <is>
-          <t>Nuclear Stocks Slide as Piper Sandler Splits the Sector: Oklo, NuScale Power and X-Energy All Drop 5%</t>
         </is>
       </c>
     </row>
@@ -9025,17 +9025,17 @@
       </c>
       <c r="AX37" s="90" t="inlineStr">
         <is>
+          <t>Remain Bullish on AI Beneficiaries Like Bloom Energy</t>
+        </is>
+      </c>
+      <c r="AY37" s="90" t="inlineStr">
+        <is>
           <t>Nvidia stock edges higher on Microsoft data center expansion report</t>
         </is>
       </c>
-      <c r="AY37" s="90" t="inlineStr">
+      <c r="AZ37" s="90" t="inlineStr">
         <is>
           <t>Sector Update: Tech Stocks Fall Late Afternoon</t>
-        </is>
-      </c>
-      <c r="AZ37" s="90" t="inlineStr">
-        <is>
-          <t>Microsoft's New School AI Rules Sacrifice Data to Preserve Access</t>
         </is>
       </c>
     </row>
@@ -10153,17 +10153,17 @@
       </c>
       <c r="AX43" s="90" t="inlineStr">
         <is>
+          <t>Nvidia Returned $26 Billion to Shareholders Last Quarter Alone. Here's What That Buys You as an Investor.</t>
+        </is>
+      </c>
+      <c r="AY43" s="90" t="inlineStr">
+        <is>
           <t>Jensen Huang explains why Nvidia will grow an astounding 70% next year</t>
         </is>
       </c>
-      <c r="AY43" s="90" t="inlineStr">
+      <c r="AZ43" s="90" t="inlineStr">
         <is>
           <t>Jensen Huang just answered Michael Burry's Nvidia bear case</t>
-        </is>
-      </c>
-      <c r="AZ43" s="90" t="inlineStr">
-        <is>
-          <t>Nvidia stock edges higher on Microsoft data center expansion report</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11640,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 10 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 10 Sep 2026, 11:08 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19576,7 +19576,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 10 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 10 Sep 2026, 11:08 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27512,7 +27512,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 10 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 10 Sep 2026, 11:08 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35448,7 +35448,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 10 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 10 Sep 2026, 11:08 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Built automatically 11 Sep 2026, 10:37 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
+          <t>Built automatically 11 Sep 2026, 11:14 PM · Yahoo Finance data · EMA 8/21 · DMA 50/100/200 · BB 20,2 · MACD 12/26/9</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -3107,7 +3107,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 11 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 11 Sep 2026, 11:14 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -6960,17 +6960,17 @@
       </c>
       <c r="AX26" s="79" t="inlineStr">
         <is>
+          <t>Palantir Co-Founder Peter Thiel's Hedge Fund Just Made a Big Bet on This AI Stock</t>
+        </is>
+      </c>
+      <c r="AY26" s="79" t="inlineStr">
+        <is>
           <t>Amazon Gains as S&amp;P Flags Its $100 Billion Debt Spree</t>
         </is>
       </c>
-      <c r="AY26" s="79" t="inlineStr">
+      <c r="AZ26" s="79" t="inlineStr">
         <is>
           <t>‘The Largest IPO Ever, Surpassing SpaceX’: Anthropic Is Up Next</t>
-        </is>
-      </c>
-      <c r="AZ26" s="79" t="inlineStr">
-        <is>
-          <t>OpenAI Rethinks Its Next Big Move</t>
         </is>
       </c>
     </row>
@@ -8088,17 +8088,17 @@
       </c>
       <c r="AX32" s="79" t="inlineStr">
         <is>
+          <t>Oracle Just Showed a Less Painful Way to Finance AI Clouds. That’s Awkward for CoreWeave</t>
+        </is>
+      </c>
+      <c r="AY32" s="79" t="inlineStr">
+        <is>
           <t>Oracle's AI Cloud Growth Lifts CoreWeave, Nebius and IREN</t>
         </is>
       </c>
-      <c r="AY32" s="79" t="inlineStr">
+      <c r="AZ32" s="79" t="inlineStr">
         <is>
           <t>CoreWeave Is My Top IPO Pick Right Now: Over 75% of Its Revenue Is Locked In Through Contracts</t>
-        </is>
-      </c>
-      <c r="AZ32" s="79" t="inlineStr">
-        <is>
-          <t>AMD, BE, CRWV In Focus: Situational Awareness Has Been Reportedly Buying Options Tied To These Stocks</t>
         </is>
       </c>
     </row>
@@ -9404,17 +9404,17 @@
       </c>
       <c r="AX39" s="90" t="inlineStr">
         <is>
+          <t>AI’s HBM Shortage Strengthens Micron’s Hand—and Pressures Nvidia’s GPU Economics</t>
+        </is>
+      </c>
+      <c r="AY39" s="90" t="inlineStr">
+        <is>
           <t>Applied Materials vs. Micron Technology: Which Technology Stock Is a Better Buy in 2026?</t>
         </is>
       </c>
-      <c r="AY39" s="90" t="inlineStr">
+      <c r="AZ39" s="90" t="inlineStr">
         <is>
           <t>Micron Takes Unexpected Step as Tensions Rise</t>
-        </is>
-      </c>
-      <c r="AZ39" s="90" t="inlineStr">
-        <is>
-          <t>Micron Stays Flat as 68-Month Bonuses Fail to End Strike Risk</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 11 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 11 Sep 2026, 11:14 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -19579,7 +19579,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 11 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 11 Sep 2026, 11:14 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -27515,7 +27515,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 11 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 11 Sep 2026, 11:14 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
@@ -35451,7 +35451,7 @@
     <row r="3">
       <c r="A3" s="43" t="inlineStr">
         <is>
-          <t>Built 11 Sep 2026, 10:37 PM · Yahoo Finance data</t>
+          <t>Built 11 Sep 2026, 11:14 PM · Yahoo Finance data</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
